--- a/input/ES/reg_employmentSelection.xlsx
+++ b/input/ES/reg_employmentSelection.xlsx
@@ -112,7 +112,7 @@
     <t>Dcpst_Partnered_L1</t>
   </si>
   <si>
-    <t>D_Children_L1</t>
+    <t>Dnc1_plus_L1</t>
   </si>
   <si>
     <t>Dhe_Fair</t>
@@ -384,76 +384,76 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>-1.5090670259752375</v>
+        <v>-1.5639821051047229</v>
       </c>
       <c r="C2">
-        <v>0.0009293715671375211</v>
+        <v>0.00078416851707491719</v>
       </c>
       <c r="D2">
-        <v>6.5939590218764928e-05</v>
+        <v>5.6510429966023098e-05</v>
       </c>
       <c r="E2">
-        <v>3.8964058081485925e-05</v>
+        <v>3.7635611863224171e-05</v>
       </c>
       <c r="F2">
-        <v>-3.6747856855345921e-07</v>
+        <v>-3.6283733161908621e-07</v>
       </c>
       <c r="G2">
-        <v>-8.2649467598979083e-05</v>
+        <v>-7.039577270400799e-05</v>
       </c>
       <c r="H2">
-        <v>0.00014546984069706937</v>
+        <v>6.5030443682439386e-05</v>
       </c>
       <c r="I2">
-        <v>1.4063014012856656e-06</v>
+        <v>1.2315124902761905e-06</v>
       </c>
       <c r="J2">
-        <v>-2.8928945045269539e-06</v>
+        <v>-1.3182613244439658e-06</v>
       </c>
       <c r="K2">
-        <v>2.7976290864514004e-05</v>
+        <v>2.1378629626480057e-05</v>
       </c>
       <c r="L2">
-        <v>-0.00032551784212786472</v>
+        <v>1.3131742014200829e-06</v>
       </c>
       <c r="M2">
-        <v>4.1338163344759515e-06</v>
+        <v>7.0215748909776632e-07</v>
       </c>
       <c r="N2">
-        <v>7.6788026095513063e-06</v>
+        <v>5.3289683635173845e-06</v>
       </c>
       <c r="O2">
-        <v>7.8073842175752648e-06</v>
+        <v>4.9740709114392471e-06</v>
       </c>
       <c r="P2">
-        <v>7.5573288102211253e-06</v>
+        <v>1.9876746229329357e-06</v>
       </c>
       <c r="Q2">
-        <v>4.2636101886433158e-06</v>
+        <v>2.8493485357173865e-06</v>
       </c>
       <c r="R2">
-        <v>5.575094918599639e-06</v>
+        <v>3.7886423362497602e-06</v>
       </c>
       <c r="S2">
-        <v>-1.4976374090251716e-06</v>
+        <v>6.4079993556668044e-07</v>
       </c>
       <c r="T2">
-        <v>7.5926666273633648e-06</v>
+        <v>5.7738368143280504e-06</v>
       </c>
       <c r="U2">
-        <v>5.7726603500998899e-06</v>
+        <v>6.4399516836442697e-06</v>
       </c>
       <c r="V2">
-        <v>6.0233655465737843e-07</v>
+        <v>-4.1962939247760638e-07</v>
       </c>
       <c r="W2">
-        <v>1.0357376828053962e-05</v>
+        <v>9.9562976616470948e-06</v>
       </c>
       <c r="X2">
-        <v>7.0355137455296531e-06</v>
+        <v>4.3000236693587114e-06</v>
       </c>
       <c r="Y2">
-        <v>-0.0010549303565369052</v>
+        <v>-0.000988449099072807</v>
       </c>
     </row>
     <row r="3">
@@ -461,76 +461,76 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>-2.1844827448042201</v>
+        <v>-2.211386952091174</v>
       </c>
       <c r="C3">
-        <v>6.5939590218764928e-05</v>
+        <v>5.6510429966023098e-05</v>
       </c>
       <c r="D3">
-        <v>0.00014204296070054702</v>
+        <v>0.00012475674006656997</v>
       </c>
       <c r="E3">
-        <v>3.7426069445123086e-06</v>
+        <v>3.017744319980551e-06</v>
       </c>
       <c r="F3">
-        <v>-3.6928959970728824e-08</v>
+        <v>-3.1029971572066036e-08</v>
       </c>
       <c r="G3">
-        <v>9.869928802659639e-06</v>
+        <v>5.1666718248454747e-06</v>
       </c>
       <c r="H3">
-        <v>-7.1111208068774362e-06</v>
+        <v>-2.2170649792781237e-06</v>
       </c>
       <c r="I3">
-        <v>-5.5831150859886049e-07</v>
+        <v>-3.4820038044586338e-07</v>
       </c>
       <c r="J3">
-        <v>-4.5753298564472916e-07</v>
+        <v>-3.9934781626548072e-07</v>
       </c>
       <c r="K3">
-        <v>-5.5584865270452876e-06</v>
+        <v>-3.5473730971942918e-06</v>
       </c>
       <c r="L3">
-        <v>7.7053693409763462e-06</v>
+        <v>-4.5310110640387007e-06</v>
       </c>
       <c r="M3">
-        <v>4.1652921443208112e-06</v>
+        <v>2.9258082990574438e-06</v>
       </c>
       <c r="N3">
-        <v>1.0034603960398511e-05</v>
+        <v>8.3163865729851295e-06</v>
       </c>
       <c r="O3">
-        <v>1.3329044110333632e-05</v>
+        <v>1.06937542840598e-05</v>
       </c>
       <c r="P3">
-        <v>1.6490280799426178e-05</v>
+        <v>1.2852034929053951e-05</v>
       </c>
       <c r="Q3">
-        <v>3.2379203620187892e-06</v>
+        <v>2.1422429351680539e-06</v>
       </c>
       <c r="R3">
-        <v>6.0245040494769332e-06</v>
+        <v>3.1392237086245195e-06</v>
       </c>
       <c r="S3">
-        <v>-2.0398014275715767e-06</v>
+        <v>-2.167488109638385e-06</v>
       </c>
       <c r="T3">
-        <v>2.5797321779958534e-06</v>
+        <v>1.7903095210014873e-06</v>
       </c>
       <c r="U3">
-        <v>-6.3772008551939256e-06</v>
+        <v>-6.2092317259988623e-06</v>
       </c>
       <c r="V3">
-        <v>-5.1722876145704883e-06</v>
+        <v>-4.7750209927426335e-06</v>
       </c>
       <c r="W3">
-        <v>6.449379893992628e-06</v>
+        <v>5.711084054726912e-06</v>
       </c>
       <c r="X3">
-        <v>1.1898052516156756e-05</v>
+        <v>9.0455988857617261e-06</v>
       </c>
       <c r="Y3">
-        <v>-0.00014452076130769679</v>
+        <v>-0.00011661033011537262</v>
       </c>
     </row>
     <row r="4">
@@ -538,76 +538,76 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>0.13647218693108973</v>
+        <v>0.16108450835381913</v>
       </c>
       <c r="C4">
-        <v>3.8964058081485925e-05</v>
+        <v>3.7635611863224171e-05</v>
       </c>
       <c r="D4">
-        <v>3.7426069445123086e-06</v>
+        <v>3.017744319980551e-06</v>
       </c>
       <c r="E4">
-        <v>1.2041441634318664e-05</v>
+        <v>1.1223192227731414e-05</v>
       </c>
       <c r="F4">
-        <v>-1.2469087893979793e-07</v>
+        <v>-1.1694061406071668e-07</v>
       </c>
       <c r="G4">
-        <v>3.2449595164339233e-05</v>
+        <v>3.3610049370447209e-05</v>
       </c>
       <c r="H4">
-        <v>1.6968785943824576e-05</v>
+        <v>3.3000727896372248e-05</v>
       </c>
       <c r="I4">
-        <v>-6.7691213419160087e-07</v>
+        <v>-7.1261346565590155e-07</v>
       </c>
       <c r="J4">
-        <v>-3.1021621967327237e-07</v>
+        <v>-6.4716647053636789e-07</v>
       </c>
       <c r="K4">
-        <v>-1.4545161526152748e-05</v>
+        <v>-8.5858951284043146e-06</v>
       </c>
       <c r="L4">
-        <v>4.6097793289385932e-05</v>
+        <v>-1.2849626124034959e-05</v>
       </c>
       <c r="M4">
-        <v>2.1742794418809269e-06</v>
+        <v>2.2092011821935227e-06</v>
       </c>
       <c r="N4">
-        <v>4.6444781233828095e-06</v>
+        <v>4.8071559307926343e-06</v>
       </c>
       <c r="O4">
-        <v>5.9720767372216962e-06</v>
+        <v>6.4945157506179902e-06</v>
       </c>
       <c r="P4">
-        <v>1.0198964825918879e-05</v>
+        <v>1.0515512924367032e-05</v>
       </c>
       <c r="Q4">
-        <v>7.2614108078310702e-07</v>
+        <v>1.4292546320355303e-06</v>
       </c>
       <c r="R4">
-        <v>5.7393906957967364e-08</v>
+        <v>1.1910413340624589e-06</v>
       </c>
       <c r="S4">
-        <v>1.0909093054176679e-07</v>
+        <v>4.8703722193004131e-07</v>
       </c>
       <c r="T4">
-        <v>8.570012247718916e-07</v>
+        <v>1.6663707198308055e-06</v>
       </c>
       <c r="U4">
-        <v>-3.8601954097936526e-08</v>
+        <v>3.2829403045377973e-07</v>
       </c>
       <c r="V4">
-        <v>-2.1091692782088654e-06</v>
+        <v>-1.5924073443884118e-06</v>
       </c>
       <c r="W4">
-        <v>4.239596629926488e-07</v>
+        <v>5.1319639636195038e-07</v>
       </c>
       <c r="X4">
-        <v>-4.8358358493944411e-07</v>
+        <v>3.5952893214442572e-07</v>
       </c>
       <c r="Y4">
-        <v>-0.0002714613930900531</v>
+        <v>-0.00025058045398493442</v>
       </c>
     </row>
     <row r="5">
@@ -615,76 +615,76 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>-0.0017092736789568205</v>
+        <v>-0.0019619241892195132</v>
       </c>
       <c r="C5">
-        <v>-3.6747856855345921e-07</v>
+        <v>-3.6283733161908621e-07</v>
       </c>
       <c r="D5">
-        <v>-3.6928959970728824e-08</v>
+        <v>-3.1029971572066036e-08</v>
       </c>
       <c r="E5">
-        <v>-1.2469087893979793e-07</v>
+        <v>-1.1694061406071668e-07</v>
       </c>
       <c r="F5">
-        <v>1.3658747726850149e-09</v>
+        <v>1.2838258062748602e-09</v>
       </c>
       <c r="G5">
-        <v>-8.4268201218108507e-08</v>
+        <v>-1.3819125315440107e-07</v>
       </c>
       <c r="H5">
-        <v>1.1015148704404287e-07</v>
+        <v>-1.2238019519191427e-07</v>
       </c>
       <c r="I5">
-        <v>1.1468194863817829e-09</v>
+        <v>2.5299765949039795e-09</v>
       </c>
       <c r="J5">
-        <v>-3.3357207361747394e-09</v>
+        <v>1.6560383094180782e-09</v>
       </c>
       <c r="K5">
-        <v>1.4307032349910165e-07</v>
+        <v>7.5035629993986244e-08</v>
       </c>
       <c r="L5">
-        <v>-5.4480093930321596e-07</v>
+        <v>1.5406217445556951e-07</v>
       </c>
       <c r="M5">
-        <v>-2.3604867355907627e-08</v>
+        <v>-2.499418773271056e-08</v>
       </c>
       <c r="N5">
-        <v>-4.7920189695280926e-08</v>
+        <v>-5.1140697227538733e-08</v>
       </c>
       <c r="O5">
-        <v>-5.3242234643711658e-08</v>
+        <v>-6.1787783522582937e-08</v>
       </c>
       <c r="P5">
-        <v>-8.3101626087108728e-08</v>
+        <v>-9.1527524773972747e-08</v>
       </c>
       <c r="Q5">
-        <v>-1.0031208201299662e-08</v>
+        <v>-1.800406641222405e-08</v>
       </c>
       <c r="R5">
-        <v>-4.9873484225541933e-09</v>
+        <v>-1.7016004741115924e-08</v>
       </c>
       <c r="S5">
-        <v>-6.5535565323370044e-10</v>
+        <v>-4.731693085333438e-09</v>
       </c>
       <c r="T5">
-        <v>-1.1251710434941407e-08</v>
+        <v>-2.0071084534453949e-08</v>
       </c>
       <c r="U5">
-        <v>3.4145696828080349e-09</v>
+        <v>-1.0096604103184873e-09</v>
       </c>
       <c r="V5">
-        <v>2.4040497405546126e-08</v>
+        <v>1.8423286454227841e-08</v>
       </c>
       <c r="W5">
-        <v>-6.8730687389085826e-09</v>
+        <v>-6.605817393049726e-09</v>
       </c>
       <c r="X5">
-        <v>1.7531733545419866e-09</v>
+        <v>-6.2584565743969258e-09</v>
       </c>
       <c r="Y5">
-        <v>2.6517524962267183e-06</v>
+        <v>2.468879685493119e-06</v>
       </c>
     </row>
     <row r="6">
@@ -692,76 +692,76 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>-0.49208265491103315</v>
+        <v>-0.41785121806622522</v>
       </c>
       <c r="C6">
-        <v>-8.2649467598979083e-05</v>
+        <v>-7.039577270400799e-05</v>
       </c>
       <c r="D6">
-        <v>9.869928802659639e-06</v>
+        <v>5.1666718248454747e-06</v>
       </c>
       <c r="E6">
-        <v>3.2449595164339233e-05</v>
+        <v>3.3610049370447209e-05</v>
       </c>
       <c r="F6">
-        <v>-8.4268201218108507e-08</v>
+        <v>-1.3819125315440107e-07</v>
       </c>
       <c r="G6">
-        <v>0.0027406658040213753</v>
+        <v>0.0024000527169121873</v>
       </c>
       <c r="H6">
-        <v>0.0011847725792919531</v>
+        <v>0.0010589709655374269</v>
       </c>
       <c r="I6">
-        <v>-5.7327128045770827e-05</v>
+        <v>-4.9910978295631958e-05</v>
       </c>
       <c r="J6">
-        <v>-2.5177852508779739e-05</v>
+        <v>-2.2347408961617136e-05</v>
       </c>
       <c r="K6">
-        <v>-2.3877242956462883e-05</v>
+        <v>-5.7516142519885521e-06</v>
       </c>
       <c r="L6">
-        <v>-0.00011092495913184315</v>
+        <v>-5.3936625776325893e-05</v>
       </c>
       <c r="M6">
-        <v>3.4651126689636989e-06</v>
+        <v>7.2504078839186843e-06</v>
       </c>
       <c r="N6">
-        <v>3.9735423690947288e-06</v>
+        <v>8.397672489878123e-06</v>
       </c>
       <c r="O6">
-        <v>3.9036656278633539e-06</v>
+        <v>1.1239893869760726e-05</v>
       </c>
       <c r="P6">
-        <v>2.9754531112494045e-05</v>
+        <v>3.2628129655894026e-05</v>
       </c>
       <c r="Q6">
-        <v>2.8620203262038928e-06</v>
+        <v>4.445423449641639e-06</v>
       </c>
       <c r="R6">
-        <v>-1.0267717028836291e-07</v>
+        <v>1.5113902613509924e-06</v>
       </c>
       <c r="S6">
-        <v>-5.1497703129434517e-06</v>
+        <v>-1.9115657197659095e-06</v>
       </c>
       <c r="T6">
-        <v>-1.1543054323875125e-05</v>
+        <v>-5.6664484676520657e-06</v>
       </c>
       <c r="U6">
-        <v>-1.700380279706316e-05</v>
+        <v>-1.1448503958290276e-05</v>
       </c>
       <c r="V6">
-        <v>-1.522079164008946e-05</v>
+        <v>-1.0149676103076937e-05</v>
       </c>
       <c r="W6">
-        <v>8.6955938711988e-06</v>
+        <v>6.7976865026077628e-06</v>
       </c>
       <c r="X6">
-        <v>8.379934847303358e-06</v>
+        <v>6.1670635498055813e-06</v>
       </c>
       <c r="Y6">
-        <v>-0.0013105522706281948</v>
+        <v>-0.0012440409183924889</v>
       </c>
     </row>
     <row r="7">
@@ -769,76 +769,76 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-0.46536382102111468</v>
+        <v>-0.56218065557254982</v>
       </c>
       <c r="C7">
-        <v>0.00014546984069706937</v>
+        <v>6.5030443682439386e-05</v>
       </c>
       <c r="D7">
-        <v>-7.1111208068774362e-06</v>
+        <v>-2.2170649792781237e-06</v>
       </c>
       <c r="E7">
-        <v>1.6968785943824576e-05</v>
+        <v>3.3000727896372248e-05</v>
       </c>
       <c r="F7">
-        <v>1.1015148704404287e-07</v>
+        <v>-1.2238019519191427e-07</v>
       </c>
       <c r="G7">
-        <v>0.0011847725792919531</v>
+        <v>0.0010589709655374269</v>
       </c>
       <c r="H7">
-        <v>0.0025549319742349647</v>
+        <v>0.0021822171272897709</v>
       </c>
       <c r="I7">
-        <v>-2.5353589372427201e-05</v>
+        <v>-2.2490125244901001e-05</v>
       </c>
       <c r="J7">
-        <v>-5.1657051188189589e-05</v>
+        <v>-4.4131453235267739e-05</v>
       </c>
       <c r="K7">
-        <v>-1.4611121202416772e-05</v>
+        <v>1.2559438219915094e-05</v>
       </c>
       <c r="L7">
-        <v>-0.00082336219691097723</v>
+        <v>-0.00010929767442597621</v>
       </c>
       <c r="M7">
-        <v>9.1695621981783713e-06</v>
+        <v>1.213231572676465e-05</v>
       </c>
       <c r="N7">
-        <v>1.1024378804380761e-06</v>
+        <v>1.0834434063884267e-05</v>
       </c>
       <c r="O7">
-        <v>-6.7846411801802064e-06</v>
+        <v>9.6105601958717439e-06</v>
       </c>
       <c r="P7">
-        <v>3.1322992523865581e-05</v>
+        <v>3.8898908288649526e-05</v>
       </c>
       <c r="Q7">
-        <v>4.2939548835341625e-06</v>
+        <v>7.9633759505789005e-06</v>
       </c>
       <c r="R7">
-        <v>-1.1069092011884696e-05</v>
+        <v>-5.5233640045138422e-06</v>
       </c>
       <c r="S7">
-        <v>-2.902826063173506e-05</v>
+        <v>-1.7014921598287376e-05</v>
       </c>
       <c r="T7">
-        <v>-2.3206953553328635e-05</v>
+        <v>-1.3287409139150585e-05</v>
       </c>
       <c r="U7">
-        <v>-5.5925882771811329e-05</v>
+        <v>-3.5950549136931192e-05</v>
       </c>
       <c r="V7">
-        <v>-2.8529712476297917e-05</v>
+        <v>-1.9387934875485656e-05</v>
       </c>
       <c r="W7">
-        <v>1.5581745572557169e-05</v>
+        <v>1.5502196411901637e-05</v>
       </c>
       <c r="X7">
-        <v>1.6524604911675522e-05</v>
+        <v>1.5542241449421002e-05</v>
       </c>
       <c r="Y7">
-        <v>-0.0010286658564525621</v>
+        <v>-0.0012388207517911992</v>
       </c>
     </row>
     <row r="8">
@@ -846,76 +846,76 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.0081780660329256252</v>
+        <v>0.005073429261713152</v>
       </c>
       <c r="C8">
-        <v>1.4063014012856656e-06</v>
+        <v>1.2315124902761905e-06</v>
       </c>
       <c r="D8">
-        <v>-5.5831150859886049e-07</v>
+        <v>-3.4820038044586338e-07</v>
       </c>
       <c r="E8">
-        <v>-6.7691213419160087e-07</v>
+        <v>-7.1261346565590155e-07</v>
       </c>
       <c r="F8">
-        <v>1.1468194863817829e-09</v>
+        <v>2.5299765949039795e-09</v>
       </c>
       <c r="G8">
-        <v>-5.7327128045770827e-05</v>
+        <v>-4.9910978295631958e-05</v>
       </c>
       <c r="H8">
-        <v>-2.5353589372427201e-05</v>
+        <v>-2.2490125244901001e-05</v>
       </c>
       <c r="I8">
-        <v>1.3023850692425051e-06</v>
+        <v>1.1265527512108246e-06</v>
       </c>
       <c r="J8">
-        <v>5.8332498396481159e-07</v>
+        <v>5.1285198580812575e-07</v>
       </c>
       <c r="K8">
-        <v>4.636455775020252e-07</v>
+        <v>6.3907408000988397e-08</v>
       </c>
       <c r="L8">
-        <v>2.4606077090752738e-06</v>
+        <v>1.2225484190903565e-06</v>
       </c>
       <c r="M8">
-        <v>-2.6253920270744545e-08</v>
+        <v>-1.2074615915184401e-07</v>
       </c>
       <c r="N8">
-        <v>-3.2402927123500821e-08</v>
+        <v>-1.195793569453512e-07</v>
       </c>
       <c r="O8">
-        <v>1.9240449379248079e-07</v>
+        <v>-4.2281365264753337e-09</v>
       </c>
       <c r="P8">
-        <v>-1.7569416165642021e-07</v>
+        <v>-3.1814625114640597e-07</v>
       </c>
       <c r="Q8">
-        <v>5.7718601815146839e-08</v>
+        <v>-1.7877272226906577e-09</v>
       </c>
       <c r="R8">
-        <v>1.0356089281036475e-07</v>
+        <v>1.6470714984843657e-08</v>
       </c>
       <c r="S8">
-        <v>1.1168479755137243e-07</v>
+        <v>3.2785114306925699e-08</v>
       </c>
       <c r="T8">
-        <v>1.7111120631175475e-07</v>
+        <v>3.6338635616813778e-08</v>
       </c>
       <c r="U8">
-        <v>3.0278273217855394e-07</v>
+        <v>1.784541399021381e-07</v>
       </c>
       <c r="V8">
-        <v>2.5497860948027182e-07</v>
+        <v>1.5115619323630546e-07</v>
       </c>
       <c r="W8">
-        <v>-1.0280251246839305e-07</v>
+        <v>-8.0470731857337259e-08</v>
       </c>
       <c r="X8">
-        <v>-5.2568120058640001e-08</v>
+        <v>-5.4897924928440445e-08</v>
       </c>
       <c r="Y8">
-        <v>2.6685349817706093e-05</v>
+        <v>2.5491124340933407e-05</v>
       </c>
     </row>
     <row r="9">
@@ -923,76 +923,76 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>0.0034527525758931412</v>
+        <v>0.0034851226663128172</v>
       </c>
       <c r="C9">
-        <v>-2.8928945045269539e-06</v>
+        <v>-1.3182613244439658e-06</v>
       </c>
       <c r="D9">
-        <v>-4.5753298564472916e-07</v>
+        <v>-3.9934781626548072e-07</v>
       </c>
       <c r="E9">
-        <v>-3.1021621967327237e-07</v>
+        <v>-6.4716647053636789e-07</v>
       </c>
       <c r="F9">
-        <v>-3.3357207361747394e-09</v>
+        <v>1.6560383094180782e-09</v>
       </c>
       <c r="G9">
-        <v>-2.5177852508779739e-05</v>
+        <v>-2.2347408961617136e-05</v>
       </c>
       <c r="H9">
-        <v>-5.1657051188189589e-05</v>
+        <v>-4.4131453235267739e-05</v>
       </c>
       <c r="I9">
-        <v>5.8332498396481159e-07</v>
+        <v>5.1285198580812575e-07</v>
       </c>
       <c r="J9">
-        <v>1.1275439917184828e-06</v>
+        <v>9.6431705659565206e-07</v>
       </c>
       <c r="K9">
-        <v>1.2998879535794256e-07</v>
+        <v>-4.4040107225794681e-07</v>
       </c>
       <c r="L9">
-        <v>1.5869858793830436e-05</v>
+        <v>2.3358430651709334e-06</v>
       </c>
       <c r="M9">
-        <v>-2.3012902127943347e-07</v>
+        <v>-3.1838925744568299e-07</v>
       </c>
       <c r="N9">
-        <v>2.5283880043404898e-08</v>
+        <v>-2.2587083220543757e-07</v>
       </c>
       <c r="O9">
-        <v>6.4985493886801833e-07</v>
+        <v>1.7742873602856898e-07</v>
       </c>
       <c r="P9">
-        <v>1.2444968043174353e-07</v>
+        <v>-2.3193825979991529e-07</v>
       </c>
       <c r="Q9">
-        <v>8.3425119060992701e-08</v>
+        <v>-2.5994502078208996e-08</v>
       </c>
       <c r="R9">
-        <v>5.6141453734698148e-07</v>
+        <v>3.6804642476238213e-07</v>
       </c>
       <c r="S9">
-        <v>3.6555775350960959e-07</v>
+        <v>1.4522606577529837e-07</v>
       </c>
       <c r="T9">
-        <v>4.5347012479434286e-07</v>
+        <v>2.406435429129941e-07</v>
       </c>
       <c r="U9">
-        <v>7.974185894975233e-07</v>
+        <v>4.2919121904164667e-07</v>
       </c>
       <c r="V9">
-        <v>4.3578735223408231e-07</v>
+        <v>2.6854037537018175e-07</v>
       </c>
       <c r="W9">
-        <v>-1.5285424393132197e-07</v>
+        <v>-2.0894545913527595e-07</v>
       </c>
       <c r="X9">
-        <v>-3.9044512839800034e-08</v>
+        <v>-1.2396507342169301e-07</v>
       </c>
       <c r="Y9">
-        <v>1.9701823854459415e-05</v>
+        <v>2.4221675374156273e-05</v>
       </c>
     </row>
     <row r="10">
@@ -1000,76 +1000,76 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>-0.084203674159357533</v>
+        <v>-0.047879868588837291</v>
       </c>
       <c r="C10">
-        <v>2.7976290864514004e-05</v>
+        <v>2.1378629626480057e-05</v>
       </c>
       <c r="D10">
-        <v>-5.5584865270452876e-06</v>
+        <v>-3.5473730971942918e-06</v>
       </c>
       <c r="E10">
-        <v>-1.4545161526152748e-05</v>
+        <v>-8.5858951284043146e-06</v>
       </c>
       <c r="F10">
-        <v>1.4307032349910165e-07</v>
+        <v>7.5035629993986244e-08</v>
       </c>
       <c r="G10">
-        <v>-2.3877242956462883e-05</v>
+        <v>-5.7516142519885521e-06</v>
       </c>
       <c r="H10">
-        <v>-1.4611121202416772e-05</v>
+        <v>1.2559438219915094e-05</v>
       </c>
       <c r="I10">
-        <v>4.636455775020252e-07</v>
+        <v>6.3907408000988397e-08</v>
       </c>
       <c r="J10">
-        <v>1.2998879535794256e-07</v>
+        <v>-4.4040107225794681e-07</v>
       </c>
       <c r="K10">
-        <v>0.00017177482479434065</v>
+        <v>0.00016652515357767087</v>
       </c>
       <c r="L10">
-        <v>-2.9636703580534476e-05</v>
+        <v>-5.1532009367745993e-05</v>
       </c>
       <c r="M10">
-        <v>-9.0753645074032009e-06</v>
+        <v>-6.5288587245640478e-06</v>
       </c>
       <c r="N10">
-        <v>-2.1792949305867839e-05</v>
+        <v>-1.5842017212085519e-05</v>
       </c>
       <c r="O10">
-        <v>-3.2235304277782257e-05</v>
+        <v>-2.364816035365556e-05</v>
       </c>
       <c r="P10">
-        <v>-3.1327524633515145e-05</v>
+        <v>-2.2938093223347163e-05</v>
       </c>
       <c r="Q10">
-        <v>-5.9580706376392294e-06</v>
+        <v>-2.7587541248345288e-06</v>
       </c>
       <c r="R10">
-        <v>1.3416188361933879e-06</v>
+        <v>2.9565684692139051e-06</v>
       </c>
       <c r="S10">
-        <v>-5.2425375587558747e-06</v>
+        <v>-3.3105430912645903e-06</v>
       </c>
       <c r="T10">
-        <v>-5.1141406128629676e-06</v>
+        <v>-2.5221500356785842e-06</v>
       </c>
       <c r="U10">
-        <v>-2.3615602021981738e-06</v>
+        <v>3.3716769143997658e-08</v>
       </c>
       <c r="V10">
-        <v>1.3846801038372074e-05</v>
+        <v>1.1505396567742331e-05</v>
       </c>
       <c r="W10">
-        <v>-1.3345004104120418e-06</v>
+        <v>-8.8210213924130594e-07</v>
       </c>
       <c r="X10">
-        <v>-6.8615739832329165e-07</v>
+        <v>4.0556182386317124e-07</v>
       </c>
       <c r="Y10">
-        <v>0.00026755006816287787</v>
+        <v>0.00016157160861471681</v>
       </c>
     </row>
     <row r="11">
@@ -1077,76 +1077,76 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>-0.77192596621563891</v>
+        <v>-0.11382159883560995</v>
       </c>
       <c r="C11">
-        <v>-0.00032551784212786472</v>
+        <v>1.3131742014200829e-06</v>
       </c>
       <c r="D11">
-        <v>7.7053693409763462e-06</v>
+        <v>-4.5310110640387007e-06</v>
       </c>
       <c r="E11">
-        <v>4.6097793289385932e-05</v>
+        <v>-1.2849626124034959e-05</v>
       </c>
       <c r="F11">
-        <v>-5.4480093930321596e-07</v>
+        <v>1.5406217445556951e-07</v>
       </c>
       <c r="G11">
-        <v>-0.00011092495913184315</v>
+        <v>-5.3936625776325893e-05</v>
       </c>
       <c r="H11">
-        <v>-0.00082336219691097723</v>
+        <v>-0.00010929767442597621</v>
       </c>
       <c r="I11">
-        <v>2.4606077090752738e-06</v>
+        <v>1.2225484190903565e-06</v>
       </c>
       <c r="J11">
-        <v>1.5869858793830436e-05</v>
+        <v>2.3358430651709334e-06</v>
       </c>
       <c r="K11">
-        <v>-2.9636703580534476e-05</v>
+        <v>-5.1532009367745993e-05</v>
       </c>
       <c r="L11">
-        <v>0.0057540055331795365</v>
+        <v>0.00017559153000910627</v>
       </c>
       <c r="M11">
-        <v>3.8612528387516943e-06</v>
+        <v>-5.0293050855584149e-06</v>
       </c>
       <c r="N11">
-        <v>1.3955470321749656e-05</v>
+        <v>-1.0765851420839752e-05</v>
       </c>
       <c r="O11">
-        <v>1.7397590282903228e-05</v>
+        <v>-1.6521843496977614e-05</v>
       </c>
       <c r="P11">
-        <v>4.4750517046325869e-06</v>
+        <v>-1.8568543181393855e-05</v>
       </c>
       <c r="Q11">
-        <v>-4.1510337420614264e-06</v>
+        <v>-7.2214097515647985e-06</v>
       </c>
       <c r="R11">
-        <v>4.2027737865672014e-06</v>
+        <v>-7.3758746655500656e-06</v>
       </c>
       <c r="S11">
-        <v>1.6923700458096433e-05</v>
+        <v>-4.312334110483636e-06</v>
       </c>
       <c r="T11">
-        <v>4.0933953295506993e-06</v>
+        <v>-7.1298840373377753e-06</v>
       </c>
       <c r="U11">
-        <v>3.2814391434223279e-05</v>
+        <v>-6.2404596342951593e-06</v>
       </c>
       <c r="V11">
-        <v>1.6026598790000384e-05</v>
+        <v>-2.7339106883459257e-07</v>
       </c>
       <c r="W11">
-        <v>-7.2863947464846939e-06</v>
+        <v>-2.0963572648921408e-06</v>
       </c>
       <c r="X11">
-        <v>-2.9528375826878163e-05</v>
+        <v>-5.0720331981070855e-06</v>
       </c>
       <c r="Y11">
-        <v>-0.00088185876998194172</v>
+        <v>0.00022785976442534005</v>
       </c>
     </row>
     <row r="12">
@@ -1154,76 +1154,76 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>0.24633238664013499</v>
+        <v>0.25102880918005366</v>
       </c>
       <c r="C12">
-        <v>4.1338163344759515e-06</v>
+        <v>7.0215748909776632e-07</v>
       </c>
       <c r="D12">
-        <v>4.1652921443208112e-06</v>
+        <v>2.9258082990574438e-06</v>
       </c>
       <c r="E12">
-        <v>2.1742794418809269e-06</v>
+        <v>2.2092011821935227e-06</v>
       </c>
       <c r="F12">
-        <v>-2.3604867355907627e-08</v>
+        <v>-2.499418773271056e-08</v>
       </c>
       <c r="G12">
-        <v>3.4651126689636989e-06</v>
+        <v>7.2504078839186843e-06</v>
       </c>
       <c r="H12">
-        <v>9.1695621981783713e-06</v>
+        <v>1.213231572676465e-05</v>
       </c>
       <c r="I12">
-        <v>-2.6253920270744545e-08</v>
+        <v>-1.2074615915184401e-07</v>
       </c>
       <c r="J12">
-        <v>-2.3012902127943347e-07</v>
+        <v>-3.1838925744568299e-07</v>
       </c>
       <c r="K12">
-        <v>-9.0753645074032009e-06</v>
+        <v>-6.5288587245640478e-06</v>
       </c>
       <c r="L12">
-        <v>3.8612528387516943e-06</v>
+        <v>-5.0293050855584149e-06</v>
       </c>
       <c r="M12">
-        <v>0.0052078460204913486</v>
+        <v>0.0043513499012550767</v>
       </c>
       <c r="N12">
-        <v>0.0043007060841178772</v>
+        <v>0.0035703204687164009</v>
       </c>
       <c r="O12">
-        <v>0.0043000530682319642</v>
+        <v>0.0035693703197701211</v>
       </c>
       <c r="P12">
-        <v>0.004299143650955994</v>
+        <v>0.0035680951857395928</v>
       </c>
       <c r="Q12">
-        <v>4.536155307830573e-06</v>
+        <v>7.244894926365883e-06</v>
       </c>
       <c r="R12">
-        <v>1.2774472026211097e-05</v>
+        <v>1.2911383648716147e-05</v>
       </c>
       <c r="S12">
-        <v>1.7062806309530191e-06</v>
+        <v>4.5776914590981024e-06</v>
       </c>
       <c r="T12">
-        <v>7.8058066934647512e-06</v>
+        <v>9.7991299640515841e-06</v>
       </c>
       <c r="U12">
-        <v>2.0303412738913006e-06</v>
+        <v>2.6405051996475392e-06</v>
       </c>
       <c r="V12">
-        <v>9.6240102269608946e-06</v>
+        <v>1.0781726965084075e-05</v>
       </c>
       <c r="W12">
-        <v>-2.1881698121816384e-06</v>
+        <v>-2.659226834504982e-06</v>
       </c>
       <c r="X12">
-        <v>4.3516053563866506e-06</v>
+        <v>2.8522856670761173e-06</v>
       </c>
       <c r="Y12">
-        <v>-0.0043468763354454132</v>
+        <v>-0.0036145091879106</v>
       </c>
     </row>
     <row r="13">
@@ -1231,76 +1231,76 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>0.50923638874010424</v>
+        <v>0.520951020332732</v>
       </c>
       <c r="C13">
-        <v>7.6788026095513063e-06</v>
+        <v>5.3289683635173845e-06</v>
       </c>
       <c r="D13">
-        <v>1.0034603960398511e-05</v>
+        <v>8.3163865729851295e-06</v>
       </c>
       <c r="E13">
-        <v>4.6444781233828095e-06</v>
+        <v>4.8071559307926343e-06</v>
       </c>
       <c r="F13">
-        <v>-4.7920189695280926e-08</v>
+        <v>-5.1140697227538733e-08</v>
       </c>
       <c r="G13">
-        <v>3.9735423690947288e-06</v>
+        <v>8.397672489878123e-06</v>
       </c>
       <c r="H13">
-        <v>1.1024378804380761e-06</v>
+        <v>1.0834434063884267e-05</v>
       </c>
       <c r="I13">
-        <v>-3.2402927123500821e-08</v>
+        <v>-1.195793569453512e-07</v>
       </c>
       <c r="J13">
-        <v>2.5283880043404898e-08</v>
+        <v>-2.2587083220543757e-07</v>
       </c>
       <c r="K13">
-        <v>-2.1792949305867839e-05</v>
+        <v>-1.5842017212085519e-05</v>
       </c>
       <c r="L13">
-        <v>1.3955470321749656e-05</v>
+        <v>-1.0765851420839752e-05</v>
       </c>
       <c r="M13">
-        <v>0.0043007060841178772</v>
+        <v>0.0035703204687164009</v>
       </c>
       <c r="N13">
-        <v>0.0044757530923939734</v>
+        <v>0.0037206624654834916</v>
       </c>
       <c r="O13">
-        <v>0.0043059613841144005</v>
+        <v>0.0035747873517132777</v>
       </c>
       <c r="P13">
-        <v>0.0043075386652724193</v>
+        <v>0.0035760122346091888</v>
       </c>
       <c r="Q13">
-        <v>-1.6781364933534645e-06</v>
+        <v>1.8399964780818195e-06</v>
       </c>
       <c r="R13">
-        <v>4.2312743863822614e-06</v>
+        <v>5.6532644853852615e-06</v>
       </c>
       <c r="S13">
-        <v>-7.4026137389406044e-06</v>
+        <v>-2.6796835551761859e-06</v>
       </c>
       <c r="T13">
-        <v>4.9934415580902061e-06</v>
+        <v>6.9866038140402347e-06</v>
       </c>
       <c r="U13">
-        <v>-6.510458729558588e-06</v>
+        <v>-4.7112244350561817e-06</v>
       </c>
       <c r="V13">
-        <v>-5.4920975788681298e-06</v>
+        <v>-8.029157398520406e-07</v>
       </c>
       <c r="W13">
-        <v>-7.1226765481819864e-06</v>
+        <v>-6.8262886919653498e-06</v>
       </c>
       <c r="X13">
-        <v>3.2200834082005357e-06</v>
+        <v>2.2617914458459829e-06</v>
       </c>
       <c r="Y13">
-        <v>-0.0044000963654414939</v>
+        <v>-0.0036696532994213793</v>
       </c>
     </row>
     <row r="14">
@@ -1308,76 +1308,76 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0.65043610121229956</v>
+        <v>0.67871006496297759</v>
       </c>
       <c r="C14">
-        <v>7.8073842175752648e-06</v>
+        <v>4.9740709114392471e-06</v>
       </c>
       <c r="D14">
-        <v>1.3329044110333632e-05</v>
+        <v>1.06937542840598e-05</v>
       </c>
       <c r="E14">
-        <v>5.9720767372216962e-06</v>
+        <v>6.4945157506179902e-06</v>
       </c>
       <c r="F14">
-        <v>-5.3242234643711658e-08</v>
+        <v>-6.1787783522582937e-08</v>
       </c>
       <c r="G14">
-        <v>3.9036656278633539e-06</v>
+        <v>1.1239893869760726e-05</v>
       </c>
       <c r="H14">
-        <v>-6.7846411801802064e-06</v>
+        <v>9.6105601958717439e-06</v>
       </c>
       <c r="I14">
-        <v>1.9240449379248079e-07</v>
+        <v>-4.2281365264753337e-09</v>
       </c>
       <c r="J14">
-        <v>6.4985493886801833e-07</v>
+        <v>1.7742873602856898e-07</v>
       </c>
       <c r="K14">
-        <v>-3.2235304277782257e-05</v>
+        <v>-2.364816035365556e-05</v>
       </c>
       <c r="L14">
-        <v>1.7397590282903228e-05</v>
+        <v>-1.6521843496977614e-05</v>
       </c>
       <c r="M14">
-        <v>0.0043000530682319642</v>
+        <v>0.0035693703197701211</v>
       </c>
       <c r="N14">
-        <v>0.0043059613841144005</v>
+        <v>0.0035747873517132777</v>
       </c>
       <c r="O14">
-        <v>0.0043705842032816982</v>
+        <v>0.0036312711649776168</v>
       </c>
       <c r="P14">
-        <v>0.0043292655799181678</v>
+        <v>0.0035940650119536226</v>
       </c>
       <c r="Q14">
-        <v>-1.0402552457463308e-05</v>
+        <v>-4.5278148072298315e-06</v>
       </c>
       <c r="R14">
-        <v>-2.0015504535873709e-06</v>
+        <v>1.4764703699844011e-06</v>
       </c>
       <c r="S14">
-        <v>-1.6216094678504019e-05</v>
+        <v>-9.7091994508373408e-06</v>
       </c>
       <c r="T14">
-        <v>-2.9173039289013191e-07</v>
+        <v>3.7743477250128951e-06</v>
       </c>
       <c r="U14">
-        <v>-1.2557784687938035e-05</v>
+        <v>-9.2885581969664831e-06</v>
       </c>
       <c r="V14">
-        <v>1.4695235030674021e-06</v>
+        <v>5.0788656043477425e-06</v>
       </c>
       <c r="W14">
-        <v>-6.2455986156359512e-06</v>
+        <v>-7.1179462224887442e-06</v>
       </c>
       <c r="X14">
-        <v>7.2239502471942131e-06</v>
+        <v>4.895541103505398e-06</v>
       </c>
       <c r="Y14">
-        <v>-0.0044612043691336827</v>
+        <v>-0.0037313408862465368</v>
       </c>
     </row>
     <row r="15">
@@ -1385,76 +1385,76 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>0.61675190926548218</v>
+        <v>0.67172158065640086</v>
       </c>
       <c r="C15">
-        <v>7.5573288102211253e-06</v>
+        <v>1.9876746229329357e-06</v>
       </c>
       <c r="D15">
-        <v>1.6490280799426178e-05</v>
+        <v>1.2852034929053951e-05</v>
       </c>
       <c r="E15">
-        <v>1.0198964825918879e-05</v>
+        <v>1.0515512924367032e-05</v>
       </c>
       <c r="F15">
-        <v>-8.3101626087108728e-08</v>
+        <v>-9.1527524773972747e-08</v>
       </c>
       <c r="G15">
-        <v>2.9754531112494045e-05</v>
+        <v>3.2628129655894026e-05</v>
       </c>
       <c r="H15">
-        <v>3.1322992523865581e-05</v>
+        <v>3.8898908288649526e-05</v>
       </c>
       <c r="I15">
-        <v>-1.7569416165642021e-07</v>
+        <v>-3.1814625114640597e-07</v>
       </c>
       <c r="J15">
-        <v>1.2444968043174353e-07</v>
+        <v>-2.3193825979991529e-07</v>
       </c>
       <c r="K15">
-        <v>-3.1327524633515145e-05</v>
+        <v>-2.2938093223347163e-05</v>
       </c>
       <c r="L15">
-        <v>4.4750517046325869e-06</v>
+        <v>-1.8568543181393855e-05</v>
       </c>
       <c r="M15">
-        <v>0.004299143650955994</v>
+        <v>0.0035680951857395928</v>
       </c>
       <c r="N15">
-        <v>0.0043075386652724193</v>
+        <v>0.0035760122346091888</v>
       </c>
       <c r="O15">
-        <v>0.0043292655799181678</v>
+        <v>0.0035940650119536226</v>
       </c>
       <c r="P15">
-        <v>0.0045274589691009911</v>
+        <v>0.0037737378252681989</v>
       </c>
       <c r="Q15">
-        <v>-1.8721883572335427e-05</v>
+        <v>-1.2042210257219639e-05</v>
       </c>
       <c r="R15">
-        <v>-1.2408239390042952e-05</v>
+        <v>-7.5414786816058968e-06</v>
       </c>
       <c r="S15">
-        <v>-2.0682266280592468e-05</v>
+        <v>-1.3507510707194651e-05</v>
       </c>
       <c r="T15">
-        <v>-1.5831521131190614e-05</v>
+        <v>-8.9710496959651904e-06</v>
       </c>
       <c r="U15">
-        <v>-2.4676664520045875e-05</v>
+        <v>-1.9415624512475184e-05</v>
       </c>
       <c r="V15">
-        <v>-1.0234499504098115e-05</v>
+        <v>-5.5689124964271585e-06</v>
       </c>
       <c r="W15">
-        <v>-1.0576543168340934e-05</v>
+        <v>-1.1797723467004485e-05</v>
       </c>
       <c r="X15">
-        <v>7.1690052865917662e-06</v>
+        <v>4.4898699790875024e-06</v>
       </c>
       <c r="Y15">
-        <v>-0.0045967698067886833</v>
+        <v>-0.0038544324578319118</v>
       </c>
     </row>
     <row r="16">
@@ -1462,76 +1462,76 @@
         <v>36</v>
       </c>
       <c r="B16">
-        <v>0.043299145993451374</v>
+        <v>0.073692222743085373</v>
       </c>
       <c r="C16">
-        <v>4.2636101886433158e-06</v>
+        <v>2.8493485357173865e-06</v>
       </c>
       <c r="D16">
-        <v>3.2379203620187892e-06</v>
+        <v>2.1422429351680539e-06</v>
       </c>
       <c r="E16">
-        <v>7.2614108078310702e-07</v>
+        <v>1.4292546320355303e-06</v>
       </c>
       <c r="F16">
-        <v>-1.0031208201299662e-08</v>
+        <v>-1.800406641222405e-08</v>
       </c>
       <c r="G16">
-        <v>2.8620203262038928e-06</v>
+        <v>4.445423449641639e-06</v>
       </c>
       <c r="H16">
-        <v>4.2939548835341625e-06</v>
+        <v>7.9633759505789005e-06</v>
       </c>
       <c r="I16">
-        <v>5.7718601815146839e-08</v>
+        <v>-1.7877272226906577e-09</v>
       </c>
       <c r="J16">
-        <v>8.3425119060992701e-08</v>
+        <v>-2.5994502078208996e-08</v>
       </c>
       <c r="K16">
-        <v>-5.9580706376392294e-06</v>
+        <v>-2.7587541248345288e-06</v>
       </c>
       <c r="L16">
-        <v>-4.1510337420614264e-06</v>
+        <v>-7.2214097515647985e-06</v>
       </c>
       <c r="M16">
-        <v>4.536155307830573e-06</v>
+        <v>7.244894926365883e-06</v>
       </c>
       <c r="N16">
-        <v>-1.6781364933534645e-06</v>
+        <v>1.8399964780818195e-06</v>
       </c>
       <c r="O16">
-        <v>-1.0402552457463308e-05</v>
+        <v>-4.5278148072298315e-06</v>
       </c>
       <c r="P16">
-        <v>-1.8721883572335427e-05</v>
+        <v>-1.2042210257219639e-05</v>
       </c>
       <c r="Q16">
-        <v>0.00044138068346047545</v>
+        <v>0.00039857818172638548</v>
       </c>
       <c r="R16">
-        <v>0.00023213212747061733</v>
+        <v>0.00020916679615355069</v>
       </c>
       <c r="S16">
-        <v>0.00023043838941843884</v>
+        <v>0.00020784636961141418</v>
       </c>
       <c r="T16">
-        <v>0.00023131015545587539</v>
+        <v>0.00020863600195786676</v>
       </c>
       <c r="U16">
-        <v>0.00022998618130566442</v>
+        <v>0.00020758448624725895</v>
       </c>
       <c r="V16">
-        <v>0.00022914413497782379</v>
+        <v>0.00020675818443960476</v>
       </c>
       <c r="W16">
-        <v>1.0728623583437715e-06</v>
+        <v>1.375355982132621e-06</v>
       </c>
       <c r="X16">
-        <v>-2.5669139939127136e-07</v>
+        <v>8.2531002632138115e-08</v>
       </c>
       <c r="Y16">
-        <v>-0.00023393594692061324</v>
+        <v>-0.00022892873610641688</v>
       </c>
     </row>
     <row r="17">
@@ -1539,76 +1539,76 @@
         <v>37</v>
       </c>
       <c r="B17">
-        <v>-0.016221274505915744</v>
+        <v>0.05126475579648359</v>
       </c>
       <c r="C17">
-        <v>5.575094918599639e-06</v>
+        <v>3.7886423362497602e-06</v>
       </c>
       <c r="D17">
-        <v>6.0245040494769332e-06</v>
+        <v>3.1392237086245195e-06</v>
       </c>
       <c r="E17">
-        <v>5.7393906957967364e-08</v>
+        <v>1.1910413340624589e-06</v>
       </c>
       <c r="F17">
-        <v>-4.9873484225541933e-09</v>
+        <v>-1.7016004741115924e-08</v>
       </c>
       <c r="G17">
-        <v>-1.0267717028836291e-07</v>
+        <v>1.5113902613509924e-06</v>
       </c>
       <c r="H17">
-        <v>-1.1069092011884696e-05</v>
+        <v>-5.5233640045138422e-06</v>
       </c>
       <c r="I17">
-        <v>1.0356089281036475e-07</v>
+        <v>1.6470714984843657e-08</v>
       </c>
       <c r="J17">
-        <v>5.6141453734698148e-07</v>
+        <v>3.6804642476238213e-07</v>
       </c>
       <c r="K17">
-        <v>1.3416188361933879e-06</v>
+        <v>2.9565684692139051e-06</v>
       </c>
       <c r="L17">
-        <v>4.2027737865672014e-06</v>
+        <v>-7.3758746655500656e-06</v>
       </c>
       <c r="M17">
-        <v>1.2774472026211097e-05</v>
+        <v>1.2911383648716147e-05</v>
       </c>
       <c r="N17">
-        <v>4.2312743863822614e-06</v>
+        <v>5.6532644853852615e-06</v>
       </c>
       <c r="O17">
-        <v>-2.0015504535873709e-06</v>
+        <v>1.4764703699844011e-06</v>
       </c>
       <c r="P17">
-        <v>-1.2408239390042952e-05</v>
+        <v>-7.5414786816058968e-06</v>
       </c>
       <c r="Q17">
-        <v>0.00023213212747061733</v>
+        <v>0.00020916679615355069</v>
       </c>
       <c r="R17">
-        <v>0.00053377643211219414</v>
+        <v>0.00047853684428967132</v>
       </c>
       <c r="S17">
-        <v>0.00022982842768083639</v>
+        <v>0.00020734517434658174</v>
       </c>
       <c r="T17">
-        <v>0.00023142961487592555</v>
+        <v>0.00020873398824343837</v>
       </c>
       <c r="U17">
-        <v>0.00022947164752944421</v>
+        <v>0.00020723874029475849</v>
       </c>
       <c r="V17">
-        <v>0.0002297127653882869</v>
+        <v>0.00020723423948553212</v>
       </c>
       <c r="W17">
-        <v>-1.843736926814521e-06</v>
+        <v>-8.9308460403442874e-07</v>
       </c>
       <c r="X17">
-        <v>-7.7675370219925999e-06</v>
+        <v>-4.7206916125607647e-06</v>
       </c>
       <c r="Y17">
-        <v>-0.00023047971297573627</v>
+        <v>-0.00023084883665623171</v>
       </c>
     </row>
     <row r="18">
@@ -1616,76 +1616,76 @@
         <v>38</v>
       </c>
       <c r="B18">
-        <v>-0.0388117146229063</v>
+        <v>-0.014076818221382494</v>
       </c>
       <c r="C18">
-        <v>-1.4976374090251716e-06</v>
+        <v>6.4079993556668044e-07</v>
       </c>
       <c r="D18">
-        <v>-2.0398014275715767e-06</v>
+        <v>-2.167488109638385e-06</v>
       </c>
       <c r="E18">
-        <v>1.0909093054176679e-07</v>
+        <v>4.8703722193004131e-07</v>
       </c>
       <c r="F18">
-        <v>-6.5535565323370044e-10</v>
+        <v>-4.731693085333438e-09</v>
       </c>
       <c r="G18">
-        <v>-5.1497703129434517e-06</v>
+        <v>-1.9115657197659095e-06</v>
       </c>
       <c r="H18">
-        <v>-2.902826063173506e-05</v>
+        <v>-1.7014921598287376e-05</v>
       </c>
       <c r="I18">
-        <v>1.1168479755137243e-07</v>
+        <v>3.2785114306925699e-08</v>
       </c>
       <c r="J18">
-        <v>3.6555775350960959e-07</v>
+        <v>1.4522606577529837e-07</v>
       </c>
       <c r="K18">
-        <v>-5.2425375587558747e-06</v>
+        <v>-3.3105430912645903e-06</v>
       </c>
       <c r="L18">
-        <v>1.6923700458096433e-05</v>
+        <v>-4.312334110483636e-06</v>
       </c>
       <c r="M18">
-        <v>1.7062806309530191e-06</v>
+        <v>4.5776914590981024e-06</v>
       </c>
       <c r="N18">
-        <v>-7.4026137389406044e-06</v>
+        <v>-2.6796835551761859e-06</v>
       </c>
       <c r="O18">
-        <v>-1.6216094678504019e-05</v>
+        <v>-9.7091994508373408e-06</v>
       </c>
       <c r="P18">
-        <v>-2.0682266280592468e-05</v>
+        <v>-1.3507510707194651e-05</v>
       </c>
       <c r="Q18">
-        <v>0.00023043838941843884</v>
+        <v>0.00020784636961141418</v>
       </c>
       <c r="R18">
-        <v>0.00022982842768083639</v>
+        <v>0.00020734517434658174</v>
       </c>
       <c r="S18">
-        <v>0.0004299858484190636</v>
+        <v>0.00038720143444915628</v>
       </c>
       <c r="T18">
-        <v>0.00023103523410615933</v>
+        <v>0.00020828084976414133</v>
       </c>
       <c r="U18">
-        <v>0.00023328250313897292</v>
+        <v>0.00021008513291280714</v>
       </c>
       <c r="V18">
-        <v>0.00023069392649076326</v>
+        <v>0.0002078348288325775</v>
       </c>
       <c r="W18">
-        <v>-6.1420063790584963e-06</v>
+        <v>-4.9775195416931294e-06</v>
       </c>
       <c r="X18">
-        <v>-6.9327736194005213e-06</v>
+        <v>-5.8113497166520079e-06</v>
       </c>
       <c r="Y18">
-        <v>-0.00021071833549293878</v>
+        <v>-0.00020253055970155418</v>
       </c>
     </row>
     <row r="19">
@@ -1693,76 +1693,76 @@
         <v>39</v>
       </c>
       <c r="B19">
-        <v>0.057025108645005963</v>
+        <v>0.09378628572061265</v>
       </c>
       <c r="C19">
-        <v>7.5926666273633648e-06</v>
+        <v>5.7738368143280504e-06</v>
       </c>
       <c r="D19">
-        <v>2.5797321779958534e-06</v>
+        <v>1.7903095210014873e-06</v>
       </c>
       <c r="E19">
-        <v>8.570012247718916e-07</v>
+        <v>1.6663707198308055e-06</v>
       </c>
       <c r="F19">
-        <v>-1.1251710434941407e-08</v>
+        <v>-2.0071084534453949e-08</v>
       </c>
       <c r="G19">
-        <v>-1.1543054323875125e-05</v>
+        <v>-5.6664484676520657e-06</v>
       </c>
       <c r="H19">
-        <v>-2.3206953553328635e-05</v>
+        <v>-1.3287409139150585e-05</v>
       </c>
       <c r="I19">
-        <v>1.7111120631175475e-07</v>
+        <v>3.6338635616813778e-08</v>
       </c>
       <c r="J19">
-        <v>4.5347012479434286e-07</v>
+        <v>2.406435429129941e-07</v>
       </c>
       <c r="K19">
-        <v>-5.1141406128629676e-06</v>
+        <v>-2.5221500356785842e-06</v>
       </c>
       <c r="L19">
-        <v>4.0933953295506993e-06</v>
+        <v>-7.1298840373377753e-06</v>
       </c>
       <c r="M19">
-        <v>7.8058066934647512e-06</v>
+        <v>9.7991299640515841e-06</v>
       </c>
       <c r="N19">
-        <v>4.9934415580902061e-06</v>
+        <v>6.9866038140402347e-06</v>
       </c>
       <c r="O19">
-        <v>-2.9173039289013191e-07</v>
+        <v>3.7743477250128951e-06</v>
       </c>
       <c r="P19">
-        <v>-1.5831521131190614e-05</v>
+        <v>-8.9710496959651904e-06</v>
       </c>
       <c r="Q19">
-        <v>0.00023131015545587539</v>
+        <v>0.00020863600195786676</v>
       </c>
       <c r="R19">
-        <v>0.00023142961487592555</v>
+        <v>0.00020873398824343837</v>
       </c>
       <c r="S19">
-        <v>0.00023103523410615933</v>
+        <v>0.00020828084976414133</v>
       </c>
       <c r="T19">
-        <v>0.0003710893458051386</v>
+        <v>0.00032751469574160804</v>
       </c>
       <c r="U19">
-        <v>0.00023185269557246871</v>
+        <v>0.00020900457198413748</v>
       </c>
       <c r="V19">
-        <v>0.00023057587495740349</v>
+        <v>0.00020786332807523817</v>
       </c>
       <c r="W19">
-        <v>4.8301752520641106e-06</v>
+        <v>6.4923544262157329e-06</v>
       </c>
       <c r="X19">
-        <v>4.2025562091222498e-06</v>
+        <v>5.9119263836670848e-06</v>
       </c>
       <c r="Y19">
-        <v>-0.00024062626068008437</v>
+        <v>-0.00023757989767552652</v>
       </c>
     </row>
     <row r="20">
@@ -1770,76 +1770,76 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <v>-0.14042850568275228</v>
+        <v>-0.1015328748478599</v>
       </c>
       <c r="C20">
-        <v>5.7726603500998899e-06</v>
+        <v>6.4399516836442697e-06</v>
       </c>
       <c r="D20">
-        <v>-6.3772008551939256e-06</v>
+        <v>-6.2092317259988623e-06</v>
       </c>
       <c r="E20">
-        <v>-3.8601954097936526e-08</v>
+        <v>3.2829403045377973e-07</v>
       </c>
       <c r="F20">
-        <v>3.4145696828080349e-09</v>
+        <v>-1.0096604103184873e-09</v>
       </c>
       <c r="G20">
-        <v>-1.700380279706316e-05</v>
+        <v>-1.1448503958290276e-05</v>
       </c>
       <c r="H20">
-        <v>-5.5925882771811329e-05</v>
+        <v>-3.5950549136931192e-05</v>
       </c>
       <c r="I20">
-        <v>3.0278273217855394e-07</v>
+        <v>1.784541399021381e-07</v>
       </c>
       <c r="J20">
-        <v>7.974185894975233e-07</v>
+        <v>4.2919121904164667e-07</v>
       </c>
       <c r="K20">
-        <v>-2.3615602021981738e-06</v>
+        <v>3.3716769143997658e-08</v>
       </c>
       <c r="L20">
-        <v>3.2814391434223279e-05</v>
+        <v>-6.2404596342951593e-06</v>
       </c>
       <c r="M20">
-        <v>2.0303412738913006e-06</v>
+        <v>2.6405051996475392e-06</v>
       </c>
       <c r="N20">
-        <v>-6.510458729558588e-06</v>
+        <v>-4.7112244350561817e-06</v>
       </c>
       <c r="O20">
-        <v>-1.2557784687938035e-05</v>
+        <v>-9.2885581969664831e-06</v>
       </c>
       <c r="P20">
-        <v>-2.4676664520045875e-05</v>
+        <v>-1.9415624512475184e-05</v>
       </c>
       <c r="Q20">
-        <v>0.00022998618130566442</v>
+        <v>0.00020758448624725895</v>
       </c>
       <c r="R20">
-        <v>0.00022947164752944421</v>
+        <v>0.00020723874029475849</v>
       </c>
       <c r="S20">
-        <v>0.00023328250313897292</v>
+        <v>0.00021008513291280714</v>
       </c>
       <c r="T20">
-        <v>0.00023185269557246871</v>
+        <v>0.00020900457198413748</v>
       </c>
       <c r="U20">
-        <v>0.00039680243525847382</v>
+        <v>0.00035523530052020022</v>
       </c>
       <c r="V20">
-        <v>0.00023288449335761612</v>
+        <v>0.00020958615474129622</v>
       </c>
       <c r="W20">
-        <v>-1.9573508040404356e-06</v>
+        <v>-2.0323145377481024e-07</v>
       </c>
       <c r="X20">
-        <v>-4.0247167864966488e-06</v>
+        <v>-1.9230246924610818e-06</v>
       </c>
       <c r="Y20">
-        <v>-0.00021355649063945054</v>
+        <v>-0.000201066317566371</v>
       </c>
     </row>
     <row r="21">
@@ -1847,76 +1847,76 @@
         <v>41</v>
       </c>
       <c r="B21">
-        <v>-0.074457721263041524</v>
+        <v>-0.049806128178538564</v>
       </c>
       <c r="C21">
-        <v>6.0233655465737843e-07</v>
+        <v>-4.1962939247760638e-07</v>
       </c>
       <c r="D21">
-        <v>-5.1722876145704883e-06</v>
+        <v>-4.7750209927426335e-06</v>
       </c>
       <c r="E21">
-        <v>-2.1091692782088654e-06</v>
+        <v>-1.5924073443884118e-06</v>
       </c>
       <c r="F21">
-        <v>2.4040497405546126e-08</v>
+        <v>1.8423286454227841e-08</v>
       </c>
       <c r="G21">
-        <v>-1.522079164008946e-05</v>
+        <v>-1.0149676103076937e-05</v>
       </c>
       <c r="H21">
-        <v>-2.8529712476297917e-05</v>
+        <v>-1.9387934875485656e-05</v>
       </c>
       <c r="I21">
-        <v>2.5497860948027182e-07</v>
+        <v>1.5115619323630546e-07</v>
       </c>
       <c r="J21">
-        <v>4.3578735223408231e-07</v>
+        <v>2.6854037537018175e-07</v>
       </c>
       <c r="K21">
-        <v>1.3846801038372074e-05</v>
+        <v>1.1505396567742331e-05</v>
       </c>
       <c r="L21">
-        <v>1.6026598790000384e-05</v>
+        <v>-2.7339106883459257e-07</v>
       </c>
       <c r="M21">
-        <v>9.6240102269608946e-06</v>
+        <v>1.0781726965084075e-05</v>
       </c>
       <c r="N21">
-        <v>-5.4920975788681298e-06</v>
+        <v>-8.029157398520406e-07</v>
       </c>
       <c r="O21">
-        <v>1.4695235030674021e-06</v>
+        <v>5.0788656043477425e-06</v>
       </c>
       <c r="P21">
-        <v>-1.0234499504098115e-05</v>
+        <v>-5.5689124964271585e-06</v>
       </c>
       <c r="Q21">
-        <v>0.00022914413497782379</v>
+        <v>0.00020675818443960476</v>
       </c>
       <c r="R21">
-        <v>0.0002297127653882869</v>
+        <v>0.00020723423948553212</v>
       </c>
       <c r="S21">
-        <v>0.00023069392649076326</v>
+        <v>0.0002078348288325775</v>
       </c>
       <c r="T21">
-        <v>0.00023057587495740349</v>
+        <v>0.00020786332807523817</v>
       </c>
       <c r="U21">
-        <v>0.00023288449335761612</v>
+        <v>0.00020958615474129622</v>
       </c>
       <c r="V21">
-        <v>0.001026855962446144</v>
+        <v>0.00091779250483804752</v>
       </c>
       <c r="W21">
-        <v>5.0137147331231602e-06</v>
+        <v>5.2602395908732781e-06</v>
       </c>
       <c r="X21">
-        <v>4.976984367818873e-06</v>
+        <v>5.6574551329543511e-06</v>
       </c>
       <c r="Y21">
-        <v>-0.00019078624041394076</v>
+        <v>-0.00018173958476425619</v>
       </c>
     </row>
     <row r="22">
@@ -1924,76 +1924,76 @@
         <v>42</v>
       </c>
       <c r="B22">
-        <v>-0.057299250243023528</v>
+        <v>-0.0923495704559784</v>
       </c>
       <c r="C22">
-        <v>1.0357376828053962e-05</v>
+        <v>9.9562976616470948e-06</v>
       </c>
       <c r="D22">
-        <v>6.449379893992628e-06</v>
+        <v>5.711084054726912e-06</v>
       </c>
       <c r="E22">
-        <v>4.239596629926488e-07</v>
+        <v>5.1319639636195038e-07</v>
       </c>
       <c r="F22">
-        <v>-6.8730687389085826e-09</v>
+        <v>-6.605817393049726e-09</v>
       </c>
       <c r="G22">
-        <v>8.6955938711988e-06</v>
+        <v>6.7976865026077628e-06</v>
       </c>
       <c r="H22">
-        <v>1.5581745572557169e-05</v>
+        <v>1.5502196411901637e-05</v>
       </c>
       <c r="I22">
-        <v>-1.0280251246839305e-07</v>
+        <v>-8.0470731857337259e-08</v>
       </c>
       <c r="J22">
-        <v>-1.5285424393132197e-07</v>
+        <v>-2.0894545913527595e-07</v>
       </c>
       <c r="K22">
-        <v>-1.3345004104120418e-06</v>
+        <v>-8.8210213924130594e-07</v>
       </c>
       <c r="L22">
-        <v>-7.2863947464846939e-06</v>
+        <v>-2.0963572648921408e-06</v>
       </c>
       <c r="M22">
-        <v>-2.1881698121816384e-06</v>
+        <v>-2.659226834504982e-06</v>
       </c>
       <c r="N22">
-        <v>-7.1226765481819864e-06</v>
+        <v>-6.8262886919653498e-06</v>
       </c>
       <c r="O22">
-        <v>-6.2455986156359512e-06</v>
+        <v>-7.1179462224887442e-06</v>
       </c>
       <c r="P22">
-        <v>-1.0576543168340934e-05</v>
+        <v>-1.1797723467004485e-05</v>
       </c>
       <c r="Q22">
-        <v>1.0728623583437715e-06</v>
+        <v>1.375355982132621e-06</v>
       </c>
       <c r="R22">
-        <v>-1.843736926814521e-06</v>
+        <v>-8.9308460403442874e-07</v>
       </c>
       <c r="S22">
-        <v>-6.1420063790584963e-06</v>
+        <v>-4.9775195416931294e-06</v>
       </c>
       <c r="T22">
-        <v>4.8301752520641106e-06</v>
+        <v>6.4923544262157329e-06</v>
       </c>
       <c r="U22">
-        <v>-1.9573508040404356e-06</v>
+        <v>-2.0323145377481024e-07</v>
       </c>
       <c r="V22">
-        <v>5.0137147331231602e-06</v>
+        <v>5.2602395908732781e-06</v>
       </c>
       <c r="W22">
-        <v>0.0005116466051101749</v>
+        <v>0.00051575269920147078</v>
       </c>
       <c r="X22">
-        <v>3.759728127852206e-05</v>
+        <v>3.236362748455832e-05</v>
       </c>
       <c r="Y22">
-        <v>-3.8807915643076574e-05</v>
+        <v>-3.7151624126349185e-05</v>
       </c>
     </row>
     <row r="23">
@@ -2001,76 +2001,76 @@
         <v>43</v>
       </c>
       <c r="B23">
-        <v>0.037129283881508407</v>
+        <v>0.040627500029932775</v>
       </c>
       <c r="C23">
-        <v>7.0355137455296531e-06</v>
+        <v>4.3000236693587114e-06</v>
       </c>
       <c r="D23">
-        <v>1.1898052516156756e-05</v>
+        <v>9.0455988857617261e-06</v>
       </c>
       <c r="E23">
-        <v>-4.8358358493944411e-07</v>
+        <v>3.5952893214442572e-07</v>
       </c>
       <c r="F23">
-        <v>1.7531733545419866e-09</v>
+        <v>-6.2584565743969258e-09</v>
       </c>
       <c r="G23">
-        <v>8.379934847303358e-06</v>
+        <v>6.1670635498055813e-06</v>
       </c>
       <c r="H23">
-        <v>1.6524604911675522e-05</v>
+        <v>1.5542241449421002e-05</v>
       </c>
       <c r="I23">
-        <v>-5.2568120058640001e-08</v>
+        <v>-5.4897924928440445e-08</v>
       </c>
       <c r="J23">
-        <v>-3.9044512839800034e-08</v>
+        <v>-1.2396507342169301e-07</v>
       </c>
       <c r="K23">
-        <v>-6.8615739832329165e-07</v>
+        <v>4.0556182386317124e-07</v>
       </c>
       <c r="L23">
-        <v>-2.9528375826878163e-05</v>
+        <v>-5.0720331981070855e-06</v>
       </c>
       <c r="M23">
-        <v>4.3516053563866506e-06</v>
+        <v>2.8522856670761173e-06</v>
       </c>
       <c r="N23">
-        <v>3.2200834082005357e-06</v>
+        <v>2.2617914458459829e-06</v>
       </c>
       <c r="O23">
-        <v>7.2239502471942131e-06</v>
+        <v>4.895541103505398e-06</v>
       </c>
       <c r="P23">
-        <v>7.1690052865917662e-06</v>
+        <v>4.4898699790875024e-06</v>
       </c>
       <c r="Q23">
-        <v>-2.5669139939127136e-07</v>
+        <v>8.2531002632138115e-08</v>
       </c>
       <c r="R23">
-        <v>-7.7675370219925999e-06</v>
+        <v>-4.7206916125607647e-06</v>
       </c>
       <c r="S23">
-        <v>-6.9327736194005213e-06</v>
+        <v>-5.8113497166520079e-06</v>
       </c>
       <c r="T23">
-        <v>4.2025562091222498e-06</v>
+        <v>5.9119263836670848e-06</v>
       </c>
       <c r="U23">
-        <v>-4.0247167864966488e-06</v>
+        <v>-1.9230246924610818e-06</v>
       </c>
       <c r="V23">
-        <v>4.976984367818873e-06</v>
+        <v>5.6574551329543511e-06</v>
       </c>
       <c r="W23">
-        <v>3.759728127852206e-05</v>
+        <v>3.236362748455832e-05</v>
       </c>
       <c r="X23">
-        <v>0.00060266800858814387</v>
+        <v>0.00061848160784097475</v>
       </c>
       <c r="Y23">
-        <v>-3.4024001492931245e-05</v>
+        <v>-4.4096993446648153e-05</v>
       </c>
     </row>
     <row r="24">
@@ -2078,76 +2078,76 @@
         <v>44</v>
       </c>
       <c r="B24">
-        <v>-1.6668664512367881</v>
+        <v>-2.1863205181631735</v>
       </c>
       <c r="C24">
-        <v>-0.0010549303565369052</v>
+        <v>-0.000988449099072807</v>
       </c>
       <c r="D24">
-        <v>-0.00014452076130769679</v>
+        <v>-0.00011661033011537262</v>
       </c>
       <c r="E24">
-        <v>-0.0002714613930900531</v>
+        <v>-0.00025058045398493442</v>
       </c>
       <c r="F24">
-        <v>2.6517524962267183e-06</v>
+        <v>2.468879685493119e-06</v>
       </c>
       <c r="G24">
-        <v>-0.0013105522706281948</v>
+        <v>-0.0012440409183924889</v>
       </c>
       <c r="H24">
-        <v>-0.0010286658564525621</v>
+        <v>-0.0012388207517911992</v>
       </c>
       <c r="I24">
-        <v>2.6685349817706093e-05</v>
+        <v>2.5491124340933407e-05</v>
       </c>
       <c r="J24">
-        <v>1.9701823854459415e-05</v>
+        <v>2.4221675374156273e-05</v>
       </c>
       <c r="K24">
-        <v>0.00026755006816287787</v>
+        <v>0.00016157160861471681</v>
       </c>
       <c r="L24">
-        <v>-0.00088185876998194172</v>
+        <v>0.00022785976442534005</v>
       </c>
       <c r="M24">
-        <v>-0.0043468763354454132</v>
+        <v>-0.0036145091879106</v>
       </c>
       <c r="N24">
-        <v>-0.0044000963654414939</v>
+        <v>-0.0036696532994213793</v>
       </c>
       <c r="O24">
-        <v>-0.0044612043691336827</v>
+        <v>-0.0037313408862465368</v>
       </c>
       <c r="P24">
-        <v>-0.0045967698067886833</v>
+        <v>-0.0038544324578319118</v>
       </c>
       <c r="Q24">
-        <v>-0.00023393594692061324</v>
+        <v>-0.00022892873610641688</v>
       </c>
       <c r="R24">
-        <v>-0.00023047971297573627</v>
+        <v>-0.00023084883665623171</v>
       </c>
       <c r="S24">
-        <v>-0.00021071833549293878</v>
+        <v>-0.00020253055970155418</v>
       </c>
       <c r="T24">
-        <v>-0.00024062626068008437</v>
+        <v>-0.00023757989767552652</v>
       </c>
       <c r="U24">
-        <v>-0.00021355649063945054</v>
+        <v>-0.000201066317566371</v>
       </c>
       <c r="V24">
-        <v>-0.00019078624041394076</v>
+        <v>-0.00018173958476425619</v>
       </c>
       <c r="W24">
-        <v>-3.8807915643076574e-05</v>
+        <v>-3.7151624126349185e-05</v>
       </c>
       <c r="X24">
-        <v>-3.4024001492931245e-05</v>
+        <v>-4.4096993446648153e-05</v>
       </c>
       <c r="Y24">
-        <v>0.011099175054119295</v>
+        <v>0.0097744381883295758</v>
       </c>
     </row>
   </sheetData>
@@ -2241,76 +2241,76 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>-1.4931074320606004</v>
+        <v>-1.5460064491678762</v>
       </c>
       <c r="C2">
-        <v>0.00088126224871907328</v>
+        <v>0.00074185927597689031</v>
       </c>
       <c r="D2">
-        <v>8.1034713460495839e-05</v>
+        <v>7.1127309180528319e-05</v>
       </c>
       <c r="E2">
-        <v>3.7480134356225276e-05</v>
+        <v>3.8262834476235461e-05</v>
       </c>
       <c r="F2">
-        <v>-3.4713581164327136e-07</v>
+        <v>-3.6678866170883542e-07</v>
       </c>
       <c r="G2">
-        <v>-6.9159806415700065e-06</v>
+        <v>1.2316807841300401e-05</v>
       </c>
       <c r="H2">
-        <v>0.00020736673415861295</v>
+        <v>0.00014361884622716918</v>
       </c>
       <c r="I2">
-        <v>3.3097525688243883e-09</v>
+        <v>-3.3654529133260882e-07</v>
       </c>
       <c r="J2">
-        <v>-3.9889513541697308e-06</v>
+        <v>-2.7787692507174424e-06</v>
       </c>
       <c r="K2">
-        <v>2.1181623876570087e-05</v>
+        <v>2.9299995597658994e-05</v>
       </c>
       <c r="L2">
-        <v>-0.00028683737752833061</v>
+        <v>-3.0593206335037479e-05</v>
       </c>
       <c r="M2">
-        <v>-2.5807732715972184e-06</v>
+        <v>8.1451424063230457e-07</v>
       </c>
       <c r="N2">
-        <v>2.2449223507265445e-06</v>
+        <v>5.2516755494281457e-06</v>
       </c>
       <c r="O2">
-        <v>1.1131559091931821e-05</v>
+        <v>1.3574403627642298e-05</v>
       </c>
       <c r="P2">
-        <v>9.0443193928869113e-06</v>
+        <v>1.0409829902196513e-05</v>
       </c>
       <c r="Q2">
-        <v>7.2456559364568627e-06</v>
+        <v>4.7139542634746805e-06</v>
       </c>
       <c r="R2">
-        <v>4.6786959759314729e-06</v>
+        <v>1.475789271907036e-06</v>
       </c>
       <c r="S2">
-        <v>4.4968088864321487e-06</v>
+        <v>5.0773710577164088e-06</v>
       </c>
       <c r="T2">
-        <v>5.5963377198540407e-06</v>
+        <v>5.0413155862304047e-06</v>
       </c>
       <c r="U2">
-        <v>-3.7407432588798661e-06</v>
+        <v>-5.5285281196880353e-07</v>
       </c>
       <c r="V2">
-        <v>-2.0324119055380697e-06</v>
+        <v>2.8447485046941679e-07</v>
       </c>
       <c r="W2">
-        <v>9.6384478227815581e-06</v>
+        <v>9.8708634542819802e-06</v>
       </c>
       <c r="X2">
-        <v>2.9188835806084935e-06</v>
+        <v>5.8212419359163504e-07</v>
       </c>
       <c r="Y2">
-        <v>-0.0010294999162681253</v>
+        <v>-0.0010091629345850475</v>
       </c>
     </row>
     <row r="3">
@@ -2318,76 +2318,76 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>-2.0066162176245093</v>
+        <v>-2.0631663802872913</v>
       </c>
       <c r="C3">
-        <v>8.1034713460495839e-05</v>
+        <v>7.1127309180528319e-05</v>
       </c>
       <c r="D3">
-        <v>0.00016668502886221123</v>
+        <v>0.00014736760412597174</v>
       </c>
       <c r="E3">
-        <v>6.5249011384914685e-06</v>
+        <v>5.2247219769474625e-06</v>
       </c>
       <c r="F3">
-        <v>-6.8383320854421358e-08</v>
+        <v>-5.5171957437349748e-08</v>
       </c>
       <c r="G3">
-        <v>1.659225433474523e-05</v>
+        <v>1.2304378202020726e-05</v>
       </c>
       <c r="H3">
-        <v>-5.6122550013353312e-06</v>
+        <v>-4.7313988346049695e-06</v>
       </c>
       <c r="I3">
-        <v>-7.2051756438039053e-07</v>
+        <v>-4.8536132895246721e-07</v>
       </c>
       <c r="J3">
-        <v>-5.2305558349983376e-07</v>
+        <v>-3.6189512696978139e-07</v>
       </c>
       <c r="K3">
-        <v>1.8908203754649223e-05</v>
+        <v>1.3554640395691092e-05</v>
       </c>
       <c r="L3">
-        <v>1.2143907099235864e-05</v>
+        <v>3.0899032643850771e-06</v>
       </c>
       <c r="M3">
-        <v>5.5022057819434356e-06</v>
+        <v>6.1584748857115287e-06</v>
       </c>
       <c r="N3">
-        <v>1.0633711617590407e-05</v>
+        <v>8.7362210170806128e-06</v>
       </c>
       <c r="O3">
-        <v>2.0418435026734166e-05</v>
+        <v>1.6296170461959572e-05</v>
       </c>
       <c r="P3">
-        <v>2.5592259870643269e-05</v>
+        <v>2.0649284692382934e-05</v>
       </c>
       <c r="Q3">
-        <v>7.5294385777120658e-06</v>
+        <v>5.6289877470251649e-06</v>
       </c>
       <c r="R3">
-        <v>5.8498764915852253e-06</v>
+        <v>4.9529091190151011e-06</v>
       </c>
       <c r="S3">
-        <v>3.461372794127233e-06</v>
+        <v>3.7391885805211703e-06</v>
       </c>
       <c r="T3">
-        <v>3.6105993138311025e-06</v>
+        <v>2.8678310875438164e-06</v>
       </c>
       <c r="U3">
-        <v>-5.2066045992323442e-06</v>
+        <v>-3.6402324597503306e-06</v>
       </c>
       <c r="V3">
-        <v>-8.9386513252424649e-06</v>
+        <v>-7.5315705023342392e-06</v>
       </c>
       <c r="W3">
-        <v>8.1890817646018631e-06</v>
+        <v>6.7521108945201596e-06</v>
       </c>
       <c r="X3">
-        <v>9.5969579910589285e-06</v>
+        <v>6.5766276111471332e-06</v>
       </c>
       <c r="Y3">
-        <v>-0.00021579444375254827</v>
+        <v>-0.00017795279878205056</v>
       </c>
     </row>
     <row r="4">
@@ -2395,76 +2395,76 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>0.14516237783823921</v>
+        <v>0.16261647740890892</v>
       </c>
       <c r="C4">
-        <v>3.7480134356225276e-05</v>
+        <v>3.8262834476235461e-05</v>
       </c>
       <c r="D4">
-        <v>6.5249011384914685e-06</v>
+        <v>5.2247219769474625e-06</v>
       </c>
       <c r="E4">
-        <v>1.1303171481240903e-05</v>
+        <v>1.0207595034967712e-05</v>
       </c>
       <c r="F4">
-        <v>-1.1337954842942293e-07</v>
+        <v>-1.0295275784698111e-07</v>
       </c>
       <c r="G4">
-        <v>4.4775093548048516e-05</v>
+        <v>4.2941379733458038e-05</v>
       </c>
       <c r="H4">
-        <v>3.8467759561372122e-05</v>
+        <v>4.7396015767334004e-05</v>
       </c>
       <c r="I4">
-        <v>-9.2352878403446254e-07</v>
+        <v>-8.9389413889426779e-07</v>
       </c>
       <c r="J4">
-        <v>-7.6994277698212685e-07</v>
+        <v>-9.5176883071592331e-07</v>
       </c>
       <c r="K4">
-        <v>-1.2594004191337129e-05</v>
+        <v>-4.6891523105274465e-06</v>
       </c>
       <c r="L4">
-        <v>3.841691273959718e-05</v>
+        <v>-1.1340096863135722e-05</v>
       </c>
       <c r="M4">
-        <v>1.4913293897839792e-06</v>
+        <v>1.7972441888854037e-06</v>
       </c>
       <c r="N4">
-        <v>3.7773045482607974e-06</v>
+        <v>3.9677836071922204e-06</v>
       </c>
       <c r="O4">
-        <v>5.7320576508925695e-06</v>
+        <v>5.9906863780168437e-06</v>
       </c>
       <c r="P4">
-        <v>1.1524196383877076e-05</v>
+        <v>1.1405668610090365e-05</v>
       </c>
       <c r="Q4">
-        <v>3.5215394732287934e-07</v>
+        <v>1.1376983638802547e-06</v>
       </c>
       <c r="R4">
-        <v>-4.788584723277864e-07</v>
+        <v>1.3520636707573905e-07</v>
       </c>
       <c r="S4">
-        <v>3.1799205785004463e-07</v>
+        <v>3.856358699013978e-07</v>
       </c>
       <c r="T4">
-        <v>3.3620727800952382e-07</v>
+        <v>1.0623117599141848e-06</v>
       </c>
       <c r="U4">
-        <v>-7.8068490041055079e-07</v>
+        <v>-3.9097935948372816e-07</v>
       </c>
       <c r="V4">
-        <v>-1.6160452525814243e-06</v>
+        <v>-1.7237746172763759e-06</v>
       </c>
       <c r="W4">
-        <v>3.3325530035804443e-07</v>
+        <v>5.2972168521386966e-07</v>
       </c>
       <c r="X4">
-        <v>-6.7546704682154576e-07</v>
+        <v>2.81561731566845e-07</v>
       </c>
       <c r="Y4">
-        <v>-0.00026373953153217405</v>
+        <v>-0.00023829272713437683</v>
       </c>
     </row>
     <row r="5">
@@ -2472,76 +2472,76 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>-0.0019110229600048333</v>
+        <v>-0.0020783381670518601</v>
       </c>
       <c r="C5">
-        <v>-3.4713581164327136e-07</v>
+        <v>-3.6678866170883542e-07</v>
       </c>
       <c r="D5">
-        <v>-6.8383320854421358e-08</v>
+        <v>-5.5171957437349748e-08</v>
       </c>
       <c r="E5">
-        <v>-1.1337954842942293e-07</v>
+        <v>-1.0295275784698111e-07</v>
       </c>
       <c r="F5">
-        <v>1.2148699399149345e-09</v>
+        <v>1.1086094879298779e-09</v>
       </c>
       <c r="G5">
-        <v>-1.9092117360212847e-07</v>
+        <v>-2.0853527006566698e-07</v>
       </c>
       <c r="H5">
-        <v>-9.9344048452925519e-08</v>
+        <v>-2.4801098632227966e-07</v>
       </c>
       <c r="I5">
-        <v>3.5606115341832966e-09</v>
+        <v>4.1153924732624663e-09</v>
       </c>
       <c r="J5">
-        <v>1.473734371004006e-09</v>
+        <v>4.5961776018602967e-09</v>
       </c>
       <c r="K5">
-        <v>1.0115109968394638e-07</v>
+        <v>8.1772473813449551e-09</v>
       </c>
       <c r="L5">
-        <v>-4.4555498084698835e-07</v>
+        <v>1.4277629272208715e-07</v>
       </c>
       <c r="M5">
-        <v>-1.813676760997569e-08</v>
+        <v>-2.0742673358443559e-08</v>
       </c>
       <c r="N5">
-        <v>-4.2587128415869166e-08</v>
+        <v>-4.4417070425668185e-08</v>
       </c>
       <c r="O5">
-        <v>-5.3362782066716421e-08</v>
+        <v>-5.7511358333741033e-08</v>
       </c>
       <c r="P5">
-        <v>-9.7211342333525317e-08</v>
+        <v>-9.9584726958435395e-08</v>
       </c>
       <c r="Q5">
-        <v>-3.5589737379494572e-09</v>
+        <v>-1.3023512750519646e-08</v>
       </c>
       <c r="R5">
-        <v>5.1556238432710148e-09</v>
+        <v>-2.1917872757918884e-09</v>
       </c>
       <c r="S5">
-        <v>-1.2916800895048729e-09</v>
+        <v>-2.2879595987887436e-09</v>
       </c>
       <c r="T5">
-        <v>-3.1192837767867353e-09</v>
+        <v>-1.135626081217945e-08</v>
       </c>
       <c r="U5">
-        <v>1.1404235299276586e-08</v>
+        <v>6.7051813669920668e-09</v>
       </c>
       <c r="V5">
-        <v>1.8967771427845141e-08</v>
+        <v>2.0539560819921629e-08</v>
       </c>
       <c r="W5">
-        <v>-5.4103383631268919e-09</v>
+        <v>-6.811222601876056e-09</v>
       </c>
       <c r="X5">
-        <v>2.8470515065478158e-09</v>
+        <v>-7.3035174080840374e-09</v>
       </c>
       <c r="Y5">
-        <v>2.4784389354271559e-06</v>
+        <v>2.2520893764479928e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2549,76 +2549,76 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>-0.40215590192922041</v>
+        <v>-0.40445329507655498</v>
       </c>
       <c r="C6">
-        <v>-6.9159806415700065e-06</v>
+        <v>1.2316807841300401e-05</v>
       </c>
       <c r="D6">
-        <v>1.659225433474523e-05</v>
+        <v>1.2304378202020726e-05</v>
       </c>
       <c r="E6">
-        <v>4.4775093548048516e-05</v>
+        <v>4.2941379733458038e-05</v>
       </c>
       <c r="F6">
-        <v>-1.9092117360212847e-07</v>
+        <v>-2.0853527006566698e-07</v>
       </c>
       <c r="G6">
-        <v>0.0028092678154449909</v>
+        <v>0.0024676833570865804</v>
       </c>
       <c r="H6">
-        <v>0.001385333930858524</v>
+        <v>0.0012416490308238912</v>
       </c>
       <c r="I6">
-        <v>-5.7387063380046889e-05</v>
+        <v>-5.004752773841493e-05</v>
       </c>
       <c r="J6">
-        <v>-2.8006970596586216e-05</v>
+        <v>-2.4903501124605532e-05</v>
       </c>
       <c r="K6">
-        <v>-1.1428228747573122e-05</v>
+        <v>3.0675842468176357e-06</v>
       </c>
       <c r="L6">
-        <v>-6.0332344000403756e-05</v>
+        <v>-3.2808599970423157e-05</v>
       </c>
       <c r="M6">
-        <v>-1.0566522706814078e-06</v>
+        <v>6.2998570857282109e-06</v>
       </c>
       <c r="N6">
-        <v>4.4415982986075906e-06</v>
+        <v>1.1616314376034311e-05</v>
       </c>
       <c r="O6">
-        <v>1.7965915899443305e-06</v>
+        <v>1.0634478621029562e-05</v>
       </c>
       <c r="P6">
-        <v>1.837633076279049e-05</v>
+        <v>2.3313705154268485e-05</v>
       </c>
       <c r="Q6">
-        <v>1.3598296649109354e-05</v>
+        <v>1.033380214884674e-05</v>
       </c>
       <c r="R6">
-        <v>3.3446012570931049e-07</v>
+        <v>-1.5983658163690932e-06</v>
       </c>
       <c r="S6">
-        <v>3.0979378589852233e-06</v>
+        <v>3.2841584103402222e-06</v>
       </c>
       <c r="T6">
-        <v>1.4234135488934159e-07</v>
+        <v>1.2198167281873962e-06</v>
       </c>
       <c r="U6">
-        <v>-9.657051726672173e-06</v>
+        <v>-7.1341812363080214e-06</v>
       </c>
       <c r="V6">
-        <v>-1.6736609328579967e-05</v>
+        <v>-1.6149463471300828e-05</v>
       </c>
       <c r="W6">
-        <v>6.4824673322319149e-06</v>
+        <v>3.5164232718433765e-06</v>
       </c>
       <c r="X6">
-        <v>1.0146859009114377e-05</v>
+        <v>6.1814706224520246e-06</v>
       </c>
       <c r="Y6">
-        <v>-0.0017176667705921383</v>
+        <v>-0.0015973748514898495</v>
       </c>
     </row>
     <row r="7">
@@ -2626,76 +2626,76 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-0.45801965394433925</v>
+        <v>-0.55952293906001582</v>
       </c>
       <c r="C7">
-        <v>0.00020736673415861295</v>
+        <v>0.00014361884622716918</v>
       </c>
       <c r="D7">
-        <v>-5.6122550013353312e-06</v>
+        <v>-4.7313988346049695e-06</v>
       </c>
       <c r="E7">
-        <v>3.8467759561372122e-05</v>
+        <v>4.7396015767334004e-05</v>
       </c>
       <c r="F7">
-        <v>-9.9344048452925519e-08</v>
+        <v>-2.4801098632227966e-07</v>
       </c>
       <c r="G7">
-        <v>0.001385333930858524</v>
+        <v>0.0012416490308238912</v>
       </c>
       <c r="H7">
-        <v>0.002354545014179088</v>
+        <v>0.0020375968091834659</v>
       </c>
       <c r="I7">
-        <v>-2.8009827272141567e-05</v>
+        <v>-2.4931311946448055e-05</v>
       </c>
       <c r="J7">
-        <v>-4.6816232067668888e-05</v>
+        <v>-4.0423737980276256e-05</v>
       </c>
       <c r="K7">
-        <v>-1.6319347368878732e-05</v>
+        <v>2.187496206123607e-05</v>
       </c>
       <c r="L7">
-        <v>-0.00056997044953129613</v>
+        <v>-9.3552762080917795e-05</v>
       </c>
       <c r="M7">
-        <v>5.9926171016395566e-06</v>
+        <v>6.595168468449342e-06</v>
       </c>
       <c r="N7">
-        <v>7.2397517129888693e-06</v>
+        <v>9.7102020257150727e-06</v>
       </c>
       <c r="O7">
-        <v>2.3097342580070783e-06</v>
+        <v>8.9704729425338402e-06</v>
       </c>
       <c r="P7">
-        <v>3.7842266690118836e-05</v>
+        <v>3.8080107364049523e-05</v>
       </c>
       <c r="Q7">
-        <v>1.7006070005523222e-05</v>
+        <v>1.3755952924265165e-05</v>
       </c>
       <c r="R7">
-        <v>1.1214253004292201e-05</v>
+        <v>6.0822533613291908e-06</v>
       </c>
       <c r="S7">
-        <v>-1.3339835607572016e-05</v>
+        <v>-9.8248169219184643e-06</v>
       </c>
       <c r="T7">
-        <v>-9.6056342678271775e-06</v>
+        <v>-6.5845070314333895e-06</v>
       </c>
       <c r="U7">
-        <v>-3.6630246879555746e-05</v>
+        <v>-2.6950809347737109e-05</v>
       </c>
       <c r="V7">
-        <v>-2.0791676948765986e-05</v>
+        <v>-1.6774356798898917e-05</v>
       </c>
       <c r="W7">
-        <v>1.5942545712687472e-05</v>
+        <v>1.3440128479261074e-05</v>
       </c>
       <c r="X7">
-        <v>1.282983737758712e-05</v>
+        <v>8.0929138313141475e-06</v>
       </c>
       <c r="Y7">
-        <v>-0.001641534893640093</v>
+        <v>-0.0017070767879386211</v>
       </c>
     </row>
     <row r="8">
@@ -2703,76 +2703,76 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.010630982645658406</v>
+        <v>0.0078531881034314167</v>
       </c>
       <c r="C8">
-        <v>3.3097525688243883e-09</v>
+        <v>-3.3654529133260882e-07</v>
       </c>
       <c r="D8">
-        <v>-7.2051756438039053e-07</v>
+        <v>-4.8536132895246721e-07</v>
       </c>
       <c r="E8">
-        <v>-9.2352878403446254e-07</v>
+        <v>-8.9389413889426779e-07</v>
       </c>
       <c r="F8">
-        <v>3.5606115341832966e-09</v>
+        <v>4.1153924732624663e-09</v>
       </c>
       <c r="G8">
-        <v>-5.7387063380046889e-05</v>
+        <v>-5.004752773841493e-05</v>
       </c>
       <c r="H8">
-        <v>-2.8009827272141567e-05</v>
+        <v>-2.4931311946448055e-05</v>
       </c>
       <c r="I8">
-        <v>1.2823656123542237e-06</v>
+        <v>1.1118684232665928e-06</v>
       </c>
       <c r="J8">
-        <v>6.1311620070001059e-07</v>
+        <v>5.4216338944754081e-07</v>
       </c>
       <c r="K8">
-        <v>2.3015098171596306e-07</v>
+        <v>-1.4959815778763455e-07</v>
       </c>
       <c r="L8">
-        <v>1.2263063017742003e-06</v>
+        <v>7.7595637113846023e-07</v>
       </c>
       <c r="M8">
-        <v>-6.0968424069681744e-08</v>
+        <v>-2.1086753819495792e-07</v>
       </c>
       <c r="N8">
-        <v>-1.0139020786646742e-07</v>
+        <v>-2.9243053409817955e-07</v>
       </c>
       <c r="O8">
-        <v>1.9437373507396579e-07</v>
+        <v>-7.754482250792062e-08</v>
       </c>
       <c r="P8">
-        <v>-4.7402737994483427e-08</v>
+        <v>-2.4438220384864619e-07</v>
       </c>
       <c r="Q8">
-        <v>-2.3188828964921934e-07</v>
+        <v>-1.7597343318703924e-07</v>
       </c>
       <c r="R8">
-        <v>2.0222481588391114e-07</v>
+        <v>2.0023807243427352e-07</v>
       </c>
       <c r="S8">
-        <v>-1.3976972193366799e-07</v>
+        <v>-1.4347763511109743e-07</v>
       </c>
       <c r="T8">
-        <v>-4.96494742982345e-08</v>
+        <v>-7.8919752797592873e-08</v>
       </c>
       <c r="U8">
-        <v>1.1420549954854578e-07</v>
+        <v>6.7134884473391549e-08</v>
       </c>
       <c r="V8">
-        <v>2.3154987275362712e-07</v>
+        <v>2.489725370848461e-07</v>
       </c>
       <c r="W8">
-        <v>-1.5242565842766108e-07</v>
+        <v>-8.9457257439142707e-08</v>
       </c>
       <c r="X8">
-        <v>-1.3822898401567202e-07</v>
+        <v>-9.0324261697324879e-08</v>
       </c>
       <c r="Y8">
-        <v>3.4119827807001024e-05</v>
+        <v>3.1810528837995031e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2780,76 +2780,76 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>0.0086888111991849475</v>
+        <v>0.0080208465668391727</v>
       </c>
       <c r="C9">
-        <v>-3.9889513541697308e-06</v>
+        <v>-2.7787692507174424e-06</v>
       </c>
       <c r="D9">
-        <v>-5.2305558349983376e-07</v>
+        <v>-3.6189512696978139e-07</v>
       </c>
       <c r="E9">
-        <v>-7.6994277698212685e-07</v>
+        <v>-9.5176883071592331e-07</v>
       </c>
       <c r="F9">
-        <v>1.473734371004006e-09</v>
+        <v>4.5961776018602967e-09</v>
       </c>
       <c r="G9">
-        <v>-2.8006970596586216e-05</v>
+        <v>-2.4903501124605532e-05</v>
       </c>
       <c r="H9">
-        <v>-4.6816232067668888e-05</v>
+        <v>-4.0423737980276256e-05</v>
       </c>
       <c r="I9">
-        <v>6.1311620070001059e-07</v>
+        <v>5.4216338944754081e-07</v>
       </c>
       <c r="J9">
-        <v>1.0110165189889259e-06</v>
+        <v>8.7344236838964641e-07</v>
       </c>
       <c r="K9">
-        <v>2.7627077212290344e-07</v>
+        <v>-5.5213885212638789e-07</v>
       </c>
       <c r="L9">
-        <v>1.0771681665320797e-05</v>
+        <v>1.9192673242762582e-06</v>
       </c>
       <c r="M9">
-        <v>-1.7037559348692194e-07</v>
+        <v>-1.8240829761097256e-07</v>
       </c>
       <c r="N9">
-        <v>-3.4626067462249874e-08</v>
+        <v>-1.3375345390145304e-07</v>
       </c>
       <c r="O9">
-        <v>4.8762065098008017e-07</v>
+        <v>2.3673839023044497e-07</v>
       </c>
       <c r="P9">
-        <v>-1.0748778501240509e-08</v>
+        <v>-1.5338639367471443e-07</v>
       </c>
       <c r="Q9">
-        <v>-1.3740885584091291e-07</v>
+        <v>-1.0494553494808636e-07</v>
       </c>
       <c r="R9">
-        <v>2.5273990251856378e-07</v>
+        <v>2.8374691822122306e-07</v>
       </c>
       <c r="S9">
-        <v>-6.6261763486728533e-08</v>
+        <v>-1.0341255561561333e-07</v>
       </c>
       <c r="T9">
-        <v>2.4506734068147263e-07</v>
+        <v>1.7205688342084376e-07</v>
       </c>
       <c r="U9">
-        <v>4.7437413414241964e-07</v>
+        <v>2.9814959143307689e-07</v>
       </c>
       <c r="V9">
-        <v>3.4264700537060355e-07</v>
+        <v>2.8503368931597679e-07</v>
       </c>
       <c r="W9">
-        <v>-2.47302376772063e-07</v>
+        <v>-2.3589796548736957e-07</v>
       </c>
       <c r="X9">
-        <v>-7.2897794159852285e-08</v>
+        <v>-5.2446991717774343e-08</v>
       </c>
       <c r="Y9">
-        <v>3.1628269683129238e-05</v>
+        <v>3.3037982872207643e-05</v>
       </c>
     </row>
     <row r="10">
@@ -2857,76 +2857,76 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>0.15410316476893779</v>
+        <v>0.20605154236790166</v>
       </c>
       <c r="C10">
-        <v>2.1181623876570087e-05</v>
+        <v>2.9299995597658994e-05</v>
       </c>
       <c r="D10">
-        <v>1.8908203754649223e-05</v>
+        <v>1.3554640395691092e-05</v>
       </c>
       <c r="E10">
-        <v>-1.2594004191337129e-05</v>
+        <v>-4.6891523105274465e-06</v>
       </c>
       <c r="F10">
-        <v>1.0115109968394638e-07</v>
+        <v>8.1772473813449551e-09</v>
       </c>
       <c r="G10">
-        <v>-1.1428228747573122e-05</v>
+        <v>3.0675842468176357e-06</v>
       </c>
       <c r="H10">
-        <v>-1.6319347368878732e-05</v>
+        <v>2.187496206123607e-05</v>
       </c>
       <c r="I10">
-        <v>2.3015098171596306e-07</v>
+        <v>-1.4959815778763455e-07</v>
       </c>
       <c r="J10">
-        <v>2.7627077212290344e-07</v>
+        <v>-5.5213885212638789e-07</v>
       </c>
       <c r="K10">
-        <v>0.00019427740912200949</v>
+        <v>0.00023008369371460257</v>
       </c>
       <c r="L10">
-        <v>-3.9218961996986305e-05</v>
+        <v>-0.00011035552383841623</v>
       </c>
       <c r="M10">
-        <v>-7.6004769005007201e-06</v>
+        <v>-7.0570154316241152e-06</v>
       </c>
       <c r="N10">
-        <v>-1.218270947647014e-05</v>
+        <v>-8.1620334106983963e-06</v>
       </c>
       <c r="O10">
-        <v>-1.8584357651659845e-05</v>
+        <v>-1.135505270575036e-05</v>
       </c>
       <c r="P10">
-        <v>-1.9633909771095949e-05</v>
+        <v>-1.2200835958301007e-05</v>
       </c>
       <c r="Q10">
-        <v>-1.5982326030038879e-06</v>
+        <v>1.5913325136274265e-06</v>
       </c>
       <c r="R10">
-        <v>-6.1145754506021908e-06</v>
+        <v>-3.9312042216032015e-06</v>
       </c>
       <c r="S10">
-        <v>-7.1006594844046298e-07</v>
+        <v>4.8638431624895905e-07</v>
       </c>
       <c r="T10">
-        <v>-5.254379638952359e-06</v>
+        <v>-2.4263538692595373e-06</v>
       </c>
       <c r="U10">
-        <v>-8.2404119105670048e-06</v>
+        <v>-4.0107813510467981e-06</v>
       </c>
       <c r="V10">
-        <v>4.9793400878022437e-06</v>
+        <v>2.8524696327124353e-06</v>
       </c>
       <c r="W10">
-        <v>2.9848961278604991e-06</v>
+        <v>2.7034192129034835e-06</v>
       </c>
       <c r="X10">
-        <v>6.4606430594300683e-06</v>
+        <v>8.1932214358755726e-06</v>
       </c>
       <c r="Y10">
-        <v>0.00024292610784200461</v>
+        <v>0.0001003666649968226</v>
       </c>
     </row>
     <row r="11">
@@ -2934,76 +2934,76 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>-0.56950909896412427</v>
+        <v>-0.071142389713377746</v>
       </c>
       <c r="C11">
-        <v>-0.00028683737752833061</v>
+        <v>-3.0593206335037479e-05</v>
       </c>
       <c r="D11">
-        <v>1.2143907099235864e-05</v>
+        <v>3.0899032643850771e-06</v>
       </c>
       <c r="E11">
-        <v>3.841691273959718e-05</v>
+        <v>-1.1340096863135722e-05</v>
       </c>
       <c r="F11">
-        <v>-4.4555498084698835e-07</v>
+        <v>1.4277629272208715e-07</v>
       </c>
       <c r="G11">
-        <v>-6.0332344000403756e-05</v>
+        <v>-3.2808599970423157e-05</v>
       </c>
       <c r="H11">
-        <v>-0.00056997044953129613</v>
+        <v>-9.3552762080917795e-05</v>
       </c>
       <c r="I11">
-        <v>1.2263063017742003e-06</v>
+        <v>7.7595637113846023e-07</v>
       </c>
       <c r="J11">
-        <v>1.0771681665320797e-05</v>
+        <v>1.9192673242762582e-06</v>
       </c>
       <c r="K11">
-        <v>-3.9218961996986305e-05</v>
+        <v>-0.00011035552383841623</v>
       </c>
       <c r="L11">
-        <v>0.003321068015656548</v>
+        <v>0.00021361871890326719</v>
       </c>
       <c r="M11">
-        <v>1.9473030651958505e-06</v>
+        <v>-4.6401978890251903e-07</v>
       </c>
       <c r="N11">
-        <v>8.7244270353972167e-06</v>
+        <v>-5.2916737142418794e-06</v>
       </c>
       <c r="O11">
-        <v>1.4742824534149821e-05</v>
+        <v>-9.897401144103683e-06</v>
       </c>
       <c r="P11">
-        <v>9.7135696694266552e-06</v>
+        <v>-1.1154289291371927e-05</v>
       </c>
       <c r="Q11">
-        <v>-1.562448986181933e-05</v>
+        <v>-6.4484341091051955e-06</v>
       </c>
       <c r="R11">
-        <v>-1.0956883040093351e-05</v>
+        <v>-3.4091826417708757e-06</v>
       </c>
       <c r="S11">
-        <v>5.4065448195434943e-06</v>
+        <v>-2.4618847921282577e-06</v>
       </c>
       <c r="T11">
-        <v>-6.754186885884511e-06</v>
+        <v>-4.6965827888657116e-06</v>
       </c>
       <c r="U11">
-        <v>8.2211571203110157e-06</v>
+        <v>-5.4452538270770068e-06</v>
       </c>
       <c r="V11">
-        <v>1.4671527136994214e-05</v>
+        <v>4.3054478666509737e-06</v>
       </c>
       <c r="W11">
-        <v>-7.4309136767208855e-06</v>
+        <v>-3.2083549705464349e-06</v>
       </c>
       <c r="X11">
-        <v>-2.9111968417128596e-05</v>
+        <v>-7.1832783393610755e-06</v>
       </c>
       <c r="Y11">
-        <v>-0.00071992333683462348</v>
+        <v>0.00020857984561314282</v>
       </c>
     </row>
     <row r="12">
@@ -3011,76 +3011,76 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>0.22774479455038815</v>
+        <v>0.16627566388520262</v>
       </c>
       <c r="C12">
-        <v>-2.5807732715972184e-06</v>
+        <v>8.1451424063230457e-07</v>
       </c>
       <c r="D12">
-        <v>5.5022057819434356e-06</v>
+        <v>6.1584748857115287e-06</v>
       </c>
       <c r="E12">
-        <v>1.4913293897839792e-06</v>
+        <v>1.7972441888854037e-06</v>
       </c>
       <c r="F12">
-        <v>-1.813676760997569e-08</v>
+        <v>-2.0742673358443559e-08</v>
       </c>
       <c r="G12">
-        <v>-1.0566522706814078e-06</v>
+        <v>6.2998570857282109e-06</v>
       </c>
       <c r="H12">
-        <v>5.9926171016395566e-06</v>
+        <v>6.595168468449342e-06</v>
       </c>
       <c r="I12">
-        <v>-6.0968424069681744e-08</v>
+        <v>-2.1086753819495792e-07</v>
       </c>
       <c r="J12">
-        <v>-1.7037559348692194e-07</v>
+        <v>-1.8240829761097256e-07</v>
       </c>
       <c r="K12">
-        <v>-7.6004769005007201e-06</v>
+        <v>-7.0570154316241152e-06</v>
       </c>
       <c r="L12">
-        <v>1.9473030651958505e-06</v>
+        <v>-4.6401978890251903e-07</v>
       </c>
       <c r="M12">
-        <v>0.0057745760910762611</v>
+        <v>0.0047403022034546195</v>
       </c>
       <c r="N12">
-        <v>0.0047819014267983006</v>
+        <v>0.0038930219198128249</v>
       </c>
       <c r="O12">
-        <v>0.0047801769777425594</v>
+        <v>0.0038916340266215701</v>
       </c>
       <c r="P12">
-        <v>0.0047779856725034993</v>
+        <v>0.00388982212086435</v>
       </c>
       <c r="Q12">
-        <v>1.1759698693194616e-05</v>
+        <v>9.8135710890202127e-06</v>
       </c>
       <c r="R12">
-        <v>8.9742904114076624e-06</v>
+        <v>5.4467675971230724e-06</v>
       </c>
       <c r="S12">
-        <v>1.912798683664904e-07</v>
+        <v>-1.3079083319450394e-06</v>
       </c>
       <c r="T12">
-        <v>4.095404382028887e-06</v>
+        <v>2.9265692149753987e-06</v>
       </c>
       <c r="U12">
-        <v>1.2345215254236423e-05</v>
+        <v>7.136691153376414e-06</v>
       </c>
       <c r="V12">
-        <v>2.0123675183939937e-06</v>
+        <v>2.6182428855198913e-06</v>
       </c>
       <c r="W12">
-        <v>-9.3463584703514809e-07</v>
+        <v>-1.3556909987937132e-06</v>
       </c>
       <c r="X12">
-        <v>-4.921581141314747e-06</v>
+        <v>-4.9414103891404907e-06</v>
       </c>
       <c r="Y12">
-        <v>-0.0048079674914148617</v>
+        <v>-0.0039260031461625022</v>
       </c>
     </row>
     <row r="13">
@@ -3088,76 +3088,76 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>0.65215086724084803</v>
+        <v>0.61625138071883057</v>
       </c>
       <c r="C13">
-        <v>2.2449223507265445e-06</v>
+        <v>5.2516755494281457e-06</v>
       </c>
       <c r="D13">
-        <v>1.0633711617590407e-05</v>
+        <v>8.7362210170806128e-06</v>
       </c>
       <c r="E13">
-        <v>3.7773045482607974e-06</v>
+        <v>3.9677836071922204e-06</v>
       </c>
       <c r="F13">
-        <v>-4.2587128415869166e-08</v>
+        <v>-4.4417070425668185e-08</v>
       </c>
       <c r="G13">
-        <v>4.4415982986075906e-06</v>
+        <v>1.1616314376034311e-05</v>
       </c>
       <c r="H13">
-        <v>7.2397517129888693e-06</v>
+        <v>9.7102020257150727e-06</v>
       </c>
       <c r="I13">
-        <v>-1.0139020786646742e-07</v>
+        <v>-2.9243053409817955e-07</v>
       </c>
       <c r="J13">
-        <v>-3.4626067462249874e-08</v>
+        <v>-1.3375345390145304e-07</v>
       </c>
       <c r="K13">
-        <v>-1.218270947647014e-05</v>
+        <v>-8.1620334106983963e-06</v>
       </c>
       <c r="L13">
-        <v>8.7244270353972167e-06</v>
+        <v>-5.2916737142418794e-06</v>
       </c>
       <c r="M13">
-        <v>0.0047819014267983006</v>
+        <v>0.0038930219198128249</v>
       </c>
       <c r="N13">
-        <v>0.0049658196652320897</v>
+        <v>0.0040531068044618156</v>
       </c>
       <c r="O13">
-        <v>0.0047839502503286679</v>
+        <v>0.003894609859351444</v>
       </c>
       <c r="P13">
-        <v>0.004784049861645729</v>
+        <v>0.0038948225549202192</v>
       </c>
       <c r="Q13">
-        <v>4.9598564429616796e-06</v>
+        <v>4.4224526467484451e-06</v>
       </c>
       <c r="R13">
-        <v>-1.2959440681927956e-06</v>
+        <v>-3.0855684194046595e-06</v>
       </c>
       <c r="S13">
-        <v>-1.2175125501668219e-05</v>
+        <v>-1.0996434993788847e-05</v>
       </c>
       <c r="T13">
-        <v>-4.0842236171308583e-06</v>
+        <v>-4.0316322069063894e-06</v>
       </c>
       <c r="U13">
-        <v>3.4655904526250205e-07</v>
+        <v>-3.130433976287556e-06</v>
       </c>
       <c r="V13">
-        <v>-9.0407583303293799e-06</v>
+        <v>-8.8040636403090522e-06</v>
       </c>
       <c r="W13">
-        <v>-2.1683503841257326e-06</v>
+        <v>-2.9113400901915666e-06</v>
       </c>
       <c r="X13">
-        <v>-6.5375264993869841e-06</v>
+        <v>-6.5313501605727725e-06</v>
       </c>
       <c r="Y13">
-        <v>-0.0048550492459284288</v>
+        <v>-0.0039684595616753726</v>
       </c>
     </row>
     <row r="14">
@@ -3165,76 +3165,76 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0.87253001618960668</v>
+        <v>0.85196728271191591</v>
       </c>
       <c r="C14">
-        <v>1.1131559091931821e-05</v>
+        <v>1.3574403627642298e-05</v>
       </c>
       <c r="D14">
-        <v>2.0418435026734166e-05</v>
+        <v>1.6296170461959572e-05</v>
       </c>
       <c r="E14">
-        <v>5.7320576508925695e-06</v>
+        <v>5.9906863780168437e-06</v>
       </c>
       <c r="F14">
-        <v>-5.3362782066716421e-08</v>
+        <v>-5.7511358333741033e-08</v>
       </c>
       <c r="G14">
-        <v>1.7965915899443305e-06</v>
+        <v>1.0634478621029562e-05</v>
       </c>
       <c r="H14">
-        <v>2.3097342580070783e-06</v>
+        <v>8.9704729425338402e-06</v>
       </c>
       <c r="I14">
-        <v>1.9437373507396579e-07</v>
+        <v>-7.754482250792062e-08</v>
       </c>
       <c r="J14">
-        <v>4.8762065098008017e-07</v>
+        <v>2.3673839023044497e-07</v>
       </c>
       <c r="K14">
-        <v>-1.8584357651659845e-05</v>
+        <v>-1.135505270575036e-05</v>
       </c>
       <c r="L14">
-        <v>1.4742824534149821e-05</v>
+        <v>-9.897401144103683e-06</v>
       </c>
       <c r="M14">
-        <v>0.0047801769777425594</v>
+        <v>0.0038916340266215701</v>
       </c>
       <c r="N14">
-        <v>0.0047839502503286679</v>
+        <v>0.003894609859351444</v>
       </c>
       <c r="O14">
-        <v>0.0048474915402331956</v>
+        <v>0.0039514114708592493</v>
       </c>
       <c r="P14">
-        <v>0.0048066575561497823</v>
+        <v>0.0039142311181402717</v>
       </c>
       <c r="Q14">
-        <v>1.1254154947917979e-06</v>
+        <v>1.4373122825228862e-06</v>
       </c>
       <c r="R14">
-        <v>-7.4310610776348563e-06</v>
+        <v>-6.7394280491303658e-06</v>
       </c>
       <c r="S14">
-        <v>-1.6593664541966332e-05</v>
+        <v>-1.463974879293817e-05</v>
       </c>
       <c r="T14">
-        <v>-6.2250385280830157e-06</v>
+        <v>-4.8628611382178034e-06</v>
       </c>
       <c r="U14">
-        <v>-2.0656496600463415e-06</v>
+        <v>-5.2237151995880842e-06</v>
       </c>
       <c r="V14">
-        <v>-2.3247995583761593e-06</v>
+        <v>-1.8005579362521338e-06</v>
       </c>
       <c r="W14">
-        <v>-2.80883941783318e-06</v>
+        <v>-4.4401585189376866e-06</v>
       </c>
       <c r="X14">
-        <v>-2.7427582930699747e-06</v>
+        <v>-3.9346942739277752e-06</v>
       </c>
       <c r="Y14">
-        <v>-0.0049391848959026525</v>
+        <v>-0.0040473251642220553</v>
       </c>
     </row>
     <row r="15">
@@ -3242,76 +3242,76 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>0.88846439281509948</v>
+        <v>0.87867284981098215</v>
       </c>
       <c r="C15">
-        <v>9.0443193928869113e-06</v>
+        <v>1.0409829902196513e-05</v>
       </c>
       <c r="D15">
-        <v>2.5592259870643269e-05</v>
+        <v>2.0649284692382934e-05</v>
       </c>
       <c r="E15">
-        <v>1.1524196383877076e-05</v>
+        <v>1.1405668610090365e-05</v>
       </c>
       <c r="F15">
-        <v>-9.7211342333525317e-08</v>
+        <v>-9.9584726958435395e-08</v>
       </c>
       <c r="G15">
-        <v>1.837633076279049e-05</v>
+        <v>2.3313705154268485e-05</v>
       </c>
       <c r="H15">
-        <v>3.7842266690118836e-05</v>
+        <v>3.8080107364049523e-05</v>
       </c>
       <c r="I15">
-        <v>-4.7402737994483427e-08</v>
+        <v>-2.4438220384864619e-07</v>
       </c>
       <c r="J15">
-        <v>-1.0748778501240509e-08</v>
+        <v>-1.5338639367471443e-07</v>
       </c>
       <c r="K15">
-        <v>-1.9633909771095949e-05</v>
+        <v>-1.2200835958301007e-05</v>
       </c>
       <c r="L15">
-        <v>9.7135696694266552e-06</v>
+        <v>-1.1154289291371927e-05</v>
       </c>
       <c r="M15">
-        <v>0.0047779856725034993</v>
+        <v>0.00388982212086435</v>
       </c>
       <c r="N15">
-        <v>0.004784049861645729</v>
+        <v>0.0038948225549202192</v>
       </c>
       <c r="O15">
-        <v>0.0048066575561497823</v>
+        <v>0.0039142311181402717</v>
       </c>
       <c r="P15">
-        <v>0.0050050684359274162</v>
+        <v>0.0040976458269792373</v>
       </c>
       <c r="Q15">
-        <v>-4.6164957813229758e-06</v>
+        <v>-2.74113629743431e-06</v>
       </c>
       <c r="R15">
-        <v>-1.5689504152163422e-05</v>
+        <v>-1.369519334991702e-05</v>
       </c>
       <c r="S15">
-        <v>-1.9026374733207223e-05</v>
+        <v>-1.6902907372494234e-05</v>
       </c>
       <c r="T15">
-        <v>-1.9198716051258179e-05</v>
+        <v>-1.5663377653003625e-05</v>
       </c>
       <c r="U15">
-        <v>-1.3879248732277458e-05</v>
+        <v>-1.4907747462991578e-05</v>
       </c>
       <c r="V15">
-        <v>-1.4121242175962859e-05</v>
+        <v>-1.1334228750512927e-05</v>
       </c>
       <c r="W15">
-        <v>-7.3103236347676152e-06</v>
+        <v>-8.9437289691714801e-06</v>
       </c>
       <c r="X15">
-        <v>-5.1111078295608531e-06</v>
+        <v>-5.8095064108495878e-06</v>
       </c>
       <c r="Y15">
-        <v>-0.0051160007903314157</v>
+        <v>-0.0042099395338169848</v>
       </c>
     </row>
     <row r="16">
@@ -3319,76 +3319,76 @@
         <v>36</v>
       </c>
       <c r="B16">
-        <v>0.035772240868528857</v>
+        <v>0.06523109340489297</v>
       </c>
       <c r="C16">
-        <v>7.2456559364568627e-06</v>
+        <v>4.7139542634746805e-06</v>
       </c>
       <c r="D16">
-        <v>7.5294385777120658e-06</v>
+        <v>5.6289877470251649e-06</v>
       </c>
       <c r="E16">
-        <v>3.5215394732287934e-07</v>
+        <v>1.1376983638802547e-06</v>
       </c>
       <c r="F16">
-        <v>-3.5589737379494572e-09</v>
+        <v>-1.3023512750519646e-08</v>
       </c>
       <c r="G16">
-        <v>1.3598296649109354e-05</v>
+        <v>1.033380214884674e-05</v>
       </c>
       <c r="H16">
-        <v>1.7006070005523222e-05</v>
+        <v>1.3755952924265165e-05</v>
       </c>
       <c r="I16">
-        <v>-2.3188828964921934e-07</v>
+        <v>-1.7597343318703924e-07</v>
       </c>
       <c r="J16">
-        <v>-1.3740885584091291e-07</v>
+        <v>-1.0494553494808636e-07</v>
       </c>
       <c r="K16">
-        <v>-1.5982326030038879e-06</v>
+        <v>1.5913325136274265e-06</v>
       </c>
       <c r="L16">
-        <v>-1.562448986181933e-05</v>
+        <v>-6.4484341091051955e-06</v>
       </c>
       <c r="M16">
-        <v>1.1759698693194616e-05</v>
+        <v>9.8135710890202127e-06</v>
       </c>
       <c r="N16">
-        <v>4.9598564429616796e-06</v>
+        <v>4.4224526467484451e-06</v>
       </c>
       <c r="O16">
-        <v>1.1254154947917979e-06</v>
+        <v>1.4373122825228862e-06</v>
       </c>
       <c r="P16">
-        <v>-4.6164957813229758e-06</v>
+        <v>-2.74113629743431e-06</v>
       </c>
       <c r="Q16">
-        <v>0.00046398720800014214</v>
+        <v>0.00042832217986366234</v>
       </c>
       <c r="R16">
-        <v>0.00024828944271723316</v>
+        <v>0.00022708055567406265</v>
       </c>
       <c r="S16">
-        <v>0.00024480097573438352</v>
+        <v>0.00022450465058317809</v>
       </c>
       <c r="T16">
-        <v>0.00024671949046909449</v>
+        <v>0.00022604538442442789</v>
       </c>
       <c r="U16">
-        <v>0.00024475710751927123</v>
+        <v>0.00022456941302367904</v>
       </c>
       <c r="V16">
-        <v>0.00024477806859044958</v>
+        <v>0.00022432489412153934</v>
       </c>
       <c r="W16">
-        <v>5.5001110873580757e-06</v>
+        <v>5.2792927337328599e-06</v>
       </c>
       <c r="X16">
-        <v>4.7524926420566386e-06</v>
+        <v>4.4121196453801455e-06</v>
       </c>
       <c r="Y16">
-        <v>-0.00026285859601497033</v>
+        <v>-0.00025535226197773018</v>
       </c>
     </row>
     <row r="17">
@@ -3396,76 +3396,76 @@
         <v>37</v>
       </c>
       <c r="B17">
-        <v>-0.047961207944290325</v>
+        <v>-0.0062842375936854817</v>
       </c>
       <c r="C17">
-        <v>4.6786959759314729e-06</v>
+        <v>1.475789271907036e-06</v>
       </c>
       <c r="D17">
-        <v>5.8498764915852253e-06</v>
+        <v>4.9529091190151011e-06</v>
       </c>
       <c r="E17">
-        <v>-4.788584723277864e-07</v>
+        <v>1.3520636707573905e-07</v>
       </c>
       <c r="F17">
-        <v>5.1556238432710148e-09</v>
+        <v>-2.1917872757918884e-09</v>
       </c>
       <c r="G17">
-        <v>3.3446012570931049e-07</v>
+        <v>-1.5983658163690932e-06</v>
       </c>
       <c r="H17">
-        <v>1.1214253004292201e-05</v>
+        <v>6.0822533613291908e-06</v>
       </c>
       <c r="I17">
-        <v>2.0222481588391114e-07</v>
+        <v>2.0023807243427352e-07</v>
       </c>
       <c r="J17">
-        <v>2.5273990251856378e-07</v>
+        <v>2.8374691822122306e-07</v>
       </c>
       <c r="K17">
-        <v>-6.1145754506021908e-06</v>
+        <v>-3.9312042216032015e-06</v>
       </c>
       <c r="L17">
-        <v>-1.0956883040093351e-05</v>
+        <v>-3.4091826417708757e-06</v>
       </c>
       <c r="M17">
-        <v>8.9742904114076624e-06</v>
+        <v>5.4467675971230724e-06</v>
       </c>
       <c r="N17">
-        <v>-1.2959440681927956e-06</v>
+        <v>-3.0855684194046595e-06</v>
       </c>
       <c r="O17">
-        <v>-7.4310610776348563e-06</v>
+        <v>-6.7394280491303658e-06</v>
       </c>
       <c r="P17">
-        <v>-1.5689504152163422e-05</v>
+        <v>-1.369519334991702e-05</v>
       </c>
       <c r="Q17">
-        <v>0.00024828944271723316</v>
+        <v>0.00022708055567406265</v>
       </c>
       <c r="R17">
-        <v>0.00055755697618271069</v>
+        <v>0.00051200281380742239</v>
       </c>
       <c r="S17">
-        <v>0.00024404471236330036</v>
+        <v>0.00022382136463458909</v>
       </c>
       <c r="T17">
-        <v>0.00024748082554298012</v>
+        <v>0.00022654064949469355</v>
       </c>
       <c r="U17">
-        <v>0.00024495755623901483</v>
+        <v>0.00022464497208162524</v>
       </c>
       <c r="V17">
-        <v>0.00024503011586069824</v>
+        <v>0.0002246568224508247</v>
       </c>
       <c r="W17">
-        <v>8.3710227685053373e-07</v>
+        <v>1.8032814053186563e-06</v>
       </c>
       <c r="X17">
-        <v>-7.2203952460360568e-06</v>
+        <v>-5.1379565714724444e-06</v>
       </c>
       <c r="Y17">
-        <v>-0.00023944567755706451</v>
+        <v>-0.00022862382284855395</v>
       </c>
     </row>
     <row r="18">
@@ -3473,76 +3473,76 @@
         <v>38</v>
       </c>
       <c r="B18">
-        <v>-0.0099586383628289168</v>
+        <v>-0.014430187908926735</v>
       </c>
       <c r="C18">
-        <v>4.4968088864321487e-06</v>
+        <v>5.0773710577164088e-06</v>
       </c>
       <c r="D18">
-        <v>3.461372794127233e-06</v>
+        <v>3.7391885805211703e-06</v>
       </c>
       <c r="E18">
-        <v>3.1799205785004463e-07</v>
+        <v>3.856358699013978e-07</v>
       </c>
       <c r="F18">
-        <v>-1.2916800895048729e-09</v>
+        <v>-2.2879595987887436e-09</v>
       </c>
       <c r="G18">
-        <v>3.0979378589852233e-06</v>
+        <v>3.2841584103402222e-06</v>
       </c>
       <c r="H18">
-        <v>-1.3339835607572016e-05</v>
+        <v>-9.8248169219184643e-06</v>
       </c>
       <c r="I18">
-        <v>-1.3976972193366799e-07</v>
+        <v>-1.4347763511109743e-07</v>
       </c>
       <c r="J18">
-        <v>-6.6261763486728533e-08</v>
+        <v>-1.0341255561561333e-07</v>
       </c>
       <c r="K18">
-        <v>-7.1006594844046298e-07</v>
+        <v>4.8638431624895905e-07</v>
       </c>
       <c r="L18">
-        <v>5.4065448195434943e-06</v>
+        <v>-2.4618847921282577e-06</v>
       </c>
       <c r="M18">
-        <v>1.912798683664904e-07</v>
+        <v>-1.3079083319450394e-06</v>
       </c>
       <c r="N18">
-        <v>-1.2175125501668219e-05</v>
+        <v>-1.0996434993788847e-05</v>
       </c>
       <c r="O18">
-        <v>-1.6593664541966332e-05</v>
+        <v>-1.463974879293817e-05</v>
       </c>
       <c r="P18">
-        <v>-1.9026374733207223e-05</v>
+        <v>-1.6902907372494234e-05</v>
       </c>
       <c r="Q18">
-        <v>0.00024480097573438352</v>
+        <v>0.00022450465058317809</v>
       </c>
       <c r="R18">
-        <v>0.00024404471236330036</v>
+        <v>0.00022382136463458909</v>
       </c>
       <c r="S18">
-        <v>0.00044036551939691324</v>
+        <v>0.00040226629257242226</v>
       </c>
       <c r="T18">
-        <v>0.00024576202309815984</v>
+        <v>0.00022529362316647266</v>
       </c>
       <c r="U18">
-        <v>0.00024751315721820459</v>
+        <v>0.00022688816140487367</v>
       </c>
       <c r="V18">
-        <v>0.00024604668432688892</v>
+        <v>0.0002253067882303158</v>
       </c>
       <c r="W18">
-        <v>-2.3909358245420085e-06</v>
+        <v>-1.5058069435629418e-06</v>
       </c>
       <c r="X18">
-        <v>-1.2412780384941919e-06</v>
+        <v>-9.74592210611528e-07</v>
       </c>
       <c r="Y18">
-        <v>-0.00023469585957665515</v>
+        <v>-0.00021770546718838539</v>
       </c>
     </row>
     <row r="19">
@@ -3550,76 +3550,76 @@
         <v>39</v>
       </c>
       <c r="B19">
-        <v>0.021573077040099933</v>
+        <v>0.053105085497117378</v>
       </c>
       <c r="C19">
-        <v>5.5963377198540407e-06</v>
+        <v>5.0413155862304047e-06</v>
       </c>
       <c r="D19">
-        <v>3.6105993138311025e-06</v>
+        <v>2.8678310875438164e-06</v>
       </c>
       <c r="E19">
-        <v>3.3620727800952382e-07</v>
+        <v>1.0623117599141848e-06</v>
       </c>
       <c r="F19">
-        <v>-3.1192837767867353e-09</v>
+        <v>-1.135626081217945e-08</v>
       </c>
       <c r="G19">
-        <v>1.4234135488934159e-07</v>
+        <v>1.2198167281873962e-06</v>
       </c>
       <c r="H19">
-        <v>-9.6056342678271775e-06</v>
+        <v>-6.5845070314333895e-06</v>
       </c>
       <c r="I19">
-        <v>-4.96494742982345e-08</v>
+        <v>-7.8919752797592873e-08</v>
       </c>
       <c r="J19">
-        <v>2.4506734068147263e-07</v>
+        <v>1.7205688342084376e-07</v>
       </c>
       <c r="K19">
-        <v>-5.254379638952359e-06</v>
+        <v>-2.4263538692595373e-06</v>
       </c>
       <c r="L19">
-        <v>-6.754186885884511e-06</v>
+        <v>-4.6965827888657116e-06</v>
       </c>
       <c r="M19">
-        <v>4.095404382028887e-06</v>
+        <v>2.9265692149753987e-06</v>
       </c>
       <c r="N19">
-        <v>-4.0842236171308583e-06</v>
+        <v>-4.0316322069063894e-06</v>
       </c>
       <c r="O19">
-        <v>-6.2250385280830157e-06</v>
+        <v>-4.8628611382178034e-06</v>
       </c>
       <c r="P19">
-        <v>-1.9198716051258179e-05</v>
+        <v>-1.5663377653003625e-05</v>
       </c>
       <c r="Q19">
-        <v>0.00024671949046909449</v>
+        <v>0.00022604538442442789</v>
       </c>
       <c r="R19">
-        <v>0.00024748082554298012</v>
+        <v>0.00022654064949469355</v>
       </c>
       <c r="S19">
-        <v>0.00024576202309815984</v>
+        <v>0.00022529362316647266</v>
       </c>
       <c r="T19">
-        <v>0.00038740668546035197</v>
+        <v>0.00034869245399130034</v>
       </c>
       <c r="U19">
-        <v>0.00024680956801047054</v>
+        <v>0.00022618966129471629</v>
       </c>
       <c r="V19">
-        <v>0.00024622155425128937</v>
+        <v>0.00022547167070155024</v>
       </c>
       <c r="W19">
-        <v>8.1393119473376692e-06</v>
+        <v>9.5411654398226646e-06</v>
       </c>
       <c r="X19">
-        <v>5.4295910347743422e-06</v>
+        <v>7.2317327120563419e-06</v>
       </c>
       <c r="Y19">
-        <v>-0.00024633193862060818</v>
+        <v>-0.0002415196802777973</v>
       </c>
     </row>
     <row r="20">
@@ -3627,76 +3627,76 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <v>-0.090261766173713412</v>
+        <v>-0.084363934370389013</v>
       </c>
       <c r="C20">
-        <v>-3.7407432588798661e-06</v>
+        <v>-5.5285281196880353e-07</v>
       </c>
       <c r="D20">
-        <v>-5.2066045992323442e-06</v>
+        <v>-3.6402324597503306e-06</v>
       </c>
       <c r="E20">
-        <v>-7.8068490041055079e-07</v>
+        <v>-3.9097935948372816e-07</v>
       </c>
       <c r="F20">
-        <v>1.1404235299276586e-08</v>
+        <v>6.7051813669920668e-09</v>
       </c>
       <c r="G20">
-        <v>-9.657051726672173e-06</v>
+        <v>-7.1341812363080214e-06</v>
       </c>
       <c r="H20">
-        <v>-3.6630246879555746e-05</v>
+        <v>-2.6950809347737109e-05</v>
       </c>
       <c r="I20">
-        <v>1.1420549954854578e-07</v>
+        <v>6.7134884473391549e-08</v>
       </c>
       <c r="J20">
-        <v>4.7437413414241964e-07</v>
+        <v>2.9814959143307689e-07</v>
       </c>
       <c r="K20">
-        <v>-8.2404119105670048e-06</v>
+        <v>-4.0107813510467981e-06</v>
       </c>
       <c r="L20">
-        <v>8.2211571203110157e-06</v>
+        <v>-5.4452538270770068e-06</v>
       </c>
       <c r="M20">
-        <v>1.2345215254236423e-05</v>
+        <v>7.136691153376414e-06</v>
       </c>
       <c r="N20">
-        <v>3.4655904526250205e-07</v>
+        <v>-3.130433976287556e-06</v>
       </c>
       <c r="O20">
-        <v>-2.0656496600463415e-06</v>
+        <v>-5.2237151995880842e-06</v>
       </c>
       <c r="P20">
-        <v>-1.3879248732277458e-05</v>
+        <v>-1.4907747462991578e-05</v>
       </c>
       <c r="Q20">
-        <v>0.00024475710751927123</v>
+        <v>0.00022456941302367904</v>
       </c>
       <c r="R20">
-        <v>0.00024495755623901483</v>
+        <v>0.00022464497208162524</v>
       </c>
       <c r="S20">
-        <v>0.00024751315721820459</v>
+        <v>0.00022688816140487367</v>
       </c>
       <c r="T20">
-        <v>0.00024680956801047054</v>
+        <v>0.00022618966129471629</v>
       </c>
       <c r="U20">
-        <v>0.00041021804326797092</v>
+        <v>0.00037307943059568103</v>
       </c>
       <c r="V20">
-        <v>0.00024773881862780487</v>
+        <v>0.0002265770997219273</v>
       </c>
       <c r="W20">
-        <v>-2.8211321965545443e-07</v>
+        <v>1.0161843698381578e-06</v>
       </c>
       <c r="X20">
-        <v>-4.5600031851447997e-07</v>
+        <v>4.8447017718101804e-07</v>
       </c>
       <c r="Y20">
-        <v>-0.00021936391431912701</v>
+        <v>-0.00020549649817245403</v>
       </c>
     </row>
     <row r="21">
@@ -3704,76 +3704,76 @@
         <v>41</v>
       </c>
       <c r="B21">
-        <v>-0.080131495975958436</v>
+        <v>-0.074610262536690092</v>
       </c>
       <c r="C21">
-        <v>-2.0324119055380697e-06</v>
+        <v>2.8447485046941679e-07</v>
       </c>
       <c r="D21">
-        <v>-8.9386513252424649e-06</v>
+        <v>-7.5315705023342392e-06</v>
       </c>
       <c r="E21">
-        <v>-1.6160452525814243e-06</v>
+        <v>-1.7237746172763759e-06</v>
       </c>
       <c r="F21">
-        <v>1.8967771427845141e-08</v>
+        <v>2.0539560819921629e-08</v>
       </c>
       <c r="G21">
-        <v>-1.6736609328579967e-05</v>
+        <v>-1.6149463471300828e-05</v>
       </c>
       <c r="H21">
-        <v>-2.0791676948765986e-05</v>
+        <v>-1.6774356798898917e-05</v>
       </c>
       <c r="I21">
-        <v>2.3154987275362712e-07</v>
+        <v>2.489725370848461e-07</v>
       </c>
       <c r="J21">
-        <v>3.4264700537060355e-07</v>
+        <v>2.8503368931597679e-07</v>
       </c>
       <c r="K21">
-        <v>4.9793400878022437e-06</v>
+        <v>2.8524696327124353e-06</v>
       </c>
       <c r="L21">
-        <v>1.4671527136994214e-05</v>
+        <v>4.3054478666509737e-06</v>
       </c>
       <c r="M21">
-        <v>2.0123675183939937e-06</v>
+        <v>2.6182428855198913e-06</v>
       </c>
       <c r="N21">
-        <v>-9.0407583303293799e-06</v>
+        <v>-8.8040636403090522e-06</v>
       </c>
       <c r="O21">
-        <v>-2.3247995583761593e-06</v>
+        <v>-1.8005579362521338e-06</v>
       </c>
       <c r="P21">
-        <v>-1.4121242175962859e-05</v>
+        <v>-1.1334228750512927e-05</v>
       </c>
       <c r="Q21">
-        <v>0.00024477806859044958</v>
+        <v>0.00022432489412153934</v>
       </c>
       <c r="R21">
-        <v>0.00024503011586069824</v>
+        <v>0.0002246568224508247</v>
       </c>
       <c r="S21">
-        <v>0.00024604668432688892</v>
+        <v>0.0002253067882303158</v>
       </c>
       <c r="T21">
-        <v>0.00024622155425128937</v>
+        <v>0.00022547167070155024</v>
       </c>
       <c r="U21">
-        <v>0.00024773881862780487</v>
+        <v>0.0002265770997219273</v>
       </c>
       <c r="V21">
-        <v>0.0010541690376712693</v>
+        <v>0.00095895101091874062</v>
       </c>
       <c r="W21">
-        <v>5.2807664048829268e-06</v>
+        <v>5.4054820268133583e-06</v>
       </c>
       <c r="X21">
-        <v>1.9605768827186995e-06</v>
+        <v>2.3593985310642801e-06</v>
       </c>
       <c r="Y21">
-        <v>-0.00020700455199358791</v>
+        <v>-0.00018719933015364345</v>
       </c>
     </row>
     <row r="22">
@@ -3781,76 +3781,76 @@
         <v>42</v>
       </c>
       <c r="B22">
-        <v>-0.039625551381243254</v>
+        <v>-0.069929299218011429</v>
       </c>
       <c r="C22">
-        <v>9.6384478227815581e-06</v>
+        <v>9.8708634542819802e-06</v>
       </c>
       <c r="D22">
-        <v>8.1890817646018631e-06</v>
+        <v>6.7521108945201596e-06</v>
       </c>
       <c r="E22">
-        <v>3.3325530035804443e-07</v>
+        <v>5.2972168521386966e-07</v>
       </c>
       <c r="F22">
-        <v>-5.4103383631268919e-09</v>
+        <v>-6.811222601876056e-09</v>
       </c>
       <c r="G22">
-        <v>6.4824673322319149e-06</v>
+        <v>3.5164232718433765e-06</v>
       </c>
       <c r="H22">
-        <v>1.5942545712687472e-05</v>
+        <v>1.3440128479261074e-05</v>
       </c>
       <c r="I22">
-        <v>-1.5242565842766108e-07</v>
+        <v>-8.9457257439142707e-08</v>
       </c>
       <c r="J22">
-        <v>-2.47302376772063e-07</v>
+        <v>-2.3589796548736957e-07</v>
       </c>
       <c r="K22">
-        <v>2.9848961278604991e-06</v>
+        <v>2.7034192129034835e-06</v>
       </c>
       <c r="L22">
-        <v>-7.4309136767208855e-06</v>
+        <v>-3.2083549705464349e-06</v>
       </c>
       <c r="M22">
-        <v>-9.3463584703514809e-07</v>
+        <v>-1.3556909987937132e-06</v>
       </c>
       <c r="N22">
-        <v>-2.1683503841257326e-06</v>
+        <v>-2.9113400901915666e-06</v>
       </c>
       <c r="O22">
-        <v>-2.80883941783318e-06</v>
+        <v>-4.4401585189376866e-06</v>
       </c>
       <c r="P22">
-        <v>-7.3103236347676152e-06</v>
+        <v>-8.9437289691714801e-06</v>
       </c>
       <c r="Q22">
-        <v>5.5001110873580757e-06</v>
+        <v>5.2792927337328599e-06</v>
       </c>
       <c r="R22">
-        <v>8.3710227685053373e-07</v>
+        <v>1.8032814053186563e-06</v>
       </c>
       <c r="S22">
-        <v>-2.3909358245420085e-06</v>
+        <v>-1.5058069435629418e-06</v>
       </c>
       <c r="T22">
-        <v>8.1393119473376692e-06</v>
+        <v>9.5411654398226646e-06</v>
       </c>
       <c r="U22">
-        <v>-2.8211321965545443e-07</v>
+        <v>1.0161843698381578e-06</v>
       </c>
       <c r="V22">
-        <v>5.2807664048829268e-06</v>
+        <v>5.4054820268133583e-06</v>
       </c>
       <c r="W22">
-        <v>0.00052647483248267457</v>
+        <v>0.00054229008954361402</v>
       </c>
       <c r="X22">
-        <v>3.7482334371068409e-05</v>
+        <v>3.2941834480353262e-05</v>
       </c>
       <c r="Y22">
-        <v>-4.4649934583265899e-05</v>
+        <v>-4.3338269283435703e-05</v>
       </c>
     </row>
     <row r="23">
@@ -3858,76 +3858,76 @@
         <v>43</v>
       </c>
       <c r="B23">
-        <v>0.10152919136694535</v>
+        <v>0.10585350426389045</v>
       </c>
       <c r="C23">
-        <v>2.9188835806084935e-06</v>
+        <v>5.8212419359163504e-07</v>
       </c>
       <c r="D23">
-        <v>9.5969579910589285e-06</v>
+        <v>6.5766276111471332e-06</v>
       </c>
       <c r="E23">
-        <v>-6.7546704682154576e-07</v>
+        <v>2.81561731566845e-07</v>
       </c>
       <c r="F23">
-        <v>2.8470515065478158e-09</v>
+        <v>-7.3035174080840374e-09</v>
       </c>
       <c r="G23">
-        <v>1.0146859009114377e-05</v>
+        <v>6.1814706224520246e-06</v>
       </c>
       <c r="H23">
-        <v>1.282983737758712e-05</v>
+        <v>8.0929138313141475e-06</v>
       </c>
       <c r="I23">
-        <v>-1.3822898401567202e-07</v>
+        <v>-9.0324261697324879e-08</v>
       </c>
       <c r="J23">
-        <v>-7.2897794159852285e-08</v>
+        <v>-5.2446991717774343e-08</v>
       </c>
       <c r="K23">
-        <v>6.4606430594300683e-06</v>
+        <v>8.1932214358755726e-06</v>
       </c>
       <c r="L23">
-        <v>-2.9111968417128596e-05</v>
+        <v>-7.1832783393610755e-06</v>
       </c>
       <c r="M23">
-        <v>-4.921581141314747e-06</v>
+        <v>-4.9414103891404907e-06</v>
       </c>
       <c r="N23">
-        <v>-6.5375264993869841e-06</v>
+        <v>-6.5313501605727725e-06</v>
       </c>
       <c r="O23">
-        <v>-2.7427582930699747e-06</v>
+        <v>-3.9346942739277752e-06</v>
       </c>
       <c r="P23">
-        <v>-5.1111078295608531e-06</v>
+        <v>-5.8095064108495878e-06</v>
       </c>
       <c r="Q23">
-        <v>4.7524926420566386e-06</v>
+        <v>4.4121196453801455e-06</v>
       </c>
       <c r="R23">
-        <v>-7.2203952460360568e-06</v>
+        <v>-5.1379565714724444e-06</v>
       </c>
       <c r="S23">
-        <v>-1.2412780384941919e-06</v>
+        <v>-9.74592210611528e-07</v>
       </c>
       <c r="T23">
-        <v>5.4295910347743422e-06</v>
+        <v>7.2317327120563419e-06</v>
       </c>
       <c r="U23">
-        <v>-4.5600031851447997e-07</v>
+        <v>4.8447017718101804e-07</v>
       </c>
       <c r="V23">
-        <v>1.9605768827186995e-06</v>
+        <v>2.3593985310642801e-06</v>
       </c>
       <c r="W23">
-        <v>3.7482334371068409e-05</v>
+        <v>3.2941834480353262e-05</v>
       </c>
       <c r="X23">
-        <v>0.00061924335570956207</v>
+        <v>0.00065287306084434876</v>
       </c>
       <c r="Y23">
-        <v>-2.059539587623336e-05</v>
+        <v>-3.2956895014691565e-05</v>
       </c>
     </row>
     <row r="24">
@@ -3935,76 +3935,76 @@
         <v>44</v>
       </c>
       <c r="B24">
-        <v>-2.0718776811725865</v>
+        <v>-2.345887481015275</v>
       </c>
       <c r="C24">
-        <v>-0.0010294999162681253</v>
+        <v>-0.0010091629345850475</v>
       </c>
       <c r="D24">
-        <v>-0.00021579444375254827</v>
+        <v>-0.00017795279878205056</v>
       </c>
       <c r="E24">
-        <v>-0.00026373953153217405</v>
+        <v>-0.00023829272713437683</v>
       </c>
       <c r="F24">
-        <v>2.4784389354271559e-06</v>
+        <v>2.2520893764479928e-06</v>
       </c>
       <c r="G24">
-        <v>-0.0017176667705921383</v>
+        <v>-0.0015973748514898495</v>
       </c>
       <c r="H24">
-        <v>-0.001641534893640093</v>
+        <v>-0.0017070767879386211</v>
       </c>
       <c r="I24">
-        <v>3.4119827807001024e-05</v>
+        <v>3.1810528837995031e-05</v>
       </c>
       <c r="J24">
-        <v>3.1628269683129238e-05</v>
+        <v>3.3037982872207643e-05</v>
       </c>
       <c r="K24">
-        <v>0.00024292610784200461</v>
+        <v>0.0001003666649968226</v>
       </c>
       <c r="L24">
-        <v>-0.00071992333683462348</v>
+        <v>0.00020857984561314282</v>
       </c>
       <c r="M24">
-        <v>-0.0048079674914148617</v>
+        <v>-0.0039260031461625022</v>
       </c>
       <c r="N24">
-        <v>-0.0048550492459284288</v>
+        <v>-0.0039684595616753726</v>
       </c>
       <c r="O24">
-        <v>-0.0049391848959026525</v>
+        <v>-0.0040473251642220553</v>
       </c>
       <c r="P24">
-        <v>-0.0051160007903314157</v>
+        <v>-0.0042099395338169848</v>
       </c>
       <c r="Q24">
-        <v>-0.00026285859601497033</v>
+        <v>-0.00025535226197773018</v>
       </c>
       <c r="R24">
-        <v>-0.00023944567755706451</v>
+        <v>-0.00022862382284855395</v>
       </c>
       <c r="S24">
-        <v>-0.00023469585957665515</v>
+        <v>-0.00021770546718838539</v>
       </c>
       <c r="T24">
-        <v>-0.00024633193862060818</v>
+        <v>-0.0002415196802777973</v>
       </c>
       <c r="U24">
-        <v>-0.00021936391431912701</v>
+        <v>-0.00020549649817245403</v>
       </c>
       <c r="V24">
-        <v>-0.00020700455199358791</v>
+        <v>-0.00018719933015364345</v>
       </c>
       <c r="W24">
-        <v>-4.4649934583265899e-05</v>
+        <v>-4.3338269283435703e-05</v>
       </c>
       <c r="X24">
-        <v>-2.059539587623336e-05</v>
+        <v>-3.2956895014691565e-05</v>
       </c>
       <c r="Y24">
-        <v>0.011687416587102381</v>
+        <v>0.010128412532825152</v>
       </c>
     </row>
   </sheetData>
@@ -4092,70 +4092,70 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>0.17014374725874731</v>
+        <v>0.18089287681396107</v>
       </c>
       <c r="C2">
-        <v>2.7641248179177731e-05</v>
+        <v>2.8212913668428682e-05</v>
       </c>
       <c r="D2">
-        <v>-2.9752309138037896e-07</v>
+        <v>-3.0691379851234826e-07</v>
       </c>
       <c r="E2">
-        <v>5.8394029302185777e-05</v>
+        <v>6.063477857212771e-05</v>
       </c>
       <c r="F2">
-        <v>1.9943208227427917e-05</v>
+        <v>3.3356012755703419e-05</v>
       </c>
       <c r="G2">
-        <v>-1.1948458505697271e-06</v>
+        <v>-1.2559209551958806e-06</v>
       </c>
       <c r="H2">
-        <v>-2.9320010919685017e-07</v>
+        <v>-6.3503684383640648e-07</v>
       </c>
       <c r="I2">
-        <v>-2.9712524022510405e-05</v>
+        <v>-1.4397647411004721e-05</v>
       </c>
       <c r="J2">
-        <v>0.00016081141338037384</v>
+        <v>-3.9679366302887217e-05</v>
       </c>
       <c r="K2">
-        <v>3.6510617712709015e-06</v>
+        <v>4.2028376785807685e-06</v>
       </c>
       <c r="L2">
-        <v>6.2889950113016039e-06</v>
+        <v>7.4441482841678547e-06</v>
       </c>
       <c r="M2">
-        <v>8.2166831471416972e-06</v>
+        <v>1.0437781295209378e-05</v>
       </c>
       <c r="N2">
-        <v>1.6531827363676571e-05</v>
+        <v>1.7487215950198862e-05</v>
       </c>
       <c r="O2">
-        <v>7.705159970196287e-07</v>
+        <v>2.8229266893473244e-06</v>
       </c>
       <c r="P2">
-        <v>1.2761219926602492e-06</v>
+        <v>3.966196669338332e-06</v>
       </c>
       <c r="Q2">
-        <v>-4.5510911764586781e-08</v>
+        <v>2.4485614070246394e-06</v>
       </c>
       <c r="R2">
-        <v>2.7833101866618982e-06</v>
+        <v>5.4005619281371689e-06</v>
       </c>
       <c r="S2">
-        <v>1.0676091693178568e-06</v>
+        <v>3.7941119332633169e-06</v>
       </c>
       <c r="T2">
-        <v>-1.5859953528869536e-06</v>
+        <v>-2.260043436936677e-07</v>
       </c>
       <c r="U2">
-        <v>6.4428046560659967e-07</v>
+        <v>7.4443879859393309e-07</v>
       </c>
       <c r="V2">
-        <v>-2.4608444896981984e-06</v>
+        <v>-1.2530163930393205e-06</v>
       </c>
       <c r="W2">
-        <v>-0.00059359067019433044</v>
+        <v>-0.00059580463930211712</v>
       </c>
     </row>
     <row r="3">
@@ -4163,70 +4163,70 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>-0.0018508176979263615</v>
+        <v>-0.0019629843801187408</v>
       </c>
       <c r="C3">
-        <v>-2.9752309138037896e-07</v>
+        <v>-3.0691379851234826e-07</v>
       </c>
       <c r="D3">
-        <v>3.35302866193851e-09</v>
+        <v>3.4688889446205778e-09</v>
       </c>
       <c r="E3">
-        <v>-8.3657930650728686e-08</v>
+        <v>-1.9754853126007579e-07</v>
       </c>
       <c r="F3">
-        <v>3.540701833779376e-07</v>
+        <v>1.0942923784018472e-07</v>
       </c>
       <c r="G3">
-        <v>1.6798347094729204e-10</v>
+        <v>2.9943114029847789e-09</v>
       </c>
       <c r="H3">
-        <v>-1.0014637822747125e-08</v>
+        <v>-3.9311914200199616e-09</v>
       </c>
       <c r="I3">
-        <v>2.9914837004289935e-07</v>
+        <v>1.2577045123085712e-07</v>
       </c>
       <c r="J3">
-        <v>-1.8367437377076091e-06</v>
+        <v>4.6375741995682274e-07</v>
       </c>
       <c r="K3">
-        <v>-3.9295665709805132e-08</v>
+        <v>-4.7539607402531409e-08</v>
       </c>
       <c r="L3">
-        <v>-6.2576892984300325e-08</v>
+        <v>-7.927015650839e-08</v>
       </c>
       <c r="M3">
-        <v>-6.4585399908488573e-08</v>
+        <v>-9.6075044869187431e-08</v>
       </c>
       <c r="N3">
-        <v>-1.236459840830648e-07</v>
+        <v>-1.4499094689611371e-07</v>
       </c>
       <c r="O3">
-        <v>-9.060370695877769e-09</v>
+        <v>-3.303726107889257e-08</v>
       </c>
       <c r="P3">
-        <v>-1.8017851790243963e-08</v>
+        <v>-4.7734409116666451e-08</v>
       </c>
       <c r="Q3">
-        <v>-3.333472753250566e-10</v>
+        <v>-2.8193403910187247e-08</v>
       </c>
       <c r="R3">
-        <v>-2.932623301597289e-08</v>
+        <v>-5.9293833597263886e-08</v>
       </c>
       <c r="S3">
-        <v>-8.8701674518747906e-09</v>
+        <v>-4.0261836804159125e-08</v>
       </c>
       <c r="T3">
-        <v>2.1438709781452967e-08</v>
+        <v>5.7295706707113009e-09</v>
       </c>
       <c r="U3">
-        <v>-1.2732135065008081e-08</v>
+        <v>-1.1439799954674747e-08</v>
       </c>
       <c r="V3">
-        <v>2.1652126458575811e-08</v>
+        <v>1.1122820945452113e-08</v>
       </c>
       <c r="W3">
-        <v>6.0770771535445493e-06</v>
+        <v>6.2060900132489428e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4234,70 +4234,70 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>-0.33802256165219158</v>
+        <v>-0.27152055268581243</v>
       </c>
       <c r="C4">
-        <v>5.8394029302185777e-05</v>
+        <v>6.063477857212771e-05</v>
       </c>
       <c r="D4">
-        <v>-8.3657930650728686e-08</v>
+        <v>-1.9754853126007579e-07</v>
       </c>
       <c r="E4">
-        <v>0.0062484818541166977</v>
+        <v>0.0054203978755018433</v>
       </c>
       <c r="F4">
-        <v>0.0023390144439787252</v>
+        <v>0.0020539264026555202</v>
       </c>
       <c r="G4">
-        <v>-0.00013190667385029422</v>
+        <v>-0.00011340164810100889</v>
       </c>
       <c r="H4">
-        <v>-5.0650915671182051e-05</v>
+        <v>-4.4202376761918845e-05</v>
       </c>
       <c r="I4">
-        <v>-3.4766794955318233e-05</v>
+        <v>2.0658265705622886e-06</v>
       </c>
       <c r="J4">
-        <v>-0.00091301477034113254</v>
+        <v>-0.0001080580730689578</v>
       </c>
       <c r="K4">
-        <v>3.2614017622155135e-05</v>
+        <v>4.2464294603838156e-05</v>
       </c>
       <c r="L4">
-        <v>3.9119554126281782e-05</v>
+        <v>4.3060216919538143e-05</v>
       </c>
       <c r="M4">
-        <v>2.6904312381815766e-05</v>
+        <v>3.9098711939538353e-05</v>
       </c>
       <c r="N4">
-        <v>7.1764061345541696e-05</v>
+        <v>8.1062023029481985e-05</v>
       </c>
       <c r="O4">
-        <v>2.0966854594261814e-05</v>
+        <v>2.599957346847167e-05</v>
       </c>
       <c r="P4">
-        <v>2.8900472890601289e-05</v>
+        <v>3.0139903629620366e-05</v>
       </c>
       <c r="Q4">
-        <v>8.5898755718704239e-06</v>
+        <v>1.6520134236658164e-05</v>
       </c>
       <c r="R4">
-        <v>2.4301926811353437e-06</v>
+        <v>1.5319065618404014e-05</v>
       </c>
       <c r="S4">
-        <v>-2.9850623349376928e-05</v>
+        <v>-1.0223069220110485e-05</v>
       </c>
       <c r="T4">
-        <v>-8.6732879960193984e-06</v>
+        <v>-1.6559814167977748e-07</v>
       </c>
       <c r="U4">
-        <v>1.8501259477093743e-05</v>
+        <v>1.5951222429015683e-05</v>
       </c>
       <c r="V4">
-        <v>2.8483267344695754e-05</v>
+        <v>2.8115213761436599e-05</v>
       </c>
       <c r="W4">
-        <v>-0.0025197464125829567</v>
+        <v>-0.0023801401078947602</v>
       </c>
     </row>
     <row r="5">
@@ -4305,70 +4305,70 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>-0.38331208009613871</v>
+        <v>-0.36622317016271977</v>
       </c>
       <c r="C5">
-        <v>1.9943208227427917e-05</v>
+        <v>3.3356012755703419e-05</v>
       </c>
       <c r="D5">
-        <v>3.540701833779376e-07</v>
+        <v>1.0942923784018472e-07</v>
       </c>
       <c r="E5">
-        <v>0.0023390144439787252</v>
+        <v>0.0020539264026555202</v>
       </c>
       <c r="F5">
-        <v>0.0056137678150741431</v>
+        <v>0.0050535262368869016</v>
       </c>
       <c r="G5">
-        <v>-5.0982736715361419e-05</v>
+        <v>-4.4455034063569681e-05</v>
       </c>
       <c r="H5">
-        <v>-0.00011520850467847132</v>
+        <v>-0.00010307170964818179</v>
       </c>
       <c r="I5">
-        <v>-2.4273691368978177e-05</v>
+        <v>2.2843827951540523e-05</v>
       </c>
       <c r="J5">
-        <v>-0.0015435138978368913</v>
+        <v>-0.00015317044663431837</v>
       </c>
       <c r="K5">
-        <v>3.8335730390101046e-05</v>
+        <v>3.1424032450837755e-05</v>
       </c>
       <c r="L5">
-        <v>1.1874579954668238e-06</v>
+        <v>-1.1132732308966357e-06</v>
       </c>
       <c r="M5">
-        <v>-1.9503099936211304e-05</v>
+        <v>-1.1206726195968309e-05</v>
       </c>
       <c r="N5">
-        <v>4.8283929973070806e-05</v>
+        <v>4.7530408677333024e-05</v>
       </c>
       <c r="O5">
-        <v>1.9205211876510931e-05</v>
+        <v>2.2028409212036811e-05</v>
       </c>
       <c r="P5">
-        <v>-1.6822782732872847e-05</v>
+        <v>-1.0838641651333534e-05</v>
       </c>
       <c r="Q5">
-        <v>-7.4351468300296375e-05</v>
+        <v>-5.6215128617929705e-05</v>
       </c>
       <c r="R5">
-        <v>-3.704536155166998e-05</v>
+        <v>-2.4961829883317909e-05</v>
       </c>
       <c r="S5">
-        <v>-0.00011679445542834764</v>
+        <v>-9.5365212390587952e-05</v>
       </c>
       <c r="T5">
-        <v>-8.0583503672852257e-05</v>
+        <v>-6.031309723040548e-05</v>
       </c>
       <c r="U5">
-        <v>2.8927638536724631e-05</v>
+        <v>3.2369995515503299e-05</v>
       </c>
       <c r="V5">
-        <v>4.1511906589945642e-05</v>
+        <v>4.3041152185741951e-05</v>
       </c>
       <c r="W5">
-        <v>-0.0016560323521552008</v>
+        <v>-0.0017237712088299412</v>
       </c>
     </row>
     <row r="6">
@@ -4376,70 +4376,70 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>0.0040707227108623982</v>
+        <v>0.0017773661695320868</v>
       </c>
       <c r="C6">
-        <v>-1.1948458505697271e-06</v>
+        <v>-1.2559209551958806e-06</v>
       </c>
       <c r="D6">
-        <v>1.6798347094729204e-10</v>
+        <v>2.9943114029847789e-09</v>
       </c>
       <c r="E6">
-        <v>-0.00013190667385029422</v>
+        <v>-0.00011340164810100889</v>
       </c>
       <c r="F6">
-        <v>-5.0982736715361419e-05</v>
+        <v>-4.4455034063569681e-05</v>
       </c>
       <c r="G6">
-        <v>2.9852442316628557e-06</v>
+        <v>2.5429865299558371e-06</v>
       </c>
       <c r="H6">
-        <v>1.1811109353561096e-06</v>
+        <v>1.0227883541590456e-06</v>
       </c>
       <c r="I6">
-        <v>7.8701214649372011e-07</v>
+        <v>-5.8620147961938666e-08</v>
       </c>
       <c r="J6">
-        <v>1.9033474556482359e-05</v>
+        <v>2.4132211773751256e-06</v>
       </c>
       <c r="K6">
-        <v>-3.7308452549334355e-07</v>
+        <v>-5.4336720171077805e-07</v>
       </c>
       <c r="L6">
-        <v>-5.6590254061306472e-07</v>
+        <v>-5.9585217425194744e-07</v>
       </c>
       <c r="M6">
-        <v>2.1439546846429527e-07</v>
+        <v>-7.732426681770509e-08</v>
       </c>
       <c r="N6">
-        <v>-4.5671431492077351e-07</v>
+        <v>-7.0516570278752119e-07</v>
       </c>
       <c r="O6">
-        <v>-1.7532779879655227e-07</v>
+        <v>-3.0470227802096388e-07</v>
       </c>
       <c r="P6">
-        <v>-4.3421541706204456e-07</v>
+        <v>-5.3078848873932977e-07</v>
       </c>
       <c r="Q6">
-        <v>-1.6469409410990925e-07</v>
+        <v>-3.3794786108738866e-07</v>
       </c>
       <c r="R6">
-        <v>-2.0110568675159677e-07</v>
+        <v>-4.766370617079262e-07</v>
       </c>
       <c r="S6">
-        <v>5.3371271921616794e-07</v>
+        <v>1.4481119756810726e-07</v>
       </c>
       <c r="T6">
-        <v>-4.3486899884683458e-08</v>
+        <v>-1.8760321035369524e-07</v>
       </c>
       <c r="U6">
-        <v>-1.8409577426498135e-07</v>
+        <v>-1.8809430049115851e-07</v>
       </c>
       <c r="V6">
-        <v>-3.7475403016374888e-07</v>
+        <v>-4.5847018074486989e-07</v>
       </c>
       <c r="W6">
-        <v>5.0807519243301652e-05</v>
+        <v>4.8074717002199028e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4447,70 +4447,70 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>-0.00026934857912513368</v>
+        <v>-0.0015926984005508531</v>
       </c>
       <c r="C7">
-        <v>-2.9320010919685017e-07</v>
+        <v>-6.3503684383640648e-07</v>
       </c>
       <c r="D7">
-        <v>-1.0014637822747125e-08</v>
+        <v>-3.9311914200199616e-09</v>
       </c>
       <c r="E7">
-        <v>-5.0650915671182051e-05</v>
+        <v>-4.4202376761918845e-05</v>
       </c>
       <c r="F7">
-        <v>-0.00011520850467847132</v>
+        <v>-0.00010307170964818179</v>
       </c>
       <c r="G7">
-        <v>1.1811109353561096e-06</v>
+        <v>1.0227883541590456e-06</v>
       </c>
       <c r="H7">
-        <v>2.5277830860317053e-06</v>
+        <v>2.2438032928197734e-06</v>
       </c>
       <c r="I7">
-        <v>2.1603443374333957e-07</v>
+        <v>-7.883536688883599e-07</v>
       </c>
       <c r="J7">
-        <v>3.1090882260400725e-05</v>
+        <v>3.416956312080981e-06</v>
       </c>
       <c r="K7">
-        <v>-9.5582888537576614e-07</v>
+        <v>-7.8597116053919424e-07</v>
       </c>
       <c r="L7">
-        <v>9.2499442936916578e-08</v>
+        <v>1.0203691265460072e-07</v>
       </c>
       <c r="M7">
-        <v>1.4409741923628842e-06</v>
+        <v>1.0716499487448371e-06</v>
       </c>
       <c r="N7">
-        <v>5.1103239425865161e-07</v>
+        <v>2.3770926427101751e-07</v>
       </c>
       <c r="O7">
-        <v>1.6360988913932569e-08</v>
+        <v>-1.3503755523513163e-07</v>
       </c>
       <c r="P7">
-        <v>9.7152109445072656e-07</v>
+        <v>7.0406438012282245e-07</v>
       </c>
       <c r="Q7">
-        <v>1.2246797172414812e-06</v>
+        <v>8.5989235956969206e-07</v>
       </c>
       <c r="R7">
-        <v>8.1351876415390696e-07</v>
+        <v>5.1460498825877545e-07</v>
       </c>
       <c r="S7">
-        <v>1.9325278104527057e-06</v>
+        <v>1.5035721594131189e-06</v>
       </c>
       <c r="T7">
-        <v>1.4709641125568748e-06</v>
+        <v>1.0564369302850906e-06</v>
       </c>
       <c r="U7">
-        <v>-2.6681804510713692e-07</v>
+        <v>-4.6454352798112921e-07</v>
       </c>
       <c r="V7">
-        <v>-2.1963049024837856e-07</v>
+        <v>-4.4799985437316903e-07</v>
       </c>
       <c r="W7">
-        <v>3.0501911214222998e-05</v>
+        <v>3.3253971797968724e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4518,70 +4518,70 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>-0.0046494359518024549</v>
+        <v>0.011237057209964908</v>
       </c>
       <c r="C8">
-        <v>-2.9712524022510405e-05</v>
+        <v>-1.4397647411004721e-05</v>
       </c>
       <c r="D8">
-        <v>2.9914837004289935e-07</v>
+        <v>1.2577045123085712e-07</v>
       </c>
       <c r="E8">
-        <v>-3.4766794955318233e-05</v>
+        <v>2.0658265705622886e-06</v>
       </c>
       <c r="F8">
-        <v>-2.4273691368978177e-05</v>
+        <v>2.2843827951540523e-05</v>
       </c>
       <c r="G8">
-        <v>7.8701214649372011e-07</v>
+        <v>-5.8620147961938666e-08</v>
       </c>
       <c r="H8">
-        <v>2.1603443374333957e-07</v>
+        <v>-7.883536688883599e-07</v>
       </c>
       <c r="I8">
-        <v>0.00031806895373103845</v>
+        <v>0.00030541345328910491</v>
       </c>
       <c r="J8">
-        <v>-3.3451692978826539e-05</v>
+        <v>-9.9022114498574442e-05</v>
       </c>
       <c r="K8">
-        <v>-1.163685199377583e-05</v>
+        <v>-1.3873904259895689e-05</v>
       </c>
       <c r="L8">
-        <v>-2.2979749744229155e-05</v>
+        <v>-2.1690594962824576e-05</v>
       </c>
       <c r="M8">
-        <v>-3.6073269483900146e-05</v>
+        <v>-3.1420034970895341e-05</v>
       </c>
       <c r="N8">
-        <v>-3.4098805278405466e-05</v>
+        <v>-2.9780660796980464e-05</v>
       </c>
       <c r="O8">
-        <v>-8.2078193977082233e-06</v>
+        <v>-2.8389918702481635e-06</v>
       </c>
       <c r="P8">
-        <v>7.3286828540267778e-06</v>
+        <v>1.0046695204955815e-05</v>
       </c>
       <c r="Q8">
-        <v>-5.6297964760295236e-06</v>
+        <v>-2.4553952783814192e-06</v>
       </c>
       <c r="R8">
-        <v>-8.7334575095057433e-06</v>
+        <v>-4.2684872494050983e-06</v>
       </c>
       <c r="S8">
-        <v>-2.606697666044876e-06</v>
+        <v>2.0932982755478784e-06</v>
       </c>
       <c r="T8">
-        <v>1.9901236583877612e-05</v>
+        <v>1.9162917473249433e-05</v>
       </c>
       <c r="U8">
-        <v>-5.9311727403353487e-06</v>
+        <v>-4.1330805374154734e-06</v>
       </c>
       <c r="V8">
-        <v>-6.1797809405181669e-06</v>
+        <v>-3.5013528475145101e-06</v>
       </c>
       <c r="W8">
-        <v>0.00052362790018054656</v>
+        <v>0.00025058448675194386</v>
       </c>
     </row>
     <row r="9">
@@ -4589,70 +4589,70 @@
         <v>31</v>
       </c>
       <c r="B9">
-        <v>-1.2249560361058816</v>
+        <v>-0.067066454648628135</v>
       </c>
       <c r="C9">
-        <v>0.00016081141338037384</v>
+        <v>-3.9679366302887217e-05</v>
       </c>
       <c r="D9">
-        <v>-1.8367437377076091e-06</v>
+        <v>4.6375741995682274e-07</v>
       </c>
       <c r="E9">
-        <v>-0.00091301477034113254</v>
+        <v>-0.0001080580730689578</v>
       </c>
       <c r="F9">
-        <v>-0.0015435138978368913</v>
+        <v>-0.00015317044663431837</v>
       </c>
       <c r="G9">
-        <v>1.9033474556482359e-05</v>
+        <v>2.4132211773751256e-06</v>
       </c>
       <c r="H9">
-        <v>3.1090882260400725e-05</v>
+        <v>3.416956312080981e-06</v>
       </c>
       <c r="I9">
-        <v>-3.3451692978826539e-05</v>
+        <v>-9.9022114498574442e-05</v>
       </c>
       <c r="J9">
-        <v>0.26499699863351184</v>
+        <v>0.00035472363758384486</v>
       </c>
       <c r="K9">
-        <v>1.7411053795563521e-06</v>
+        <v>-1.933984459083775e-06</v>
       </c>
       <c r="L9">
-        <v>1.2524489490131492e-05</v>
+        <v>-1.0576689999532813e-05</v>
       </c>
       <c r="M9">
-        <v>4.3658215107989195e-05</v>
+        <v>-2.0697117126476888e-05</v>
       </c>
       <c r="N9">
-        <v>-3.825337019856601e-05</v>
+        <v>-2.1731803636424753e-05</v>
       </c>
       <c r="O9">
-        <v>1.7949650897805859e-05</v>
+        <v>-1.4742208723077788e-05</v>
       </c>
       <c r="P9">
-        <v>4.4802395825620039e-05</v>
+        <v>-1.5373924110957966e-05</v>
       </c>
       <c r="Q9">
-        <v>6.7766769180182033e-05</v>
+        <v>-1.3802407198192849e-05</v>
       </c>
       <c r="R9">
-        <v>5.0253621813979872e-05</v>
+        <v>-1.6767369914502567e-05</v>
       </c>
       <c r="S9">
-        <v>1.9353312420564719e-05</v>
+        <v>-1.8532693821311366e-05</v>
       </c>
       <c r="T9">
-        <v>0.00011820103657441367</v>
+        <v>-7.5491457290265346e-06</v>
       </c>
       <c r="U9">
-        <v>5.2480443651226256e-05</v>
+        <v>-6.1301798897019849e-06</v>
       </c>
       <c r="V9">
-        <v>2.3362080216173504e-05</v>
+        <v>-8.6713804594057136e-06</v>
       </c>
       <c r="W9">
-        <v>-0.003333707186346417</v>
+        <v>0.00073539763712275152</v>
       </c>
     </row>
     <row r="10">
@@ -4660,70 +4660,70 @@
         <v>32</v>
       </c>
       <c r="B10">
-        <v>0.22800117834656972</v>
+        <v>0.18373691429854508</v>
       </c>
       <c r="C10">
-        <v>3.6510617712709015e-06</v>
+        <v>4.2028376785807685e-06</v>
       </c>
       <c r="D10">
-        <v>-3.9295665709805132e-08</v>
+        <v>-4.7539607402531409e-08</v>
       </c>
       <c r="E10">
-        <v>3.2614017622155135e-05</v>
+        <v>4.2464294603838156e-05</v>
       </c>
       <c r="F10">
-        <v>3.8335730390101046e-05</v>
+        <v>3.1424032450837755e-05</v>
       </c>
       <c r="G10">
-        <v>-3.7308452549334355e-07</v>
+        <v>-5.4336720171077805e-07</v>
       </c>
       <c r="H10">
-        <v>-9.5582888537576614e-07</v>
+        <v>-7.8597116053919424e-07</v>
       </c>
       <c r="I10">
-        <v>-1.163685199377583e-05</v>
+        <v>-1.3873904259895689e-05</v>
       </c>
       <c r="J10">
-        <v>1.7411053795563521e-06</v>
+        <v>-1.933984459083775e-06</v>
       </c>
       <c r="K10">
-        <v>0.011996860277546236</v>
+        <v>0.010045728191650874</v>
       </c>
       <c r="L10">
-        <v>0.0099307463012206863</v>
+        <v>0.0083056359566592384</v>
       </c>
       <c r="M10">
-        <v>0.0099278855991242962</v>
+        <v>0.0083025286830316607</v>
       </c>
       <c r="N10">
-        <v>0.0099248852094064467</v>
+        <v>0.0082985549939215315</v>
       </c>
       <c r="O10">
-        <v>2.0991702486070284e-05</v>
+        <v>1.2307005584410866e-05</v>
       </c>
       <c r="P10">
-        <v>4.4083330463202299e-05</v>
+        <v>3.7392509999887669e-05</v>
       </c>
       <c r="Q10">
-        <v>1.8354590839911024e-05</v>
+        <v>2.5549619243840432e-05</v>
       </c>
       <c r="R10">
-        <v>1.7502692522889457e-05</v>
+        <v>2.9361686160015165e-05</v>
       </c>
       <c r="S10">
-        <v>2.6272956383322867e-05</v>
+        <v>2.6052897418697094e-05</v>
       </c>
       <c r="T10">
-        <v>6.0247749972652565e-05</v>
+        <v>6.3604519814932238e-05</v>
       </c>
       <c r="U10">
-        <v>-1.4915699964949509e-05</v>
+        <v>-1.0893199412724915e-05</v>
       </c>
       <c r="V10">
-        <v>3.6694161314550386e-05</v>
+        <v>3.1086774629481877e-05</v>
       </c>
       <c r="W10">
-        <v>-0.010024002271480469</v>
+        <v>-0.0084058833483083573</v>
       </c>
     </row>
     <row r="11">
@@ -4731,70 +4731,70 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>0.458261994672364</v>
+        <v>0.42231251129335928</v>
       </c>
       <c r="C11">
-        <v>6.2889950113016039e-06</v>
+        <v>7.4441482841678547e-06</v>
       </c>
       <c r="D11">
-        <v>-6.2576892984300325e-08</v>
+        <v>-7.927015650839e-08</v>
       </c>
       <c r="E11">
-        <v>3.9119554126281782e-05</v>
+        <v>4.3060216919538143e-05</v>
       </c>
       <c r="F11">
-        <v>1.1874579954668238e-06</v>
+        <v>-1.1132732308966357e-06</v>
       </c>
       <c r="G11">
-        <v>-5.6590254061306472e-07</v>
+        <v>-5.9585217425194744e-07</v>
       </c>
       <c r="H11">
-        <v>9.2499442936916578e-08</v>
+        <v>1.0203691265460072e-07</v>
       </c>
       <c r="I11">
-        <v>-2.2979749744229155e-05</v>
+        <v>-2.1690594962824576e-05</v>
       </c>
       <c r="J11">
-        <v>1.2524489490131492e-05</v>
+        <v>-1.0576689999532813e-05</v>
       </c>
       <c r="K11">
-        <v>0.0099307463012206863</v>
+        <v>0.0083056359566592384</v>
       </c>
       <c r="L11">
-        <v>0.010294318498476172</v>
+        <v>0.0086119814891286797</v>
       </c>
       <c r="M11">
-        <v>0.009936176237852078</v>
+        <v>0.0083097659464238319</v>
       </c>
       <c r="N11">
-        <v>0.009939098564167451</v>
+        <v>0.0083109663353309726</v>
       </c>
       <c r="O11">
-        <v>-1.4966078079019057e-06</v>
+        <v>-7.3782835128364404e-06</v>
       </c>
       <c r="P11">
-        <v>1.4085628590994038e-05</v>
+        <v>1.1574224310175558e-05</v>
       </c>
       <c r="Q11">
-        <v>-1.0119234219867484e-05</v>
+        <v>4.278264441372339e-06</v>
       </c>
       <c r="R11">
-        <v>4.2900460984274778e-06</v>
+        <v>1.6779112074569375e-05</v>
       </c>
       <c r="S11">
-        <v>-2.7713845261787437e-06</v>
+        <v>8.5049575997847311e-07</v>
       </c>
       <c r="T11">
-        <v>1.6082066797378114e-05</v>
+        <v>2.9610352200449452e-05</v>
       </c>
       <c r="U11">
-        <v>-1.81417392115132e-05</v>
+        <v>-1.5517592066413316e-05</v>
       </c>
       <c r="V11">
-        <v>3.2174505271338713e-05</v>
+        <v>2.8611271935898903e-05</v>
       </c>
       <c r="W11">
-        <v>-0.010075066009677398</v>
+        <v>-0.0084661599263487521</v>
       </c>
     </row>
     <row r="12">
@@ -4802,70 +4802,70 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0.62017909682280792</v>
+        <v>0.59055375337138849</v>
       </c>
       <c r="C12">
-        <v>8.2166831471416972e-06</v>
+        <v>1.0437781295209378e-05</v>
       </c>
       <c r="D12">
-        <v>-6.4585399908488573e-08</v>
+        <v>-9.6075044869187431e-08</v>
       </c>
       <c r="E12">
-        <v>2.6904312381815766e-05</v>
+        <v>3.9098711939538353e-05</v>
       </c>
       <c r="F12">
-        <v>-1.9503099936211304e-05</v>
+        <v>-1.1206726195968309e-05</v>
       </c>
       <c r="G12">
-        <v>2.1439546846429527e-07</v>
+        <v>-7.732426681770509e-08</v>
       </c>
       <c r="H12">
-        <v>1.4409741923628842e-06</v>
+        <v>1.0716499487448371e-06</v>
       </c>
       <c r="I12">
-        <v>-3.6073269483900146e-05</v>
+        <v>-3.1420034970895341e-05</v>
       </c>
       <c r="J12">
-        <v>4.3658215107989195e-05</v>
+        <v>-2.0697117126476888e-05</v>
       </c>
       <c r="K12">
-        <v>0.0099278855991242962</v>
+        <v>0.0083025286830316607</v>
       </c>
       <c r="L12">
-        <v>0.009936176237852078</v>
+        <v>0.0083097659464238319</v>
       </c>
       <c r="M12">
-        <v>0.010062435486731488</v>
+        <v>0.0084193913005867708</v>
       </c>
       <c r="N12">
-        <v>0.0099791152717346766</v>
+        <v>0.0083438776297522464</v>
       </c>
       <c r="O12">
-        <v>-1.7926795352679869e-05</v>
+        <v>-1.9062794287339976e-05</v>
       </c>
       <c r="P12">
-        <v>4.7982103806131071e-06</v>
+        <v>6.1133393623238874e-06</v>
       </c>
       <c r="Q12">
-        <v>-2.7373492872553125e-05</v>
+        <v>-9.1106574615597486e-06</v>
       </c>
       <c r="R12">
-        <v>-9.5150565468413429e-06</v>
+        <v>7.4634355775772413e-06</v>
       </c>
       <c r="S12">
-        <v>-1.5376978392558241e-05</v>
+        <v>-8.2807623491552341e-06</v>
       </c>
       <c r="T12">
-        <v>2.5813175832062609e-05</v>
+        <v>3.9261263618007132e-05</v>
       </c>
       <c r="U12">
-        <v>-1.883973666230486e-05</v>
+        <v>-1.8194938227746931e-05</v>
       </c>
       <c r="V12">
-        <v>3.6563390223014352e-05</v>
+        <v>3.0842942201597627e-05</v>
       </c>
       <c r="W12">
-        <v>-0.010180503499418746</v>
+        <v>-0.008581535024973776</v>
       </c>
     </row>
     <row r="13">
@@ -4873,70 +4873,70 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>0.62176838212978269</v>
+        <v>0.61398603387151329</v>
       </c>
       <c r="C13">
-        <v>1.6531827363676571e-05</v>
+        <v>1.7487215950198862e-05</v>
       </c>
       <c r="D13">
-        <v>-1.236459840830648e-07</v>
+        <v>-1.4499094689611371e-07</v>
       </c>
       <c r="E13">
-        <v>7.1764061345541696e-05</v>
+        <v>8.1062023029481985e-05</v>
       </c>
       <c r="F13">
-        <v>4.8283929973070806e-05</v>
+        <v>4.7530408677333024e-05</v>
       </c>
       <c r="G13">
-        <v>-4.5671431492077351e-07</v>
+        <v>-7.0516570278752119e-07</v>
       </c>
       <c r="H13">
-        <v>5.1103239425865161e-07</v>
+        <v>2.3770926427101751e-07</v>
       </c>
       <c r="I13">
-        <v>-3.4098805278405466e-05</v>
+        <v>-2.9780660796980464e-05</v>
       </c>
       <c r="J13">
-        <v>-3.825337019856601e-05</v>
+        <v>-2.1731803636424753e-05</v>
       </c>
       <c r="K13">
-        <v>0.0099248852094064467</v>
+        <v>0.0082985549939215315</v>
       </c>
       <c r="L13">
-        <v>0.009939098564167451</v>
+        <v>0.0083109663353309726</v>
       </c>
       <c r="M13">
-        <v>0.0099791152717346766</v>
+        <v>0.0083438776297522464</v>
       </c>
       <c r="N13">
-        <v>0.010364705026425836</v>
+        <v>0.0086893342071832115</v>
       </c>
       <c r="O13">
-        <v>-3.6511549441189977e-05</v>
+        <v>-3.5069800268511275e-05</v>
       </c>
       <c r="P13">
-        <v>-2.0322990590757065e-05</v>
+        <v>-1.497059078441965e-05</v>
       </c>
       <c r="Q13">
-        <v>-3.8144505001714748e-05</v>
+        <v>-1.6954410243606868e-05</v>
       </c>
       <c r="R13">
-        <v>-4.1644807801824919e-05</v>
+        <v>-1.7618570052276386e-05</v>
       </c>
       <c r="S13">
-        <v>-4.2854933628888447e-05</v>
+        <v>-3.0955975819405522e-05</v>
       </c>
       <c r="T13">
-        <v>4.1535868367828817e-06</v>
+        <v>2.0652545769368004e-05</v>
       </c>
       <c r="U13">
-        <v>-2.5205775768008805e-05</v>
+        <v>-2.547821829792273e-05</v>
       </c>
       <c r="V13">
-        <v>3.3571330108055821e-05</v>
+        <v>2.7384510137669768e-05</v>
       </c>
       <c r="W13">
-        <v>-0.010438023339420467</v>
+        <v>-0.0088014022867021775</v>
       </c>
     </row>
     <row r="14">
@@ -4944,70 +4944,70 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>0.038913533961997489</v>
+        <v>0.047730861148993373</v>
       </c>
       <c r="C14">
-        <v>7.705159970196287e-07</v>
+        <v>2.8229266893473244e-06</v>
       </c>
       <c r="D14">
-        <v>-9.060370695877769e-09</v>
+        <v>-3.303726107889257e-08</v>
       </c>
       <c r="E14">
-        <v>2.0966854594261814e-05</v>
+        <v>2.599957346847167e-05</v>
       </c>
       <c r="F14">
-        <v>1.9205211876510931e-05</v>
+        <v>2.2028409212036811e-05</v>
       </c>
       <c r="G14">
-        <v>-1.7532779879655227e-07</v>
+        <v>-3.0470227802096388e-07</v>
       </c>
       <c r="H14">
-        <v>1.6360988913932569e-08</v>
+        <v>-1.3503755523513163e-07</v>
       </c>
       <c r="I14">
-        <v>-8.2078193977082233e-06</v>
+        <v>-2.8389918702481635e-06</v>
       </c>
       <c r="J14">
-        <v>1.7949650897805859e-05</v>
+        <v>-1.4742208723077788e-05</v>
       </c>
       <c r="K14">
-        <v>2.0991702486070284e-05</v>
+        <v>1.2307005584410866e-05</v>
       </c>
       <c r="L14">
-        <v>-1.4966078079019057e-06</v>
+        <v>-7.3782835128364404e-06</v>
       </c>
       <c r="M14">
-        <v>-1.7926795352679869e-05</v>
+        <v>-1.9062794287339976e-05</v>
       </c>
       <c r="N14">
-        <v>-3.6511549441189977e-05</v>
+        <v>-3.5069800268511275e-05</v>
       </c>
       <c r="O14">
-        <v>0.00088185088718027997</v>
+        <v>0.00078788751528976477</v>
       </c>
       <c r="P14">
-        <v>0.00047211848011037181</v>
+        <v>0.00042442360439880693</v>
       </c>
       <c r="Q14">
-        <v>0.00046923668070882545</v>
+        <v>0.00042216584961812901</v>
       </c>
       <c r="R14">
-        <v>0.0004710651843647419</v>
+        <v>0.00042366929378590614</v>
       </c>
       <c r="S14">
-        <v>0.000469497365033381</v>
+        <v>0.00042262458653135986</v>
       </c>
       <c r="T14">
-        <v>0.00046818112937872293</v>
+        <v>0.00042096771102720658</v>
       </c>
       <c r="U14">
-        <v>1.7360087563435116e-06</v>
+        <v>4.511674315152125e-06</v>
       </c>
       <c r="V14">
-        <v>-5.3093052501861922e-07</v>
+        <v>5.955067363998736e-07</v>
       </c>
       <c r="W14">
-        <v>-0.00047255300945799831</v>
+        <v>-0.00046041484561411771</v>
       </c>
     </row>
     <row r="15">
@@ -5015,70 +5015,70 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>0.042330565213303015</v>
+        <v>0.073644463486289766</v>
       </c>
       <c r="C15">
-        <v>1.2761219926602492e-06</v>
+        <v>3.966196669338332e-06</v>
       </c>
       <c r="D15">
-        <v>-1.8017851790243963e-08</v>
+        <v>-4.7734409116666451e-08</v>
       </c>
       <c r="E15">
-        <v>2.8900472890601289e-05</v>
+        <v>3.0139903629620366e-05</v>
       </c>
       <c r="F15">
-        <v>-1.6822782732872847e-05</v>
+        <v>-1.0838641651333534e-05</v>
       </c>
       <c r="G15">
-        <v>-4.3421541706204456e-07</v>
+        <v>-5.3078848873932977e-07</v>
       </c>
       <c r="H15">
-        <v>9.7152109445072656e-07</v>
+        <v>7.0406438012282245e-07</v>
       </c>
       <c r="I15">
-        <v>7.3286828540267778e-06</v>
+        <v>1.0046695204955815e-05</v>
       </c>
       <c r="J15">
-        <v>4.4802395825620039e-05</v>
+        <v>-1.5373924110957966e-05</v>
       </c>
       <c r="K15">
-        <v>4.4083330463202299e-05</v>
+        <v>3.7392509999887669e-05</v>
       </c>
       <c r="L15">
-        <v>1.4085628590994038e-05</v>
+        <v>1.1574224310175558e-05</v>
       </c>
       <c r="M15">
-        <v>4.7982103806131071e-06</v>
+        <v>6.1133393623238874e-06</v>
       </c>
       <c r="N15">
-        <v>-2.0322990590757065e-05</v>
+        <v>-1.497059078441965e-05</v>
       </c>
       <c r="O15">
-        <v>0.00047211848011037181</v>
+        <v>0.00042442360439880693</v>
       </c>
       <c r="P15">
-        <v>0.0010629374166165224</v>
+        <v>0.00094675269720894935</v>
       </c>
       <c r="Q15">
-        <v>0.00046927009111282924</v>
+        <v>0.00042214722913441744</v>
       </c>
       <c r="R15">
-        <v>0.00047173769707258039</v>
+        <v>0.00042438899469800776</v>
       </c>
       <c r="S15">
-        <v>0.00047014273902040276</v>
+        <v>0.00042329754278658846</v>
       </c>
       <c r="T15">
-        <v>0.00047047650778599451</v>
+        <v>0.00042305978563627678</v>
       </c>
       <c r="U15">
-        <v>-5.1777168574167428e-06</v>
+        <v>-2.3792089849083077e-06</v>
       </c>
       <c r="V15">
-        <v>-1.431906753762378e-05</v>
+        <v>-1.0135363846915328e-05</v>
       </c>
       <c r="W15">
-        <v>-0.00050786740170574057</v>
+        <v>-0.00051168780119030749</v>
       </c>
     </row>
     <row r="16">
@@ -5086,70 +5086,70 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>-0.099250221202378683</v>
+        <v>-0.078750656186057547</v>
       </c>
       <c r="C16">
-        <v>-4.5510911764586781e-08</v>
+        <v>2.4485614070246394e-06</v>
       </c>
       <c r="D16">
-        <v>-3.333472753250566e-10</v>
+        <v>-2.8193403910187247e-08</v>
       </c>
       <c r="E16">
-        <v>8.5898755718704239e-06</v>
+        <v>1.6520134236658164e-05</v>
       </c>
       <c r="F16">
-        <v>-7.4351468300296375e-05</v>
+        <v>-5.6215128617929705e-05</v>
       </c>
       <c r="G16">
-        <v>-1.6469409410990925e-07</v>
+        <v>-3.3794786108738866e-07</v>
       </c>
       <c r="H16">
-        <v>1.2246797172414812e-06</v>
+        <v>8.5989235956969206e-07</v>
       </c>
       <c r="I16">
-        <v>-5.6297964760295236e-06</v>
+        <v>-2.4553952783814192e-06</v>
       </c>
       <c r="J16">
-        <v>6.7766769180182033e-05</v>
+        <v>-1.3802407198192849e-05</v>
       </c>
       <c r="K16">
-        <v>1.8354590839911024e-05</v>
+        <v>2.5549619243840432e-05</v>
       </c>
       <c r="L16">
-        <v>-1.0119234219867484e-05</v>
+        <v>4.278264441372339e-06</v>
       </c>
       <c r="M16">
-        <v>-2.7373492872553125e-05</v>
+        <v>-9.1106574615597486e-06</v>
       </c>
       <c r="N16">
-        <v>-3.8144505001714748e-05</v>
+        <v>-1.6954410243606868e-05</v>
       </c>
       <c r="O16">
-        <v>0.00046923668070882545</v>
+        <v>0.00042216584961812901</v>
       </c>
       <c r="P16">
-        <v>0.00046927009111282924</v>
+        <v>0.00042214722913441744</v>
       </c>
       <c r="Q16">
-        <v>0.00087148373394928301</v>
+        <v>0.000781690444002283</v>
       </c>
       <c r="R16">
-        <v>0.00047043437434652583</v>
+        <v>0.00042322053426806683</v>
       </c>
       <c r="S16">
-        <v>0.00047312580990481359</v>
+        <v>0.00042570182051519914</v>
       </c>
       <c r="T16">
-        <v>0.00047010430500697502</v>
+        <v>0.00042237196742181692</v>
       </c>
       <c r="U16">
-        <v>-1.1203049043353548e-05</v>
+        <v>-8.433700117015425e-06</v>
       </c>
       <c r="V16">
-        <v>-1.1725305442614947e-05</v>
+        <v>-9.5689870257478539e-06</v>
       </c>
       <c r="W16">
-        <v>-0.00043269247586881542</v>
+        <v>-0.00045272100484141194</v>
       </c>
     </row>
     <row r="17">
@@ -5157,70 +5157,70 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>0.03580376024157797</v>
+        <v>0.052858735945145424</v>
       </c>
       <c r="C17">
-        <v>2.7833101866618982e-06</v>
+        <v>5.4005619281371689e-06</v>
       </c>
       <c r="D17">
-        <v>-2.932623301597289e-08</v>
+        <v>-5.9293833597263886e-08</v>
       </c>
       <c r="E17">
-        <v>2.4301926811353437e-06</v>
+        <v>1.5319065618404014e-05</v>
       </c>
       <c r="F17">
-        <v>-3.704536155166998e-05</v>
+        <v>-2.4961829883317909e-05</v>
       </c>
       <c r="G17">
-        <v>-2.0110568675159677e-07</v>
+        <v>-4.766370617079262e-07</v>
       </c>
       <c r="H17">
-        <v>8.1351876415390696e-07</v>
+        <v>5.1460498825877545e-07</v>
       </c>
       <c r="I17">
-        <v>-8.7334575095057433e-06</v>
+        <v>-4.2684872494050983e-06</v>
       </c>
       <c r="J17">
-        <v>5.0253621813979872e-05</v>
+        <v>-1.6767369914502567e-05</v>
       </c>
       <c r="K17">
-        <v>1.7502692522889457e-05</v>
+        <v>2.9361686160015165e-05</v>
       </c>
       <c r="L17">
-        <v>4.2900460984274778e-06</v>
+        <v>1.6779112074569375e-05</v>
       </c>
       <c r="M17">
-        <v>-9.5150565468413429e-06</v>
+        <v>7.4634355775772413e-06</v>
       </c>
       <c r="N17">
-        <v>-4.1644807801824919e-05</v>
+        <v>-1.7618570052276386e-05</v>
       </c>
       <c r="O17">
-        <v>0.0004710651843647419</v>
+        <v>0.00042366929378590614</v>
       </c>
       <c r="P17">
-        <v>0.00047173769707258039</v>
+        <v>0.00042438899469800776</v>
       </c>
       <c r="Q17">
-        <v>0.00047043437434652583</v>
+        <v>0.00042322053426806683</v>
       </c>
       <c r="R17">
-        <v>0.00074315463006871605</v>
+        <v>0.00065228594021584036</v>
       </c>
       <c r="S17">
-        <v>0.00047303262473484331</v>
+        <v>0.00042560259212658704</v>
       </c>
       <c r="T17">
-        <v>0.00047114234067771404</v>
+        <v>0.00042344558241930619</v>
       </c>
       <c r="U17">
-        <v>1.0286197996808977e-05</v>
+        <v>1.4478853865859706e-05</v>
       </c>
       <c r="V17">
-        <v>1.1737240965023073e-05</v>
+        <v>1.4669598420611913e-05</v>
       </c>
       <c r="W17">
-        <v>-0.00051609055701025094</v>
+        <v>-0.00053495396980473664</v>
       </c>
     </row>
     <row r="18">
@@ -5228,70 +5228,70 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>-0.18592944609549883</v>
+        <v>-0.16106599499737467</v>
       </c>
       <c r="C18">
-        <v>1.0676091693178568e-06</v>
+        <v>3.7941119332633169e-06</v>
       </c>
       <c r="D18">
-        <v>-8.8701674518747906e-09</v>
+        <v>-4.0261836804159125e-08</v>
       </c>
       <c r="E18">
-        <v>-2.9850623349376928e-05</v>
+        <v>-1.0223069220110485e-05</v>
       </c>
       <c r="F18">
-        <v>-0.00011679445542834764</v>
+        <v>-9.5365212390587952e-05</v>
       </c>
       <c r="G18">
-        <v>5.3371271921616794e-07</v>
+        <v>1.4481119756810726e-07</v>
       </c>
       <c r="H18">
-        <v>1.9325278104527057e-06</v>
+        <v>1.5035721594131189e-06</v>
       </c>
       <c r="I18">
-        <v>-2.606697666044876e-06</v>
+        <v>2.0932982755478784e-06</v>
       </c>
       <c r="J18">
-        <v>1.9353312420564719e-05</v>
+        <v>-1.8532693821311366e-05</v>
       </c>
       <c r="K18">
-        <v>2.6272956383322867e-05</v>
+        <v>2.6052897418697094e-05</v>
       </c>
       <c r="L18">
-        <v>-2.7713845261787437e-06</v>
+        <v>8.5049575997847311e-07</v>
       </c>
       <c r="M18">
-        <v>-1.5376978392558241e-05</v>
+        <v>-8.2807623491552341e-06</v>
       </c>
       <c r="N18">
-        <v>-4.2854933628888447e-05</v>
+        <v>-3.0955975819405522e-05</v>
       </c>
       <c r="O18">
-        <v>0.000469497365033381</v>
+        <v>0.00042262458653135986</v>
       </c>
       <c r="P18">
-        <v>0.00047014273902040276</v>
+        <v>0.00042329754278658846</v>
       </c>
       <c r="Q18">
-        <v>0.00047312580990481359</v>
+        <v>0.00042570182051519914</v>
       </c>
       <c r="R18">
-        <v>0.00047303262473484331</v>
+        <v>0.00042560259212658704</v>
       </c>
       <c r="S18">
-        <v>0.00082437807573208495</v>
+        <v>0.00073552618280577434</v>
       </c>
       <c r="T18">
-        <v>0.00047377353263053059</v>
+        <v>0.00042567794357330685</v>
       </c>
       <c r="U18">
-        <v>-3.4409571029095844e-06</v>
+        <v>1.1964294534219665e-06</v>
       </c>
       <c r="V18">
-        <v>-4.5646146519466256e-06</v>
+        <v>-1.4660471262690201e-06</v>
       </c>
       <c r="W18">
-        <v>-0.00047264219823420645</v>
+        <v>-0.00048487283954277727</v>
       </c>
     </row>
     <row r="19">
@@ -5299,70 +5299,70 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>-0.16943328765990912</v>
+        <v>-0.135825802120836</v>
       </c>
       <c r="C19">
-        <v>-1.5859953528869536e-06</v>
+        <v>-2.260043436936677e-07</v>
       </c>
       <c r="D19">
-        <v>2.1438709781452967e-08</v>
+        <v>5.7295706707113009e-09</v>
       </c>
       <c r="E19">
-        <v>-8.6732879960193984e-06</v>
+        <v>-1.6559814167977748e-07</v>
       </c>
       <c r="F19">
-        <v>-8.0583503672852257e-05</v>
+        <v>-6.031309723040548e-05</v>
       </c>
       <c r="G19">
-        <v>-4.3486899884683458e-08</v>
+        <v>-1.8760321035369524e-07</v>
       </c>
       <c r="H19">
-        <v>1.4709641125568748e-06</v>
+        <v>1.0564369302850906e-06</v>
       </c>
       <c r="I19">
-        <v>1.9901236583877612e-05</v>
+        <v>1.9162917473249433e-05</v>
       </c>
       <c r="J19">
-        <v>0.00011820103657441367</v>
+        <v>-7.5491457290265346e-06</v>
       </c>
       <c r="K19">
-        <v>6.0247749972652565e-05</v>
+        <v>6.3604519814932238e-05</v>
       </c>
       <c r="L19">
-        <v>1.6082066797378114e-05</v>
+        <v>2.9610352200449452e-05</v>
       </c>
       <c r="M19">
-        <v>2.5813175832062609e-05</v>
+        <v>3.9261263618007132e-05</v>
       </c>
       <c r="N19">
-        <v>4.1535868367828817e-06</v>
+        <v>2.0652545769368004e-05</v>
       </c>
       <c r="O19">
-        <v>0.00046818112937872293</v>
+        <v>0.00042096771102720658</v>
       </c>
       <c r="P19">
-        <v>0.00047047650778599451</v>
+        <v>0.00042305978563627678</v>
       </c>
       <c r="Q19">
-        <v>0.00047010430500697502</v>
+        <v>0.00042237196742181692</v>
       </c>
       <c r="R19">
-        <v>0.00047114234067771404</v>
+        <v>0.00042344558241930619</v>
       </c>
       <c r="S19">
-        <v>0.00047377353263053059</v>
+        <v>0.00042567794357330685</v>
       </c>
       <c r="T19">
-        <v>0.002088132716805365</v>
+        <v>0.0018658660179841919</v>
       </c>
       <c r="U19">
-        <v>6.4620514914735336e-06</v>
+        <v>9.4091446190515509e-06</v>
       </c>
       <c r="V19">
-        <v>9.5869230351245819e-06</v>
+        <v>1.0174472272877877e-05</v>
       </c>
       <c r="W19">
-        <v>-0.00047502079889227838</v>
+        <v>-0.00046567019009640314</v>
       </c>
     </row>
     <row r="20">
@@ -5370,70 +5370,70 @@
         <v>42</v>
       </c>
       <c r="B20">
-        <v>-0.11328358163543387</v>
+        <v>-0.15204688728582652</v>
       </c>
       <c r="C20">
-        <v>6.4428046560659967e-07</v>
+        <v>7.4443879859393309e-07</v>
       </c>
       <c r="D20">
-        <v>-1.2732135065008081e-08</v>
+        <v>-1.1439799954674747e-08</v>
       </c>
       <c r="E20">
-        <v>1.8501259477093743e-05</v>
+        <v>1.5951222429015683e-05</v>
       </c>
       <c r="F20">
-        <v>2.8927638536724631e-05</v>
+        <v>3.2369995515503299e-05</v>
       </c>
       <c r="G20">
-        <v>-1.8409577426498135e-07</v>
+        <v>-1.8809430049115851e-07</v>
       </c>
       <c r="H20">
-        <v>-2.6681804510713692e-07</v>
+        <v>-4.6454352798112921e-07</v>
       </c>
       <c r="I20">
-        <v>-5.9311727403353487e-06</v>
+        <v>-4.1330805374154734e-06</v>
       </c>
       <c r="J20">
-        <v>5.2480443651226256e-05</v>
+        <v>-6.1301798897019849e-06</v>
       </c>
       <c r="K20">
-        <v>-1.4915699964949509e-05</v>
+        <v>-1.0893199412724915e-05</v>
       </c>
       <c r="L20">
-        <v>-1.81417392115132e-05</v>
+        <v>-1.5517592066413316e-05</v>
       </c>
       <c r="M20">
-        <v>-1.883973666230486e-05</v>
+        <v>-1.8194938227746931e-05</v>
       </c>
       <c r="N20">
-        <v>-2.5205775768008805e-05</v>
+        <v>-2.547821829792273e-05</v>
       </c>
       <c r="O20">
-        <v>1.7360087563435116e-06</v>
+        <v>4.511674315152125e-06</v>
       </c>
       <c r="P20">
-        <v>-5.1777168574167428e-06</v>
+        <v>-2.3792089849083077e-06</v>
       </c>
       <c r="Q20">
-        <v>-1.1203049043353548e-05</v>
+        <v>-8.433700117015425e-06</v>
       </c>
       <c r="R20">
-        <v>1.0286197996808977e-05</v>
+        <v>1.4478853865859706e-05</v>
       </c>
       <c r="S20">
-        <v>-3.4409571029095844e-06</v>
+        <v>1.1964294534219665e-06</v>
       </c>
       <c r="T20">
-        <v>6.4620514914735336e-06</v>
+        <v>9.4091446190515509e-06</v>
       </c>
       <c r="U20">
-        <v>0.00092181448671570156</v>
+        <v>0.00091154740707888294</v>
       </c>
       <c r="V20">
-        <v>7.5744778613289876e-05</v>
+        <v>6.4887733205119507e-05</v>
       </c>
       <c r="W20">
-        <v>-5.8595920483942314e-05</v>
+        <v>-5.5688541172194622e-05</v>
       </c>
     </row>
     <row r="21">
@@ -5441,70 +5441,70 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>0.025606980698442285</v>
+        <v>0.026663191684803276</v>
       </c>
       <c r="C21">
-        <v>-2.4608444896981984e-06</v>
+        <v>-1.2530163930393205e-06</v>
       </c>
       <c r="D21">
-        <v>2.1652126458575811e-08</v>
+        <v>1.1122820945452113e-08</v>
       </c>
       <c r="E21">
-        <v>2.8483267344695754e-05</v>
+        <v>2.8115213761436599e-05</v>
       </c>
       <c r="F21">
-        <v>4.1511906589945642e-05</v>
+        <v>4.3041152185741951e-05</v>
       </c>
       <c r="G21">
-        <v>-3.7475403016374888e-07</v>
+        <v>-4.5847018074486989e-07</v>
       </c>
       <c r="H21">
-        <v>-2.1963049024837856e-07</v>
+        <v>-4.4799985437316903e-07</v>
       </c>
       <c r="I21">
-        <v>-6.1797809405181669e-06</v>
+        <v>-3.5013528475145101e-06</v>
       </c>
       <c r="J21">
-        <v>2.3362080216173504e-05</v>
+        <v>-8.6713804594057136e-06</v>
       </c>
       <c r="K21">
-        <v>3.6694161314550386e-05</v>
+        <v>3.1086774629481877e-05</v>
       </c>
       <c r="L21">
-        <v>3.2174505271338713e-05</v>
+        <v>2.8611271935898903e-05</v>
       </c>
       <c r="M21">
-        <v>3.6563390223014352e-05</v>
+        <v>3.0842942201597627e-05</v>
       </c>
       <c r="N21">
-        <v>3.3571330108055821e-05</v>
+        <v>2.7384510137669768e-05</v>
       </c>
       <c r="O21">
-        <v>-5.3093052501861922e-07</v>
+        <v>5.955067363998736e-07</v>
       </c>
       <c r="P21">
-        <v>-1.431906753762378e-05</v>
+        <v>-1.0135363846915328e-05</v>
       </c>
       <c r="Q21">
-        <v>-1.1725305442614947e-05</v>
+        <v>-9.5689870257478539e-06</v>
       </c>
       <c r="R21">
-        <v>1.1737240965023073e-05</v>
+        <v>1.4669598420611913e-05</v>
       </c>
       <c r="S21">
-        <v>-4.5646146519466256e-06</v>
+        <v>-1.4660471262690201e-06</v>
       </c>
       <c r="T21">
-        <v>9.5869230351245819e-06</v>
+        <v>1.0174472272877877e-05</v>
       </c>
       <c r="U21">
-        <v>7.5744778613289876e-05</v>
+        <v>6.4887733205119507e-05</v>
       </c>
       <c r="V21">
-        <v>0.0010538940613670769</v>
+        <v>0.001082927021884643</v>
       </c>
       <c r="W21">
-        <v>-5.2191780212693045e-05</v>
+        <v>-6.4304610506759309e-05</v>
       </c>
     </row>
     <row r="22">
@@ -5512,70 +5512,70 @@
         <v>44</v>
       </c>
       <c r="B22">
-        <v>-2.7948010327052972</v>
+        <v>-2.9550289227465547</v>
       </c>
       <c r="C22">
-        <v>-0.00059359067019433044</v>
+        <v>-0.00059580463930211712</v>
       </c>
       <c r="D22">
-        <v>6.0770771535445493e-06</v>
+        <v>6.2060900132489428e-06</v>
       </c>
       <c r="E22">
-        <v>-0.0025197464125829567</v>
+        <v>-0.0023801401078947602</v>
       </c>
       <c r="F22">
-        <v>-0.0016560323521552008</v>
+        <v>-0.0017237712088299412</v>
       </c>
       <c r="G22">
-        <v>5.0807519243301652e-05</v>
+        <v>4.8074717002199028e-05</v>
       </c>
       <c r="H22">
-        <v>3.0501911214222998e-05</v>
+        <v>3.3253971797968724e-05</v>
       </c>
       <c r="I22">
-        <v>0.00052362790018054656</v>
+        <v>0.00025058448675194386</v>
       </c>
       <c r="J22">
-        <v>-0.003333707186346417</v>
+        <v>0.00073539763712275152</v>
       </c>
       <c r="K22">
-        <v>-0.010024002271480469</v>
+        <v>-0.0084058833483083573</v>
       </c>
       <c r="L22">
-        <v>-0.010075066009677398</v>
+        <v>-0.0084661599263487521</v>
       </c>
       <c r="M22">
-        <v>-0.010180503499418746</v>
+        <v>-0.008581535024973776</v>
       </c>
       <c r="N22">
-        <v>-0.010438023339420467</v>
+        <v>-0.0088014022867021775</v>
       </c>
       <c r="O22">
-        <v>-0.00047255300945799831</v>
+        <v>-0.00046041484561411771</v>
       </c>
       <c r="P22">
-        <v>-0.00050786740170574057</v>
+        <v>-0.00051168780119030749</v>
       </c>
       <c r="Q22">
-        <v>-0.00043269247586881542</v>
+        <v>-0.00045272100484141194</v>
       </c>
       <c r="R22">
-        <v>-0.00051609055701025094</v>
+        <v>-0.00053495396980473664</v>
       </c>
       <c r="S22">
-        <v>-0.00047264219823420645</v>
+        <v>-0.00048487283954277727</v>
       </c>
       <c r="T22">
-        <v>-0.00047502079889227838</v>
+        <v>-0.00046567019009640314</v>
       </c>
       <c r="U22">
-        <v>-5.8595920483942314e-05</v>
+        <v>-5.5688541172194622e-05</v>
       </c>
       <c r="V22">
-        <v>-5.2191780212693045e-05</v>
+        <v>-6.4304610506759309e-05</v>
       </c>
       <c r="W22">
-        <v>0.023966291865025968</v>
+        <v>0.022043792023922266</v>
       </c>
     </row>
   </sheetData>
@@ -5663,70 +5663,70 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>0.17506722218668996</v>
+        <v>0.17442859940526151</v>
       </c>
       <c r="C2">
-        <v>2.4383979518252191e-05</v>
+        <v>2.3540481476380495e-05</v>
       </c>
       <c r="D2">
-        <v>-2.5154161321019696e-07</v>
+        <v>-2.4690738897113527e-07</v>
       </c>
       <c r="E2">
-        <v>9.2684637959449234e-05</v>
+        <v>8.6326187823058498e-05</v>
       </c>
       <c r="F2">
-        <v>6.5735064898773618e-05</v>
+        <v>6.7279629578022288e-05</v>
       </c>
       <c r="G2">
-        <v>-1.9818959085379269e-06</v>
+        <v>-1.841771682607623e-06</v>
       </c>
       <c r="H2">
-        <v>-1.3557146720993352e-06</v>
+        <v>-1.4047848056821556e-06</v>
       </c>
       <c r="I2">
-        <v>-2.9258870682401835e-05</v>
+        <v>-8.3784328262538214e-06</v>
       </c>
       <c r="J2">
-        <v>0.00013315244763569835</v>
+        <v>-3.26669937577565e-05</v>
       </c>
       <c r="K2">
-        <v>1.067612383873258e-06</v>
+        <v>3.8135368253258901e-06</v>
       </c>
       <c r="L2">
-        <v>1.1816989752240151e-06</v>
+        <v>4.1298777112637637e-06</v>
       </c>
       <c r="M2">
-        <v>1.557291920292537e-06</v>
+        <v>5.4177598559751168e-06</v>
       </c>
       <c r="N2">
-        <v>1.2332342093267566e-05</v>
+        <v>1.4982633842108601e-05</v>
       </c>
       <c r="O2">
-        <v>4.3872140298603005e-07</v>
+        <v>1.4492586215457886e-06</v>
       </c>
       <c r="P2">
-        <v>1.0962357744224739e-06</v>
+        <v>2.1257839484117095e-06</v>
       </c>
       <c r="Q2">
-        <v>1.0509072585291445e-06</v>
+        <v>1.8089963045000926e-06</v>
       </c>
       <c r="R2">
-        <v>1.4213483259107471e-06</v>
+        <v>2.9204160683974874e-06</v>
       </c>
       <c r="S2">
-        <v>2.5175172823005021e-07</v>
+        <v>1.8904551487158973e-06</v>
       </c>
       <c r="T2">
-        <v>4.6327688598461331e-07</v>
+        <v>-6.6572586339490597e-07</v>
       </c>
       <c r="U2">
-        <v>1.1102097858498659e-06</v>
+        <v>1.1732112743566433e-06</v>
       </c>
       <c r="V2">
-        <v>-3.7875560303615868e-06</v>
+        <v>-2.8424526832009631e-06</v>
       </c>
       <c r="W2">
-        <v>-0.0005376225640889629</v>
+        <v>-0.00051560859631771924</v>
       </c>
     </row>
     <row r="3">
@@ -5734,70 +5734,70 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>-0.0019947230783767074</v>
+        <v>-0.001982681450141399</v>
       </c>
       <c r="C3">
-        <v>-2.5154161321019696e-07</v>
+        <v>-2.4690738897113527e-07</v>
       </c>
       <c r="D3">
-        <v>2.749399772458454e-09</v>
+        <v>2.7261971320221491e-09</v>
       </c>
       <c r="E3">
-        <v>-4.0602176026941059e-07</v>
+        <v>-4.3319953195562748e-07</v>
       </c>
       <c r="F3">
-        <v>-1.0127867610176458e-07</v>
+        <v>-2.205601942484314e-07</v>
       </c>
       <c r="G3">
-        <v>8.2625156777265378e-09</v>
+        <v>9.0139420847144023e-09</v>
       </c>
       <c r="H3">
-        <v>1.2717736372856673e-09</v>
+        <v>4.2066689288053733e-09</v>
       </c>
       <c r="I3">
-        <v>2.6018302588475731e-07</v>
+        <v>2.1102870308185995e-08</v>
       </c>
       <c r="J3">
-        <v>-1.462828374068274e-06</v>
+        <v>3.9420474748565146e-07</v>
       </c>
       <c r="K3">
-        <v>-1.6091183284793418e-08</v>
+        <v>-4.1955528622624714e-08</v>
       </c>
       <c r="L3">
-        <v>-1.0022543965964785e-08</v>
+        <v>-4.1606169583271956e-08</v>
       </c>
       <c r="M3">
-        <v>7.6130078202181579e-09</v>
+        <v>-3.8288062129341314e-08</v>
       </c>
       <c r="N3">
-        <v>-7.4160989483513046e-08</v>
+        <v>-1.1131903512515188e-07</v>
       </c>
       <c r="O3">
-        <v>2.0648083408687755e-09</v>
+        <v>-1.0633933954931216e-08</v>
       </c>
       <c r="P3">
-        <v>-8.5531451048050645e-09</v>
+        <v>-2.0288623176399256e-08</v>
       </c>
       <c r="Q3">
-        <v>-5.4983769330868275e-09</v>
+        <v>-1.5471502880211322e-08</v>
       </c>
       <c r="R3">
-        <v>-1.0102287857832988e-08</v>
+        <v>-2.7270549691602506e-08</v>
       </c>
       <c r="S3">
-        <v>2.3320067725331959e-09</v>
+        <v>-1.743519163661006e-08</v>
       </c>
       <c r="T3">
-        <v>-3.1533175762774457e-09</v>
+        <v>9.075061433684419e-09</v>
       </c>
       <c r="U3">
-        <v>-1.3265344362586473e-08</v>
+        <v>-1.245225106256128e-08</v>
       </c>
       <c r="V3">
-        <v>3.2228859357369165e-08</v>
+        <v>2.4818422905359576e-08</v>
       </c>
       <c r="W3">
-        <v>5.2041780256028574e-06</v>
+        <v>5.1027282669180229e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5805,70 +5805,70 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>-0.18970511635980813</v>
+        <v>-0.22303604243477251</v>
       </c>
       <c r="C4">
-        <v>9.2684637959449234e-05</v>
+        <v>8.6326187823058498e-05</v>
       </c>
       <c r="D4">
-        <v>-4.0602176026941059e-07</v>
+        <v>-4.3319953195562748e-07</v>
       </c>
       <c r="E4">
-        <v>0.0061129676552613638</v>
+        <v>0.0052530126720557848</v>
       </c>
       <c r="F4">
-        <v>0.0027289783380811516</v>
+        <v>0.0023632006392280444</v>
       </c>
       <c r="G4">
-        <v>-0.00012658454849789251</v>
+        <v>-0.00010769552662273962</v>
       </c>
       <c r="H4">
-        <v>-5.6197500271803086e-05</v>
+        <v>-4.8206448817158059e-05</v>
       </c>
       <c r="I4">
-        <v>-2.4051419106634025e-05</v>
+        <v>1.5140063761703109e-05</v>
       </c>
       <c r="J4">
-        <v>-0.00012938007513319834</v>
+        <v>-7.5574110702302988e-05</v>
       </c>
       <c r="K4">
-        <v>-3.8216450846375859e-06</v>
+        <v>1.9026621487829628e-05</v>
       </c>
       <c r="L4">
-        <v>1.215049930160794e-05</v>
+        <v>2.5377330503558154e-05</v>
       </c>
       <c r="M4">
-        <v>2.2499087497850764e-06</v>
+        <v>1.701013276155872e-05</v>
       </c>
       <c r="N4">
-        <v>2.2218839697348027e-05</v>
+        <v>3.4848488909314376e-05</v>
       </c>
       <c r="O4">
-        <v>4.8300767906043883e-05</v>
+        <v>4.5527246550326887e-05</v>
       </c>
       <c r="P4">
-        <v>2.2513374964042759e-05</v>
+        <v>2.2485546038093937e-05</v>
       </c>
       <c r="Q4">
-        <v>2.9649431080900753e-05</v>
+        <v>3.0269242733900469e-05</v>
       </c>
       <c r="R4">
-        <v>3.101580451640605e-05</v>
+        <v>3.4038198616015766e-05</v>
       </c>
       <c r="S4">
-        <v>-5.6933961550265461e-06</v>
+        <v>3.9166500075902682e-06</v>
       </c>
       <c r="T4">
-        <v>-1.5312375890319195e-05</v>
+        <v>-1.797114129143143e-05</v>
       </c>
       <c r="U4">
-        <v>1.3754055509507192e-05</v>
+        <v>1.0660073195828203e-05</v>
       </c>
       <c r="V4">
-        <v>2.1926694904936809e-05</v>
+        <v>1.7911249677234527e-05</v>
       </c>
       <c r="W4">
-        <v>-0.0034951515357835084</v>
+        <v>-0.0031596309752217316</v>
       </c>
     </row>
     <row r="5">
@@ -5876,70 +5876,70 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>-0.33214492007443297</v>
+        <v>-0.3681065448670513</v>
       </c>
       <c r="C5">
-        <v>6.5735064898773618e-05</v>
+        <v>6.7279629578022288e-05</v>
       </c>
       <c r="D5">
-        <v>-1.0127867610176458e-07</v>
+        <v>-2.205601942484314e-07</v>
       </c>
       <c r="E5">
-        <v>0.0027289783380811516</v>
+        <v>0.0023632006392280444</v>
       </c>
       <c r="F5">
-        <v>0.0047612206796333132</v>
+        <v>0.0042197355274177333</v>
       </c>
       <c r="G5">
-        <v>-5.6305966152428003e-05</v>
+        <v>-4.828029927428279e-05</v>
       </c>
       <c r="H5">
-        <v>-9.6564051730453789e-05</v>
+        <v>-8.4900586554641382e-05</v>
       </c>
       <c r="I5">
-        <v>-3.022181075841756e-05</v>
+        <v>2.1408138502450647e-05</v>
       </c>
       <c r="J5">
-        <v>-0.00095647360535605088</v>
+        <v>-0.00010774041306279599</v>
       </c>
       <c r="K5">
-        <v>2.0377678816295995e-05</v>
+        <v>1.7419654993261306e-05</v>
       </c>
       <c r="L5">
-        <v>9.1746420983213502e-06</v>
+        <v>-2.0851529617931658e-06</v>
       </c>
       <c r="M5">
-        <v>-8.6869900484101091e-06</v>
+        <v>-1.7230834154677863e-05</v>
       </c>
       <c r="N5">
-        <v>5.2562023301968803e-05</v>
+        <v>3.2197462247023512e-05</v>
       </c>
       <c r="O5">
-        <v>5.6910683863529433e-05</v>
+        <v>5.2569146040668454e-05</v>
       </c>
       <c r="P5">
-        <v>4.0067254405445394e-05</v>
+        <v>3.2682154206748211e-05</v>
       </c>
       <c r="Q5">
-        <v>-1.459545194759504e-05</v>
+        <v>-1.0065880009931665e-05</v>
       </c>
       <c r="R5">
-        <v>2.272125956267224e-06</v>
+        <v>9.8866562788718838e-06</v>
       </c>
       <c r="S5">
-        <v>-6.2825308508051593e-05</v>
+        <v>-4.8109150269245218e-05</v>
       </c>
       <c r="T5">
-        <v>-3.4896278334126017e-05</v>
+        <v>-2.8828232449395916e-05</v>
       </c>
       <c r="U5">
-        <v>3.8510969066483677e-05</v>
+        <v>3.3227023837756691e-05</v>
       </c>
       <c r="V5">
-        <v>2.0384502718689275e-05</v>
+        <v>1.9449267148431614e-05</v>
       </c>
       <c r="W5">
-        <v>-0.0029229828724894602</v>
+        <v>-0.002716288639685099</v>
       </c>
     </row>
     <row r="6">
@@ -5947,70 +5947,70 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>0.0028016801426387341</v>
+        <v>0.0024884314897051021</v>
       </c>
       <c r="C6">
-        <v>-1.9818959085379269e-06</v>
+        <v>-1.841771682607623e-06</v>
       </c>
       <c r="D6">
-        <v>8.2625156777265378e-09</v>
+        <v>9.0139420847144023e-09</v>
       </c>
       <c r="E6">
-        <v>-0.00012658454849789251</v>
+        <v>-0.00010769552662273962</v>
       </c>
       <c r="F6">
-        <v>-5.6305966152428003e-05</v>
+        <v>-4.828029927428279e-05</v>
       </c>
       <c r="G6">
-        <v>2.8192459703972366e-06</v>
+        <v>2.3747427634620731e-06</v>
       </c>
       <c r="H6">
-        <v>1.243082381290842e-06</v>
+        <v>1.0557914605659875e-06</v>
       </c>
       <c r="I6">
-        <v>4.7670169970641314e-07</v>
+        <v>-4.9441835118983433e-07</v>
       </c>
       <c r="J6">
-        <v>2.4284385179500861e-06</v>
+        <v>1.7788426622228975e-06</v>
       </c>
       <c r="K6">
-        <v>-5.2823080268943994e-08</v>
+        <v>-5.6989828509411284e-07</v>
       </c>
       <c r="L6">
-        <v>-3.2460690023255557e-07</v>
+        <v>-6.9025219356646058e-07</v>
       </c>
       <c r="M6">
-        <v>2.2103156800620932e-07</v>
+        <v>-2.2880282408566839e-07</v>
       </c>
       <c r="N6">
-        <v>-4.8991675277028192e-08</v>
+        <v>-4.4683293823429392e-07</v>
       </c>
       <c r="O6">
-        <v>-9.5555633216184534e-07</v>
+        <v>-8.9551885398833311e-07</v>
       </c>
       <c r="P6">
-        <v>-2.227092381147214e-07</v>
+        <v>-2.3032673164631348e-07</v>
       </c>
       <c r="Q6">
-        <v>-7.8633380437838424e-07</v>
+        <v>-7.6771661917475667e-07</v>
       </c>
       <c r="R6">
-        <v>-7.4382698762537833e-07</v>
+        <v>-7.7994779567172666e-07</v>
       </c>
       <c r="S6">
-        <v>-4.1411358330712673e-08</v>
+        <v>-2.1150540845897405e-07</v>
       </c>
       <c r="T6">
-        <v>2.3241110484949679e-07</v>
+        <v>3.0132978253550991e-07</v>
       </c>
       <c r="U6">
-        <v>-2.8167438997013632e-07</v>
+        <v>-2.528205994179068e-07</v>
       </c>
       <c r="V6">
-        <v>-3.2808101323384381e-07</v>
+        <v>-2.9313864847253634e-07</v>
       </c>
       <c r="W6">
-        <v>7.1608218535988509e-05</v>
+        <v>6.4544112324254916e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6018,70 +6018,70 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>0.0015858785992986881</v>
+        <v>0.0018072833798249547</v>
       </c>
       <c r="C7">
-        <v>-1.3557146720993352e-06</v>
+        <v>-1.4047848056821556e-06</v>
       </c>
       <c r="D7">
-        <v>1.2717736372856673e-09</v>
+        <v>4.2066689288053733e-09</v>
       </c>
       <c r="E7">
-        <v>-5.6197500271803086e-05</v>
+        <v>-4.8206448817158059e-05</v>
       </c>
       <c r="F7">
-        <v>-9.6564051730453789e-05</v>
+        <v>-8.4900586554641382e-05</v>
       </c>
       <c r="G7">
-        <v>1.243082381290842e-06</v>
+        <v>1.0557914605659875e-06</v>
       </c>
       <c r="H7">
-        <v>2.1016170523950299e-06</v>
+        <v>1.8319155251811902e-06</v>
       </c>
       <c r="I7">
-        <v>4.3664284133598971e-07</v>
+        <v>-7.7768997739940933e-07</v>
       </c>
       <c r="J7">
-        <v>1.8558798497279576e-05</v>
+        <v>2.4492094754093477e-06</v>
       </c>
       <c r="K7">
-        <v>-2.6933672667383386e-07</v>
+        <v>-2.939926663553366e-07</v>
       </c>
       <c r="L7">
-        <v>1.5218451887476079e-07</v>
+        <v>2.6043621860971037e-07</v>
       </c>
       <c r="M7">
-        <v>1.1452365498298725e-06</v>
+        <v>1.1239820612721362e-06</v>
       </c>
       <c r="N7">
-        <v>2.686496278392668e-07</v>
+        <v>4.457761217491508e-07</v>
       </c>
       <c r="O7">
-        <v>-8.6391057769693324e-07</v>
+        <v>-8.1171599895270211e-07</v>
       </c>
       <c r="P7">
-        <v>-1.2491177931334186e-07</v>
+        <v>-6.729975605870186e-08</v>
       </c>
       <c r="Q7">
-        <v>-3.3098441281693578e-07</v>
+        <v>-3.5189121771052658e-07</v>
       </c>
       <c r="R7">
-        <v>5.5540469325208818e-09</v>
+        <v>-1.4947989252864334e-07</v>
       </c>
       <c r="S7">
-        <v>7.8909170608581384e-07</v>
+        <v>5.2467382060500317e-07</v>
       </c>
       <c r="T7">
-        <v>6.0078527922802455e-07</v>
+        <v>5.0367721789776936e-07</v>
       </c>
       <c r="U7">
-        <v>-6.6228993684569063e-07</v>
+        <v>-6.4949585722650761e-07</v>
       </c>
       <c r="V7">
-        <v>-1.3548594262643645e-07</v>
+        <v>-2.397107008800051e-07</v>
       </c>
       <c r="W7">
-        <v>5.7525089240895356e-05</v>
+        <v>5.3759915239246632e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6089,70 +6089,70 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>0.17499963997598839</v>
+        <v>0.18118017266028952</v>
       </c>
       <c r="C8">
-        <v>-2.9258870682401835e-05</v>
+        <v>-8.3784328262538214e-06</v>
       </c>
       <c r="D8">
-        <v>2.6018302588475731e-07</v>
+        <v>2.1102870308185995e-08</v>
       </c>
       <c r="E8">
-        <v>-2.4051419106634025e-05</v>
+        <v>1.5140063761703109e-05</v>
       </c>
       <c r="F8">
-        <v>-3.022181075841756e-05</v>
+        <v>2.1408138502450647e-05</v>
       </c>
       <c r="G8">
-        <v>4.7670169970641314e-07</v>
+        <v>-4.9441835118983433e-07</v>
       </c>
       <c r="H8">
-        <v>4.3664284133598971e-07</v>
+        <v>-7.7768997739940933e-07</v>
       </c>
       <c r="I8">
-        <v>0.00034327823176675941</v>
+        <v>0.00039252652657021818</v>
       </c>
       <c r="J8">
-        <v>-7.5027716278430975e-05</v>
+        <v>-0.0001925530822904217</v>
       </c>
       <c r="K8">
-        <v>-1.1092028943360559e-05</v>
+        <v>-1.430822479609374e-05</v>
       </c>
       <c r="L8">
-        <v>-1.5940040212476883e-05</v>
+        <v>-1.3360498493370884e-05</v>
       </c>
       <c r="M8">
-        <v>-2.4447394452737402e-05</v>
+        <v>-1.9186665910185408e-05</v>
       </c>
       <c r="N8">
-        <v>-2.4758126170353e-05</v>
+        <v>-2.0610247432579201e-05</v>
       </c>
       <c r="O8">
-        <v>-1.8460883139649595e-06</v>
+        <v>3.5781469862081961e-06</v>
       </c>
       <c r="P8">
-        <v>-9.0336353472270046e-06</v>
+        <v>-5.886360260662342e-06</v>
       </c>
       <c r="Q8">
-        <v>-4.403391235684271e-06</v>
+        <v>1.5912262714970239e-07</v>
       </c>
       <c r="R8">
-        <v>-9.6204798947946073e-06</v>
+        <v>-3.7783358534563469e-06</v>
       </c>
       <c r="S8">
-        <v>-1.9495668683271825e-05</v>
+        <v>-8.2011121265418905e-06</v>
       </c>
       <c r="T8">
-        <v>4.6038010503024925e-06</v>
+        <v>5.2804444345689541e-06</v>
       </c>
       <c r="U8">
-        <v>-2.9758441612844177e-07</v>
+        <v>2.0687404830747441e-07</v>
       </c>
       <c r="V8">
-        <v>1.3435139598592764e-05</v>
+        <v>1.2270848759757568e-05</v>
       </c>
       <c r="W8">
-        <v>0.00056486995841063684</v>
+        <v>0.00017673063316534754</v>
       </c>
     </row>
     <row r="9">
@@ -6160,70 +6160,70 @@
         <v>31</v>
       </c>
       <c r="B9">
-        <v>-0.3696740041874681</v>
+        <v>0.0084346163214327717</v>
       </c>
       <c r="C9">
-        <v>0.00013315244763569835</v>
+        <v>-3.26669937577565e-05</v>
       </c>
       <c r="D9">
-        <v>-1.462828374068274e-06</v>
+        <v>3.9420474748565146e-07</v>
       </c>
       <c r="E9">
-        <v>-0.00012938007513319834</v>
+        <v>-7.5574110702302988e-05</v>
       </c>
       <c r="F9">
-        <v>-0.00095647360535605088</v>
+        <v>-0.00010774041306279599</v>
       </c>
       <c r="G9">
-        <v>2.4284385179500861e-06</v>
+        <v>1.7788426622228975e-06</v>
       </c>
       <c r="H9">
-        <v>1.8558798497279576e-05</v>
+        <v>2.4492094754093477e-06</v>
       </c>
       <c r="I9">
-        <v>-7.5027716278430975e-05</v>
+        <v>-0.0001925530822904217</v>
       </c>
       <c r="J9">
-        <v>0.044778604189208829</v>
+        <v>0.00038738937217769977</v>
       </c>
       <c r="K9">
-        <v>-1.2399477992222296e-05</v>
+        <v>-9.5594446015547581e-07</v>
       </c>
       <c r="L9">
-        <v>-3.9306622806414596e-06</v>
+        <v>-6.7261859159997749e-06</v>
       </c>
       <c r="M9">
-        <v>9.9750203729218675e-06</v>
+        <v>-1.3352235170336306e-05</v>
       </c>
       <c r="N9">
-        <v>-2.4961417020613514e-05</v>
+        <v>-1.2568228752221557e-05</v>
       </c>
       <c r="O9">
-        <v>-2.6849662710422302e-05</v>
+        <v>-9.8776580981759437e-06</v>
       </c>
       <c r="P9">
-        <v>-2.1991327025974331e-05</v>
+        <v>-5.2227460761625133e-06</v>
       </c>
       <c r="Q9">
-        <v>-2.0824028727684947e-05</v>
+        <v>-7.756584569302615e-06</v>
       </c>
       <c r="R9">
-        <v>-5.6702693440790487e-05</v>
+        <v>-9.1967218759688907e-06</v>
       </c>
       <c r="S9">
-        <v>-5.110144748122501e-06</v>
+        <v>-1.4450608672886047e-05</v>
       </c>
       <c r="T9">
-        <v>5.662081572278844e-05</v>
+        <v>3.6155749779488691e-06</v>
       </c>
       <c r="U9">
-        <v>2.3344505612602102e-05</v>
+        <v>-5.6013434902318745e-06</v>
       </c>
       <c r="V9">
-        <v>-4.0616795497297109e-05</v>
+        <v>-4.1956606850279706e-06</v>
       </c>
       <c r="W9">
-        <v>-0.0027516766328533888</v>
+        <v>0.00061800271623847585</v>
       </c>
     </row>
     <row r="10">
@@ -6231,70 +6231,70 @@
         <v>32</v>
       </c>
       <c r="B10">
-        <v>0.19044755985018055</v>
+        <v>0.18317355276611266</v>
       </c>
       <c r="C10">
-        <v>1.067612383873258e-06</v>
+        <v>3.8135368253258901e-06</v>
       </c>
       <c r="D10">
-        <v>-1.6091183284793418e-08</v>
+        <v>-4.1955528622624714e-08</v>
       </c>
       <c r="E10">
-        <v>-3.8216450846375859e-06</v>
+        <v>1.9026621487829628e-05</v>
       </c>
       <c r="F10">
-        <v>2.0377678816295995e-05</v>
+        <v>1.7419654993261306e-05</v>
       </c>
       <c r="G10">
-        <v>-5.2823080268943994e-08</v>
+        <v>-5.6989828509411284e-07</v>
       </c>
       <c r="H10">
-        <v>-2.6933672667383386e-07</v>
+        <v>-2.939926663553366e-07</v>
       </c>
       <c r="I10">
-        <v>-1.1092028943360559e-05</v>
+        <v>-1.430822479609374e-05</v>
       </c>
       <c r="J10">
-        <v>-1.2399477992222296e-05</v>
+        <v>-9.5594446015547581e-07</v>
       </c>
       <c r="K10">
-        <v>0.011511830058613776</v>
+        <v>0.0091287707700556265</v>
       </c>
       <c r="L10">
-        <v>0.0096602715031731384</v>
+        <v>0.0075787279332324032</v>
       </c>
       <c r="M10">
-        <v>0.0096572662486520584</v>
+        <v>0.0075769016576795753</v>
       </c>
       <c r="N10">
-        <v>0.0096533106970403265</v>
+        <v>0.0075749332213773295</v>
       </c>
       <c r="O10">
-        <v>4.7770986842013629e-06</v>
+        <v>1.2066759158126881e-05</v>
       </c>
       <c r="P10">
-        <v>-5.944174974961879e-07</v>
+        <v>9.214418427847123e-06</v>
       </c>
       <c r="Q10">
-        <v>-2.9312869855195421e-05</v>
+        <v>-1.7769371088324239e-05</v>
       </c>
       <c r="R10">
-        <v>-1.7473094770705755e-05</v>
+        <v>-8.4978045359928363e-06</v>
       </c>
       <c r="S10">
-        <v>1.7048849545395391e-06</v>
+        <v>3.3824494668758707e-06</v>
       </c>
       <c r="T10">
-        <v>1.1732014867307723e-06</v>
+        <v>1.481619248703994e-05</v>
       </c>
       <c r="U10">
-        <v>4.0270479406493028e-06</v>
+        <v>1.3310316153190914e-07</v>
       </c>
       <c r="V10">
-        <v>-6.2258963814059713e-06</v>
+        <v>-7.2460163601834341e-06</v>
       </c>
       <c r="W10">
-        <v>-0.009656403581416749</v>
+        <v>-0.0076458550531630643</v>
       </c>
     </row>
     <row r="11">
@@ -6302,70 +6302,70 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>0.67009213599584516</v>
+        <v>0.66015162492825919</v>
       </c>
       <c r="C11">
-        <v>1.1816989752240151e-06</v>
+        <v>4.1298777112637637e-06</v>
       </c>
       <c r="D11">
-        <v>-1.0022543965964785e-08</v>
+        <v>-4.1606169583271956e-08</v>
       </c>
       <c r="E11">
-        <v>1.215049930160794e-05</v>
+        <v>2.5377330503558154e-05</v>
       </c>
       <c r="F11">
-        <v>9.1746420983213502e-06</v>
+        <v>-2.0851529617931658e-06</v>
       </c>
       <c r="G11">
-        <v>-3.2460690023255557e-07</v>
+        <v>-6.9025219356646058e-07</v>
       </c>
       <c r="H11">
-        <v>1.5218451887476079e-07</v>
+        <v>2.6043621860971037e-07</v>
       </c>
       <c r="I11">
-        <v>-1.5940040212476883e-05</v>
+        <v>-1.3360498493370884e-05</v>
       </c>
       <c r="J11">
-        <v>-3.9306622806414596e-06</v>
+        <v>-6.7261859159997749e-06</v>
       </c>
       <c r="K11">
-        <v>0.0096602715031731384</v>
+        <v>0.0075787279332324032</v>
       </c>
       <c r="L11">
-        <v>0.010015551445784169</v>
+        <v>0.0078798369488180947</v>
       </c>
       <c r="M11">
-        <v>0.0096648652894109899</v>
+        <v>0.0075829129875069155</v>
       </c>
       <c r="N11">
-        <v>0.0096661887986971701</v>
+        <v>0.0075853494344380792</v>
       </c>
       <c r="O11">
-        <v>4.6521039143289761e-06</v>
+        <v>1.0946253038199972e-05</v>
       </c>
       <c r="P11">
-        <v>-1.2458457135501609e-05</v>
+        <v>1.6896487130998159e-07</v>
       </c>
       <c r="Q11">
-        <v>-4.7456789289987367e-05</v>
+        <v>-3.0271987084079494e-05</v>
       </c>
       <c r="R11">
-        <v>-2.7010474321541585e-05</v>
+        <v>-1.4824240716207742e-05</v>
       </c>
       <c r="S11">
-        <v>-1.2146908825660423e-05</v>
+        <v>-6.0374694249166864e-06</v>
       </c>
       <c r="T11">
-        <v>-9.5116862632838159e-06</v>
+        <v>3.4151414074549665e-07</v>
       </c>
       <c r="U11">
-        <v>7.6262764598954057e-06</v>
+        <v>1.707739533103869e-06</v>
       </c>
       <c r="V11">
-        <v>-5.0282638781215512e-06</v>
+        <v>-8.1754913156325658e-06</v>
       </c>
       <c r="W11">
-        <v>-0.0096750486755672726</v>
+        <v>-0.0076619075026903684</v>
       </c>
     </row>
     <row r="12">
@@ -6373,70 +6373,70 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0.88458666854901336</v>
+        <v>0.87334503596806046</v>
       </c>
       <c r="C12">
-        <v>1.557291920292537e-06</v>
+        <v>5.4177598559751168e-06</v>
       </c>
       <c r="D12">
-        <v>7.6130078202181579e-09</v>
+        <v>-3.8288062129341314e-08</v>
       </c>
       <c r="E12">
-        <v>2.2499087497850764e-06</v>
+        <v>1.701013276155872e-05</v>
       </c>
       <c r="F12">
-        <v>-8.6869900484101091e-06</v>
+        <v>-1.7230834154677863e-05</v>
       </c>
       <c r="G12">
-        <v>2.2103156800620932e-07</v>
+        <v>-2.2880282408566839e-07</v>
       </c>
       <c r="H12">
-        <v>1.1452365498298725e-06</v>
+        <v>1.1239820612721362e-06</v>
       </c>
       <c r="I12">
-        <v>-2.4447394452737402e-05</v>
+        <v>-1.9186665910185408e-05</v>
       </c>
       <c r="J12">
-        <v>9.9750203729218675e-06</v>
+        <v>-1.3352235170336306e-05</v>
       </c>
       <c r="K12">
-        <v>0.0096572662486520584</v>
+        <v>0.0075769016576795753</v>
       </c>
       <c r="L12">
-        <v>0.0096648652894109899</v>
+        <v>0.0075829129875069155</v>
       </c>
       <c r="M12">
-        <v>0.0097790175692240404</v>
+        <v>0.0076829782088214289</v>
       </c>
       <c r="N12">
-        <v>0.0097035065413749282</v>
+        <v>0.0076175042916605089</v>
       </c>
       <c r="O12">
-        <v>2.7025835524371946e-06</v>
+        <v>9.1514009541485662e-06</v>
       </c>
       <c r="P12">
-        <v>-2.2576966191663289e-05</v>
+        <v>-5.4263467083948212e-06</v>
       </c>
       <c r="Q12">
-        <v>-5.3278956442177662e-05</v>
+        <v>-3.6030654339676646e-05</v>
       </c>
       <c r="R12">
-        <v>-2.6258303735504035e-05</v>
+        <v>-1.4222841955696582e-05</v>
       </c>
       <c r="S12">
-        <v>-1.4568485737438353e-05</v>
+        <v>-9.5051060439650973e-06</v>
       </c>
       <c r="T12">
-        <v>7.2569544600576911e-06</v>
+        <v>1.8040122792191925e-05</v>
       </c>
       <c r="U12">
-        <v>4.454682823626064e-06</v>
+        <v>-2.545610202908781e-06</v>
       </c>
       <c r="V12">
-        <v>-1.671239411723229e-06</v>
+        <v>-6.110561385893571e-06</v>
       </c>
       <c r="W12">
-        <v>-0.0097596644490405057</v>
+        <v>-0.007751660929322811</v>
       </c>
     </row>
     <row r="13">
@@ -6444,70 +6444,70 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>0.91339255205179559</v>
+        <v>0.93043534444253428</v>
       </c>
       <c r="C13">
-        <v>1.2332342093267566e-05</v>
+        <v>1.4982633842108601e-05</v>
       </c>
       <c r="D13">
-        <v>-7.4160989483513046e-08</v>
+        <v>-1.1131903512515188e-07</v>
       </c>
       <c r="E13">
-        <v>2.2218839697348027e-05</v>
+        <v>3.4848488909314376e-05</v>
       </c>
       <c r="F13">
-        <v>5.2562023301968803e-05</v>
+        <v>3.2197462247023512e-05</v>
       </c>
       <c r="G13">
-        <v>-4.8991675277028192e-08</v>
+        <v>-4.4683293823429392e-07</v>
       </c>
       <c r="H13">
-        <v>2.686496278392668e-07</v>
+        <v>4.457761217491508e-07</v>
       </c>
       <c r="I13">
-        <v>-2.4758126170353e-05</v>
+        <v>-2.0610247432579201e-05</v>
       </c>
       <c r="J13">
-        <v>-2.4961417020613514e-05</v>
+        <v>-1.2568228752221557e-05</v>
       </c>
       <c r="K13">
-        <v>0.0096533106970403265</v>
+        <v>0.0075749332213773295</v>
       </c>
       <c r="L13">
-        <v>0.0096661887986971701</v>
+        <v>0.0075853494344380792</v>
       </c>
       <c r="M13">
-        <v>0.0097035065413749282</v>
+        <v>0.0076175042916605089</v>
       </c>
       <c r="N13">
-        <v>0.010065499892358875</v>
+        <v>0.0079487363934019929</v>
       </c>
       <c r="O13">
-        <v>-9.7268400920737951e-06</v>
+        <v>-2.7626626719943299e-07</v>
       </c>
       <c r="P13">
-        <v>-3.821643540764674e-05</v>
+        <v>-1.6484606955236573e-05</v>
       </c>
       <c r="Q13">
-        <v>-6.0203768992631846e-05</v>
+        <v>-4.1697871549088424e-05</v>
       </c>
       <c r="R13">
-        <v>-5.2752050957380865e-05</v>
+        <v>-3.5121561303235003e-05</v>
       </c>
       <c r="S13">
-        <v>-3.8344098069851079e-05</v>
+        <v>-2.8907810716398229e-05</v>
       </c>
       <c r="T13">
-        <v>-1.8210359731343668e-05</v>
+        <v>-2.1462327603964768e-06</v>
       </c>
       <c r="U13">
-        <v>-2.9422288518517345e-06</v>
+        <v>-1.0478736349004337e-05</v>
       </c>
       <c r="V13">
-        <v>-8.6381259195390145e-06</v>
+        <v>-1.2285942338857328e-05</v>
       </c>
       <c r="W13">
-        <v>-0.010083273930940844</v>
+        <v>-0.0080401891750455576</v>
       </c>
     </row>
     <row r="14">
@@ -6515,70 +6515,70 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>0.073773792161670404</v>
+        <v>0.069190686957279243</v>
       </c>
       <c r="C14">
-        <v>4.3872140298603005e-07</v>
+        <v>1.4492586215457886e-06</v>
       </c>
       <c r="D14">
-        <v>2.0648083408687755e-09</v>
+        <v>-1.0633933954931216e-08</v>
       </c>
       <c r="E14">
-        <v>4.8300767906043883e-05</v>
+        <v>4.5527246550326887e-05</v>
       </c>
       <c r="F14">
-        <v>5.6910683863529433e-05</v>
+        <v>5.2569146040668454e-05</v>
       </c>
       <c r="G14">
-        <v>-9.5555633216184534e-07</v>
+        <v>-8.9551885398833311e-07</v>
       </c>
       <c r="H14">
-        <v>-8.6391057769693324e-07</v>
+        <v>-8.1171599895270211e-07</v>
       </c>
       <c r="I14">
-        <v>-1.8460883139649595e-06</v>
+        <v>3.5781469862081961e-06</v>
       </c>
       <c r="J14">
-        <v>-2.6849662710422302e-05</v>
+        <v>-9.8776580981759437e-06</v>
       </c>
       <c r="K14">
-        <v>4.7770986842013629e-06</v>
+        <v>1.2066759158126881e-05</v>
       </c>
       <c r="L14">
-        <v>4.6521039143289761e-06</v>
+        <v>1.0946253038199972e-05</v>
       </c>
       <c r="M14">
-        <v>2.7025835524371946e-06</v>
+        <v>9.1514009541485662e-06</v>
       </c>
       <c r="N14">
-        <v>-9.7268400920737951e-06</v>
+        <v>-2.7626626719943299e-07</v>
       </c>
       <c r="O14">
-        <v>0.00085188450627591823</v>
+        <v>0.00077000748332730175</v>
       </c>
       <c r="P14">
-        <v>0.0004591764686186453</v>
+        <v>0.00041717281603157553</v>
       </c>
       <c r="Q14">
-        <v>0.00045504423856345316</v>
+        <v>0.00041384963517607525</v>
       </c>
       <c r="R14">
-        <v>0.00045779644369693733</v>
+        <v>0.00041626155201825019</v>
       </c>
       <c r="S14">
-        <v>0.00045558358824117134</v>
+        <v>0.00041442414588120457</v>
       </c>
       <c r="T14">
-        <v>0.00045650447631648109</v>
+        <v>0.00041478874938270745</v>
       </c>
       <c r="U14">
-        <v>5.61043068727634e-06</v>
+        <v>6.073500478057615e-06</v>
       </c>
       <c r="V14">
-        <v>4.1519655496266016e-06</v>
+        <v>4.6126928665743164e-06</v>
       </c>
       <c r="W14">
-        <v>-0.00049034256180230287</v>
+        <v>-0.00047283649417752971</v>
       </c>
     </row>
     <row r="15">
@@ -6586,70 +6586,70 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>0.016201815744773387</v>
+        <v>0.024647006097917118</v>
       </c>
       <c r="C15">
-        <v>1.0962357744224739e-06</v>
+        <v>2.1257839484117095e-06</v>
       </c>
       <c r="D15">
-        <v>-8.5531451048050645e-09</v>
+        <v>-2.0288623176399256e-08</v>
       </c>
       <c r="E15">
-        <v>2.2513374964042759e-05</v>
+        <v>2.2485546038093937e-05</v>
       </c>
       <c r="F15">
-        <v>4.0067254405445394e-05</v>
+        <v>3.2682154206748211e-05</v>
       </c>
       <c r="G15">
-        <v>-2.227092381147214e-07</v>
+        <v>-2.3032673164631348e-07</v>
       </c>
       <c r="H15">
-        <v>-1.2491177931334186e-07</v>
+        <v>-6.729975605870186e-08</v>
       </c>
       <c r="I15">
-        <v>-9.0336353472270046e-06</v>
+        <v>-5.886360260662342e-06</v>
       </c>
       <c r="J15">
-        <v>-2.1991327025974331e-05</v>
+        <v>-5.2227460761625133e-06</v>
       </c>
       <c r="K15">
-        <v>-5.944174974961879e-07</v>
+        <v>9.214418427847123e-06</v>
       </c>
       <c r="L15">
-        <v>-1.2458457135501609e-05</v>
+        <v>1.6896487130998159e-07</v>
       </c>
       <c r="M15">
-        <v>-2.2576966191663289e-05</v>
+        <v>-5.4263467083948212e-06</v>
       </c>
       <c r="N15">
-        <v>-3.821643540764674e-05</v>
+        <v>-1.6484606955236573e-05</v>
       </c>
       <c r="O15">
-        <v>0.0004591764686186453</v>
+        <v>0.00041717281603157553</v>
       </c>
       <c r="P15">
-        <v>0.0010481331800292898</v>
+        <v>0.00093504658143020393</v>
       </c>
       <c r="Q15">
-        <v>0.00045412513950462204</v>
+        <v>0.00041282945650045281</v>
       </c>
       <c r="R15">
-        <v>0.00045869565606238992</v>
+        <v>0.00041672751216224099</v>
       </c>
       <c r="S15">
-        <v>0.00045577226547236936</v>
+        <v>0.0004142531003056002</v>
       </c>
       <c r="T15">
-        <v>0.00045648725447521732</v>
+        <v>0.00041471591399255483</v>
       </c>
       <c r="U15">
-        <v>-3.3915979216699326e-06</v>
+        <v>-2.1115892635215897e-06</v>
       </c>
       <c r="V15">
-        <v>-1.9559921153166349e-05</v>
+        <v>-1.2822743613043456e-05</v>
       </c>
       <c r="W15">
-        <v>-0.00047616259705704603</v>
+        <v>-0.00047078789341754629</v>
       </c>
     </row>
     <row r="16">
@@ -6657,70 +6657,70 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>-0.064679135437807039</v>
+        <v>-0.069678774954667982</v>
       </c>
       <c r="C16">
-        <v>1.0509072585291445e-06</v>
+        <v>1.8089963045000926e-06</v>
       </c>
       <c r="D16">
-        <v>-5.4983769330868275e-09</v>
+        <v>-1.5471502880211322e-08</v>
       </c>
       <c r="E16">
-        <v>2.9649431080900753e-05</v>
+        <v>3.0269242733900469e-05</v>
       </c>
       <c r="F16">
-        <v>-1.459545194759504e-05</v>
+        <v>-1.0065880009931665e-05</v>
       </c>
       <c r="G16">
-        <v>-7.8633380437838424e-07</v>
+        <v>-7.6771661917475667e-07</v>
       </c>
       <c r="H16">
-        <v>-3.3098441281693578e-07</v>
+        <v>-3.5189121771052658e-07</v>
       </c>
       <c r="I16">
-        <v>-4.403391235684271e-06</v>
+        <v>1.5912262714970239e-07</v>
       </c>
       <c r="J16">
-        <v>-2.0824028727684947e-05</v>
+        <v>-7.756584569302615e-06</v>
       </c>
       <c r="K16">
-        <v>-2.9312869855195421e-05</v>
+        <v>-1.7769371088324239e-05</v>
       </c>
       <c r="L16">
-        <v>-4.7456789289987367e-05</v>
+        <v>-3.0271987084079494e-05</v>
       </c>
       <c r="M16">
-        <v>-5.3278956442177662e-05</v>
+        <v>-3.6030654339676646e-05</v>
       </c>
       <c r="N16">
-        <v>-6.0203768992631846e-05</v>
+        <v>-4.1697871549088424e-05</v>
       </c>
       <c r="O16">
-        <v>0.00045504423856345316</v>
+        <v>0.00041384963517607525</v>
       </c>
       <c r="P16">
-        <v>0.00045412513950462204</v>
+        <v>0.00041282945650045281</v>
       </c>
       <c r="Q16">
-        <v>0.00079329124471609201</v>
+        <v>0.00071787682315140782</v>
       </c>
       <c r="R16">
-        <v>0.00045701417411151259</v>
+        <v>0.00041535799384057309</v>
       </c>
       <c r="S16">
-        <v>0.00046013846310186406</v>
+        <v>0.00041838650803731396</v>
       </c>
       <c r="T16">
-        <v>0.00045715126013975077</v>
+        <v>0.00041511656591378967</v>
       </c>
       <c r="U16">
-        <v>-7.1726262594326638e-06</v>
+        <v>-4.9947029892120068e-06</v>
       </c>
       <c r="V16">
-        <v>-6.7636576269655553e-06</v>
+        <v>-5.5193359418054806e-06</v>
       </c>
       <c r="W16">
-        <v>-0.00042236919031441638</v>
+        <v>-0.00041325986896345254</v>
       </c>
     </row>
     <row r="17">
@@ -6728,70 +6728,70 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>0.027287359773946529</v>
+        <v>0.023169664787710036</v>
       </c>
       <c r="C17">
-        <v>1.4213483259107471e-06</v>
+        <v>2.9204160683974874e-06</v>
       </c>
       <c r="D17">
-        <v>-1.0102287857832988e-08</v>
+        <v>-2.7270549691602506e-08</v>
       </c>
       <c r="E17">
-        <v>3.101580451640605e-05</v>
+        <v>3.4038198616015766e-05</v>
       </c>
       <c r="F17">
-        <v>2.272125956267224e-06</v>
+        <v>9.8866562788718838e-06</v>
       </c>
       <c r="G17">
-        <v>-7.4382698762537833e-07</v>
+        <v>-7.7994779567172666e-07</v>
       </c>
       <c r="H17">
-        <v>5.5540469325208818e-09</v>
+        <v>-1.4947989252864334e-07</v>
       </c>
       <c r="I17">
-        <v>-9.6204798947946073e-06</v>
+        <v>-3.7783358534563469e-06</v>
       </c>
       <c r="J17">
-        <v>-5.6702693440790487e-05</v>
+        <v>-9.1967218759688907e-06</v>
       </c>
       <c r="K17">
-        <v>-1.7473094770705755e-05</v>
+        <v>-8.4978045359928363e-06</v>
       </c>
       <c r="L17">
-        <v>-2.7010474321541585e-05</v>
+        <v>-1.4824240716207742e-05</v>
       </c>
       <c r="M17">
-        <v>-2.6258303735504035e-05</v>
+        <v>-1.4222841955696582e-05</v>
       </c>
       <c r="N17">
-        <v>-5.2752050957380865e-05</v>
+        <v>-3.5121561303235003e-05</v>
       </c>
       <c r="O17">
-        <v>0.00045779644369693733</v>
+        <v>0.00041626155201825019</v>
       </c>
       <c r="P17">
-        <v>0.00045869565606238992</v>
+        <v>0.00041672751216224099</v>
       </c>
       <c r="Q17">
-        <v>0.00045701417411151259</v>
+        <v>0.00041535799384057309</v>
       </c>
       <c r="R17">
-        <v>0.00071759616113220852</v>
+        <v>0.00063389242032125767</v>
       </c>
       <c r="S17">
-        <v>0.00045890183158109972</v>
+        <v>0.0004170031744904781</v>
       </c>
       <c r="T17">
-        <v>0.00045835114642473011</v>
+        <v>0.00041612161306906615</v>
       </c>
       <c r="U17">
-        <v>1.1051330255817302e-05</v>
+        <v>1.464070092988265e-05</v>
       </c>
       <c r="V17">
-        <v>6.8479165008000864e-06</v>
+        <v>1.0174941497393464e-05</v>
       </c>
       <c r="W17">
-        <v>-0.00046510661863207944</v>
+        <v>-0.00046798244563567363</v>
       </c>
     </row>
     <row r="18">
@@ -6799,70 +6799,70 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>-0.11854054557536563</v>
+        <v>-0.12921933829819451</v>
       </c>
       <c r="C18">
-        <v>2.5175172823005021e-07</v>
+        <v>1.8904551487158973e-06</v>
       </c>
       <c r="D18">
-        <v>2.3320067725331959e-09</v>
+        <v>-1.743519163661006e-08</v>
       </c>
       <c r="E18">
-        <v>-5.6933961550265461e-06</v>
+        <v>3.9166500075902682e-06</v>
       </c>
       <c r="F18">
-        <v>-6.2825308508051593e-05</v>
+        <v>-4.8109150269245218e-05</v>
       </c>
       <c r="G18">
-        <v>-4.1411358330712673e-08</v>
+        <v>-2.1150540845897405e-07</v>
       </c>
       <c r="H18">
-        <v>7.8909170608581384e-07</v>
+        <v>5.2467382060500317e-07</v>
       </c>
       <c r="I18">
-        <v>-1.9495668683271825e-05</v>
+        <v>-8.2011121265418905e-06</v>
       </c>
       <c r="J18">
-        <v>-5.110144748122501e-06</v>
+        <v>-1.4450608672886047e-05</v>
       </c>
       <c r="K18">
-        <v>1.7048849545395391e-06</v>
+        <v>3.3824494668758707e-06</v>
       </c>
       <c r="L18">
-        <v>-1.2146908825660423e-05</v>
+        <v>-6.0374694249166864e-06</v>
       </c>
       <c r="M18">
-        <v>-1.4568485737438353e-05</v>
+        <v>-9.5051060439650973e-06</v>
       </c>
       <c r="N18">
-        <v>-3.8344098069851079e-05</v>
+        <v>-2.8907810716398229e-05</v>
       </c>
       <c r="O18">
-        <v>0.00045558358824117134</v>
+        <v>0.00041442414588120457</v>
       </c>
       <c r="P18">
-        <v>0.00045577226547236936</v>
+        <v>0.0004142531003056002</v>
       </c>
       <c r="Q18">
-        <v>0.00046013846310186406</v>
+        <v>0.00041838650803731396</v>
       </c>
       <c r="R18">
-        <v>0.00045890183158109972</v>
+        <v>0.0004170031744904781</v>
       </c>
       <c r="S18">
-        <v>0.00076814794722531864</v>
+        <v>0.00068784708859319767</v>
       </c>
       <c r="T18">
-        <v>0.00045887739900240144</v>
+        <v>0.00041636070603264392</v>
       </c>
       <c r="U18">
-        <v>-3.7711783392627753e-06</v>
+        <v>1.1402193500351788e-07</v>
       </c>
       <c r="V18">
-        <v>-4.4244624726818801e-06</v>
+        <v>-1.6509465377052728e-06</v>
       </c>
       <c r="W18">
-        <v>-0.00043108848861972892</v>
+        <v>-0.00043093230257717726</v>
       </c>
     </row>
     <row r="19">
@@ -6870,70 +6870,70 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>-0.12849091305817534</v>
+        <v>-0.14926305479798871</v>
       </c>
       <c r="C19">
-        <v>4.6327688598461331e-07</v>
+        <v>-6.6572586339490597e-07</v>
       </c>
       <c r="D19">
-        <v>-3.1533175762774457e-09</v>
+        <v>9.075061433684419e-09</v>
       </c>
       <c r="E19">
-        <v>-1.5312375890319195e-05</v>
+        <v>-1.797114129143143e-05</v>
       </c>
       <c r="F19">
-        <v>-3.4896278334126017e-05</v>
+        <v>-2.8828232449395916e-05</v>
       </c>
       <c r="G19">
-        <v>2.3241110484949679e-07</v>
+        <v>3.0132978253550991e-07</v>
       </c>
       <c r="H19">
-        <v>6.0078527922802455e-07</v>
+        <v>5.0367721789776936e-07</v>
       </c>
       <c r="I19">
-        <v>4.6038010503024925e-06</v>
+        <v>5.2804444345689541e-06</v>
       </c>
       <c r="J19">
-        <v>5.662081572278844e-05</v>
+        <v>3.6155749779488691e-06</v>
       </c>
       <c r="K19">
-        <v>1.1732014867307723e-06</v>
+        <v>1.481619248703994e-05</v>
       </c>
       <c r="L19">
-        <v>-9.5116862632838159e-06</v>
+        <v>3.4151414074549665e-07</v>
       </c>
       <c r="M19">
-        <v>7.2569544600576911e-06</v>
+        <v>1.8040122792191925e-05</v>
       </c>
       <c r="N19">
-        <v>-1.8210359731343668e-05</v>
+        <v>-2.1462327603964768e-06</v>
       </c>
       <c r="O19">
-        <v>0.00045650447631648109</v>
+        <v>0.00041478874938270745</v>
       </c>
       <c r="P19">
-        <v>0.00045648725447521732</v>
+        <v>0.00041471591399255483</v>
       </c>
       <c r="Q19">
-        <v>0.00045715126013975077</v>
+        <v>0.00041511656591378967</v>
       </c>
       <c r="R19">
-        <v>0.00045835114642473011</v>
+        <v>0.00041612161306906615</v>
       </c>
       <c r="S19">
-        <v>0.00045887739900240144</v>
+        <v>0.00041636070603264392</v>
       </c>
       <c r="T19">
-        <v>0.0020285640819254144</v>
+        <v>0.0017919283938224509</v>
       </c>
       <c r="U19">
-        <v>1.0325058584687925e-05</v>
+        <v>1.0769361950415997e-05</v>
       </c>
       <c r="V19">
-        <v>1.285403673742524e-06</v>
+        <v>3.6313079182258825e-06</v>
       </c>
       <c r="W19">
-        <v>-0.00047100216080141189</v>
+        <v>-0.00041903953640824672</v>
       </c>
     </row>
     <row r="20">
@@ -6941,70 +6941,70 @@
         <v>42</v>
       </c>
       <c r="B20">
-        <v>-0.042526837026015632</v>
+        <v>-0.068637034543818004</v>
       </c>
       <c r="C20">
-        <v>1.1102097858498659e-06</v>
+        <v>1.1732112743566433e-06</v>
       </c>
       <c r="D20">
-        <v>-1.3265344362586473e-08</v>
+        <v>-1.245225106256128e-08</v>
       </c>
       <c r="E20">
-        <v>1.3754055509507192e-05</v>
+        <v>1.0660073195828203e-05</v>
       </c>
       <c r="F20">
-        <v>3.8510969066483677e-05</v>
+        <v>3.3227023837756691e-05</v>
       </c>
       <c r="G20">
-        <v>-2.8167438997013632e-07</v>
+        <v>-2.528205994179068e-07</v>
       </c>
       <c r="H20">
-        <v>-6.6228993684569063e-07</v>
+        <v>-6.4949585722650761e-07</v>
       </c>
       <c r="I20">
-        <v>-2.9758441612844177e-07</v>
+        <v>2.0687404830747441e-07</v>
       </c>
       <c r="J20">
-        <v>2.3344505612602102e-05</v>
+        <v>-5.6013434902318745e-06</v>
       </c>
       <c r="K20">
-        <v>4.0270479406493028e-06</v>
+        <v>1.3310316153190914e-07</v>
       </c>
       <c r="L20">
-        <v>7.6262764598954057e-06</v>
+        <v>1.707739533103869e-06</v>
       </c>
       <c r="M20">
-        <v>4.454682823626064e-06</v>
+        <v>-2.545610202908781e-06</v>
       </c>
       <c r="N20">
-        <v>-2.9422288518517345e-06</v>
+        <v>-1.0478736349004337e-05</v>
       </c>
       <c r="O20">
-        <v>5.61043068727634e-06</v>
+        <v>6.073500478057615e-06</v>
       </c>
       <c r="P20">
-        <v>-3.3915979216699326e-06</v>
+        <v>-2.1115892635215897e-06</v>
       </c>
       <c r="Q20">
-        <v>-7.1726262594326638e-06</v>
+        <v>-4.9947029892120068e-06</v>
       </c>
       <c r="R20">
-        <v>1.1051330255817302e-05</v>
+        <v>1.464070092988265e-05</v>
       </c>
       <c r="S20">
-        <v>-3.7711783392627753e-06</v>
+        <v>1.1402193500351788e-07</v>
       </c>
       <c r="T20">
-        <v>1.0325058584687925e-05</v>
+        <v>1.0769361950415997e-05</v>
       </c>
       <c r="U20">
-        <v>0.00089509256497684331</v>
+        <v>0.00089079758868779678</v>
       </c>
       <c r="V20">
-        <v>6.8306639607071523e-05</v>
+        <v>5.8560093931156922e-05</v>
       </c>
       <c r="W20">
-        <v>-9.6150934237597866e-05</v>
+        <v>-8.2864152426535042e-05</v>
       </c>
     </row>
     <row r="21">
@@ -7012,70 +7012,70 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>0.090132539167039894</v>
+        <v>0.10454114967837186</v>
       </c>
       <c r="C21">
-        <v>-3.7875560303615868e-06</v>
+        <v>-2.8424526832009631e-06</v>
       </c>
       <c r="D21">
-        <v>3.2228859357369165e-08</v>
+        <v>2.4818422905359576e-08</v>
       </c>
       <c r="E21">
-        <v>2.1926694904936809e-05</v>
+        <v>1.7911249677234527e-05</v>
       </c>
       <c r="F21">
-        <v>2.0384502718689275e-05</v>
+        <v>1.9449267148431614e-05</v>
       </c>
       <c r="G21">
-        <v>-3.2808101323384381e-07</v>
+        <v>-2.9313864847253634e-07</v>
       </c>
       <c r="H21">
-        <v>-1.3548594262643645e-07</v>
+        <v>-2.397107008800051e-07</v>
       </c>
       <c r="I21">
-        <v>1.3435139598592764e-05</v>
+        <v>1.2270848759757568e-05</v>
       </c>
       <c r="J21">
-        <v>-4.0616795497297109e-05</v>
+        <v>-4.1956606850279706e-06</v>
       </c>
       <c r="K21">
-        <v>-6.2258963814059713e-06</v>
+        <v>-7.2460163601834341e-06</v>
       </c>
       <c r="L21">
-        <v>-5.0282638781215512e-06</v>
+        <v>-8.1754913156325658e-06</v>
       </c>
       <c r="M21">
-        <v>-1.671239411723229e-06</v>
+        <v>-6.110561385893571e-06</v>
       </c>
       <c r="N21">
-        <v>-8.6381259195390145e-06</v>
+        <v>-1.2285942338857328e-05</v>
       </c>
       <c r="O21">
-        <v>4.1519655496266016e-06</v>
+        <v>4.6126928665743164e-06</v>
       </c>
       <c r="P21">
-        <v>-1.9559921153166349e-05</v>
+        <v>-1.2822743613043456e-05</v>
       </c>
       <c r="Q21">
-        <v>-6.7636576269655553e-06</v>
+        <v>-5.5193359418054806e-06</v>
       </c>
       <c r="R21">
-        <v>6.8479165008000864e-06</v>
+        <v>1.0174941497393464e-05</v>
       </c>
       <c r="S21">
-        <v>-4.4244624726818801e-06</v>
+        <v>-1.6509465377052728e-06</v>
       </c>
       <c r="T21">
-        <v>1.285403673742524e-06</v>
+        <v>3.6313079182258825e-06</v>
       </c>
       <c r="U21">
-        <v>6.8306639607071523e-05</v>
+        <v>5.8560093931156922e-05</v>
       </c>
       <c r="V21">
-        <v>0.0010714689164394314</v>
+        <v>0.0011226860874147904</v>
       </c>
       <c r="W21">
-        <v>2.2770166788042257e-05</v>
+        <v>1.2718508345571935e-05</v>
       </c>
     </row>
     <row r="22">
@@ -7083,70 +7083,70 @@
         <v>44</v>
       </c>
       <c r="B22">
-        <v>-3.0546313783400461</v>
+        <v>-2.9914302801842108</v>
       </c>
       <c r="C22">
-        <v>-0.0005376225640889629</v>
+        <v>-0.00051560859631771924</v>
       </c>
       <c r="D22">
-        <v>5.2041780256028574e-06</v>
+        <v>5.1027282669180229e-06</v>
       </c>
       <c r="E22">
-        <v>-0.0034951515357835084</v>
+        <v>-0.0031596309752217316</v>
       </c>
       <c r="F22">
-        <v>-0.0029229828724894602</v>
+        <v>-0.002716288639685099</v>
       </c>
       <c r="G22">
-        <v>7.1608218535988509e-05</v>
+        <v>6.4544112324254916e-05</v>
       </c>
       <c r="H22">
-        <v>5.7525089240895356e-05</v>
+        <v>5.3759915239246632e-05</v>
       </c>
       <c r="I22">
-        <v>0.00056486995841063684</v>
+        <v>0.00017673063316534754</v>
       </c>
       <c r="J22">
-        <v>-0.0027516766328533888</v>
+        <v>0.00061800271623847585</v>
       </c>
       <c r="K22">
-        <v>-0.009656403581416749</v>
+        <v>-0.0076458550531630643</v>
       </c>
       <c r="L22">
-        <v>-0.0096750486755672726</v>
+        <v>-0.0076619075026903684</v>
       </c>
       <c r="M22">
-        <v>-0.0097596644490405057</v>
+        <v>-0.007751660929322811</v>
       </c>
       <c r="N22">
-        <v>-0.010083273930940844</v>
+        <v>-0.0080401891750455576</v>
       </c>
       <c r="O22">
-        <v>-0.00049034256180230287</v>
+        <v>-0.00047283649417752971</v>
       </c>
       <c r="P22">
-        <v>-0.00047616259705704603</v>
+        <v>-0.00047078789341754629</v>
       </c>
       <c r="Q22">
-        <v>-0.00042236919031441638</v>
+        <v>-0.00041325986896345254</v>
       </c>
       <c r="R22">
-        <v>-0.00046510661863207944</v>
+        <v>-0.00046798244563567363</v>
       </c>
       <c r="S22">
-        <v>-0.00043108848861972892</v>
+        <v>-0.00043093230257717726</v>
       </c>
       <c r="T22">
-        <v>-0.00047100216080141189</v>
+        <v>-0.00041903953640824672</v>
       </c>
       <c r="U22">
-        <v>-9.6150934237597866e-05</v>
+        <v>-8.2864152426535042e-05</v>
       </c>
       <c r="V22">
-        <v>2.2770166788042257e-05</v>
+        <v>1.2718508345571935e-05</v>
       </c>
       <c r="W22">
-        <v>0.022916944246539075</v>
+        <v>0.020134109862578915</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_employmentSelection.xlsx
+++ b/input/ES/reg_employmentSelection.xlsx
@@ -384,76 +384,76 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>-1.5639821051047229</v>
+        <v>-1.577482365608581</v>
       </c>
       <c r="C2">
-        <v>0.00078416851707491719</v>
+        <v>0.00078757303448114555</v>
       </c>
       <c r="D2">
-        <v>5.6510429966023098e-05</v>
+        <v>5.699368159562538e-05</v>
       </c>
       <c r="E2">
-        <v>3.7635611863224171e-05</v>
+        <v>3.7793676776640814e-05</v>
       </c>
       <c r="F2">
-        <v>-3.6283733161908621e-07</v>
+        <v>-3.6418953456302739e-07</v>
       </c>
       <c r="G2">
-        <v>-7.039577270400799e-05</v>
+        <v>-6.914230034986348e-05</v>
       </c>
       <c r="H2">
-        <v>6.5030443682439386e-05</v>
+        <v>6.7281170523516729e-05</v>
       </c>
       <c r="I2">
-        <v>1.2315124902761905e-06</v>
+        <v>1.2048132821244012e-06</v>
       </c>
       <c r="J2">
-        <v>-1.3182613244439658e-06</v>
+        <v>-1.3648060641901778e-06</v>
       </c>
       <c r="K2">
-        <v>2.1378629626480057e-05</v>
+        <v>2.1439497551592387e-05</v>
       </c>
       <c r="L2">
-        <v>1.3131742014200829e-06</v>
+        <v>1.3458024764383759e-06</v>
       </c>
       <c r="M2">
-        <v>7.0215748909776632e-07</v>
+        <v>5.9028078636401459e-07</v>
       </c>
       <c r="N2">
-        <v>5.3289683635173845e-06</v>
+        <v>5.1051509280343249e-06</v>
       </c>
       <c r="O2">
-        <v>4.9740709114392471e-06</v>
+        <v>4.8607902423147592e-06</v>
       </c>
       <c r="P2">
-        <v>1.9876746229329357e-06</v>
+        <v>1.9284411210990118e-06</v>
       </c>
       <c r="Q2">
-        <v>2.8493485357173865e-06</v>
+        <v>2.8625945207049448e-06</v>
       </c>
       <c r="R2">
-        <v>3.7886423362497602e-06</v>
+        <v>3.759834000307216e-06</v>
       </c>
       <c r="S2">
-        <v>6.4079993556668044e-07</v>
+        <v>5.7401949537125118e-07</v>
       </c>
       <c r="T2">
-        <v>5.7738368143280504e-06</v>
+        <v>5.736884804500962e-06</v>
       </c>
       <c r="U2">
-        <v>6.4399516836442697e-06</v>
+        <v>6.4308524325009454e-06</v>
       </c>
       <c r="V2">
-        <v>-4.1962939247760638e-07</v>
+        <v>-4.2449270722484388e-07</v>
       </c>
       <c r="W2">
-        <v>9.9562976616470948e-06</v>
+        <v>9.9154514910156613e-06</v>
       </c>
       <c r="X2">
-        <v>4.3000236693587114e-06</v>
+        <v>4.4080477075468059e-06</v>
       </c>
       <c r="Y2">
-        <v>-0.000988449099072807</v>
+        <v>-0.00099309852096993948</v>
       </c>
     </row>
     <row r="3">
@@ -461,76 +461,76 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>-2.211386952091174</v>
+        <v>-2.2154712600795841</v>
       </c>
       <c r="C3">
-        <v>5.6510429966023098e-05</v>
+        <v>5.699368159562538e-05</v>
       </c>
       <c r="D3">
-        <v>0.00012475674006656997</v>
+        <v>0.00012483953510101289</v>
       </c>
       <c r="E3">
-        <v>3.017744319980551e-06</v>
+        <v>3.0121515772836897e-06</v>
       </c>
       <c r="F3">
-        <v>-3.1029971572066036e-08</v>
+        <v>-3.07526338809503e-08</v>
       </c>
       <c r="G3">
-        <v>5.1666718248454747e-06</v>
+        <v>5.8769554902043026e-06</v>
       </c>
       <c r="H3">
-        <v>-2.2170649792781237e-06</v>
+        <v>-1.8311166838060058e-06</v>
       </c>
       <c r="I3">
-        <v>-3.4820038044586338e-07</v>
+        <v>-3.6500340493763753e-07</v>
       </c>
       <c r="J3">
-        <v>-3.9934781626548072e-07</v>
+        <v>-4.0967327252641896e-07</v>
       </c>
       <c r="K3">
-        <v>-3.5473730971942918e-06</v>
+        <v>-3.580590229525579e-06</v>
       </c>
       <c r="L3">
-        <v>-4.5310110640387007e-06</v>
+        <v>-4.1318779779253134e-06</v>
       </c>
       <c r="M3">
-        <v>2.9258082990574438e-06</v>
+        <v>2.8413217147769655e-06</v>
       </c>
       <c r="N3">
-        <v>8.3163865729851295e-06</v>
+        <v>8.0920555668338997e-06</v>
       </c>
       <c r="O3">
-        <v>1.06937542840598e-05</v>
+        <v>1.062733572271395e-05</v>
       </c>
       <c r="P3">
-        <v>1.2852034929053951e-05</v>
+        <v>1.2861097919746893e-05</v>
       </c>
       <c r="Q3">
-        <v>2.1422429351680539e-06</v>
+        <v>2.0028269068119913e-06</v>
       </c>
       <c r="R3">
-        <v>3.1392237086245195e-06</v>
+        <v>3.0200197275771797e-06</v>
       </c>
       <c r="S3">
-        <v>-2.167488109638385e-06</v>
+        <v>-2.4128980061865548e-06</v>
       </c>
       <c r="T3">
-        <v>1.7903095210014873e-06</v>
+        <v>1.7093014299367719e-06</v>
       </c>
       <c r="U3">
-        <v>-6.2092317259988623e-06</v>
+        <v>-6.3523805671575023e-06</v>
       </c>
       <c r="V3">
-        <v>-4.7750209927426335e-06</v>
+        <v>-4.6367972362147762e-06</v>
       </c>
       <c r="W3">
-        <v>5.711084054726912e-06</v>
+        <v>5.5397407375916393e-06</v>
       </c>
       <c r="X3">
-        <v>9.0455988857617261e-06</v>
+        <v>8.9720374448379542e-06</v>
       </c>
       <c r="Y3">
-        <v>-0.00011661033011537262</v>
+        <v>-0.00011721838844687722</v>
       </c>
     </row>
     <row r="4">
@@ -538,76 +538,76 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>0.16108450835381913</v>
+        <v>0.16099042849627174</v>
       </c>
       <c r="C4">
-        <v>3.7635611863224171e-05</v>
+        <v>3.7793676776640814e-05</v>
       </c>
       <c r="D4">
-        <v>3.017744319980551e-06</v>
+        <v>3.0121515772836897e-06</v>
       </c>
       <c r="E4">
-        <v>1.1223192227731414e-05</v>
+        <v>1.1305830643889793e-05</v>
       </c>
       <c r="F4">
-        <v>-1.1694061406071668e-07</v>
+        <v>-1.1786907411107868e-07</v>
       </c>
       <c r="G4">
-        <v>3.3610049370447209e-05</v>
+        <v>3.3862253328535479e-05</v>
       </c>
       <c r="H4">
-        <v>3.3000727896372248e-05</v>
+        <v>3.3515627042587226e-05</v>
       </c>
       <c r="I4">
-        <v>-7.1261346565590155e-07</v>
+        <v>-7.1790443122578872e-07</v>
       </c>
       <c r="J4">
-        <v>-6.4716647053636789e-07</v>
+        <v>-6.5769499656390078e-07</v>
       </c>
       <c r="K4">
-        <v>-8.5858951284043146e-06</v>
+        <v>-8.4402585779852944e-06</v>
       </c>
       <c r="L4">
-        <v>-1.2849626124034959e-05</v>
+        <v>-1.3106794664545801e-05</v>
       </c>
       <c r="M4">
-        <v>2.2092011821935227e-06</v>
+        <v>2.2443450283016929e-06</v>
       </c>
       <c r="N4">
-        <v>4.8071559307926343e-06</v>
+        <v>4.8417717685456671e-06</v>
       </c>
       <c r="O4">
-        <v>6.4945157506179902e-06</v>
+        <v>6.5115107533637894e-06</v>
       </c>
       <c r="P4">
-        <v>1.0515512924367032e-05</v>
+        <v>1.0562414049499762e-05</v>
       </c>
       <c r="Q4">
-        <v>1.4292546320355303e-06</v>
+        <v>1.4235205166774607e-06</v>
       </c>
       <c r="R4">
-        <v>1.1910413340624589e-06</v>
+        <v>1.178570278737875e-06</v>
       </c>
       <c r="S4">
-        <v>4.8703722193004131e-07</v>
+        <v>4.8090966906169126e-07</v>
       </c>
       <c r="T4">
-        <v>1.6663707198308055e-06</v>
+        <v>1.6627613582729379e-06</v>
       </c>
       <c r="U4">
-        <v>3.2829403045377973e-07</v>
+        <v>3.2246844718863284e-07</v>
       </c>
       <c r="V4">
-        <v>-1.5924073443884118e-06</v>
+        <v>-1.5465187624462614e-06</v>
       </c>
       <c r="W4">
-        <v>5.1319639636195038e-07</v>
+        <v>5.4630878984697236e-07</v>
       </c>
       <c r="X4">
-        <v>3.5952893214442572e-07</v>
+        <v>4.0532211642489738e-07</v>
       </c>
       <c r="Y4">
-        <v>-0.00025058045398493442</v>
+        <v>-0.00025229472413872513</v>
       </c>
     </row>
     <row r="5">
@@ -615,76 +615,76 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>-0.0019619241892195132</v>
+        <v>-0.0019636339292433344</v>
       </c>
       <c r="C5">
-        <v>-3.6283733161908621e-07</v>
+        <v>-3.6418953456302739e-07</v>
       </c>
       <c r="D5">
-        <v>-3.1029971572066036e-08</v>
+        <v>-3.07526338809503e-08</v>
       </c>
       <c r="E5">
-        <v>-1.1694061406071668e-07</v>
+        <v>-1.1786907411107868e-07</v>
       </c>
       <c r="F5">
-        <v>1.2838258062748602e-09</v>
+        <v>1.294481197421596e-09</v>
       </c>
       <c r="G5">
-        <v>-1.3819125315440107e-07</v>
+        <v>-1.405443214486644e-07</v>
       </c>
       <c r="H5">
-        <v>-1.2238019519191427e-07</v>
+        <v>-1.2776195393357496e-07</v>
       </c>
       <c r="I5">
-        <v>2.5299765949039795e-09</v>
+        <v>2.5787002734849297e-09</v>
       </c>
       <c r="J5">
-        <v>1.6560383094180782e-09</v>
+        <v>1.7649944165524716e-09</v>
       </c>
       <c r="K5">
-        <v>7.5035629993986244e-08</v>
+        <v>7.314534665699316e-08</v>
       </c>
       <c r="L5">
-        <v>1.5406217445556951e-07</v>
+        <v>1.5732232647926429e-07</v>
       </c>
       <c r="M5">
-        <v>-2.499418773271056e-08</v>
+        <v>-2.5434729507913763e-08</v>
       </c>
       <c r="N5">
-        <v>-5.1140697227538733e-08</v>
+        <v>-5.1546329032097234e-08</v>
       </c>
       <c r="O5">
-        <v>-6.1787783522582937e-08</v>
+        <v>-6.1939329435683823e-08</v>
       </c>
       <c r="P5">
-        <v>-9.1527524773972747e-08</v>
+        <v>-9.1979313853705399e-08</v>
       </c>
       <c r="Q5">
-        <v>-1.800406641222405e-08</v>
+        <v>-1.7877888888929421e-08</v>
       </c>
       <c r="R5">
-        <v>-1.7016004741115924e-08</v>
+        <v>-1.6927703041294986e-08</v>
       </c>
       <c r="S5">
-        <v>-4.731693085333438e-09</v>
+        <v>-4.6668756085052081e-09</v>
       </c>
       <c r="T5">
-        <v>-2.0071084534453949e-08</v>
+        <v>-2.0051108673750957e-08</v>
       </c>
       <c r="U5">
-        <v>-1.0096604103184873e-09</v>
+        <v>-9.5352400363220659e-10</v>
       </c>
       <c r="V5">
-        <v>1.8423286454227841e-08</v>
+        <v>1.7848451360334781e-08</v>
       </c>
       <c r="W5">
-        <v>-6.605817393049726e-09</v>
+        <v>-7.0840347204203425e-09</v>
       </c>
       <c r="X5">
-        <v>-6.2584565743969258e-09</v>
+        <v>-6.7621399990584406e-09</v>
       </c>
       <c r="Y5">
-        <v>2.468879685493119e-06</v>
+        <v>2.4874896908678085e-06</v>
       </c>
     </row>
     <row r="6">
@@ -692,76 +692,76 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>-0.41785121806622522</v>
+        <v>-0.42345100253023377</v>
       </c>
       <c r="C6">
-        <v>-7.039577270400799e-05</v>
+        <v>-6.914230034986348e-05</v>
       </c>
       <c r="D6">
-        <v>5.1666718248454747e-06</v>
+        <v>5.8769554902043026e-06</v>
       </c>
       <c r="E6">
-        <v>3.3610049370447209e-05</v>
+        <v>3.3862253328535479e-05</v>
       </c>
       <c r="F6">
-        <v>-1.3819125315440107e-07</v>
+        <v>-1.405443214486644e-07</v>
       </c>
       <c r="G6">
-        <v>0.0024000527169121873</v>
+        <v>0.002409703425254134</v>
       </c>
       <c r="H6">
-        <v>0.0010589709655374269</v>
+        <v>0.0010627527246711583</v>
       </c>
       <c r="I6">
-        <v>-4.9910978295631958e-05</v>
+        <v>-5.0112884496575182e-05</v>
       </c>
       <c r="J6">
-        <v>-2.2347408961617136e-05</v>
+        <v>-2.2427606192300533e-05</v>
       </c>
       <c r="K6">
-        <v>-5.7516142519885521e-06</v>
+        <v>-4.9797090098398636e-06</v>
       </c>
       <c r="L6">
-        <v>-5.3936625776325893e-05</v>
+        <v>-5.5283438720190011e-05</v>
       </c>
       <c r="M6">
-        <v>7.2504078839186843e-06</v>
+        <v>7.1674452892406823e-06</v>
       </c>
       <c r="N6">
-        <v>8.397672489878123e-06</v>
+        <v>8.6099513089398514e-06</v>
       </c>
       <c r="O6">
-        <v>1.1239893869760726e-05</v>
+        <v>1.1415153222290404e-05</v>
       </c>
       <c r="P6">
-        <v>3.2628129655894026e-05</v>
+        <v>3.2827544449442049e-05</v>
       </c>
       <c r="Q6">
-        <v>4.445423449641639e-06</v>
+        <v>4.8732857632976776e-06</v>
       </c>
       <c r="R6">
-        <v>1.5113902613509924e-06</v>
+        <v>1.504498556332856e-06</v>
       </c>
       <c r="S6">
-        <v>-1.9115657197659095e-06</v>
+        <v>-1.9781797199175846e-06</v>
       </c>
       <c r="T6">
-        <v>-5.6664484676520657e-06</v>
+        <v>-5.5319646321372754e-06</v>
       </c>
       <c r="U6">
-        <v>-1.1448503958290276e-05</v>
+        <v>-1.1611480897317256e-05</v>
       </c>
       <c r="V6">
-        <v>-1.0149676103076937e-05</v>
+        <v>-1.0218844545338312e-05</v>
       </c>
       <c r="W6">
-        <v>6.7976865026077628e-06</v>
+        <v>6.6579561869896883e-06</v>
       </c>
       <c r="X6">
-        <v>6.1670635498055813e-06</v>
+        <v>6.3451601328965603e-06</v>
       </c>
       <c r="Y6">
-        <v>-0.0012440409183924889</v>
+        <v>-0.0012507625103392551</v>
       </c>
     </row>
     <row r="7">
@@ -769,76 +769,76 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-0.56218065557254982</v>
+        <v>-0.56261152744549803</v>
       </c>
       <c r="C7">
-        <v>6.5030443682439386e-05</v>
+        <v>6.7281170523516729e-05</v>
       </c>
       <c r="D7">
-        <v>-2.2170649792781237e-06</v>
+        <v>-1.8311166838060058e-06</v>
       </c>
       <c r="E7">
-        <v>3.3000727896372248e-05</v>
+        <v>3.3515627042587226e-05</v>
       </c>
       <c r="F7">
-        <v>-1.2238019519191427e-07</v>
+        <v>-1.2776195393357496e-07</v>
       </c>
       <c r="G7">
-        <v>0.0010589709655374269</v>
+        <v>0.0010627527246711583</v>
       </c>
       <c r="H7">
-        <v>0.0021822171272897709</v>
+        <v>0.0021939979502267797</v>
       </c>
       <c r="I7">
-        <v>-2.2490125244901001e-05</v>
+        <v>-2.2567597056830977e-05</v>
       </c>
       <c r="J7">
-        <v>-4.4131453235267739e-05</v>
+        <v>-4.4376557510629882e-05</v>
       </c>
       <c r="K7">
-        <v>1.2559438219915094e-05</v>
+        <v>1.433526743097214e-05</v>
       </c>
       <c r="L7">
-        <v>-0.00010929767442597621</v>
+        <v>-0.00011239437131380168</v>
       </c>
       <c r="M7">
-        <v>1.213231572676465e-05</v>
+        <v>1.2145353253368749e-05</v>
       </c>
       <c r="N7">
-        <v>1.0834434063884267e-05</v>
+        <v>1.078676700011727e-05</v>
       </c>
       <c r="O7">
-        <v>9.6105601958717439e-06</v>
+        <v>9.534227646613156e-06</v>
       </c>
       <c r="P7">
-        <v>3.8898908288649526e-05</v>
+        <v>3.9010181603094671e-05</v>
       </c>
       <c r="Q7">
-        <v>7.9633759505789005e-06</v>
+        <v>8.3164767321658455e-06</v>
       </c>
       <c r="R7">
-        <v>-5.5233640045138422e-06</v>
+        <v>-5.7556187337109119e-06</v>
       </c>
       <c r="S7">
-        <v>-1.7014921598287376e-05</v>
+        <v>-1.7046291545810205e-05</v>
       </c>
       <c r="T7">
-        <v>-1.3287409139150585e-05</v>
+        <v>-1.2988412160836089e-05</v>
       </c>
       <c r="U7">
-        <v>-3.5950549136931192e-05</v>
+        <v>-3.6082790884597123e-05</v>
       </c>
       <c r="V7">
-        <v>-1.9387934875485656e-05</v>
+        <v>-1.9314611712412368e-05</v>
       </c>
       <c r="W7">
-        <v>1.5502196411901637e-05</v>
+        <v>1.5364197845167787e-05</v>
       </c>
       <c r="X7">
-        <v>1.5542241449421002e-05</v>
+        <v>1.5932771462732996e-05</v>
       </c>
       <c r="Y7">
-        <v>-0.0012388207517911992</v>
+        <v>-0.0012503041707290195</v>
       </c>
     </row>
     <row r="8">
@@ -846,76 +846,76 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.005073429261713152</v>
+        <v>0.0051666842216324506</v>
       </c>
       <c r="C8">
-        <v>1.2315124902761905e-06</v>
+        <v>1.2048132821244012e-06</v>
       </c>
       <c r="D8">
-        <v>-3.4820038044586338e-07</v>
+        <v>-3.6500340493763753e-07</v>
       </c>
       <c r="E8">
-        <v>-7.1261346565590155e-07</v>
+        <v>-7.1790443122578872e-07</v>
       </c>
       <c r="F8">
-        <v>2.5299765949039795e-09</v>
+        <v>2.5787002734849297e-09</v>
       </c>
       <c r="G8">
-        <v>-4.9910978295631958e-05</v>
+        <v>-5.0112884496575182e-05</v>
       </c>
       <c r="H8">
-        <v>-2.2490125244901001e-05</v>
+        <v>-2.2567597056830977e-05</v>
       </c>
       <c r="I8">
-        <v>1.1265527512108246e-06</v>
+        <v>1.130875351294358e-06</v>
       </c>
       <c r="J8">
-        <v>5.1285198580812575e-07</v>
+        <v>5.1452474929939692e-07</v>
       </c>
       <c r="K8">
-        <v>6.3907408000988397e-08</v>
+        <v>4.8789263537601835e-08</v>
       </c>
       <c r="L8">
-        <v>1.2225484190903565e-06</v>
+        <v>1.2458854235625857e-06</v>
       </c>
       <c r="M8">
-        <v>-1.2074615915184401e-07</v>
+        <v>-1.1128263243365947e-07</v>
       </c>
       <c r="N8">
-        <v>-1.195793569453512e-07</v>
+        <v>-1.1772922216912714e-07</v>
       </c>
       <c r="O8">
-        <v>-4.2281365264753337e-09</v>
+        <v>-1.8206144200683642e-09</v>
       </c>
       <c r="P8">
-        <v>-3.1814625114640597e-07</v>
+        <v>-3.1537604152042487e-07</v>
       </c>
       <c r="Q8">
-        <v>-1.7877272226906577e-09</v>
+        <v>-9.7212390663943119e-09</v>
       </c>
       <c r="R8">
-        <v>1.6470714984843657e-08</v>
+        <v>1.7409468455269698e-08</v>
       </c>
       <c r="S8">
-        <v>3.2785114306925699e-08</v>
+        <v>3.3591308395722893e-08</v>
       </c>
       <c r="T8">
-        <v>3.6338635616813778e-08</v>
+        <v>3.4439220642453433e-08</v>
       </c>
       <c r="U8">
-        <v>1.784541399021381e-07</v>
+        <v>1.8182331757358624e-07</v>
       </c>
       <c r="V8">
-        <v>1.5115619323630546e-07</v>
+        <v>1.5061429402537124e-07</v>
       </c>
       <c r="W8">
-        <v>-8.0470731857337259e-08</v>
+        <v>-7.7403302727960661e-08</v>
       </c>
       <c r="X8">
-        <v>-5.4897924928440445e-08</v>
+        <v>-5.6021037201607934e-08</v>
       </c>
       <c r="Y8">
-        <v>2.5491124340933407e-05</v>
+        <v>2.5627798791456673e-05</v>
       </c>
     </row>
     <row r="9">
@@ -923,76 +923,76 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>0.0034851226663128172</v>
+        <v>0.0034662871717521457</v>
       </c>
       <c r="C9">
-        <v>-1.3182613244439658e-06</v>
+        <v>-1.3648060641901778e-06</v>
       </c>
       <c r="D9">
-        <v>-3.9934781626548072e-07</v>
+        <v>-4.0967327252641896e-07</v>
       </c>
       <c r="E9">
-        <v>-6.4716647053636789e-07</v>
+        <v>-6.5769499656390078e-07</v>
       </c>
       <c r="F9">
-        <v>1.6560383094180782e-09</v>
+        <v>1.7649944165524716e-09</v>
       </c>
       <c r="G9">
-        <v>-2.2347408961617136e-05</v>
+        <v>-2.2427606192300533e-05</v>
       </c>
       <c r="H9">
-        <v>-4.4131453235267739e-05</v>
+        <v>-4.4376557510629882e-05</v>
       </c>
       <c r="I9">
-        <v>5.1285198580812575e-07</v>
+        <v>5.1452474929939692e-07</v>
       </c>
       <c r="J9">
-        <v>9.6431705659565206e-07</v>
+        <v>9.6958631562493796e-07</v>
       </c>
       <c r="K9">
-        <v>-4.4040107225794681e-07</v>
+        <v>-4.7545168266514061e-07</v>
       </c>
       <c r="L9">
-        <v>2.3358430651709334e-06</v>
+        <v>2.3937216971513414e-06</v>
       </c>
       <c r="M9">
-        <v>-3.1838925744568299e-07</v>
+        <v>-3.2141197783149047e-07</v>
       </c>
       <c r="N9">
-        <v>-2.2587083220543757e-07</v>
+        <v>-2.2825374269972557e-07</v>
       </c>
       <c r="O9">
-        <v>1.7742873602856898e-07</v>
+        <v>1.7682540274371714e-07</v>
       </c>
       <c r="P9">
-        <v>-2.3193825979991529e-07</v>
+        <v>-2.3591763203369005e-07</v>
       </c>
       <c r="Q9">
-        <v>-2.5994502078208996e-08</v>
+        <v>-3.2299563272393614e-08</v>
       </c>
       <c r="R9">
-        <v>3.6804642476238213e-07</v>
+        <v>3.7279684143280041e-07</v>
       </c>
       <c r="S9">
-        <v>1.4522606577529837e-07</v>
+        <v>1.4552354290964423e-07</v>
       </c>
       <c r="T9">
-        <v>2.406435429129941e-07</v>
+        <v>2.3335993640902808e-07</v>
       </c>
       <c r="U9">
-        <v>4.2919121904164667e-07</v>
+        <v>4.3254146204420034e-07</v>
       </c>
       <c r="V9">
-        <v>2.6854037537018175e-07</v>
+        <v>2.6355758540149212e-07</v>
       </c>
       <c r="W9">
-        <v>-2.0894545913527595e-07</v>
+        <v>-2.042803182526439e-07</v>
       </c>
       <c r="X9">
-        <v>-1.2396507342169301e-07</v>
+        <v>-1.2896416623809115e-07</v>
       </c>
       <c r="Y9">
-        <v>2.4221675374156273e-05</v>
+        <v>2.4462636574844633e-05</v>
       </c>
     </row>
     <row r="10">
@@ -1000,76 +1000,76 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>-0.047879868588837291</v>
+        <v>-0.045998186025236823</v>
       </c>
       <c r="C10">
-        <v>2.1378629626480057e-05</v>
+        <v>2.1439497551592387e-05</v>
       </c>
       <c r="D10">
-        <v>-3.5473730971942918e-06</v>
+        <v>-3.580590229525579e-06</v>
       </c>
       <c r="E10">
-        <v>-8.5858951284043146e-06</v>
+        <v>-8.4402585779852944e-06</v>
       </c>
       <c r="F10">
-        <v>7.5035629993986244e-08</v>
+        <v>7.314534665699316e-08</v>
       </c>
       <c r="G10">
-        <v>-5.7516142519885521e-06</v>
+        <v>-4.9797090098398636e-06</v>
       </c>
       <c r="H10">
-        <v>1.2559438219915094e-05</v>
+        <v>1.433526743097214e-05</v>
       </c>
       <c r="I10">
-        <v>6.3907408000988397e-08</v>
+        <v>4.8789263537601835e-08</v>
       </c>
       <c r="J10">
-        <v>-4.4040107225794681e-07</v>
+        <v>-4.7545168266514061e-07</v>
       </c>
       <c r="K10">
-        <v>0.00016652515357767087</v>
+        <v>0.00016799723784415314</v>
       </c>
       <c r="L10">
-        <v>-5.1532009367745993e-05</v>
+        <v>-5.3677858640336147e-05</v>
       </c>
       <c r="M10">
-        <v>-6.5288587245640478e-06</v>
+        <v>-6.5819604144089208e-06</v>
       </c>
       <c r="N10">
-        <v>-1.5842017212085519e-05</v>
+        <v>-1.5904368563854731e-05</v>
       </c>
       <c r="O10">
-        <v>-2.364816035365556e-05</v>
+        <v>-2.373753494629186e-05</v>
       </c>
       <c r="P10">
-        <v>-2.2938093223347163e-05</v>
+        <v>-2.3009149144296783e-05</v>
       </c>
       <c r="Q10">
-        <v>-2.7587541248345288e-06</v>
+        <v>-2.6197996212978847e-06</v>
       </c>
       <c r="R10">
-        <v>2.9565684692139051e-06</v>
+        <v>3.0533854435091779e-06</v>
       </c>
       <c r="S10">
-        <v>-3.3105430912645903e-06</v>
+        <v>-3.2784814314428069e-06</v>
       </c>
       <c r="T10">
-        <v>-2.5221500356785842e-06</v>
+        <v>-2.3311719155054624e-06</v>
       </c>
       <c r="U10">
-        <v>3.3716769143997658e-08</v>
+        <v>1.5022836475517798e-07</v>
       </c>
       <c r="V10">
-        <v>1.1505396567742331e-05</v>
+        <v>1.1724136590822772e-05</v>
       </c>
       <c r="W10">
-        <v>-8.8210213924130594e-07</v>
+        <v>-7.7222601092049771e-07</v>
       </c>
       <c r="X10">
-        <v>4.0556182386317124e-07</v>
+        <v>4.6357544280030496e-07</v>
       </c>
       <c r="Y10">
-        <v>0.00016157160861471681</v>
+        <v>0.00015915900734784594</v>
       </c>
     </row>
     <row r="11">
@@ -1077,76 +1077,76 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>-0.11382159883560995</v>
+        <v>-0.11982533180292289</v>
       </c>
       <c r="C11">
-        <v>1.3131742014200829e-06</v>
+        <v>1.3458024764383759e-06</v>
       </c>
       <c r="D11">
-        <v>-4.5310110640387007e-06</v>
+        <v>-4.1318779779253134e-06</v>
       </c>
       <c r="E11">
-        <v>-1.2849626124034959e-05</v>
+        <v>-1.3106794664545801e-05</v>
       </c>
       <c r="F11">
-        <v>1.5406217445556951e-07</v>
+        <v>1.5732232647926429e-07</v>
       </c>
       <c r="G11">
-        <v>-5.3936625776325893e-05</v>
+        <v>-5.5283438720190011e-05</v>
       </c>
       <c r="H11">
-        <v>-0.00010929767442597621</v>
+        <v>-0.00011239437131380168</v>
       </c>
       <c r="I11">
-        <v>1.2225484190903565e-06</v>
+        <v>1.2458854235625857e-06</v>
       </c>
       <c r="J11">
-        <v>2.3358430651709334e-06</v>
+        <v>2.3937216971513414e-06</v>
       </c>
       <c r="K11">
-        <v>-5.1532009367745993e-05</v>
+        <v>-5.3677858640336147e-05</v>
       </c>
       <c r="L11">
-        <v>0.00017559153000910627</v>
+        <v>0.00017753240089045554</v>
       </c>
       <c r="M11">
-        <v>-5.0293050855584149e-06</v>
+        <v>-5.3737417042318503e-06</v>
       </c>
       <c r="N11">
-        <v>-1.0765851420839752e-05</v>
+        <v>-1.0981124575140699e-05</v>
       </c>
       <c r="O11">
-        <v>-1.6521843496977614e-05</v>
+        <v>-1.6603702468657804e-05</v>
       </c>
       <c r="P11">
-        <v>-1.8568543181393855e-05</v>
+        <v>-1.8716123572759232e-05</v>
       </c>
       <c r="Q11">
-        <v>-7.2214097515647985e-06</v>
+        <v>-7.3448072448627564e-06</v>
       </c>
       <c r="R11">
-        <v>-7.3758746655500656e-06</v>
+        <v>-7.1861325040677328e-06</v>
       </c>
       <c r="S11">
-        <v>-4.312334110483636e-06</v>
+        <v>-4.1239763400899074e-06</v>
       </c>
       <c r="T11">
-        <v>-7.1298840373377753e-06</v>
+        <v>-7.2965831502472852e-06</v>
       </c>
       <c r="U11">
-        <v>-6.2404596342951593e-06</v>
+        <v>-6.1505745509341717e-06</v>
       </c>
       <c r="V11">
-        <v>-2.7339106883459257e-07</v>
+        <v>-8.9422852147303345e-07</v>
       </c>
       <c r="W11">
-        <v>-2.0963572648921408e-06</v>
+        <v>-2.2881814769898051e-06</v>
       </c>
       <c r="X11">
-        <v>-5.0720331981070855e-06</v>
+        <v>-5.3822970121752696e-06</v>
       </c>
       <c r="Y11">
-        <v>0.00022785976442534005</v>
+        <v>0.0002324886960668921</v>
       </c>
     </row>
     <row r="12">
@@ -1154,76 +1154,76 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>0.25102880918005366</v>
+        <v>0.25280543106962788</v>
       </c>
       <c r="C12">
-        <v>7.0215748909776632e-07</v>
+        <v>5.9028078636401459e-07</v>
       </c>
       <c r="D12">
-        <v>2.9258082990574438e-06</v>
+        <v>2.8413217147769655e-06</v>
       </c>
       <c r="E12">
-        <v>2.2092011821935227e-06</v>
+        <v>2.2443450283016929e-06</v>
       </c>
       <c r="F12">
-        <v>-2.499418773271056e-08</v>
+        <v>-2.5434729507913763e-08</v>
       </c>
       <c r="G12">
-        <v>7.2504078839186843e-06</v>
+        <v>7.1674452892406823e-06</v>
       </c>
       <c r="H12">
-        <v>1.213231572676465e-05</v>
+        <v>1.2145353253368749e-05</v>
       </c>
       <c r="I12">
-        <v>-1.2074615915184401e-07</v>
+        <v>-1.1128263243365947e-07</v>
       </c>
       <c r="J12">
-        <v>-3.1838925744568299e-07</v>
+        <v>-3.2141197783149047e-07</v>
       </c>
       <c r="K12">
-        <v>-6.5288587245640478e-06</v>
+        <v>-6.5819604144089208e-06</v>
       </c>
       <c r="L12">
-        <v>-5.0293050855584149e-06</v>
+        <v>-5.3737417042318503e-06</v>
       </c>
       <c r="M12">
-        <v>0.0043513499012550767</v>
+        <v>0.004372957178233868</v>
       </c>
       <c r="N12">
-        <v>0.0035703204687164009</v>
+        <v>0.0035888054515906846</v>
       </c>
       <c r="O12">
-        <v>0.0035693703197701211</v>
+        <v>0.0035878538529015985</v>
       </c>
       <c r="P12">
-        <v>0.0035680951857395928</v>
+        <v>0.00358659742904364</v>
       </c>
       <c r="Q12">
-        <v>7.244894926365883e-06</v>
+        <v>7.796928143678902e-06</v>
       </c>
       <c r="R12">
-        <v>1.2911383648716147e-05</v>
+        <v>1.2453878747349054e-05</v>
       </c>
       <c r="S12">
-        <v>4.5776914590981024e-06</v>
+        <v>4.6349414388659616e-06</v>
       </c>
       <c r="T12">
-        <v>9.7991299640515841e-06</v>
+        <v>9.9424377755175992e-06</v>
       </c>
       <c r="U12">
-        <v>2.6405051996475392e-06</v>
+        <v>2.3077716223311246e-06</v>
       </c>
       <c r="V12">
-        <v>1.0781726965084075e-05</v>
+        <v>1.09488323283905e-05</v>
       </c>
       <c r="W12">
-        <v>-2.659226834504982e-06</v>
+        <v>-3.6183243356996005e-06</v>
       </c>
       <c r="X12">
-        <v>2.8522856670761173e-06</v>
+        <v>2.848929717393889e-06</v>
       </c>
       <c r="Y12">
-        <v>-0.0036145091879106</v>
+        <v>-0.0036334008134786574</v>
       </c>
     </row>
     <row r="13">
@@ -1231,76 +1231,76 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>0.520951020332732</v>
+        <v>0.52157037460033107</v>
       </c>
       <c r="C13">
-        <v>5.3289683635173845e-06</v>
+        <v>5.1051509280343249e-06</v>
       </c>
       <c r="D13">
-        <v>8.3163865729851295e-06</v>
+        <v>8.0920555668338997e-06</v>
       </c>
       <c r="E13">
-        <v>4.8071559307926343e-06</v>
+        <v>4.8417717685456671e-06</v>
       </c>
       <c r="F13">
-        <v>-5.1140697227538733e-08</v>
+        <v>-5.1546329032097234e-08</v>
       </c>
       <c r="G13">
-        <v>8.397672489878123e-06</v>
+        <v>8.6099513089398514e-06</v>
       </c>
       <c r="H13">
-        <v>1.0834434063884267e-05</v>
+        <v>1.078676700011727e-05</v>
       </c>
       <c r="I13">
-        <v>-1.195793569453512e-07</v>
+        <v>-1.1772922216912714e-07</v>
       </c>
       <c r="J13">
-        <v>-2.2587083220543757e-07</v>
+        <v>-2.2825374269972557e-07</v>
       </c>
       <c r="K13">
-        <v>-1.5842017212085519e-05</v>
+        <v>-1.5904368563854731e-05</v>
       </c>
       <c r="L13">
-        <v>-1.0765851420839752e-05</v>
+        <v>-1.0981124575140699e-05</v>
       </c>
       <c r="M13">
-        <v>0.0035703204687164009</v>
+        <v>0.0035888054515906846</v>
       </c>
       <c r="N13">
-        <v>0.0037206624654834916</v>
+        <v>0.0037396739614343737</v>
       </c>
       <c r="O13">
-        <v>0.0035747873517132777</v>
+        <v>0.0035932635813044241</v>
       </c>
       <c r="P13">
-        <v>0.0035760122346091888</v>
+        <v>0.0035945134525349849</v>
       </c>
       <c r="Q13">
-        <v>1.8399964780818195e-06</v>
+        <v>2.0865113036044023e-06</v>
       </c>
       <c r="R13">
-        <v>5.6532644853852615e-06</v>
+        <v>5.1069692374107912e-06</v>
       </c>
       <c r="S13">
-        <v>-2.6796835551761859e-06</v>
+        <v>-2.6682920428674508e-06</v>
       </c>
       <c r="T13">
-        <v>6.9866038140402347e-06</v>
+        <v>6.9525373830177476e-06</v>
       </c>
       <c r="U13">
-        <v>-4.7112244350561817e-06</v>
+        <v>-5.0922965882223362e-06</v>
       </c>
       <c r="V13">
-        <v>-8.029157398520406e-07</v>
+        <v>-6.1477327371782184e-07</v>
       </c>
       <c r="W13">
-        <v>-6.8262886919653498e-06</v>
+        <v>-7.6993170199178874e-06</v>
       </c>
       <c r="X13">
-        <v>2.2617914458459829e-06</v>
+        <v>2.3170809090563424e-06</v>
       </c>
       <c r="Y13">
-        <v>-0.0036696532994213793</v>
+        <v>-0.0036884452319085187</v>
       </c>
     </row>
     <row r="14">
@@ -1308,76 +1308,76 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0.67871006496297759</v>
+        <v>0.67643052677394822</v>
       </c>
       <c r="C14">
-        <v>4.9740709114392471e-06</v>
+        <v>4.8607902423147592e-06</v>
       </c>
       <c r="D14">
-        <v>1.06937542840598e-05</v>
+        <v>1.062733572271395e-05</v>
       </c>
       <c r="E14">
-        <v>6.4945157506179902e-06</v>
+        <v>6.5115107533637894e-06</v>
       </c>
       <c r="F14">
-        <v>-6.1787783522582937e-08</v>
+        <v>-6.1939329435683823e-08</v>
       </c>
       <c r="G14">
-        <v>1.1239893869760726e-05</v>
+        <v>1.1415153222290404e-05</v>
       </c>
       <c r="H14">
-        <v>9.6105601958717439e-06</v>
+        <v>9.534227646613156e-06</v>
       </c>
       <c r="I14">
-        <v>-4.2281365264753337e-09</v>
+        <v>-1.8206144200683642e-09</v>
       </c>
       <c r="J14">
-        <v>1.7742873602856898e-07</v>
+        <v>1.7682540274371714e-07</v>
       </c>
       <c r="K14">
-        <v>-2.364816035365556e-05</v>
+        <v>-2.373753494629186e-05</v>
       </c>
       <c r="L14">
-        <v>-1.6521843496977614e-05</v>
+        <v>-1.6603702468657804e-05</v>
       </c>
       <c r="M14">
-        <v>0.0035693703197701211</v>
+        <v>0.0035878538529015985</v>
       </c>
       <c r="N14">
-        <v>0.0035747873517132777</v>
+        <v>0.0035932635813044241</v>
       </c>
       <c r="O14">
-        <v>0.0036312711649776168</v>
+        <v>0.0036498719074989508</v>
       </c>
       <c r="P14">
-        <v>0.0035940650119536226</v>
+        <v>0.0036126075904647599</v>
       </c>
       <c r="Q14">
-        <v>-4.5278148072298315e-06</v>
+        <v>-4.3263167789895133e-06</v>
       </c>
       <c r="R14">
-        <v>1.4764703699844011e-06</v>
+        <v>9.0247306661077234e-07</v>
       </c>
       <c r="S14">
-        <v>-9.7091994508373408e-06</v>
+        <v>-9.7948247443882297e-06</v>
       </c>
       <c r="T14">
-        <v>3.7743477250128951e-06</v>
+        <v>3.7826019202283942e-06</v>
       </c>
       <c r="U14">
-        <v>-9.2885581969664831e-06</v>
+        <v>-9.6351420970411226e-06</v>
       </c>
       <c r="V14">
-        <v>5.0788656043477425e-06</v>
+        <v>5.3159601723452231e-06</v>
       </c>
       <c r="W14">
-        <v>-7.1179462224887442e-06</v>
+        <v>-7.9803980682089089e-06</v>
       </c>
       <c r="X14">
-        <v>4.895541103505398e-06</v>
+        <v>4.964210520537333e-06</v>
       </c>
       <c r="Y14">
-        <v>-0.0037313408862465368</v>
+        <v>-0.0037500106803139621</v>
       </c>
     </row>
     <row r="15">
@@ -1385,76 +1385,76 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>0.67172158065640086</v>
+        <v>0.6697323857460088</v>
       </c>
       <c r="C15">
-        <v>1.9876746229329357e-06</v>
+        <v>1.9284411210990118e-06</v>
       </c>
       <c r="D15">
-        <v>1.2852034929053951e-05</v>
+        <v>1.2861097919746893e-05</v>
       </c>
       <c r="E15">
-        <v>1.0515512924367032e-05</v>
+        <v>1.0562414049499762e-05</v>
       </c>
       <c r="F15">
-        <v>-9.1527524773972747e-08</v>
+        <v>-9.1979313853705399e-08</v>
       </c>
       <c r="G15">
-        <v>3.2628129655894026e-05</v>
+        <v>3.2827544449442049e-05</v>
       </c>
       <c r="H15">
-        <v>3.8898908288649526e-05</v>
+        <v>3.9010181603094671e-05</v>
       </c>
       <c r="I15">
-        <v>-3.1814625114640597e-07</v>
+        <v>-3.1537604152042487e-07</v>
       </c>
       <c r="J15">
-        <v>-2.3193825979991529e-07</v>
+        <v>-2.3591763203369005e-07</v>
       </c>
       <c r="K15">
-        <v>-2.2938093223347163e-05</v>
+        <v>-2.3009149144296783e-05</v>
       </c>
       <c r="L15">
-        <v>-1.8568543181393855e-05</v>
+        <v>-1.8716123572759232e-05</v>
       </c>
       <c r="M15">
-        <v>0.0035680951857395928</v>
+        <v>0.00358659742904364</v>
       </c>
       <c r="N15">
-        <v>0.0035760122346091888</v>
+        <v>0.0035945134525349849</v>
       </c>
       <c r="O15">
-        <v>0.0035940650119536226</v>
+        <v>0.0036126075904647599</v>
       </c>
       <c r="P15">
-        <v>0.0037737378252681989</v>
+        <v>0.0037926545188960081</v>
       </c>
       <c r="Q15">
-        <v>-1.2042210257219639e-05</v>
+        <v>-1.180491652666714e-05</v>
       </c>
       <c r="R15">
-        <v>-7.5414786816058968e-06</v>
+        <v>-8.1415857327138934e-06</v>
       </c>
       <c r="S15">
-        <v>-1.3507510707194651e-05</v>
+        <v>-1.365607456398905e-05</v>
       </c>
       <c r="T15">
-        <v>-8.9710496959651904e-06</v>
+        <v>-9.0499108089618218e-06</v>
       </c>
       <c r="U15">
-        <v>-1.9415624512475184e-05</v>
+        <v>-1.988841745252533e-05</v>
       </c>
       <c r="V15">
-        <v>-5.5689124964271585e-06</v>
+        <v>-5.4459401332375212e-06</v>
       </c>
       <c r="W15">
-        <v>-1.1797723467004485e-05</v>
+        <v>-1.2775478515754379e-05</v>
       </c>
       <c r="X15">
-        <v>4.4898699790875024e-06</v>
+        <v>4.6301228970105289e-06</v>
       </c>
       <c r="Y15">
-        <v>-0.0038544324578319118</v>
+        <v>-0.003873809971319319</v>
       </c>
     </row>
     <row r="16">
@@ -1462,76 +1462,76 @@
         <v>36</v>
       </c>
       <c r="B16">
-        <v>0.073692222743085373</v>
+        <v>0.073939030733738878</v>
       </c>
       <c r="C16">
-        <v>2.8493485357173865e-06</v>
+        <v>2.8625945207049448e-06</v>
       </c>
       <c r="D16">
-        <v>2.1422429351680539e-06</v>
+        <v>2.0028269068119913e-06</v>
       </c>
       <c r="E16">
-        <v>1.4292546320355303e-06</v>
+        <v>1.4235205166774607e-06</v>
       </c>
       <c r="F16">
-        <v>-1.800406641222405e-08</v>
+        <v>-1.7877888888929421e-08</v>
       </c>
       <c r="G16">
-        <v>4.445423449641639e-06</v>
+        <v>4.8732857632976776e-06</v>
       </c>
       <c r="H16">
-        <v>7.9633759505789005e-06</v>
+        <v>8.3164767321658455e-06</v>
       </c>
       <c r="I16">
-        <v>-1.7877272226906577e-09</v>
+        <v>-9.7212390663943119e-09</v>
       </c>
       <c r="J16">
-        <v>-2.5994502078208996e-08</v>
+        <v>-3.2299563272393614e-08</v>
       </c>
       <c r="K16">
-        <v>-2.7587541248345288e-06</v>
+        <v>-2.6197996212978847e-06</v>
       </c>
       <c r="L16">
-        <v>-7.2214097515647985e-06</v>
+        <v>-7.3448072448627564e-06</v>
       </c>
       <c r="M16">
-        <v>7.244894926365883e-06</v>
+        <v>7.796928143678902e-06</v>
       </c>
       <c r="N16">
-        <v>1.8399964780818195e-06</v>
+        <v>2.0865113036044023e-06</v>
       </c>
       <c r="O16">
-        <v>-4.5278148072298315e-06</v>
+        <v>-4.3263167789895133e-06</v>
       </c>
       <c r="P16">
-        <v>-1.2042210257219639e-05</v>
+        <v>-1.180491652666714e-05</v>
       </c>
       <c r="Q16">
-        <v>0.00039857818172638548</v>
+        <v>0.00039952377021493105</v>
       </c>
       <c r="R16">
-        <v>0.00020916679615355069</v>
+        <v>0.00020970808892838833</v>
       </c>
       <c r="S16">
-        <v>0.00020784636961141418</v>
+        <v>0.00020839606423495708</v>
       </c>
       <c r="T16">
-        <v>0.00020863600195786676</v>
+        <v>0.00020918703948760966</v>
       </c>
       <c r="U16">
-        <v>0.00020758448624725895</v>
+        <v>0.00020814866367216048</v>
       </c>
       <c r="V16">
-        <v>0.00020675818443960476</v>
+        <v>0.00020734765954582212</v>
       </c>
       <c r="W16">
-        <v>1.375355982132621e-06</v>
+        <v>1.4240997745217489e-06</v>
       </c>
       <c r="X16">
-        <v>8.2531002632138115e-08</v>
+        <v>1.6156980382192108e-07</v>
       </c>
       <c r="Y16">
-        <v>-0.00022892873610641688</v>
+        <v>-0.00022973963415141353</v>
       </c>
     </row>
     <row r="17">
@@ -1539,76 +1539,76 @@
         <v>37</v>
       </c>
       <c r="B17">
-        <v>0.05126475579648359</v>
+        <v>0.05473605787533857</v>
       </c>
       <c r="C17">
-        <v>3.7886423362497602e-06</v>
+        <v>3.759834000307216e-06</v>
       </c>
       <c r="D17">
-        <v>3.1392237086245195e-06</v>
+        <v>3.0200197275771797e-06</v>
       </c>
       <c r="E17">
-        <v>1.1910413340624589e-06</v>
+        <v>1.178570278737875e-06</v>
       </c>
       <c r="F17">
-        <v>-1.7016004741115924e-08</v>
+        <v>-1.6927703041294986e-08</v>
       </c>
       <c r="G17">
-        <v>1.5113902613509924e-06</v>
+        <v>1.504498556332856e-06</v>
       </c>
       <c r="H17">
-        <v>-5.5233640045138422e-06</v>
+        <v>-5.7556187337109119e-06</v>
       </c>
       <c r="I17">
-        <v>1.6470714984843657e-08</v>
+        <v>1.7409468455269698e-08</v>
       </c>
       <c r="J17">
-        <v>3.6804642476238213e-07</v>
+        <v>3.7279684143280041e-07</v>
       </c>
       <c r="K17">
-        <v>2.9565684692139051e-06</v>
+        <v>3.0533854435091779e-06</v>
       </c>
       <c r="L17">
-        <v>-7.3758746655500656e-06</v>
+        <v>-7.1861325040677328e-06</v>
       </c>
       <c r="M17">
-        <v>1.2911383648716147e-05</v>
+        <v>1.2453878747349054e-05</v>
       </c>
       <c r="N17">
-        <v>5.6532644853852615e-06</v>
+        <v>5.1069692374107912e-06</v>
       </c>
       <c r="O17">
-        <v>1.4764703699844011e-06</v>
+        <v>9.0247306661077234e-07</v>
       </c>
       <c r="P17">
-        <v>-7.5414786816058968e-06</v>
+        <v>-8.1415857327138934e-06</v>
       </c>
       <c r="Q17">
-        <v>0.00020916679615355069</v>
+        <v>0.00020970808892838833</v>
       </c>
       <c r="R17">
-        <v>0.00047853684428967132</v>
+        <v>0.00047970203285934218</v>
       </c>
       <c r="S17">
-        <v>0.00020734517434658174</v>
+        <v>0.0002078808772396059</v>
       </c>
       <c r="T17">
-        <v>0.00020873398824343837</v>
+        <v>0.000209266645245289</v>
       </c>
       <c r="U17">
-        <v>0.00020723874029475849</v>
+        <v>0.00020778396247767469</v>
       </c>
       <c r="V17">
-        <v>0.00020723423948553212</v>
+        <v>0.0002078106975997259</v>
       </c>
       <c r="W17">
-        <v>-8.9308460403442874e-07</v>
+        <v>-7.7695844309462783e-07</v>
       </c>
       <c r="X17">
-        <v>-4.7206916125607647e-06</v>
+        <v>-4.8549173605707801e-06</v>
       </c>
       <c r="Y17">
-        <v>-0.00023084883665623171</v>
+        <v>-0.00023051851957970958</v>
       </c>
     </row>
     <row r="18">
@@ -1616,76 +1616,76 @@
         <v>38</v>
       </c>
       <c r="B18">
-        <v>-0.014076818221382494</v>
+        <v>-0.011406352161242117</v>
       </c>
       <c r="C18">
-        <v>6.4079993556668044e-07</v>
+        <v>5.7401949537125118e-07</v>
       </c>
       <c r="D18">
-        <v>-2.167488109638385e-06</v>
+        <v>-2.4128980061865548e-06</v>
       </c>
       <c r="E18">
-        <v>4.8703722193004131e-07</v>
+        <v>4.8090966906169126e-07</v>
       </c>
       <c r="F18">
-        <v>-4.731693085333438e-09</v>
+        <v>-4.6668756085052081e-09</v>
       </c>
       <c r="G18">
-        <v>-1.9115657197659095e-06</v>
+        <v>-1.9781797199175846e-06</v>
       </c>
       <c r="H18">
-        <v>-1.7014921598287376e-05</v>
+        <v>-1.7046291545810205e-05</v>
       </c>
       <c r="I18">
-        <v>3.2785114306925699e-08</v>
+        <v>3.3591308395722893e-08</v>
       </c>
       <c r="J18">
-        <v>1.4522606577529837e-07</v>
+        <v>1.4552354290964423e-07</v>
       </c>
       <c r="K18">
-        <v>-3.3105430912645903e-06</v>
+        <v>-3.2784814314428069e-06</v>
       </c>
       <c r="L18">
-        <v>-4.312334110483636e-06</v>
+        <v>-4.1239763400899074e-06</v>
       </c>
       <c r="M18">
-        <v>4.5776914590981024e-06</v>
+        <v>4.6349414388659616e-06</v>
       </c>
       <c r="N18">
-        <v>-2.6796835551761859e-06</v>
+        <v>-2.6682920428674508e-06</v>
       </c>
       <c r="O18">
-        <v>-9.7091994508373408e-06</v>
+        <v>-9.7948247443882297e-06</v>
       </c>
       <c r="P18">
-        <v>-1.3507510707194651e-05</v>
+        <v>-1.365607456398905e-05</v>
       </c>
       <c r="Q18">
-        <v>0.00020784636961141418</v>
+        <v>0.00020839606423495708</v>
       </c>
       <c r="R18">
-        <v>0.00020734517434658174</v>
+        <v>0.0002078808772396059</v>
       </c>
       <c r="S18">
-        <v>0.00038720143444915628</v>
+        <v>0.00038811341295038796</v>
       </c>
       <c r="T18">
-        <v>0.00020828084976414133</v>
+        <v>0.00020883198976503459</v>
       </c>
       <c r="U18">
-        <v>0.00021008513291280714</v>
+        <v>0.00021064119155054603</v>
       </c>
       <c r="V18">
-        <v>0.0002078348288325775</v>
+        <v>0.00020841724370849164</v>
       </c>
       <c r="W18">
-        <v>-4.9775195416931294e-06</v>
+        <v>-4.9296783591883805e-06</v>
       </c>
       <c r="X18">
-        <v>-5.8113497166520079e-06</v>
+        <v>-5.7235287156870373e-06</v>
       </c>
       <c r="Y18">
-        <v>-0.00020253055970155418</v>
+        <v>-0.0002028385161672271</v>
       </c>
     </row>
     <row r="19">
@@ -1693,76 +1693,76 @@
         <v>39</v>
       </c>
       <c r="B19">
-        <v>0.09378628572061265</v>
+        <v>0.095650862321854518</v>
       </c>
       <c r="C19">
-        <v>5.7738368143280504e-06</v>
+        <v>5.736884804500962e-06</v>
       </c>
       <c r="D19">
-        <v>1.7903095210014873e-06</v>
+        <v>1.7093014299367719e-06</v>
       </c>
       <c r="E19">
-        <v>1.6663707198308055e-06</v>
+        <v>1.6627613582729379e-06</v>
       </c>
       <c r="F19">
-        <v>-2.0071084534453949e-08</v>
+        <v>-2.0051108673750957e-08</v>
       </c>
       <c r="G19">
-        <v>-5.6664484676520657e-06</v>
+        <v>-5.5319646321372754e-06</v>
       </c>
       <c r="H19">
-        <v>-1.3287409139150585e-05</v>
+        <v>-1.2988412160836089e-05</v>
       </c>
       <c r="I19">
-        <v>3.6338635616813778e-08</v>
+        <v>3.4439220642453433e-08</v>
       </c>
       <c r="J19">
-        <v>2.406435429129941e-07</v>
+        <v>2.3335993640902808e-07</v>
       </c>
       <c r="K19">
-        <v>-2.5221500356785842e-06</v>
+        <v>-2.3311719155054624e-06</v>
       </c>
       <c r="L19">
-        <v>-7.1298840373377753e-06</v>
+        <v>-7.2965831502472852e-06</v>
       </c>
       <c r="M19">
-        <v>9.7991299640515841e-06</v>
+        <v>9.9424377755175992e-06</v>
       </c>
       <c r="N19">
-        <v>6.9866038140402347e-06</v>
+        <v>6.9525373830177476e-06</v>
       </c>
       <c r="O19">
-        <v>3.7743477250128951e-06</v>
+        <v>3.7826019202283942e-06</v>
       </c>
       <c r="P19">
-        <v>-8.9710496959651904e-06</v>
+        <v>-9.0499108089618218e-06</v>
       </c>
       <c r="Q19">
-        <v>0.00020863600195786676</v>
+        <v>0.00020918703948760966</v>
       </c>
       <c r="R19">
-        <v>0.00020873398824343837</v>
+        <v>0.000209266645245289</v>
       </c>
       <c r="S19">
-        <v>0.00020828084976414133</v>
+        <v>0.00020883198976503459</v>
       </c>
       <c r="T19">
-        <v>0.00032751469574160804</v>
+        <v>0.0003282765798828837</v>
       </c>
       <c r="U19">
-        <v>0.00020900457198413748</v>
+        <v>0.00020956701882821193</v>
       </c>
       <c r="V19">
-        <v>0.00020786332807523817</v>
+        <v>0.00020846723956346317</v>
       </c>
       <c r="W19">
-        <v>6.4923544262157329e-06</v>
+        <v>6.5574405688142069e-06</v>
       </c>
       <c r="X19">
-        <v>5.9119263836670848e-06</v>
+        <v>6.0630947576270373e-06</v>
       </c>
       <c r="Y19">
-        <v>-0.00023757989767552652</v>
+        <v>-0.00023801216049149871</v>
       </c>
     </row>
     <row r="20">
@@ -1770,76 +1770,76 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <v>-0.1015328748478599</v>
+        <v>-0.10081636936924131</v>
       </c>
       <c r="C20">
-        <v>6.4399516836442697e-06</v>
+        <v>6.4308524325009454e-06</v>
       </c>
       <c r="D20">
-        <v>-6.2092317259988623e-06</v>
+        <v>-6.3523805671575023e-06</v>
       </c>
       <c r="E20">
-        <v>3.2829403045377973e-07</v>
+        <v>3.2246844718863284e-07</v>
       </c>
       <c r="F20">
-        <v>-1.0096604103184873e-09</v>
+        <v>-9.5352400363220659e-10</v>
       </c>
       <c r="G20">
-        <v>-1.1448503958290276e-05</v>
+        <v>-1.1611480897317256e-05</v>
       </c>
       <c r="H20">
-        <v>-3.5950549136931192e-05</v>
+        <v>-3.6082790884597123e-05</v>
       </c>
       <c r="I20">
-        <v>1.784541399021381e-07</v>
+        <v>1.8182331757358624e-07</v>
       </c>
       <c r="J20">
-        <v>4.2919121904164667e-07</v>
+        <v>4.3254146204420034e-07</v>
       </c>
       <c r="K20">
-        <v>3.3716769143997658e-08</v>
+        <v>1.5022836475517798e-07</v>
       </c>
       <c r="L20">
-        <v>-6.2404596342951593e-06</v>
+        <v>-6.1505745509341717e-06</v>
       </c>
       <c r="M20">
-        <v>2.6405051996475392e-06</v>
+        <v>2.3077716223311246e-06</v>
       </c>
       <c r="N20">
-        <v>-4.7112244350561817e-06</v>
+        <v>-5.0922965882223362e-06</v>
       </c>
       <c r="O20">
-        <v>-9.2885581969664831e-06</v>
+        <v>-9.6351420970411226e-06</v>
       </c>
       <c r="P20">
-        <v>-1.9415624512475184e-05</v>
+        <v>-1.988841745252533e-05</v>
       </c>
       <c r="Q20">
-        <v>0.00020758448624725895</v>
+        <v>0.00020814866367216048</v>
       </c>
       <c r="R20">
-        <v>0.00020723874029475849</v>
+        <v>0.00020778396247767469</v>
       </c>
       <c r="S20">
-        <v>0.00021008513291280714</v>
+        <v>0.00021064119155054603</v>
       </c>
       <c r="T20">
-        <v>0.00020900457198413748</v>
+        <v>0.00020956701882821193</v>
       </c>
       <c r="U20">
-        <v>0.00035523530052020022</v>
+        <v>0.00035630446974883119</v>
       </c>
       <c r="V20">
-        <v>0.00020958615474129622</v>
+        <v>0.00021018918497203189</v>
       </c>
       <c r="W20">
-        <v>-2.0323145377481024e-07</v>
+        <v>-2.0963625016866275e-07</v>
       </c>
       <c r="X20">
-        <v>-1.9230246924610818e-06</v>
+        <v>-1.8346114928346179e-06</v>
       </c>
       <c r="Y20">
-        <v>-0.000201066317566371</v>
+        <v>-0.00020113984537291935</v>
       </c>
     </row>
     <row r="21">
@@ -1847,76 +1847,76 @@
         <v>41</v>
       </c>
       <c r="B21">
-        <v>-0.049806128178538564</v>
+        <v>-0.046609943731560064</v>
       </c>
       <c r="C21">
-        <v>-4.1962939247760638e-07</v>
+        <v>-4.2449270722484388e-07</v>
       </c>
       <c r="D21">
-        <v>-4.7750209927426335e-06</v>
+        <v>-4.6367972362147762e-06</v>
       </c>
       <c r="E21">
-        <v>-1.5924073443884118e-06</v>
+        <v>-1.5465187624462614e-06</v>
       </c>
       <c r="F21">
-        <v>1.8423286454227841e-08</v>
+        <v>1.7848451360334781e-08</v>
       </c>
       <c r="G21">
-        <v>-1.0149676103076937e-05</v>
+        <v>-1.0218844545338312e-05</v>
       </c>
       <c r="H21">
-        <v>-1.9387934875485656e-05</v>
+        <v>-1.9314611712412368e-05</v>
       </c>
       <c r="I21">
-        <v>1.5115619323630546e-07</v>
+        <v>1.5061429402537124e-07</v>
       </c>
       <c r="J21">
-        <v>2.6854037537018175e-07</v>
+        <v>2.6355758540149212e-07</v>
       </c>
       <c r="K21">
-        <v>1.1505396567742331e-05</v>
+        <v>1.1724136590822772e-05</v>
       </c>
       <c r="L21">
-        <v>-2.7339106883459257e-07</v>
+        <v>-8.9422852147303345e-07</v>
       </c>
       <c r="M21">
-        <v>1.0781726965084075e-05</v>
+        <v>1.09488323283905e-05</v>
       </c>
       <c r="N21">
-        <v>-8.029157398520406e-07</v>
+        <v>-6.1477327371782184e-07</v>
       </c>
       <c r="O21">
-        <v>5.0788656043477425e-06</v>
+        <v>5.3159601723452231e-06</v>
       </c>
       <c r="P21">
-        <v>-5.5689124964271585e-06</v>
+        <v>-5.4459401332375212e-06</v>
       </c>
       <c r="Q21">
-        <v>0.00020675818443960476</v>
+        <v>0.00020734765954582212</v>
       </c>
       <c r="R21">
-        <v>0.00020723423948553212</v>
+        <v>0.0002078106975997259</v>
       </c>
       <c r="S21">
-        <v>0.0002078348288325775</v>
+        <v>0.00020841724370849164</v>
       </c>
       <c r="T21">
-        <v>0.00020786332807523817</v>
+        <v>0.00020846723956346317</v>
       </c>
       <c r="U21">
-        <v>0.00020958615474129622</v>
+        <v>0.00021018918497203189</v>
       </c>
       <c r="V21">
-        <v>0.00091779250483804752</v>
+        <v>0.00092007927223266488</v>
       </c>
       <c r="W21">
-        <v>5.2602395908732781e-06</v>
+        <v>5.4314226619757109e-06</v>
       </c>
       <c r="X21">
-        <v>5.6574551329543511e-06</v>
+        <v>5.7695025754377264e-06</v>
       </c>
       <c r="Y21">
-        <v>-0.00018173958476425619</v>
+        <v>-0.00018320331100858756</v>
       </c>
     </row>
     <row r="22">
@@ -1924,76 +1924,76 @@
         <v>42</v>
       </c>
       <c r="B22">
-        <v>-0.0923495704559784</v>
+        <v>-0.090353240044207653</v>
       </c>
       <c r="C22">
-        <v>9.9562976616470948e-06</v>
+        <v>9.9154514910156613e-06</v>
       </c>
       <c r="D22">
-        <v>5.711084054726912e-06</v>
+        <v>5.5397407375916393e-06</v>
       </c>
       <c r="E22">
-        <v>5.1319639636195038e-07</v>
+        <v>5.4630878984697236e-07</v>
       </c>
       <c r="F22">
-        <v>-6.605817393049726e-09</v>
+        <v>-7.0840347204203425e-09</v>
       </c>
       <c r="G22">
-        <v>6.7976865026077628e-06</v>
+        <v>6.6579561869896883e-06</v>
       </c>
       <c r="H22">
-        <v>1.5502196411901637e-05</v>
+        <v>1.5364197845167787e-05</v>
       </c>
       <c r="I22">
-        <v>-8.0470731857337259e-08</v>
+        <v>-7.7403302727960661e-08</v>
       </c>
       <c r="J22">
-        <v>-2.0894545913527595e-07</v>
+        <v>-2.042803182526439e-07</v>
       </c>
       <c r="K22">
-        <v>-8.8210213924130594e-07</v>
+        <v>-7.7222601092049771e-07</v>
       </c>
       <c r="L22">
-        <v>-2.0963572648921408e-06</v>
+        <v>-2.2881814769898051e-06</v>
       </c>
       <c r="M22">
-        <v>-2.659226834504982e-06</v>
+        <v>-3.6183243356996005e-06</v>
       </c>
       <c r="N22">
-        <v>-6.8262886919653498e-06</v>
+        <v>-7.6993170199178874e-06</v>
       </c>
       <c r="O22">
-        <v>-7.1179462224887442e-06</v>
+        <v>-7.9803980682089089e-06</v>
       </c>
       <c r="P22">
-        <v>-1.1797723467004485e-05</v>
+        <v>-1.2775478515754379e-05</v>
       </c>
       <c r="Q22">
-        <v>1.375355982132621e-06</v>
+        <v>1.4240997745217489e-06</v>
       </c>
       <c r="R22">
-        <v>-8.9308460403442874e-07</v>
+        <v>-7.7695844309462783e-07</v>
       </c>
       <c r="S22">
-        <v>-4.9775195416931294e-06</v>
+        <v>-4.9296783591883805e-06</v>
       </c>
       <c r="T22">
-        <v>6.4923544262157329e-06</v>
+        <v>6.5574405688142069e-06</v>
       </c>
       <c r="U22">
-        <v>-2.0323145377481024e-07</v>
+        <v>-2.0963625016866275e-07</v>
       </c>
       <c r="V22">
-        <v>5.2602395908732781e-06</v>
+        <v>5.4314226619757109e-06</v>
       </c>
       <c r="W22">
-        <v>0.00051575269920147078</v>
+        <v>0.00051744714241828168</v>
       </c>
       <c r="X22">
-        <v>3.236362748455832e-05</v>
+        <v>3.2441371723777231e-05</v>
       </c>
       <c r="Y22">
-        <v>-3.7151624126349185e-05</v>
+        <v>-3.6789810356556627e-05</v>
       </c>
     </row>
     <row r="23">
@@ -2001,76 +2001,76 @@
         <v>43</v>
       </c>
       <c r="B23">
-        <v>0.040627500029932775</v>
+        <v>0.041230905834958712</v>
       </c>
       <c r="C23">
-        <v>4.3000236693587114e-06</v>
+        <v>4.4080477075468059e-06</v>
       </c>
       <c r="D23">
-        <v>9.0455988857617261e-06</v>
+        <v>8.9720374448379542e-06</v>
       </c>
       <c r="E23">
-        <v>3.5952893214442572e-07</v>
+        <v>4.0532211642489738e-07</v>
       </c>
       <c r="F23">
-        <v>-6.2584565743969258e-09</v>
+        <v>-6.7621399990584406e-09</v>
       </c>
       <c r="G23">
-        <v>6.1670635498055813e-06</v>
+        <v>6.3451601328965603e-06</v>
       </c>
       <c r="H23">
-        <v>1.5542241449421002e-05</v>
+        <v>1.5932771462732996e-05</v>
       </c>
       <c r="I23">
-        <v>-5.4897924928440445e-08</v>
+        <v>-5.6021037201607934e-08</v>
       </c>
       <c r="J23">
-        <v>-1.2396507342169301e-07</v>
+        <v>-1.2896416623809115e-07</v>
       </c>
       <c r="K23">
-        <v>4.0556182386317124e-07</v>
+        <v>4.6357544280030496e-07</v>
       </c>
       <c r="L23">
-        <v>-5.0720331981070855e-06</v>
+        <v>-5.3822970121752696e-06</v>
       </c>
       <c r="M23">
-        <v>2.8522856670761173e-06</v>
+        <v>2.848929717393889e-06</v>
       </c>
       <c r="N23">
-        <v>2.2617914458459829e-06</v>
+        <v>2.3170809090563424e-06</v>
       </c>
       <c r="O23">
-        <v>4.895541103505398e-06</v>
+        <v>4.964210520537333e-06</v>
       </c>
       <c r="P23">
-        <v>4.4898699790875024e-06</v>
+        <v>4.6301228970105289e-06</v>
       </c>
       <c r="Q23">
-        <v>8.2531002632138115e-08</v>
+        <v>1.6156980382192108e-07</v>
       </c>
       <c r="R23">
-        <v>-4.7206916125607647e-06</v>
+        <v>-4.8549173605707801e-06</v>
       </c>
       <c r="S23">
-        <v>-5.8113497166520079e-06</v>
+        <v>-5.7235287156870373e-06</v>
       </c>
       <c r="T23">
-        <v>5.9119263836670848e-06</v>
+        <v>6.0630947576270373e-06</v>
       </c>
       <c r="U23">
-        <v>-1.9230246924610818e-06</v>
+        <v>-1.8346114928346179e-06</v>
       </c>
       <c r="V23">
-        <v>5.6574551329543511e-06</v>
+        <v>5.7695025754377264e-06</v>
       </c>
       <c r="W23">
-        <v>3.236362748455832e-05</v>
+        <v>3.2441371723777231e-05</v>
       </c>
       <c r="X23">
-        <v>0.00061848160784097475</v>
+        <v>0.00061898709946216321</v>
       </c>
       <c r="Y23">
-        <v>-4.4096993446648153e-05</v>
+        <v>-4.5257485045778354e-05</v>
       </c>
     </row>
     <row r="24">
@@ -2078,76 +2078,76 @@
         <v>44</v>
       </c>
       <c r="B24">
-        <v>-2.1863205181631735</v>
+        <v>-2.1748096756334805</v>
       </c>
       <c r="C24">
-        <v>-0.000988449099072807</v>
+        <v>-0.00099309852096993948</v>
       </c>
       <c r="D24">
-        <v>-0.00011661033011537262</v>
+        <v>-0.00011721838844687722</v>
       </c>
       <c r="E24">
-        <v>-0.00025058045398493442</v>
+        <v>-0.00025229472413872513</v>
       </c>
       <c r="F24">
-        <v>2.468879685493119e-06</v>
+        <v>2.4874896908678085e-06</v>
       </c>
       <c r="G24">
-        <v>-0.0012440409183924889</v>
+        <v>-0.0012507625103392551</v>
       </c>
       <c r="H24">
-        <v>-0.0012388207517911992</v>
+        <v>-0.0012503041707290195</v>
       </c>
       <c r="I24">
-        <v>2.5491124340933407e-05</v>
+        <v>2.5627798791456673e-05</v>
       </c>
       <c r="J24">
-        <v>2.4221675374156273e-05</v>
+        <v>2.4462636574844633e-05</v>
       </c>
       <c r="K24">
-        <v>0.00016157160861471681</v>
+        <v>0.00015915900734784594</v>
       </c>
       <c r="L24">
-        <v>0.00022785976442534005</v>
+        <v>0.0002324886960668921</v>
       </c>
       <c r="M24">
-        <v>-0.0036145091879106</v>
+        <v>-0.0036334008134786574</v>
       </c>
       <c r="N24">
-        <v>-0.0036696532994213793</v>
+        <v>-0.0036884452319085187</v>
       </c>
       <c r="O24">
-        <v>-0.0037313408862465368</v>
+        <v>-0.0037500106803139621</v>
       </c>
       <c r="P24">
-        <v>-0.0038544324578319118</v>
+        <v>-0.003873809971319319</v>
       </c>
       <c r="Q24">
-        <v>-0.00022892873610641688</v>
+        <v>-0.00022973963415141353</v>
       </c>
       <c r="R24">
-        <v>-0.00023084883665623171</v>
+        <v>-0.00023051851957970958</v>
       </c>
       <c r="S24">
-        <v>-0.00020253055970155418</v>
+        <v>-0.0002028385161672271</v>
       </c>
       <c r="T24">
-        <v>-0.00023757989767552652</v>
+        <v>-0.00023801216049149871</v>
       </c>
       <c r="U24">
-        <v>-0.000201066317566371</v>
+        <v>-0.00020113984537291935</v>
       </c>
       <c r="V24">
-        <v>-0.00018173958476425619</v>
+        <v>-0.00018320331100858756</v>
       </c>
       <c r="W24">
-        <v>-3.7151624126349185e-05</v>
+        <v>-3.6789810356556627e-05</v>
       </c>
       <c r="X24">
-        <v>-4.4096993446648153e-05</v>
+        <v>-4.5257485045778354e-05</v>
       </c>
       <c r="Y24">
-        <v>0.0097744381883295758</v>
+        <v>0.0098305369894430283</v>
       </c>
     </row>
   </sheetData>
@@ -2241,76 +2241,76 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>-1.5460064491678762</v>
+        <v>-1.5534078702640852</v>
       </c>
       <c r="C2">
-        <v>0.00074185927597689031</v>
+        <v>0.00074299281200900804</v>
       </c>
       <c r="D2">
-        <v>7.1127309180528319e-05</v>
+        <v>7.1509299021764512e-05</v>
       </c>
       <c r="E2">
-        <v>3.8262834476235461e-05</v>
+        <v>3.829410605252206e-05</v>
       </c>
       <c r="F2">
-        <v>-3.6678866170883542e-07</v>
+        <v>-3.6729315963095582e-07</v>
       </c>
       <c r="G2">
-        <v>1.2316807841300401e-05</v>
+        <v>1.2418137528721418e-05</v>
       </c>
       <c r="H2">
-        <v>0.00014361884622716918</v>
+        <v>0.00014380774018393099</v>
       </c>
       <c r="I2">
-        <v>-3.3654529133260882e-07</v>
+        <v>-3.4090383550529796e-07</v>
       </c>
       <c r="J2">
-        <v>-2.7787692507174424e-06</v>
+        <v>-2.7854505337700108e-06</v>
       </c>
       <c r="K2">
-        <v>2.9299995597658994e-05</v>
+        <v>3.0073559366418488e-05</v>
       </c>
       <c r="L2">
-        <v>-3.0593206335037479e-05</v>
+        <v>-3.1425980612539153e-05</v>
       </c>
       <c r="M2">
-        <v>8.1451424063230457e-07</v>
+        <v>9.0358333396242056e-07</v>
       </c>
       <c r="N2">
-        <v>5.2516755494281457e-06</v>
+        <v>5.304675852491514e-06</v>
       </c>
       <c r="O2">
-        <v>1.3574403627642298e-05</v>
+        <v>1.3609147092019972e-05</v>
       </c>
       <c r="P2">
-        <v>1.0409829902196513e-05</v>
+        <v>1.0501868568789808e-05</v>
       </c>
       <c r="Q2">
-        <v>4.7139542634746805e-06</v>
+        <v>4.8596498173291322e-06</v>
       </c>
       <c r="R2">
-        <v>1.475789271907036e-06</v>
+        <v>1.5557591121329328e-06</v>
       </c>
       <c r="S2">
-        <v>5.0773710577164088e-06</v>
+        <v>5.173650996695142e-06</v>
       </c>
       <c r="T2">
-        <v>5.0413155862304047e-06</v>
+        <v>5.0338164339660409e-06</v>
       </c>
       <c r="U2">
-        <v>-5.5285281196880353e-07</v>
+        <v>-5.0655196481250468e-07</v>
       </c>
       <c r="V2">
-        <v>2.8447485046941679e-07</v>
+        <v>4.8471676014940943e-07</v>
       </c>
       <c r="W2">
-        <v>9.8708634542819802e-06</v>
+        <v>9.9270873030602194e-06</v>
       </c>
       <c r="X2">
-        <v>5.8212419359163504e-07</v>
+        <v>4.4099699277390498e-07</v>
       </c>
       <c r="Y2">
-        <v>-0.0010091629345850475</v>
+        <v>-0.0010096918967565623</v>
       </c>
     </row>
     <row r="3">
@@ -2318,76 +2318,76 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>-2.0631663802872913</v>
+        <v>-2.0623003957644182</v>
       </c>
       <c r="C3">
-        <v>7.1127309180528319e-05</v>
+        <v>7.1509299021764512e-05</v>
       </c>
       <c r="D3">
-        <v>0.00014736760412597174</v>
+        <v>0.00014717730269502973</v>
       </c>
       <c r="E3">
-        <v>5.2247219769474625e-06</v>
+        <v>5.2713806292258596e-06</v>
       </c>
       <c r="F3">
-        <v>-5.5171957437349748e-08</v>
+        <v>-5.5540594453561954e-08</v>
       </c>
       <c r="G3">
-        <v>1.2304378202020726e-05</v>
+        <v>1.2541861679921589e-05</v>
       </c>
       <c r="H3">
-        <v>-4.7313988346049695e-06</v>
+        <v>-4.5039046464542548e-06</v>
       </c>
       <c r="I3">
-        <v>-4.8536132895246721e-07</v>
+        <v>-4.9120740538597431e-07</v>
       </c>
       <c r="J3">
-        <v>-3.6189512696978139e-07</v>
+        <v>-3.6783598553024198e-07</v>
       </c>
       <c r="K3">
-        <v>1.3554640395691092e-05</v>
+        <v>1.3680431048328541e-05</v>
       </c>
       <c r="L3">
-        <v>3.0899032643850771e-06</v>
+        <v>2.915837037720206e-06</v>
       </c>
       <c r="M3">
-        <v>6.1584748857115287e-06</v>
+        <v>5.8506298839506958e-06</v>
       </c>
       <c r="N3">
-        <v>8.7362210170806128e-06</v>
+        <v>8.6358777854924327e-06</v>
       </c>
       <c r="O3">
-        <v>1.6296170461959572e-05</v>
+        <v>1.6291491836058057e-05</v>
       </c>
       <c r="P3">
-        <v>2.0649284692382934e-05</v>
+        <v>2.0701605388371849e-05</v>
       </c>
       <c r="Q3">
-        <v>5.6289877470251649e-06</v>
+        <v>5.6244933470996151e-06</v>
       </c>
       <c r="R3">
-        <v>4.9529091190151011e-06</v>
+        <v>4.9341332014652764e-06</v>
       </c>
       <c r="S3">
-        <v>3.7391885805211703e-06</v>
+        <v>3.9216878895765623e-06</v>
       </c>
       <c r="T3">
-        <v>2.8678310875438164e-06</v>
+        <v>2.8421775099493309e-06</v>
       </c>
       <c r="U3">
-        <v>-3.6402324597503306e-06</v>
+        <v>-3.5491157806904594e-06</v>
       </c>
       <c r="V3">
-        <v>-7.5315705023342392e-06</v>
+        <v>-7.4325632025394498e-06</v>
       </c>
       <c r="W3">
-        <v>6.7521108945201596e-06</v>
+        <v>6.646686904458306e-06</v>
       </c>
       <c r="X3">
-        <v>6.5766276111471332e-06</v>
+        <v>6.5175322309821035e-06</v>
       </c>
       <c r="Y3">
-        <v>-0.00017795279878205056</v>
+        <v>-0.00017929425668358154</v>
       </c>
     </row>
     <row r="4">
@@ -2395,76 +2395,76 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>0.16261647740890892</v>
+        <v>0.16221023744435242</v>
       </c>
       <c r="C4">
-        <v>3.8262834476235461e-05</v>
+        <v>3.829410605252206e-05</v>
       </c>
       <c r="D4">
-        <v>5.2247219769474625e-06</v>
+        <v>5.2713806292258596e-06</v>
       </c>
       <c r="E4">
-        <v>1.0207595034967712e-05</v>
+        <v>1.0205024929216828e-05</v>
       </c>
       <c r="F4">
-        <v>-1.0295275784698111e-07</v>
+        <v>-1.0296419129764437e-07</v>
       </c>
       <c r="G4">
-        <v>4.2941379733458038e-05</v>
+        <v>4.2880716078150277e-05</v>
       </c>
       <c r="H4">
-        <v>4.7396015767334004e-05</v>
+        <v>4.7453876322145411e-05</v>
       </c>
       <c r="I4">
-        <v>-8.9389413889426779e-07</v>
+        <v>-8.9265369237292435e-07</v>
       </c>
       <c r="J4">
-        <v>-9.5176883071592331e-07</v>
+        <v>-9.527002654562902e-07</v>
       </c>
       <c r="K4">
-        <v>-4.6891523105274465e-06</v>
+        <v>-4.5463633883475079e-06</v>
       </c>
       <c r="L4">
-        <v>-1.1340096863135722e-05</v>
+        <v>-1.1422854171567873e-05</v>
       </c>
       <c r="M4">
-        <v>1.7972441888854037e-06</v>
+        <v>1.8347123579713675e-06</v>
       </c>
       <c r="N4">
-        <v>3.9677836071922204e-06</v>
+        <v>3.9853470569118922e-06</v>
       </c>
       <c r="O4">
-        <v>5.9906863780168437e-06</v>
+        <v>5.982381435820698e-06</v>
       </c>
       <c r="P4">
-        <v>1.1405668610090365e-05</v>
+        <v>1.1378697897718211e-05</v>
       </c>
       <c r="Q4">
-        <v>1.1376983638802547e-06</v>
+        <v>1.145925561760928e-06</v>
       </c>
       <c r="R4">
-        <v>1.3520636707573905e-07</v>
+        <v>1.2727996522658692e-07</v>
       </c>
       <c r="S4">
-        <v>3.856358699013978e-07</v>
+        <v>3.6958613459211639e-07</v>
       </c>
       <c r="T4">
-        <v>1.0623117599141848e-06</v>
+        <v>1.0558088071830358e-06</v>
       </c>
       <c r="U4">
-        <v>-3.9097935948372816e-07</v>
+        <v>-4.0571523860573422e-07</v>
       </c>
       <c r="V4">
-        <v>-1.7237746172763759e-06</v>
+        <v>-1.6900262467597306e-06</v>
       </c>
       <c r="W4">
-        <v>5.2972168521386966e-07</v>
+        <v>5.5575161389209792e-07</v>
       </c>
       <c r="X4">
-        <v>2.81561731566845e-07</v>
+        <v>2.6983948173981394e-07</v>
       </c>
       <c r="Y4">
-        <v>-0.00023829272713437683</v>
+        <v>-0.0002381866332478734</v>
       </c>
     </row>
     <row r="5">
@@ -2472,76 +2472,76 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>-0.0020783381670518601</v>
+        <v>-0.0020741615408410366</v>
       </c>
       <c r="C5">
-        <v>-3.6678866170883542e-07</v>
+        <v>-3.6729315963095582e-07</v>
       </c>
       <c r="D5">
-        <v>-5.5171957437349748e-08</v>
+        <v>-5.5540594453561954e-08</v>
       </c>
       <c r="E5">
-        <v>-1.0295275784698111e-07</v>
+        <v>-1.0296419129764437e-07</v>
       </c>
       <c r="F5">
-        <v>1.1086094879298779e-09</v>
+        <v>1.1091009265611972e-09</v>
       </c>
       <c r="G5">
-        <v>-2.0853527006566698e-07</v>
+        <v>-2.082665443778523e-07</v>
       </c>
       <c r="H5">
-        <v>-2.4801098632227966e-07</v>
+        <v>-2.492734603316852e-07</v>
       </c>
       <c r="I5">
-        <v>4.1153924732624663e-09</v>
+        <v>4.109595654756675e-09</v>
       </c>
       <c r="J5">
-        <v>4.5961776018602967e-09</v>
+        <v>4.6183132419541624e-09</v>
       </c>
       <c r="K5">
-        <v>8.1772473813449551e-09</v>
+        <v>6.4050313227444246e-09</v>
       </c>
       <c r="L5">
-        <v>1.4277629272208715e-07</v>
+        <v>1.4393957014288687e-07</v>
       </c>
       <c r="M5">
-        <v>-2.0742673358443559e-08</v>
+        <v>-2.114363120143479e-08</v>
       </c>
       <c r="N5">
-        <v>-4.4417070425668185e-08</v>
+        <v>-4.46075467954602e-08</v>
       </c>
       <c r="O5">
-        <v>-5.7511358333741033e-08</v>
+        <v>-5.7405270481852933e-08</v>
       </c>
       <c r="P5">
-        <v>-9.9584726958435395e-08</v>
+        <v>-9.930328057319226e-08</v>
       </c>
       <c r="Q5">
-        <v>-1.3023512750519646e-08</v>
+        <v>-1.3067820517723416e-08</v>
       </c>
       <c r="R5">
-        <v>-2.1917872757918884e-09</v>
+        <v>-2.0422671921531978e-09</v>
       </c>
       <c r="S5">
-        <v>-2.2879595987887436e-09</v>
+        <v>-2.1232571263531069e-09</v>
       </c>
       <c r="T5">
-        <v>-1.135626081217945e-08</v>
+        <v>-1.135151967988023e-08</v>
       </c>
       <c r="U5">
-        <v>6.7051813669920668e-09</v>
+        <v>6.8156652398992608e-09</v>
       </c>
       <c r="V5">
-        <v>2.0539560819921629e-08</v>
+        <v>2.0034526493199685e-08</v>
       </c>
       <c r="W5">
-        <v>-6.811222601876056e-09</v>
+        <v>-7.1273582057857486e-09</v>
       </c>
       <c r="X5">
-        <v>-7.3035174080840374e-09</v>
+        <v>-7.2580327824294464e-09</v>
       </c>
       <c r="Y5">
-        <v>2.2520893764479928e-06</v>
+        <v>2.251931959082401e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2549,76 +2549,76 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>-0.40445329507655498</v>
+        <v>-0.40220489251481556</v>
       </c>
       <c r="C6">
-        <v>1.2316807841300401e-05</v>
+        <v>1.2418137528721418e-05</v>
       </c>
       <c r="D6">
-        <v>1.2304378202020726e-05</v>
+        <v>1.2541861679921589e-05</v>
       </c>
       <c r="E6">
-        <v>4.2941379733458038e-05</v>
+        <v>4.2880716078150277e-05</v>
       </c>
       <c r="F6">
-        <v>-2.0853527006566698e-07</v>
+        <v>-2.082665443778523e-07</v>
       </c>
       <c r="G6">
-        <v>0.0024676833570865804</v>
+        <v>0.0024671765144578897</v>
       </c>
       <c r="H6">
-        <v>0.0012416490308238912</v>
+        <v>0.0012403416897076947</v>
       </c>
       <c r="I6">
-        <v>-5.004752773841493e-05</v>
+        <v>-5.0040523911062593e-05</v>
       </c>
       <c r="J6">
-        <v>-2.4903501124605532e-05</v>
+        <v>-2.4882351054204576e-05</v>
       </c>
       <c r="K6">
-        <v>3.0675842468176357e-06</v>
+        <v>3.7111647851789431e-06</v>
       </c>
       <c r="L6">
-        <v>-3.2808599970423157e-05</v>
+        <v>-3.3132854098288399e-05</v>
       </c>
       <c r="M6">
-        <v>6.2998570857282109e-06</v>
+        <v>6.4503114908645359e-06</v>
       </c>
       <c r="N6">
-        <v>1.1616314376034311e-05</v>
+        <v>1.1738380092110525e-05</v>
       </c>
       <c r="O6">
-        <v>1.0634478621029562e-05</v>
+        <v>1.0626025525528105e-05</v>
       </c>
       <c r="P6">
-        <v>2.3313705154268485e-05</v>
+        <v>2.3416132947670187e-05</v>
       </c>
       <c r="Q6">
-        <v>1.033380214884674e-05</v>
+        <v>1.0472263580282824e-05</v>
       </c>
       <c r="R6">
-        <v>-1.5983658163690932e-06</v>
+        <v>-1.2839996300519261e-06</v>
       </c>
       <c r="S6">
-        <v>3.2841584103402222e-06</v>
+        <v>3.1537870993364678e-06</v>
       </c>
       <c r="T6">
-        <v>1.2198167281873962e-06</v>
+        <v>1.0070443971852951e-06</v>
       </c>
       <c r="U6">
-        <v>-7.1341812363080214e-06</v>
+        <v>-7.3984096013794654e-06</v>
       </c>
       <c r="V6">
-        <v>-1.6149463471300828e-05</v>
+        <v>-1.6598194895405799e-05</v>
       </c>
       <c r="W6">
-        <v>3.5164232718433765e-06</v>
+        <v>3.385973094613812e-06</v>
       </c>
       <c r="X6">
-        <v>6.1814706224520246e-06</v>
+        <v>6.1850035599557911e-06</v>
       </c>
       <c r="Y6">
-        <v>-0.0015973748514898495</v>
+        <v>-0.0015950522206416482</v>
       </c>
     </row>
     <row r="7">
@@ -2626,76 +2626,76 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-0.55952293906001582</v>
+        <v>-0.55276296341428344</v>
       </c>
       <c r="C7">
-        <v>0.00014361884622716918</v>
+        <v>0.00014380774018393099</v>
       </c>
       <c r="D7">
-        <v>-4.7313988346049695e-06</v>
+        <v>-4.5039046464542548e-06</v>
       </c>
       <c r="E7">
-        <v>4.7396015767334004e-05</v>
+        <v>4.7453876322145411e-05</v>
       </c>
       <c r="F7">
-        <v>-2.4801098632227966e-07</v>
+        <v>-2.492734603316852e-07</v>
       </c>
       <c r="G7">
-        <v>0.0012416490308238912</v>
+        <v>0.0012403416897076947</v>
       </c>
       <c r="H7">
-        <v>0.0020375968091834659</v>
+        <v>0.0020366372077641063</v>
       </c>
       <c r="I7">
-        <v>-2.4931311946448055e-05</v>
+        <v>-2.4913028405153921e-05</v>
       </c>
       <c r="J7">
-        <v>-4.0423737980276256e-05</v>
+        <v>-4.0410551376822449e-05</v>
       </c>
       <c r="K7">
-        <v>2.187496206123607e-05</v>
+        <v>2.3559610593069953e-05</v>
       </c>
       <c r="L7">
-        <v>-9.3552762080917795e-05</v>
+        <v>-9.507586028544105e-05</v>
       </c>
       <c r="M7">
-        <v>6.595168468449342e-06</v>
+        <v>7.104964804731731e-06</v>
       </c>
       <c r="N7">
-        <v>9.7102020257150727e-06</v>
+        <v>1.0081337915602618e-05</v>
       </c>
       <c r="O7">
-        <v>8.9704729425338402e-06</v>
+        <v>9.0576149775718285e-06</v>
       </c>
       <c r="P7">
-        <v>3.8080107364049523e-05</v>
+        <v>3.8184168885640958e-05</v>
       </c>
       <c r="Q7">
-        <v>1.3755952924265165e-05</v>
+        <v>1.4144223330877058e-05</v>
       </c>
       <c r="R7">
-        <v>6.0822533613291908e-06</v>
+        <v>6.4050279178905578e-06</v>
       </c>
       <c r="S7">
-        <v>-9.8248169219184643e-06</v>
+        <v>-9.8226709645208974e-06</v>
       </c>
       <c r="T7">
-        <v>-6.5845070314333895e-06</v>
+        <v>-6.5677653578270621e-06</v>
       </c>
       <c r="U7">
-        <v>-2.6950809347737109e-05</v>
+        <v>-2.7071114036435235e-05</v>
       </c>
       <c r="V7">
-        <v>-1.6774356798898917e-05</v>
+        <v>-1.6717414056993305e-05</v>
       </c>
       <c r="W7">
-        <v>1.3440128479261074e-05</v>
+        <v>1.3414268690361624e-05</v>
       </c>
       <c r="X7">
-        <v>8.0929138313141475e-06</v>
+        <v>7.7783317021278509e-06</v>
       </c>
       <c r="Y7">
-        <v>-0.0017070767879386211</v>
+        <v>-0.0017069303726679895</v>
       </c>
     </row>
     <row r="8">
@@ -2703,76 +2703,76 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.0078531881034314167</v>
+        <v>0.0078688102801000703</v>
       </c>
       <c r="C8">
-        <v>-3.3654529133260882e-07</v>
+        <v>-3.4090383550529796e-07</v>
       </c>
       <c r="D8">
-        <v>-4.8536132895246721e-07</v>
+        <v>-4.9120740538597431e-07</v>
       </c>
       <c r="E8">
-        <v>-8.9389413889426779e-07</v>
+        <v>-8.9265369237292435e-07</v>
       </c>
       <c r="F8">
-        <v>4.1153924732624663e-09</v>
+        <v>4.109595654756675e-09</v>
       </c>
       <c r="G8">
-        <v>-5.004752773841493e-05</v>
+        <v>-5.0040523911062593e-05</v>
       </c>
       <c r="H8">
-        <v>-2.4931311946448055e-05</v>
+        <v>-2.4913028405153921e-05</v>
       </c>
       <c r="I8">
-        <v>1.1118684232665928e-06</v>
+        <v>1.1116271889412432e-06</v>
       </c>
       <c r="J8">
-        <v>5.4216338944754081e-07</v>
+        <v>5.4179375918135935e-07</v>
       </c>
       <c r="K8">
-        <v>-1.4959815778763455e-07</v>
+        <v>-1.6434594043021074e-07</v>
       </c>
       <c r="L8">
-        <v>7.7595637113846023e-07</v>
+        <v>7.8573586604683354e-07</v>
       </c>
       <c r="M8">
-        <v>-2.1086753819495792e-07</v>
+        <v>-2.1393062230282454e-07</v>
       </c>
       <c r="N8">
-        <v>-2.9243053409817955e-07</v>
+        <v>-2.9420249312123849e-07</v>
       </c>
       <c r="O8">
-        <v>-7.754482250792062e-08</v>
+        <v>-7.6760336787353502e-08</v>
       </c>
       <c r="P8">
-        <v>-2.4438220384864619e-07</v>
+        <v>-2.4509288200584686e-07</v>
       </c>
       <c r="Q8">
-        <v>-1.7597343318703924e-07</v>
+        <v>-1.7956939589844593e-07</v>
       </c>
       <c r="R8">
-        <v>2.0023807243427352e-07</v>
+        <v>1.9422425840396567e-07</v>
       </c>
       <c r="S8">
-        <v>-1.4347763511109743e-07</v>
+        <v>-1.4032025952341667e-07</v>
       </c>
       <c r="T8">
-        <v>-7.8919752797592873e-08</v>
+        <v>-7.4107303190926498e-08</v>
       </c>
       <c r="U8">
-        <v>6.7134884473391549e-08</v>
+        <v>7.2659859772372322e-08</v>
       </c>
       <c r="V8">
-        <v>2.489725370848461e-07</v>
+        <v>2.5646588833028497e-07</v>
       </c>
       <c r="W8">
-        <v>-8.9457257439142707e-08</v>
+        <v>-8.6640295740320201e-08</v>
       </c>
       <c r="X8">
-        <v>-9.0324261697324879e-08</v>
+        <v>-9.1018842172097784e-08</v>
       </c>
       <c r="Y8">
-        <v>3.1810528837995031e-05</v>
+        <v>3.1768759411703956e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2780,76 +2780,76 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>0.0080208465668391727</v>
+        <v>0.0079623083111143335</v>
       </c>
       <c r="C9">
-        <v>-2.7787692507174424e-06</v>
+        <v>-2.7854505337700108e-06</v>
       </c>
       <c r="D9">
-        <v>-3.6189512696978139e-07</v>
+        <v>-3.6783598553024198e-07</v>
       </c>
       <c r="E9">
-        <v>-9.5176883071592331e-07</v>
+        <v>-9.527002654562902e-07</v>
       </c>
       <c r="F9">
-        <v>4.5961776018602967e-09</v>
+        <v>4.6183132419541624e-09</v>
       </c>
       <c r="G9">
-        <v>-2.4903501124605532e-05</v>
+        <v>-2.4882351054204576e-05</v>
       </c>
       <c r="H9">
-        <v>-4.0423737980276256e-05</v>
+        <v>-4.0410551376822449e-05</v>
       </c>
       <c r="I9">
-        <v>5.4216338944754081e-07</v>
+        <v>5.4179375918135935e-07</v>
       </c>
       <c r="J9">
-        <v>8.7344236838964641e-07</v>
+        <v>8.7318763936535476e-07</v>
       </c>
       <c r="K9">
-        <v>-5.5213885212638789e-07</v>
+        <v>-5.8638107983484074e-07</v>
       </c>
       <c r="L9">
-        <v>1.9192673242762582e-06</v>
+        <v>1.9514786861180271e-06</v>
       </c>
       <c r="M9">
-        <v>-1.8240829761097256e-07</v>
+        <v>-1.9154714388804311e-07</v>
       </c>
       <c r="N9">
-        <v>-1.3375345390145304e-07</v>
+        <v>-1.4048204897765968e-07</v>
       </c>
       <c r="O9">
-        <v>2.3673839023044497e-07</v>
+        <v>2.360727800060098e-07</v>
       </c>
       <c r="P9">
-        <v>-1.5338639367471443e-07</v>
+        <v>-1.5377998466341689e-07</v>
       </c>
       <c r="Q9">
-        <v>-1.0494553494808636e-07</v>
+        <v>-1.119981419246582e-07</v>
       </c>
       <c r="R9">
-        <v>2.8374691822122306e-07</v>
+        <v>2.773163004222667e-07</v>
       </c>
       <c r="S9">
-        <v>-1.0341255561561333e-07</v>
+        <v>-1.0255076431256754e-07</v>
       </c>
       <c r="T9">
-        <v>1.7205688342084376e-07</v>
+        <v>1.7210339360454175e-07</v>
       </c>
       <c r="U9">
-        <v>2.9814959143307689e-07</v>
+        <v>3.0079454138238682e-07</v>
       </c>
       <c r="V9">
-        <v>2.8503368931597679e-07</v>
+        <v>2.8320493425306157e-07</v>
       </c>
       <c r="W9">
-        <v>-2.3589796548736957e-07</v>
+        <v>-2.3479635954616842e-07</v>
       </c>
       <c r="X9">
-        <v>-5.2446991717774343e-08</v>
+        <v>-4.7106878851704288e-08</v>
       </c>
       <c r="Y9">
-        <v>3.3037982872207643e-05</v>
+        <v>3.303608122063139e-05</v>
       </c>
     </row>
     <row r="10">
@@ -2857,76 +2857,76 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>0.20605154236790166</v>
+        <v>0.20400872860889585</v>
       </c>
       <c r="C10">
-        <v>2.9299995597658994e-05</v>
+        <v>3.0073559366418488e-05</v>
       </c>
       <c r="D10">
-        <v>1.3554640395691092e-05</v>
+        <v>1.3680431048328541e-05</v>
       </c>
       <c r="E10">
-        <v>-4.6891523105274465e-06</v>
+        <v>-4.5463633883475079e-06</v>
       </c>
       <c r="F10">
-        <v>8.1772473813449551e-09</v>
+        <v>6.4050313227444246e-09</v>
       </c>
       <c r="G10">
-        <v>3.0675842468176357e-06</v>
+        <v>3.7111647851789431e-06</v>
       </c>
       <c r="H10">
-        <v>2.187496206123607e-05</v>
+        <v>2.3559610593069953e-05</v>
       </c>
       <c r="I10">
-        <v>-1.4959815778763455e-07</v>
+        <v>-1.6434594043021074e-07</v>
       </c>
       <c r="J10">
-        <v>-5.5213885212638789e-07</v>
+        <v>-5.8638107983484074e-07</v>
       </c>
       <c r="K10">
-        <v>0.00023008369371460257</v>
+        <v>0.00023183106230684596</v>
       </c>
       <c r="L10">
-        <v>-0.00011035552383841623</v>
+        <v>-0.00011236933857346887</v>
       </c>
       <c r="M10">
-        <v>-7.0570154316241152e-06</v>
+        <v>-6.7687320124569774e-06</v>
       </c>
       <c r="N10">
-        <v>-8.1620334106983963e-06</v>
+        <v>-7.9793450399339677e-06</v>
       </c>
       <c r="O10">
-        <v>-1.135505270575036e-05</v>
+        <v>-1.1394022399580312e-05</v>
       </c>
       <c r="P10">
-        <v>-1.2200835958301007e-05</v>
+        <v>-1.2249450085433839e-05</v>
       </c>
       <c r="Q10">
-        <v>1.5913325136274265e-06</v>
+        <v>1.7135900488611677e-06</v>
       </c>
       <c r="R10">
-        <v>-3.9312042216032015e-06</v>
+        <v>-3.9160593753671144e-06</v>
       </c>
       <c r="S10">
-        <v>4.8638431624895905e-07</v>
+        <v>5.0390345740298027e-07</v>
       </c>
       <c r="T10">
-        <v>-2.4263538692595373e-06</v>
+        <v>-2.2390089323472749e-06</v>
       </c>
       <c r="U10">
-        <v>-4.0107813510467981e-06</v>
+        <v>-3.9378479098398279e-06</v>
       </c>
       <c r="V10">
-        <v>2.8524696327124353e-06</v>
+        <v>3.2703868080553761e-06</v>
       </c>
       <c r="W10">
-        <v>2.7034192129034835e-06</v>
+        <v>2.7999535241356691e-06</v>
       </c>
       <c r="X10">
-        <v>8.1932214358755726e-06</v>
+        <v>8.2945220073543603e-06</v>
       </c>
       <c r="Y10">
-        <v>0.0001003666649968226</v>
+        <v>9.7567365737442701e-05</v>
       </c>
     </row>
     <row r="11">
@@ -2934,76 +2934,76 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>-0.071142389713377746</v>
+        <v>-0.069441015036014062</v>
       </c>
       <c r="C11">
-        <v>-3.0593206335037479e-05</v>
+        <v>-3.1425980612539153e-05</v>
       </c>
       <c r="D11">
-        <v>3.0899032643850771e-06</v>
+        <v>2.915837037720206e-06</v>
       </c>
       <c r="E11">
-        <v>-1.1340096863135722e-05</v>
+        <v>-1.1422854171567873e-05</v>
       </c>
       <c r="F11">
-        <v>1.4277629272208715e-07</v>
+        <v>1.4393957014288687e-07</v>
       </c>
       <c r="G11">
-        <v>-3.2808599970423157e-05</v>
+        <v>-3.3132854098288399e-05</v>
       </c>
       <c r="H11">
-        <v>-9.3552762080917795e-05</v>
+        <v>-9.507586028544105e-05</v>
       </c>
       <c r="I11">
-        <v>7.7595637113846023e-07</v>
+        <v>7.8573586604683354e-07</v>
       </c>
       <c r="J11">
-        <v>1.9192673242762582e-06</v>
+        <v>1.9514786861180271e-06</v>
       </c>
       <c r="K11">
-        <v>-0.00011035552383841623</v>
+        <v>-0.00011236933857346887</v>
       </c>
       <c r="L11">
-        <v>0.00021361871890326719</v>
+        <v>0.00021410050938308205</v>
       </c>
       <c r="M11">
-        <v>-4.6401978890251903e-07</v>
+        <v>-9.8233133115692656e-07</v>
       </c>
       <c r="N11">
-        <v>-5.2916737142418794e-06</v>
+        <v>-5.5884174669560793e-06</v>
       </c>
       <c r="O11">
-        <v>-9.897401144103683e-06</v>
+        <v>-9.7594706270910626e-06</v>
       </c>
       <c r="P11">
-        <v>-1.1154289291371927e-05</v>
+        <v>-1.1043881660563278e-05</v>
       </c>
       <c r="Q11">
-        <v>-6.4484341091051955e-06</v>
+        <v>-6.5571675115234232e-06</v>
       </c>
       <c r="R11">
-        <v>-3.4091826417708757e-06</v>
+        <v>-3.2537940630825466e-06</v>
       </c>
       <c r="S11">
-        <v>-2.4618847921282577e-06</v>
+        <v>-2.3295278497693406e-06</v>
       </c>
       <c r="T11">
-        <v>-4.6965827888657116e-06</v>
+        <v>-4.8624293556948119e-06</v>
       </c>
       <c r="U11">
-        <v>-5.4452538270770068e-06</v>
+        <v>-5.345183701464613e-06</v>
       </c>
       <c r="V11">
-        <v>4.3054478666509737e-06</v>
+        <v>3.5300602758547455e-06</v>
       </c>
       <c r="W11">
-        <v>-3.2083549705464349e-06</v>
+        <v>-3.4440484272296107e-06</v>
       </c>
       <c r="X11">
-        <v>-7.1832783393610755e-06</v>
+        <v>-7.2830993972605194e-06</v>
       </c>
       <c r="Y11">
-        <v>0.00020857984561314282</v>
+        <v>0.00021011173211139144</v>
       </c>
     </row>
     <row r="12">
@@ -3011,76 +3011,76 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>0.16627566388520262</v>
+        <v>0.16897892093543973</v>
       </c>
       <c r="C12">
-        <v>8.1451424063230457e-07</v>
+        <v>9.0358333396242056e-07</v>
       </c>
       <c r="D12">
-        <v>6.1584748857115287e-06</v>
+        <v>5.8506298839506958e-06</v>
       </c>
       <c r="E12">
-        <v>1.7972441888854037e-06</v>
+        <v>1.8347123579713675e-06</v>
       </c>
       <c r="F12">
-        <v>-2.0742673358443559e-08</v>
+        <v>-2.114363120143479e-08</v>
       </c>
       <c r="G12">
-        <v>6.2998570857282109e-06</v>
+        <v>6.4503114908645359e-06</v>
       </c>
       <c r="H12">
-        <v>6.595168468449342e-06</v>
+        <v>7.104964804731731e-06</v>
       </c>
       <c r="I12">
-        <v>-2.1086753819495792e-07</v>
+        <v>-2.1393062230282454e-07</v>
       </c>
       <c r="J12">
-        <v>-1.8240829761097256e-07</v>
+        <v>-1.9154714388804311e-07</v>
       </c>
       <c r="K12">
-        <v>-7.0570154316241152e-06</v>
+        <v>-6.7687320124569774e-06</v>
       </c>
       <c r="L12">
-        <v>-4.6401978890251903e-07</v>
+        <v>-9.8233133115692656e-07</v>
       </c>
       <c r="M12">
-        <v>0.0047403022034546195</v>
+        <v>0.0047363005330738201</v>
       </c>
       <c r="N12">
-        <v>0.0038930219198128249</v>
+        <v>0.0038906649226269009</v>
       </c>
       <c r="O12">
-        <v>0.0038916340266215701</v>
+        <v>0.0038892884571985493</v>
       </c>
       <c r="P12">
-        <v>0.00388982212086435</v>
+        <v>0.0038875099251143548</v>
       </c>
       <c r="Q12">
-        <v>9.8135710890202127e-06</v>
+        <v>9.7182225040282137e-06</v>
       </c>
       <c r="R12">
-        <v>5.4467675971230724e-06</v>
+        <v>5.4129285787436505e-06</v>
       </c>
       <c r="S12">
-        <v>-1.3079083319450394e-06</v>
+        <v>-1.3142335930263726e-06</v>
       </c>
       <c r="T12">
-        <v>2.9265692149753987e-06</v>
+        <v>2.8757250570624602e-06</v>
       </c>
       <c r="U12">
-        <v>7.136691153376414e-06</v>
+        <v>7.1397231396171031e-06</v>
       </c>
       <c r="V12">
-        <v>2.6182428855198913e-06</v>
+        <v>2.6040608889536327e-06</v>
       </c>
       <c r="W12">
-        <v>-1.3556909987937132e-06</v>
+        <v>-1.535190002280966e-06</v>
       </c>
       <c r="X12">
-        <v>-4.9414103891404907e-06</v>
+        <v>-4.94936854496475e-06</v>
       </c>
       <c r="Y12">
-        <v>-0.0039260031461625022</v>
+        <v>-0.0039243840081503887</v>
       </c>
     </row>
     <row r="13">
@@ -3088,76 +3088,76 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>0.61625138071883057</v>
+        <v>0.61695585711760448</v>
       </c>
       <c r="C13">
-        <v>5.2516755494281457e-06</v>
+        <v>5.304675852491514e-06</v>
       </c>
       <c r="D13">
-        <v>8.7362210170806128e-06</v>
+        <v>8.6358777854924327e-06</v>
       </c>
       <c r="E13">
-        <v>3.9677836071922204e-06</v>
+        <v>3.9853470569118922e-06</v>
       </c>
       <c r="F13">
-        <v>-4.4417070425668185e-08</v>
+        <v>-4.46075467954602e-08</v>
       </c>
       <c r="G13">
-        <v>1.1616314376034311e-05</v>
+        <v>1.1738380092110525e-05</v>
       </c>
       <c r="H13">
-        <v>9.7102020257150727e-06</v>
+        <v>1.0081337915602618e-05</v>
       </c>
       <c r="I13">
-        <v>-2.9243053409817955e-07</v>
+        <v>-2.9420249312123849e-07</v>
       </c>
       <c r="J13">
-        <v>-1.3375345390145304e-07</v>
+        <v>-1.4048204897765968e-07</v>
       </c>
       <c r="K13">
-        <v>-8.1620334106983963e-06</v>
+        <v>-7.9793450399339677e-06</v>
       </c>
       <c r="L13">
-        <v>-5.2916737142418794e-06</v>
+        <v>-5.5884174669560793e-06</v>
       </c>
       <c r="M13">
-        <v>0.0038930219198128249</v>
+        <v>0.0038906649226269009</v>
       </c>
       <c r="N13">
-        <v>0.0040531068044618156</v>
+        <v>0.0040506618713113188</v>
       </c>
       <c r="O13">
-        <v>0.003894609859351444</v>
+        <v>0.0038922661048355202</v>
       </c>
       <c r="P13">
-        <v>0.0038948225549202192</v>
+        <v>0.0038924884649776097</v>
       </c>
       <c r="Q13">
-        <v>4.4224526467484451e-06</v>
+        <v>4.3707923411174409e-06</v>
       </c>
       <c r="R13">
-        <v>-3.0855684194046595e-06</v>
+        <v>-3.1155670316236541e-06</v>
       </c>
       <c r="S13">
-        <v>-1.0996434993788847e-05</v>
+        <v>-1.1011043810274453e-05</v>
       </c>
       <c r="T13">
-        <v>-4.0316322069063894e-06</v>
+        <v>-4.0352095146620328e-06</v>
       </c>
       <c r="U13">
-        <v>-3.130433976287556e-06</v>
+        <v>-3.1427702880073069e-06</v>
       </c>
       <c r="V13">
-        <v>-8.8040636403090522e-06</v>
+        <v>-8.8084823902473771e-06</v>
       </c>
       <c r="W13">
-        <v>-2.9113400901915666e-06</v>
+        <v>-2.9017279506888178e-06</v>
       </c>
       <c r="X13">
-        <v>-6.5313501605727725e-06</v>
+        <v>-6.5256966257938215e-06</v>
       </c>
       <c r="Y13">
-        <v>-0.0039684595616753726</v>
+        <v>-0.0039664828139294077</v>
       </c>
     </row>
     <row r="14">
@@ -3165,76 +3165,76 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0.85196728271191591</v>
+        <v>0.85082650624819989</v>
       </c>
       <c r="C14">
-        <v>1.3574403627642298e-05</v>
+        <v>1.3609147092019972e-05</v>
       </c>
       <c r="D14">
-        <v>1.6296170461959572e-05</v>
+        <v>1.6291491836058057e-05</v>
       </c>
       <c r="E14">
-        <v>5.9906863780168437e-06</v>
+        <v>5.982381435820698e-06</v>
       </c>
       <c r="F14">
-        <v>-5.7511358333741033e-08</v>
+        <v>-5.7405270481852933e-08</v>
       </c>
       <c r="G14">
-        <v>1.0634478621029562e-05</v>
+        <v>1.0626025525528105e-05</v>
       </c>
       <c r="H14">
-        <v>8.9704729425338402e-06</v>
+        <v>9.0576149775718285e-06</v>
       </c>
       <c r="I14">
-        <v>-7.754482250792062e-08</v>
+        <v>-7.6760336787353502e-08</v>
       </c>
       <c r="J14">
-        <v>2.3673839023044497e-07</v>
+        <v>2.360727800060098e-07</v>
       </c>
       <c r="K14">
-        <v>-1.135505270575036e-05</v>
+        <v>-1.1394022399580312e-05</v>
       </c>
       <c r="L14">
-        <v>-9.897401144103683e-06</v>
+        <v>-9.7594706270910626e-06</v>
       </c>
       <c r="M14">
-        <v>0.0038916340266215701</v>
+        <v>0.0038892884571985493</v>
       </c>
       <c r="N14">
-        <v>0.003894609859351444</v>
+        <v>0.0038922661048355202</v>
       </c>
       <c r="O14">
-        <v>0.0039514114708592493</v>
+        <v>0.0039489938894343348</v>
       </c>
       <c r="P14">
-        <v>0.0039142311181402717</v>
+        <v>0.0039118671553177199</v>
       </c>
       <c r="Q14">
-        <v>1.4373122825228862e-06</v>
+        <v>1.3234422522517207e-06</v>
       </c>
       <c r="R14">
-        <v>-6.7394280491303658e-06</v>
+        <v>-6.7820837061591412e-06</v>
       </c>
       <c r="S14">
-        <v>-1.463974879293817e-05</v>
+        <v>-1.4667035369595016e-05</v>
       </c>
       <c r="T14">
-        <v>-4.8628611382178034e-06</v>
+        <v>-4.8850992364449534e-06</v>
       </c>
       <c r="U14">
-        <v>-5.2237151995880842e-06</v>
+        <v>-5.2557936165260552e-06</v>
       </c>
       <c r="V14">
-        <v>-1.8005579362521338e-06</v>
+        <v>-1.7988827677729689e-06</v>
       </c>
       <c r="W14">
-        <v>-4.4401585189376866e-06</v>
+        <v>-4.4117503053185965e-06</v>
       </c>
       <c r="X14">
-        <v>-3.9346942739277752e-06</v>
+        <v>-3.9159099235375396e-06</v>
       </c>
       <c r="Y14">
-        <v>-0.0040473251642220553</v>
+        <v>-0.0040448240361537387</v>
       </c>
     </row>
     <row r="15">
@@ -3242,76 +3242,76 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>0.87867284981098215</v>
+        <v>0.87629923681296884</v>
       </c>
       <c r="C15">
-        <v>1.0409829902196513e-05</v>
+        <v>1.0501868568789808e-05</v>
       </c>
       <c r="D15">
-        <v>2.0649284692382934e-05</v>
+        <v>2.0701605388371849e-05</v>
       </c>
       <c r="E15">
-        <v>1.1405668610090365e-05</v>
+        <v>1.1378697897718211e-05</v>
       </c>
       <c r="F15">
-        <v>-9.9584726958435395e-08</v>
+        <v>-9.930328057319226e-08</v>
       </c>
       <c r="G15">
-        <v>2.3313705154268485e-05</v>
+        <v>2.3416132947670187e-05</v>
       </c>
       <c r="H15">
-        <v>3.8080107364049523e-05</v>
+        <v>3.8184168885640958e-05</v>
       </c>
       <c r="I15">
-        <v>-2.4438220384864619e-07</v>
+        <v>-2.4509288200584686e-07</v>
       </c>
       <c r="J15">
-        <v>-1.5338639367471443e-07</v>
+        <v>-1.5377998466341689e-07</v>
       </c>
       <c r="K15">
-        <v>-1.2200835958301007e-05</v>
+        <v>-1.2249450085433839e-05</v>
       </c>
       <c r="L15">
-        <v>-1.1154289291371927e-05</v>
+        <v>-1.1043881660563278e-05</v>
       </c>
       <c r="M15">
-        <v>0.00388982212086435</v>
+        <v>0.0038875099251143548</v>
       </c>
       <c r="N15">
-        <v>0.0038948225549202192</v>
+        <v>0.0038924884649776097</v>
       </c>
       <c r="O15">
-        <v>0.0039142311181402717</v>
+        <v>0.0039118671553177199</v>
       </c>
       <c r="P15">
-        <v>0.0040976458269792373</v>
+        <v>0.0040948800455974828</v>
       </c>
       <c r="Q15">
-        <v>-2.74113629743431e-06</v>
+        <v>-2.735974630565266e-06</v>
       </c>
       <c r="R15">
-        <v>-1.369519334991702e-05</v>
+        <v>-1.370058119933159e-05</v>
       </c>
       <c r="S15">
-        <v>-1.6902907372494234e-05</v>
+        <v>-1.6940381433147692e-05</v>
       </c>
       <c r="T15">
-        <v>-1.5663377653003625e-05</v>
+        <v>-1.5643830281320719e-05</v>
       </c>
       <c r="U15">
-        <v>-1.4907747462991578e-05</v>
+        <v>-1.4880848994417933e-05</v>
       </c>
       <c r="V15">
-        <v>-1.1334228750512927e-05</v>
+        <v>-1.1235184689076597e-05</v>
       </c>
       <c r="W15">
-        <v>-8.9437289691714801e-06</v>
+        <v>-8.8476166284484315e-06</v>
       </c>
       <c r="X15">
-        <v>-5.8095064108495878e-06</v>
+        <v>-5.8181300615266672e-06</v>
       </c>
       <c r="Y15">
-        <v>-0.0042099395338169848</v>
+        <v>-0.0042070436081594054</v>
       </c>
     </row>
     <row r="16">
@@ -3319,76 +3319,76 @@
         <v>36</v>
       </c>
       <c r="B16">
-        <v>0.06523109340489297</v>
+        <v>0.063566978992011941</v>
       </c>
       <c r="C16">
-        <v>4.7139542634746805e-06</v>
+        <v>4.8596498173291322e-06</v>
       </c>
       <c r="D16">
-        <v>5.6289877470251649e-06</v>
+        <v>5.6244933470996151e-06</v>
       </c>
       <c r="E16">
-        <v>1.1376983638802547e-06</v>
+        <v>1.145925561760928e-06</v>
       </c>
       <c r="F16">
-        <v>-1.3023512750519646e-08</v>
+        <v>-1.3067820517723416e-08</v>
       </c>
       <c r="G16">
-        <v>1.033380214884674e-05</v>
+        <v>1.0472263580282824e-05</v>
       </c>
       <c r="H16">
-        <v>1.3755952924265165e-05</v>
+        <v>1.4144223330877058e-05</v>
       </c>
       <c r="I16">
-        <v>-1.7597343318703924e-07</v>
+        <v>-1.7956939589844593e-07</v>
       </c>
       <c r="J16">
-        <v>-1.0494553494808636e-07</v>
+        <v>-1.119981419246582e-07</v>
       </c>
       <c r="K16">
-        <v>1.5913325136274265e-06</v>
+        <v>1.7135900488611677e-06</v>
       </c>
       <c r="L16">
-        <v>-6.4484341091051955e-06</v>
+        <v>-6.5571675115234232e-06</v>
       </c>
       <c r="M16">
-        <v>9.8135710890202127e-06</v>
+        <v>9.7182225040282137e-06</v>
       </c>
       <c r="N16">
-        <v>4.4224526467484451e-06</v>
+        <v>4.3707923411174409e-06</v>
       </c>
       <c r="O16">
-        <v>1.4373122825228862e-06</v>
+        <v>1.3234422522517207e-06</v>
       </c>
       <c r="P16">
-        <v>-2.74113629743431e-06</v>
+        <v>-2.735974630565266e-06</v>
       </c>
       <c r="Q16">
-        <v>0.00042832217986366234</v>
+        <v>0.00042757130777282065</v>
       </c>
       <c r="R16">
-        <v>0.00022708055567406265</v>
+        <v>0.00022682579501686931</v>
       </c>
       <c r="S16">
-        <v>0.00022450465058317809</v>
+        <v>0.00022424653859322294</v>
       </c>
       <c r="T16">
-        <v>0.00022604538442442789</v>
+        <v>0.00022578900057727993</v>
       </c>
       <c r="U16">
-        <v>0.00022456941302367904</v>
+        <v>0.00022430238164636624</v>
       </c>
       <c r="V16">
-        <v>0.00022432489412153934</v>
+        <v>0.00022408729929085904</v>
       </c>
       <c r="W16">
-        <v>5.2792927337328599e-06</v>
+        <v>5.4340547670740986e-06</v>
       </c>
       <c r="X16">
-        <v>4.4121196453801455e-06</v>
+        <v>4.4249661319536601e-06</v>
       </c>
       <c r="Y16">
-        <v>-0.00025535226197773018</v>
+        <v>-0.00025534441360154322</v>
       </c>
     </row>
     <row r="17">
@@ -3396,76 +3396,76 @@
         <v>37</v>
       </c>
       <c r="B17">
-        <v>-0.0062842375936854817</v>
+        <v>-0.0076245418788843155</v>
       </c>
       <c r="C17">
-        <v>1.475789271907036e-06</v>
+        <v>1.5557591121329328e-06</v>
       </c>
       <c r="D17">
-        <v>4.9529091190151011e-06</v>
+        <v>4.9341332014652764e-06</v>
       </c>
       <c r="E17">
-        <v>1.3520636707573905e-07</v>
+        <v>1.2727996522658692e-07</v>
       </c>
       <c r="F17">
-        <v>-2.1917872757918884e-09</v>
+        <v>-2.0422671921531978e-09</v>
       </c>
       <c r="G17">
-        <v>-1.5983658163690932e-06</v>
+        <v>-1.2839996300519261e-06</v>
       </c>
       <c r="H17">
-        <v>6.0822533613291908e-06</v>
+        <v>6.4050279178905578e-06</v>
       </c>
       <c r="I17">
-        <v>2.0023807243427352e-07</v>
+        <v>1.9422425840396567e-07</v>
       </c>
       <c r="J17">
-        <v>2.8374691822122306e-07</v>
+        <v>2.773163004222667e-07</v>
       </c>
       <c r="K17">
-        <v>-3.9312042216032015e-06</v>
+        <v>-3.9160593753671144e-06</v>
       </c>
       <c r="L17">
-        <v>-3.4091826417708757e-06</v>
+        <v>-3.2537940630825466e-06</v>
       </c>
       <c r="M17">
-        <v>5.4467675971230724e-06</v>
+        <v>5.4129285787436505e-06</v>
       </c>
       <c r="N17">
-        <v>-3.0855684194046595e-06</v>
+        <v>-3.1155670316236541e-06</v>
       </c>
       <c r="O17">
-        <v>-6.7394280491303658e-06</v>
+        <v>-6.7820837061591412e-06</v>
       </c>
       <c r="P17">
-        <v>-1.369519334991702e-05</v>
+        <v>-1.370058119933159e-05</v>
       </c>
       <c r="Q17">
-        <v>0.00022708055567406265</v>
+        <v>0.00022682579501686931</v>
       </c>
       <c r="R17">
-        <v>0.00051200281380742239</v>
+        <v>0.00051134433679849648</v>
       </c>
       <c r="S17">
-        <v>0.00022382136463458909</v>
+        <v>0.00022356964854286442</v>
       </c>
       <c r="T17">
-        <v>0.00022654064949469355</v>
+        <v>0.00022627384659600533</v>
       </c>
       <c r="U17">
-        <v>0.00022464497208162524</v>
+        <v>0.00022437139196139854</v>
       </c>
       <c r="V17">
-        <v>0.0002246568224508247</v>
+        <v>0.00022440708522501266</v>
       </c>
       <c r="W17">
-        <v>1.8032814053186563e-06</v>
+        <v>1.8430072341922298e-06</v>
       </c>
       <c r="X17">
-        <v>-5.1379565714724444e-06</v>
+        <v>-5.0227555449651865e-06</v>
       </c>
       <c r="Y17">
-        <v>-0.00022862382284855395</v>
+        <v>-0.00022837255817040287</v>
       </c>
     </row>
     <row r="18">
@@ -3473,76 +3473,76 @@
         <v>38</v>
       </c>
       <c r="B18">
-        <v>-0.014430187908926735</v>
+        <v>-0.016842784124330518</v>
       </c>
       <c r="C18">
-        <v>5.0773710577164088e-06</v>
+        <v>5.173650996695142e-06</v>
       </c>
       <c r="D18">
-        <v>3.7391885805211703e-06</v>
+        <v>3.9216878895765623e-06</v>
       </c>
       <c r="E18">
-        <v>3.856358699013978e-07</v>
+        <v>3.6958613459211639e-07</v>
       </c>
       <c r="F18">
-        <v>-2.2879595987887436e-09</v>
+        <v>-2.1232571263531069e-09</v>
       </c>
       <c r="G18">
-        <v>3.2841584103402222e-06</v>
+        <v>3.1537870993364678e-06</v>
       </c>
       <c r="H18">
-        <v>-9.8248169219184643e-06</v>
+        <v>-9.8226709645208974e-06</v>
       </c>
       <c r="I18">
-        <v>-1.4347763511109743e-07</v>
+        <v>-1.4032025952341667e-07</v>
       </c>
       <c r="J18">
-        <v>-1.0341255561561333e-07</v>
+        <v>-1.0255076431256754e-07</v>
       </c>
       <c r="K18">
-        <v>4.8638431624895905e-07</v>
+        <v>5.0390345740298027e-07</v>
       </c>
       <c r="L18">
-        <v>-2.4618847921282577e-06</v>
+        <v>-2.3295278497693406e-06</v>
       </c>
       <c r="M18">
-        <v>-1.3079083319450394e-06</v>
+        <v>-1.3142335930263726e-06</v>
       </c>
       <c r="N18">
-        <v>-1.0996434993788847e-05</v>
+        <v>-1.1011043810274453e-05</v>
       </c>
       <c r="O18">
-        <v>-1.463974879293817e-05</v>
+        <v>-1.4667035369595016e-05</v>
       </c>
       <c r="P18">
-        <v>-1.6902907372494234e-05</v>
+        <v>-1.6940381433147692e-05</v>
       </c>
       <c r="Q18">
-        <v>0.00022450465058317809</v>
+        <v>0.00022424653859322294</v>
       </c>
       <c r="R18">
-        <v>0.00022382136463458909</v>
+        <v>0.00022356964854286442</v>
       </c>
       <c r="S18">
-        <v>0.00040226629257242226</v>
+        <v>0.00040173651757020184</v>
       </c>
       <c r="T18">
-        <v>0.00022529362316647266</v>
+        <v>0.00022503118828069428</v>
       </c>
       <c r="U18">
-        <v>0.00022688816140487367</v>
+        <v>0.00022661056225080719</v>
       </c>
       <c r="V18">
-        <v>0.0002253067882303158</v>
+        <v>0.00022505032427709275</v>
       </c>
       <c r="W18">
-        <v>-1.5058069435629418e-06</v>
+        <v>-1.4156551655240957e-06</v>
       </c>
       <c r="X18">
-        <v>-9.74592210611528e-07</v>
+        <v>-9.7882427825728354e-07</v>
       </c>
       <c r="Y18">
-        <v>-0.00021770546718838539</v>
+        <v>-0.00021719577000382846</v>
       </c>
     </row>
     <row r="19">
@@ -3550,76 +3550,76 @@
         <v>39</v>
       </c>
       <c r="B19">
-        <v>0.053105085497117378</v>
+        <v>0.052761079385239558</v>
       </c>
       <c r="C19">
-        <v>5.0413155862304047e-06</v>
+        <v>5.0338164339660409e-06</v>
       </c>
       <c r="D19">
-        <v>2.8678310875438164e-06</v>
+        <v>2.8421775099493309e-06</v>
       </c>
       <c r="E19">
-        <v>1.0623117599141848e-06</v>
+        <v>1.0558088071830358e-06</v>
       </c>
       <c r="F19">
-        <v>-1.135626081217945e-08</v>
+        <v>-1.135151967988023e-08</v>
       </c>
       <c r="G19">
-        <v>1.2198167281873962e-06</v>
+        <v>1.0070443971852951e-06</v>
       </c>
       <c r="H19">
-        <v>-6.5845070314333895e-06</v>
+        <v>-6.5677653578270621e-06</v>
       </c>
       <c r="I19">
-        <v>-7.8919752797592873e-08</v>
+        <v>-7.4107303190926498e-08</v>
       </c>
       <c r="J19">
-        <v>1.7205688342084376e-07</v>
+        <v>1.7210339360454175e-07</v>
       </c>
       <c r="K19">
-        <v>-2.4263538692595373e-06</v>
+        <v>-2.2390089323472749e-06</v>
       </c>
       <c r="L19">
-        <v>-4.6965827888657116e-06</v>
+        <v>-4.8624293556948119e-06</v>
       </c>
       <c r="M19">
-        <v>2.9265692149753987e-06</v>
+        <v>2.8757250570624602e-06</v>
       </c>
       <c r="N19">
-        <v>-4.0316322069063894e-06</v>
+        <v>-4.0352095146620328e-06</v>
       </c>
       <c r="O19">
-        <v>-4.8628611382178034e-06</v>
+        <v>-4.8850992364449534e-06</v>
       </c>
       <c r="P19">
-        <v>-1.5663377653003625e-05</v>
+        <v>-1.5643830281320719e-05</v>
       </c>
       <c r="Q19">
-        <v>0.00022604538442442789</v>
+        <v>0.00022578900057727993</v>
       </c>
       <c r="R19">
-        <v>0.00022654064949469355</v>
+        <v>0.00022627384659600533</v>
       </c>
       <c r="S19">
-        <v>0.00022529362316647266</v>
+        <v>0.00022503118828069428</v>
       </c>
       <c r="T19">
-        <v>0.00034869245399130034</v>
+        <v>0.00034828512569801243</v>
       </c>
       <c r="U19">
-        <v>0.00022618966129471629</v>
+        <v>0.00022592126527763576</v>
       </c>
       <c r="V19">
-        <v>0.00022547167070155024</v>
+        <v>0.00022522621914895888</v>
       </c>
       <c r="W19">
-        <v>9.5411654398226646e-06</v>
+        <v>9.6106571820926985e-06</v>
       </c>
       <c r="X19">
-        <v>7.2317327120563419e-06</v>
+        <v>7.2324398060051756e-06</v>
       </c>
       <c r="Y19">
-        <v>-0.0002415196802777973</v>
+        <v>-0.00024100480067444866</v>
       </c>
     </row>
     <row r="20">
@@ -3627,76 +3627,76 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <v>-0.084363934370389013</v>
+        <v>-0.085687137554312981</v>
       </c>
       <c r="C20">
-        <v>-5.5285281196880353e-07</v>
+        <v>-5.0655196481250468e-07</v>
       </c>
       <c r="D20">
-        <v>-3.6402324597503306e-06</v>
+        <v>-3.5491157806904594e-06</v>
       </c>
       <c r="E20">
-        <v>-3.9097935948372816e-07</v>
+        <v>-4.0571523860573422e-07</v>
       </c>
       <c r="F20">
-        <v>6.7051813669920668e-09</v>
+        <v>6.8156652398992608e-09</v>
       </c>
       <c r="G20">
-        <v>-7.1341812363080214e-06</v>
+        <v>-7.3984096013794654e-06</v>
       </c>
       <c r="H20">
-        <v>-2.6950809347737109e-05</v>
+        <v>-2.7071114036435235e-05</v>
       </c>
       <c r="I20">
-        <v>6.7134884473391549e-08</v>
+        <v>7.2659859772372322e-08</v>
       </c>
       <c r="J20">
-        <v>2.9814959143307689e-07</v>
+        <v>3.0079454138238682e-07</v>
       </c>
       <c r="K20">
-        <v>-4.0107813510467981e-06</v>
+        <v>-3.9378479098398279e-06</v>
       </c>
       <c r="L20">
-        <v>-5.4452538270770068e-06</v>
+        <v>-5.345183701464613e-06</v>
       </c>
       <c r="M20">
-        <v>7.136691153376414e-06</v>
+        <v>7.1397231396171031e-06</v>
       </c>
       <c r="N20">
-        <v>-3.130433976287556e-06</v>
+        <v>-3.1427702880073069e-06</v>
       </c>
       <c r="O20">
-        <v>-5.2237151995880842e-06</v>
+        <v>-5.2557936165260552e-06</v>
       </c>
       <c r="P20">
-        <v>-1.4907747462991578e-05</v>
+        <v>-1.4880848994417933e-05</v>
       </c>
       <c r="Q20">
-        <v>0.00022456941302367904</v>
+        <v>0.00022430238164636624</v>
       </c>
       <c r="R20">
-        <v>0.00022464497208162524</v>
+        <v>0.00022437139196139854</v>
       </c>
       <c r="S20">
-        <v>0.00022688816140487367</v>
+        <v>0.00022661056225080719</v>
       </c>
       <c r="T20">
-        <v>0.00022618966129471629</v>
+        <v>0.00022592126527763576</v>
       </c>
       <c r="U20">
-        <v>0.00037307943059568103</v>
+        <v>0.00037263728138000598</v>
       </c>
       <c r="V20">
-        <v>0.0002265770997219273</v>
+        <v>0.00022632553219887621</v>
       </c>
       <c r="W20">
-        <v>1.0161843698381578e-06</v>
+        <v>1.1076535110197458e-06</v>
       </c>
       <c r="X20">
-        <v>4.8447017718101804e-07</v>
+        <v>5.0696291891076035e-07</v>
       </c>
       <c r="Y20">
-        <v>-0.00020549649817245403</v>
+        <v>-0.00020487621859752623</v>
       </c>
     </row>
     <row r="21">
@@ -3704,76 +3704,76 @@
         <v>41</v>
       </c>
       <c r="B21">
-        <v>-0.074610262536690092</v>
+        <v>-0.07600692160361569</v>
       </c>
       <c r="C21">
-        <v>2.8447485046941679e-07</v>
+        <v>4.8471676014940943e-07</v>
       </c>
       <c r="D21">
-        <v>-7.5315705023342392e-06</v>
+        <v>-7.4325632025394498e-06</v>
       </c>
       <c r="E21">
-        <v>-1.7237746172763759e-06</v>
+        <v>-1.6900262467597306e-06</v>
       </c>
       <c r="F21">
-        <v>2.0539560819921629e-08</v>
+        <v>2.0034526493199685e-08</v>
       </c>
       <c r="G21">
-        <v>-1.6149463471300828e-05</v>
+        <v>-1.6598194895405799e-05</v>
       </c>
       <c r="H21">
-        <v>-1.6774356798898917e-05</v>
+        <v>-1.6717414056993305e-05</v>
       </c>
       <c r="I21">
-        <v>2.489725370848461e-07</v>
+        <v>2.5646588833028497e-07</v>
       </c>
       <c r="J21">
-        <v>2.8503368931597679e-07</v>
+        <v>2.8320493425306157e-07</v>
       </c>
       <c r="K21">
-        <v>2.8524696327124353e-06</v>
+        <v>3.2703868080553761e-06</v>
       </c>
       <c r="L21">
-        <v>4.3054478666509737e-06</v>
+        <v>3.5300602758547455e-06</v>
       </c>
       <c r="M21">
-        <v>2.6182428855198913e-06</v>
+        <v>2.6040608889536327e-06</v>
       </c>
       <c r="N21">
-        <v>-8.8040636403090522e-06</v>
+        <v>-8.8084823902473771e-06</v>
       </c>
       <c r="O21">
-        <v>-1.8005579362521338e-06</v>
+        <v>-1.7988827677729689e-06</v>
       </c>
       <c r="P21">
-        <v>-1.1334228750512927e-05</v>
+        <v>-1.1235184689076597e-05</v>
       </c>
       <c r="Q21">
-        <v>0.00022432489412153934</v>
+        <v>0.00022408729929085904</v>
       </c>
       <c r="R21">
-        <v>0.0002246568224508247</v>
+        <v>0.00022440708522501266</v>
       </c>
       <c r="S21">
-        <v>0.0002253067882303158</v>
+        <v>0.00022505032427709275</v>
       </c>
       <c r="T21">
-        <v>0.00022547167070155024</v>
+        <v>0.00022522621914895888</v>
       </c>
       <c r="U21">
-        <v>0.0002265770997219273</v>
+        <v>0.00022632553219887621</v>
       </c>
       <c r="V21">
-        <v>0.00095895101091874062</v>
+        <v>0.00095808138649024503</v>
       </c>
       <c r="W21">
-        <v>5.4054820268133583e-06</v>
+        <v>5.5669149371990802e-06</v>
       </c>
       <c r="X21">
-        <v>2.3593985310642801e-06</v>
+        <v>2.5605650105126629e-06</v>
       </c>
       <c r="Y21">
-        <v>-0.00018719933015364345</v>
+        <v>-0.00018739934627477989</v>
       </c>
     </row>
     <row r="22">
@@ -3781,76 +3781,76 @@
         <v>42</v>
       </c>
       <c r="B22">
-        <v>-0.069929299218011429</v>
+        <v>-0.069060357925321947</v>
       </c>
       <c r="C22">
-        <v>9.8708634542819802e-06</v>
+        <v>9.9270873030602194e-06</v>
       </c>
       <c r="D22">
-        <v>6.7521108945201596e-06</v>
+        <v>6.646686904458306e-06</v>
       </c>
       <c r="E22">
-        <v>5.2972168521386966e-07</v>
+        <v>5.5575161389209792e-07</v>
       </c>
       <c r="F22">
-        <v>-6.811222601876056e-09</v>
+        <v>-7.1273582057857486e-09</v>
       </c>
       <c r="G22">
-        <v>3.5164232718433765e-06</v>
+        <v>3.385973094613812e-06</v>
       </c>
       <c r="H22">
-        <v>1.3440128479261074e-05</v>
+        <v>1.3414268690361624e-05</v>
       </c>
       <c r="I22">
-        <v>-8.9457257439142707e-08</v>
+        <v>-8.6640295740320201e-08</v>
       </c>
       <c r="J22">
-        <v>-2.3589796548736957e-07</v>
+        <v>-2.3479635954616842e-07</v>
       </c>
       <c r="K22">
-        <v>2.7034192129034835e-06</v>
+        <v>2.7999535241356691e-06</v>
       </c>
       <c r="L22">
-        <v>-3.2083549705464349e-06</v>
+        <v>-3.4440484272296107e-06</v>
       </c>
       <c r="M22">
-        <v>-1.3556909987937132e-06</v>
+        <v>-1.535190002280966e-06</v>
       </c>
       <c r="N22">
-        <v>-2.9113400901915666e-06</v>
+        <v>-2.9017279506888178e-06</v>
       </c>
       <c r="O22">
-        <v>-4.4401585189376866e-06</v>
+        <v>-4.4117503053185965e-06</v>
       </c>
       <c r="P22">
-        <v>-8.9437289691714801e-06</v>
+        <v>-8.8476166284484315e-06</v>
       </c>
       <c r="Q22">
-        <v>5.2792927337328599e-06</v>
+        <v>5.4340547670740986e-06</v>
       </c>
       <c r="R22">
-        <v>1.8032814053186563e-06</v>
+        <v>1.8430072341922298e-06</v>
       </c>
       <c r="S22">
-        <v>-1.5058069435629418e-06</v>
+        <v>-1.4156551655240957e-06</v>
       </c>
       <c r="T22">
-        <v>9.5411654398226646e-06</v>
+        <v>9.6106571820926985e-06</v>
       </c>
       <c r="U22">
-        <v>1.0161843698381578e-06</v>
+        <v>1.1076535110197458e-06</v>
       </c>
       <c r="V22">
-        <v>5.4054820268133583e-06</v>
+        <v>5.5669149371990802e-06</v>
       </c>
       <c r="W22">
-        <v>0.00054229008954361402</v>
+        <v>0.00054163263502109973</v>
       </c>
       <c r="X22">
-        <v>3.2941834480353262e-05</v>
+        <v>3.2895588874628127e-05</v>
       </c>
       <c r="Y22">
-        <v>-4.3338269283435703e-05</v>
+        <v>-4.3823941064528181e-05</v>
       </c>
     </row>
     <row r="23">
@@ -3858,76 +3858,76 @@
         <v>43</v>
       </c>
       <c r="B23">
-        <v>0.10585350426389045</v>
+        <v>0.10688185194570429</v>
       </c>
       <c r="C23">
-        <v>5.8212419359163504e-07</v>
+        <v>4.4099699277390498e-07</v>
       </c>
       <c r="D23">
-        <v>6.5766276111471332e-06</v>
+        <v>6.5175322309821035e-06</v>
       </c>
       <c r="E23">
-        <v>2.81561731566845e-07</v>
+        <v>2.6983948173981394e-07</v>
       </c>
       <c r="F23">
-        <v>-7.3035174080840374e-09</v>
+        <v>-7.2580327824294464e-09</v>
       </c>
       <c r="G23">
-        <v>6.1814706224520246e-06</v>
+        <v>6.1850035599557911e-06</v>
       </c>
       <c r="H23">
-        <v>8.0929138313141475e-06</v>
+        <v>7.7783317021278509e-06</v>
       </c>
       <c r="I23">
-        <v>-9.0324261697324879e-08</v>
+        <v>-9.1018842172097784e-08</v>
       </c>
       <c r="J23">
-        <v>-5.2446991717774343e-08</v>
+        <v>-4.7106878851704288e-08</v>
       </c>
       <c r="K23">
-        <v>8.1932214358755726e-06</v>
+        <v>8.2945220073543603e-06</v>
       </c>
       <c r="L23">
-        <v>-7.1832783393610755e-06</v>
+        <v>-7.2830993972605194e-06</v>
       </c>
       <c r="M23">
-        <v>-4.9414103891404907e-06</v>
+        <v>-4.94936854496475e-06</v>
       </c>
       <c r="N23">
-        <v>-6.5313501605727725e-06</v>
+        <v>-6.5256966257938215e-06</v>
       </c>
       <c r="O23">
-        <v>-3.9346942739277752e-06</v>
+        <v>-3.9159099235375396e-06</v>
       </c>
       <c r="P23">
-        <v>-5.8095064108495878e-06</v>
+        <v>-5.8181300615266672e-06</v>
       </c>
       <c r="Q23">
-        <v>4.4121196453801455e-06</v>
+        <v>4.4249661319536601e-06</v>
       </c>
       <c r="R23">
-        <v>-5.1379565714724444e-06</v>
+        <v>-5.0227555449651865e-06</v>
       </c>
       <c r="S23">
-        <v>-9.74592210611528e-07</v>
+        <v>-9.7882427825728354e-07</v>
       </c>
       <c r="T23">
-        <v>7.2317327120563419e-06</v>
+        <v>7.2324398060051756e-06</v>
       </c>
       <c r="U23">
-        <v>4.8447017718101804e-07</v>
+        <v>5.0696291891076035e-07</v>
       </c>
       <c r="V23">
-        <v>2.3593985310642801e-06</v>
+        <v>2.5605650105126629e-06</v>
       </c>
       <c r="W23">
-        <v>3.2941834480353262e-05</v>
+        <v>3.2895588874628127e-05</v>
       </c>
       <c r="X23">
-        <v>0.00065287306084434876</v>
+        <v>0.00065274524929682801</v>
       </c>
       <c r="Y23">
-        <v>-3.2956895014691565e-05</v>
+        <v>-3.2455320506445094e-05</v>
       </c>
     </row>
     <row r="24">
@@ -3935,76 +3935,76 @@
         <v>44</v>
       </c>
       <c r="B24">
-        <v>-2.345887481015275</v>
+        <v>-2.3374978940084312</v>
       </c>
       <c r="C24">
-        <v>-0.0010091629345850475</v>
+        <v>-0.0010096918967565623</v>
       </c>
       <c r="D24">
-        <v>-0.00017795279878205056</v>
+        <v>-0.00017929425668358154</v>
       </c>
       <c r="E24">
-        <v>-0.00023829272713437683</v>
+        <v>-0.0002381866332478734</v>
       </c>
       <c r="F24">
-        <v>2.2520893764479928e-06</v>
+        <v>2.251931959082401e-06</v>
       </c>
       <c r="G24">
-        <v>-0.0015973748514898495</v>
+        <v>-0.0015950522206416482</v>
       </c>
       <c r="H24">
-        <v>-0.0017070767879386211</v>
+        <v>-0.0017069303726679895</v>
       </c>
       <c r="I24">
-        <v>3.1810528837995031e-05</v>
+        <v>3.1768759411703956e-05</v>
       </c>
       <c r="J24">
-        <v>3.3037982872207643e-05</v>
+        <v>3.303608122063139e-05</v>
       </c>
       <c r="K24">
-        <v>0.0001003666649968226</v>
+        <v>9.7567365737442701e-05</v>
       </c>
       <c r="L24">
-        <v>0.00020857984561314282</v>
+        <v>0.00021011173211139144</v>
       </c>
       <c r="M24">
-        <v>-0.0039260031461625022</v>
+        <v>-0.0039243840081503887</v>
       </c>
       <c r="N24">
-        <v>-0.0039684595616753726</v>
+        <v>-0.0039664828139294077</v>
       </c>
       <c r="O24">
-        <v>-0.0040473251642220553</v>
+        <v>-0.0040448240361537387</v>
       </c>
       <c r="P24">
-        <v>-0.0042099395338169848</v>
+        <v>-0.0042070436081594054</v>
       </c>
       <c r="Q24">
-        <v>-0.00025535226197773018</v>
+        <v>-0.00025534441360154322</v>
       </c>
       <c r="R24">
-        <v>-0.00022862382284855395</v>
+        <v>-0.00022837255817040287</v>
       </c>
       <c r="S24">
-        <v>-0.00021770546718838539</v>
+        <v>-0.00021719577000382846</v>
       </c>
       <c r="T24">
-        <v>-0.0002415196802777973</v>
+        <v>-0.00024100480067444866</v>
       </c>
       <c r="U24">
-        <v>-0.00020549649817245403</v>
+        <v>-0.00020487621859752623</v>
       </c>
       <c r="V24">
-        <v>-0.00018719933015364345</v>
+        <v>-0.00018739934627477989</v>
       </c>
       <c r="W24">
-        <v>-4.3338269283435703e-05</v>
+        <v>-4.3823941064528181e-05</v>
       </c>
       <c r="X24">
-        <v>-3.2956895014691565e-05</v>
+        <v>-3.2455320506445094e-05</v>
       </c>
       <c r="Y24">
-        <v>0.010128412532825152</v>
+        <v>0.010121975367309652</v>
       </c>
     </row>
   </sheetData>
@@ -4092,70 +4092,70 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>0.18089287681396107</v>
+        <v>0.18155289999776023</v>
       </c>
       <c r="C2">
-        <v>2.8212913668428682e-05</v>
+        <v>2.8570344048192584e-05</v>
       </c>
       <c r="D2">
-        <v>-3.0691379851234826e-07</v>
+        <v>-3.1087574256456382e-07</v>
       </c>
       <c r="E2">
-        <v>6.063477857212771e-05</v>
+        <v>6.145594119162167e-05</v>
       </c>
       <c r="F2">
-        <v>3.3356012755703419e-05</v>
+        <v>3.5417925874530029e-05</v>
       </c>
       <c r="G2">
-        <v>-1.2559209551958806e-06</v>
+        <v>-1.2715783864496432e-06</v>
       </c>
       <c r="H2">
-        <v>-6.3503684383640648e-07</v>
+        <v>-6.7501083671175927e-07</v>
       </c>
       <c r="I2">
-        <v>-1.4397647411004721e-05</v>
+        <v>-1.389602399273057e-05</v>
       </c>
       <c r="J2">
-        <v>-3.9679366302887217e-05</v>
+        <v>-4.071762363064737e-05</v>
       </c>
       <c r="K2">
-        <v>4.2028376785807685e-06</v>
+        <v>4.2256430281573402e-06</v>
       </c>
       <c r="L2">
-        <v>7.4441482841678547e-06</v>
+        <v>7.5137478233992957e-06</v>
       </c>
       <c r="M2">
-        <v>1.0437781295209378e-05</v>
+        <v>1.0421809366738927e-05</v>
       </c>
       <c r="N2">
-        <v>1.7487215950198862e-05</v>
+        <v>1.7528688346052032e-05</v>
       </c>
       <c r="O2">
-        <v>2.8229266893473244e-06</v>
+        <v>2.6908205779039368e-06</v>
       </c>
       <c r="P2">
-        <v>3.966196669338332e-06</v>
+        <v>3.9634462420549206e-06</v>
       </c>
       <c r="Q2">
-        <v>2.4485614070246394e-06</v>
+        <v>2.4335226986637456e-06</v>
       </c>
       <c r="R2">
-        <v>5.4005619281371689e-06</v>
+        <v>5.3475667911221148e-06</v>
       </c>
       <c r="S2">
-        <v>3.7941119332633169e-06</v>
+        <v>3.7934002192214932e-06</v>
       </c>
       <c r="T2">
-        <v>-2.260043436936677e-07</v>
+        <v>-6.4655709140265847e-08</v>
       </c>
       <c r="U2">
-        <v>7.4443879859393309e-07</v>
+        <v>8.069340261440761e-07</v>
       </c>
       <c r="V2">
-        <v>-1.2530163930393205e-06</v>
+        <v>-1.1644310149497e-06</v>
       </c>
       <c r="W2">
-        <v>-0.00059580463930211712</v>
+        <v>-0.00060316515687003835</v>
       </c>
     </row>
     <row r="3">
@@ -4163,70 +4163,70 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>-0.0019629843801187408</v>
+        <v>-0.0019734815189099823</v>
       </c>
       <c r="C3">
-        <v>-3.0691379851234826e-07</v>
+        <v>-3.1087574256456382e-07</v>
       </c>
       <c r="D3">
-        <v>3.4688889446205778e-09</v>
+        <v>3.5134805097760216e-09</v>
       </c>
       <c r="E3">
-        <v>-1.9754853126007579e-07</v>
+        <v>-2.0414389628300173e-07</v>
       </c>
       <c r="F3">
-        <v>1.0942923784018472e-07</v>
+        <v>8.8351797042472906e-08</v>
       </c>
       <c r="G3">
-        <v>2.9943114029847789e-09</v>
+        <v>3.1194493670003663e-09</v>
       </c>
       <c r="H3">
-        <v>-3.9311914200199616e-09</v>
+        <v>-3.5221238744751483e-09</v>
       </c>
       <c r="I3">
-        <v>1.2577045123085712e-07</v>
+        <v>1.1980984957276447e-07</v>
       </c>
       <c r="J3">
-        <v>4.6375741995682274e-07</v>
+        <v>4.761386104823883e-07</v>
       </c>
       <c r="K3">
-        <v>-4.7539607402531409e-08</v>
+        <v>-4.7670154323545336e-08</v>
       </c>
       <c r="L3">
-        <v>-7.927015650839e-08</v>
+        <v>-8.0057769711292844e-08</v>
       </c>
       <c r="M3">
-        <v>-9.6075044869187431e-08</v>
+        <v>-9.5835780141784615e-08</v>
       </c>
       <c r="N3">
-        <v>-1.4499094689611371e-07</v>
+        <v>-1.4524158596248764e-07</v>
       </c>
       <c r="O3">
-        <v>-3.303726107889257e-08</v>
+        <v>-3.1540914682322173e-08</v>
       </c>
       <c r="P3">
-        <v>-4.7734409116666451e-08</v>
+        <v>-4.8031299484466901e-08</v>
       </c>
       <c r="Q3">
-        <v>-2.8193403910187247e-08</v>
+        <v>-2.8093261492609513e-08</v>
       </c>
       <c r="R3">
-        <v>-5.9293833597263886e-08</v>
+        <v>-5.8791859272004374e-08</v>
       </c>
       <c r="S3">
-        <v>-4.0261836804159125e-08</v>
+        <v>-4.0427055481624849e-08</v>
       </c>
       <c r="T3">
-        <v>5.7295706707113009e-09</v>
+        <v>3.7341562483775182e-09</v>
       </c>
       <c r="U3">
-        <v>-1.1439799954674747e-08</v>
+        <v>-1.2321991127483736e-08</v>
       </c>
       <c r="V3">
-        <v>1.1122820945452113e-08</v>
+        <v>1.0237557915597247e-08</v>
       </c>
       <c r="W3">
-        <v>6.2060900132489428e-06</v>
+        <v>6.2857373250009652e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4234,70 +4234,70 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>-0.27152055268581243</v>
+        <v>-0.2656763243635798</v>
       </c>
       <c r="C4">
-        <v>6.063477857212771e-05</v>
+        <v>6.145594119162167e-05</v>
       </c>
       <c r="D4">
-        <v>-1.9754853126007579e-07</v>
+        <v>-2.0414389628300173e-07</v>
       </c>
       <c r="E4">
-        <v>0.0054203978755018433</v>
+        <v>0.0054500186693699493</v>
       </c>
       <c r="F4">
-        <v>0.0020539264026555202</v>
+        <v>0.0020705646219560557</v>
       </c>
       <c r="G4">
-        <v>-0.00011340164810100889</v>
+        <v>-0.00011398018716582164</v>
       </c>
       <c r="H4">
-        <v>-4.4202376761918845e-05</v>
+        <v>-4.4527126883032722e-05</v>
       </c>
       <c r="I4">
-        <v>2.0658265705622886e-06</v>
+        <v>4.5689924842101498e-06</v>
       </c>
       <c r="J4">
-        <v>-0.0001080580730689578</v>
+        <v>-0.0001109602217266641</v>
       </c>
       <c r="K4">
-        <v>4.2464294603838156e-05</v>
+        <v>4.282961246756731e-05</v>
       </c>
       <c r="L4">
-        <v>4.3060216919538143e-05</v>
+        <v>4.2493466319664416e-05</v>
       </c>
       <c r="M4">
-        <v>3.9098711939538353e-05</v>
+        <v>3.8593958948113477e-05</v>
       </c>
       <c r="N4">
-        <v>8.1062023029481985e-05</v>
+        <v>8.1361097263202655e-05</v>
       </c>
       <c r="O4">
-        <v>2.599957346847167e-05</v>
+        <v>2.6625627524506123e-05</v>
       </c>
       <c r="P4">
-        <v>3.0139903629620366e-05</v>
+        <v>2.9133457784574754e-05</v>
       </c>
       <c r="Q4">
-        <v>1.6520134236658164e-05</v>
+        <v>1.5636866182581312e-05</v>
       </c>
       <c r="R4">
-        <v>1.5319065618404014e-05</v>
+        <v>1.585609166826472e-05</v>
       </c>
       <c r="S4">
-        <v>-1.0223069220110485e-05</v>
+        <v>-1.1666304287785337e-05</v>
       </c>
       <c r="T4">
-        <v>-1.6559814167977748e-07</v>
+        <v>-2.5758658654818884e-07</v>
       </c>
       <c r="U4">
-        <v>1.5951222429015683e-05</v>
+        <v>1.5059445286503816e-05</v>
       </c>
       <c r="V4">
-        <v>2.8115213761436599e-05</v>
+        <v>2.7777225986964383e-05</v>
       </c>
       <c r="W4">
-        <v>-0.0023801401078947602</v>
+        <v>-0.0024038095953505842</v>
       </c>
     </row>
     <row r="5">
@@ -4305,70 +4305,70 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>-0.36622317016271977</v>
+        <v>-0.36908335085649657</v>
       </c>
       <c r="C5">
-        <v>3.3356012755703419e-05</v>
+        <v>3.5417925874530029e-05</v>
       </c>
       <c r="D5">
-        <v>1.0942923784018472e-07</v>
+        <v>8.8351797042472906e-08</v>
       </c>
       <c r="E5">
-        <v>0.0020539264026555202</v>
+        <v>0.0020705646219560557</v>
       </c>
       <c r="F5">
-        <v>0.0050535262368869016</v>
+        <v>0.0050920032068113522</v>
       </c>
       <c r="G5">
-        <v>-4.4455034063569681e-05</v>
+        <v>-4.4779583271372593e-05</v>
       </c>
       <c r="H5">
-        <v>-0.00010307170964818179</v>
+        <v>-0.00010385139638680865</v>
       </c>
       <c r="I5">
-        <v>2.2843827951540523e-05</v>
+        <v>2.6223679441483103e-05</v>
       </c>
       <c r="J5">
-        <v>-0.00015317044663431837</v>
+        <v>-0.00016060492989324388</v>
       </c>
       <c r="K5">
-        <v>3.1424032450837755e-05</v>
+        <v>3.2666500406564806e-05</v>
       </c>
       <c r="L5">
-        <v>-1.1132732308966357e-06</v>
+        <v>-6.9686470291604932e-07</v>
       </c>
       <c r="M5">
-        <v>-1.1206726195968309e-05</v>
+        <v>-1.2017844458756736e-05</v>
       </c>
       <c r="N5">
-        <v>4.7530408677333024e-05</v>
+        <v>4.7401913242479336e-05</v>
       </c>
       <c r="O5">
-        <v>2.2028409212036811e-05</v>
+        <v>2.282328641040083e-05</v>
       </c>
       <c r="P5">
-        <v>-1.0838641651333534e-05</v>
+        <v>-1.2405574572347641e-05</v>
       </c>
       <c r="Q5">
-        <v>-5.6215128617929705e-05</v>
+        <v>-5.6082656110512338e-05</v>
       </c>
       <c r="R5">
-        <v>-2.4961829883317909e-05</v>
+        <v>-2.4882826621797857e-05</v>
       </c>
       <c r="S5">
-        <v>-9.5365212390587952e-05</v>
+        <v>-9.7056687944450552e-05</v>
       </c>
       <c r="T5">
-        <v>-6.031309723040548e-05</v>
+        <v>-6.0964852193156274e-05</v>
       </c>
       <c r="U5">
-        <v>3.2369995515503299e-05</v>
+        <v>3.1849958787050858e-05</v>
       </c>
       <c r="V5">
-        <v>4.3041152185741951e-05</v>
+        <v>4.4330517297866446e-05</v>
       </c>
       <c r="W5">
-        <v>-0.0017237712088299412</v>
+        <v>-0.001770431700220244</v>
       </c>
     </row>
     <row r="6">
@@ -4376,70 +4376,70 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>0.0017773661695320868</v>
+        <v>0.0015697344324824361</v>
       </c>
       <c r="C6">
-        <v>-1.2559209551958806e-06</v>
+        <v>-1.2715783864496432e-06</v>
       </c>
       <c r="D6">
-        <v>2.9943114029847789e-09</v>
+        <v>3.1194493670003663e-09</v>
       </c>
       <c r="E6">
-        <v>-0.00011340164810100889</v>
+        <v>-0.00011398018716582164</v>
       </c>
       <c r="F6">
-        <v>-4.4455034063569681e-05</v>
+        <v>-4.4779583271372593e-05</v>
       </c>
       <c r="G6">
-        <v>2.5429865299558371e-06</v>
+        <v>2.5543413399711525e-06</v>
       </c>
       <c r="H6">
-        <v>1.0227883541590456e-06</v>
+        <v>1.029147216541347e-06</v>
       </c>
       <c r="I6">
-        <v>-5.8620147961938666e-08</v>
+        <v>-1.1424393235353971e-07</v>
       </c>
       <c r="J6">
-        <v>2.4132211773751256e-06</v>
+        <v>2.464918200603723e-06</v>
       </c>
       <c r="K6">
-        <v>-5.4336720171077805e-07</v>
+        <v>-5.7116826918548636e-07</v>
       </c>
       <c r="L6">
-        <v>-5.9585217425194744e-07</v>
+        <v>-5.9261344475577458e-07</v>
       </c>
       <c r="M6">
-        <v>-7.732426681770509e-08</v>
+        <v>-8.0575090080943078e-08</v>
       </c>
       <c r="N6">
-        <v>-7.0516570278752119e-07</v>
+        <v>-7.2106363225308409e-07</v>
       </c>
       <c r="O6">
-        <v>-3.0470227802096388e-07</v>
+        <v>-3.1006659675244876e-07</v>
       </c>
       <c r="P6">
-        <v>-5.3078848873932977e-07</v>
+        <v>-5.0793801075564197e-07</v>
       </c>
       <c r="Q6">
-        <v>-3.3794786108738866e-07</v>
+        <v>-3.0768773176249578e-07</v>
       </c>
       <c r="R6">
-        <v>-4.766370617079262e-07</v>
+        <v>-4.8158960944848539e-07</v>
       </c>
       <c r="S6">
-        <v>1.4481119756810726e-07</v>
+        <v>1.8668074382521674e-07</v>
       </c>
       <c r="T6">
-        <v>-1.8760321035369524e-07</v>
+        <v>-1.8504666670830908e-07</v>
       </c>
       <c r="U6">
-        <v>-1.8809430049115851e-07</v>
+        <v>-1.5407544467246968e-07</v>
       </c>
       <c r="V6">
-        <v>-4.5847018074486989e-07</v>
+        <v>-4.4440045106206145e-07</v>
       </c>
       <c r="W6">
-        <v>4.8074717002199028e-05</v>
+        <v>4.8533752831501739e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4447,70 +4447,70 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>-0.0015926984005508531</v>
+        <v>-0.0015117054103097728</v>
       </c>
       <c r="C7">
-        <v>-6.3503684383640648e-07</v>
+        <v>-6.7501083671175927e-07</v>
       </c>
       <c r="D7">
-        <v>-3.9311914200199616e-09</v>
+        <v>-3.5221238744751483e-09</v>
       </c>
       <c r="E7">
-        <v>-4.4202376761918845e-05</v>
+        <v>-4.4527126883032722e-05</v>
       </c>
       <c r="F7">
-        <v>-0.00010307170964818179</v>
+        <v>-0.00010385139638680865</v>
       </c>
       <c r="G7">
-        <v>1.0227883541590456e-06</v>
+        <v>1.029147216541347e-06</v>
       </c>
       <c r="H7">
-        <v>2.2438032928197734e-06</v>
+        <v>2.2602958425552557e-06</v>
       </c>
       <c r="I7">
-        <v>-7.883536688883599e-07</v>
+        <v>-8.5832584056232064e-07</v>
       </c>
       <c r="J7">
-        <v>3.416956312080981e-06</v>
+        <v>3.5592394255664058e-06</v>
       </c>
       <c r="K7">
-        <v>-7.8597116053919424e-07</v>
+        <v>-8.057193435553014e-07</v>
       </c>
       <c r="L7">
-        <v>1.0203691265460072e-07</v>
+        <v>1.0543264573085097e-07</v>
       </c>
       <c r="M7">
-        <v>1.0716499487448371e-06</v>
+        <v>1.1016189313236715e-06</v>
       </c>
       <c r="N7">
-        <v>2.3770926427101751e-07</v>
+        <v>2.5431908612260742e-07</v>
       </c>
       <c r="O7">
-        <v>-1.3503755523513163e-07</v>
+        <v>-1.4312763594037549e-07</v>
       </c>
       <c r="P7">
-        <v>7.0406438012282245e-07</v>
+        <v>7.3477227987356569e-07</v>
       </c>
       <c r="Q7">
-        <v>8.5989235956969206e-07</v>
+        <v>8.6235231722208974e-07</v>
       </c>
       <c r="R7">
-        <v>5.1460498825877545e-07</v>
+        <v>5.1579616379850797e-07</v>
       </c>
       <c r="S7">
-        <v>1.5035721594131189e-06</v>
+        <v>1.546394438380446e-06</v>
       </c>
       <c r="T7">
-        <v>1.0564369302850906e-06</v>
+        <v>1.0627879244639522e-06</v>
       </c>
       <c r="U7">
-        <v>-4.6454352798112921e-07</v>
+        <v>-4.5695583106736617e-07</v>
       </c>
       <c r="V7">
-        <v>-4.4799985437316903e-07</v>
+        <v>-4.835835820950629e-07</v>
       </c>
       <c r="W7">
-        <v>3.3253971797968724e-05</v>
+        <v>3.4140276008591438e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4518,70 +4518,70 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>0.011237057209964908</v>
+        <v>0.011759827817618723</v>
       </c>
       <c r="C8">
-        <v>-1.4397647411004721e-05</v>
+        <v>-1.389602399273057e-05</v>
       </c>
       <c r="D8">
-        <v>1.2577045123085712e-07</v>
+        <v>1.1980984957276447e-07</v>
       </c>
       <c r="E8">
-        <v>2.0658265705622886e-06</v>
+        <v>4.5689924842101498e-06</v>
       </c>
       <c r="F8">
-        <v>2.2843827951540523e-05</v>
+        <v>2.6223679441483103e-05</v>
       </c>
       <c r="G8">
-        <v>-5.8620147961938666e-08</v>
+        <v>-1.1424393235353971e-07</v>
       </c>
       <c r="H8">
-        <v>-7.883536688883599e-07</v>
+        <v>-8.5832584056232064e-07</v>
       </c>
       <c r="I8">
-        <v>0.00030541345328910491</v>
+        <v>0.00030905744799336301</v>
       </c>
       <c r="J8">
-        <v>-9.9022114498574442e-05</v>
+        <v>-0.00010383605532654903</v>
       </c>
       <c r="K8">
-        <v>-1.3873904259895689e-05</v>
+        <v>-1.397948033387334e-05</v>
       </c>
       <c r="L8">
-        <v>-2.1690594962824576e-05</v>
+        <v>-2.1906402007598587e-05</v>
       </c>
       <c r="M8">
-        <v>-3.1420034970895341e-05</v>
+        <v>-3.1530913625294984e-05</v>
       </c>
       <c r="N8">
-        <v>-2.9780660796980464e-05</v>
+        <v>-2.9843770527605796e-05</v>
       </c>
       <c r="O8">
-        <v>-2.8389918702481635e-06</v>
+        <v>-2.7445511323062559e-06</v>
       </c>
       <c r="P8">
-        <v>1.0046695204955815e-05</v>
+        <v>1.0213125544215012e-05</v>
       </c>
       <c r="Q8">
-        <v>-2.4553952783814192e-06</v>
+        <v>-2.4831665391248349e-06</v>
       </c>
       <c r="R8">
-        <v>-4.2684872494050983e-06</v>
+        <v>-4.1943860419286646e-06</v>
       </c>
       <c r="S8">
-        <v>2.0932982755478784e-06</v>
+        <v>2.1397193312234625e-06</v>
       </c>
       <c r="T8">
-        <v>1.9162917473249433e-05</v>
+        <v>1.9888332058516673e-05</v>
       </c>
       <c r="U8">
-        <v>-4.1330805374154734e-06</v>
+        <v>-4.15183881333172e-06</v>
       </c>
       <c r="V8">
-        <v>-3.5013528475145101e-06</v>
+        <v>-3.2352132206972869e-06</v>
       </c>
       <c r="W8">
-        <v>0.00025058448675194386</v>
+        <v>0.00024084293525438653</v>
       </c>
     </row>
     <row r="9">
@@ -4589,70 +4589,70 @@
         <v>31</v>
       </c>
       <c r="B9">
-        <v>-0.067066454648628135</v>
+        <v>-0.0735028052363388</v>
       </c>
       <c r="C9">
-        <v>-3.9679366302887217e-05</v>
+        <v>-4.071762363064737e-05</v>
       </c>
       <c r="D9">
-        <v>4.6375741995682274e-07</v>
+        <v>4.761386104823883e-07</v>
       </c>
       <c r="E9">
-        <v>-0.0001080580730689578</v>
+        <v>-0.0001109602217266641</v>
       </c>
       <c r="F9">
-        <v>-0.00015317044663431837</v>
+        <v>-0.00016060492989324388</v>
       </c>
       <c r="G9">
-        <v>2.4132211773751256e-06</v>
+        <v>2.464918200603723e-06</v>
       </c>
       <c r="H9">
-        <v>3.416956312080981e-06</v>
+        <v>3.5592394255664058e-06</v>
       </c>
       <c r="I9">
-        <v>-9.9022114498574442e-05</v>
+        <v>-0.00010383605532654903</v>
       </c>
       <c r="J9">
-        <v>0.00035472363758384486</v>
+        <v>0.00036018826458980493</v>
       </c>
       <c r="K9">
-        <v>-1.933984459083775e-06</v>
+        <v>-2.289510459484894e-06</v>
       </c>
       <c r="L9">
-        <v>-1.0576689999532813e-05</v>
+        <v>-1.1368170324656441e-05</v>
       </c>
       <c r="M9">
-        <v>-2.0697117126476888e-05</v>
+        <v>-2.1049743298634971e-05</v>
       </c>
       <c r="N9">
-        <v>-2.1731803636424753e-05</v>
+        <v>-2.2435771438959328e-05</v>
       </c>
       <c r="O9">
-        <v>-1.4742208723077788e-05</v>
+        <v>-1.4400891528318456e-05</v>
       </c>
       <c r="P9">
-        <v>-1.5373924110957966e-05</v>
+        <v>-1.5014695985072795e-05</v>
       </c>
       <c r="Q9">
-        <v>-1.3802407198192849e-05</v>
+        <v>-1.3441947556693481e-05</v>
       </c>
       <c r="R9">
-        <v>-1.6767369914502567e-05</v>
+        <v>-1.6690232790303464e-05</v>
       </c>
       <c r="S9">
-        <v>-1.8532693821311366e-05</v>
+        <v>-1.847066177338908e-05</v>
       </c>
       <c r="T9">
-        <v>-7.5491457290265346e-06</v>
+        <v>-9.0537301972672647e-06</v>
       </c>
       <c r="U9">
-        <v>-6.1301798897019849e-06</v>
+        <v>-6.302902167343029e-06</v>
       </c>
       <c r="V9">
-        <v>-8.6713804594057136e-06</v>
+        <v>-9.6927214389597718e-06</v>
       </c>
       <c r="W9">
-        <v>0.00073539763712275152</v>
+        <v>0.00075537537556103862</v>
       </c>
     </row>
     <row r="10">
@@ -4660,70 +4660,70 @@
         <v>32</v>
       </c>
       <c r="B10">
-        <v>0.18373691429854508</v>
+        <v>0.1881930507100977</v>
       </c>
       <c r="C10">
-        <v>4.2028376785807685e-06</v>
+        <v>4.2256430281573402e-06</v>
       </c>
       <c r="D10">
-        <v>-4.7539607402531409e-08</v>
+        <v>-4.7670154323545336e-08</v>
       </c>
       <c r="E10">
-        <v>4.2464294603838156e-05</v>
+        <v>4.282961246756731e-05</v>
       </c>
       <c r="F10">
-        <v>3.1424032450837755e-05</v>
+        <v>3.2666500406564806e-05</v>
       </c>
       <c r="G10">
-        <v>-5.4336720171077805e-07</v>
+        <v>-5.7116826918548636e-07</v>
       </c>
       <c r="H10">
-        <v>-7.8597116053919424e-07</v>
+        <v>-8.057193435553014e-07</v>
       </c>
       <c r="I10">
-        <v>-1.3873904259895689e-05</v>
+        <v>-1.397948033387334e-05</v>
       </c>
       <c r="J10">
-        <v>-1.933984459083775e-06</v>
+        <v>-2.289510459484894e-06</v>
       </c>
       <c r="K10">
-        <v>0.010045728191650874</v>
+        <v>0.010075357280448175</v>
       </c>
       <c r="L10">
-        <v>0.0083056359566592384</v>
+        <v>0.0083244380839020034</v>
       </c>
       <c r="M10">
-        <v>0.0083025286830316607</v>
+        <v>0.0083213928568735482</v>
       </c>
       <c r="N10">
-        <v>0.0082985549939215315</v>
+        <v>0.0083174425108174348</v>
       </c>
       <c r="O10">
-        <v>1.2307005584410866e-05</v>
+        <v>1.0586429136039377e-05</v>
       </c>
       <c r="P10">
-        <v>3.7392509999887669e-05</v>
+        <v>3.7034334804804891e-05</v>
       </c>
       <c r="Q10">
-        <v>2.5549619243840432e-05</v>
+        <v>2.5499859968154204e-05</v>
       </c>
       <c r="R10">
-        <v>2.9361686160015165e-05</v>
+        <v>2.9369425247035511e-05</v>
       </c>
       <c r="S10">
-        <v>2.6052897418697094e-05</v>
+        <v>2.5490299116642237e-05</v>
       </c>
       <c r="T10">
-        <v>6.3604519814932238e-05</v>
+        <v>6.3528439298659805e-05</v>
       </c>
       <c r="U10">
-        <v>-1.0893199412724915e-05</v>
+        <v>-1.0917210013414117e-05</v>
       </c>
       <c r="V10">
-        <v>3.1086774629481877e-05</v>
+        <v>3.1208504634171185e-05</v>
       </c>
       <c r="W10">
-        <v>-0.0084058833483083573</v>
+        <v>-0.0084247799088486997</v>
       </c>
     </row>
     <row r="11">
@@ -4731,70 +4731,70 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>0.42231251129335928</v>
+        <v>0.42438350477581488</v>
       </c>
       <c r="C11">
-        <v>7.4441482841678547e-06</v>
+        <v>7.5137478233992957e-06</v>
       </c>
       <c r="D11">
-        <v>-7.927015650839e-08</v>
+        <v>-8.0057769711292844e-08</v>
       </c>
       <c r="E11">
-        <v>4.3060216919538143e-05</v>
+        <v>4.2493466319664416e-05</v>
       </c>
       <c r="F11">
-        <v>-1.1132732308966357e-06</v>
+        <v>-6.9686470291604932e-07</v>
       </c>
       <c r="G11">
-        <v>-5.9585217425194744e-07</v>
+        <v>-5.9261344475577458e-07</v>
       </c>
       <c r="H11">
-        <v>1.0203691265460072e-07</v>
+        <v>1.0543264573085097e-07</v>
       </c>
       <c r="I11">
-        <v>-2.1690594962824576e-05</v>
+        <v>-2.1906402007598587e-05</v>
       </c>
       <c r="J11">
-        <v>-1.0576689999532813e-05</v>
+        <v>-1.1368170324656441e-05</v>
       </c>
       <c r="K11">
-        <v>0.0083056359566592384</v>
+        <v>0.0083244380839020034</v>
       </c>
       <c r="L11">
-        <v>0.0086119814891286797</v>
+        <v>0.0086328770475936206</v>
       </c>
       <c r="M11">
-        <v>0.0083097659464238319</v>
+        <v>0.0083287974905321954</v>
       </c>
       <c r="N11">
-        <v>0.0083109663353309726</v>
+        <v>0.0083300520549830764</v>
       </c>
       <c r="O11">
-        <v>-7.3782835128364404e-06</v>
+        <v>-8.3925004862748435e-06</v>
       </c>
       <c r="P11">
-        <v>1.1574224310175558e-05</v>
+        <v>1.1635983171439328e-05</v>
       </c>
       <c r="Q11">
-        <v>4.278264441372339e-06</v>
+        <v>4.8432088118500886e-06</v>
       </c>
       <c r="R11">
-        <v>1.6779112074569375e-05</v>
+        <v>1.6952945242436227e-05</v>
       </c>
       <c r="S11">
-        <v>8.5049575997847311e-07</v>
+        <v>1.0130206111364534e-06</v>
       </c>
       <c r="T11">
-        <v>2.9610352200449452e-05</v>
+        <v>2.9900476401665128e-05</v>
       </c>
       <c r="U11">
-        <v>-1.5517592066413316e-05</v>
+        <v>-1.5247802569949079e-05</v>
       </c>
       <c r="V11">
-        <v>2.8611271935898903e-05</v>
+        <v>2.8923726321032941e-05</v>
       </c>
       <c r="W11">
-        <v>-0.0084661599263487521</v>
+        <v>-0.0084862620601519525</v>
       </c>
     </row>
     <row r="12">
@@ -4802,70 +4802,70 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0.59055375337138849</v>
+        <v>0.59213545452888128</v>
       </c>
       <c r="C12">
-        <v>1.0437781295209378e-05</v>
+        <v>1.0421809366738927e-05</v>
       </c>
       <c r="D12">
-        <v>-9.6075044869187431e-08</v>
+        <v>-9.5835780141784615e-08</v>
       </c>
       <c r="E12">
-        <v>3.9098711939538353e-05</v>
+        <v>3.8593958948113477e-05</v>
       </c>
       <c r="F12">
-        <v>-1.1206726195968309e-05</v>
+        <v>-1.2017844458756736e-05</v>
       </c>
       <c r="G12">
-        <v>-7.732426681770509e-08</v>
+        <v>-8.0575090080943078e-08</v>
       </c>
       <c r="H12">
-        <v>1.0716499487448371e-06</v>
+        <v>1.1016189313236715e-06</v>
       </c>
       <c r="I12">
-        <v>-3.1420034970895341e-05</v>
+        <v>-3.1530913625294984e-05</v>
       </c>
       <c r="J12">
-        <v>-2.0697117126476888e-05</v>
+        <v>-2.1049743298634971e-05</v>
       </c>
       <c r="K12">
-        <v>0.0083025286830316607</v>
+        <v>0.0083213928568735482</v>
       </c>
       <c r="L12">
-        <v>0.0083097659464238319</v>
+        <v>0.0083287974905321954</v>
       </c>
       <c r="M12">
-        <v>0.0084193913005867708</v>
+        <v>0.0084389901486324852</v>
       </c>
       <c r="N12">
-        <v>0.0083438776297522464</v>
+        <v>0.0083631005278954496</v>
       </c>
       <c r="O12">
-        <v>-1.9062794287339976e-05</v>
+        <v>-2.0280159142167288e-05</v>
       </c>
       <c r="P12">
-        <v>6.1133393623238874e-06</v>
+        <v>6.0438681110631606e-06</v>
       </c>
       <c r="Q12">
-        <v>-9.1106574615597486e-06</v>
+        <v>-9.0207803534152328e-06</v>
       </c>
       <c r="R12">
-        <v>7.4634355775772413e-06</v>
+        <v>7.505536415173934e-06</v>
       </c>
       <c r="S12">
-        <v>-8.2807623491552341e-06</v>
+        <v>-7.9589026881772388e-06</v>
       </c>
       <c r="T12">
-        <v>3.9261263618007132e-05</v>
+        <v>3.9688445556501515e-05</v>
       </c>
       <c r="U12">
-        <v>-1.8194938227746931e-05</v>
+        <v>-1.8060678776986776e-05</v>
       </c>
       <c r="V12">
-        <v>3.0842942201597627e-05</v>
+        <v>3.1319981314868425e-05</v>
       </c>
       <c r="W12">
-        <v>-0.008581535024973776</v>
+        <v>-0.0086001536817800328</v>
       </c>
     </row>
     <row r="13">
@@ -4873,70 +4873,70 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>0.61398603387151329</v>
+        <v>0.61389342286671667</v>
       </c>
       <c r="C13">
-        <v>1.7487215950198862e-05</v>
+        <v>1.7528688346052032e-05</v>
       </c>
       <c r="D13">
-        <v>-1.4499094689611371e-07</v>
+        <v>-1.4524158596248764e-07</v>
       </c>
       <c r="E13">
-        <v>8.1062023029481985e-05</v>
+        <v>8.1361097263202655e-05</v>
       </c>
       <c r="F13">
-        <v>4.7530408677333024e-05</v>
+        <v>4.7401913242479336e-05</v>
       </c>
       <c r="G13">
-        <v>-7.0516570278752119e-07</v>
+        <v>-7.2106363225308409e-07</v>
       </c>
       <c r="H13">
-        <v>2.3770926427101751e-07</v>
+        <v>2.5431908612260742e-07</v>
       </c>
       <c r="I13">
-        <v>-2.9780660796980464e-05</v>
+        <v>-2.9843770527605796e-05</v>
       </c>
       <c r="J13">
-        <v>-2.1731803636424753e-05</v>
+        <v>-2.2435771438959328e-05</v>
       </c>
       <c r="K13">
-        <v>0.0082985549939215315</v>
+        <v>0.0083174425108174348</v>
       </c>
       <c r="L13">
-        <v>0.0083109663353309726</v>
+        <v>0.0083300520549830764</v>
       </c>
       <c r="M13">
-        <v>0.0083438776297522464</v>
+        <v>0.0083631005278954496</v>
       </c>
       <c r="N13">
-        <v>0.0086893342071832115</v>
+        <v>0.0087092708959277138</v>
       </c>
       <c r="O13">
-        <v>-3.5069800268511275e-05</v>
+        <v>-3.6740225446297214e-05</v>
       </c>
       <c r="P13">
-        <v>-1.497059078441965e-05</v>
+        <v>-1.5325092418868761e-05</v>
       </c>
       <c r="Q13">
-        <v>-1.6954410243606868e-05</v>
+        <v>-1.7321796456453597e-05</v>
       </c>
       <c r="R13">
-        <v>-1.7618570052276386e-05</v>
+        <v>-1.8380531742525957e-05</v>
       </c>
       <c r="S13">
-        <v>-3.0955975819405522e-05</v>
+        <v>-3.1419540571314957e-05</v>
       </c>
       <c r="T13">
-        <v>2.0652545769368004e-05</v>
+        <v>2.0461576165022261e-05</v>
       </c>
       <c r="U13">
-        <v>-2.547821829792273e-05</v>
+        <v>-2.4944467072463328e-05</v>
       </c>
       <c r="V13">
-        <v>2.7384510137669768e-05</v>
+        <v>2.7813336893919011e-05</v>
       </c>
       <c r="W13">
-        <v>-0.0088014022867021775</v>
+        <v>-0.0088210926366561106</v>
       </c>
     </row>
     <row r="14">
@@ -4944,70 +4944,70 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>0.047730861148993373</v>
+        <v>0.044665837633688928</v>
       </c>
       <c r="C14">
-        <v>2.8229266893473244e-06</v>
+        <v>2.6908205779039368e-06</v>
       </c>
       <c r="D14">
-        <v>-3.303726107889257e-08</v>
+        <v>-3.1540914682322173e-08</v>
       </c>
       <c r="E14">
-        <v>2.599957346847167e-05</v>
+        <v>2.6625627524506123e-05</v>
       </c>
       <c r="F14">
-        <v>2.2028409212036811e-05</v>
+        <v>2.282328641040083e-05</v>
       </c>
       <c r="G14">
-        <v>-3.0470227802096388e-07</v>
+        <v>-3.1006659675244876e-07</v>
       </c>
       <c r="H14">
-        <v>-1.3503755523513163e-07</v>
+        <v>-1.4312763594037549e-07</v>
       </c>
       <c r="I14">
-        <v>-2.8389918702481635e-06</v>
+        <v>-2.7445511323062559e-06</v>
       </c>
       <c r="J14">
-        <v>-1.4742208723077788e-05</v>
+        <v>-1.4400891528318456e-05</v>
       </c>
       <c r="K14">
-        <v>1.2307005584410866e-05</v>
+        <v>1.0586429136039377e-05</v>
       </c>
       <c r="L14">
-        <v>-7.3782835128364404e-06</v>
+        <v>-8.3925004862748435e-06</v>
       </c>
       <c r="M14">
-        <v>-1.9062794287339976e-05</v>
+        <v>-2.0280159142167288e-05</v>
       </c>
       <c r="N14">
-        <v>-3.5069800268511275e-05</v>
+        <v>-3.6740225446297214e-05</v>
       </c>
       <c r="O14">
-        <v>0.00078788751528976477</v>
+        <v>0.00079146276760389857</v>
       </c>
       <c r="P14">
-        <v>0.00042442360439880693</v>
+        <v>0.00042680234977038626</v>
       </c>
       <c r="Q14">
-        <v>0.00042216584961812901</v>
+        <v>0.00042458049230776024</v>
       </c>
       <c r="R14">
-        <v>0.00042366929378590614</v>
+        <v>0.00042610579003990381</v>
       </c>
       <c r="S14">
-        <v>0.00042262458653135986</v>
+        <v>0.00042503162829690244</v>
       </c>
       <c r="T14">
-        <v>0.00042096771102720658</v>
+        <v>0.00042341226599239105</v>
       </c>
       <c r="U14">
-        <v>4.511674315152125e-06</v>
+        <v>4.6932215830166055e-06</v>
       </c>
       <c r="V14">
-        <v>5.955067363998736e-07</v>
+        <v>6.4666430914938073e-07</v>
       </c>
       <c r="W14">
-        <v>-0.00046041484561411771</v>
+        <v>-0.00045920424133217381</v>
       </c>
     </row>
     <row r="15">
@@ -5015,70 +5015,70 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>0.073644463486289766</v>
+        <v>0.075895006123659292</v>
       </c>
       <c r="C15">
-        <v>3.966196669338332e-06</v>
+        <v>3.9634462420549206e-06</v>
       </c>
       <c r="D15">
-        <v>-4.7734409116666451e-08</v>
+        <v>-4.8031299484466901e-08</v>
       </c>
       <c r="E15">
-        <v>3.0139903629620366e-05</v>
+        <v>2.9133457784574754e-05</v>
       </c>
       <c r="F15">
-        <v>-1.0838641651333534e-05</v>
+        <v>-1.2405574572347641e-05</v>
       </c>
       <c r="G15">
-        <v>-5.3078848873932977e-07</v>
+        <v>-5.0793801075564197e-07</v>
       </c>
       <c r="H15">
-        <v>7.0406438012282245e-07</v>
+        <v>7.3477227987356569e-07</v>
       </c>
       <c r="I15">
-        <v>1.0046695204955815e-05</v>
+        <v>1.0213125544215012e-05</v>
       </c>
       <c r="J15">
-        <v>-1.5373924110957966e-05</v>
+        <v>-1.5014695985072795e-05</v>
       </c>
       <c r="K15">
-        <v>3.7392509999887669e-05</v>
+        <v>3.7034334804804891e-05</v>
       </c>
       <c r="L15">
-        <v>1.1574224310175558e-05</v>
+        <v>1.1635983171439328e-05</v>
       </c>
       <c r="M15">
-        <v>6.1133393623238874e-06</v>
+        <v>6.0438681110631606e-06</v>
       </c>
       <c r="N15">
-        <v>-1.497059078441965e-05</v>
+        <v>-1.5325092418868761e-05</v>
       </c>
       <c r="O15">
-        <v>0.00042442360439880693</v>
+        <v>0.00042680234977038626</v>
       </c>
       <c r="P15">
-        <v>0.00094675269720894935</v>
+        <v>0.00095209424713423008</v>
       </c>
       <c r="Q15">
-        <v>0.00042214722913441744</v>
+        <v>0.00042457371932190974</v>
       </c>
       <c r="R15">
-        <v>0.00042438899469800776</v>
+        <v>0.00042679469348868638</v>
       </c>
       <c r="S15">
-        <v>0.00042329754278658846</v>
+        <v>0.00042573989361616475</v>
       </c>
       <c r="T15">
-        <v>0.00042305978563627678</v>
+        <v>0.00042550883480385127</v>
       </c>
       <c r="U15">
-        <v>-2.3792089849083077e-06</v>
+        <v>-2.9789803774232463e-06</v>
       </c>
       <c r="V15">
-        <v>-1.0135363846915328e-05</v>
+        <v>-1.0144597258308413e-05</v>
       </c>
       <c r="W15">
-        <v>-0.00051168780119030749</v>
+        <v>-0.00051328285815676581</v>
       </c>
     </row>
     <row r="16">
@@ -5086,70 +5086,70 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>-0.078750656186057547</v>
+        <v>-0.078559355519992241</v>
       </c>
       <c r="C16">
-        <v>2.4485614070246394e-06</v>
+        <v>2.4335226986637456e-06</v>
       </c>
       <c r="D16">
-        <v>-2.8193403910187247e-08</v>
+        <v>-2.8093261492609513e-08</v>
       </c>
       <c r="E16">
-        <v>1.6520134236658164e-05</v>
+        <v>1.5636866182581312e-05</v>
       </c>
       <c r="F16">
-        <v>-5.6215128617929705e-05</v>
+        <v>-5.6082656110512338e-05</v>
       </c>
       <c r="G16">
-        <v>-3.3794786108738866e-07</v>
+        <v>-3.0768773176249578e-07</v>
       </c>
       <c r="H16">
-        <v>8.5989235956969206e-07</v>
+        <v>8.6235231722208974e-07</v>
       </c>
       <c r="I16">
-        <v>-2.4553952783814192e-06</v>
+        <v>-2.4831665391248349e-06</v>
       </c>
       <c r="J16">
-        <v>-1.3802407198192849e-05</v>
+        <v>-1.3441947556693481e-05</v>
       </c>
       <c r="K16">
-        <v>2.5549619243840432e-05</v>
+        <v>2.5499859968154204e-05</v>
       </c>
       <c r="L16">
-        <v>4.278264441372339e-06</v>
+        <v>4.8432088118500886e-06</v>
       </c>
       <c r="M16">
-        <v>-9.1106574615597486e-06</v>
+        <v>-9.0207803534152328e-06</v>
       </c>
       <c r="N16">
-        <v>-1.6954410243606868e-05</v>
+        <v>-1.7321796456453597e-05</v>
       </c>
       <c r="O16">
-        <v>0.00042216584961812901</v>
+        <v>0.00042458049230776024</v>
       </c>
       <c r="P16">
-        <v>0.00042214722913441744</v>
+        <v>0.00042457371932190974</v>
       </c>
       <c r="Q16">
-        <v>0.000781690444002283</v>
+        <v>0.00078689575591916973</v>
       </c>
       <c r="R16">
-        <v>0.00042322053426806683</v>
+        <v>0.00042565890012678722</v>
       </c>
       <c r="S16">
-        <v>0.00042570182051519914</v>
+        <v>0.00042813268871159265</v>
       </c>
       <c r="T16">
-        <v>0.00042237196742181692</v>
+        <v>0.00042484622022401046</v>
       </c>
       <c r="U16">
-        <v>-8.433700117015425e-06</v>
+        <v>-8.4091661124160725e-06</v>
       </c>
       <c r="V16">
-        <v>-9.5689870257478539e-06</v>
+        <v>-9.598559698960017e-06</v>
       </c>
       <c r="W16">
-        <v>-0.00045272100484141194</v>
+        <v>-0.00045503111222629575</v>
       </c>
     </row>
     <row r="17">
@@ -5157,70 +5157,70 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>0.052858735945145424</v>
+        <v>0.049808799646905461</v>
       </c>
       <c r="C17">
-        <v>5.4005619281371689e-06</v>
+        <v>5.3475667911221148e-06</v>
       </c>
       <c r="D17">
-        <v>-5.9293833597263886e-08</v>
+        <v>-5.8791859272004374e-08</v>
       </c>
       <c r="E17">
-        <v>1.5319065618404014e-05</v>
+        <v>1.585609166826472e-05</v>
       </c>
       <c r="F17">
-        <v>-2.4961829883317909e-05</v>
+        <v>-2.4882826621797857e-05</v>
       </c>
       <c r="G17">
-        <v>-4.766370617079262e-07</v>
+        <v>-4.8158960944848539e-07</v>
       </c>
       <c r="H17">
-        <v>5.1460498825877545e-07</v>
+        <v>5.1579616379850797e-07</v>
       </c>
       <c r="I17">
-        <v>-4.2684872494050983e-06</v>
+        <v>-4.1943860419286646e-06</v>
       </c>
       <c r="J17">
-        <v>-1.6767369914502567e-05</v>
+        <v>-1.6690232790303464e-05</v>
       </c>
       <c r="K17">
-        <v>2.9361686160015165e-05</v>
+        <v>2.9369425247035511e-05</v>
       </c>
       <c r="L17">
-        <v>1.6779112074569375e-05</v>
+        <v>1.6952945242436227e-05</v>
       </c>
       <c r="M17">
-        <v>7.4634355775772413e-06</v>
+        <v>7.505536415173934e-06</v>
       </c>
       <c r="N17">
-        <v>-1.7618570052276386e-05</v>
+        <v>-1.8380531742525957e-05</v>
       </c>
       <c r="O17">
-        <v>0.00042366929378590614</v>
+        <v>0.00042610579003990381</v>
       </c>
       <c r="P17">
-        <v>0.00042438899469800776</v>
+        <v>0.00042679469348868638</v>
       </c>
       <c r="Q17">
-        <v>0.00042322053426806683</v>
+        <v>0.00042565890012678722</v>
       </c>
       <c r="R17">
-        <v>0.00065228594021584036</v>
+        <v>0.00065506845019029539</v>
       </c>
       <c r="S17">
-        <v>0.00042560259212658704</v>
+        <v>0.00042807596145240785</v>
       </c>
       <c r="T17">
-        <v>0.00042344558241930619</v>
+        <v>0.00042595954371383237</v>
       </c>
       <c r="U17">
-        <v>1.4478853865859706e-05</v>
+        <v>1.4332402949034842e-05</v>
       </c>
       <c r="V17">
-        <v>1.4669598420611913e-05</v>
+        <v>1.5137607980180931e-05</v>
       </c>
       <c r="W17">
-        <v>-0.00053495396980473664</v>
+        <v>-0.00053613896188978421</v>
       </c>
     </row>
     <row r="18">
@@ -5228,70 +5228,70 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>-0.16106599499737467</v>
+        <v>-0.16290734733350259</v>
       </c>
       <c r="C18">
-        <v>3.7941119332633169e-06</v>
+        <v>3.7934002192214932e-06</v>
       </c>
       <c r="D18">
-        <v>-4.0261836804159125e-08</v>
+        <v>-4.0427055481624849e-08</v>
       </c>
       <c r="E18">
-        <v>-1.0223069220110485e-05</v>
+        <v>-1.1666304287785337e-05</v>
       </c>
       <c r="F18">
-        <v>-9.5365212390587952e-05</v>
+        <v>-9.7056687944450552e-05</v>
       </c>
       <c r="G18">
-        <v>1.4481119756810726e-07</v>
+        <v>1.8668074382521674e-07</v>
       </c>
       <c r="H18">
-        <v>1.5035721594131189e-06</v>
+        <v>1.546394438380446e-06</v>
       </c>
       <c r="I18">
-        <v>2.0932982755478784e-06</v>
+        <v>2.1397193312234625e-06</v>
       </c>
       <c r="J18">
-        <v>-1.8532693821311366e-05</v>
+        <v>-1.847066177338908e-05</v>
       </c>
       <c r="K18">
-        <v>2.6052897418697094e-05</v>
+        <v>2.5490299116642237e-05</v>
       </c>
       <c r="L18">
-        <v>8.5049575997847311e-07</v>
+        <v>1.0130206111364534e-06</v>
       </c>
       <c r="M18">
-        <v>-8.2807623491552341e-06</v>
+        <v>-7.9589026881772388e-06</v>
       </c>
       <c r="N18">
-        <v>-3.0955975819405522e-05</v>
+        <v>-3.1419540571314957e-05</v>
       </c>
       <c r="O18">
-        <v>0.00042262458653135986</v>
+        <v>0.00042503162829690244</v>
       </c>
       <c r="P18">
-        <v>0.00042329754278658846</v>
+        <v>0.00042573989361616475</v>
       </c>
       <c r="Q18">
-        <v>0.00042570182051519914</v>
+        <v>0.00042813268871159265</v>
       </c>
       <c r="R18">
-        <v>0.00042560259212658704</v>
+        <v>0.00042807596145240785</v>
       </c>
       <c r="S18">
-        <v>0.00073552618280577434</v>
+        <v>0.00074008553137856639</v>
       </c>
       <c r="T18">
-        <v>0.00042567794357330685</v>
+        <v>0.00042826219681928011</v>
       </c>
       <c r="U18">
-        <v>1.1964294534219665e-06</v>
+        <v>1.1174810937961752e-06</v>
       </c>
       <c r="V18">
-        <v>-1.4660471262690201e-06</v>
+        <v>-1.6261100121297391e-06</v>
       </c>
       <c r="W18">
-        <v>-0.00048487283954277727</v>
+        <v>-0.00048725010414383017</v>
       </c>
     </row>
     <row r="19">
@@ -5299,70 +5299,70 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>-0.135825802120836</v>
+        <v>-0.13485782272844796</v>
       </c>
       <c r="C19">
-        <v>-2.260043436936677e-07</v>
+        <v>-6.4655709140265847e-08</v>
       </c>
       <c r="D19">
-        <v>5.7295706707113009e-09</v>
+        <v>3.7341562483775182e-09</v>
       </c>
       <c r="E19">
-        <v>-1.6559814167977748e-07</v>
+        <v>-2.5758658654818884e-07</v>
       </c>
       <c r="F19">
-        <v>-6.031309723040548e-05</v>
+        <v>-6.0964852193156274e-05</v>
       </c>
       <c r="G19">
-        <v>-1.8760321035369524e-07</v>
+        <v>-1.8504666670830908e-07</v>
       </c>
       <c r="H19">
-        <v>1.0564369302850906e-06</v>
+        <v>1.0627879244639522e-06</v>
       </c>
       <c r="I19">
-        <v>1.9162917473249433e-05</v>
+        <v>1.9888332058516673e-05</v>
       </c>
       <c r="J19">
-        <v>-7.5491457290265346e-06</v>
+        <v>-9.0537301972672647e-06</v>
       </c>
       <c r="K19">
-        <v>6.3604519814932238e-05</v>
+        <v>6.3528439298659805e-05</v>
       </c>
       <c r="L19">
-        <v>2.9610352200449452e-05</v>
+        <v>2.9900476401665128e-05</v>
       </c>
       <c r="M19">
-        <v>3.9261263618007132e-05</v>
+        <v>3.9688445556501515e-05</v>
       </c>
       <c r="N19">
-        <v>2.0652545769368004e-05</v>
+        <v>2.0461576165022261e-05</v>
       </c>
       <c r="O19">
-        <v>0.00042096771102720658</v>
+        <v>0.00042341226599239105</v>
       </c>
       <c r="P19">
-        <v>0.00042305978563627678</v>
+        <v>0.00042550883480385127</v>
       </c>
       <c r="Q19">
-        <v>0.00042237196742181692</v>
+        <v>0.00042484622022401046</v>
       </c>
       <c r="R19">
-        <v>0.00042344558241930619</v>
+        <v>0.00042595954371383237</v>
       </c>
       <c r="S19">
-        <v>0.00042567794357330685</v>
+        <v>0.00042826219681928011</v>
       </c>
       <c r="T19">
-        <v>0.0018658660179841919</v>
+        <v>0.0018722965194935702</v>
       </c>
       <c r="U19">
-        <v>9.4091446190515509e-06</v>
+        <v>9.2373642362989621e-06</v>
       </c>
       <c r="V19">
-        <v>1.0174472272877877e-05</v>
+        <v>1.0271877166896574e-05</v>
       </c>
       <c r="W19">
-        <v>-0.00046567019009640314</v>
+        <v>-0.00047109444147433671</v>
       </c>
     </row>
     <row r="20">
@@ -5370,70 +5370,70 @@
         <v>42</v>
       </c>
       <c r="B20">
-        <v>-0.15204688728582652</v>
+        <v>-0.15171461846593687</v>
       </c>
       <c r="C20">
-        <v>7.4443879859393309e-07</v>
+        <v>8.069340261440761e-07</v>
       </c>
       <c r="D20">
-        <v>-1.1439799954674747e-08</v>
+        <v>-1.2321991127483736e-08</v>
       </c>
       <c r="E20">
-        <v>1.5951222429015683e-05</v>
+        <v>1.5059445286503816e-05</v>
       </c>
       <c r="F20">
-        <v>3.2369995515503299e-05</v>
+        <v>3.1849958787050858e-05</v>
       </c>
       <c r="G20">
-        <v>-1.8809430049115851e-07</v>
+        <v>-1.5407544467246968e-07</v>
       </c>
       <c r="H20">
-        <v>-4.6454352798112921e-07</v>
+        <v>-4.5695583106736617e-07</v>
       </c>
       <c r="I20">
-        <v>-4.1330805374154734e-06</v>
+        <v>-4.15183881333172e-06</v>
       </c>
       <c r="J20">
-        <v>-6.1301798897019849e-06</v>
+        <v>-6.302902167343029e-06</v>
       </c>
       <c r="K20">
-        <v>-1.0893199412724915e-05</v>
+        <v>-1.0917210013414117e-05</v>
       </c>
       <c r="L20">
-        <v>-1.5517592066413316e-05</v>
+        <v>-1.5247802569949079e-05</v>
       </c>
       <c r="M20">
-        <v>-1.8194938227746931e-05</v>
+        <v>-1.8060678776986776e-05</v>
       </c>
       <c r="N20">
-        <v>-2.547821829792273e-05</v>
+        <v>-2.4944467072463328e-05</v>
       </c>
       <c r="O20">
-        <v>4.511674315152125e-06</v>
+        <v>4.6932215830166055e-06</v>
       </c>
       <c r="P20">
-        <v>-2.3792089849083077e-06</v>
+        <v>-2.9789803774232463e-06</v>
       </c>
       <c r="Q20">
-        <v>-8.433700117015425e-06</v>
+        <v>-8.4091661124160725e-06</v>
       </c>
       <c r="R20">
-        <v>1.4478853865859706e-05</v>
+        <v>1.4332402949034842e-05</v>
       </c>
       <c r="S20">
-        <v>1.1964294534219665e-06</v>
+        <v>1.1174810937961752e-06</v>
       </c>
       <c r="T20">
-        <v>9.4091446190515509e-06</v>
+        <v>9.2373642362989621e-06</v>
       </c>
       <c r="U20">
-        <v>0.00091154740707888294</v>
+        <v>0.00091580665741412359</v>
       </c>
       <c r="V20">
-        <v>6.4887733205119507e-05</v>
+        <v>6.5177998576722629e-05</v>
       </c>
       <c r="W20">
-        <v>-5.5688541172194622e-05</v>
+        <v>-5.700716726785389e-05</v>
       </c>
     </row>
     <row r="21">
@@ -5441,70 +5441,70 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>0.026663191684803276</v>
+        <v>0.026647917846439117</v>
       </c>
       <c r="C21">
-        <v>-1.2530163930393205e-06</v>
+        <v>-1.1644310149497e-06</v>
       </c>
       <c r="D21">
-        <v>1.1122820945452113e-08</v>
+        <v>1.0237557915597247e-08</v>
       </c>
       <c r="E21">
-        <v>2.8115213761436599e-05</v>
+        <v>2.7777225986964383e-05</v>
       </c>
       <c r="F21">
-        <v>4.3041152185741951e-05</v>
+        <v>4.4330517297866446e-05</v>
       </c>
       <c r="G21">
-        <v>-4.5847018074486989e-07</v>
+        <v>-4.4440045106206145e-07</v>
       </c>
       <c r="H21">
-        <v>-4.4799985437316903e-07</v>
+        <v>-4.835835820950629e-07</v>
       </c>
       <c r="I21">
-        <v>-3.5013528475145101e-06</v>
+        <v>-3.2352132206972869e-06</v>
       </c>
       <c r="J21">
-        <v>-8.6713804594057136e-06</v>
+        <v>-9.6927214389597718e-06</v>
       </c>
       <c r="K21">
-        <v>3.1086774629481877e-05</v>
+        <v>3.1208504634171185e-05</v>
       </c>
       <c r="L21">
-        <v>2.8611271935898903e-05</v>
+        <v>2.8923726321032941e-05</v>
       </c>
       <c r="M21">
-        <v>3.0842942201597627e-05</v>
+        <v>3.1319981314868425e-05</v>
       </c>
       <c r="N21">
-        <v>2.7384510137669768e-05</v>
+        <v>2.7813336893919011e-05</v>
       </c>
       <c r="O21">
-        <v>5.955067363998736e-07</v>
+        <v>6.4666430914938073e-07</v>
       </c>
       <c r="P21">
-        <v>-1.0135363846915328e-05</v>
+        <v>-1.0144597258308413e-05</v>
       </c>
       <c r="Q21">
-        <v>-9.5689870257478539e-06</v>
+        <v>-9.598559698960017e-06</v>
       </c>
       <c r="R21">
-        <v>1.4669598420611913e-05</v>
+        <v>1.5137607980180931e-05</v>
       </c>
       <c r="S21">
-        <v>-1.4660471262690201e-06</v>
+        <v>-1.6261100121297391e-06</v>
       </c>
       <c r="T21">
-        <v>1.0174472272877877e-05</v>
+        <v>1.0271877166896574e-05</v>
       </c>
       <c r="U21">
-        <v>6.4887733205119507e-05</v>
+        <v>6.5177998576722629e-05</v>
       </c>
       <c r="V21">
-        <v>0.001082927021884643</v>
+        <v>0.0010872144939252815</v>
       </c>
       <c r="W21">
-        <v>-6.4304610506759309e-05</v>
+        <v>-6.6831518294657922e-05</v>
       </c>
     </row>
     <row r="22">
@@ -5512,70 +5512,70 @@
         <v>44</v>
       </c>
       <c r="B22">
-        <v>-2.9550289227465547</v>
+        <v>-2.9594044678246787</v>
       </c>
       <c r="C22">
-        <v>-0.00059580463930211712</v>
+        <v>-0.00060316515687003835</v>
       </c>
       <c r="D22">
-        <v>6.2060900132489428e-06</v>
+        <v>6.2857373250009652e-06</v>
       </c>
       <c r="E22">
-        <v>-0.0023801401078947602</v>
+        <v>-0.0024038095953505842</v>
       </c>
       <c r="F22">
-        <v>-0.0017237712088299412</v>
+        <v>-0.001770431700220244</v>
       </c>
       <c r="G22">
-        <v>4.8074717002199028e-05</v>
+        <v>4.8533752831501739e-05</v>
       </c>
       <c r="H22">
-        <v>3.3253971797968724e-05</v>
+        <v>3.4140276008591438e-05</v>
       </c>
       <c r="I22">
-        <v>0.00025058448675194386</v>
+        <v>0.00024084293525438653</v>
       </c>
       <c r="J22">
-        <v>0.00073539763712275152</v>
+        <v>0.00075537537556103862</v>
       </c>
       <c r="K22">
-        <v>-0.0084058833483083573</v>
+        <v>-0.0084247799088486997</v>
       </c>
       <c r="L22">
-        <v>-0.0084661599263487521</v>
+        <v>-0.0084862620601519525</v>
       </c>
       <c r="M22">
-        <v>-0.008581535024973776</v>
+        <v>-0.0086001536817800328</v>
       </c>
       <c r="N22">
-        <v>-0.0088014022867021775</v>
+        <v>-0.0088210926366561106</v>
       </c>
       <c r="O22">
-        <v>-0.00046041484561411771</v>
+        <v>-0.00045920424133217381</v>
       </c>
       <c r="P22">
-        <v>-0.00051168780119030749</v>
+        <v>-0.00051328285815676581</v>
       </c>
       <c r="Q22">
-        <v>-0.00045272100484141194</v>
+        <v>-0.00045503111222629575</v>
       </c>
       <c r="R22">
-        <v>-0.00053495396980473664</v>
+        <v>-0.00053613896188978421</v>
       </c>
       <c r="S22">
-        <v>-0.00048487283954277727</v>
+        <v>-0.00048725010414383017</v>
       </c>
       <c r="T22">
-        <v>-0.00046567019009640314</v>
+        <v>-0.00047109444147433671</v>
       </c>
       <c r="U22">
-        <v>-5.5688541172194622e-05</v>
+        <v>-5.700716726785389e-05</v>
       </c>
       <c r="V22">
-        <v>-6.4304610506759309e-05</v>
+        <v>-6.6831518294657922e-05</v>
       </c>
       <c r="W22">
-        <v>0.022043792023922266</v>
+        <v>0.022221889399607741</v>
       </c>
     </row>
   </sheetData>
@@ -5663,70 +5663,70 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>0.17442859940526151</v>
+        <v>0.17441957349718201</v>
       </c>
       <c r="C2">
-        <v>2.3540481476380495e-05</v>
+        <v>2.3653216336438962e-05</v>
       </c>
       <c r="D2">
-        <v>-2.4690738897113527e-07</v>
+        <v>-2.4820806753585671e-07</v>
       </c>
       <c r="E2">
-        <v>8.6326187823058498e-05</v>
+        <v>8.6408013488834266e-05</v>
       </c>
       <c r="F2">
-        <v>6.7279629578022288e-05</v>
+        <v>6.7457607841798042e-05</v>
       </c>
       <c r="G2">
-        <v>-1.841771682607623e-06</v>
+        <v>-1.8434634246555212e-06</v>
       </c>
       <c r="H2">
-        <v>-1.4047848056821556e-06</v>
+        <v>-1.4081335535266328e-06</v>
       </c>
       <c r="I2">
-        <v>-8.3784328262538214e-06</v>
+        <v>-7.8965533249664074e-06</v>
       </c>
       <c r="J2">
-        <v>-3.26669937577565e-05</v>
+        <v>-3.3217205403445613e-05</v>
       </c>
       <c r="K2">
-        <v>3.8135368253258901e-06</v>
+        <v>3.8201189270419618e-06</v>
       </c>
       <c r="L2">
-        <v>4.1298777112637637e-06</v>
+        <v>4.1563256104613694e-06</v>
       </c>
       <c r="M2">
-        <v>5.4177598559751168e-06</v>
+        <v>5.428423587112085e-06</v>
       </c>
       <c r="N2">
-        <v>1.4982633842108601e-05</v>
+        <v>1.4927718324272082e-05</v>
       </c>
       <c r="O2">
-        <v>1.4492586215457886e-06</v>
+        <v>1.4887441034216219e-06</v>
       </c>
       <c r="P2">
-        <v>2.1257839484117095e-06</v>
+        <v>2.03229226350316e-06</v>
       </c>
       <c r="Q2">
-        <v>1.8089963045000926e-06</v>
+        <v>1.8156373648022923e-06</v>
       </c>
       <c r="R2">
-        <v>2.9204160683974874e-06</v>
+        <v>3.0239619789284084e-06</v>
       </c>
       <c r="S2">
-        <v>1.8904551487158973e-06</v>
+        <v>1.8997586306835277e-06</v>
       </c>
       <c r="T2">
-        <v>-6.6572586339490597e-07</v>
+        <v>-4.8436909280624247e-07</v>
       </c>
       <c r="U2">
-        <v>1.1732112743566433e-06</v>
+        <v>1.3015700873776471e-06</v>
       </c>
       <c r="V2">
-        <v>-2.8424526832009631e-06</v>
+        <v>-2.9098187938785718e-06</v>
       </c>
       <c r="W2">
-        <v>-0.00051560859631771924</v>
+        <v>-0.00051792998311778128</v>
       </c>
     </row>
     <row r="3">
@@ -5734,70 +5734,70 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>-0.001982681450141399</v>
+        <v>-0.0019832320296936652</v>
       </c>
       <c r="C3">
-        <v>-2.4690738897113527e-07</v>
+        <v>-2.4820806753585671e-07</v>
       </c>
       <c r="D3">
-        <v>2.7261971320221491e-09</v>
+        <v>2.7414406097762328e-09</v>
       </c>
       <c r="E3">
-        <v>-4.3319953195562748e-07</v>
+        <v>-4.3350434623869452e-07</v>
       </c>
       <c r="F3">
-        <v>-2.205601942484314e-07</v>
+        <v>-2.2204538131267579e-07</v>
       </c>
       <c r="G3">
-        <v>9.0139420847144023e-09</v>
+        <v>9.0230980078174794e-09</v>
       </c>
       <c r="H3">
-        <v>4.2066689288053733e-09</v>
+        <v>4.2372438593813441e-09</v>
       </c>
       <c r="I3">
-        <v>2.1102870308185995e-08</v>
+        <v>1.5068014277023063e-08</v>
       </c>
       <c r="J3">
-        <v>3.9420474748565146e-07</v>
+        <v>4.0099550812207758e-07</v>
       </c>
       <c r="K3">
-        <v>-4.1955528622624714e-08</v>
+        <v>-4.2365052368979701e-08</v>
       </c>
       <c r="L3">
-        <v>-4.1606169583271956e-08</v>
+        <v>-4.195761738377673e-08</v>
       </c>
       <c r="M3">
-        <v>-3.8288062129341314e-08</v>
+        <v>-3.8362252831692966e-08</v>
       </c>
       <c r="N3">
-        <v>-1.1131903512515188e-07</v>
+        <v>-1.1081216818507283e-07</v>
       </c>
       <c r="O3">
-        <v>-1.0633933954931216e-08</v>
+        <v>-1.1111336493412349e-08</v>
       </c>
       <c r="P3">
-        <v>-2.0288623176399256e-08</v>
+        <v>-1.9224342983125847e-08</v>
       </c>
       <c r="Q3">
-        <v>-1.5471502880211322e-08</v>
+        <v>-1.5591255410859481e-08</v>
       </c>
       <c r="R3">
-        <v>-2.7270549691602506e-08</v>
+        <v>-2.8460373058014049e-08</v>
       </c>
       <c r="S3">
-        <v>-1.743519163661006e-08</v>
+        <v>-1.7667353608075601e-08</v>
       </c>
       <c r="T3">
-        <v>9.075061433684419e-09</v>
+        <v>6.6560095154321312e-09</v>
       </c>
       <c r="U3">
-        <v>-1.245225106256128e-08</v>
+        <v>-1.3691669125166148e-08</v>
       </c>
       <c r="V3">
-        <v>2.4818422905359576e-08</v>
+        <v>2.5378159441799093e-08</v>
       </c>
       <c r="W3">
-        <v>5.1027282669180229e-06</v>
+        <v>5.1289228655816393e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5805,70 +5805,70 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>-0.22303604243477251</v>
+        <v>-0.22275121640299903</v>
       </c>
       <c r="C4">
-        <v>8.6326187823058498e-05</v>
+        <v>8.6408013488834266e-05</v>
       </c>
       <c r="D4">
-        <v>-4.3319953195562748e-07</v>
+        <v>-4.3350434623869452e-07</v>
       </c>
       <c r="E4">
-        <v>0.0052530126720557848</v>
+        <v>0.0052646824506722718</v>
       </c>
       <c r="F4">
-        <v>0.0023632006392280444</v>
+        <v>0.0023679355620368756</v>
       </c>
       <c r="G4">
-        <v>-0.00010769552662273962</v>
+        <v>-0.00010790667223245455</v>
       </c>
       <c r="H4">
-        <v>-4.8206448817158059e-05</v>
+        <v>-4.8290508043234794e-05</v>
       </c>
       <c r="I4">
-        <v>1.5140063761703109e-05</v>
+        <v>1.6549984870608197e-05</v>
       </c>
       <c r="J4">
-        <v>-7.5574110702302988e-05</v>
+        <v>-7.6911246156981567e-05</v>
       </c>
       <c r="K4">
-        <v>1.9026621487829628e-05</v>
+        <v>1.8594887747565162e-05</v>
       </c>
       <c r="L4">
-        <v>2.5377330503558154e-05</v>
+        <v>2.5256702000577653e-05</v>
       </c>
       <c r="M4">
-        <v>1.701013276155872e-05</v>
+        <v>1.7312353319764518e-05</v>
       </c>
       <c r="N4">
-        <v>3.4848488909314376e-05</v>
+        <v>3.4169145854522813e-05</v>
       </c>
       <c r="O4">
-        <v>4.5527246550326887e-05</v>
+        <v>4.5850450757501972e-05</v>
       </c>
       <c r="P4">
-        <v>2.2485546038093937e-05</v>
+        <v>2.2205987656579847e-05</v>
       </c>
       <c r="Q4">
-        <v>3.0269242733900469e-05</v>
+        <v>2.9608143243960488e-05</v>
       </c>
       <c r="R4">
-        <v>3.4038198616015766e-05</v>
+        <v>3.3770902387213425e-05</v>
       </c>
       <c r="S4">
-        <v>3.9166500075902682e-06</v>
+        <v>2.8341807186208341e-06</v>
       </c>
       <c r="T4">
-        <v>-1.797114129143143e-05</v>
+        <v>-2.0422293928908707e-05</v>
       </c>
       <c r="U4">
-        <v>1.0660073195828203e-05</v>
+        <v>1.1432320977549063e-05</v>
       </c>
       <c r="V4">
-        <v>1.7911249677234527e-05</v>
+        <v>1.8320606347170743e-05</v>
       </c>
       <c r="W4">
-        <v>-0.0031596309752217316</v>
+        <v>-0.0031633818660566052</v>
       </c>
     </row>
     <row r="5">
@@ -5876,70 +5876,70 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>-0.3681065448670513</v>
+        <v>-0.36570833073382869</v>
       </c>
       <c r="C5">
-        <v>6.7279629578022288e-05</v>
+        <v>6.7457607841798042e-05</v>
       </c>
       <c r="D5">
-        <v>-2.205601942484314e-07</v>
+        <v>-2.2204538131267579e-07</v>
       </c>
       <c r="E5">
-        <v>0.0023632006392280444</v>
+        <v>0.0023679355620368756</v>
       </c>
       <c r="F5">
-        <v>0.0042197355274177333</v>
+        <v>0.0042295931833614946</v>
       </c>
       <c r="G5">
-        <v>-4.828029927428279e-05</v>
+        <v>-4.8367082182713379e-05</v>
       </c>
       <c r="H5">
-        <v>-8.4900586554641382e-05</v>
+        <v>-8.5075806256518696e-05</v>
       </c>
       <c r="I5">
-        <v>2.1408138502450647e-05</v>
+        <v>2.3534372520484107e-05</v>
       </c>
       <c r="J5">
-        <v>-0.00010774041306279599</v>
+        <v>-0.00010982638060223331</v>
       </c>
       <c r="K5">
-        <v>1.7419654993261306e-05</v>
+        <v>1.6641639592278627e-05</v>
       </c>
       <c r="L5">
-        <v>-2.0851529617931658e-06</v>
+        <v>-1.7576749405986535e-06</v>
       </c>
       <c r="M5">
-        <v>-1.7230834154677863e-05</v>
+        <v>-1.6906245438257951e-05</v>
       </c>
       <c r="N5">
-        <v>3.2197462247023512e-05</v>
+        <v>3.1769177679788485e-05</v>
       </c>
       <c r="O5">
-        <v>5.2569146040668454e-05</v>
+        <v>5.2600385190004992e-05</v>
       </c>
       <c r="P5">
-        <v>3.2682154206748211e-05</v>
+        <v>3.2622738381269241e-05</v>
       </c>
       <c r="Q5">
-        <v>-1.0065880009931665e-05</v>
+        <v>-1.070565831753603e-05</v>
       </c>
       <c r="R5">
-        <v>9.8866562788718838e-06</v>
+        <v>9.2690361454529931e-06</v>
       </c>
       <c r="S5">
-        <v>-4.8109150269245218e-05</v>
+        <v>-4.8950482656448721e-05</v>
       </c>
       <c r="T5">
-        <v>-2.8828232449395916e-05</v>
+        <v>-3.0773233842658323e-05</v>
       </c>
       <c r="U5">
-        <v>3.3227023837756691e-05</v>
+        <v>3.3713068571135743e-05</v>
       </c>
       <c r="V5">
-        <v>1.9449267148431614e-05</v>
+        <v>1.8525096321798343e-05</v>
       </c>
       <c r="W5">
-        <v>-0.002716288639685099</v>
+        <v>-0.0027218393645978807</v>
       </c>
     </row>
     <row r="6">
@@ -5947,70 +5947,70 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>0.0024884314897051021</v>
+        <v>0.0024959611437965915</v>
       </c>
       <c r="C6">
-        <v>-1.841771682607623e-06</v>
+        <v>-1.8434634246555212e-06</v>
       </c>
       <c r="D6">
-        <v>9.0139420847144023e-09</v>
+        <v>9.0230980078174794e-09</v>
       </c>
       <c r="E6">
-        <v>-0.00010769552662273962</v>
+        <v>-0.00010790667223245455</v>
       </c>
       <c r="F6">
-        <v>-4.828029927428279e-05</v>
+        <v>-4.8367082182713379e-05</v>
       </c>
       <c r="G6">
-        <v>2.3747427634620731e-06</v>
+        <v>2.3784752538931853e-06</v>
       </c>
       <c r="H6">
-        <v>1.0557914605659875e-06</v>
+        <v>1.0573045182685934e-06</v>
       </c>
       <c r="I6">
-        <v>-4.9441835118983433e-07</v>
+        <v>-5.2512357571415426e-07</v>
       </c>
       <c r="J6">
-        <v>1.7788426622228975e-06</v>
+        <v>1.807452026875073e-06</v>
       </c>
       <c r="K6">
-        <v>-5.6989828509411284e-07</v>
+        <v>-5.610257151061379e-07</v>
       </c>
       <c r="L6">
-        <v>-6.9025219356646058e-07</v>
+        <v>-6.8888894900172109e-07</v>
       </c>
       <c r="M6">
-        <v>-2.2880282408566839e-07</v>
+        <v>-2.3530083083896913e-07</v>
       </c>
       <c r="N6">
-        <v>-4.4683293823429392e-07</v>
+        <v>-4.3244651287649999e-07</v>
       </c>
       <c r="O6">
-        <v>-8.9551885398833311e-07</v>
+        <v>-9.0399812006259743e-07</v>
       </c>
       <c r="P6">
-        <v>-2.3032673164631348e-07</v>
+        <v>-2.2536731230999098e-07</v>
       </c>
       <c r="Q6">
-        <v>-7.6771661917475667e-07</v>
+        <v>-7.5139241710276621e-07</v>
       </c>
       <c r="R6">
-        <v>-7.7994779567172666e-07</v>
+        <v>-7.7944983956979658e-07</v>
       </c>
       <c r="S6">
-        <v>-2.1150540845897405e-07</v>
+        <v>-1.8987809407692353e-07</v>
       </c>
       <c r="T6">
-        <v>3.0132978253550991e-07</v>
+        <v>3.4386245143992356e-07</v>
       </c>
       <c r="U6">
-        <v>-2.528205994179068e-07</v>
+        <v>-2.7005505003890763e-07</v>
       </c>
       <c r="V6">
-        <v>-2.9313864847253634e-07</v>
+        <v>-3.0177493836406789e-07</v>
       </c>
       <c r="W6">
-        <v>6.4544112324254916e-05</v>
+        <v>6.4616123727413073e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6018,70 +6018,70 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>0.0018072833798249547</v>
+        <v>0.0017946439855713201</v>
       </c>
       <c r="C7">
-        <v>-1.4047848056821556e-06</v>
+        <v>-1.4081335535266328e-06</v>
       </c>
       <c r="D7">
-        <v>4.2066689288053733e-09</v>
+        <v>4.2372438593813441e-09</v>
       </c>
       <c r="E7">
-        <v>-4.8206448817158059e-05</v>
+        <v>-4.8290508043234794e-05</v>
       </c>
       <c r="F7">
-        <v>-8.4900586554641382e-05</v>
+        <v>-8.5075806256518696e-05</v>
       </c>
       <c r="G7">
-        <v>1.0557914605659875e-06</v>
+        <v>1.0573045182685934e-06</v>
       </c>
       <c r="H7">
-        <v>1.8319155251811902e-06</v>
+        <v>1.8350158717330006e-06</v>
       </c>
       <c r="I7">
-        <v>-7.7768997739940933e-07</v>
+        <v>-8.2461717323305428e-07</v>
       </c>
       <c r="J7">
-        <v>2.4492094754093477e-06</v>
+        <v>2.4958049621340877e-06</v>
       </c>
       <c r="K7">
-        <v>-2.939926663553366e-07</v>
+        <v>-2.804823844159378e-07</v>
       </c>
       <c r="L7">
-        <v>2.6043621860971037e-07</v>
+        <v>2.5176871281655064e-07</v>
       </c>
       <c r="M7">
-        <v>1.1239820612721362e-06</v>
+        <v>1.1183227139817159e-06</v>
       </c>
       <c r="N7">
-        <v>4.457761217491508e-07</v>
+        <v>4.5813655212707986e-07</v>
       </c>
       <c r="O7">
-        <v>-8.1171599895270211e-07</v>
+        <v>-8.1067390634716506e-07</v>
       </c>
       <c r="P7">
-        <v>-6.729975605870186e-08</v>
+        <v>-6.502496964190471e-08</v>
       </c>
       <c r="Q7">
-        <v>-3.5189121771052658e-07</v>
+        <v>-3.376908544652675e-07</v>
       </c>
       <c r="R7">
-        <v>-1.4947989252864334e-07</v>
+        <v>-1.4331432780875421e-07</v>
       </c>
       <c r="S7">
-        <v>5.2467382060500317e-07</v>
+        <v>5.4114081621088774e-07</v>
       </c>
       <c r="T7">
-        <v>5.0367721789776936e-07</v>
+        <v>5.357136052397941e-07</v>
       </c>
       <c r="U7">
-        <v>-6.4949585722650761e-07</v>
+        <v>-6.6007886198071827e-07</v>
       </c>
       <c r="V7">
-        <v>-2.397107008800051e-07</v>
+        <v>-2.2294268233629018e-07</v>
       </c>
       <c r="W7">
-        <v>5.3759915239246632e-05</v>
+        <v>5.3859539755439353e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6089,70 +6089,70 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>0.18118017266028952</v>
+        <v>0.17952524860044669</v>
       </c>
       <c r="C8">
-        <v>-8.3784328262538214e-06</v>
+        <v>-7.8965533249664074e-06</v>
       </c>
       <c r="D8">
-        <v>2.1102870308185995e-08</v>
+        <v>1.5068014277023063e-08</v>
       </c>
       <c r="E8">
-        <v>1.5140063761703109e-05</v>
+        <v>1.6549984870608197e-05</v>
       </c>
       <c r="F8">
-        <v>2.1408138502450647e-05</v>
+        <v>2.3534372520484107e-05</v>
       </c>
       <c r="G8">
-        <v>-4.9441835118983433e-07</v>
+        <v>-5.2512357571415426e-07</v>
       </c>
       <c r="H8">
-        <v>-7.7768997739940933e-07</v>
+        <v>-8.2461717323305428e-07</v>
       </c>
       <c r="I8">
-        <v>0.00039252652657021818</v>
+        <v>0.00039689609939575073</v>
       </c>
       <c r="J8">
-        <v>-0.0001925530822904217</v>
+        <v>-0.00019742129769217796</v>
       </c>
       <c r="K8">
-        <v>-1.430822479609374e-05</v>
+        <v>-1.4019610193710646e-05</v>
       </c>
       <c r="L8">
-        <v>-1.3360498493370884e-05</v>
+        <v>-1.3140519018680742e-05</v>
       </c>
       <c r="M8">
-        <v>-1.9186665910185408e-05</v>
+        <v>-1.9336077266941346e-05</v>
       </c>
       <c r="N8">
-        <v>-2.0610247432579201e-05</v>
+        <v>-2.0733365363726523e-05</v>
       </c>
       <c r="O8">
-        <v>3.5781469862081961e-06</v>
+        <v>3.5436580866210084e-06</v>
       </c>
       <c r="P8">
-        <v>-5.886360260662342e-06</v>
+        <v>-6.3062673897952084e-06</v>
       </c>
       <c r="Q8">
-        <v>1.5912262714970239e-07</v>
+        <v>6.4266253342069854e-08</v>
       </c>
       <c r="R8">
-        <v>-3.7783358534563469e-06</v>
+        <v>-3.7232696090030961e-06</v>
       </c>
       <c r="S8">
-        <v>-8.2011121265418905e-06</v>
+        <v>-8.250902906451324e-06</v>
       </c>
       <c r="T8">
-        <v>5.2804444345689541e-06</v>
+        <v>5.7062722753078933e-06</v>
       </c>
       <c r="U8">
-        <v>2.0687404830747441e-07</v>
+        <v>1.667930938045684e-07</v>
       </c>
       <c r="V8">
-        <v>1.2270848759757568e-05</v>
+        <v>1.2450794712038474e-05</v>
       </c>
       <c r="W8">
-        <v>0.00017673063316534754</v>
+        <v>0.00016783263513429428</v>
       </c>
     </row>
     <row r="9">
@@ -6160,70 +6160,70 @@
         <v>31</v>
       </c>
       <c r="B9">
-        <v>0.0084346163214327717</v>
+        <v>0.011141269386880072</v>
       </c>
       <c r="C9">
-        <v>-3.26669937577565e-05</v>
+        <v>-3.3217205403445613e-05</v>
       </c>
       <c r="D9">
-        <v>3.9420474748565146e-07</v>
+        <v>4.0099550812207758e-07</v>
       </c>
       <c r="E9">
-        <v>-7.5574110702302988e-05</v>
+        <v>-7.6911246156981567e-05</v>
       </c>
       <c r="F9">
-        <v>-0.00010774041306279599</v>
+        <v>-0.00010982638060223331</v>
       </c>
       <c r="G9">
-        <v>1.7788426622228975e-06</v>
+        <v>1.807452026875073e-06</v>
       </c>
       <c r="H9">
-        <v>2.4492094754093477e-06</v>
+        <v>2.4958049621340877e-06</v>
       </c>
       <c r="I9">
-        <v>-0.0001925530822904217</v>
+        <v>-0.00019742129769217796</v>
       </c>
       <c r="J9">
-        <v>0.00038738937217769977</v>
+        <v>0.00039101346861878289</v>
       </c>
       <c r="K9">
-        <v>-9.5594446015547581e-07</v>
+        <v>-1.7446192468079135e-06</v>
       </c>
       <c r="L9">
-        <v>-6.7261859159997749e-06</v>
+        <v>-7.086421962048642e-06</v>
       </c>
       <c r="M9">
-        <v>-1.3352235170336306e-05</v>
+        <v>-1.3000399484950346e-05</v>
       </c>
       <c r="N9">
-        <v>-1.2568228752221557e-05</v>
+        <v>-1.2195986185794703e-05</v>
       </c>
       <c r="O9">
-        <v>-9.8776580981759437e-06</v>
+        <v>-9.8711444358592342e-06</v>
       </c>
       <c r="P9">
-        <v>-5.2227460761625133e-06</v>
+        <v>-4.2932516950534637e-06</v>
       </c>
       <c r="Q9">
-        <v>-7.756584569302615e-06</v>
+        <v>-7.4470725386476121e-06</v>
       </c>
       <c r="R9">
-        <v>-9.1967218759688907e-06</v>
+        <v>-9.2957689913393204e-06</v>
       </c>
       <c r="S9">
-        <v>-1.4450608672886047e-05</v>
+        <v>-1.4179326848369978e-05</v>
       </c>
       <c r="T9">
-        <v>3.6155749779488691e-06</v>
+        <v>2.2331090593866136e-06</v>
       </c>
       <c r="U9">
-        <v>-5.6013434902318745e-06</v>
+        <v>-6.0341965785401773e-06</v>
       </c>
       <c r="V9">
-        <v>-4.1956606850279706e-06</v>
+        <v>-4.3447695952284772e-06</v>
       </c>
       <c r="W9">
-        <v>0.00061800271623847585</v>
+        <v>0.00062828002645894045</v>
       </c>
     </row>
     <row r="10">
@@ -6231,70 +6231,70 @@
         <v>32</v>
       </c>
       <c r="B10">
-        <v>0.18317355276611266</v>
+        <v>0.18164741490466885</v>
       </c>
       <c r="C10">
-        <v>3.8135368253258901e-06</v>
+        <v>3.8201189270419618e-06</v>
       </c>
       <c r="D10">
-        <v>-4.1955528622624714e-08</v>
+        <v>-4.2365052368979701e-08</v>
       </c>
       <c r="E10">
-        <v>1.9026621487829628e-05</v>
+        <v>1.8594887747565162e-05</v>
       </c>
       <c r="F10">
-        <v>1.7419654993261306e-05</v>
+        <v>1.6641639592278627e-05</v>
       </c>
       <c r="G10">
-        <v>-5.6989828509411284e-07</v>
+        <v>-5.610257151061379e-07</v>
       </c>
       <c r="H10">
-        <v>-2.939926663553366e-07</v>
+        <v>-2.804823844159378e-07</v>
       </c>
       <c r="I10">
-        <v>-1.430822479609374e-05</v>
+        <v>-1.4019610193710646e-05</v>
       </c>
       <c r="J10">
-        <v>-9.5594446015547581e-07</v>
+        <v>-1.7446192468079135e-06</v>
       </c>
       <c r="K10">
-        <v>0.0091287707700556265</v>
+        <v>0.0091321539298681899</v>
       </c>
       <c r="L10">
-        <v>0.0075787279332324032</v>
+        <v>0.00758031571176623</v>
       </c>
       <c r="M10">
-        <v>0.0075769016576795753</v>
+        <v>0.0075784221761371201</v>
       </c>
       <c r="N10">
-        <v>0.0075749332213773295</v>
+        <v>0.007576305581060626</v>
       </c>
       <c r="O10">
-        <v>1.2066759158126881e-05</v>
+        <v>1.2421228453616872e-05</v>
       </c>
       <c r="P10">
-        <v>9.214418427847123e-06</v>
+        <v>9.2529956072158774e-06</v>
       </c>
       <c r="Q10">
-        <v>-1.7769371088324239e-05</v>
+        <v>-1.7708136540186208e-05</v>
       </c>
       <c r="R10">
-        <v>-8.4978045359928363e-06</v>
+        <v>-8.3200992319852065e-06</v>
       </c>
       <c r="S10">
-        <v>3.3824494668758707e-06</v>
+        <v>3.4636756817547866e-06</v>
       </c>
       <c r="T10">
-        <v>1.481619248703994e-05</v>
+        <v>1.491369661422263e-05</v>
       </c>
       <c r="U10">
-        <v>1.3310316153190914e-07</v>
+        <v>7.3133474030168382e-07</v>
       </c>
       <c r="V10">
-        <v>-7.2460163601834341e-06</v>
+        <v>-7.2531352844108895e-06</v>
       </c>
       <c r="W10">
-        <v>-0.0076458550531630643</v>
+        <v>-0.0076467330770613991</v>
       </c>
     </row>
     <row r="11">
@@ -6302,70 +6302,70 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>0.66015162492825919</v>
+        <v>0.66157334877777085</v>
       </c>
       <c r="C11">
-        <v>4.1298777112637637e-06</v>
+        <v>4.1563256104613694e-06</v>
       </c>
       <c r="D11">
-        <v>-4.1606169583271956e-08</v>
+        <v>-4.195761738377673e-08</v>
       </c>
       <c r="E11">
-        <v>2.5377330503558154e-05</v>
+        <v>2.5256702000577653e-05</v>
       </c>
       <c r="F11">
-        <v>-2.0851529617931658e-06</v>
+        <v>-1.7576749405986535e-06</v>
       </c>
       <c r="G11">
-        <v>-6.9025219356646058e-07</v>
+        <v>-6.8888894900172109e-07</v>
       </c>
       <c r="H11">
-        <v>2.6043621860971037e-07</v>
+        <v>2.5176871281655064e-07</v>
       </c>
       <c r="I11">
-        <v>-1.3360498493370884e-05</v>
+        <v>-1.3140519018680742e-05</v>
       </c>
       <c r="J11">
-        <v>-6.7261859159997749e-06</v>
+        <v>-7.086421962048642e-06</v>
       </c>
       <c r="K11">
-        <v>0.0075787279332324032</v>
+        <v>0.00758031571176623</v>
       </c>
       <c r="L11">
-        <v>0.0078798369488180947</v>
+        <v>0.00788210296748822</v>
       </c>
       <c r="M11">
-        <v>0.0075829129875069155</v>
+        <v>0.0075844446249812066</v>
       </c>
       <c r="N11">
-        <v>0.0075853494344380792</v>
+        <v>0.0075868582307381822</v>
       </c>
       <c r="O11">
-        <v>1.0946253038199972e-05</v>
+        <v>1.1085000429976861e-05</v>
       </c>
       <c r="P11">
-        <v>1.6896487130998159e-07</v>
+        <v>3.5105525446026543e-07</v>
       </c>
       <c r="Q11">
-        <v>-3.0271987084079494e-05</v>
+        <v>-3.0195715737612005e-05</v>
       </c>
       <c r="R11">
-        <v>-1.4824240716207742e-05</v>
+        <v>-1.4715440560455058e-05</v>
       </c>
       <c r="S11">
-        <v>-6.0374694249166864e-06</v>
+        <v>-6.0205819075949993e-06</v>
       </c>
       <c r="T11">
-        <v>3.4151414074549665e-07</v>
+        <v>4.4946440056452134e-07</v>
       </c>
       <c r="U11">
-        <v>1.707739533103869e-06</v>
+        <v>1.7034134946836298e-06</v>
       </c>
       <c r="V11">
-        <v>-8.1754913156325658e-06</v>
+        <v>-8.1473352704591869e-06</v>
       </c>
       <c r="W11">
-        <v>-0.0076619075026903684</v>
+        <v>-0.007663895437148782</v>
       </c>
     </row>
     <row r="12">
@@ -6373,70 +6373,70 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0.87334503596806046</v>
+        <v>0.8726881507313855</v>
       </c>
       <c r="C12">
-        <v>5.4177598559751168e-06</v>
+        <v>5.428423587112085e-06</v>
       </c>
       <c r="D12">
-        <v>-3.8288062129341314e-08</v>
+        <v>-3.8362252831692966e-08</v>
       </c>
       <c r="E12">
-        <v>1.701013276155872e-05</v>
+        <v>1.7312353319764518e-05</v>
       </c>
       <c r="F12">
-        <v>-1.7230834154677863e-05</v>
+        <v>-1.6906245438257951e-05</v>
       </c>
       <c r="G12">
-        <v>-2.2880282408566839e-07</v>
+        <v>-2.3530083083896913e-07</v>
       </c>
       <c r="H12">
-        <v>1.1239820612721362e-06</v>
+        <v>1.1183227139817159e-06</v>
       </c>
       <c r="I12">
-        <v>-1.9186665910185408e-05</v>
+        <v>-1.9336077266941346e-05</v>
       </c>
       <c r="J12">
-        <v>-1.3352235170336306e-05</v>
+        <v>-1.3000399484950346e-05</v>
       </c>
       <c r="K12">
-        <v>0.0075769016576795753</v>
+        <v>0.0075784221761371201</v>
       </c>
       <c r="L12">
-        <v>0.0075829129875069155</v>
+        <v>0.0075844446249812066</v>
       </c>
       <c r="M12">
-        <v>0.0076829782088214289</v>
+        <v>0.0076845395875990326</v>
       </c>
       <c r="N12">
-        <v>0.0076175042916605089</v>
+        <v>0.0076189897261084057</v>
       </c>
       <c r="O12">
-        <v>9.1514009541485662e-06</v>
+        <v>9.1360213707919382e-06</v>
       </c>
       <c r="P12">
-        <v>-5.4263467083948212e-06</v>
+        <v>-5.4254068739799388e-06</v>
       </c>
       <c r="Q12">
-        <v>-3.6030654339676646e-05</v>
+        <v>-3.6055582464771435e-05</v>
       </c>
       <c r="R12">
-        <v>-1.4222841955696582e-05</v>
+        <v>-1.4073670842270405e-05</v>
       </c>
       <c r="S12">
-        <v>-9.5051060439650973e-06</v>
+        <v>-9.5464824860947036e-06</v>
       </c>
       <c r="T12">
-        <v>1.8040122792191925e-05</v>
+        <v>1.8321113575335866e-05</v>
       </c>
       <c r="U12">
-        <v>-2.545610202908781e-06</v>
+        <v>-2.4277793420343909e-06</v>
       </c>
       <c r="V12">
-        <v>-6.110561385893571e-06</v>
+        <v>-5.9753852560077972e-06</v>
       </c>
       <c r="W12">
-        <v>-0.007751660929322811</v>
+        <v>-0.0077535733879639298</v>
       </c>
     </row>
     <row r="13">
@@ -6444,70 +6444,70 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>0.93043534444253428</v>
+        <v>0.92818931514050085</v>
       </c>
       <c r="C13">
-        <v>1.4982633842108601e-05</v>
+        <v>1.4927718324272082e-05</v>
       </c>
       <c r="D13">
-        <v>-1.1131903512515188e-07</v>
+        <v>-1.1081216818507283e-07</v>
       </c>
       <c r="E13">
-        <v>3.4848488909314376e-05</v>
+        <v>3.4169145854522813e-05</v>
       </c>
       <c r="F13">
-        <v>3.2197462247023512e-05</v>
+        <v>3.1769177679788485e-05</v>
       </c>
       <c r="G13">
-        <v>-4.4683293823429392e-07</v>
+        <v>-4.3244651287649999e-07</v>
       </c>
       <c r="H13">
-        <v>4.457761217491508e-07</v>
+        <v>4.5813655212707986e-07</v>
       </c>
       <c r="I13">
-        <v>-2.0610247432579201e-05</v>
+        <v>-2.0733365363726523e-05</v>
       </c>
       <c r="J13">
-        <v>-1.2568228752221557e-05</v>
+        <v>-1.2195986185794703e-05</v>
       </c>
       <c r="K13">
-        <v>0.0075749332213773295</v>
+        <v>0.007576305581060626</v>
       </c>
       <c r="L13">
-        <v>0.0075853494344380792</v>
+        <v>0.0075868582307381822</v>
       </c>
       <c r="M13">
-        <v>0.0076175042916605089</v>
+        <v>0.0076189897261084057</v>
       </c>
       <c r="N13">
-        <v>0.0079487363934019929</v>
+        <v>0.0079500572457554576</v>
       </c>
       <c r="O13">
-        <v>-2.7626626719943299e-07</v>
+        <v>-4.090095516640004e-07</v>
       </c>
       <c r="P13">
-        <v>-1.6484606955236573e-05</v>
+        <v>-1.6549812709951427e-05</v>
       </c>
       <c r="Q13">
-        <v>-4.1697871549088424e-05</v>
+        <v>-4.2011316991313706e-05</v>
       </c>
       <c r="R13">
-        <v>-3.5121561303235003e-05</v>
+        <v>-3.5294802414292487e-05</v>
       </c>
       <c r="S13">
-        <v>-2.8907810716398229e-05</v>
+        <v>-2.9122395137945201e-05</v>
       </c>
       <c r="T13">
-        <v>-2.1462327603964768e-06</v>
+        <v>-1.8017249153346609e-06</v>
       </c>
       <c r="U13">
-        <v>-1.0478736349004337e-05</v>
+        <v>-9.9841911143385114e-06</v>
       </c>
       <c r="V13">
-        <v>-1.2285942338857328e-05</v>
+        <v>-1.2043613251549614e-05</v>
       </c>
       <c r="W13">
-        <v>-0.0080401891750455576</v>
+        <v>-0.0080403468402342401</v>
       </c>
     </row>
     <row r="14">
@@ -6515,70 +6515,70 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>0.069190686957279243</v>
+        <v>0.068998076444433107</v>
       </c>
       <c r="C14">
-        <v>1.4492586215457886e-06</v>
+        <v>1.4887441034216219e-06</v>
       </c>
       <c r="D14">
-        <v>-1.0633933954931216e-08</v>
+        <v>-1.1111336493412349e-08</v>
       </c>
       <c r="E14">
-        <v>4.5527246550326887e-05</v>
+        <v>4.5850450757501972e-05</v>
       </c>
       <c r="F14">
-        <v>5.2569146040668454e-05</v>
+        <v>5.2600385190004992e-05</v>
       </c>
       <c r="G14">
-        <v>-8.9551885398833311e-07</v>
+        <v>-9.0399812006259743e-07</v>
       </c>
       <c r="H14">
-        <v>-8.1171599895270211e-07</v>
+        <v>-8.1067390634716506e-07</v>
       </c>
       <c r="I14">
-        <v>3.5781469862081961e-06</v>
+        <v>3.5436580866210084e-06</v>
       </c>
       <c r="J14">
-        <v>-9.8776580981759437e-06</v>
+        <v>-9.8711444358592342e-06</v>
       </c>
       <c r="K14">
-        <v>1.2066759158126881e-05</v>
+        <v>1.2421228453616872e-05</v>
       </c>
       <c r="L14">
-        <v>1.0946253038199972e-05</v>
+        <v>1.1085000429976861e-05</v>
       </c>
       <c r="M14">
-        <v>9.1514009541485662e-06</v>
+        <v>9.1360213707919382e-06</v>
       </c>
       <c r="N14">
-        <v>-2.7626626719943299e-07</v>
+        <v>-4.090095516640004e-07</v>
       </c>
       <c r="O14">
-        <v>0.00077000748332730175</v>
+        <v>0.00077009147491231692</v>
       </c>
       <c r="P14">
-        <v>0.00041717281603157553</v>
+        <v>0.00041716814642973839</v>
       </c>
       <c r="Q14">
-        <v>0.00041384963517607525</v>
+        <v>0.00041383367747480039</v>
       </c>
       <c r="R14">
-        <v>0.00041626155201825019</v>
+        <v>0.0004162682087066788</v>
       </c>
       <c r="S14">
-        <v>0.00041442414588120457</v>
+        <v>0.00041440486610124134</v>
       </c>
       <c r="T14">
-        <v>0.00041478874938270745</v>
+        <v>0.00041476956488913845</v>
       </c>
       <c r="U14">
-        <v>6.073500478057615e-06</v>
+        <v>6.6022638563916448e-06</v>
       </c>
       <c r="V14">
-        <v>4.6126928665743164e-06</v>
+        <v>4.5790182839544131e-06</v>
       </c>
       <c r="W14">
-        <v>-0.00047283649417752971</v>
+        <v>-0.00047355690283225961</v>
       </c>
     </row>
     <row r="15">
@@ -6586,70 +6586,70 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>0.024647006097917118</v>
+        <v>0.025969852097722155</v>
       </c>
       <c r="C15">
-        <v>2.1257839484117095e-06</v>
+        <v>2.03229226350316e-06</v>
       </c>
       <c r="D15">
-        <v>-2.0288623176399256e-08</v>
+        <v>-1.9224342983125847e-08</v>
       </c>
       <c r="E15">
-        <v>2.2485546038093937e-05</v>
+        <v>2.2205987656579847e-05</v>
       </c>
       <c r="F15">
-        <v>3.2682154206748211e-05</v>
+        <v>3.2622738381269241e-05</v>
       </c>
       <c r="G15">
-        <v>-2.3032673164631348e-07</v>
+        <v>-2.2536731230999098e-07</v>
       </c>
       <c r="H15">
-        <v>-6.729975605870186e-08</v>
+        <v>-6.502496964190471e-08</v>
       </c>
       <c r="I15">
-        <v>-5.886360260662342e-06</v>
+        <v>-6.3062673897952084e-06</v>
       </c>
       <c r="J15">
-        <v>-5.2227460761625133e-06</v>
+        <v>-4.2932516950534637e-06</v>
       </c>
       <c r="K15">
-        <v>9.214418427847123e-06</v>
+        <v>9.2529956072158774e-06</v>
       </c>
       <c r="L15">
-        <v>1.6896487130998159e-07</v>
+        <v>3.5105525446026543e-07</v>
       </c>
       <c r="M15">
-        <v>-5.4263467083948212e-06</v>
+        <v>-5.4254068739799388e-06</v>
       </c>
       <c r="N15">
-        <v>-1.6484606955236573e-05</v>
+        <v>-1.6549812709951427e-05</v>
       </c>
       <c r="O15">
-        <v>0.00041717281603157553</v>
+        <v>0.00041716814642973839</v>
       </c>
       <c r="P15">
-        <v>0.00093504658143020393</v>
+        <v>0.00093609830986330809</v>
       </c>
       <c r="Q15">
-        <v>0.00041282945650045281</v>
+        <v>0.00041280913728009461</v>
       </c>
       <c r="R15">
-        <v>0.00041672751216224099</v>
+        <v>0.00041668703233415565</v>
       </c>
       <c r="S15">
-        <v>0.0004142531003056002</v>
+        <v>0.00041419995165539362</v>
       </c>
       <c r="T15">
-        <v>0.00041471591399255483</v>
+        <v>0.00041466491513443587</v>
       </c>
       <c r="U15">
-        <v>-2.1115892635215897e-06</v>
+        <v>-1.7432117282338792e-06</v>
       </c>
       <c r="V15">
-        <v>-1.2822743613043456e-05</v>
+        <v>-1.2584826548470499e-05</v>
       </c>
       <c r="W15">
-        <v>-0.00047078789341754629</v>
+        <v>-0.00046895674276341081</v>
       </c>
     </row>
     <row r="16">
@@ -6657,70 +6657,70 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>-0.069678774954667982</v>
+        <v>-0.070976755656184512</v>
       </c>
       <c r="C16">
-        <v>1.8089963045000926e-06</v>
+        <v>1.8156373648022923e-06</v>
       </c>
       <c r="D16">
-        <v>-1.5471502880211322e-08</v>
+        <v>-1.5591255410859481e-08</v>
       </c>
       <c r="E16">
-        <v>3.0269242733900469e-05</v>
+        <v>2.9608143243960488e-05</v>
       </c>
       <c r="F16">
-        <v>-1.0065880009931665e-05</v>
+        <v>-1.070565831753603e-05</v>
       </c>
       <c r="G16">
-        <v>-7.6771661917475667e-07</v>
+        <v>-7.5139241710276621e-07</v>
       </c>
       <c r="H16">
-        <v>-3.5189121771052658e-07</v>
+        <v>-3.376908544652675e-07</v>
       </c>
       <c r="I16">
-        <v>1.5912262714970239e-07</v>
+        <v>6.4266253342069854e-08</v>
       </c>
       <c r="J16">
-        <v>-7.756584569302615e-06</v>
+        <v>-7.4470725386476121e-06</v>
       </c>
       <c r="K16">
-        <v>-1.7769371088324239e-05</v>
+        <v>-1.7708136540186208e-05</v>
       </c>
       <c r="L16">
-        <v>-3.0271987084079494e-05</v>
+        <v>-3.0195715737612005e-05</v>
       </c>
       <c r="M16">
-        <v>-3.6030654339676646e-05</v>
+        <v>-3.6055582464771435e-05</v>
       </c>
       <c r="N16">
-        <v>-4.1697871549088424e-05</v>
+        <v>-4.2011316991313706e-05</v>
       </c>
       <c r="O16">
-        <v>0.00041384963517607525</v>
+        <v>0.00041383367747480039</v>
       </c>
       <c r="P16">
-        <v>0.00041282945650045281</v>
+        <v>0.00041280913728009461</v>
       </c>
       <c r="Q16">
-        <v>0.00071787682315140782</v>
+        <v>0.000717316889988816</v>
       </c>
       <c r="R16">
-        <v>0.00041535799384057309</v>
+        <v>0.00041540001576074548</v>
       </c>
       <c r="S16">
-        <v>0.00041838650803731396</v>
+        <v>0.00041838212714494108</v>
       </c>
       <c r="T16">
-        <v>0.00041511656591378967</v>
+        <v>0.00041517518376969157</v>
       </c>
       <c r="U16">
-        <v>-4.9947029892120068e-06</v>
+        <v>-4.6605262847580832e-06</v>
       </c>
       <c r="V16">
-        <v>-5.5193359418054806e-06</v>
+        <v>-5.5274118045836598e-06</v>
       </c>
       <c r="W16">
-        <v>-0.00041325986896345254</v>
+        <v>-0.00041331565857763642</v>
       </c>
     </row>
     <row r="17">
@@ -6728,70 +6728,70 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>0.023169664787710036</v>
+        <v>0.026368401286869105</v>
       </c>
       <c r="C17">
-        <v>2.9204160683974874e-06</v>
+        <v>3.0239619789284084e-06</v>
       </c>
       <c r="D17">
-        <v>-2.7270549691602506e-08</v>
+        <v>-2.8460373058014049e-08</v>
       </c>
       <c r="E17">
-        <v>3.4038198616015766e-05</v>
+        <v>3.3770902387213425e-05</v>
       </c>
       <c r="F17">
-        <v>9.8866562788718838e-06</v>
+        <v>9.2690361454529931e-06</v>
       </c>
       <c r="G17">
-        <v>-7.7994779567172666e-07</v>
+        <v>-7.7944983956979658e-07</v>
       </c>
       <c r="H17">
-        <v>-1.4947989252864334e-07</v>
+        <v>-1.4331432780875421e-07</v>
       </c>
       <c r="I17">
-        <v>-3.7783358534563469e-06</v>
+        <v>-3.7232696090030961e-06</v>
       </c>
       <c r="J17">
-        <v>-9.1967218759688907e-06</v>
+        <v>-9.2957689913393204e-06</v>
       </c>
       <c r="K17">
-        <v>-8.4978045359928363e-06</v>
+        <v>-8.3200992319852065e-06</v>
       </c>
       <c r="L17">
-        <v>-1.4824240716207742e-05</v>
+        <v>-1.4715440560455058e-05</v>
       </c>
       <c r="M17">
-        <v>-1.4222841955696582e-05</v>
+        <v>-1.4073670842270405e-05</v>
       </c>
       <c r="N17">
-        <v>-3.5121561303235003e-05</v>
+        <v>-3.5294802414292487e-05</v>
       </c>
       <c r="O17">
-        <v>0.00041626155201825019</v>
+        <v>0.0004162682087066788</v>
       </c>
       <c r="P17">
-        <v>0.00041672751216224099</v>
+        <v>0.00041668703233415565</v>
       </c>
       <c r="Q17">
-        <v>0.00041535799384057309</v>
+        <v>0.00041540001576074548</v>
       </c>
       <c r="R17">
-        <v>0.00063389242032125767</v>
+        <v>0.00063472436437972597</v>
       </c>
       <c r="S17">
-        <v>0.0004170031744904781</v>
+        <v>0.00041704670728968349</v>
       </c>
       <c r="T17">
-        <v>0.00041612161306906615</v>
+        <v>0.000416182851340523</v>
       </c>
       <c r="U17">
-        <v>1.464070092988265e-05</v>
+        <v>1.5230567760312229e-05</v>
       </c>
       <c r="V17">
-        <v>1.0174941497393464e-05</v>
+        <v>1.0101795022944654e-05</v>
       </c>
       <c r="W17">
-        <v>-0.00046798244563567363</v>
+        <v>-0.00046995617542857596</v>
       </c>
     </row>
     <row r="18">
@@ -6799,70 +6799,70 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>-0.12921933829819451</v>
+        <v>-0.12950859782892746</v>
       </c>
       <c r="C18">
-        <v>1.8904551487158973e-06</v>
+        <v>1.8997586306835277e-06</v>
       </c>
       <c r="D18">
-        <v>-1.743519163661006e-08</v>
+        <v>-1.7667353608075601e-08</v>
       </c>
       <c r="E18">
-        <v>3.9166500075902682e-06</v>
+        <v>2.8341807186208341e-06</v>
       </c>
       <c r="F18">
-        <v>-4.8109150269245218e-05</v>
+        <v>-4.8950482656448721e-05</v>
       </c>
       <c r="G18">
-        <v>-2.1150540845897405e-07</v>
+        <v>-1.8987809407692353e-07</v>
       </c>
       <c r="H18">
-        <v>5.2467382060500317e-07</v>
+        <v>5.4114081621088774e-07</v>
       </c>
       <c r="I18">
-        <v>-8.2011121265418905e-06</v>
+        <v>-8.250902906451324e-06</v>
       </c>
       <c r="J18">
-        <v>-1.4450608672886047e-05</v>
+        <v>-1.4179326848369978e-05</v>
       </c>
       <c r="K18">
-        <v>3.3824494668758707e-06</v>
+        <v>3.4636756817547866e-06</v>
       </c>
       <c r="L18">
-        <v>-6.0374694249166864e-06</v>
+        <v>-6.0205819075949993e-06</v>
       </c>
       <c r="M18">
-        <v>-9.5051060439650973e-06</v>
+        <v>-9.5464824860947036e-06</v>
       </c>
       <c r="N18">
-        <v>-2.8907810716398229e-05</v>
+        <v>-2.9122395137945201e-05</v>
       </c>
       <c r="O18">
-        <v>0.00041442414588120457</v>
+        <v>0.00041440486610124134</v>
       </c>
       <c r="P18">
-        <v>0.0004142531003056002</v>
+        <v>0.00041419995165539362</v>
       </c>
       <c r="Q18">
-        <v>0.00041838650803731396</v>
+        <v>0.00041838212714494108</v>
       </c>
       <c r="R18">
-        <v>0.0004170031744904781</v>
+        <v>0.00041704670728968349</v>
       </c>
       <c r="S18">
-        <v>0.00068784708859319767</v>
+        <v>0.00068776826643983857</v>
       </c>
       <c r="T18">
-        <v>0.00041636070603264392</v>
+        <v>0.00041645822058770173</v>
       </c>
       <c r="U18">
-        <v>1.1402193500351788e-07</v>
+        <v>4.1308021335949055e-07</v>
       </c>
       <c r="V18">
-        <v>-1.6509465377052728e-06</v>
+        <v>-1.6897011452332796e-06</v>
       </c>
       <c r="W18">
-        <v>-0.00043093230257717726</v>
+        <v>-0.00043075975717233185</v>
       </c>
     </row>
     <row r="19">
@@ -6870,70 +6870,70 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>-0.14926305479798871</v>
+        <v>-0.14572879973353967</v>
       </c>
       <c r="C19">
-        <v>-6.6572586339490597e-07</v>
+        <v>-4.8436909280624247e-07</v>
       </c>
       <c r="D19">
-        <v>9.075061433684419e-09</v>
+        <v>6.6560095154321312e-09</v>
       </c>
       <c r="E19">
-        <v>-1.797114129143143e-05</v>
+        <v>-2.0422293928908707e-05</v>
       </c>
       <c r="F19">
-        <v>-2.8828232449395916e-05</v>
+        <v>-3.0773233842658323e-05</v>
       </c>
       <c r="G19">
-        <v>3.0132978253550991e-07</v>
+        <v>3.4386245143992356e-07</v>
       </c>
       <c r="H19">
-        <v>5.0367721789776936e-07</v>
+        <v>5.357136052397941e-07</v>
       </c>
       <c r="I19">
-        <v>5.2804444345689541e-06</v>
+        <v>5.7062722753078933e-06</v>
       </c>
       <c r="J19">
-        <v>3.6155749779488691e-06</v>
+        <v>2.2331090593866136e-06</v>
       </c>
       <c r="K19">
-        <v>1.481619248703994e-05</v>
+        <v>1.491369661422263e-05</v>
       </c>
       <c r="L19">
-        <v>3.4151414074549665e-07</v>
+        <v>4.4946440056452134e-07</v>
       </c>
       <c r="M19">
-        <v>1.8040122792191925e-05</v>
+        <v>1.8321113575335866e-05</v>
       </c>
       <c r="N19">
-        <v>-2.1462327603964768e-06</v>
+        <v>-1.8017249153346609e-06</v>
       </c>
       <c r="O19">
-        <v>0.00041478874938270745</v>
+        <v>0.00041476956488913845</v>
       </c>
       <c r="P19">
-        <v>0.00041471591399255483</v>
+        <v>0.00041466491513443587</v>
       </c>
       <c r="Q19">
-        <v>0.00041511656591378967</v>
+        <v>0.00041517518376969157</v>
       </c>
       <c r="R19">
-        <v>0.00041612161306906615</v>
+        <v>0.000416182851340523</v>
       </c>
       <c r="S19">
-        <v>0.00041636070603264392</v>
+        <v>0.00041645822058770173</v>
       </c>
       <c r="T19">
-        <v>0.0017919283938224509</v>
+        <v>0.0017970159288647417</v>
       </c>
       <c r="U19">
-        <v>1.0769361950415997e-05</v>
+        <v>1.103328140871752e-05</v>
       </c>
       <c r="V19">
-        <v>3.6313079182258825e-06</v>
+        <v>4.7210220195765013e-06</v>
       </c>
       <c r="W19">
-        <v>-0.00041903953640824672</v>
+        <v>-0.00042175353088571996</v>
       </c>
     </row>
     <row r="20">
@@ -6941,70 +6941,70 @@
         <v>42</v>
       </c>
       <c r="B20">
-        <v>-0.068637034543818004</v>
+        <v>-0.067141051890866291</v>
       </c>
       <c r="C20">
-        <v>1.1732112743566433e-06</v>
+        <v>1.3015700873776471e-06</v>
       </c>
       <c r="D20">
-        <v>-1.245225106256128e-08</v>
+        <v>-1.3691669125166148e-08</v>
       </c>
       <c r="E20">
-        <v>1.0660073195828203e-05</v>
+        <v>1.1432320977549063e-05</v>
       </c>
       <c r="F20">
-        <v>3.3227023837756691e-05</v>
+        <v>3.3713068571135743e-05</v>
       </c>
       <c r="G20">
-        <v>-2.528205994179068e-07</v>
+        <v>-2.7005505003890763e-07</v>
       </c>
       <c r="H20">
-        <v>-6.4949585722650761e-07</v>
+        <v>-6.6007886198071827e-07</v>
       </c>
       <c r="I20">
-        <v>2.0687404830747441e-07</v>
+        <v>1.667930938045684e-07</v>
       </c>
       <c r="J20">
-        <v>-5.6013434902318745e-06</v>
+        <v>-6.0341965785401773e-06</v>
       </c>
       <c r="K20">
-        <v>1.3310316153190914e-07</v>
+        <v>7.3133474030168382e-07</v>
       </c>
       <c r="L20">
-        <v>1.707739533103869e-06</v>
+        <v>1.7034134946836298e-06</v>
       </c>
       <c r="M20">
-        <v>-2.545610202908781e-06</v>
+        <v>-2.4277793420343909e-06</v>
       </c>
       <c r="N20">
-        <v>-1.0478736349004337e-05</v>
+        <v>-9.9841911143385114e-06</v>
       </c>
       <c r="O20">
-        <v>6.073500478057615e-06</v>
+        <v>6.6022638563916448e-06</v>
       </c>
       <c r="P20">
-        <v>-2.1115892635215897e-06</v>
+        <v>-1.7432117282338792e-06</v>
       </c>
       <c r="Q20">
-        <v>-4.9947029892120068e-06</v>
+        <v>-4.6605262847580832e-06</v>
       </c>
       <c r="R20">
-        <v>1.464070092988265e-05</v>
+        <v>1.5230567760312229e-05</v>
       </c>
       <c r="S20">
-        <v>1.1402193500351788e-07</v>
+        <v>4.1308021335949055e-07</v>
       </c>
       <c r="T20">
-        <v>1.0769361950415997e-05</v>
+        <v>1.103328140871752e-05</v>
       </c>
       <c r="U20">
-        <v>0.00089079758868779678</v>
+        <v>0.00089284862034612344</v>
       </c>
       <c r="V20">
-        <v>5.8560093931156922e-05</v>
+        <v>5.8568750274647503e-05</v>
       </c>
       <c r="W20">
-        <v>-8.2864152426535042e-05</v>
+        <v>-8.6326860105429533e-05</v>
       </c>
     </row>
     <row r="21">
@@ -7012,70 +7012,70 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>0.10454114967837186</v>
+        <v>0.10802277472818979</v>
       </c>
       <c r="C21">
-        <v>-2.8424526832009631e-06</v>
+        <v>-2.9098187938785718e-06</v>
       </c>
       <c r="D21">
-        <v>2.4818422905359576e-08</v>
+        <v>2.5378159441799093e-08</v>
       </c>
       <c r="E21">
-        <v>1.7911249677234527e-05</v>
+        <v>1.8320606347170743e-05</v>
       </c>
       <c r="F21">
-        <v>1.9449267148431614e-05</v>
+        <v>1.8525096321798343e-05</v>
       </c>
       <c r="G21">
-        <v>-2.9313864847253634e-07</v>
+        <v>-3.0177493836406789e-07</v>
       </c>
       <c r="H21">
-        <v>-2.397107008800051e-07</v>
+        <v>-2.2294268233629018e-07</v>
       </c>
       <c r="I21">
-        <v>1.2270848759757568e-05</v>
+        <v>1.2450794712038474e-05</v>
       </c>
       <c r="J21">
-        <v>-4.1956606850279706e-06</v>
+        <v>-4.3447695952284772e-06</v>
       </c>
       <c r="K21">
-        <v>-7.2460163601834341e-06</v>
+        <v>-7.2531352844108895e-06</v>
       </c>
       <c r="L21">
-        <v>-8.1754913156325658e-06</v>
+        <v>-8.1473352704591869e-06</v>
       </c>
       <c r="M21">
-        <v>-6.110561385893571e-06</v>
+        <v>-5.9753852560077972e-06</v>
       </c>
       <c r="N21">
-        <v>-1.2285942338857328e-05</v>
+        <v>-1.2043613251549614e-05</v>
       </c>
       <c r="O21">
-        <v>4.6126928665743164e-06</v>
+        <v>4.5790182839544131e-06</v>
       </c>
       <c r="P21">
-        <v>-1.2822743613043456e-05</v>
+        <v>-1.2584826548470499e-05</v>
       </c>
       <c r="Q21">
-        <v>-5.5193359418054806e-06</v>
+        <v>-5.5274118045836598e-06</v>
       </c>
       <c r="R21">
-        <v>1.0174941497393464e-05</v>
+        <v>1.0101795022944654e-05</v>
       </c>
       <c r="S21">
-        <v>-1.6509465377052728e-06</v>
+        <v>-1.6897011452332796e-06</v>
       </c>
       <c r="T21">
-        <v>3.6313079182258825e-06</v>
+        <v>4.7210220195765013e-06</v>
       </c>
       <c r="U21">
-        <v>5.8560093931156922e-05</v>
+        <v>5.8568750274647503e-05</v>
       </c>
       <c r="V21">
-        <v>0.0011226860874147904</v>
+        <v>0.0011272281330778893</v>
       </c>
       <c r="W21">
-        <v>1.2718508345571935e-05</v>
+        <v>1.437497765263601e-05</v>
       </c>
     </row>
     <row r="22">
@@ -7083,70 +7083,70 @@
         <v>44</v>
       </c>
       <c r="B22">
-        <v>-2.9914302801842108</v>
+        <v>-2.9911167933604648</v>
       </c>
       <c r="C22">
-        <v>-0.00051560859631771924</v>
+        <v>-0.00051792998311778128</v>
       </c>
       <c r="D22">
-        <v>5.1027282669180229e-06</v>
+        <v>5.1289228655816393e-06</v>
       </c>
       <c r="E22">
-        <v>-0.0031596309752217316</v>
+        <v>-0.0031633818660566052</v>
       </c>
       <c r="F22">
-        <v>-0.002716288639685099</v>
+        <v>-0.0027218393645978807</v>
       </c>
       <c r="G22">
-        <v>6.4544112324254916e-05</v>
+        <v>6.4616123727413073e-05</v>
       </c>
       <c r="H22">
-        <v>5.3759915239246632e-05</v>
+        <v>5.3859539755439353e-05</v>
       </c>
       <c r="I22">
-        <v>0.00017673063316534754</v>
+        <v>0.00016783263513429428</v>
       </c>
       <c r="J22">
-        <v>0.00061800271623847585</v>
+        <v>0.00062828002645894045</v>
       </c>
       <c r="K22">
-        <v>-0.0076458550531630643</v>
+        <v>-0.0076467330770613991</v>
       </c>
       <c r="L22">
-        <v>-0.0076619075026903684</v>
+        <v>-0.007663895437148782</v>
       </c>
       <c r="M22">
-        <v>-0.007751660929322811</v>
+        <v>-0.0077535733879639298</v>
       </c>
       <c r="N22">
-        <v>-0.0080401891750455576</v>
+        <v>-0.0080403468402342401</v>
       </c>
       <c r="O22">
-        <v>-0.00047283649417752971</v>
+        <v>-0.00047355690283225961</v>
       </c>
       <c r="P22">
-        <v>-0.00047078789341754629</v>
+        <v>-0.00046895674276341081</v>
       </c>
       <c r="Q22">
-        <v>-0.00041325986896345254</v>
+        <v>-0.00041331565857763642</v>
       </c>
       <c r="R22">
-        <v>-0.00046798244563567363</v>
+        <v>-0.00046995617542857596</v>
       </c>
       <c r="S22">
-        <v>-0.00043093230257717726</v>
+        <v>-0.00043075975717233185</v>
       </c>
       <c r="T22">
-        <v>-0.00041903953640824672</v>
+        <v>-0.00042175353088571996</v>
       </c>
       <c r="U22">
-        <v>-8.2864152426535042e-05</v>
+        <v>-8.6326860105429533e-05</v>
       </c>
       <c r="V22">
-        <v>1.2718508345571935e-05</v>
+        <v>1.437497765263601e-05</v>
       </c>
       <c r="W22">
-        <v>0.020134109862578915</v>
+        <v>0.020184952179908927</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_employmentSelection.xlsx
+++ b/input/ES/reg_employmentSelection.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="206" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="214" uniqueCount="47">
   <si>
     <t>Description</t>
   </si>
@@ -52,7 +52,7 @@
     <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
   </si>
   <si>
-    <t>15 June 2016 AK</t>
+    <t>07 Oct 2026 AK</t>
   </si>
   <si>
     <t>Description:</t>
@@ -125,6 +125,9 @@
   </si>
   <si>
     <t>Dhe_Excellent</t>
+  </si>
+  <si>
+    <t>Liwwh</t>
   </si>
   <si>
     <t>ES2</t>
@@ -299,7 +302,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -307,7 +310,7 @@
         <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
         <v>22</v>
@@ -377,6 +380,9 @@
       </c>
       <c r="Y1" t="s">
         <v>44</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="2">
@@ -384,76 +390,79 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>-1.577482365608581</v>
+        <v>-1.4953888255107675</v>
       </c>
       <c r="C2">
-        <v>0.00078757303448114555</v>
+        <v>0.00079295296221720823</v>
       </c>
       <c r="D2">
-        <v>5.699368159562538e-05</v>
+        <v>6.2769197379841118e-05</v>
       </c>
       <c r="E2">
-        <v>3.7793676776640814e-05</v>
+        <v>3.7454471307580702e-05</v>
       </c>
       <c r="F2">
-        <v>-3.6418953456302739e-07</v>
+        <v>-3.7275705456794662e-07</v>
       </c>
       <c r="G2">
-        <v>-6.914230034986348e-05</v>
+        <v>-7.521147454791726e-05</v>
       </c>
       <c r="H2">
-        <v>6.7281170523516729e-05</v>
+        <v>6.2004495700575149e-05</v>
       </c>
       <c r="I2">
-        <v>1.2048132821244012e-06</v>
+        <v>1.3286511033854452e-06</v>
       </c>
       <c r="J2">
-        <v>-1.3648060641901778e-06</v>
+        <v>-1.2456703291868549e-06</v>
       </c>
       <c r="K2">
-        <v>2.1439497551592387e-05</v>
+        <v>2.219644913675412e-05</v>
       </c>
       <c r="L2">
-        <v>1.3458024764383759e-06</v>
+        <v>-7.359396193591757e-07</v>
       </c>
       <c r="M2">
-        <v>5.9028078636401459e-07</v>
+        <v>1.5434830735697072e-06</v>
       </c>
       <c r="N2">
-        <v>5.1051509280343249e-06</v>
+        <v>7.4649403790694223e-06</v>
       </c>
       <c r="O2">
-        <v>4.8607902423147592e-06</v>
+        <v>7.0083336797136051e-06</v>
       </c>
       <c r="P2">
-        <v>1.9284411210990118e-06</v>
+        <v>3.7772961390521924e-06</v>
       </c>
       <c r="Q2">
-        <v>2.8625945207049448e-06</v>
+        <v>1.3545127696711973e-06</v>
       </c>
       <c r="R2">
-        <v>3.759834000307216e-06</v>
+        <v>1.1730175784176885e-06</v>
       </c>
       <c r="S2">
-        <v>5.7401949537125118e-07</v>
+        <v>2.2668562622614141e-06</v>
       </c>
       <c r="T2">
-        <v>5.736884804500962e-06</v>
+        <v>1.9821197461250868e-07</v>
       </c>
       <c r="U2">
-        <v>6.4308524325009454e-06</v>
+        <v>3.7098865570265707e-06</v>
       </c>
       <c r="V2">
-        <v>-4.2449270722484388e-07</v>
+        <v>6.2622780023743595e-06</v>
       </c>
       <c r="W2">
-        <v>9.9154514910156613e-06</v>
+        <v>-1.0279032563837634e-06</v>
       </c>
       <c r="X2">
-        <v>4.4080477075468059e-06</v>
+        <v>1.0067967947207182e-05</v>
       </c>
       <c r="Y2">
-        <v>-0.00099309852096993948</v>
+        <v>5.424408348775077e-06</v>
+      </c>
+      <c r="Z2">
+        <v>-0.00098527207952442343</v>
       </c>
     </row>
     <row r="3">
@@ -461,76 +470,79 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>-2.2154712600795841</v>
+        <v>-2.1068558348960442</v>
       </c>
       <c r="C3">
-        <v>5.699368159562538e-05</v>
+        <v>6.2769197379841118e-05</v>
       </c>
       <c r="D3">
-        <v>0.00012483953510101289</v>
+        <v>0.00013219026295063283</v>
       </c>
       <c r="E3">
-        <v>3.0121515772836897e-06</v>
+        <v>2.5316054820578225e-06</v>
       </c>
       <c r="F3">
-        <v>-3.07526338809503e-08</v>
+        <v>-3.7884786421972984e-08</v>
       </c>
       <c r="G3">
-        <v>5.8769554902043026e-06</v>
+        <v>-7.1283960625050584e-07</v>
       </c>
       <c r="H3">
-        <v>-1.8311166838060058e-06</v>
+        <v>-1.2667703665785595e-05</v>
       </c>
       <c r="I3">
-        <v>-3.6500340493763753e-07</v>
+        <v>-2.2999680633760394e-07</v>
       </c>
       <c r="J3">
-        <v>-4.0967327252641896e-07</v>
+        <v>-1.8235104951562917e-07</v>
       </c>
       <c r="K3">
-        <v>-3.580590229525579e-06</v>
+        <v>-2.2477718561934414e-06</v>
       </c>
       <c r="L3">
-        <v>-4.1318779779253134e-06</v>
+        <v>-5.8484349744438527e-06</v>
       </c>
       <c r="M3">
-        <v>2.8413217147769655e-06</v>
+        <v>3.4984098892758676e-06</v>
       </c>
       <c r="N3">
-        <v>8.0920555668338997e-06</v>
+        <v>9.8955201939563301e-06</v>
       </c>
       <c r="O3">
-        <v>1.062733572271395e-05</v>
+        <v>1.2243596647533884e-05</v>
       </c>
       <c r="P3">
-        <v>1.2861097919746893e-05</v>
+        <v>1.41482707920021e-05</v>
       </c>
       <c r="Q3">
-        <v>2.0028269068119913e-06</v>
+        <v>1.3849241471652581e-06</v>
       </c>
       <c r="R3">
-        <v>3.0200197275771797e-06</v>
+        <v>3.8445336244228958e-07</v>
       </c>
       <c r="S3">
-        <v>-2.4128980061865548e-06</v>
+        <v>1.3996817918555338e-06</v>
       </c>
       <c r="T3">
-        <v>1.7093014299367719e-06</v>
+        <v>-2.3420650121424808e-06</v>
       </c>
       <c r="U3">
-        <v>-6.3523805671575023e-06</v>
+        <v>-8.9408508636454302e-07</v>
       </c>
       <c r="V3">
-        <v>-4.6367972362147762e-06</v>
+        <v>-6.441441538547968e-06</v>
       </c>
       <c r="W3">
-        <v>5.5397407375916393e-06</v>
+        <v>-4.8067806564288456e-06</v>
       </c>
       <c r="X3">
-        <v>8.9720374448379542e-06</v>
+        <v>5.7283286465165247e-06</v>
       </c>
       <c r="Y3">
-        <v>-0.00011721838844687722</v>
+        <v>1.0299660153593104e-05</v>
+      </c>
+      <c r="Z3">
+        <v>-0.00010781260712777248</v>
       </c>
     </row>
     <row r="4">
@@ -538,76 +550,79 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>0.16099042849627174</v>
+        <v>0.14689729418603823</v>
       </c>
       <c r="C4">
-        <v>3.7793676776640814e-05</v>
+        <v>3.7454471307580702e-05</v>
       </c>
       <c r="D4">
-        <v>3.0121515772836897e-06</v>
+        <v>2.5316054820578225e-06</v>
       </c>
       <c r="E4">
-        <v>1.1305830643889793e-05</v>
+        <v>1.1615427373834015e-05</v>
       </c>
       <c r="F4">
-        <v>-1.1786907411107868e-07</v>
+        <v>-1.1987951241403687e-07</v>
       </c>
       <c r="G4">
-        <v>3.3862253328535479e-05</v>
+        <v>3.5628543597448561e-05</v>
       </c>
       <c r="H4">
-        <v>3.3515627042587226e-05</v>
+        <v>3.5942142205968453e-05</v>
       </c>
       <c r="I4">
-        <v>-7.1790443122578872e-07</v>
+        <v>-7.569737871403864e-07</v>
       </c>
       <c r="J4">
-        <v>-6.5769499656390078e-07</v>
+        <v>-7.112558156926794e-07</v>
       </c>
       <c r="K4">
-        <v>-8.4402585779852944e-06</v>
+        <v>-8.9300759257192039e-06</v>
       </c>
       <c r="L4">
-        <v>-1.3106794664545801e-05</v>
+        <v>-1.3393191051818346e-05</v>
       </c>
       <c r="M4">
-        <v>2.2443450283016929e-06</v>
+        <v>2.3993220286065145e-06</v>
       </c>
       <c r="N4">
-        <v>4.8417717685456671e-06</v>
+        <v>4.9909505256218536e-06</v>
       </c>
       <c r="O4">
-        <v>6.5115107533637894e-06</v>
+        <v>6.7355729372238369e-06</v>
       </c>
       <c r="P4">
-        <v>1.0562414049499762e-05</v>
+        <v>1.088549346054398e-05</v>
       </c>
       <c r="Q4">
-        <v>1.4235205166774607e-06</v>
+        <v>-1.5605865178997735e-07</v>
       </c>
       <c r="R4">
-        <v>1.178570278737875e-06</v>
+        <v>1.5782097801583171e-06</v>
       </c>
       <c r="S4">
-        <v>4.8090966906169126e-07</v>
+        <v>1.2813247039407887e-06</v>
       </c>
       <c r="T4">
-        <v>1.6627613582729379e-06</v>
+        <v>3.1860402988783951e-07</v>
       </c>
       <c r="U4">
-        <v>3.2246844718863284e-07</v>
+        <v>2.0263678840064211e-06</v>
       </c>
       <c r="V4">
-        <v>-1.5465187624462614e-06</v>
+        <v>2.6434628348609063e-07</v>
       </c>
       <c r="W4">
-        <v>5.4630878984697236e-07</v>
+        <v>-1.6950909785017579e-06</v>
       </c>
       <c r="X4">
-        <v>4.0532211642489738e-07</v>
+        <v>5.9504650960062033e-07</v>
       </c>
       <c r="Y4">
-        <v>-0.00025229472413872513</v>
+        <v>3.2671378245053026e-07</v>
+      </c>
+      <c r="Z4">
+        <v>-0.00025861855805884329</v>
       </c>
     </row>
     <row r="5">
@@ -615,76 +630,79 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>-0.0019636339292433344</v>
+        <v>-0.002025768786565909</v>
       </c>
       <c r="C5">
-        <v>-3.6418953456302739e-07</v>
+        <v>-3.7275705456794662e-07</v>
       </c>
       <c r="D5">
-        <v>-3.07526338809503e-08</v>
+        <v>-3.7884786421972984e-08</v>
       </c>
       <c r="E5">
-        <v>-1.1786907411107868e-07</v>
+        <v>-1.1987951241403687e-07</v>
       </c>
       <c r="F5">
-        <v>1.294481197421596e-09</v>
+        <v>1.336049029181926e-09</v>
       </c>
       <c r="G5">
-        <v>-1.405443214486644e-07</v>
+        <v>-1.453899358578456e-07</v>
       </c>
       <c r="H5">
-        <v>-1.2776195393357496e-07</v>
+        <v>-1.3042227056367756e-07</v>
       </c>
       <c r="I5">
-        <v>2.5787002734849297e-09</v>
+        <v>2.6852196100138868e-09</v>
       </c>
       <c r="J5">
-        <v>1.7649944165524716e-09</v>
+        <v>1.8174395357988716e-09</v>
       </c>
       <c r="K5">
-        <v>7.314534665699316e-08</v>
+        <v>7.518177652989452e-08</v>
       </c>
       <c r="L5">
-        <v>1.5732232647926429e-07</v>
+        <v>1.6481834366852625e-07</v>
       </c>
       <c r="M5">
-        <v>-2.5434729507913763e-08</v>
+        <v>-2.8055024412318066e-08</v>
       </c>
       <c r="N5">
-        <v>-5.1546329032097234e-08</v>
+        <v>-5.7337150945239371e-08</v>
       </c>
       <c r="O5">
-        <v>-6.1939329435683823e-08</v>
+        <v>-6.7630407186636376e-08</v>
       </c>
       <c r="P5">
-        <v>-9.1979313853705399e-08</v>
+        <v>-9.7550700361534012e-08</v>
       </c>
       <c r="Q5">
-        <v>-1.7877888888929421e-08</v>
+        <v>-2.1892453526480978e-09</v>
       </c>
       <c r="R5">
-        <v>-1.6927703041294986e-08</v>
+        <v>-1.4345431578920102e-08</v>
       </c>
       <c r="S5">
-        <v>-4.6668756085052081e-09</v>
+        <v>-1.3333470025109639e-08</v>
       </c>
       <c r="T5">
-        <v>-2.0051108673750957e-08</v>
+        <v>-3.0023207302428985e-09</v>
       </c>
       <c r="U5">
-        <v>-9.5352400363220659e-10</v>
+        <v>-1.658306117728798e-08</v>
       </c>
       <c r="V5">
-        <v>1.7848451360334781e-08</v>
+        <v>-5.9339638965883089e-10</v>
       </c>
       <c r="W5">
-        <v>-7.0840347204203425e-09</v>
+        <v>1.9656054393782035e-08</v>
       </c>
       <c r="X5">
-        <v>-6.7621399990584406e-09</v>
+        <v>-6.8224569067966899e-09</v>
       </c>
       <c r="Y5">
-        <v>2.4874896908678085e-06</v>
+        <v>-9.14717351804829e-09</v>
+      </c>
+      <c r="Z5">
+        <v>2.5266307796792345e-06</v>
       </c>
     </row>
     <row r="6">
@@ -692,76 +710,79 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>-0.42345100253023377</v>
+        <v>-0.53614217652725993</v>
       </c>
       <c r="C6">
-        <v>-6.914230034986348e-05</v>
+        <v>-7.521147454791726e-05</v>
       </c>
       <c r="D6">
-        <v>5.8769554902043026e-06</v>
+        <v>-7.1283960625050584e-07</v>
       </c>
       <c r="E6">
-        <v>3.3862253328535479e-05</v>
+        <v>3.5628543597448561e-05</v>
       </c>
       <c r="F6">
-        <v>-1.405443214486644e-07</v>
+        <v>-1.453899358578456e-07</v>
       </c>
       <c r="G6">
-        <v>0.002409703425254134</v>
+        <v>0.0024202613878066288</v>
       </c>
       <c r="H6">
-        <v>0.0010627527246711583</v>
+        <v>0.0010718280290491382</v>
       </c>
       <c r="I6">
-        <v>-5.0112884496575182e-05</v>
+        <v>-5.044771129002166e-05</v>
       </c>
       <c r="J6">
-        <v>-2.2427606192300533e-05</v>
+        <v>-2.2648266998356479e-05</v>
       </c>
       <c r="K6">
-        <v>-4.9797090098398636e-06</v>
+        <v>-7.6165986743787577e-06</v>
       </c>
       <c r="L6">
-        <v>-5.5283438720190011e-05</v>
+        <v>-5.5447234779507033e-05</v>
       </c>
       <c r="M6">
-        <v>7.1674452892406823e-06</v>
+        <v>8.1445274477991636e-06</v>
       </c>
       <c r="N6">
-        <v>8.6099513089398514e-06</v>
+        <v>8.3616104664535076e-06</v>
       </c>
       <c r="O6">
-        <v>1.1415153222290404e-05</v>
+        <v>1.1047075247567811e-05</v>
       </c>
       <c r="P6">
-        <v>3.2827544449442049e-05</v>
+        <v>3.319698549740437e-05</v>
       </c>
       <c r="Q6">
-        <v>4.8732857632976776e-06</v>
+        <v>-1.7375745621032226e-06</v>
       </c>
       <c r="R6">
-        <v>1.504498556332856e-06</v>
+        <v>8.1026940519441022e-06</v>
       </c>
       <c r="S6">
-        <v>-1.9781797199175846e-06</v>
+        <v>4.7019958305843498e-06</v>
       </c>
       <c r="T6">
-        <v>-5.5319646321372754e-06</v>
+        <v>-1.8533512691450214e-06</v>
       </c>
       <c r="U6">
-        <v>-1.1611480897317256e-05</v>
+        <v>-1.4612173213359944e-06</v>
       </c>
       <c r="V6">
-        <v>-1.0218844545338312e-05</v>
+        <v>-1.2139539366328588e-05</v>
       </c>
       <c r="W6">
-        <v>6.6579561869896883e-06</v>
+        <v>-9.8917098088298133e-06</v>
       </c>
       <c r="X6">
-        <v>6.3451601328965603e-06</v>
+        <v>7.3627688309860995e-06</v>
       </c>
       <c r="Y6">
-        <v>-0.0012507625103392551</v>
+        <v>4.4598003131860345e-06</v>
+      </c>
+      <c r="Z6">
+        <v>-0.001284645131895</v>
       </c>
     </row>
     <row r="7">
@@ -769,76 +790,79 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-0.56261152744549803</v>
+        <v>-0.75683792494220736</v>
       </c>
       <c r="C7">
-        <v>6.7281170523516729e-05</v>
+        <v>6.2004495700575149e-05</v>
       </c>
       <c r="D7">
-        <v>-1.8311166838060058e-06</v>
+        <v>-1.2667703665785595e-05</v>
       </c>
       <c r="E7">
-        <v>3.3515627042587226e-05</v>
+        <v>3.5942142205968453e-05</v>
       </c>
       <c r="F7">
-        <v>-1.2776195393357496e-07</v>
+        <v>-1.3042227056367756e-07</v>
       </c>
       <c r="G7">
-        <v>0.0010627527246711583</v>
+        <v>0.0010718280290491382</v>
       </c>
       <c r="H7">
-        <v>0.0021939979502267797</v>
+        <v>0.0022278316648450211</v>
       </c>
       <c r="I7">
-        <v>-2.2567597056830977e-05</v>
+        <v>-2.2788230813259265e-05</v>
       </c>
       <c r="J7">
-        <v>-4.4376557510629882e-05</v>
+        <v>-4.5167485190274483e-05</v>
       </c>
       <c r="K7">
-        <v>1.433526743097214e-05</v>
+        <v>1.0350405706673112e-05</v>
       </c>
       <c r="L7">
-        <v>-0.00011239437131380168</v>
+        <v>-0.00011268571511041256</v>
       </c>
       <c r="M7">
-        <v>1.2145353253368749e-05</v>
+        <v>1.2493033659000748e-05</v>
       </c>
       <c r="N7">
-        <v>1.078676700011727e-05</v>
+        <v>7.8134273613777463e-06</v>
       </c>
       <c r="O7">
-        <v>9.534227646613156e-06</v>
+        <v>6.5723218719825624e-06</v>
       </c>
       <c r="P7">
-        <v>3.9010181603094671e-05</v>
+        <v>3.7782438473305446e-05</v>
       </c>
       <c r="Q7">
-        <v>8.3164767321658455e-06</v>
+        <v>-2.7480565838816848e-06</v>
       </c>
       <c r="R7">
-        <v>-5.7556187337109119e-06</v>
+        <v>1.2238845624991258e-05</v>
       </c>
       <c r="S7">
-        <v>-1.7046291545810205e-05</v>
+        <v>-3.1112537259943683e-06</v>
       </c>
       <c r="T7">
-        <v>-1.2988412160836089e-05</v>
+        <v>-1.9134992747611256e-05</v>
       </c>
       <c r="U7">
-        <v>-3.6082790884597123e-05</v>
+        <v>-7.3225516524035082e-06</v>
       </c>
       <c r="V7">
-        <v>-1.9314611712412368e-05</v>
+        <v>-3.7577002294618579e-05</v>
       </c>
       <c r="W7">
-        <v>1.5364197845167787e-05</v>
+        <v>-2.0147560699880733e-05</v>
       </c>
       <c r="X7">
-        <v>1.5932771462732996e-05</v>
+        <v>1.6707003404383222e-05</v>
       </c>
       <c r="Y7">
-        <v>-0.0012503041707290195</v>
+        <v>1.4032716409895648e-05</v>
+      </c>
+      <c r="Z7">
+        <v>-0.0012961991244789463</v>
       </c>
     </row>
     <row r="8">
@@ -846,76 +870,79 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.0051666842216324506</v>
+        <v>0.0075504340374938856</v>
       </c>
       <c r="C8">
-        <v>1.2048132821244012e-06</v>
+        <v>1.3286511033854452e-06</v>
       </c>
       <c r="D8">
-        <v>-3.6500340493763753e-07</v>
+        <v>-2.2999680633760394e-07</v>
       </c>
       <c r="E8">
-        <v>-7.1790443122578872e-07</v>
+        <v>-7.569737871403864e-07</v>
       </c>
       <c r="F8">
-        <v>2.5787002734849297e-09</v>
+        <v>2.6852196100138868e-09</v>
       </c>
       <c r="G8">
-        <v>-5.0112884496575182e-05</v>
+        <v>-5.044771129002166e-05</v>
       </c>
       <c r="H8">
-        <v>-2.2567597056830977e-05</v>
+        <v>-2.2788230813259265e-05</v>
       </c>
       <c r="I8">
-        <v>1.130875351294358e-06</v>
+        <v>1.1423916790476531e-06</v>
       </c>
       <c r="J8">
-        <v>5.1452474929939692e-07</v>
+        <v>5.2034247617169564e-07</v>
       </c>
       <c r="K8">
-        <v>4.8789263537601835e-08</v>
+        <v>1.0224246224118245e-07</v>
       </c>
       <c r="L8">
-        <v>1.2458854235625857e-06</v>
+        <v>1.2535883371543181e-06</v>
       </c>
       <c r="M8">
-        <v>-1.1128263243365947e-07</v>
+        <v>-1.399952896480036e-07</v>
       </c>
       <c r="N8">
-        <v>-1.1772922216912714e-07</v>
+        <v>-1.205707987824792e-07</v>
       </c>
       <c r="O8">
-        <v>-1.8206144200683642e-09</v>
+        <v>9.1060338185148463e-09</v>
       </c>
       <c r="P8">
-        <v>-3.1537604152042487e-07</v>
+        <v>-3.1706508295979259e-07</v>
       </c>
       <c r="Q8">
-        <v>-9.7212390663943119e-09</v>
+        <v>3.7102313249916483e-08</v>
       </c>
       <c r="R8">
-        <v>1.7409468455269698e-08</v>
+        <v>-8.3015379472454521e-08</v>
       </c>
       <c r="S8">
-        <v>3.3591308395722893e-08</v>
+        <v>-5.8354365748263289e-08</v>
       </c>
       <c r="T8">
-        <v>3.4439220642453433e-08</v>
+        <v>2.3334068477341894e-08</v>
       </c>
       <c r="U8">
-        <v>1.8182331757358624e-07</v>
+        <v>-5.9690614209086779e-08</v>
       </c>
       <c r="V8">
-        <v>1.5061429402537124e-07</v>
+        <v>1.896730739084601e-07</v>
       </c>
       <c r="W8">
-        <v>-7.7403302727960661e-08</v>
+        <v>1.3217555826480361e-07</v>
       </c>
       <c r="X8">
-        <v>-5.6021037201607934e-08</v>
+        <v>-9.2291602435150209e-08</v>
       </c>
       <c r="Y8">
-        <v>2.5627798791456673e-05</v>
+        <v>-1.2556037363747723e-08</v>
+      </c>
+      <c r="Z8">
+        <v>2.6390967054190713e-05</v>
       </c>
     </row>
     <row r="9">
@@ -923,76 +950,79 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>0.0034662871717521457</v>
+        <v>0.0077627868857333797</v>
       </c>
       <c r="C9">
-        <v>-1.3648060641901778e-06</v>
+        <v>-1.2456703291868549e-06</v>
       </c>
       <c r="D9">
-        <v>-4.0967327252641896e-07</v>
+        <v>-1.8235104951562917e-07</v>
       </c>
       <c r="E9">
-        <v>-6.5769499656390078e-07</v>
+        <v>-7.112558156926794e-07</v>
       </c>
       <c r="F9">
-        <v>1.7649944165524716e-09</v>
+        <v>1.8174395357988716e-09</v>
       </c>
       <c r="G9">
-        <v>-2.2427606192300533e-05</v>
+        <v>-2.2648266998356479e-05</v>
       </c>
       <c r="H9">
-        <v>-4.4376557510629882e-05</v>
+        <v>-4.5167485190274483e-05</v>
       </c>
       <c r="I9">
-        <v>5.1452474929939692e-07</v>
+        <v>5.2034247617169564e-07</v>
       </c>
       <c r="J9">
-        <v>9.6958631562493796e-07</v>
+        <v>9.8958151688537802e-07</v>
       </c>
       <c r="K9">
-        <v>-4.7545168266514061e-07</v>
+        <v>-3.943388567201831e-07</v>
       </c>
       <c r="L9">
-        <v>2.3937216971513414e-06</v>
+        <v>2.3997455096105798e-06</v>
       </c>
       <c r="M9">
-        <v>-3.2141197783149047e-07</v>
+        <v>-3.3335007184202349e-07</v>
       </c>
       <c r="N9">
-        <v>-2.2825374269972557e-07</v>
+        <v>-1.5553663692365041e-07</v>
       </c>
       <c r="O9">
-        <v>1.7682540274371714e-07</v>
+        <v>2.6717103873942158e-07</v>
       </c>
       <c r="P9">
-        <v>-2.3591763203369005e-07</v>
+        <v>-1.8023947984771411e-07</v>
       </c>
       <c r="Q9">
-        <v>-3.2299563272393614e-08</v>
+        <v>6.0162141359146921e-08</v>
       </c>
       <c r="R9">
-        <v>3.7279684143280041e-07</v>
+        <v>-1.1186454076395495e-07</v>
       </c>
       <c r="S9">
-        <v>1.4552354290964423e-07</v>
+        <v>3.22721936267274e-07</v>
       </c>
       <c r="T9">
-        <v>2.3335993640902808e-07</v>
+        <v>1.8317184748092418e-07</v>
       </c>
       <c r="U9">
-        <v>4.3254146204420034e-07</v>
+        <v>1.1340475130608936e-07</v>
       </c>
       <c r="V9">
-        <v>2.6355758540149212e-07</v>
+        <v>4.5644426105795222e-07</v>
       </c>
       <c r="W9">
-        <v>-2.042803182526439e-07</v>
+        <v>2.7272960988452918e-07</v>
       </c>
       <c r="X9">
-        <v>-1.2896416623809115e-07</v>
+        <v>-2.3310258911807696e-07</v>
       </c>
       <c r="Y9">
-        <v>2.4462636574844633e-05</v>
+        <v>-8.7702559998273634e-08</v>
+      </c>
+      <c r="Z9">
+        <v>2.546464679012746e-05</v>
       </c>
     </row>
     <row r="10">
@@ -1000,76 +1030,79 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>-0.045998186025236823</v>
+        <v>-0.024624477212956814</v>
       </c>
       <c r="C10">
-        <v>2.1439497551592387e-05</v>
+        <v>2.219644913675412e-05</v>
       </c>
       <c r="D10">
-        <v>-3.580590229525579e-06</v>
+        <v>-2.2477718561934414e-06</v>
       </c>
       <c r="E10">
-        <v>-8.4402585779852944e-06</v>
+        <v>-8.9300759257192039e-06</v>
       </c>
       <c r="F10">
-        <v>7.314534665699316e-08</v>
+        <v>7.518177652989452e-08</v>
       </c>
       <c r="G10">
-        <v>-4.9797090098398636e-06</v>
+        <v>-7.6165986743787577e-06</v>
       </c>
       <c r="H10">
-        <v>1.433526743097214e-05</v>
+        <v>1.0350405706673112e-05</v>
       </c>
       <c r="I10">
-        <v>4.8789263537601835e-08</v>
+        <v>1.0224246224118245e-07</v>
       </c>
       <c r="J10">
-        <v>-4.7545168266514061e-07</v>
+        <v>-3.943388567201831e-07</v>
       </c>
       <c r="K10">
-        <v>0.00016799723784415314</v>
+        <v>0.00017170204669787222</v>
       </c>
       <c r="L10">
-        <v>-5.3677858640336147e-05</v>
+        <v>-5.5523263868117274e-05</v>
       </c>
       <c r="M10">
-        <v>-6.5819604144089208e-06</v>
+        <v>-6.5381047417491323e-06</v>
       </c>
       <c r="N10">
-        <v>-1.5904368563854731e-05</v>
+        <v>-1.5444966715953412e-05</v>
       </c>
       <c r="O10">
-        <v>-2.373753494629186e-05</v>
+        <v>-2.3146681895139744e-05</v>
       </c>
       <c r="P10">
-        <v>-2.3009149144296783e-05</v>
+        <v>-2.2432522750101261e-05</v>
       </c>
       <c r="Q10">
-        <v>-2.6197996212978847e-06</v>
+        <v>3.3677915190087711e-07</v>
       </c>
       <c r="R10">
-        <v>3.0533854435091779e-06</v>
+        <v>-3.3217328250843635e-06</v>
       </c>
       <c r="S10">
-        <v>-3.2784814314428069e-06</v>
+        <v>2.9383760354337081e-06</v>
       </c>
       <c r="T10">
-        <v>-2.3311719155054624e-06</v>
+        <v>-3.636547225010421e-06</v>
       </c>
       <c r="U10">
-        <v>1.5022836475517798e-07</v>
+        <v>-3.3476270551322468e-06</v>
       </c>
       <c r="V10">
-        <v>1.1724136590822772e-05</v>
+        <v>-1.7557790887960642e-07</v>
       </c>
       <c r="W10">
-        <v>-7.7222601092049771e-07</v>
+        <v>1.2083299625064571e-05</v>
       </c>
       <c r="X10">
-        <v>4.6357544280030496e-07</v>
+        <v>-9.9510835318938484e-07</v>
       </c>
       <c r="Y10">
-        <v>0.00015915900734784594</v>
+        <v>7.5836888662399902e-07</v>
+      </c>
+      <c r="Z10">
+        <v>0.0001690577638129316</v>
       </c>
     </row>
     <row r="11">
@@ -1077,76 +1110,79 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>-0.11982533180292289</v>
+        <v>-0.14231460326413176</v>
       </c>
       <c r="C11">
-        <v>1.3458024764383759e-06</v>
+        <v>-7.359396193591757e-07</v>
       </c>
       <c r="D11">
-        <v>-4.1318779779253134e-06</v>
+        <v>-5.8484349744438527e-06</v>
       </c>
       <c r="E11">
-        <v>-1.3106794664545801e-05</v>
+        <v>-1.3393191051818346e-05</v>
       </c>
       <c r="F11">
-        <v>1.5732232647926429e-07</v>
+        <v>1.6481834366852625e-07</v>
       </c>
       <c r="G11">
-        <v>-5.5283438720190011e-05</v>
+        <v>-5.5447234779507033e-05</v>
       </c>
       <c r="H11">
-        <v>-0.00011239437131380168</v>
+        <v>-0.00011268571511041256</v>
       </c>
       <c r="I11">
-        <v>1.2458854235625857e-06</v>
+        <v>1.2535883371543181e-06</v>
       </c>
       <c r="J11">
-        <v>2.3937216971513414e-06</v>
+        <v>2.3997455096105798e-06</v>
       </c>
       <c r="K11">
-        <v>-5.3677858640336147e-05</v>
+        <v>-5.5523263868117274e-05</v>
       </c>
       <c r="L11">
-        <v>0.00017753240089045554</v>
+        <v>0.00018229533412657218</v>
       </c>
       <c r="M11">
-        <v>-5.3737417042318503e-06</v>
+        <v>-6.1241191559891368e-06</v>
       </c>
       <c r="N11">
-        <v>-1.0981124575140699e-05</v>
+        <v>-1.2549078790247904e-05</v>
       </c>
       <c r="O11">
-        <v>-1.6603702468657804e-05</v>
+        <v>-1.8293384569064455e-05</v>
       </c>
       <c r="P11">
-        <v>-1.8716123572759232e-05</v>
+        <v>-2.0348279388403718e-05</v>
       </c>
       <c r="Q11">
-        <v>-7.3448072448627564e-06</v>
+        <v>-4.8896835291473912e-07</v>
       </c>
       <c r="R11">
-        <v>-7.1861325040677328e-06</v>
+        <v>-6.6428712968703971e-06</v>
       </c>
       <c r="S11">
-        <v>-4.1239763400899074e-06</v>
+        <v>-6.5356297274001287e-06</v>
       </c>
       <c r="T11">
-        <v>-7.2965831502472852e-06</v>
+        <v>-3.6811556557760552e-06</v>
       </c>
       <c r="U11">
-        <v>-6.1505745509341717e-06</v>
+        <v>-6.2233177109440549e-06</v>
       </c>
       <c r="V11">
-        <v>-8.9422852147303345e-07</v>
+        <v>-5.9288509656043902e-06</v>
       </c>
       <c r="W11">
-        <v>-2.2881814769898051e-06</v>
+        <v>-1.100428069837047e-06</v>
       </c>
       <c r="X11">
-        <v>-5.3822970121752696e-06</v>
+        <v>-2.0636570544816705e-06</v>
       </c>
       <c r="Y11">
-        <v>0.0002324886960668921</v>
+        <v>-5.9022033642328188e-06</v>
+      </c>
+      <c r="Z11">
+        <v>0.00023855756671546091</v>
       </c>
     </row>
     <row r="12">
@@ -1154,76 +1190,79 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>0.25280543106962788</v>
+        <v>0.25620717936425419</v>
       </c>
       <c r="C12">
-        <v>5.9028078636401459e-07</v>
+        <v>1.5434830735697072e-06</v>
       </c>
       <c r="D12">
-        <v>2.8413217147769655e-06</v>
+        <v>3.4984098892758676e-06</v>
       </c>
       <c r="E12">
-        <v>2.2443450283016929e-06</v>
+        <v>2.3993220286065145e-06</v>
       </c>
       <c r="F12">
-        <v>-2.5434729507913763e-08</v>
+        <v>-2.8055024412318066e-08</v>
       </c>
       <c r="G12">
-        <v>7.1674452892406823e-06</v>
+        <v>8.1445274477991636e-06</v>
       </c>
       <c r="H12">
-        <v>1.2145353253368749e-05</v>
+        <v>1.2493033659000748e-05</v>
       </c>
       <c r="I12">
-        <v>-1.1128263243365947e-07</v>
+        <v>-1.399952896480036e-07</v>
       </c>
       <c r="J12">
-        <v>-3.2141197783149047e-07</v>
+        <v>-3.3335007184202349e-07</v>
       </c>
       <c r="K12">
-        <v>-6.5819604144089208e-06</v>
+        <v>-6.5381047417491323e-06</v>
       </c>
       <c r="L12">
-        <v>-5.3737417042318503e-06</v>
+        <v>-6.1241191559891368e-06</v>
       </c>
       <c r="M12">
-        <v>0.004372957178233868</v>
+        <v>0.00445941852471703</v>
       </c>
       <c r="N12">
-        <v>0.0035888054515906846</v>
+        <v>0.0036535588356368049</v>
       </c>
       <c r="O12">
-        <v>0.0035878538529015985</v>
+        <v>0.0036525501000477254</v>
       </c>
       <c r="P12">
-        <v>0.00358659742904364</v>
+        <v>0.0036512714900911389</v>
       </c>
       <c r="Q12">
-        <v>7.796928143678902e-06</v>
+        <v>1.1675441587267794e-07</v>
       </c>
       <c r="R12">
-        <v>1.2453878747349054e-05</v>
+        <v>7.6075112208190784e-06</v>
       </c>
       <c r="S12">
-        <v>4.6349414388659616e-06</v>
+        <v>1.3425208963266993e-05</v>
       </c>
       <c r="T12">
-        <v>9.9424377755175992e-06</v>
+        <v>4.9203065808502659e-06</v>
       </c>
       <c r="U12">
-        <v>2.3077716223311246e-06</v>
+        <v>9.8614613784957174e-06</v>
       </c>
       <c r="V12">
-        <v>1.09488323283905e-05</v>
+        <v>2.9910377989261652e-06</v>
       </c>
       <c r="W12">
-        <v>-3.6183243356996005e-06</v>
+        <v>1.0687800075363452e-05</v>
       </c>
       <c r="X12">
-        <v>2.848929717393889e-06</v>
+        <v>-3.1094742686230892e-06</v>
       </c>
       <c r="Y12">
-        <v>-0.0036334008134786574</v>
+        <v>2.8753334629048894e-06</v>
+      </c>
+      <c r="Z12">
+        <v>-0.0037015595912392048</v>
       </c>
     </row>
     <row r="13">
@@ -1231,76 +1270,79 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>0.52157037460033107</v>
+        <v>0.54120895200470676</v>
       </c>
       <c r="C13">
-        <v>5.1051509280343249e-06</v>
+        <v>7.4649403790694223e-06</v>
       </c>
       <c r="D13">
-        <v>8.0920555668338997e-06</v>
+        <v>9.8955201939563301e-06</v>
       </c>
       <c r="E13">
-        <v>4.8417717685456671e-06</v>
+        <v>4.9909505256218536e-06</v>
       </c>
       <c r="F13">
-        <v>-5.1546329032097234e-08</v>
+        <v>-5.7337150945239371e-08</v>
       </c>
       <c r="G13">
-        <v>8.6099513089398514e-06</v>
+        <v>8.3616104664535076e-06</v>
       </c>
       <c r="H13">
-        <v>1.078676700011727e-05</v>
+        <v>7.8134273613777463e-06</v>
       </c>
       <c r="I13">
-        <v>-1.1772922216912714e-07</v>
+        <v>-1.205707987824792e-07</v>
       </c>
       <c r="J13">
-        <v>-2.2825374269972557e-07</v>
+        <v>-1.5553663692365041e-07</v>
       </c>
       <c r="K13">
-        <v>-1.5904368563854731e-05</v>
+        <v>-1.5444966715953412e-05</v>
       </c>
       <c r="L13">
-        <v>-1.0981124575140699e-05</v>
+        <v>-1.2549078790247904e-05</v>
       </c>
       <c r="M13">
-        <v>0.0035888054515906846</v>
+        <v>0.0036535588356368049</v>
       </c>
       <c r="N13">
-        <v>0.0037396739614343737</v>
+        <v>0.0038091446200295507</v>
       </c>
       <c r="O13">
-        <v>0.0035932635813044241</v>
+        <v>0.0036585746272456486</v>
       </c>
       <c r="P13">
-        <v>0.0035945134525349849</v>
+        <v>0.0036598642336762048</v>
       </c>
       <c r="Q13">
-        <v>2.0865113036044023e-06</v>
+        <v>4.6912235873993631e-07</v>
       </c>
       <c r="R13">
-        <v>5.1069692374107912e-06</v>
+        <v>1.0196344156339571e-06</v>
       </c>
       <c r="S13">
-        <v>-2.6682920428674508e-06</v>
+        <v>4.9805993674930386e-06</v>
       </c>
       <c r="T13">
-        <v>6.9525373830177476e-06</v>
+        <v>-2.7732288194646463e-06</v>
       </c>
       <c r="U13">
-        <v>-5.0922965882223362e-06</v>
+        <v>5.9113915357045791e-06</v>
       </c>
       <c r="V13">
-        <v>-6.1477327371782184e-07</v>
+        <v>-5.3249331859008052e-06</v>
       </c>
       <c r="W13">
-        <v>-7.6993170199178874e-06</v>
+        <v>-1.3002393484160099e-06</v>
       </c>
       <c r="X13">
-        <v>2.3170809090563424e-06</v>
+        <v>-6.7703289971330556e-06</v>
       </c>
       <c r="Y13">
-        <v>-0.0036884452319085187</v>
+        <v>2.5648833465616211e-06</v>
+      </c>
+      <c r="Z13">
+        <v>-0.0037560916943745601</v>
       </c>
     </row>
     <row r="14">
@@ -1308,76 +1350,79 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0.67643052677394822</v>
+        <v>0.68869826695567227</v>
       </c>
       <c r="C14">
-        <v>4.8607902423147592e-06</v>
+        <v>7.0083336797136051e-06</v>
       </c>
       <c r="D14">
-        <v>1.062733572271395e-05</v>
+        <v>1.2243596647533884e-05</v>
       </c>
       <c r="E14">
-        <v>6.5115107533637894e-06</v>
+        <v>6.7355729372238369e-06</v>
       </c>
       <c r="F14">
-        <v>-6.1939329435683823e-08</v>
+        <v>-6.7630407186636376e-08</v>
       </c>
       <c r="G14">
-        <v>1.1415153222290404e-05</v>
+        <v>1.1047075247567811e-05</v>
       </c>
       <c r="H14">
-        <v>9.534227646613156e-06</v>
+        <v>6.5723218719825624e-06</v>
       </c>
       <c r="I14">
-        <v>-1.8206144200683642e-09</v>
+        <v>9.1060338185148463e-09</v>
       </c>
       <c r="J14">
-        <v>1.7682540274371714e-07</v>
+        <v>2.6717103873942158e-07</v>
       </c>
       <c r="K14">
-        <v>-2.373753494629186e-05</v>
+        <v>-2.3146681895139744e-05</v>
       </c>
       <c r="L14">
-        <v>-1.6603702468657804e-05</v>
+        <v>-1.8293384569064455e-05</v>
       </c>
       <c r="M14">
-        <v>0.0035878538529015985</v>
+        <v>0.0036525501000477254</v>
       </c>
       <c r="N14">
-        <v>0.0035932635813044241</v>
+        <v>0.0036585746272456486</v>
       </c>
       <c r="O14">
-        <v>0.0036498719074989508</v>
+        <v>0.0037166777787061957</v>
       </c>
       <c r="P14">
-        <v>0.0036126075904647599</v>
+        <v>0.0036786250836621003</v>
       </c>
       <c r="Q14">
-        <v>-4.3263167789895133e-06</v>
+        <v>3.7423271936408753e-07</v>
       </c>
       <c r="R14">
-        <v>9.0247306661077234e-07</v>
+        <v>-5.1993440967017772e-06</v>
       </c>
       <c r="S14">
-        <v>-9.7948247443882297e-06</v>
+        <v>9.1743632378906163e-07</v>
       </c>
       <c r="T14">
-        <v>3.7826019202283942e-06</v>
+        <v>-9.7879831900940295e-06</v>
       </c>
       <c r="U14">
-        <v>-9.6351420970411226e-06</v>
+        <v>3.0826687148788627e-06</v>
       </c>
       <c r="V14">
-        <v>5.3159601723452231e-06</v>
+        <v>-9.5281850517983825e-06</v>
       </c>
       <c r="W14">
-        <v>-7.9803980682089089e-06</v>
+        <v>4.8707980662710806e-06</v>
       </c>
       <c r="X14">
-        <v>4.964210520537333e-06</v>
+        <v>-7.2770893064439471e-06</v>
       </c>
       <c r="Y14">
-        <v>-0.0037500106803139621</v>
+        <v>5.4268852389868896e-06</v>
+      </c>
+      <c r="Z14">
+        <v>-0.0038203584030275968</v>
       </c>
     </row>
     <row r="15">
@@ -1385,76 +1430,79 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>0.6697323857460088</v>
+        <v>0.676200938836094</v>
       </c>
       <c r="C15">
-        <v>1.9284411210990118e-06</v>
+        <v>3.7772961390521924e-06</v>
       </c>
       <c r="D15">
-        <v>1.2861097919746893e-05</v>
+        <v>1.41482707920021e-05</v>
       </c>
       <c r="E15">
-        <v>1.0562414049499762e-05</v>
+        <v>1.088549346054398e-05</v>
       </c>
       <c r="F15">
-        <v>-9.1979313853705399e-08</v>
+        <v>-9.7550700361534012e-08</v>
       </c>
       <c r="G15">
-        <v>3.2827544449442049e-05</v>
+        <v>3.319698549740437e-05</v>
       </c>
       <c r="H15">
-        <v>3.9010181603094671e-05</v>
+        <v>3.7782438473305446e-05</v>
       </c>
       <c r="I15">
-        <v>-3.1537604152042487e-07</v>
+        <v>-3.1706508295979259e-07</v>
       </c>
       <c r="J15">
-        <v>-2.3591763203369005e-07</v>
+        <v>-1.8023947984771411e-07</v>
       </c>
       <c r="K15">
-        <v>-2.3009149144296783e-05</v>
+        <v>-2.2432522750101261e-05</v>
       </c>
       <c r="L15">
-        <v>-1.8716123572759232e-05</v>
+        <v>-2.0348279388403718e-05</v>
       </c>
       <c r="M15">
-        <v>0.00358659742904364</v>
+        <v>0.0036512714900911389</v>
       </c>
       <c r="N15">
-        <v>0.0035945134525349849</v>
+        <v>0.0036598642336762048</v>
       </c>
       <c r="O15">
-        <v>0.0036126075904647599</v>
+        <v>0.0036786250836621003</v>
       </c>
       <c r="P15">
-        <v>0.0037926545188960081</v>
+        <v>0.0038611383771245834</v>
       </c>
       <c r="Q15">
-        <v>-1.180491652666714e-05</v>
+        <v>2.626833218162217e-07</v>
       </c>
       <c r="R15">
-        <v>-8.1415857327138934e-06</v>
+        <v>-1.2909067067941283e-05</v>
       </c>
       <c r="S15">
-        <v>-1.365607456398905e-05</v>
+        <v>-8.6738774494122585e-06</v>
       </c>
       <c r="T15">
-        <v>-9.0499108089618218e-06</v>
+        <v>-1.408803690208644e-05</v>
       </c>
       <c r="U15">
-        <v>-1.988841745252533e-05</v>
+        <v>-1.0088952156438576e-05</v>
       </c>
       <c r="V15">
-        <v>-5.4459401332375212e-06</v>
+        <v>-2.0151269358472895e-05</v>
       </c>
       <c r="W15">
-        <v>-1.2775478515754379e-05</v>
+        <v>-6.1321586013183323e-06</v>
       </c>
       <c r="X15">
-        <v>4.6301228970105289e-06</v>
+        <v>-1.2303093981586267e-05</v>
       </c>
       <c r="Y15">
-        <v>-0.003873809971319319</v>
+        <v>5.0101825393995855e-06</v>
+      </c>
+      <c r="Z15">
+        <v>-0.0039465038669718386</v>
       </c>
     </row>
     <row r="16">
@@ -1462,76 +1510,79 @@
         <v>36</v>
       </c>
       <c r="B16">
-        <v>0.073939030733738878</v>
+        <v>0.024772303466757004</v>
       </c>
       <c r="C16">
-        <v>2.8625945207049448e-06</v>
+        <v>1.3545127696711973e-06</v>
       </c>
       <c r="D16">
-        <v>2.0028269068119913e-06</v>
+        <v>1.3849241471652581e-06</v>
       </c>
       <c r="E16">
-        <v>1.4235205166774607e-06</v>
+        <v>-1.5605865178997735e-07</v>
       </c>
       <c r="F16">
-        <v>-1.7877888888929421e-08</v>
+        <v>-2.1892453526480978e-09</v>
       </c>
       <c r="G16">
-        <v>4.8732857632976776e-06</v>
+        <v>-1.7375745621032226e-06</v>
       </c>
       <c r="H16">
-        <v>8.3164767321658455e-06</v>
+        <v>-2.7480565838816848e-06</v>
       </c>
       <c r="I16">
-        <v>-9.7212390663943119e-09</v>
+        <v>3.7102313249916483e-08</v>
       </c>
       <c r="J16">
-        <v>-3.2299563272393614e-08</v>
+        <v>6.0162141359146921e-08</v>
       </c>
       <c r="K16">
-        <v>-2.6197996212978847e-06</v>
+        <v>3.3677915190087711e-07</v>
       </c>
       <c r="L16">
-        <v>-7.3448072448627564e-06</v>
+        <v>-4.8896835291473912e-07</v>
       </c>
       <c r="M16">
-        <v>7.796928143678902e-06</v>
+        <v>1.1675441587267794e-07</v>
       </c>
       <c r="N16">
-        <v>2.0865113036044023e-06</v>
+        <v>4.6912235873993631e-07</v>
       </c>
       <c r="O16">
-        <v>-4.3263167789895133e-06</v>
+        <v>3.7423271936408753e-07</v>
       </c>
       <c r="P16">
-        <v>-1.180491652666714e-05</v>
+        <v>2.626833218162217e-07</v>
       </c>
       <c r="Q16">
-        <v>0.00039952377021493105</v>
+        <v>4.3806135849538753e-07</v>
       </c>
       <c r="R16">
-        <v>0.00020970808892838833</v>
+        <v>-5.6530757645218554e-07</v>
       </c>
       <c r="S16">
-        <v>0.00020839606423495708</v>
+        <v>-5.2192839907697023e-07</v>
       </c>
       <c r="T16">
-        <v>0.00020918703948760966</v>
+        <v>4.1577873525771819e-08</v>
       </c>
       <c r="U16">
-        <v>0.00020814866367216048</v>
+        <v>-8.2621743337637152e-07</v>
       </c>
       <c r="V16">
-        <v>0.00020734765954582212</v>
+        <v>4.1551117315934833e-08</v>
       </c>
       <c r="W16">
-        <v>1.4240997745217489e-06</v>
+        <v>-8.444849272337797e-09</v>
       </c>
       <c r="X16">
-        <v>1.6156980382192108e-07</v>
+        <v>-7.6770653114677691e-08</v>
       </c>
       <c r="Y16">
-        <v>-0.00022973963415141353</v>
+        <v>3.5576885479050021e-07</v>
+      </c>
+      <c r="Z16">
+        <v>3.4721954951140651e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1539,76 +1590,79 @@
         <v>37</v>
       </c>
       <c r="B17">
-        <v>0.05473605787533857</v>
+        <v>0.041720528739101231</v>
       </c>
       <c r="C17">
-        <v>3.759834000307216e-06</v>
+        <v>1.1730175784176885e-06</v>
       </c>
       <c r="D17">
-        <v>3.0200197275771797e-06</v>
+        <v>3.8445336244228958e-07</v>
       </c>
       <c r="E17">
-        <v>1.178570278737875e-06</v>
+        <v>1.5782097801583171e-06</v>
       </c>
       <c r="F17">
-        <v>-1.6927703041294986e-08</v>
+        <v>-1.4345431578920102e-08</v>
       </c>
       <c r="G17">
-        <v>1.504498556332856e-06</v>
+        <v>8.1026940519441022e-06</v>
       </c>
       <c r="H17">
-        <v>-5.7556187337109119e-06</v>
+        <v>1.2238845624991258e-05</v>
       </c>
       <c r="I17">
-        <v>1.7409468455269698e-08</v>
+        <v>-8.3015379472454521e-08</v>
       </c>
       <c r="J17">
-        <v>3.7279684143280041e-07</v>
+        <v>-1.1186454076395495e-07</v>
       </c>
       <c r="K17">
-        <v>3.0533854435091779e-06</v>
+        <v>-3.3217328250843635e-06</v>
       </c>
       <c r="L17">
-        <v>-7.1861325040677328e-06</v>
+        <v>-6.6428712968703971e-06</v>
       </c>
       <c r="M17">
-        <v>1.2453878747349054e-05</v>
+        <v>7.6075112208190784e-06</v>
       </c>
       <c r="N17">
-        <v>5.1069692374107912e-06</v>
+        <v>1.0196344156339571e-06</v>
       </c>
       <c r="O17">
-        <v>9.0247306661077234e-07</v>
+        <v>-5.1993440967017772e-06</v>
       </c>
       <c r="P17">
-        <v>-8.1415857327138934e-06</v>
+        <v>-1.2909067067941283e-05</v>
       </c>
       <c r="Q17">
-        <v>0.00020970808892838833</v>
+        <v>-5.6530757645218554e-07</v>
       </c>
       <c r="R17">
-        <v>0.00047970203285934218</v>
+        <v>0.00040980606519527857</v>
       </c>
       <c r="S17">
-        <v>0.0002078808772396059</v>
+        <v>0.00021504281239235616</v>
       </c>
       <c r="T17">
-        <v>0.000209266645245289</v>
+        <v>0.00021290210108279036</v>
       </c>
       <c r="U17">
-        <v>0.00020778396247767469</v>
+        <v>0.00021487972688392307</v>
       </c>
       <c r="V17">
-        <v>0.0002078106975997259</v>
+        <v>0.00021266121926168509</v>
       </c>
       <c r="W17">
-        <v>-7.7695844309462783e-07</v>
+        <v>0.00021192862077603944</v>
       </c>
       <c r="X17">
-        <v>-4.8549173605707801e-06</v>
+        <v>1.3618483020789565e-06</v>
       </c>
       <c r="Y17">
-        <v>-0.00023051851957970958</v>
+        <v>-6.5182763612651129e-07</v>
+      </c>
+      <c r="Z17">
+        <v>-0.00023777596873273695</v>
       </c>
     </row>
     <row r="18">
@@ -1616,76 +1670,79 @@
         <v>38</v>
       </c>
       <c r="B18">
-        <v>-0.011406352161242117</v>
+        <v>0.024987092508328434</v>
       </c>
       <c r="C18">
-        <v>5.7401949537125118e-07</v>
+        <v>2.2668562622614141e-06</v>
       </c>
       <c r="D18">
-        <v>-2.4128980061865548e-06</v>
+        <v>1.3996817918555338e-06</v>
       </c>
       <c r="E18">
-        <v>4.8090966906169126e-07</v>
+        <v>1.2813247039407887e-06</v>
       </c>
       <c r="F18">
-        <v>-4.6668756085052081e-09</v>
+        <v>-1.3333470025109639e-08</v>
       </c>
       <c r="G18">
-        <v>-1.9781797199175846e-06</v>
+        <v>4.7019958305843498e-06</v>
       </c>
       <c r="H18">
-        <v>-1.7046291545810205e-05</v>
+        <v>-3.1112537259943683e-06</v>
       </c>
       <c r="I18">
-        <v>3.3591308395722893e-08</v>
+        <v>-5.8354365748263289e-08</v>
       </c>
       <c r="J18">
-        <v>1.4552354290964423e-07</v>
+        <v>3.22721936267274e-07</v>
       </c>
       <c r="K18">
-        <v>-3.2784814314428069e-06</v>
+        <v>2.9383760354337081e-06</v>
       </c>
       <c r="L18">
-        <v>-4.1239763400899074e-06</v>
+        <v>-6.5356297274001287e-06</v>
       </c>
       <c r="M18">
-        <v>4.6349414388659616e-06</v>
+        <v>1.3425208963266993e-05</v>
       </c>
       <c r="N18">
-        <v>-2.6682920428674508e-06</v>
+        <v>4.9805993674930386e-06</v>
       </c>
       <c r="O18">
-        <v>-9.7948247443882297e-06</v>
+        <v>9.1743632378906163e-07</v>
       </c>
       <c r="P18">
-        <v>-1.365607456398905e-05</v>
+        <v>-8.6738774494122585e-06</v>
       </c>
       <c r="Q18">
-        <v>0.00020839606423495708</v>
+        <v>-5.2192839907697023e-07</v>
       </c>
       <c r="R18">
-        <v>0.0002078808772396059</v>
+        <v>0.00021504281239235616</v>
       </c>
       <c r="S18">
-        <v>0.00038811341295038796</v>
+        <v>0.00049170314132991231</v>
       </c>
       <c r="T18">
-        <v>0.00020883198976503459</v>
+        <v>0.00021241743722831663</v>
       </c>
       <c r="U18">
-        <v>0.00021064119155054603</v>
+        <v>0.00021491142896570847</v>
       </c>
       <c r="V18">
-        <v>0.00020841724370849164</v>
+        <v>0.00021232546027144452</v>
       </c>
       <c r="W18">
-        <v>-4.9296783591883805e-06</v>
+        <v>0.00021247550409953786</v>
       </c>
       <c r="X18">
-        <v>-5.7235287156870373e-06</v>
+        <v>-6.0353545484223735e-07</v>
       </c>
       <c r="Y18">
-        <v>-0.0002028385161672271</v>
+        <v>-5.2829298166017293e-06</v>
+      </c>
+      <c r="Z18">
+        <v>-0.00023830141024242332</v>
       </c>
     </row>
     <row r="19">
@@ -1693,76 +1750,79 @@
         <v>39</v>
       </c>
       <c r="B19">
-        <v>0.095650862321854518</v>
+        <v>-0.0090416525463847732</v>
       </c>
       <c r="C19">
-        <v>5.736884804500962e-06</v>
+        <v>1.9821197461250868e-07</v>
       </c>
       <c r="D19">
-        <v>1.7093014299367719e-06</v>
+        <v>-2.3420650121424808e-06</v>
       </c>
       <c r="E19">
-        <v>1.6627613582729379e-06</v>
+        <v>3.1860402988783951e-07</v>
       </c>
       <c r="F19">
-        <v>-2.0051108673750957e-08</v>
+        <v>-3.0023207302428985e-09</v>
       </c>
       <c r="G19">
-        <v>-5.5319646321372754e-06</v>
+        <v>-1.8533512691450214e-06</v>
       </c>
       <c r="H19">
-        <v>-1.2988412160836089e-05</v>
+        <v>-1.9134992747611256e-05</v>
       </c>
       <c r="I19">
-        <v>3.4439220642453433e-08</v>
+        <v>2.3334068477341894e-08</v>
       </c>
       <c r="J19">
-        <v>2.3335993640902808e-07</v>
+        <v>1.8317184748092418e-07</v>
       </c>
       <c r="K19">
-        <v>-2.3311719155054624e-06</v>
+        <v>-3.636547225010421e-06</v>
       </c>
       <c r="L19">
-        <v>-7.2965831502472852e-06</v>
+        <v>-3.6811556557760552e-06</v>
       </c>
       <c r="M19">
-        <v>9.9424377755175992e-06</v>
+        <v>4.9203065808502659e-06</v>
       </c>
       <c r="N19">
-        <v>6.9525373830177476e-06</v>
+        <v>-2.7732288194646463e-06</v>
       </c>
       <c r="O19">
-        <v>3.7826019202283942e-06</v>
+        <v>-9.7879831900940295e-06</v>
       </c>
       <c r="P19">
-        <v>-9.0499108089618218e-06</v>
+        <v>-1.408803690208644e-05</v>
       </c>
       <c r="Q19">
-        <v>0.00020918703948760966</v>
+        <v>4.1577873525771819e-08</v>
       </c>
       <c r="R19">
-        <v>0.000209266645245289</v>
+        <v>0.00021290210108279036</v>
       </c>
       <c r="S19">
-        <v>0.00020883198976503459</v>
+        <v>0.00021241743722831663</v>
       </c>
       <c r="T19">
-        <v>0.0003282765798828837</v>
+        <v>0.00039748162633626908</v>
       </c>
       <c r="U19">
-        <v>0.00020956701882821193</v>
+        <v>0.0002133450881521164</v>
       </c>
       <c r="V19">
-        <v>0.00020846723956346317</v>
+        <v>0.00021536812748487104</v>
       </c>
       <c r="W19">
-        <v>6.5574405688142069e-06</v>
+        <v>0.0002131104994607427</v>
       </c>
       <c r="X19">
-        <v>6.0630947576270373e-06</v>
+        <v>-4.7776348466195438e-06</v>
       </c>
       <c r="Y19">
-        <v>-0.00023801216049149871</v>
+        <v>-6.297724614630115e-06</v>
+      </c>
+      <c r="Z19">
+        <v>-0.00020419301444688011</v>
       </c>
     </row>
     <row r="20">
@@ -1770,76 +1830,79 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <v>-0.10081636936924131</v>
+        <v>0.047792528039750697</v>
       </c>
       <c r="C20">
-        <v>6.4308524325009454e-06</v>
+        <v>3.7098865570265707e-06</v>
       </c>
       <c r="D20">
-        <v>-6.3523805671575023e-06</v>
+        <v>-8.9408508636454302e-07</v>
       </c>
       <c r="E20">
-        <v>3.2246844718863284e-07</v>
+        <v>2.0263678840064211e-06</v>
       </c>
       <c r="F20">
-        <v>-9.5352400363220659e-10</v>
+        <v>-1.658306117728798e-08</v>
       </c>
       <c r="G20">
-        <v>-1.1611480897317256e-05</v>
+        <v>-1.4612173213359944e-06</v>
       </c>
       <c r="H20">
-        <v>-3.6082790884597123e-05</v>
+        <v>-7.3225516524035082e-06</v>
       </c>
       <c r="I20">
-        <v>1.8182331757358624e-07</v>
+        <v>-5.9690614209086779e-08</v>
       </c>
       <c r="J20">
-        <v>4.3254146204420034e-07</v>
+        <v>1.1340475130608936e-07</v>
       </c>
       <c r="K20">
-        <v>1.5022836475517798e-07</v>
+        <v>-3.3476270551322468e-06</v>
       </c>
       <c r="L20">
-        <v>-6.1505745509341717e-06</v>
+        <v>-6.2233177109440549e-06</v>
       </c>
       <c r="M20">
-        <v>2.3077716223311246e-06</v>
+        <v>9.8614613784957174e-06</v>
       </c>
       <c r="N20">
-        <v>-5.0922965882223362e-06</v>
+        <v>5.9113915357045791e-06</v>
       </c>
       <c r="O20">
-        <v>-9.6351420970411226e-06</v>
+        <v>3.0826687148788627e-06</v>
       </c>
       <c r="P20">
-        <v>-1.988841745252533e-05</v>
+        <v>-1.0088952156438576e-05</v>
       </c>
       <c r="Q20">
-        <v>0.00020814866367216048</v>
+        <v>-8.2621743337637152e-07</v>
       </c>
       <c r="R20">
-        <v>0.00020778396247767469</v>
+        <v>0.00021487972688392307</v>
       </c>
       <c r="S20">
-        <v>0.00021064119155054603</v>
+        <v>0.00021491142896570847</v>
       </c>
       <c r="T20">
-        <v>0.00020956701882821193</v>
+        <v>0.0002133450881521164</v>
       </c>
       <c r="U20">
-        <v>0.00035630446974883119</v>
+        <v>0.00033716062340404484</v>
       </c>
       <c r="V20">
-        <v>0.00021018918497203189</v>
+        <v>0.00021407303290563135</v>
       </c>
       <c r="W20">
-        <v>-2.0963625016866275e-07</v>
+        <v>0.00021307148000961903</v>
       </c>
       <c r="X20">
-        <v>-1.8346114928346179e-06</v>
+        <v>7.1166812937265415e-06</v>
       </c>
       <c r="Y20">
-        <v>-0.00020113984537291935</v>
+        <v>5.4928055442230703e-06</v>
+      </c>
+      <c r="Z20">
+        <v>-0.00025058086239383931</v>
       </c>
     </row>
     <row r="21">
@@ -1847,76 +1910,79 @@
         <v>41</v>
       </c>
       <c r="B21">
-        <v>-0.046609943731560064</v>
+        <v>-0.097686315497994253</v>
       </c>
       <c r="C21">
-        <v>-4.2449270722484388e-07</v>
+        <v>6.2622780023743595e-06</v>
       </c>
       <c r="D21">
-        <v>-4.6367972362147762e-06</v>
+        <v>-6.441441538547968e-06</v>
       </c>
       <c r="E21">
-        <v>-1.5465187624462614e-06</v>
+        <v>2.6434628348609063e-07</v>
       </c>
       <c r="F21">
-        <v>1.7848451360334781e-08</v>
+        <v>-5.9339638965883089e-10</v>
       </c>
       <c r="G21">
-        <v>-1.0218844545338312e-05</v>
+        <v>-1.2139539366328588e-05</v>
       </c>
       <c r="H21">
-        <v>-1.9314611712412368e-05</v>
+        <v>-3.7577002294618579e-05</v>
       </c>
       <c r="I21">
-        <v>1.5061429402537124e-07</v>
+        <v>1.896730739084601e-07</v>
       </c>
       <c r="J21">
-        <v>2.6355758540149212e-07</v>
+        <v>4.5644426105795222e-07</v>
       </c>
       <c r="K21">
-        <v>1.1724136590822772e-05</v>
+        <v>-1.7557790887960642e-07</v>
       </c>
       <c r="L21">
-        <v>-8.9422852147303345e-07</v>
+        <v>-5.9288509656043902e-06</v>
       </c>
       <c r="M21">
-        <v>1.09488323283905e-05</v>
+        <v>2.9910377989261652e-06</v>
       </c>
       <c r="N21">
-        <v>-6.1477327371782184e-07</v>
+        <v>-5.3249331859008052e-06</v>
       </c>
       <c r="O21">
-        <v>5.3159601723452231e-06</v>
+        <v>-9.5281850517983825e-06</v>
       </c>
       <c r="P21">
-        <v>-5.4459401332375212e-06</v>
+        <v>-2.0151269358472895e-05</v>
       </c>
       <c r="Q21">
-        <v>0.00020734765954582212</v>
+        <v>4.1551117315934833e-08</v>
       </c>
       <c r="R21">
-        <v>0.0002078106975997259</v>
+        <v>0.00021266121926168509</v>
       </c>
       <c r="S21">
-        <v>0.00020841724370849164</v>
+        <v>0.00021232546027144452</v>
       </c>
       <c r="T21">
-        <v>0.00020846723956346317</v>
+        <v>0.00021536812748487104</v>
       </c>
       <c r="U21">
-        <v>0.00021018918497203189</v>
+        <v>0.00021407303290563135</v>
       </c>
       <c r="V21">
-        <v>0.00092007927223266488</v>
+        <v>0.00036333484207408054</v>
       </c>
       <c r="W21">
-        <v>5.4314226619757109e-06</v>
+        <v>0.0002148946918419303</v>
       </c>
       <c r="X21">
-        <v>5.7695025754377264e-06</v>
+        <v>-1.1331936893811937e-07</v>
       </c>
       <c r="Y21">
-        <v>-0.00018320331100858756</v>
+        <v>-1.899680438628804e-06</v>
+      </c>
+      <c r="Z21">
+        <v>-0.00020426448680112408</v>
       </c>
     </row>
     <row r="22">
@@ -1924,76 +1990,79 @@
         <v>42</v>
       </c>
       <c r="B22">
-        <v>-0.090353240044207653</v>
+        <v>-0.046436675608536753</v>
       </c>
       <c r="C22">
-        <v>9.9154514910156613e-06</v>
+        <v>-1.0279032563837634e-06</v>
       </c>
       <c r="D22">
-        <v>5.5397407375916393e-06</v>
+        <v>-4.8067806564288456e-06</v>
       </c>
       <c r="E22">
-        <v>5.4630878984697236e-07</v>
+        <v>-1.6950909785017579e-06</v>
       </c>
       <c r="F22">
-        <v>-7.0840347204203425e-09</v>
+        <v>1.9656054393782035e-08</v>
       </c>
       <c r="G22">
-        <v>6.6579561869896883e-06</v>
+        <v>-9.8917098088298133e-06</v>
       </c>
       <c r="H22">
-        <v>1.5364197845167787e-05</v>
+        <v>-2.0147560699880733e-05</v>
       </c>
       <c r="I22">
-        <v>-7.7403302727960661e-08</v>
+        <v>1.3217555826480361e-07</v>
       </c>
       <c r="J22">
-        <v>-2.042803182526439e-07</v>
+        <v>2.7272960988452918e-07</v>
       </c>
       <c r="K22">
-        <v>-7.7222601092049771e-07</v>
+        <v>1.2083299625064571e-05</v>
       </c>
       <c r="L22">
-        <v>-2.2881814769898051e-06</v>
+        <v>-1.100428069837047e-06</v>
       </c>
       <c r="M22">
-        <v>-3.6183243356996005e-06</v>
+        <v>1.0687800075363452e-05</v>
       </c>
       <c r="N22">
-        <v>-7.6993170199178874e-06</v>
+        <v>-1.3002393484160099e-06</v>
       </c>
       <c r="O22">
-        <v>-7.9803980682089089e-06</v>
+        <v>4.8707980662710806e-06</v>
       </c>
       <c r="P22">
-        <v>-1.2775478515754379e-05</v>
+        <v>-6.1321586013183323e-06</v>
       </c>
       <c r="Q22">
-        <v>1.4240997745217489e-06</v>
+        <v>-8.444849272337797e-09</v>
       </c>
       <c r="R22">
-        <v>-7.7695844309462783e-07</v>
+        <v>0.00021192862077603944</v>
       </c>
       <c r="S22">
-        <v>-4.9296783591883805e-06</v>
+        <v>0.00021247550409953786</v>
       </c>
       <c r="T22">
-        <v>6.5574405688142069e-06</v>
+        <v>0.0002131104994607427</v>
       </c>
       <c r="U22">
-        <v>-2.0963625016866275e-07</v>
+        <v>0.00021307148000961903</v>
       </c>
       <c r="V22">
-        <v>5.4314226619757109e-06</v>
+        <v>0.0002148946918419303</v>
       </c>
       <c r="W22">
-        <v>0.00051744714241828168</v>
+        <v>0.00093735863487444209</v>
       </c>
       <c r="X22">
-        <v>3.2441371723777231e-05</v>
+        <v>5.4545248457518216e-06</v>
       </c>
       <c r="Y22">
-        <v>-3.6789810356556627e-05</v>
+        <v>5.6054379645182468e-06</v>
+      </c>
+      <c r="Z22">
+        <v>-0.00018417179648963505</v>
       </c>
     </row>
     <row r="23">
@@ -2001,76 +2070,79 @@
         <v>43</v>
       </c>
       <c r="B23">
-        <v>0.041230905834958712</v>
+        <v>-0.093903117116050122</v>
       </c>
       <c r="C23">
-        <v>4.4080477075468059e-06</v>
+        <v>1.0067967947207182e-05</v>
       </c>
       <c r="D23">
-        <v>8.9720374448379542e-06</v>
+        <v>5.7283286465165247e-06</v>
       </c>
       <c r="E23">
-        <v>4.0532211642489738e-07</v>
+        <v>5.9504650960062033e-07</v>
       </c>
       <c r="F23">
-        <v>-6.7621399990584406e-09</v>
+        <v>-6.8224569067966899e-09</v>
       </c>
       <c r="G23">
-        <v>6.3451601328965603e-06</v>
+        <v>7.3627688309860995e-06</v>
       </c>
       <c r="H23">
-        <v>1.5932771462732996e-05</v>
+        <v>1.6707003404383222e-05</v>
       </c>
       <c r="I23">
-        <v>-5.6021037201607934e-08</v>
+        <v>-9.2291602435150209e-08</v>
       </c>
       <c r="J23">
-        <v>-1.2896416623809115e-07</v>
+        <v>-2.3310258911807696e-07</v>
       </c>
       <c r="K23">
-        <v>4.6357544280030496e-07</v>
+        <v>-9.9510835318938484e-07</v>
       </c>
       <c r="L23">
-        <v>-5.3822970121752696e-06</v>
+        <v>-2.0636570544816705e-06</v>
       </c>
       <c r="M23">
-        <v>2.848929717393889e-06</v>
+        <v>-3.1094742686230892e-06</v>
       </c>
       <c r="N23">
-        <v>2.3170809090563424e-06</v>
+        <v>-6.7703289971330556e-06</v>
       </c>
       <c r="O23">
-        <v>4.964210520537333e-06</v>
+        <v>-7.2770893064439471e-06</v>
       </c>
       <c r="P23">
-        <v>4.6301228970105289e-06</v>
+        <v>-1.2303093981586267e-05</v>
       </c>
       <c r="Q23">
-        <v>1.6156980382192108e-07</v>
+        <v>-7.6770653114677691e-08</v>
       </c>
       <c r="R23">
-        <v>-4.8549173605707801e-06</v>
+        <v>1.3618483020789565e-06</v>
       </c>
       <c r="S23">
-        <v>-5.7235287156870373e-06</v>
+        <v>-6.0353545484223735e-07</v>
       </c>
       <c r="T23">
-        <v>6.0630947576270373e-06</v>
+        <v>-4.7776348466195438e-06</v>
       </c>
       <c r="U23">
-        <v>-1.8346114928346179e-06</v>
+        <v>7.1166812937265415e-06</v>
       </c>
       <c r="V23">
-        <v>5.7695025754377264e-06</v>
+        <v>-1.1331936893811937e-07</v>
       </c>
       <c r="W23">
-        <v>3.2441371723777231e-05</v>
+        <v>5.4545248457518216e-06</v>
       </c>
       <c r="X23">
-        <v>0.00061898709946216321</v>
+        <v>0.00053172249765430599</v>
       </c>
       <c r="Y23">
-        <v>-4.5257485045778354e-05</v>
+        <v>3.310606755991974e-05</v>
+      </c>
+      <c r="Z23">
+        <v>-3.981472253050485e-05</v>
       </c>
     </row>
     <row r="24">
@@ -2078,76 +2150,159 @@
         <v>44</v>
       </c>
       <c r="B24">
-        <v>-2.1748096756334805</v>
+        <v>0.060312716857902474</v>
       </c>
       <c r="C24">
-        <v>-0.00099309852096993948</v>
+        <v>5.424408348775077e-06</v>
       </c>
       <c r="D24">
-        <v>-0.00011721838844687722</v>
+        <v>1.0299660153593104e-05</v>
       </c>
       <c r="E24">
-        <v>-0.00025229472413872513</v>
+        <v>3.2671378245053026e-07</v>
       </c>
       <c r="F24">
-        <v>2.4874896908678085e-06</v>
+        <v>-9.14717351804829e-09</v>
       </c>
       <c r="G24">
-        <v>-0.0012507625103392551</v>
+        <v>4.4598003131860345e-06</v>
       </c>
       <c r="H24">
-        <v>-0.0012503041707290195</v>
+        <v>1.4032716409895648e-05</v>
       </c>
       <c r="I24">
-        <v>2.5627798791456673e-05</v>
+        <v>-1.2556037363747723e-08</v>
       </c>
       <c r="J24">
-        <v>2.4462636574844633e-05</v>
+        <v>-8.7702559998273634e-08</v>
       </c>
       <c r="K24">
-        <v>0.00015915900734784594</v>
+        <v>7.5836888662399902e-07</v>
       </c>
       <c r="L24">
-        <v>0.0002324886960668921</v>
+        <v>-5.9022033642328188e-06</v>
       </c>
       <c r="M24">
-        <v>-0.0036334008134786574</v>
+        <v>2.8753334629048894e-06</v>
       </c>
       <c r="N24">
-        <v>-0.0036884452319085187</v>
+        <v>2.5648833465616211e-06</v>
       </c>
       <c r="O24">
-        <v>-0.0037500106803139621</v>
+        <v>5.4268852389868896e-06</v>
       </c>
       <c r="P24">
-        <v>-0.003873809971319319</v>
+        <v>5.0101825393995855e-06</v>
       </c>
       <c r="Q24">
-        <v>-0.00022973963415141353</v>
+        <v>3.5576885479050021e-07</v>
       </c>
       <c r="R24">
-        <v>-0.00023051851957970958</v>
+        <v>-6.5182763612651129e-07</v>
       </c>
       <c r="S24">
-        <v>-0.0002028385161672271</v>
+        <v>-5.2829298166017293e-06</v>
       </c>
       <c r="T24">
-        <v>-0.00023801216049149871</v>
+        <v>-6.297724614630115e-06</v>
       </c>
       <c r="U24">
-        <v>-0.00020113984537291935</v>
+        <v>5.4928055442230703e-06</v>
       </c>
       <c r="V24">
-        <v>-0.00018320331100858756</v>
+        <v>-1.899680438628804e-06</v>
       </c>
       <c r="W24">
-        <v>-3.6789810356556627e-05</v>
+        <v>5.6054379645182468e-06</v>
       </c>
       <c r="X24">
-        <v>-4.5257485045778354e-05</v>
+        <v>3.310606755991974e-05</v>
       </c>
       <c r="Y24">
-        <v>0.0098305369894430283</v>
+        <v>0.00063249979262917954</v>
+      </c>
+      <c r="Z24">
+        <v>-4.3951727024398901e-05</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25">
+        <v>-1.880252291617593</v>
+      </c>
+      <c r="C25">
+        <v>-0.00098527207952442343</v>
+      </c>
+      <c r="D25">
+        <v>-0.00010781260712777248</v>
+      </c>
+      <c r="E25">
+        <v>-0.00025861855805884329</v>
+      </c>
+      <c r="F25">
+        <v>2.5266307796792345e-06</v>
+      </c>
+      <c r="G25">
+        <v>-0.001284645131895</v>
+      </c>
+      <c r="H25">
+        <v>-0.0012961991244789463</v>
+      </c>
+      <c r="I25">
+        <v>2.6390967054190713e-05</v>
+      </c>
+      <c r="J25">
+        <v>2.546464679012746e-05</v>
+      </c>
+      <c r="K25">
+        <v>0.0001690577638129316</v>
+      </c>
+      <c r="L25">
+        <v>0.00023855756671546091</v>
+      </c>
+      <c r="M25">
+        <v>-0.0037015595912392048</v>
+      </c>
+      <c r="N25">
+        <v>-0.0037560916943745601</v>
+      </c>
+      <c r="O25">
+        <v>-0.0038203584030275968</v>
+      </c>
+      <c r="P25">
+        <v>-0.0039465038669718386</v>
+      </c>
+      <c r="Q25">
+        <v>3.4721954951140651e-06</v>
+      </c>
+      <c r="R25">
+        <v>-0.00023777596873273695</v>
+      </c>
+      <c r="S25">
+        <v>-0.00023830141024242332</v>
+      </c>
+      <c r="T25">
+        <v>-0.00020419301444688011</v>
+      </c>
+      <c r="U25">
+        <v>-0.00025058086239383931</v>
+      </c>
+      <c r="V25">
+        <v>-0.00020426448680112408</v>
+      </c>
+      <c r="W25">
+        <v>-0.00018417179648963505</v>
+      </c>
+      <c r="X25">
+        <v>-3.981472253050485e-05</v>
+      </c>
+      <c r="Y25">
+        <v>-4.3951727024398901e-05</v>
+      </c>
+      <c r="Z25">
+        <v>0.010027638094606611</v>
       </c>
     </row>
   </sheetData>
@@ -2156,7 +2311,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2164,7 +2319,7 @@
         <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
         <v>22</v>
@@ -2234,6 +2389,9 @@
       </c>
       <c r="Y1" t="s">
         <v>44</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="2">
@@ -2241,76 +2399,79 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>-1.5534078702640852</v>
+        <v>-1.5119046433058672</v>
       </c>
       <c r="C2">
-        <v>0.00074299281200900804</v>
+        <v>0.00074480432306117716</v>
       </c>
       <c r="D2">
-        <v>7.1509299021764512e-05</v>
+        <v>7.4644608296686946e-05</v>
       </c>
       <c r="E2">
-        <v>3.829410605252206e-05</v>
+        <v>3.8184542742572916e-05</v>
       </c>
       <c r="F2">
-        <v>-3.6729315963095582e-07</v>
+        <v>-3.7867807665385084e-07</v>
       </c>
       <c r="G2">
-        <v>1.2418137528721418e-05</v>
+        <v>1.0783963824768933e-05</v>
       </c>
       <c r="H2">
-        <v>0.00014380774018393099</v>
+        <v>0.00014261311400211351</v>
       </c>
       <c r="I2">
-        <v>-3.4090383550529796e-07</v>
+        <v>-3.5399938377595492e-07</v>
       </c>
       <c r="J2">
-        <v>-2.7854505337700108e-06</v>
+        <v>-2.8491774217188196e-06</v>
       </c>
       <c r="K2">
-        <v>3.0073559366418488e-05</v>
+        <v>2.7724124918554051e-05</v>
       </c>
       <c r="L2">
-        <v>-3.1425980612539153e-05</v>
+        <v>-3.2654401785258909e-05</v>
       </c>
       <c r="M2">
-        <v>9.0358333396242056e-07</v>
+        <v>1.2385726934758439e-06</v>
       </c>
       <c r="N2">
-        <v>5.304675852491514e-06</v>
+        <v>5.3413786208552239e-06</v>
       </c>
       <c r="O2">
-        <v>1.3609147092019972e-05</v>
+        <v>1.3151906849918221e-05</v>
       </c>
       <c r="P2">
-        <v>1.0501868568789808e-05</v>
+        <v>9.9488445790209983e-06</v>
       </c>
       <c r="Q2">
-        <v>4.8596498173291322e-06</v>
+        <v>1.2393325404755773e-06</v>
       </c>
       <c r="R2">
-        <v>1.5557591121329328e-06</v>
+        <v>3.9632794342010818e-06</v>
       </c>
       <c r="S2">
-        <v>5.173650996695142e-06</v>
+        <v>8.4298213658371647e-07</v>
       </c>
       <c r="T2">
-        <v>5.0338164339660409e-06</v>
+        <v>4.5460383531528139e-06</v>
       </c>
       <c r="U2">
-        <v>-5.0655196481250468e-07</v>
+        <v>4.0744330786291569e-06</v>
       </c>
       <c r="V2">
-        <v>4.8471676014940943e-07</v>
+        <v>-3.1490801063459474e-07</v>
       </c>
       <c r="W2">
-        <v>9.9270873030602194e-06</v>
+        <v>9.3964422099393236e-07</v>
       </c>
       <c r="X2">
-        <v>4.4099699277390498e-07</v>
+        <v>1.0762653435339464e-05</v>
       </c>
       <c r="Y2">
-        <v>-0.0010096918967565623</v>
+        <v>1.9117010318668043e-06</v>
+      </c>
+      <c r="Z2">
+        <v>-0.0010029561851752527</v>
       </c>
     </row>
     <row r="3">
@@ -2318,76 +2479,79 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>-2.0623003957644182</v>
+        <v>-1.9979409540638908</v>
       </c>
       <c r="C3">
-        <v>7.1509299021764512e-05</v>
+        <v>7.4644608296686946e-05</v>
       </c>
       <c r="D3">
-        <v>0.00014717730269502973</v>
+        <v>0.00015215137772514899</v>
       </c>
       <c r="E3">
-        <v>5.2713806292258596e-06</v>
+        <v>4.5343364252946508e-06</v>
       </c>
       <c r="F3">
-        <v>-5.5540594453561954e-08</v>
+        <v>-6.4140094919061599e-08</v>
       </c>
       <c r="G3">
-        <v>1.2541861679921589e-05</v>
+        <v>8.5009531722933288e-06</v>
       </c>
       <c r="H3">
-        <v>-4.5039046464542548e-06</v>
+        <v>-9.8179373253631775e-06</v>
       </c>
       <c r="I3">
-        <v>-4.9120740538597431e-07</v>
+        <v>-4.7454813363573028e-07</v>
       </c>
       <c r="J3">
-        <v>-3.6783598553024198e-07</v>
+        <v>-3.8473692638846086e-07</v>
       </c>
       <c r="K3">
-        <v>1.3680431048328541e-05</v>
+        <v>1.0002824042872186e-05</v>
       </c>
       <c r="L3">
-        <v>2.915837037720206e-06</v>
+        <v>2.9717360553289379e-06</v>
       </c>
       <c r="M3">
-        <v>5.8506298839506958e-06</v>
+        <v>6.099275628632999e-06</v>
       </c>
       <c r="N3">
-        <v>8.6358777854924327e-06</v>
+        <v>8.353865319956605e-06</v>
       </c>
       <c r="O3">
-        <v>1.6291491836058057e-05</v>
+        <v>1.5227159847267708e-05</v>
       </c>
       <c r="P3">
-        <v>2.0701605388371849e-05</v>
+        <v>1.9552485746670844e-05</v>
       </c>
       <c r="Q3">
-        <v>5.6244933470996151e-06</v>
+        <v>1.6866508726446092e-06</v>
       </c>
       <c r="R3">
-        <v>4.9341332014652764e-06</v>
+        <v>3.9086068283105493e-06</v>
       </c>
       <c r="S3">
-        <v>3.9216878895765623e-06</v>
+        <v>3.5976856876239776e-06</v>
       </c>
       <c r="T3">
-        <v>2.8421775099493309e-06</v>
+        <v>2.8439660661865338e-06</v>
       </c>
       <c r="U3">
-        <v>-3.5491157806904594e-06</v>
+        <v>1.199413865635238e-06</v>
       </c>
       <c r="V3">
-        <v>-7.4325632025394498e-06</v>
+        <v>-3.547830013831227e-06</v>
       </c>
       <c r="W3">
-        <v>6.646686904458306e-06</v>
+        <v>-7.1038295865027607e-06</v>
       </c>
       <c r="X3">
-        <v>6.5175322309821035e-06</v>
+        <v>7.4954840592643433e-06</v>
       </c>
       <c r="Y3">
-        <v>-0.00017929425668358154</v>
+        <v>8.5817809702140198e-06</v>
+      </c>
+      <c r="Z3">
+        <v>-0.00015871617962612343</v>
       </c>
     </row>
     <row r="4">
@@ -2395,76 +2559,79 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>0.16221023744435242</v>
+        <v>0.14978653660817604</v>
       </c>
       <c r="C4">
-        <v>3.829410605252206e-05</v>
+        <v>3.8184542742572916e-05</v>
       </c>
       <c r="D4">
-        <v>5.2713806292258596e-06</v>
+        <v>4.5343364252946508e-06</v>
       </c>
       <c r="E4">
-        <v>1.0205024929216828e-05</v>
+        <v>1.0575725508447904e-05</v>
       </c>
       <c r="F4">
-        <v>-1.0296419129764437e-07</v>
+        <v>-1.031246668309417e-07</v>
       </c>
       <c r="G4">
-        <v>4.2880716078150277e-05</v>
+        <v>4.4466049982890539e-05</v>
       </c>
       <c r="H4">
-        <v>4.7453876322145411e-05</v>
+        <v>4.9851366062722257e-05</v>
       </c>
       <c r="I4">
-        <v>-8.9265369237292435e-07</v>
+        <v>-9.099235593930563e-07</v>
       </c>
       <c r="J4">
-        <v>-9.527002654562902e-07</v>
+        <v>-9.7241696047701264e-07</v>
       </c>
       <c r="K4">
-        <v>-4.5463633883475079e-06</v>
+        <v>-3.9813118300248785e-06</v>
       </c>
       <c r="L4">
-        <v>-1.1422854171567873e-05</v>
+        <v>-1.1527986227504631e-05</v>
       </c>
       <c r="M4">
-        <v>1.8347123579713675e-06</v>
+        <v>1.6259765070946532e-06</v>
       </c>
       <c r="N4">
-        <v>3.9853470569118922e-06</v>
+        <v>3.7442414272217576e-06</v>
       </c>
       <c r="O4">
-        <v>5.982381435820698e-06</v>
+        <v>5.8899140055001755e-06</v>
       </c>
       <c r="P4">
-        <v>1.1378697897718211e-05</v>
+        <v>1.1357698525163242e-05</v>
       </c>
       <c r="Q4">
-        <v>1.145925561760928e-06</v>
+        <v>-3.9450239456118955e-07</v>
       </c>
       <c r="R4">
-        <v>1.2727996522658692e-07</v>
+        <v>1.5462111143178356e-06</v>
       </c>
       <c r="S4">
-        <v>3.6958613459211639e-07</v>
+        <v>4.8856976430231101e-07</v>
       </c>
       <c r="T4">
-        <v>1.0558088071830358e-06</v>
+        <v>6.436485590325927e-07</v>
       </c>
       <c r="U4">
-        <v>-4.0571523860573422e-07</v>
+        <v>1.4496419870999995e-06</v>
       </c>
       <c r="V4">
-        <v>-1.6900262467597306e-06</v>
+        <v>-3.9260086888248597e-07</v>
       </c>
       <c r="W4">
-        <v>5.5575161389209792e-07</v>
+        <v>-1.7611908335470048e-06</v>
       </c>
       <c r="X4">
-        <v>2.6983948173981394e-07</v>
+        <v>5.4492633783507718e-07</v>
       </c>
       <c r="Y4">
-        <v>-0.0002381866332478734</v>
+        <v>-1.1056520360351545e-07</v>
+      </c>
+      <c r="Z4">
+        <v>-0.00024671039711147752</v>
       </c>
     </row>
     <row r="5">
@@ -2472,76 +2639,79 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>-0.0020741615408410366</v>
+        <v>-0.0022093145452353018</v>
       </c>
       <c r="C5">
-        <v>-3.6729315963095582e-07</v>
+        <v>-3.7867807665385084e-07</v>
       </c>
       <c r="D5">
-        <v>-5.5540594453561954e-08</v>
+        <v>-6.4140094919061599e-08</v>
       </c>
       <c r="E5">
-        <v>-1.0296419129764437e-07</v>
+        <v>-1.031246668309417e-07</v>
       </c>
       <c r="F5">
-        <v>1.1091009265611972e-09</v>
+        <v>1.1619345252304783e-09</v>
       </c>
       <c r="G5">
-        <v>-2.082665443778523e-07</v>
+        <v>-2.067917610554734e-07</v>
       </c>
       <c r="H5">
-        <v>-2.492734603316852e-07</v>
+        <v>-2.5027556177629451e-07</v>
       </c>
       <c r="I5">
-        <v>4.109595654756675e-09</v>
+        <v>4.2718125138988097e-09</v>
       </c>
       <c r="J5">
-        <v>4.6183132419541624e-09</v>
+        <v>4.9814071880827221e-09</v>
       </c>
       <c r="K5">
-        <v>6.4050313227444246e-09</v>
+        <v>2.0761275983965132e-08</v>
       </c>
       <c r="L5">
-        <v>1.4393957014288687e-07</v>
+        <v>1.4689326219744967e-07</v>
       </c>
       <c r="M5">
-        <v>-2.114363120143479e-08</v>
+        <v>-2.5181437905048764e-08</v>
       </c>
       <c r="N5">
-        <v>-4.46075467954602e-08</v>
+        <v>-4.8478879008098037e-08</v>
       </c>
       <c r="O5">
-        <v>-5.7405270481852933e-08</v>
+        <v>-5.9505372947161693e-08</v>
       </c>
       <c r="P5">
-        <v>-9.930328057319226e-08</v>
+        <v>-1.0183354696659351e-07</v>
       </c>
       <c r="Q5">
-        <v>-1.3067820517723416e-08</v>
+        <v>-5.1428931448976588e-09</v>
       </c>
       <c r="R5">
-        <v>-2.0422671921531978e-09</v>
+        <v>-8.5661675028303912e-09</v>
       </c>
       <c r="S5">
-        <v>-2.1232571263531069e-09</v>
+        <v>1.5928041619644622e-09</v>
       </c>
       <c r="T5">
-        <v>-1.135151967988023e-08</v>
+        <v>1.085906362031441e-09</v>
       </c>
       <c r="U5">
-        <v>6.8156652398992608e-09</v>
+        <v>-6.8228523243410321e-09</v>
       </c>
       <c r="V5">
-        <v>2.0034526493199685e-08</v>
+        <v>6.2112822855097321e-09</v>
       </c>
       <c r="W5">
-        <v>-7.1273582057857486e-09</v>
+        <v>1.892532694301619e-08</v>
       </c>
       <c r="X5">
-        <v>-7.2580327824294464e-09</v>
+        <v>-9.4961746388675996e-09</v>
       </c>
       <c r="Y5">
-        <v>2.251931959082401e-06</v>
+        <v>-1.4353501110381609e-08</v>
+      </c>
+      <c r="Z5">
+        <v>2.2400436684662503e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2549,76 +2719,79 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>-0.40220489251481556</v>
+        <v>-0.45894888764520736</v>
       </c>
       <c r="C6">
-        <v>1.2418137528721418e-05</v>
+        <v>1.0783963824768933e-05</v>
       </c>
       <c r="D6">
-        <v>1.2541861679921589e-05</v>
+        <v>8.5009531722933288e-06</v>
       </c>
       <c r="E6">
-        <v>4.2880716078150277e-05</v>
+        <v>4.4466049982890539e-05</v>
       </c>
       <c r="F6">
-        <v>-2.082665443778523e-07</v>
+        <v>-2.067917610554734e-07</v>
       </c>
       <c r="G6">
-        <v>0.0024671765144578897</v>
+        <v>0.0024779438053995494</v>
       </c>
       <c r="H6">
-        <v>0.0012403416897076947</v>
+        <v>0.0012509480917148755</v>
       </c>
       <c r="I6">
-        <v>-5.0040523911062593e-05</v>
+        <v>-5.0252623346016066e-05</v>
       </c>
       <c r="J6">
-        <v>-2.4882351054204576e-05</v>
+        <v>-2.4970447004528078e-05</v>
       </c>
       <c r="K6">
-        <v>3.7111647851789431e-06</v>
+        <v>8.4766903949988977e-06</v>
       </c>
       <c r="L6">
-        <v>-3.3132854098288399e-05</v>
+        <v>-3.4436549217286674e-05</v>
       </c>
       <c r="M6">
-        <v>6.4503114908645359e-06</v>
+        <v>6.3892461252516722e-06</v>
       </c>
       <c r="N6">
-        <v>1.1738380092110525e-05</v>
+        <v>1.1589576818660003e-05</v>
       </c>
       <c r="O6">
-        <v>1.0626025525528105e-05</v>
+        <v>1.1342580840969737e-05</v>
       </c>
       <c r="P6">
-        <v>2.3416132947670187e-05</v>
+        <v>2.4506489279030254e-05</v>
       </c>
       <c r="Q6">
-        <v>1.0472263580282824e-05</v>
+        <v>-1.8846047714032213e-06</v>
       </c>
       <c r="R6">
-        <v>-1.2839996300519261e-06</v>
+        <v>1.3231368883243209e-05</v>
       </c>
       <c r="S6">
-        <v>3.1537870993364678e-06</v>
+        <v>1.085894875605428e-06</v>
       </c>
       <c r="T6">
-        <v>1.0070443971852951e-06</v>
+        <v>5.0540282429910243e-06</v>
       </c>
       <c r="U6">
-        <v>-7.3984096013794654e-06</v>
+        <v>3.3701263996210521e-06</v>
       </c>
       <c r="V6">
-        <v>-1.6598194895405799e-05</v>
+        <v>-6.7526105690024268e-06</v>
       </c>
       <c r="W6">
-        <v>3.385973094613812e-06</v>
+        <v>-1.7205640467171731e-05</v>
       </c>
       <c r="X6">
-        <v>6.1850035599557911e-06</v>
+        <v>2.4054865098395072e-06</v>
       </c>
       <c r="Y6">
-        <v>-0.0015950522206416482</v>
+        <v>3.5554818089718553e-06</v>
+      </c>
+      <c r="Z6">
+        <v>-0.0016344679025398991</v>
       </c>
     </row>
     <row r="7">
@@ -2626,76 +2799,79 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-0.55276296341428344</v>
+        <v>-0.63288960026779828</v>
       </c>
       <c r="C7">
-        <v>0.00014380774018393099</v>
+        <v>0.00014261311400211351</v>
       </c>
       <c r="D7">
-        <v>-4.5039046464542548e-06</v>
+        <v>-9.8179373253631775e-06</v>
       </c>
       <c r="E7">
-        <v>4.7453876322145411e-05</v>
+        <v>4.9851366062722257e-05</v>
       </c>
       <c r="F7">
-        <v>-2.492734603316852e-07</v>
+        <v>-2.5027556177629451e-07</v>
       </c>
       <c r="G7">
-        <v>0.0012403416897076947</v>
+        <v>0.0012509480917148755</v>
       </c>
       <c r="H7">
-        <v>0.0020366372077641063</v>
+        <v>0.0020530522031853597</v>
       </c>
       <c r="I7">
-        <v>-2.4913028405153921e-05</v>
+        <v>-2.5043251088363348e-05</v>
       </c>
       <c r="J7">
-        <v>-4.0410551376822449e-05</v>
+        <v>-4.0592279432582176e-05</v>
       </c>
       <c r="K7">
-        <v>2.3559610593069953e-05</v>
+        <v>2.9958736779338945e-05</v>
       </c>
       <c r="L7">
-        <v>-9.507586028544105e-05</v>
+        <v>-9.8366074254701116e-05</v>
       </c>
       <c r="M7">
-        <v>7.104964804731731e-06</v>
+        <v>6.5217940507529939e-06</v>
       </c>
       <c r="N7">
-        <v>1.0081337915602618e-05</v>
+        <v>9.5041217299401699e-06</v>
       </c>
       <c r="O7">
-        <v>9.0576149775718285e-06</v>
+        <v>9.6261610564730548e-06</v>
       </c>
       <c r="P7">
-        <v>3.8184168885640958e-05</v>
+        <v>3.8976246672223474e-05</v>
       </c>
       <c r="Q7">
-        <v>1.4144223330877058e-05</v>
+        <v>-2.5310783454745721e-06</v>
       </c>
       <c r="R7">
-        <v>6.4050279178905578e-06</v>
+        <v>1.7554673480068753e-05</v>
       </c>
       <c r="S7">
-        <v>-9.8226709645208974e-06</v>
+        <v>9.4115451096629495e-06</v>
       </c>
       <c r="T7">
-        <v>-6.5677653578270621e-06</v>
+        <v>-7.3693943925352351e-06</v>
       </c>
       <c r="U7">
-        <v>-2.7071114036435235e-05</v>
+        <v>-4.0671306048767876e-06</v>
       </c>
       <c r="V7">
-        <v>-1.6717414056993305e-05</v>
+        <v>-2.7078231002793961e-05</v>
       </c>
       <c r="W7">
-        <v>1.3414268690361624e-05</v>
+        <v>-1.7444592044385005e-05</v>
       </c>
       <c r="X7">
-        <v>7.7783317021278509e-06</v>
+        <v>1.225145714772948e-05</v>
       </c>
       <c r="Y7">
-        <v>-0.0017069303726679895</v>
+        <v>3.8106426221348864e-06</v>
+      </c>
+      <c r="Z7">
+        <v>-0.0017643339865585791</v>
       </c>
     </row>
     <row r="8">
@@ -2703,76 +2879,79 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.0078688102801000703</v>
+        <v>0.0079702532006677741</v>
       </c>
       <c r="C8">
-        <v>-3.4090383550529796e-07</v>
+        <v>-3.5399938377595492e-07</v>
       </c>
       <c r="D8">
-        <v>-4.9120740538597431e-07</v>
+        <v>-4.7454813363573028e-07</v>
       </c>
       <c r="E8">
-        <v>-8.9265369237292435e-07</v>
+        <v>-9.099235593930563e-07</v>
       </c>
       <c r="F8">
-        <v>4.109595654756675e-09</v>
+        <v>4.2718125138988097e-09</v>
       </c>
       <c r="G8">
-        <v>-5.0040523911062593e-05</v>
+        <v>-5.0252623346016066e-05</v>
       </c>
       <c r="H8">
-        <v>-2.4913028405153921e-05</v>
+        <v>-2.5043251088363348e-05</v>
       </c>
       <c r="I8">
-        <v>1.1116271889412432e-06</v>
+        <v>1.118581319066911e-06</v>
       </c>
       <c r="J8">
-        <v>5.4179375918135935e-07</v>
+        <v>5.4473819677106406e-07</v>
       </c>
       <c r="K8">
-        <v>-1.6434594043021074e-07</v>
+        <v>-1.8565198786125387e-07</v>
       </c>
       <c r="L8">
-        <v>7.8573586604683354e-07</v>
+        <v>8.2346034610022261e-07</v>
       </c>
       <c r="M8">
-        <v>-2.1393062230282454e-07</v>
+        <v>-2.3666991894242001e-07</v>
       </c>
       <c r="N8">
-        <v>-2.9420249312123849e-07</v>
+        <v>-3.1237369592601003e-07</v>
       </c>
       <c r="O8">
-        <v>-7.6760336787353502e-08</v>
+        <v>-9.4371243174124007e-08</v>
       </c>
       <c r="P8">
-        <v>-2.4509288200584686e-07</v>
+        <v>-2.6436306428626772e-07</v>
       </c>
       <c r="Q8">
-        <v>-1.7956939589844593e-07</v>
+        <v>1.8164198694055217e-09</v>
       </c>
       <c r="R8">
-        <v>1.9422425840396567e-07</v>
+        <v>-2.0318789540486316e-07</v>
       </c>
       <c r="S8">
-        <v>-1.4032025952341667e-07</v>
+        <v>1.7049486516304781e-07</v>
       </c>
       <c r="T8">
-        <v>-7.4107303190926498e-08</v>
+        <v>-1.5780939055829622e-07</v>
       </c>
       <c r="U8">
-        <v>7.2659859772372322e-08</v>
+        <v>-9.6368299099360385e-08</v>
       </c>
       <c r="V8">
-        <v>2.5646588833028497e-07</v>
+        <v>5.2358429818358016e-08</v>
       </c>
       <c r="W8">
-        <v>-8.6640295740320201e-08</v>
+        <v>2.5664808279232504e-07</v>
       </c>
       <c r="X8">
-        <v>-9.1018842172097784e-08</v>
+        <v>-7.8026640033679147e-08</v>
       </c>
       <c r="Y8">
-        <v>3.1768759411703956e-05</v>
+        <v>-8.3993790234535201e-08</v>
+      </c>
+      <c r="Z8">
+        <v>3.2161338848841617e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2780,76 +2959,79 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>0.0079623083111143335</v>
+        <v>0.007680186988444148</v>
       </c>
       <c r="C9">
-        <v>-2.7854505337700108e-06</v>
+        <v>-2.8491774217188196e-06</v>
       </c>
       <c r="D9">
-        <v>-3.6783598553024198e-07</v>
+        <v>-3.8473692638846086e-07</v>
       </c>
       <c r="E9">
-        <v>-9.527002654562902e-07</v>
+        <v>-9.7241696047701264e-07</v>
       </c>
       <c r="F9">
-        <v>4.6183132419541624e-09</v>
+        <v>4.9814071880827221e-09</v>
       </c>
       <c r="G9">
-        <v>-2.4882351054204576e-05</v>
+        <v>-2.4970447004528078e-05</v>
       </c>
       <c r="H9">
-        <v>-4.0410551376822449e-05</v>
+        <v>-4.0592279432582176e-05</v>
       </c>
       <c r="I9">
-        <v>5.4179375918135935e-07</v>
+        <v>5.4473819677106406e-07</v>
       </c>
       <c r="J9">
-        <v>8.7318763936535476e-07</v>
+        <v>8.7945531291906463e-07</v>
       </c>
       <c r="K9">
-        <v>-5.8638107983484074e-07</v>
+        <v>-5.6687720849000214e-07</v>
       </c>
       <c r="L9">
-        <v>1.9514786861180271e-06</v>
+        <v>2.0301513354837717e-06</v>
       </c>
       <c r="M9">
-        <v>-1.9154714388804311e-07</v>
+        <v>-2.3021650144167556e-07</v>
       </c>
       <c r="N9">
-        <v>-1.4048204897765968e-07</v>
+        <v>-1.7642771791145761e-07</v>
       </c>
       <c r="O9">
-        <v>2.360727800060098e-07</v>
+        <v>2.0845690950579224e-07</v>
       </c>
       <c r="P9">
-        <v>-1.5377998466341689e-07</v>
+        <v>-1.8086437911347351e-07</v>
       </c>
       <c r="Q9">
-        <v>-1.119981419246582e-07</v>
+        <v>-1.6032495462126945e-08</v>
       </c>
       <c r="R9">
-        <v>2.773163004222667e-07</v>
+        <v>-1.2090801269148628e-07</v>
       </c>
       <c r="S9">
-        <v>-1.0255076431256754e-07</v>
+        <v>2.6595986308377279e-07</v>
       </c>
       <c r="T9">
-        <v>1.7210339360454175e-07</v>
+        <v>-1.1738406825515454e-07</v>
       </c>
       <c r="U9">
-        <v>3.0079454138238682e-07</v>
+        <v>1.7659140015421925e-07</v>
       </c>
       <c r="V9">
-        <v>2.8320493425306157e-07</v>
+        <v>2.8754249963561004e-07</v>
       </c>
       <c r="W9">
-        <v>-2.3479635954616842e-07</v>
+        <v>2.7964978771509953e-07</v>
       </c>
       <c r="X9">
-        <v>-4.7106878851704288e-08</v>
+        <v>-2.2683095591702518e-07</v>
       </c>
       <c r="Y9">
-        <v>3.303608122063139e-05</v>
+        <v>-4.7772217982981966e-08</v>
+      </c>
+      <c r="Z9">
+        <v>3.3431135112370259e-05</v>
       </c>
     </row>
     <row r="10">
@@ -2857,76 +3039,79 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>0.20400872860889585</v>
+        <v>0.13945872870269871</v>
       </c>
       <c r="C10">
-        <v>3.0073559366418488e-05</v>
+        <v>2.7724124918554051e-05</v>
       </c>
       <c r="D10">
-        <v>1.3680431048328541e-05</v>
+        <v>1.0002824042872186e-05</v>
       </c>
       <c r="E10">
-        <v>-4.5463633883475079e-06</v>
+        <v>-3.9813118300248785e-06</v>
       </c>
       <c r="F10">
-        <v>6.4050313227444246e-09</v>
+        <v>2.0761275983965132e-08</v>
       </c>
       <c r="G10">
-        <v>3.7111647851789431e-06</v>
+        <v>8.4766903949988977e-06</v>
       </c>
       <c r="H10">
-        <v>2.3559610593069953e-05</v>
+        <v>2.9958736779338945e-05</v>
       </c>
       <c r="I10">
-        <v>-1.6434594043021074e-07</v>
+        <v>-1.8565198786125387e-07</v>
       </c>
       <c r="J10">
-        <v>-5.8638107983484074e-07</v>
+        <v>-5.6687720849000214e-07</v>
       </c>
       <c r="K10">
-        <v>0.00023183106230684596</v>
+        <v>0.0002409129079672664</v>
       </c>
       <c r="L10">
-        <v>-0.00011236933857346887</v>
+        <v>-0.00011314016279499965</v>
       </c>
       <c r="M10">
-        <v>-6.7687320124569774e-06</v>
+        <v>-9.0424144923953108e-06</v>
       </c>
       <c r="N10">
-        <v>-7.9793450399339677e-06</v>
+        <v>-1.0309581816041945e-05</v>
       </c>
       <c r="O10">
-        <v>-1.1394022399580312e-05</v>
+        <v>-1.2976239359061047e-05</v>
       </c>
       <c r="P10">
-        <v>-1.2249450085433839e-05</v>
+        <v>-1.3838514884894678e-05</v>
       </c>
       <c r="Q10">
-        <v>1.7135900488611677e-06</v>
+        <v>-2.1484919776733364e-06</v>
       </c>
       <c r="R10">
-        <v>-3.9160593753671144e-06</v>
+        <v>3.6991841186999155e-06</v>
       </c>
       <c r="S10">
-        <v>5.0390345740298027e-07</v>
+        <v>-2.5691726994650038e-06</v>
       </c>
       <c r="T10">
-        <v>-2.2390089323472749e-06</v>
+        <v>1.7016441522360874e-06</v>
       </c>
       <c r="U10">
-        <v>-3.9378479098398279e-06</v>
+        <v>-4.6965833906039355e-07</v>
       </c>
       <c r="V10">
-        <v>3.2703868080553761e-06</v>
+        <v>-4.0712087287902474e-06</v>
       </c>
       <c r="W10">
-        <v>2.7999535241356691e-06</v>
+        <v>2.8477634177974831e-06</v>
       </c>
       <c r="X10">
-        <v>8.2945220073543603e-06</v>
+        <v>2.0740955678939318e-06</v>
       </c>
       <c r="Y10">
-        <v>9.7567365737442701e-05</v>
+        <v>6.0985516529011777e-06</v>
+      </c>
+      <c r="Z10">
+        <v>8.0285793007983425e-05</v>
       </c>
     </row>
     <row r="11">
@@ -2934,76 +3119,79 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>-0.069441015036014062</v>
+        <v>-0.073301421416028731</v>
       </c>
       <c r="C11">
-        <v>-3.1425980612539153e-05</v>
+        <v>-3.2654401785258909e-05</v>
       </c>
       <c r="D11">
-        <v>2.915837037720206e-06</v>
+        <v>2.9717360553289379e-06</v>
       </c>
       <c r="E11">
-        <v>-1.1422854171567873e-05</v>
+        <v>-1.1527986227504631e-05</v>
       </c>
       <c r="F11">
-        <v>1.4393957014288687e-07</v>
+        <v>1.4689326219744967e-07</v>
       </c>
       <c r="G11">
-        <v>-3.3132854098288399e-05</v>
+        <v>-3.4436549217286674e-05</v>
       </c>
       <c r="H11">
-        <v>-9.507586028544105e-05</v>
+        <v>-9.8366074254701116e-05</v>
       </c>
       <c r="I11">
-        <v>7.8573586604683354e-07</v>
+        <v>8.2346034610022261e-07</v>
       </c>
       <c r="J11">
-        <v>1.9514786861180271e-06</v>
+        <v>2.0301513354837717e-06</v>
       </c>
       <c r="K11">
-        <v>-0.00011236933857346887</v>
+        <v>-0.00011314016279499965</v>
       </c>
       <c r="L11">
-        <v>0.00021410050938308205</v>
+        <v>0.00021621440361579058</v>
       </c>
       <c r="M11">
-        <v>-9.8233133115692656e-07</v>
+        <v>-2.9059367922951444e-07</v>
       </c>
       <c r="N11">
-        <v>-5.5884174669560793e-06</v>
+        <v>-5.1884499334061844e-06</v>
       </c>
       <c r="O11">
-        <v>-9.7594706270910626e-06</v>
+        <v>-9.3366555361797484e-06</v>
       </c>
       <c r="P11">
-        <v>-1.1043881660563278e-05</v>
+        <v>-1.0560898623446062e-05</v>
       </c>
       <c r="Q11">
-        <v>-6.5571675115234232e-06</v>
+        <v>-1.7683471038533799e-07</v>
       </c>
       <c r="R11">
-        <v>-3.2537940630825466e-06</v>
+        <v>-6.4706856787242577e-06</v>
       </c>
       <c r="S11">
-        <v>-2.3295278497693406e-06</v>
+        <v>-3.0834348848241215e-06</v>
       </c>
       <c r="T11">
-        <v>-4.8624293556948119e-06</v>
+        <v>-2.1439838532321594e-06</v>
       </c>
       <c r="U11">
-        <v>-5.345183701464613e-06</v>
+        <v>-4.5050495602512912e-06</v>
       </c>
       <c r="V11">
-        <v>3.5300602758547455e-06</v>
+        <v>-5.3135203889994488e-06</v>
       </c>
       <c r="W11">
-        <v>-3.4440484272296107e-06</v>
+        <v>3.4702826084420064e-06</v>
       </c>
       <c r="X11">
-        <v>-7.2830993972605194e-06</v>
+        <v>-3.3648348434563507e-06</v>
       </c>
       <c r="Y11">
-        <v>0.00021011173211139144</v>
+        <v>-7.6796688624362341e-06</v>
+      </c>
+      <c r="Z11">
+        <v>0.00021121672626932243</v>
       </c>
     </row>
     <row r="12">
@@ -3011,76 +3199,79 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>0.16897892093543973</v>
+        <v>0.18475635362875711</v>
       </c>
       <c r="C12">
-        <v>9.0358333396242056e-07</v>
+        <v>1.2385726934758439e-06</v>
       </c>
       <c r="D12">
-        <v>5.8506298839506958e-06</v>
+        <v>6.099275628632999e-06</v>
       </c>
       <c r="E12">
-        <v>1.8347123579713675e-06</v>
+        <v>1.6259765070946532e-06</v>
       </c>
       <c r="F12">
-        <v>-2.114363120143479e-08</v>
+        <v>-2.5181437905048764e-08</v>
       </c>
       <c r="G12">
-        <v>6.4503114908645359e-06</v>
+        <v>6.3892461252516722e-06</v>
       </c>
       <c r="H12">
-        <v>7.104964804731731e-06</v>
+        <v>6.5217940507529939e-06</v>
       </c>
       <c r="I12">
-        <v>-2.1393062230282454e-07</v>
+        <v>-2.3666991894242001e-07</v>
       </c>
       <c r="J12">
-        <v>-1.9154714388804311e-07</v>
+        <v>-2.3021650144167556e-07</v>
       </c>
       <c r="K12">
-        <v>-6.7687320124569774e-06</v>
+        <v>-9.0424144923953108e-06</v>
       </c>
       <c r="L12">
-        <v>-9.8233133115692656e-07</v>
+        <v>-2.9059367922951444e-07</v>
       </c>
       <c r="M12">
-        <v>0.0047363005330738201</v>
+        <v>0.0048829965884322766</v>
       </c>
       <c r="N12">
-        <v>0.0038906649226269009</v>
+        <v>0.0040141369454839062</v>
       </c>
       <c r="O12">
-        <v>0.0038892884571985493</v>
+        <v>0.0040123500538709021</v>
       </c>
       <c r="P12">
-        <v>0.0038875099251143548</v>
+        <v>0.0040104376643684721</v>
       </c>
       <c r="Q12">
-        <v>9.7182225040282137e-06</v>
+        <v>6.5697120248799109e-07</v>
       </c>
       <c r="R12">
-        <v>5.4129285787436505e-06</v>
+        <v>9.0155830145163785e-06</v>
       </c>
       <c r="S12">
-        <v>-1.3142335930263726e-06</v>
+        <v>3.829407246216574e-06</v>
       </c>
       <c r="T12">
-        <v>2.8757250570624602e-06</v>
+        <v>-2.7869714604667948e-06</v>
       </c>
       <c r="U12">
-        <v>7.1397231396171031e-06</v>
+        <v>1.5640492685799255e-06</v>
       </c>
       <c r="V12">
-        <v>2.6040608889536327e-06</v>
+        <v>7.3311935416573251e-06</v>
       </c>
       <c r="W12">
-        <v>-1.535190002280966e-06</v>
+        <v>2.5953865832603693e-06</v>
       </c>
       <c r="X12">
-        <v>-4.94936854496475e-06</v>
+        <v>-1.726445848590218e-06</v>
       </c>
       <c r="Y12">
-        <v>-0.0039243840081503887</v>
+        <v>-3.4817736032051729e-06</v>
+      </c>
+      <c r="Z12">
+        <v>-0.0040406324809560499</v>
       </c>
     </row>
     <row r="13">
@@ -3088,76 +3279,79 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>0.61695585711760448</v>
+        <v>0.62799832698717018</v>
       </c>
       <c r="C13">
-        <v>5.304675852491514e-06</v>
+        <v>5.3413786208552239e-06</v>
       </c>
       <c r="D13">
-        <v>8.6358777854924327e-06</v>
+        <v>8.353865319956605e-06</v>
       </c>
       <c r="E13">
-        <v>3.9853470569118922e-06</v>
+        <v>3.7442414272217576e-06</v>
       </c>
       <c r="F13">
-        <v>-4.46075467954602e-08</v>
+        <v>-4.8478879008098037e-08</v>
       </c>
       <c r="G13">
-        <v>1.1738380092110525e-05</v>
+        <v>1.1589576818660003e-05</v>
       </c>
       <c r="H13">
-        <v>1.0081337915602618e-05</v>
+        <v>9.5041217299401699e-06</v>
       </c>
       <c r="I13">
-        <v>-2.9420249312123849e-07</v>
+        <v>-3.1237369592601003e-07</v>
       </c>
       <c r="J13">
-        <v>-1.4048204897765968e-07</v>
+        <v>-1.7642771791145761e-07</v>
       </c>
       <c r="K13">
-        <v>-7.9793450399339677e-06</v>
+        <v>-1.0309581816041945e-05</v>
       </c>
       <c r="L13">
-        <v>-5.5884174669560793e-06</v>
+        <v>-5.1884499334061844e-06</v>
       </c>
       <c r="M13">
-        <v>0.0038906649226269009</v>
+        <v>0.0040141369454839062</v>
       </c>
       <c r="N13">
-        <v>0.0040506618713113188</v>
+        <v>0.0041775679204924671</v>
       </c>
       <c r="O13">
-        <v>0.0038922661048355202</v>
+        <v>0.0040152448975161945</v>
       </c>
       <c r="P13">
-        <v>0.0038924884649776097</v>
+        <v>0.004015316630445233</v>
       </c>
       <c r="Q13">
-        <v>4.3707923411174409e-06</v>
+        <v>6.7042916062461001e-07</v>
       </c>
       <c r="R13">
-        <v>-3.1155670316236541e-06</v>
+        <v>3.491025074086102e-06</v>
       </c>
       <c r="S13">
-        <v>-1.1011043810274453e-05</v>
+        <v>-4.5279147613843767e-06</v>
       </c>
       <c r="T13">
-        <v>-4.0352095146620328e-06</v>
+        <v>-1.2387949773481286e-05</v>
       </c>
       <c r="U13">
-        <v>-3.1427702880073069e-06</v>
+        <v>-5.3694235400459939e-06</v>
       </c>
       <c r="V13">
-        <v>-8.8084823902473771e-06</v>
+        <v>-3.0192034740033046e-06</v>
       </c>
       <c r="W13">
-        <v>-2.9017279506888178e-06</v>
+        <v>-8.8565235369922937e-06</v>
       </c>
       <c r="X13">
-        <v>-6.5256966257938215e-06</v>
+        <v>-3.0208232874988315e-06</v>
       </c>
       <c r="Y13">
-        <v>-0.0039664828139294077</v>
+        <v>-4.7581654038956133e-06</v>
+      </c>
+      <c r="Z13">
+        <v>-0.0040816017920346694</v>
       </c>
     </row>
     <row r="14">
@@ -3165,76 +3359,79 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0.85082650624819989</v>
+        <v>0.84968567084161783</v>
       </c>
       <c r="C14">
-        <v>1.3609147092019972e-05</v>
+        <v>1.3151906849918221e-05</v>
       </c>
       <c r="D14">
-        <v>1.6291491836058057e-05</v>
+        <v>1.5227159847267708e-05</v>
       </c>
       <c r="E14">
-        <v>5.982381435820698e-06</v>
+        <v>5.8899140055001755e-06</v>
       </c>
       <c r="F14">
-        <v>-5.7405270481852933e-08</v>
+        <v>-5.9505372947161693e-08</v>
       </c>
       <c r="G14">
-        <v>1.0626025525528105e-05</v>
+        <v>1.1342580840969737e-05</v>
       </c>
       <c r="H14">
-        <v>9.0576149775718285e-06</v>
+        <v>9.6261610564730548e-06</v>
       </c>
       <c r="I14">
-        <v>-7.6760336787353502e-08</v>
+        <v>-9.4371243174124007e-08</v>
       </c>
       <c r="J14">
-        <v>2.360727800060098e-07</v>
+        <v>2.0845690950579224e-07</v>
       </c>
       <c r="K14">
-        <v>-1.1394022399580312e-05</v>
+        <v>-1.2976239359061047e-05</v>
       </c>
       <c r="L14">
-        <v>-9.7594706270910626e-06</v>
+        <v>-9.3366555361797484e-06</v>
       </c>
       <c r="M14">
-        <v>0.0038892884571985493</v>
+        <v>0.0040123500538709021</v>
       </c>
       <c r="N14">
-        <v>0.0038922661048355202</v>
+        <v>0.0040152448975161945</v>
       </c>
       <c r="O14">
-        <v>0.0039489938894343348</v>
+        <v>0.004072326179995648</v>
       </c>
       <c r="P14">
-        <v>0.0039118671553177199</v>
+        <v>0.0040346495845549561</v>
       </c>
       <c r="Q14">
-        <v>1.3234422522517207e-06</v>
+        <v>3.3722077948023636e-07</v>
       </c>
       <c r="R14">
-        <v>-6.7820837061591412e-06</v>
+        <v>7.0241917594079191e-07</v>
       </c>
       <c r="S14">
-        <v>-1.4667035369595016e-05</v>
+        <v>-8.0903706099064371e-06</v>
       </c>
       <c r="T14">
-        <v>-4.8850992364449534e-06</v>
+        <v>-1.5837446548368857e-05</v>
       </c>
       <c r="U14">
-        <v>-5.2557936165260552e-06</v>
+        <v>-5.9263315668050691e-06</v>
       </c>
       <c r="V14">
-        <v>-1.7988827677729689e-06</v>
+        <v>-5.1454291506282748e-06</v>
       </c>
       <c r="W14">
-        <v>-4.4117503053185965e-06</v>
+        <v>-2.0082545613976215e-06</v>
       </c>
       <c r="X14">
-        <v>-3.9159099235375396e-06</v>
+        <v>-4.7720822319297898e-06</v>
       </c>
       <c r="Y14">
-        <v>-0.0040448240361537387</v>
+        <v>-2.5253203326530597e-06</v>
+      </c>
+      <c r="Z14">
+        <v>-0.0041640303852207754</v>
       </c>
     </row>
     <row r="15">
@@ -3242,76 +3439,79 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>0.87629923681296884</v>
+        <v>0.87446847977058906</v>
       </c>
       <c r="C15">
-        <v>1.0501868568789808e-05</v>
+        <v>9.9488445790209983e-06</v>
       </c>
       <c r="D15">
-        <v>2.0701605388371849e-05</v>
+        <v>1.9552485746670844e-05</v>
       </c>
       <c r="E15">
-        <v>1.1378697897718211e-05</v>
+        <v>1.1357698525163242e-05</v>
       </c>
       <c r="F15">
-        <v>-9.930328057319226e-08</v>
+        <v>-1.0183354696659351e-07</v>
       </c>
       <c r="G15">
-        <v>2.3416132947670187e-05</v>
+        <v>2.4506489279030254e-05</v>
       </c>
       <c r="H15">
-        <v>3.8184168885640958e-05</v>
+        <v>3.8976246672223474e-05</v>
       </c>
       <c r="I15">
-        <v>-2.4509288200584686e-07</v>
+        <v>-2.6436306428626772e-07</v>
       </c>
       <c r="J15">
-        <v>-1.5377998466341689e-07</v>
+        <v>-1.8086437911347351e-07</v>
       </c>
       <c r="K15">
-        <v>-1.2249450085433839e-05</v>
+        <v>-1.3838514884894678e-05</v>
       </c>
       <c r="L15">
-        <v>-1.1043881660563278e-05</v>
+        <v>-1.0560898623446062e-05</v>
       </c>
       <c r="M15">
-        <v>0.0038875099251143548</v>
+        <v>0.0040104376643684721</v>
       </c>
       <c r="N15">
-        <v>0.0038924884649776097</v>
+        <v>0.004015316630445233</v>
       </c>
       <c r="O15">
-        <v>0.0039118671553177199</v>
+        <v>0.0040346495845549561</v>
       </c>
       <c r="P15">
-        <v>0.0040948800455974828</v>
+        <v>0.0042185304498161477</v>
       </c>
       <c r="Q15">
-        <v>-2.735974630565266e-06</v>
+        <v>3.0792250491707701e-07</v>
       </c>
       <c r="R15">
-        <v>-1.370058119933159e-05</v>
+        <v>-3.5691176855097808e-06</v>
       </c>
       <c r="S15">
-        <v>-1.6940381433147692e-05</v>
+        <v>-1.5091047428085732e-05</v>
       </c>
       <c r="T15">
-        <v>-1.5643830281320719e-05</v>
+        <v>-1.8112197914833833e-05</v>
       </c>
       <c r="U15">
-        <v>-1.4880848994417933e-05</v>
+        <v>-1.6785308262909444e-05</v>
       </c>
       <c r="V15">
-        <v>-1.1235184689076597e-05</v>
+        <v>-1.4848770413268449e-05</v>
       </c>
       <c r="W15">
-        <v>-8.8476166284484315e-06</v>
+        <v>-1.1402762757424832e-05</v>
       </c>
       <c r="X15">
-        <v>-5.8181300615266672e-06</v>
+        <v>-9.3909845320485178e-06</v>
       </c>
       <c r="Y15">
-        <v>-0.0042070436081594054</v>
+        <v>-4.6229873994539743e-06</v>
+      </c>
+      <c r="Z15">
+        <v>-0.0043277562451338293</v>
       </c>
     </row>
     <row r="16">
@@ -3319,76 +3519,79 @@
         <v>36</v>
       </c>
       <c r="B16">
-        <v>0.063566978992011941</v>
+        <v>0.027619728502664625</v>
       </c>
       <c r="C16">
-        <v>4.8596498173291322e-06</v>
+        <v>1.2393325404755773e-06</v>
       </c>
       <c r="D16">
-        <v>5.6244933470996151e-06</v>
+        <v>1.6866508726446092e-06</v>
       </c>
       <c r="E16">
-        <v>1.145925561760928e-06</v>
+        <v>-3.9450239456118955e-07</v>
       </c>
       <c r="F16">
-        <v>-1.3067820517723416e-08</v>
+        <v>-5.1428931448976588e-09</v>
       </c>
       <c r="G16">
-        <v>1.0472263580282824e-05</v>
+        <v>-1.8846047714032213e-06</v>
       </c>
       <c r="H16">
-        <v>1.4144223330877058e-05</v>
+        <v>-2.5310783454745721e-06</v>
       </c>
       <c r="I16">
-        <v>-1.7956939589844593e-07</v>
+        <v>1.8164198694055217e-09</v>
       </c>
       <c r="J16">
-        <v>-1.119981419246582e-07</v>
+        <v>-1.6032495462126945e-08</v>
       </c>
       <c r="K16">
-        <v>1.7135900488611677e-06</v>
+        <v>-2.1484919776733364e-06</v>
       </c>
       <c r="L16">
-        <v>-6.5571675115234232e-06</v>
+        <v>-1.7683471038533799e-07</v>
       </c>
       <c r="M16">
-        <v>9.7182225040282137e-06</v>
+        <v>6.5697120248799109e-07</v>
       </c>
       <c r="N16">
-        <v>4.3707923411174409e-06</v>
+        <v>6.7042916062461001e-07</v>
       </c>
       <c r="O16">
-        <v>1.3234422522517207e-06</v>
+        <v>3.3722077948023636e-07</v>
       </c>
       <c r="P16">
-        <v>-2.735974630565266e-06</v>
+        <v>3.0792250491707701e-07</v>
       </c>
       <c r="Q16">
-        <v>0.00042757130777282065</v>
+        <v>9.5790438001144953e-07</v>
       </c>
       <c r="R16">
-        <v>0.00022682579501686931</v>
+        <v>-8.8818700244393091e-07</v>
       </c>
       <c r="S16">
-        <v>0.00022424653859322294</v>
+        <v>-7.477474940093258e-07</v>
       </c>
       <c r="T16">
-        <v>0.00022578900057727993</v>
+        <v>-6.1038590454142285e-07</v>
       </c>
       <c r="U16">
-        <v>0.00022430238164636624</v>
+        <v>-8.8151226671131569e-07</v>
       </c>
       <c r="V16">
-        <v>0.00022408729929085904</v>
+        <v>6.3929846600101761e-08</v>
       </c>
       <c r="W16">
-        <v>5.4340547670740986e-06</v>
+        <v>1.9497853716723549e-07</v>
       </c>
       <c r="X16">
-        <v>4.4249661319536601e-06</v>
+        <v>2.5390559283501458e-07</v>
       </c>
       <c r="Y16">
-        <v>-0.00025534441360154322</v>
+        <v>1.1222093368602964e-06</v>
+      </c>
+      <c r="Z16">
+        <v>1.0620349589535507e-05</v>
       </c>
     </row>
     <row r="17">
@@ -3396,76 +3599,79 @@
         <v>37</v>
       </c>
       <c r="B17">
-        <v>-0.0076245418788843155</v>
+        <v>0.03674132890109584</v>
       </c>
       <c r="C17">
-        <v>1.5557591121329328e-06</v>
+        <v>3.9632794342010818e-06</v>
       </c>
       <c r="D17">
-        <v>4.9341332014652764e-06</v>
+        <v>3.9086068283105493e-06</v>
       </c>
       <c r="E17">
-        <v>1.2727996522658692e-07</v>
+        <v>1.5462111143178356e-06</v>
       </c>
       <c r="F17">
-        <v>-2.0422671921531978e-09</v>
+        <v>-8.5661675028303912e-09</v>
       </c>
       <c r="G17">
-        <v>-1.2839996300519261e-06</v>
+        <v>1.3231368883243209e-05</v>
       </c>
       <c r="H17">
-        <v>6.4050279178905578e-06</v>
+        <v>1.7554673480068753e-05</v>
       </c>
       <c r="I17">
-        <v>1.9422425840396567e-07</v>
+        <v>-2.0318789540486316e-07</v>
       </c>
       <c r="J17">
-        <v>2.773163004222667e-07</v>
+        <v>-1.2090801269148628e-07</v>
       </c>
       <c r="K17">
-        <v>-3.9160593753671144e-06</v>
+        <v>3.6991841186999155e-06</v>
       </c>
       <c r="L17">
-        <v>-3.2537940630825466e-06</v>
+        <v>-6.4706856787242577e-06</v>
       </c>
       <c r="M17">
-        <v>5.4129285787436505e-06</v>
+        <v>9.0155830145163785e-06</v>
       </c>
       <c r="N17">
-        <v>-3.1155670316236541e-06</v>
+        <v>3.491025074086102e-06</v>
       </c>
       <c r="O17">
-        <v>-6.7820837061591412e-06</v>
+        <v>7.0241917594079191e-07</v>
       </c>
       <c r="P17">
-        <v>-1.370058119933159e-05</v>
+        <v>-3.5691176855097808e-06</v>
       </c>
       <c r="Q17">
-        <v>0.00022682579501686931</v>
+        <v>-8.8818700244393091e-07</v>
       </c>
       <c r="R17">
-        <v>0.00051134433679849648</v>
+        <v>0.00043362429278317685</v>
       </c>
       <c r="S17">
-        <v>0.00022356964854286442</v>
+        <v>0.00023073329044840432</v>
       </c>
       <c r="T17">
-        <v>0.00022627384659600533</v>
+        <v>0.00022805315901684424</v>
       </c>
       <c r="U17">
-        <v>0.00022437139196139854</v>
+        <v>0.00022983126126665878</v>
       </c>
       <c r="V17">
-        <v>0.00022440708522501266</v>
+        <v>0.00022747854856051118</v>
       </c>
       <c r="W17">
-        <v>1.8430072341922298e-06</v>
+        <v>0.00022715728074463665</v>
       </c>
       <c r="X17">
-        <v>-5.0227555449651865e-06</v>
+        <v>5.1921395075385809e-06</v>
       </c>
       <c r="Y17">
-        <v>-0.00022837255817040287</v>
+        <v>3.556630499189163e-06</v>
+      </c>
+      <c r="Z17">
+        <v>-0.00026895958367919643</v>
       </c>
     </row>
     <row r="18">
@@ -3473,76 +3679,79 @@
         <v>38</v>
       </c>
       <c r="B18">
-        <v>-0.016842784124330518</v>
+        <v>-0.029763917896110995</v>
       </c>
       <c r="C18">
-        <v>5.173650996695142e-06</v>
+        <v>8.4298213658371647e-07</v>
       </c>
       <c r="D18">
-        <v>3.9216878895765623e-06</v>
+        <v>3.5976856876239776e-06</v>
       </c>
       <c r="E18">
-        <v>3.6958613459211639e-07</v>
+        <v>4.8856976430231101e-07</v>
       </c>
       <c r="F18">
-        <v>-2.1232571263531069e-09</v>
+        <v>1.5928041619644622e-09</v>
       </c>
       <c r="G18">
-        <v>3.1537870993364678e-06</v>
+        <v>1.085894875605428e-06</v>
       </c>
       <c r="H18">
-        <v>-9.8226709645208974e-06</v>
+        <v>9.4115451096629495e-06</v>
       </c>
       <c r="I18">
-        <v>-1.4032025952341667e-07</v>
+        <v>1.7049486516304781e-07</v>
       </c>
       <c r="J18">
-        <v>-1.0255076431256754e-07</v>
+        <v>2.6595986308377279e-07</v>
       </c>
       <c r="K18">
-        <v>5.0390345740298027e-07</v>
+        <v>-2.5691726994650038e-06</v>
       </c>
       <c r="L18">
-        <v>-2.3295278497693406e-06</v>
+        <v>-3.0834348848241215e-06</v>
       </c>
       <c r="M18">
-        <v>-1.3142335930263726e-06</v>
+        <v>3.829407246216574e-06</v>
       </c>
       <c r="N18">
-        <v>-1.1011043810274453e-05</v>
+        <v>-4.5279147613843767e-06</v>
       </c>
       <c r="O18">
-        <v>-1.4667035369595016e-05</v>
+        <v>-8.0903706099064371e-06</v>
       </c>
       <c r="P18">
-        <v>-1.6940381433147692e-05</v>
+        <v>-1.5091047428085732e-05</v>
       </c>
       <c r="Q18">
-        <v>0.00022424653859322294</v>
+        <v>-7.477474940093258e-07</v>
       </c>
       <c r="R18">
-        <v>0.00022356964854286442</v>
+        <v>0.00023073329044840432</v>
       </c>
       <c r="S18">
-        <v>0.00040173651757020184</v>
+        <v>0.00051789977863087163</v>
       </c>
       <c r="T18">
-        <v>0.00022503118828069428</v>
+        <v>0.00022726462477014412</v>
       </c>
       <c r="U18">
-        <v>0.00022661056225080719</v>
+        <v>0.00023014977408649414</v>
       </c>
       <c r="V18">
-        <v>0.00022505032427709275</v>
+        <v>0.00022751292162971802</v>
       </c>
       <c r="W18">
-        <v>-1.4156551655240957e-06</v>
+        <v>0.00022746099623792559</v>
       </c>
       <c r="X18">
-        <v>-9.7882427825728354e-07</v>
+        <v>1.5744284359086614e-06</v>
       </c>
       <c r="Y18">
-        <v>-0.00021719577000382846</v>
+        <v>-6.0588042249540153e-06</v>
+      </c>
+      <c r="Z18">
+        <v>-0.00024008032364950525</v>
       </c>
     </row>
     <row r="19">
@@ -3550,76 +3759,79 @@
         <v>39</v>
       </c>
       <c r="B19">
-        <v>0.052761079385239558</v>
+        <v>-0.034975473206550908</v>
       </c>
       <c r="C19">
-        <v>5.0338164339660409e-06</v>
+        <v>4.5460383531528139e-06</v>
       </c>
       <c r="D19">
-        <v>2.8421775099493309e-06</v>
+        <v>2.8439660661865338e-06</v>
       </c>
       <c r="E19">
-        <v>1.0558088071830358e-06</v>
+        <v>6.436485590325927e-07</v>
       </c>
       <c r="F19">
-        <v>-1.135151967988023e-08</v>
+        <v>1.085906362031441e-09</v>
       </c>
       <c r="G19">
-        <v>1.0070443971852951e-06</v>
+        <v>5.0540282429910243e-06</v>
       </c>
       <c r="H19">
-        <v>-6.5677653578270621e-06</v>
+        <v>-7.3693943925352351e-06</v>
       </c>
       <c r="I19">
-        <v>-7.4107303190926498e-08</v>
+        <v>-1.5780939055829622e-07</v>
       </c>
       <c r="J19">
-        <v>1.7210339360454175e-07</v>
+        <v>-1.1738406825515454e-07</v>
       </c>
       <c r="K19">
-        <v>-2.2390089323472749e-06</v>
+        <v>1.7016441522360874e-06</v>
       </c>
       <c r="L19">
-        <v>-4.8624293556948119e-06</v>
+        <v>-2.1439838532321594e-06</v>
       </c>
       <c r="M19">
-        <v>2.8757250570624602e-06</v>
+        <v>-2.7869714604667948e-06</v>
       </c>
       <c r="N19">
-        <v>-4.0352095146620328e-06</v>
+        <v>-1.2387949773481286e-05</v>
       </c>
       <c r="O19">
-        <v>-4.8850992364449534e-06</v>
+        <v>-1.5837446548368857e-05</v>
       </c>
       <c r="P19">
-        <v>-1.5643830281320719e-05</v>
+        <v>-1.8112197914833833e-05</v>
       </c>
       <c r="Q19">
-        <v>0.00022578900057727993</v>
+        <v>-6.1038590454142285e-07</v>
       </c>
       <c r="R19">
-        <v>0.00022627384659600533</v>
+        <v>0.00022805315901684424</v>
       </c>
       <c r="S19">
-        <v>0.00022503118828069428</v>
+        <v>0.00022726462477014412</v>
       </c>
       <c r="T19">
-        <v>0.00034828512569801243</v>
+        <v>0.00040783190412116367</v>
       </c>
       <c r="U19">
-        <v>0.00022592126527763576</v>
+        <v>0.00022884972844813007</v>
       </c>
       <c r="V19">
-        <v>0.00022522621914895888</v>
+        <v>0.00022985585059856305</v>
       </c>
       <c r="W19">
-        <v>9.6106571820926985e-06</v>
+        <v>0.00022818581372264073</v>
       </c>
       <c r="X19">
-        <v>7.2324398060051756e-06</v>
+        <v>-1.9458038378820056e-06</v>
       </c>
       <c r="Y19">
-        <v>-0.00024100480067444866</v>
+        <v>-1.5420676985794609e-06</v>
+      </c>
+      <c r="Z19">
+        <v>-0.00022691868160200208</v>
       </c>
     </row>
     <row r="20">
@@ -3627,76 +3839,79 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <v>-0.085687137554312981</v>
+        <v>0.026338825024021899</v>
       </c>
       <c r="C20">
-        <v>-5.0655196481250468e-07</v>
+        <v>4.0744330786291569e-06</v>
       </c>
       <c r="D20">
-        <v>-3.5491157806904594e-06</v>
+        <v>1.199413865635238e-06</v>
       </c>
       <c r="E20">
-        <v>-4.0571523860573422e-07</v>
+        <v>1.4496419870999995e-06</v>
       </c>
       <c r="F20">
-        <v>6.8156652398992608e-09</v>
+        <v>-6.8228523243410321e-09</v>
       </c>
       <c r="G20">
-        <v>-7.3984096013794654e-06</v>
+        <v>3.3701263996210521e-06</v>
       </c>
       <c r="H20">
-        <v>-2.7071114036435235e-05</v>
+        <v>-4.0671306048767876e-06</v>
       </c>
       <c r="I20">
-        <v>7.2659859772372322e-08</v>
+        <v>-9.6368299099360385e-08</v>
       </c>
       <c r="J20">
-        <v>3.0079454138238682e-07</v>
+        <v>1.7659140015421925e-07</v>
       </c>
       <c r="K20">
-        <v>-3.9378479098398279e-06</v>
+        <v>-4.6965833906039355e-07</v>
       </c>
       <c r="L20">
-        <v>-5.345183701464613e-06</v>
+        <v>-4.5050495602512912e-06</v>
       </c>
       <c r="M20">
-        <v>7.1397231396171031e-06</v>
+        <v>1.5640492685799255e-06</v>
       </c>
       <c r="N20">
-        <v>-3.1427702880073069e-06</v>
+        <v>-5.3694235400459939e-06</v>
       </c>
       <c r="O20">
-        <v>-5.2557936165260552e-06</v>
+        <v>-5.9263315668050691e-06</v>
       </c>
       <c r="P20">
-        <v>-1.4880848994417933e-05</v>
+        <v>-1.6785308262909444e-05</v>
       </c>
       <c r="Q20">
-        <v>0.00022430238164636624</v>
+        <v>-8.8151226671131569e-07</v>
       </c>
       <c r="R20">
-        <v>0.00022437139196139854</v>
+        <v>0.00022983126126665878</v>
       </c>
       <c r="S20">
-        <v>0.00022661056225080719</v>
+        <v>0.00023014977408649414</v>
       </c>
       <c r="T20">
-        <v>0.00022592126527763576</v>
+        <v>0.00022884972844813007</v>
       </c>
       <c r="U20">
-        <v>0.00037263728138000598</v>
+        <v>0.0003541286487533252</v>
       </c>
       <c r="V20">
-        <v>0.00022632553219887621</v>
+        <v>0.00022913639206277378</v>
       </c>
       <c r="W20">
-        <v>1.1076535110197458e-06</v>
+        <v>0.00022832214416890345</v>
       </c>
       <c r="X20">
-        <v>5.0696291891076035e-07</v>
+        <v>9.5794351118444556e-06</v>
       </c>
       <c r="Y20">
-        <v>-0.00020487621859752623</v>
+        <v>6.6513031158763959e-06</v>
+      </c>
+      <c r="Z20">
+        <v>-0.00025390981872632006</v>
       </c>
     </row>
     <row r="21">
@@ -3704,76 +3919,79 @@
         <v>41</v>
       </c>
       <c r="B21">
-        <v>-0.07600692160361569</v>
+        <v>-0.083751864613068633</v>
       </c>
       <c r="C21">
-        <v>4.8471676014940943e-07</v>
+        <v>-3.1490801063459474e-07</v>
       </c>
       <c r="D21">
-        <v>-7.4325632025394498e-06</v>
+        <v>-3.547830013831227e-06</v>
       </c>
       <c r="E21">
-        <v>-1.6900262467597306e-06</v>
+        <v>-3.9260086888248597e-07</v>
       </c>
       <c r="F21">
-        <v>2.0034526493199685e-08</v>
+        <v>6.2112822855097321e-09</v>
       </c>
       <c r="G21">
-        <v>-1.6598194895405799e-05</v>
+        <v>-6.7526105690024268e-06</v>
       </c>
       <c r="H21">
-        <v>-1.6717414056993305e-05</v>
+        <v>-2.7078231002793961e-05</v>
       </c>
       <c r="I21">
-        <v>2.5646588833028497e-07</v>
+        <v>5.2358429818358016e-08</v>
       </c>
       <c r="J21">
-        <v>2.8320493425306157e-07</v>
+        <v>2.8754249963561004e-07</v>
       </c>
       <c r="K21">
-        <v>3.2703868080553761e-06</v>
+        <v>-4.0712087287902474e-06</v>
       </c>
       <c r="L21">
-        <v>3.5300602758547455e-06</v>
+        <v>-5.3135203889994488e-06</v>
       </c>
       <c r="M21">
-        <v>2.6040608889536327e-06</v>
+        <v>7.3311935416573251e-06</v>
       </c>
       <c r="N21">
-        <v>-8.8084823902473771e-06</v>
+        <v>-3.0192034740033046e-06</v>
       </c>
       <c r="O21">
-        <v>-1.7988827677729689e-06</v>
+        <v>-5.1454291506282748e-06</v>
       </c>
       <c r="P21">
-        <v>-1.1235184689076597e-05</v>
+        <v>-1.4848770413268449e-05</v>
       </c>
       <c r="Q21">
-        <v>0.00022408729929085904</v>
+        <v>6.3929846600101761e-08</v>
       </c>
       <c r="R21">
-        <v>0.00022440708522501266</v>
+        <v>0.00022747854856051118</v>
       </c>
       <c r="S21">
-        <v>0.00022505032427709275</v>
+        <v>0.00022751292162971802</v>
       </c>
       <c r="T21">
-        <v>0.00022522621914895888</v>
+        <v>0.00022985585059856305</v>
       </c>
       <c r="U21">
-        <v>0.00022632553219887621</v>
+        <v>0.00022913639206277378</v>
       </c>
       <c r="V21">
-        <v>0.00095808138649024503</v>
+        <v>0.00037767951925536886</v>
       </c>
       <c r="W21">
-        <v>5.5669149371990802e-06</v>
+        <v>0.0002296277829786722</v>
       </c>
       <c r="X21">
-        <v>2.5605650105126629e-06</v>
+        <v>1.3399314615998981e-06</v>
       </c>
       <c r="Y21">
-        <v>-0.00018739934627477989</v>
+        <v>7.6143171949770915e-07</v>
+      </c>
+      <c r="Z21">
+        <v>-0.00020847322910526718</v>
       </c>
     </row>
     <row r="22">
@@ -3781,76 +3999,79 @@
         <v>42</v>
       </c>
       <c r="B22">
-        <v>-0.069060357925321947</v>
+        <v>-0.070957818630636105</v>
       </c>
       <c r="C22">
-        <v>9.9270873030602194e-06</v>
+        <v>9.3964422099393236e-07</v>
       </c>
       <c r="D22">
-        <v>6.646686904458306e-06</v>
+        <v>-7.1038295865027607e-06</v>
       </c>
       <c r="E22">
-        <v>5.5575161389209792e-07</v>
+        <v>-1.7611908335470048e-06</v>
       </c>
       <c r="F22">
-        <v>-7.1273582057857486e-09</v>
+        <v>1.892532694301619e-08</v>
       </c>
       <c r="G22">
-        <v>3.385973094613812e-06</v>
+        <v>-1.7205640467171731e-05</v>
       </c>
       <c r="H22">
-        <v>1.3414268690361624e-05</v>
+        <v>-1.7444592044385005e-05</v>
       </c>
       <c r="I22">
-        <v>-8.6640295740320201e-08</v>
+        <v>2.5664808279232504e-07</v>
       </c>
       <c r="J22">
-        <v>-2.3479635954616842e-07</v>
+        <v>2.7964978771509953e-07</v>
       </c>
       <c r="K22">
-        <v>2.7999535241356691e-06</v>
+        <v>2.8477634177974831e-06</v>
       </c>
       <c r="L22">
-        <v>-3.4440484272296107e-06</v>
+        <v>3.4702826084420064e-06</v>
       </c>
       <c r="M22">
-        <v>-1.535190002280966e-06</v>
+        <v>2.5953865832603693e-06</v>
       </c>
       <c r="N22">
-        <v>-2.9017279506888178e-06</v>
+        <v>-8.8565235369922937e-06</v>
       </c>
       <c r="O22">
-        <v>-4.4117503053185965e-06</v>
+        <v>-2.0082545613976215e-06</v>
       </c>
       <c r="P22">
-        <v>-8.8476166284484315e-06</v>
+        <v>-1.1402762757424832e-05</v>
       </c>
       <c r="Q22">
-        <v>5.4340547670740986e-06</v>
+        <v>1.9497853716723549e-07</v>
       </c>
       <c r="R22">
-        <v>1.8430072341922298e-06</v>
+        <v>0.00022715728074463665</v>
       </c>
       <c r="S22">
-        <v>-1.4156551655240957e-06</v>
+        <v>0.00022746099623792559</v>
       </c>
       <c r="T22">
-        <v>9.6106571820926985e-06</v>
+        <v>0.00022818581372264073</v>
       </c>
       <c r="U22">
-        <v>1.1076535110197458e-06</v>
+        <v>0.00022832214416890345</v>
       </c>
       <c r="V22">
-        <v>5.5669149371990802e-06</v>
+        <v>0.0002296277829786722</v>
       </c>
       <c r="W22">
-        <v>0.00054163263502109973</v>
+        <v>0.00097070467625051888</v>
       </c>
       <c r="X22">
-        <v>3.2895588874628127e-05</v>
+        <v>5.7603731808141601e-06</v>
       </c>
       <c r="Y22">
-        <v>-4.3823941064528181e-05</v>
+        <v>3.090883224014475e-06</v>
+      </c>
+      <c r="Z22">
+        <v>-0.00018839407143784391</v>
       </c>
     </row>
     <row r="23">
@@ -3858,76 +4079,79 @@
         <v>43</v>
       </c>
       <c r="B23">
-        <v>0.10688185194570429</v>
+        <v>-0.060058790869018046</v>
       </c>
       <c r="C23">
-        <v>4.4099699277390498e-07</v>
+        <v>1.0762653435339464e-05</v>
       </c>
       <c r="D23">
-        <v>6.5175322309821035e-06</v>
+        <v>7.4954840592643433e-06</v>
       </c>
       <c r="E23">
-        <v>2.6983948173981394e-07</v>
+        <v>5.4492633783507718e-07</v>
       </c>
       <c r="F23">
-        <v>-7.2580327824294464e-09</v>
+        <v>-9.4961746388675996e-09</v>
       </c>
       <c r="G23">
-        <v>6.1850035599557911e-06</v>
+        <v>2.4054865098395072e-06</v>
       </c>
       <c r="H23">
-        <v>7.7783317021278509e-06</v>
+        <v>1.225145714772948e-05</v>
       </c>
       <c r="I23">
-        <v>-9.1018842172097784e-08</v>
+        <v>-7.8026640033679147e-08</v>
       </c>
       <c r="J23">
-        <v>-4.7106878851704288e-08</v>
+        <v>-2.2683095591702518e-07</v>
       </c>
       <c r="K23">
-        <v>8.2945220073543603e-06</v>
+        <v>2.0740955678939318e-06</v>
       </c>
       <c r="L23">
-        <v>-7.2830993972605194e-06</v>
+        <v>-3.3648348434563507e-06</v>
       </c>
       <c r="M23">
-        <v>-4.94936854496475e-06</v>
+        <v>-1.726445848590218e-06</v>
       </c>
       <c r="N23">
-        <v>-6.5256966257938215e-06</v>
+        <v>-3.0208232874988315e-06</v>
       </c>
       <c r="O23">
-        <v>-3.9159099235375396e-06</v>
+        <v>-4.7720822319297898e-06</v>
       </c>
       <c r="P23">
-        <v>-5.8181300615266672e-06</v>
+        <v>-9.3909845320485178e-06</v>
       </c>
       <c r="Q23">
-        <v>4.4249661319536601e-06</v>
+        <v>2.5390559283501458e-07</v>
       </c>
       <c r="R23">
-        <v>-5.0227555449651865e-06</v>
+        <v>5.1921395075385809e-06</v>
       </c>
       <c r="S23">
-        <v>-9.7882427825728354e-07</v>
+        <v>1.5744284359086614e-06</v>
       </c>
       <c r="T23">
-        <v>7.2324398060051756e-06</v>
+        <v>-1.9458038378820056e-06</v>
       </c>
       <c r="U23">
-        <v>5.0696291891076035e-07</v>
+        <v>9.5794351118444556e-06</v>
       </c>
       <c r="V23">
-        <v>2.5605650105126629e-06</v>
+        <v>1.3399314615998981e-06</v>
       </c>
       <c r="W23">
-        <v>3.2895588874628127e-05</v>
+        <v>5.7603731808141601e-06</v>
       </c>
       <c r="X23">
-        <v>0.00065274524929682801</v>
+        <v>0.00055480864831225713</v>
       </c>
       <c r="Y23">
-        <v>-3.2455320506445094e-05</v>
+        <v>3.3584570259844272e-05</v>
+      </c>
+      <c r="Z23">
+        <v>-4.305804941414625e-05</v>
       </c>
     </row>
     <row r="24">
@@ -3935,76 +4159,159 @@
         <v>44</v>
       </c>
       <c r="B24">
-        <v>-2.3374978940084312</v>
+        <v>0.13788700562763845</v>
       </c>
       <c r="C24">
-        <v>-0.0010096918967565623</v>
+        <v>1.9117010318668043e-06</v>
       </c>
       <c r="D24">
-        <v>-0.00017929425668358154</v>
+        <v>8.5817809702140198e-06</v>
       </c>
       <c r="E24">
-        <v>-0.0002381866332478734</v>
+        <v>-1.1056520360351545e-07</v>
       </c>
       <c r="F24">
-        <v>2.251931959082401e-06</v>
+        <v>-1.4353501110381609e-08</v>
       </c>
       <c r="G24">
-        <v>-0.0015950522206416482</v>
+        <v>3.5554818089718553e-06</v>
       </c>
       <c r="H24">
-        <v>-0.0017069303726679895</v>
+        <v>3.8106426221348864e-06</v>
       </c>
       <c r="I24">
-        <v>3.1768759411703956e-05</v>
+        <v>-8.3993790234535201e-08</v>
       </c>
       <c r="J24">
-        <v>3.303608122063139e-05</v>
+        <v>-4.7772217982981966e-08</v>
       </c>
       <c r="K24">
-        <v>9.7567365737442701e-05</v>
+        <v>6.0985516529011777e-06</v>
       </c>
       <c r="L24">
-        <v>0.00021011173211139144</v>
+        <v>-7.6796688624362341e-06</v>
       </c>
       <c r="M24">
-        <v>-0.0039243840081503887</v>
+        <v>-3.4817736032051729e-06</v>
       </c>
       <c r="N24">
-        <v>-0.0039664828139294077</v>
+        <v>-4.7581654038956133e-06</v>
       </c>
       <c r="O24">
-        <v>-0.0040448240361537387</v>
+        <v>-2.5253203326530597e-06</v>
       </c>
       <c r="P24">
-        <v>-0.0042070436081594054</v>
+        <v>-4.6229873994539743e-06</v>
       </c>
       <c r="Q24">
-        <v>-0.00025534441360154322</v>
+        <v>1.1222093368602964e-06</v>
       </c>
       <c r="R24">
-        <v>-0.00022837255817040287</v>
+        <v>3.556630499189163e-06</v>
       </c>
       <c r="S24">
-        <v>-0.00021719577000382846</v>
+        <v>-6.0588042249540153e-06</v>
       </c>
       <c r="T24">
-        <v>-0.00024100480067444866</v>
+        <v>-1.5420676985794609e-06</v>
       </c>
       <c r="U24">
-        <v>-0.00020487621859752623</v>
+        <v>6.6513031158763959e-06</v>
       </c>
       <c r="V24">
-        <v>-0.00018739934627477989</v>
+        <v>7.6143171949770915e-07</v>
       </c>
       <c r="W24">
-        <v>-4.3823941064528181e-05</v>
+        <v>3.090883224014475e-06</v>
       </c>
       <c r="X24">
-        <v>-3.2455320506445094e-05</v>
+        <v>3.3584570259844272e-05</v>
       </c>
       <c r="Y24">
-        <v>0.010121975367309652</v>
+        <v>0.00066562990108023912</v>
+      </c>
+      <c r="Z24">
+        <v>-2.2863599700261748e-05</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25">
+        <v>-2.007175460808277</v>
+      </c>
+      <c r="C25">
+        <v>-0.0010029561851752527</v>
+      </c>
+      <c r="D25">
+        <v>-0.00015871617962612343</v>
+      </c>
+      <c r="E25">
+        <v>-0.00024671039711147752</v>
+      </c>
+      <c r="F25">
+        <v>2.2400436684662503e-06</v>
+      </c>
+      <c r="G25">
+        <v>-0.0016344679025398991</v>
+      </c>
+      <c r="H25">
+        <v>-0.0017643339865585791</v>
+      </c>
+      <c r="I25">
+        <v>3.2161338848841617e-05</v>
+      </c>
+      <c r="J25">
+        <v>3.3431135112370259e-05</v>
+      </c>
+      <c r="K25">
+        <v>8.0285793007983425e-05</v>
+      </c>
+      <c r="L25">
+        <v>0.00021121672626932243</v>
+      </c>
+      <c r="M25">
+        <v>-0.0040406324809560499</v>
+      </c>
+      <c r="N25">
+        <v>-0.0040816017920346694</v>
+      </c>
+      <c r="O25">
+        <v>-0.0041640303852207754</v>
+      </c>
+      <c r="P25">
+        <v>-0.0043277562451338293</v>
+      </c>
+      <c r="Q25">
+        <v>1.0620349589535507e-05</v>
+      </c>
+      <c r="R25">
+        <v>-0.00026895958367919643</v>
+      </c>
+      <c r="S25">
+        <v>-0.00024008032364950525</v>
+      </c>
+      <c r="T25">
+        <v>-0.00022691868160200208</v>
+      </c>
+      <c r="U25">
+        <v>-0.00025390981872632006</v>
+      </c>
+      <c r="V25">
+        <v>-0.00020847322910526718</v>
+      </c>
+      <c r="W25">
+        <v>-0.00018839407143784391</v>
+      </c>
+      <c r="X25">
+        <v>-4.305804941414625e-05</v>
+      </c>
+      <c r="Y25">
+        <v>-2.2863599700261748e-05</v>
+      </c>
+      <c r="Z25">
+        <v>0.0104468752985879</v>
       </c>
     </row>
   </sheetData>
@@ -4013,7 +4320,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4021,7 +4328,7 @@
         <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
         <v>24</v>
@@ -4085,6 +4392,9 @@
       </c>
       <c r="W1" t="s">
         <v>44</v>
+      </c>
+      <c r="X1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="2">
@@ -4092,70 +4402,73 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>0.18155289999776023</v>
+        <v>0.15780959588465302</v>
       </c>
       <c r="C2">
-        <v>2.8570344048192584e-05</v>
+        <v>2.9788869757628298e-05</v>
       </c>
       <c r="D2">
-        <v>-3.1087574256456382e-07</v>
+        <v>-3.1732530065509644e-07</v>
       </c>
       <c r="E2">
-        <v>6.145594119162167e-05</v>
+        <v>6.7874139074927133e-05</v>
       </c>
       <c r="F2">
-        <v>3.5417925874530029e-05</v>
+        <v>4.426875542944387e-05</v>
       </c>
       <c r="G2">
-        <v>-1.2715783864496432e-06</v>
+        <v>-1.4000736308627829e-06</v>
       </c>
       <c r="H2">
-        <v>-6.7501083671175927e-07</v>
+        <v>-8.5737039268332509e-07</v>
       </c>
       <c r="I2">
-        <v>-1.389602399273057e-05</v>
+        <v>-1.4618614651801889e-05</v>
       </c>
       <c r="J2">
-        <v>-4.071762363064737e-05</v>
+        <v>-4.124105739835972e-05</v>
       </c>
       <c r="K2">
-        <v>4.2256430281573402e-06</v>
+        <v>4.5693619109330559e-06</v>
       </c>
       <c r="L2">
-        <v>7.5137478233992957e-06</v>
+        <v>7.5695315095912442e-06</v>
       </c>
       <c r="M2">
-        <v>1.0421809366738927e-05</v>
+        <v>1.0897020363040167e-05</v>
       </c>
       <c r="N2">
-        <v>1.7528688346052032e-05</v>
+        <v>1.8393181137025421e-05</v>
       </c>
       <c r="O2">
-        <v>2.6908205779039368e-06</v>
+        <v>-7.6452733741350328e-07</v>
       </c>
       <c r="P2">
-        <v>3.9634462420549206e-06</v>
+        <v>4.0270904893893519e-06</v>
       </c>
       <c r="Q2">
-        <v>2.4335226986637456e-06</v>
+        <v>5.2385002328871272e-06</v>
       </c>
       <c r="R2">
-        <v>5.3475667911221148e-06</v>
+        <v>2.4231498495329883e-06</v>
       </c>
       <c r="S2">
-        <v>3.7934002192214932e-06</v>
+        <v>7.1597743536237204e-06</v>
       </c>
       <c r="T2">
-        <v>-6.4655709140265847e-08</v>
+        <v>3.6638367474764933e-06</v>
       </c>
       <c r="U2">
-        <v>8.069340261440761e-07</v>
+        <v>-9.0969752831655091e-08</v>
       </c>
       <c r="V2">
-        <v>-1.1644310149497e-06</v>
+        <v>1.0431852262641661e-06</v>
       </c>
       <c r="W2">
-        <v>-0.00060316515687003835</v>
+        <v>-1.6902010121146817e-06</v>
+      </c>
+      <c r="X2">
+        <v>-0.0006304128855597462</v>
       </c>
     </row>
     <row r="3">
@@ -4163,70 +4476,73 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>-0.0019734815189099823</v>
+        <v>-0.0019714459742618553</v>
       </c>
       <c r="C3">
-        <v>-3.1087574256456382e-07</v>
+        <v>-3.1732530065509644e-07</v>
       </c>
       <c r="D3">
-        <v>3.5134805097760216e-09</v>
+        <v>3.591085245047575e-09</v>
       </c>
       <c r="E3">
-        <v>-2.0414389628300173e-07</v>
+        <v>-2.2558277365457942e-07</v>
       </c>
       <c r="F3">
-        <v>8.8351797042472906e-08</v>
+        <v>6.8417126580518613e-08</v>
       </c>
       <c r="G3">
-        <v>3.1194493670003663e-09</v>
+        <v>3.5198752650413267e-09</v>
       </c>
       <c r="H3">
-        <v>-3.5221238744751483e-09</v>
+        <v>-3.2175457103163668e-09</v>
       </c>
       <c r="I3">
-        <v>1.1980984957276447e-07</v>
+        <v>1.2224389992535361e-07</v>
       </c>
       <c r="J3">
-        <v>4.761386104823883e-07</v>
+        <v>4.9003292407097127e-07</v>
       </c>
       <c r="K3">
-        <v>-4.7670154323545336e-08</v>
+        <v>-4.563757170066402e-08</v>
       </c>
       <c r="L3">
-        <v>-8.0057769711292844e-08</v>
+        <v>-8.3284597261071689e-08</v>
       </c>
       <c r="M3">
-        <v>-9.5835780141784615e-08</v>
+        <v>-9.8560846821640437e-08</v>
       </c>
       <c r="N3">
-        <v>-1.4524158596248764e-07</v>
+        <v>-1.5008458546326047e-07</v>
       </c>
       <c r="O3">
-        <v>-3.1540914682322173e-08</v>
+        <v>-6.4018967794351553e-10</v>
       </c>
       <c r="P3">
-        <v>-4.8031299484466901e-08</v>
+        <v>-3.1056359549501946e-08</v>
       </c>
       <c r="Q3">
-        <v>-2.8093261492609513e-08</v>
+        <v>-4.7783714794227333e-08</v>
       </c>
       <c r="R3">
-        <v>-5.8791859272004374e-08</v>
+        <v>-2.7412828300569529e-08</v>
       </c>
       <c r="S3">
-        <v>-4.0427055481624849e-08</v>
+        <v>-5.8653693398855124e-08</v>
       </c>
       <c r="T3">
-        <v>3.7341562483775182e-09</v>
+        <v>-4.0511729934063368e-08</v>
       </c>
       <c r="U3">
-        <v>-1.2321991127483736e-08</v>
+        <v>3.8287290382989888e-09</v>
       </c>
       <c r="V3">
-        <v>1.0237557915597247e-08</v>
+        <v>-1.0027361254123305e-08</v>
       </c>
       <c r="W3">
-        <v>6.2857373250009652e-06</v>
+        <v>8.1476041608400728e-09</v>
+      </c>
+      <c r="X3">
+        <v>6.4155037467783289e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4234,70 +4550,73 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>-0.2656763243635798</v>
+        <v>-0.39921678991903153</v>
       </c>
       <c r="C4">
-        <v>6.145594119162167e-05</v>
+        <v>6.7874139074927133e-05</v>
       </c>
       <c r="D4">
-        <v>-2.0414389628300173e-07</v>
+        <v>-2.2558277365457942e-07</v>
       </c>
       <c r="E4">
-        <v>0.0054500186693699493</v>
+        <v>0.0055520790614022085</v>
       </c>
       <c r="F4">
-        <v>0.0020705646219560557</v>
+        <v>0.0021372209562648624</v>
       </c>
       <c r="G4">
-        <v>-0.00011398018716582164</v>
+        <v>-0.00011618173020817429</v>
       </c>
       <c r="H4">
-        <v>-4.4527126883032722e-05</v>
+        <v>-4.5996535764994508e-05</v>
       </c>
       <c r="I4">
-        <v>4.5689924842101498e-06</v>
+        <v>2.2646989258864597e-06</v>
       </c>
       <c r="J4">
-        <v>-0.0001109602217266641</v>
+        <v>-0.00011244112206871323</v>
       </c>
       <c r="K4">
-        <v>4.282961246756731e-05</v>
+        <v>4.9609504167499245e-05</v>
       </c>
       <c r="L4">
-        <v>4.2493466319664416e-05</v>
+        <v>4.7653686225048939e-05</v>
       </c>
       <c r="M4">
-        <v>3.8593958948113477e-05</v>
+        <v>4.6044103403549796e-05</v>
       </c>
       <c r="N4">
-        <v>8.1361097263202655e-05</v>
+        <v>9.0691766568169133e-05</v>
       </c>
       <c r="O4">
-        <v>2.6625627524506123e-05</v>
+        <v>-4.777910833021885e-06</v>
       </c>
       <c r="P4">
-        <v>2.9133457784574754e-05</v>
+        <v>3.6028865475585582e-05</v>
       </c>
       <c r="Q4">
-        <v>1.5636866182581312e-05</v>
+        <v>3.7076509170658546e-05</v>
       </c>
       <c r="R4">
-        <v>1.585609166826472e-05</v>
+        <v>1.7512566867786819e-05</v>
       </c>
       <c r="S4">
-        <v>-1.1666304287785337e-05</v>
+        <v>2.8008398524890667e-05</v>
       </c>
       <c r="T4">
-        <v>-2.5758658654818884e-07</v>
+        <v>-1.2010776328894211e-05</v>
       </c>
       <c r="U4">
-        <v>1.5059445286503816e-05</v>
+        <v>2.4554238971554915e-06</v>
       </c>
       <c r="V4">
-        <v>2.7777225986964383e-05</v>
+        <v>1.8988390956102695e-05</v>
       </c>
       <c r="W4">
-        <v>-0.0024038095953505842</v>
+        <v>2.6589158637947094e-05</v>
+      </c>
+      <c r="X4">
+        <v>-0.002568229213450051</v>
       </c>
     </row>
     <row r="5">
@@ -4305,70 +4624,73 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>-0.36908335085649657</v>
+        <v>-0.59120536782597655</v>
       </c>
       <c r="C5">
-        <v>3.5417925874530029e-05</v>
+        <v>4.426875542944387e-05</v>
       </c>
       <c r="D5">
-        <v>8.8351797042472906e-08</v>
+        <v>6.8417126580518613e-08</v>
       </c>
       <c r="E5">
-        <v>0.0020705646219560557</v>
+        <v>0.0021372209562648624</v>
       </c>
       <c r="F5">
-        <v>0.0050920032068113522</v>
+        <v>0.0052370489222406643</v>
       </c>
       <c r="G5">
-        <v>-4.4779583271372593e-05</v>
+        <v>-4.6199503244527474e-05</v>
       </c>
       <c r="H5">
-        <v>-0.00010385139638680865</v>
+        <v>-0.00010698243770226929</v>
       </c>
       <c r="I5">
-        <v>2.6223679441483103e-05</v>
+        <v>2.2798458428164564e-05</v>
       </c>
       <c r="J5">
-        <v>-0.00016060492989324388</v>
+        <v>-0.00016152811421116844</v>
       </c>
       <c r="K5">
-        <v>3.2666500406564806e-05</v>
+        <v>3.4843511443092634e-05</v>
       </c>
       <c r="L5">
-        <v>-6.9686470291604932e-07</v>
+        <v>-3.879696242586406e-06</v>
       </c>
       <c r="M5">
-        <v>-1.2017844458756736e-05</v>
+        <v>-1.0720208317576709e-05</v>
       </c>
       <c r="N5">
-        <v>4.7401913242479336e-05</v>
+        <v>5.2792239731769882e-05</v>
       </c>
       <c r="O5">
-        <v>2.282328641040083e-05</v>
+        <v>-7.8994016279695514e-06</v>
       </c>
       <c r="P5">
-        <v>-1.2405574572347641e-05</v>
+        <v>3.7307573828210386e-05</v>
       </c>
       <c r="Q5">
-        <v>-5.6082656110512338e-05</v>
+        <v>-1.8466190281054838e-06</v>
       </c>
       <c r="R5">
-        <v>-2.4882826621797857e-05</v>
+        <v>-5.8318349893103538e-05</v>
       </c>
       <c r="S5">
-        <v>-9.7056687944450552e-05</v>
+        <v>-6.8496055620500233e-06</v>
       </c>
       <c r="T5">
-        <v>-6.0964852193156274e-05</v>
+        <v>-0.00010041792123738913</v>
       </c>
       <c r="U5">
-        <v>3.1849958787050858e-05</v>
+        <v>-6.3679342426135744e-05</v>
       </c>
       <c r="V5">
-        <v>4.4330517297866446e-05</v>
+        <v>3.7566140918254881e-05</v>
       </c>
       <c r="W5">
-        <v>-0.001770431700220244</v>
+        <v>3.9743411659292438e-05</v>
+      </c>
+      <c r="X5">
+        <v>-0.0019846097145459971</v>
       </c>
     </row>
     <row r="6">
@@ -4376,70 +4698,73 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>0.0015697344324824361</v>
+        <v>0.0041559553451572112</v>
       </c>
       <c r="C6">
-        <v>-1.2715783864496432e-06</v>
+        <v>-1.4000736308627829e-06</v>
       </c>
       <c r="D6">
-        <v>3.1194493670003663e-09</v>
+        <v>3.5198752650413267e-09</v>
       </c>
       <c r="E6">
-        <v>-0.00011398018716582164</v>
+        <v>-0.00011618173020817429</v>
       </c>
       <c r="F6">
-        <v>-4.4779583271372593e-05</v>
+        <v>-4.6199503244527474e-05</v>
       </c>
       <c r="G6">
-        <v>2.5543413399711525e-06</v>
+        <v>2.6061584109886152e-06</v>
       </c>
       <c r="H6">
-        <v>1.029147216541347e-06</v>
+        <v>1.0618225879102475e-06</v>
       </c>
       <c r="I6">
-        <v>-1.1424393235353971e-07</v>
+        <v>-8.3644787598844327e-08</v>
       </c>
       <c r="J6">
-        <v>2.464918200603723e-06</v>
+        <v>2.5245077790999407e-06</v>
       </c>
       <c r="K6">
-        <v>-5.7116826918548636e-07</v>
+        <v>-7.1308087136185138e-07</v>
       </c>
       <c r="L6">
-        <v>-5.9261344475577458e-07</v>
+        <v>-7.3502425340134914e-07</v>
       </c>
       <c r="M6">
-        <v>-8.0575090080943078e-08</v>
+        <v>-2.4223498502268031e-07</v>
       </c>
       <c r="N6">
-        <v>-7.2106363225308409e-07</v>
+        <v>-9.0958006689417377e-07</v>
       </c>
       <c r="O6">
-        <v>-3.1006659675244876e-07</v>
+        <v>9.5474295452152603e-08</v>
       </c>
       <c r="P6">
-        <v>-5.0793801075564197e-07</v>
+        <v>-5.0408378862786373e-07</v>
       </c>
       <c r="Q6">
-        <v>-3.0768773176249578e-07</v>
+        <v>-6.6355724969193097e-07</v>
       </c>
       <c r="R6">
-        <v>-4.8158960944848539e-07</v>
+        <v>-3.6395007813032639e-07</v>
       </c>
       <c r="S6">
-        <v>1.8668074382521674e-07</v>
+        <v>-7.5163584171551396e-07</v>
       </c>
       <c r="T6">
-        <v>-1.8504666670830908e-07</v>
+        <v>1.7685463645761033e-07</v>
       </c>
       <c r="U6">
-        <v>-1.5407544467246968e-07</v>
+        <v>-2.7606086389061068e-07</v>
       </c>
       <c r="V6">
-        <v>-4.4440045106206145e-07</v>
+        <v>-2.288879098296942e-07</v>
       </c>
       <c r="W6">
-        <v>4.8533752831501739e-05</v>
+        <v>-4.2729415525341722e-07</v>
+      </c>
+      <c r="X6">
+        <v>5.186261211770031e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4447,70 +4772,73 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>-0.0015117054103097728</v>
+        <v>0.0032361259930868027</v>
       </c>
       <c r="C7">
-        <v>-6.7501083671175927e-07</v>
+        <v>-8.5737039268332509e-07</v>
       </c>
       <c r="D7">
-        <v>-3.5221238744751483e-09</v>
+        <v>-3.2175457103163668e-09</v>
       </c>
       <c r="E7">
-        <v>-4.4527126883032722e-05</v>
+        <v>-4.5996535764994508e-05</v>
       </c>
       <c r="F7">
-        <v>-0.00010385139638680865</v>
+        <v>-0.00010698243770226929</v>
       </c>
       <c r="G7">
-        <v>1.029147216541347e-06</v>
+        <v>1.0618225879102475e-06</v>
       </c>
       <c r="H7">
-        <v>2.2602958425552557e-06</v>
+        <v>2.3318953186326873e-06</v>
       </c>
       <c r="I7">
-        <v>-8.5832584056232064e-07</v>
+        <v>-8.1054052542666537e-07</v>
       </c>
       <c r="J7">
-        <v>3.5592394255664058e-06</v>
+        <v>3.5874135053682136e-06</v>
       </c>
       <c r="K7">
-        <v>-8.057193435553014e-07</v>
+        <v>-8.4300967431657132e-07</v>
       </c>
       <c r="L7">
-        <v>1.0543264573085097e-07</v>
+        <v>1.7949919777006485e-07</v>
       </c>
       <c r="M7">
-        <v>1.1016189313236715e-06</v>
+        <v>1.1071027357113411e-06</v>
       </c>
       <c r="N7">
-        <v>2.5431908612260742e-07</v>
+        <v>1.8382703028152141e-07</v>
       </c>
       <c r="O7">
-        <v>-1.4312763594037549e-07</v>
+        <v>1.7178678606024532e-07</v>
       </c>
       <c r="P7">
-        <v>7.3477227987356569e-07</v>
+        <v>-4.418125395770096e-07</v>
       </c>
       <c r="Q7">
-        <v>8.6235231722208974e-07</v>
+        <v>5.2423766880419505e-07</v>
       </c>
       <c r="R7">
-        <v>5.1579616379850797e-07</v>
+        <v>9.0037822483940582e-07</v>
       </c>
       <c r="S7">
-        <v>1.546394438380446e-06</v>
+        <v>1.2054172668947265e-07</v>
       </c>
       <c r="T7">
-        <v>1.0627879244639522e-06</v>
+        <v>1.6070718999630367e-06</v>
       </c>
       <c r="U7">
-        <v>-4.5695583106736617e-07</v>
+        <v>1.1155619207790292e-06</v>
       </c>
       <c r="V7">
-        <v>-4.835835820950629e-07</v>
+        <v>-5.751167326012992e-07</v>
       </c>
       <c r="W7">
-        <v>3.4140276008591438e-05</v>
+        <v>-3.8535023871791083e-07</v>
+      </c>
+      <c r="X7">
+        <v>3.8548946879646743e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4518,70 +4846,73 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>0.011759827817618723</v>
+        <v>0.024201055328980935</v>
       </c>
       <c r="C8">
-        <v>-1.389602399273057e-05</v>
+        <v>-1.4618614651801889e-05</v>
       </c>
       <c r="D8">
-        <v>1.1980984957276447e-07</v>
+        <v>1.2224389992535361e-07</v>
       </c>
       <c r="E8">
-        <v>4.5689924842101498e-06</v>
+        <v>2.2646989258864597e-06</v>
       </c>
       <c r="F8">
-        <v>2.6223679441483103e-05</v>
+        <v>2.2798458428164564e-05</v>
       </c>
       <c r="G8">
-        <v>-1.1424393235353971e-07</v>
+        <v>-8.3644787598844327e-08</v>
       </c>
       <c r="H8">
-        <v>-8.5832584056232064e-07</v>
+        <v>-8.1054052542666537e-07</v>
       </c>
       <c r="I8">
-        <v>0.00030905744799336301</v>
+        <v>0.0003179623104077727</v>
       </c>
       <c r="J8">
-        <v>-0.00010383605532654903</v>
+        <v>-0.00010797535573062196</v>
       </c>
       <c r="K8">
-        <v>-1.397948033387334e-05</v>
+        <v>-1.3750466447516011e-05</v>
       </c>
       <c r="L8">
-        <v>-2.1906402007598587e-05</v>
+        <v>-2.1724707888330565e-05</v>
       </c>
       <c r="M8">
-        <v>-3.1530913625294984e-05</v>
+        <v>-3.1662449154838007e-05</v>
       </c>
       <c r="N8">
-        <v>-2.9843770527605796e-05</v>
+        <v>-3.0174857046363186e-05</v>
       </c>
       <c r="O8">
-        <v>-2.7445511323062559e-06</v>
+        <v>4.6485264551940627e-07</v>
       </c>
       <c r="P8">
-        <v>1.0213125544215012e-05</v>
+        <v>-3.6198479619766149e-06</v>
       </c>
       <c r="Q8">
-        <v>-2.4831665391248349e-06</v>
+        <v>9.588524157327834e-06</v>
       </c>
       <c r="R8">
-        <v>-4.1943860419286646e-06</v>
+        <v>-3.2928121079807206e-06</v>
       </c>
       <c r="S8">
-        <v>2.1397193312234625e-06</v>
+        <v>-5.3611813450368756e-06</v>
       </c>
       <c r="T8">
-        <v>1.9888332058516673e-05</v>
+        <v>2.3227999509938086e-06</v>
       </c>
       <c r="U8">
-        <v>-4.15183881333172e-06</v>
+        <v>2.0916262014331155e-05</v>
       </c>
       <c r="V8">
-        <v>-3.2352132206972869e-06</v>
+        <v>-4.4998299667155084e-06</v>
       </c>
       <c r="W8">
-        <v>0.00024084293525438653</v>
+        <v>-3.1711733516015139e-06</v>
+      </c>
+      <c r="X8">
+        <v>0.00025683962977264595</v>
       </c>
     </row>
     <row r="9">
@@ -4589,70 +4920,73 @@
         <v>31</v>
       </c>
       <c r="B9">
-        <v>-0.0735028052363388</v>
+        <v>-0.094734567322458899</v>
       </c>
       <c r="C9">
-        <v>-4.071762363064737e-05</v>
+        <v>-4.124105739835972e-05</v>
       </c>
       <c r="D9">
-        <v>4.761386104823883e-07</v>
+        <v>4.9003292407097127e-07</v>
       </c>
       <c r="E9">
-        <v>-0.0001109602217266641</v>
+        <v>-0.00011244112206871323</v>
       </c>
       <c r="F9">
-        <v>-0.00016060492989324388</v>
+        <v>-0.00016152811421116844</v>
       </c>
       <c r="G9">
-        <v>2.464918200603723e-06</v>
+        <v>2.5245077790999407e-06</v>
       </c>
       <c r="H9">
-        <v>3.5592394255664058e-06</v>
+        <v>3.5874135053682136e-06</v>
       </c>
       <c r="I9">
-        <v>-0.00010383605532654903</v>
+        <v>-0.00010797535573062196</v>
       </c>
       <c r="J9">
-        <v>0.00036018826458980493</v>
+        <v>0.00037075140226798986</v>
       </c>
       <c r="K9">
-        <v>-2.289510459484894e-06</v>
+        <v>-1.5170424089851566e-06</v>
       </c>
       <c r="L9">
-        <v>-1.1368170324656441e-05</v>
+        <v>-1.2213788448970134e-05</v>
       </c>
       <c r="M9">
-        <v>-2.1049743298634971e-05</v>
+        <v>-2.1557027962234427e-05</v>
       </c>
       <c r="N9">
-        <v>-2.2435771438959328e-05</v>
+        <v>-2.2909691694473339e-05</v>
       </c>
       <c r="O9">
-        <v>-1.4400891528318456e-05</v>
+        <v>-9.0340323639041865e-07</v>
       </c>
       <c r="P9">
-        <v>-1.5014695985072795e-05</v>
+        <v>-1.3659499041693958e-05</v>
       </c>
       <c r="Q9">
-        <v>-1.3441947556693481e-05</v>
+        <v>-1.3638949113739535e-05</v>
       </c>
       <c r="R9">
-        <v>-1.6690232790303464e-05</v>
+        <v>-1.3108669867451985e-05</v>
       </c>
       <c r="S9">
-        <v>-1.847066177338908e-05</v>
+        <v>-1.5234774537956741e-05</v>
       </c>
       <c r="T9">
-        <v>-9.0537301972672647e-06</v>
+        <v>-1.8901241416907401e-05</v>
       </c>
       <c r="U9">
-        <v>-6.302902167343029e-06</v>
+        <v>-1.0283782886562456e-05</v>
       </c>
       <c r="V9">
-        <v>-9.6927214389597718e-06</v>
+        <v>-5.3129934987612689e-06</v>
       </c>
       <c r="W9">
-        <v>0.00075537537556103862</v>
+        <v>-1.0441367853494576e-05</v>
+      </c>
+      <c r="X9">
+        <v>0.00076330714458537835</v>
       </c>
     </row>
     <row r="10">
@@ -4660,70 +4994,73 @@
         <v>32</v>
       </c>
       <c r="B10">
-        <v>0.1881930507100977</v>
+        <v>0.16745258002849084</v>
       </c>
       <c r="C10">
-        <v>4.2256430281573402e-06</v>
+        <v>4.5693619109330559e-06</v>
       </c>
       <c r="D10">
-        <v>-4.7670154323545336e-08</v>
+        <v>-4.563757170066402e-08</v>
       </c>
       <c r="E10">
-        <v>4.282961246756731e-05</v>
+        <v>4.9609504167499245e-05</v>
       </c>
       <c r="F10">
-        <v>3.2666500406564806e-05</v>
+        <v>3.4843511443092634e-05</v>
       </c>
       <c r="G10">
-        <v>-5.7116826918548636e-07</v>
+        <v>-7.1308087136185138e-07</v>
       </c>
       <c r="H10">
-        <v>-8.057193435553014e-07</v>
+        <v>-8.4300967431657132e-07</v>
       </c>
       <c r="I10">
-        <v>-1.397948033387334e-05</v>
+        <v>-1.3750466447516011e-05</v>
       </c>
       <c r="J10">
-        <v>-2.289510459484894e-06</v>
+        <v>-1.5170424089851566e-06</v>
       </c>
       <c r="K10">
-        <v>0.010075357280448175</v>
+        <v>0.010358399884744768</v>
       </c>
       <c r="L10">
-        <v>0.0083244380839020034</v>
+        <v>0.0085614058318536149</v>
       </c>
       <c r="M10">
-        <v>0.0083213928568735482</v>
+        <v>0.0085588143547197636</v>
       </c>
       <c r="N10">
-        <v>0.0083174425108174348</v>
+        <v>0.0085549907987653336</v>
       </c>
       <c r="O10">
-        <v>1.0586429136039377e-05</v>
+        <v>-6.6400314435832658e-07</v>
       </c>
       <c r="P10">
-        <v>3.7034334804804891e-05</v>
+        <v>1.1288792504152666e-05</v>
       </c>
       <c r="Q10">
-        <v>2.5499859968154204e-05</v>
+        <v>4.0160858575013164e-05</v>
       </c>
       <c r="R10">
-        <v>2.9369425247035511e-05</v>
+        <v>2.513688683077674e-05</v>
       </c>
       <c r="S10">
-        <v>2.5490299116642237e-05</v>
+        <v>2.9189649274894314e-05</v>
       </c>
       <c r="T10">
-        <v>6.3528439298659805e-05</v>
+        <v>2.5753731620787007e-05</v>
       </c>
       <c r="U10">
-        <v>-1.0917210013414117e-05</v>
+        <v>6.1717279317217947e-05</v>
       </c>
       <c r="V10">
-        <v>3.1208504634171185e-05</v>
+        <v>-8.9877586480391351e-06</v>
       </c>
       <c r="W10">
-        <v>-0.0084247799088486997</v>
+        <v>3.0173812663316921e-05</v>
+      </c>
+      <c r="X10">
+        <v>-0.0086708572435103808</v>
       </c>
     </row>
     <row r="11">
@@ -4731,70 +5068,73 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>0.42438350477581488</v>
+        <v>0.42743994808180474</v>
       </c>
       <c r="C11">
-        <v>7.5137478233992957e-06</v>
+        <v>7.5695315095912442e-06</v>
       </c>
       <c r="D11">
-        <v>-8.0057769711292844e-08</v>
+        <v>-8.3284597261071689e-08</v>
       </c>
       <c r="E11">
-        <v>4.2493466319664416e-05</v>
+        <v>4.7653686225048939e-05</v>
       </c>
       <c r="F11">
-        <v>-6.9686470291604932e-07</v>
+        <v>-3.879696242586406e-06</v>
       </c>
       <c r="G11">
-        <v>-5.9261344475577458e-07</v>
+        <v>-7.3502425340134914e-07</v>
       </c>
       <c r="H11">
-        <v>1.0543264573085097e-07</v>
+        <v>1.7949919777006485e-07</v>
       </c>
       <c r="I11">
-        <v>-2.1906402007598587e-05</v>
+        <v>-2.1724707888330565e-05</v>
       </c>
       <c r="J11">
-        <v>-1.1368170324656441e-05</v>
+        <v>-1.2213788448970134e-05</v>
       </c>
       <c r="K11">
-        <v>0.0083244380839020034</v>
+        <v>0.0085614058318536149</v>
       </c>
       <c r="L11">
-        <v>0.0086328770475936206</v>
+        <v>0.0088800483517447598</v>
       </c>
       <c r="M11">
-        <v>0.0083287974905321954</v>
+        <v>0.0085663377984272846</v>
       </c>
       <c r="N11">
-        <v>0.0083300520549830764</v>
+        <v>0.0085676715831781505</v>
       </c>
       <c r="O11">
-        <v>-8.3925004862748435e-06</v>
+        <v>3.37895466134475e-07</v>
       </c>
       <c r="P11">
-        <v>1.1635983171439328e-05</v>
+        <v>-1.0354526693404591e-05</v>
       </c>
       <c r="Q11">
-        <v>4.8432088118500886e-06</v>
+        <v>1.1554162831344916e-05</v>
       </c>
       <c r="R11">
-        <v>1.6952945242436227e-05</v>
+        <v>4.2464172748764761e-06</v>
       </c>
       <c r="S11">
-        <v>1.0130206111364534e-06</v>
+        <v>1.5810677489142125e-05</v>
       </c>
       <c r="T11">
-        <v>2.9900476401665128e-05</v>
+        <v>-2.8453082638536971e-07</v>
       </c>
       <c r="U11">
-        <v>-1.5247802569949079e-05</v>
+        <v>2.7780412649380305e-05</v>
       </c>
       <c r="V11">
-        <v>2.8923726321032941e-05</v>
+        <v>-1.3677209213933793e-05</v>
       </c>
       <c r="W11">
-        <v>-0.0084862620601519525</v>
+        <v>2.7498920249309003e-05</v>
+      </c>
+      <c r="X11">
+        <v>-0.0087241382221249913</v>
       </c>
     </row>
     <row r="12">
@@ -4802,70 +5142,73 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0.59213545452888128</v>
+        <v>0.57970380444926661</v>
       </c>
       <c r="C12">
-        <v>1.0421809366738927e-05</v>
+        <v>1.0897020363040167e-05</v>
       </c>
       <c r="D12">
-        <v>-9.5835780141784615e-08</v>
+        <v>-9.8560846821640437e-08</v>
       </c>
       <c r="E12">
-        <v>3.8593958948113477e-05</v>
+        <v>4.6044103403549796e-05</v>
       </c>
       <c r="F12">
-        <v>-1.2017844458756736e-05</v>
+        <v>-1.0720208317576709e-05</v>
       </c>
       <c r="G12">
-        <v>-8.0575090080943078e-08</v>
+        <v>-2.4223498502268031e-07</v>
       </c>
       <c r="H12">
-        <v>1.1016189313236715e-06</v>
+        <v>1.1071027357113411e-06</v>
       </c>
       <c r="I12">
-        <v>-3.1530913625294984e-05</v>
+        <v>-3.1662449154838007e-05</v>
       </c>
       <c r="J12">
-        <v>-2.1049743298634971e-05</v>
+        <v>-2.1557027962234427e-05</v>
       </c>
       <c r="K12">
-        <v>0.0083213928568735482</v>
+        <v>0.0085588143547197636</v>
       </c>
       <c r="L12">
-        <v>0.0083287974905321954</v>
+        <v>0.0085663377984272846</v>
       </c>
       <c r="M12">
-        <v>0.0084389901486324852</v>
+        <v>0.0086794272548995598</v>
       </c>
       <c r="N12">
-        <v>0.0083631005278954496</v>
+        <v>0.0086019373177283892</v>
       </c>
       <c r="O12">
-        <v>-2.0280159142167288e-05</v>
+        <v>-1.7944262356361113e-07</v>
       </c>
       <c r="P12">
-        <v>6.0438681110631606e-06</v>
+        <v>-2.0742083240770883e-05</v>
       </c>
       <c r="Q12">
-        <v>-9.0207803534152328e-06</v>
+        <v>7.0290027431458018e-06</v>
       </c>
       <c r="R12">
-        <v>7.505536415173934e-06</v>
+        <v>-9.4849629800441548e-06</v>
       </c>
       <c r="S12">
-        <v>-7.9589026881772388e-06</v>
+        <v>8.1661887060184113e-06</v>
       </c>
       <c r="T12">
-        <v>3.9688445556501515e-05</v>
+        <v>-8.8151425820543882e-06</v>
       </c>
       <c r="U12">
-        <v>-1.8060678776986776e-05</v>
+        <v>3.8147122726039982e-05</v>
       </c>
       <c r="V12">
-        <v>3.1319981314868425e-05</v>
+        <v>-1.6550733433670255e-05</v>
       </c>
       <c r="W12">
-        <v>-0.0086001536817800328</v>
+        <v>3.0846976166291588e-05</v>
+      </c>
+      <c r="X12">
+        <v>-0.0088504752980831103</v>
       </c>
     </row>
     <row r="13">
@@ -4873,70 +5216,73 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>0.61389342286671667</v>
+        <v>0.59662002093753819</v>
       </c>
       <c r="C13">
-        <v>1.7528688346052032e-05</v>
+        <v>1.8393181137025421e-05</v>
       </c>
       <c r="D13">
-        <v>-1.4524158596248764e-07</v>
+        <v>-1.5008458546326047e-07</v>
       </c>
       <c r="E13">
-        <v>8.1361097263202655e-05</v>
+        <v>9.0691766568169133e-05</v>
       </c>
       <c r="F13">
-        <v>4.7401913242479336e-05</v>
+        <v>5.2792239731769882e-05</v>
       </c>
       <c r="G13">
-        <v>-7.2106363225308409e-07</v>
+        <v>-9.0958006689417377e-07</v>
       </c>
       <c r="H13">
-        <v>2.5431908612260742e-07</v>
+        <v>1.8382703028152141e-07</v>
       </c>
       <c r="I13">
-        <v>-2.9843770527605796e-05</v>
+        <v>-3.0174857046363186e-05</v>
       </c>
       <c r="J13">
-        <v>-2.2435771438959328e-05</v>
+        <v>-2.2909691694473339e-05</v>
       </c>
       <c r="K13">
-        <v>0.0083174425108174348</v>
+        <v>0.0085549907987653336</v>
       </c>
       <c r="L13">
-        <v>0.0083300520549830764</v>
+        <v>0.0085676715831781505</v>
       </c>
       <c r="M13">
-        <v>0.0083631005278954496</v>
+        <v>0.0086019373177283892</v>
       </c>
       <c r="N13">
-        <v>0.0087092708959277138</v>
+        <v>0.0089556587852153494</v>
       </c>
       <c r="O13">
-        <v>-3.6740225446297214e-05</v>
+        <v>-3.4996445730500403e-07</v>
       </c>
       <c r="P13">
-        <v>-1.5325092418868761e-05</v>
+        <v>-3.8245094198770377e-05</v>
       </c>
       <c r="Q13">
-        <v>-1.7321796456453597e-05</v>
+        <v>-1.5860300834626687e-05</v>
       </c>
       <c r="R13">
-        <v>-1.8380531742525957e-05</v>
+        <v>-1.8674065901334538e-05</v>
       </c>
       <c r="S13">
-        <v>-3.1419540571314957e-05</v>
+        <v>-1.8922200395226556e-05</v>
       </c>
       <c r="T13">
-        <v>2.0461576165022261e-05</v>
+        <v>-3.3330603940322538e-05</v>
       </c>
       <c r="U13">
-        <v>-2.4944467072463328e-05</v>
+        <v>1.8429706189860504e-05</v>
       </c>
       <c r="V13">
-        <v>2.7813336893919011e-05</v>
+        <v>-2.359561094517842e-05</v>
       </c>
       <c r="W13">
-        <v>-0.0088210926366561106</v>
+        <v>2.7163490296842481e-05</v>
+      </c>
+      <c r="X13">
+        <v>-0.0090807084669940579</v>
       </c>
     </row>
     <row r="14">
@@ -4944,70 +5290,73 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>0.044665837633688928</v>
+        <v>0.02845074985505127</v>
       </c>
       <c r="C14">
-        <v>2.6908205779039368e-06</v>
+        <v>-7.6452733741350328e-07</v>
       </c>
       <c r="D14">
-        <v>-3.1540914682322173e-08</v>
+        <v>-6.4018967794351553e-10</v>
       </c>
       <c r="E14">
-        <v>2.6625627524506123e-05</v>
+        <v>-4.777910833021885e-06</v>
       </c>
       <c r="F14">
-        <v>2.282328641040083e-05</v>
+        <v>-7.8994016279695514e-06</v>
       </c>
       <c r="G14">
-        <v>-3.1006659675244876e-07</v>
+        <v>9.5474295452152603e-08</v>
       </c>
       <c r="H14">
-        <v>-1.4312763594037549e-07</v>
+        <v>1.7178678606024532e-07</v>
       </c>
       <c r="I14">
-        <v>-2.7445511323062559e-06</v>
+        <v>4.6485264551940627e-07</v>
       </c>
       <c r="J14">
-        <v>-1.4400891528318456e-05</v>
+        <v>-9.0340323639041865e-07</v>
       </c>
       <c r="K14">
-        <v>1.0586429136039377e-05</v>
+        <v>-6.6400314435832658e-07</v>
       </c>
       <c r="L14">
-        <v>-8.3925004862748435e-06</v>
+        <v>3.37895466134475e-07</v>
       </c>
       <c r="M14">
-        <v>-2.0280159142167288e-05</v>
+        <v>-1.7944262356361113e-07</v>
       </c>
       <c r="N14">
-        <v>-3.6740225446297214e-05</v>
+        <v>-3.4996445730500403e-07</v>
       </c>
       <c r="O14">
-        <v>0.00079146276760389857</v>
+        <v>1.010793831368092e-06</v>
       </c>
       <c r="P14">
-        <v>0.00042680234977038626</v>
+        <v>-1.6240640413714188e-06</v>
       </c>
       <c r="Q14">
-        <v>0.00042458049230776024</v>
+        <v>-1.5614459357151735e-06</v>
       </c>
       <c r="R14">
-        <v>0.00042610579003990381</v>
+        <v>-2.3557540245253947e-08</v>
       </c>
       <c r="S14">
-        <v>0.00042503162829690244</v>
+        <v>-2.1305079744585816e-06</v>
       </c>
       <c r="T14">
-        <v>0.00042341226599239105</v>
+        <v>1.9036928906700072e-07</v>
       </c>
       <c r="U14">
-        <v>4.6932215830166055e-06</v>
+        <v>5.725314564470805e-08</v>
       </c>
       <c r="V14">
-        <v>6.4666430914938073e-07</v>
+        <v>-5.1964575137207427e-07</v>
       </c>
       <c r="W14">
-        <v>-0.00045920424133217381</v>
+        <v>8.8957570426173602e-07</v>
+      </c>
+      <c r="X14">
+        <v>1.822164115034984e-05</v>
       </c>
     </row>
     <row r="15">
@@ -5015,70 +5364,73 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>0.075895006123659292</v>
+        <v>-0.00029174326117647624</v>
       </c>
       <c r="C15">
-        <v>3.9634462420549206e-06</v>
+        <v>4.0270904893893519e-06</v>
       </c>
       <c r="D15">
-        <v>-4.8031299484466901e-08</v>
+        <v>-3.1056359549501946e-08</v>
       </c>
       <c r="E15">
-        <v>2.9133457784574754e-05</v>
+        <v>3.6028865475585582e-05</v>
       </c>
       <c r="F15">
-        <v>-1.2405574572347641e-05</v>
+        <v>3.7307573828210386e-05</v>
       </c>
       <c r="G15">
-        <v>-5.0793801075564197e-07</v>
+        <v>-5.0408378862786373e-07</v>
       </c>
       <c r="H15">
-        <v>7.3477227987356569e-07</v>
+        <v>-4.418125395770096e-07</v>
       </c>
       <c r="I15">
-        <v>1.0213125544215012e-05</v>
+        <v>-3.6198479619766149e-06</v>
       </c>
       <c r="J15">
-        <v>-1.5014695985072795e-05</v>
+        <v>-1.3659499041693958e-05</v>
       </c>
       <c r="K15">
-        <v>3.7034334804804891e-05</v>
+        <v>1.1288792504152666e-05</v>
       </c>
       <c r="L15">
-        <v>1.1635983171439328e-05</v>
+        <v>-1.0354526693404591e-05</v>
       </c>
       <c r="M15">
-        <v>6.0438681110631606e-06</v>
+        <v>-2.0742083240770883e-05</v>
       </c>
       <c r="N15">
-        <v>-1.5325092418868761e-05</v>
+        <v>-3.8245094198770377e-05</v>
       </c>
       <c r="O15">
-        <v>0.00042680234977038626</v>
+        <v>-1.6240640413714188e-06</v>
       </c>
       <c r="P15">
-        <v>0.00095209424713423008</v>
+        <v>0.00081280693939837204</v>
       </c>
       <c r="Q15">
-        <v>0.00042457371932190974</v>
+        <v>0.00044060356920449525</v>
       </c>
       <c r="R15">
-        <v>0.00042679469348868638</v>
+        <v>0.00043564850370815663</v>
       </c>
       <c r="S15">
-        <v>0.00042573989361616475</v>
+        <v>0.00044071559552172839</v>
       </c>
       <c r="T15">
-        <v>0.00042550883480385127</v>
+        <v>0.0004358797211928837</v>
       </c>
       <c r="U15">
-        <v>-2.9789803774232463e-06</v>
+        <v>0.00043450751336739351</v>
       </c>
       <c r="V15">
-        <v>-1.0144597258308413e-05</v>
+        <v>6.231779390793283e-06</v>
       </c>
       <c r="W15">
-        <v>-0.00051328285815676581</v>
+        <v>-5.2441006324947914e-07</v>
+      </c>
+      <c r="X15">
+        <v>-0.0005020623626921072</v>
       </c>
     </row>
     <row r="16">
@@ -5086,70 +5438,73 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>-0.078559355519992241</v>
+        <v>0.032273301016892179</v>
       </c>
       <c r="C16">
-        <v>2.4335226986637456e-06</v>
+        <v>5.2385002328871272e-06</v>
       </c>
       <c r="D16">
-        <v>-2.8093261492609513e-08</v>
+        <v>-4.7783714794227333e-08</v>
       </c>
       <c r="E16">
-        <v>1.5636866182581312e-05</v>
+        <v>3.7076509170658546e-05</v>
       </c>
       <c r="F16">
-        <v>-5.6082656110512338e-05</v>
+        <v>-1.8466190281054838e-06</v>
       </c>
       <c r="G16">
-        <v>-3.0768773176249578e-07</v>
+        <v>-6.6355724969193097e-07</v>
       </c>
       <c r="H16">
-        <v>8.6235231722208974e-07</v>
+        <v>5.2423766880419505e-07</v>
       </c>
       <c r="I16">
-        <v>-2.4831665391248349e-06</v>
+        <v>9.588524157327834e-06</v>
       </c>
       <c r="J16">
-        <v>-1.3441947556693481e-05</v>
+        <v>-1.3638949113739535e-05</v>
       </c>
       <c r="K16">
-        <v>2.5499859968154204e-05</v>
+        <v>4.0160858575013164e-05</v>
       </c>
       <c r="L16">
-        <v>4.8432088118500886e-06</v>
+        <v>1.1554162831344916e-05</v>
       </c>
       <c r="M16">
-        <v>-9.0207803534152328e-06</v>
+        <v>7.0290027431458018e-06</v>
       </c>
       <c r="N16">
-        <v>-1.7321796456453597e-05</v>
+        <v>-1.5860300834626687e-05</v>
       </c>
       <c r="O16">
-        <v>0.00042458049230776024</v>
+        <v>-1.5614459357151735e-06</v>
       </c>
       <c r="P16">
-        <v>0.00042457371932190974</v>
+        <v>0.00044060356920449525</v>
       </c>
       <c r="Q16">
-        <v>0.00078689575591916973</v>
+        <v>0.00097813051405798391</v>
       </c>
       <c r="R16">
-        <v>0.00042565890012678722</v>
+        <v>0.00043571936958515723</v>
       </c>
       <c r="S16">
-        <v>0.00042813268871159265</v>
+        <v>0.00044137841014744566</v>
       </c>
       <c r="T16">
-        <v>0.00042484622022401046</v>
+        <v>0.00043673902746514692</v>
       </c>
       <c r="U16">
-        <v>-8.4091661124160725e-06</v>
+        <v>0.00043677209878617779</v>
       </c>
       <c r="V16">
-        <v>-9.598559698960017e-06</v>
+        <v>-1.739368641985539e-06</v>
       </c>
       <c r="W16">
-        <v>-0.00045503111222629575</v>
+        <v>-1.1373143034635979e-05</v>
+      </c>
+      <c r="X16">
+        <v>-0.00055601351719031353</v>
       </c>
     </row>
     <row r="17">
@@ -5157,70 +5512,73 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>0.049808799646905461</v>
+        <v>-0.078140115734602514</v>
       </c>
       <c r="C17">
-        <v>5.3475667911221148e-06</v>
+        <v>2.4231498495329883e-06</v>
       </c>
       <c r="D17">
-        <v>-5.8791859272004374e-08</v>
+        <v>-2.7412828300569529e-08</v>
       </c>
       <c r="E17">
-        <v>1.585609166826472e-05</v>
+        <v>1.7512566867786819e-05</v>
       </c>
       <c r="F17">
-        <v>-2.4882826621797857e-05</v>
+        <v>-5.8318349893103538e-05</v>
       </c>
       <c r="G17">
-        <v>-4.8158960944848539e-07</v>
+        <v>-3.6395007813032639e-07</v>
       </c>
       <c r="H17">
-        <v>5.1579616379850797e-07</v>
+        <v>9.0037822483940582e-07</v>
       </c>
       <c r="I17">
-        <v>-4.1943860419286646e-06</v>
+        <v>-3.2928121079807206e-06</v>
       </c>
       <c r="J17">
-        <v>-1.6690232790303464e-05</v>
+        <v>-1.3108669867451985e-05</v>
       </c>
       <c r="K17">
-        <v>2.9369425247035511e-05</v>
+        <v>2.513688683077674e-05</v>
       </c>
       <c r="L17">
-        <v>1.6952945242436227e-05</v>
+        <v>4.2464172748764761e-06</v>
       </c>
       <c r="M17">
-        <v>7.505536415173934e-06</v>
+        <v>-9.4849629800441548e-06</v>
       </c>
       <c r="N17">
-        <v>-1.8380531742525957e-05</v>
+        <v>-1.8674065901334538e-05</v>
       </c>
       <c r="O17">
-        <v>0.00042610579003990381</v>
+        <v>-2.3557540245253947e-08</v>
       </c>
       <c r="P17">
-        <v>0.00042679469348868638</v>
+        <v>0.00043564850370815663</v>
       </c>
       <c r="Q17">
-        <v>0.00042565890012678722</v>
+        <v>0.00043571936958515723</v>
       </c>
       <c r="R17">
-        <v>0.00065506845019029539</v>
+        <v>0.00080859219556441721</v>
       </c>
       <c r="S17">
-        <v>0.00042807596145240785</v>
+        <v>0.00043681255461449736</v>
       </c>
       <c r="T17">
-        <v>0.00042595954371383237</v>
+        <v>0.00043927154805569591</v>
       </c>
       <c r="U17">
-        <v>1.4332402949034842e-05</v>
+        <v>0.00043597054763617012</v>
       </c>
       <c r="V17">
-        <v>1.5137607980180931e-05</v>
+        <v>-7.7540820766363867e-06</v>
       </c>
       <c r="W17">
-        <v>-0.00053613896188978421</v>
+        <v>-1.0273733658990947e-05</v>
+      </c>
+      <c r="X17">
+        <v>-0.00046538761201951633</v>
       </c>
     </row>
     <row r="18">
@@ -5228,70 +5586,73 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>-0.16290734733350259</v>
+        <v>-0.0095355171442726878</v>
       </c>
       <c r="C18">
-        <v>3.7934002192214932e-06</v>
+        <v>7.1597743536237204e-06</v>
       </c>
       <c r="D18">
-        <v>-4.0427055481624849e-08</v>
+        <v>-5.8653693398855124e-08</v>
       </c>
       <c r="E18">
-        <v>-1.1666304287785337e-05</v>
+        <v>2.8008398524890667e-05</v>
       </c>
       <c r="F18">
-        <v>-9.7056687944450552e-05</v>
+        <v>-6.8496055620500233e-06</v>
       </c>
       <c r="G18">
-        <v>1.8668074382521674e-07</v>
+        <v>-7.5163584171551396e-07</v>
       </c>
       <c r="H18">
-        <v>1.546394438380446e-06</v>
+        <v>1.2054172668947265e-07</v>
       </c>
       <c r="I18">
-        <v>2.1397193312234625e-06</v>
+        <v>-5.3611813450368756e-06</v>
       </c>
       <c r="J18">
-        <v>-1.847066177338908e-05</v>
+        <v>-1.5234774537956741e-05</v>
       </c>
       <c r="K18">
-        <v>2.5490299116642237e-05</v>
+        <v>2.9189649274894314e-05</v>
       </c>
       <c r="L18">
-        <v>1.0130206111364534e-06</v>
+        <v>1.5810677489142125e-05</v>
       </c>
       <c r="M18">
-        <v>-7.9589026881772388e-06</v>
+        <v>8.1661887060184113e-06</v>
       </c>
       <c r="N18">
-        <v>-3.1419540571314957e-05</v>
+        <v>-1.8922200395226556e-05</v>
       </c>
       <c r="O18">
-        <v>0.00042503162829690244</v>
+        <v>-2.1305079744585816e-06</v>
       </c>
       <c r="P18">
-        <v>0.00042573989361616475</v>
+        <v>0.00044071559552172839</v>
       </c>
       <c r="Q18">
-        <v>0.00042813268871159265</v>
+        <v>0.00044137841014744566</v>
       </c>
       <c r="R18">
-        <v>0.00042807596145240785</v>
+        <v>0.00043681255461449736</v>
       </c>
       <c r="S18">
-        <v>0.00074008553137856639</v>
+        <v>0.00067622448584042866</v>
       </c>
       <c r="T18">
-        <v>0.00042826219681928011</v>
+        <v>0.00043892440441431821</v>
       </c>
       <c r="U18">
-        <v>1.1174810937961752e-06</v>
+        <v>0.00043715827440039384</v>
       </c>
       <c r="V18">
-        <v>-1.6261100121297391e-06</v>
+        <v>1.5964051997207482e-05</v>
       </c>
       <c r="W18">
-        <v>-0.00048725010414383017</v>
+        <v>1.3496453551422755e-05</v>
+      </c>
+      <c r="X18">
+        <v>-0.00059137373213027792</v>
       </c>
     </row>
     <row r="19">
@@ -5299,70 +5660,73 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>-0.13485782272844796</v>
+        <v>-0.15570944099021733</v>
       </c>
       <c r="C19">
-        <v>-6.4655709140265847e-08</v>
+        <v>3.6638367474764933e-06</v>
       </c>
       <c r="D19">
-        <v>3.7341562483775182e-09</v>
+        <v>-4.0511729934063368e-08</v>
       </c>
       <c r="E19">
-        <v>-2.5758658654818884e-07</v>
+        <v>-1.2010776328894211e-05</v>
       </c>
       <c r="F19">
-        <v>-6.0964852193156274e-05</v>
+        <v>-0.00010041792123738913</v>
       </c>
       <c r="G19">
-        <v>-1.8504666670830908e-07</v>
+        <v>1.7685463645761033e-07</v>
       </c>
       <c r="H19">
-        <v>1.0627879244639522e-06</v>
+        <v>1.6070718999630367e-06</v>
       </c>
       <c r="I19">
-        <v>1.9888332058516673e-05</v>
+        <v>2.3227999509938086e-06</v>
       </c>
       <c r="J19">
-        <v>-9.0537301972672647e-06</v>
+        <v>-1.8901241416907401e-05</v>
       </c>
       <c r="K19">
-        <v>6.3528439298659805e-05</v>
+        <v>2.5753731620787007e-05</v>
       </c>
       <c r="L19">
-        <v>2.9900476401665128e-05</v>
+        <v>-2.8453082638536971e-07</v>
       </c>
       <c r="M19">
-        <v>3.9688445556501515e-05</v>
+        <v>-8.8151425820543882e-06</v>
       </c>
       <c r="N19">
-        <v>2.0461576165022261e-05</v>
+        <v>-3.3330603940322538e-05</v>
       </c>
       <c r="O19">
-        <v>0.00042341226599239105</v>
+        <v>1.9036928906700072e-07</v>
       </c>
       <c r="P19">
-        <v>0.00042550883480385127</v>
+        <v>0.0004358797211928837</v>
       </c>
       <c r="Q19">
-        <v>0.00042484622022401046</v>
+        <v>0.00043673902746514692</v>
       </c>
       <c r="R19">
-        <v>0.00042595954371383237</v>
+        <v>0.00043927154805569591</v>
       </c>
       <c r="S19">
-        <v>0.00042826219681928011</v>
+        <v>0.00043892440441431821</v>
       </c>
       <c r="T19">
-        <v>0.0018722965194935702</v>
+        <v>0.00075892682840928447</v>
       </c>
       <c r="U19">
-        <v>9.2373642362989621e-06</v>
+        <v>0.00043954283881575618</v>
       </c>
       <c r="V19">
-        <v>1.0271877166896574e-05</v>
+        <v>1.1906015455197556e-06</v>
       </c>
       <c r="W19">
-        <v>-0.00047109444147433671</v>
+        <v>-1.4479266280247573e-06</v>
+      </c>
+      <c r="X19">
+        <v>-0.00049425418124317754</v>
       </c>
     </row>
     <row r="20">
@@ -5370,70 +5734,73 @@
         <v>42</v>
       </c>
       <c r="B20">
-        <v>-0.15171461846593687</v>
+        <v>-0.13128335853686229</v>
       </c>
       <c r="C20">
-        <v>8.069340261440761e-07</v>
+        <v>-9.0969752831655091e-08</v>
       </c>
       <c r="D20">
-        <v>-1.2321991127483736e-08</v>
+        <v>3.8287290382989888e-09</v>
       </c>
       <c r="E20">
-        <v>1.5059445286503816e-05</v>
+        <v>2.4554238971554915e-06</v>
       </c>
       <c r="F20">
-        <v>3.1849958787050858e-05</v>
+        <v>-6.3679342426135744e-05</v>
       </c>
       <c r="G20">
-        <v>-1.5407544467246968e-07</v>
+        <v>-2.7606086389061068e-07</v>
       </c>
       <c r="H20">
-        <v>-4.5695583106736617e-07</v>
+        <v>1.1155619207790292e-06</v>
       </c>
       <c r="I20">
-        <v>-4.15183881333172e-06</v>
+        <v>2.0916262014331155e-05</v>
       </c>
       <c r="J20">
-        <v>-6.302902167343029e-06</v>
+        <v>-1.0283782886562456e-05</v>
       </c>
       <c r="K20">
-        <v>-1.0917210013414117e-05</v>
+        <v>6.1717279317217947e-05</v>
       </c>
       <c r="L20">
-        <v>-1.5247802569949079e-05</v>
+        <v>2.7780412649380305e-05</v>
       </c>
       <c r="M20">
-        <v>-1.8060678776986776e-05</v>
+        <v>3.8147122726039982e-05</v>
       </c>
       <c r="N20">
-        <v>-2.4944467072463328e-05</v>
+        <v>1.8429706189860504e-05</v>
       </c>
       <c r="O20">
-        <v>4.6932215830166055e-06</v>
+        <v>5.725314564470805e-08</v>
       </c>
       <c r="P20">
-        <v>-2.9789803774232463e-06</v>
+        <v>0.00043450751336739351</v>
       </c>
       <c r="Q20">
-        <v>-8.4091661124160725e-06</v>
+        <v>0.00043677209878617779</v>
       </c>
       <c r="R20">
-        <v>1.4332402949034842e-05</v>
+        <v>0.00043597054763617012</v>
       </c>
       <c r="S20">
-        <v>1.1174810937961752e-06</v>
+        <v>0.00043715827440039384</v>
       </c>
       <c r="T20">
-        <v>9.2373642362989621e-06</v>
+        <v>0.00043954283881575618</v>
       </c>
       <c r="U20">
-        <v>0.00091580665741412359</v>
+        <v>0.0019217064416665449</v>
       </c>
       <c r="V20">
-        <v>6.5177998576722629e-05</v>
+        <v>1.0190216712634756e-05</v>
       </c>
       <c r="W20">
-        <v>-5.700716726785389e-05</v>
+        <v>1.0380690552382738e-05</v>
+      </c>
+      <c r="X20">
+        <v>-0.0004804214894326637</v>
       </c>
     </row>
     <row r="21">
@@ -5441,70 +5808,73 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>0.026647917846439117</v>
+        <v>-0.16377483569915527</v>
       </c>
       <c r="C21">
-        <v>-1.1644310149497e-06</v>
+        <v>1.0431852262641661e-06</v>
       </c>
       <c r="D21">
-        <v>1.0237557915597247e-08</v>
+        <v>-1.0027361254123305e-08</v>
       </c>
       <c r="E21">
-        <v>2.7777225986964383e-05</v>
+        <v>1.8988390956102695e-05</v>
       </c>
       <c r="F21">
-        <v>4.4330517297866446e-05</v>
+        <v>3.7566140918254881e-05</v>
       </c>
       <c r="G21">
-        <v>-4.4440045106206145e-07</v>
+        <v>-2.288879098296942e-07</v>
       </c>
       <c r="H21">
-        <v>-4.835835820950629e-07</v>
+        <v>-5.751167326012992e-07</v>
       </c>
       <c r="I21">
-        <v>-3.2352132206972869e-06</v>
+        <v>-4.4998299667155084e-06</v>
       </c>
       <c r="J21">
-        <v>-9.6927214389597718e-06</v>
+        <v>-5.3129934987612689e-06</v>
       </c>
       <c r="K21">
-        <v>3.1208504634171185e-05</v>
+        <v>-8.9877586480391351e-06</v>
       </c>
       <c r="L21">
-        <v>2.8923726321032941e-05</v>
+        <v>-1.3677209213933793e-05</v>
       </c>
       <c r="M21">
-        <v>3.1319981314868425e-05</v>
+        <v>-1.6550733433670255e-05</v>
       </c>
       <c r="N21">
-        <v>2.7813336893919011e-05</v>
+        <v>-2.359561094517842e-05</v>
       </c>
       <c r="O21">
-        <v>6.4666430914938073e-07</v>
+        <v>-5.1964575137207427e-07</v>
       </c>
       <c r="P21">
-        <v>-1.0144597258308413e-05</v>
+        <v>6.231779390793283e-06</v>
       </c>
       <c r="Q21">
-        <v>-9.598559698960017e-06</v>
+        <v>-1.739368641985539e-06</v>
       </c>
       <c r="R21">
-        <v>1.5137607980180931e-05</v>
+        <v>-7.7540820766363867e-06</v>
       </c>
       <c r="S21">
-        <v>-1.6261100121297391e-06</v>
+        <v>1.5964051997207482e-05</v>
       </c>
       <c r="T21">
-        <v>1.0271877166896574e-05</v>
+        <v>1.1906015455197556e-06</v>
       </c>
       <c r="U21">
-        <v>6.5177998576722629e-05</v>
+        <v>1.0190216712634756e-05</v>
       </c>
       <c r="V21">
-        <v>0.0010872144939252815</v>
+        <v>0.00093534150176057527</v>
       </c>
       <c r="W21">
-        <v>-6.6831518294657922e-05</v>
+        <v>6.6317774885734363e-05</v>
+      </c>
+      <c r="X21">
+        <v>-6.7307728094297633e-05</v>
       </c>
     </row>
     <row r="22">
@@ -5512,70 +5882,147 @@
         <v>44</v>
       </c>
       <c r="B22">
-        <v>-2.9594044678246787</v>
+        <v>0.050218066518898319</v>
       </c>
       <c r="C22">
-        <v>-0.00060316515687003835</v>
+        <v>-1.6902010121146817e-06</v>
       </c>
       <c r="D22">
-        <v>6.2857373250009652e-06</v>
+        <v>8.1476041608400728e-09</v>
       </c>
       <c r="E22">
-        <v>-0.0024038095953505842</v>
+        <v>2.6589158637947094e-05</v>
       </c>
       <c r="F22">
-        <v>-0.001770431700220244</v>
+        <v>3.9743411659292438e-05</v>
       </c>
       <c r="G22">
-        <v>4.8533752831501739e-05</v>
+        <v>-4.2729415525341722e-07</v>
       </c>
       <c r="H22">
-        <v>3.4140276008591438e-05</v>
+        <v>-3.8535023871791083e-07</v>
       </c>
       <c r="I22">
-        <v>0.00024084293525438653</v>
+        <v>-3.1711733516015139e-06</v>
       </c>
       <c r="J22">
-        <v>0.00075537537556103862</v>
+        <v>-1.0441367853494576e-05</v>
       </c>
       <c r="K22">
-        <v>-0.0084247799088486997</v>
+        <v>3.0173812663316921e-05</v>
       </c>
       <c r="L22">
-        <v>-0.0084862620601519525</v>
+        <v>2.7498920249309003e-05</v>
       </c>
       <c r="M22">
-        <v>-0.0086001536817800328</v>
+        <v>3.0846976166291588e-05</v>
       </c>
       <c r="N22">
-        <v>-0.0088210926366561106</v>
+        <v>2.7163490296842481e-05</v>
       </c>
       <c r="O22">
-        <v>-0.00045920424133217381</v>
+        <v>8.8957570426173602e-07</v>
       </c>
       <c r="P22">
-        <v>-0.00051328285815676581</v>
+        <v>-5.2441006324947914e-07</v>
       </c>
       <c r="Q22">
-        <v>-0.00045503111222629575</v>
+        <v>-1.1373143034635979e-05</v>
       </c>
       <c r="R22">
-        <v>-0.00053613896188978421</v>
+        <v>-1.0273733658990947e-05</v>
       </c>
       <c r="S22">
-        <v>-0.00048725010414383017</v>
+        <v>1.3496453551422755e-05</v>
       </c>
       <c r="T22">
-        <v>-0.00047109444147433671</v>
+        <v>-1.4479266280247573e-06</v>
       </c>
       <c r="U22">
-        <v>-5.700716726785389e-05</v>
+        <v>1.0380690552382738e-05</v>
       </c>
       <c r="V22">
-        <v>-6.6831518294657922e-05</v>
+        <v>6.6317774885734363e-05</v>
       </c>
       <c r="W22">
-        <v>0.022221889399607741</v>
+        <v>0.0011160643502899775</v>
+      </c>
+      <c r="X22">
+        <v>-5.4834422646766676e-05</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23">
+        <v>-2.3947000471944588</v>
+      </c>
+      <c r="C23">
+        <v>-0.0006304128855597462</v>
+      </c>
+      <c r="D23">
+        <v>6.4155037467783289e-06</v>
+      </c>
+      <c r="E23">
+        <v>-0.002568229213450051</v>
+      </c>
+      <c r="F23">
+        <v>-0.0019846097145459971</v>
+      </c>
+      <c r="G23">
+        <v>5.186261211770031e-05</v>
+      </c>
+      <c r="H23">
+        <v>3.8548946879646743e-05</v>
+      </c>
+      <c r="I23">
+        <v>0.00025683962977264595</v>
+      </c>
+      <c r="J23">
+        <v>0.00076330714458537835</v>
+      </c>
+      <c r="K23">
+        <v>-0.0086708572435103808</v>
+      </c>
+      <c r="L23">
+        <v>-0.0087241382221249913</v>
+      </c>
+      <c r="M23">
+        <v>-0.0088504752980831103</v>
+      </c>
+      <c r="N23">
+        <v>-0.0090807084669940579</v>
+      </c>
+      <c r="O23">
+        <v>1.822164115034984e-05</v>
+      </c>
+      <c r="P23">
+        <v>-0.0005020623626921072</v>
+      </c>
+      <c r="Q23">
+        <v>-0.00055601351719031353</v>
+      </c>
+      <c r="R23">
+        <v>-0.00046538761201951633</v>
+      </c>
+      <c r="S23">
+        <v>-0.00059137373213027792</v>
+      </c>
+      <c r="T23">
+        <v>-0.00049425418124317754</v>
+      </c>
+      <c r="U23">
+        <v>-0.0004804214894326637</v>
+      </c>
+      <c r="V23">
+        <v>-6.7307728094297633e-05</v>
+      </c>
+      <c r="W23">
+        <v>-5.4834422646766676e-05</v>
+      </c>
+      <c r="X23">
+        <v>0.023093179105551278</v>
       </c>
     </row>
   </sheetData>
@@ -5584,7 +6031,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5592,7 +6039,7 @@
         <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
         <v>24</v>
@@ -5656,6 +6103,9 @@
       </c>
       <c r="W1" t="s">
         <v>44</v>
+      </c>
+      <c r="X1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="2">
@@ -5663,70 +6113,73 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>0.17441957349718201</v>
+        <v>0.15307227566462778</v>
       </c>
       <c r="C2">
-        <v>2.3653216336438962e-05</v>
+        <v>2.4600173435376448e-05</v>
       </c>
       <c r="D2">
-        <v>-2.4820806753585671e-07</v>
+        <v>-2.4781471538406612e-07</v>
       </c>
       <c r="E2">
-        <v>8.6408013488834266e-05</v>
+        <v>8.9992337032211291e-05</v>
       </c>
       <c r="F2">
-        <v>6.7457607841798042e-05</v>
+        <v>7.1774710709165504e-05</v>
       </c>
       <c r="G2">
-        <v>-1.8434634246555212e-06</v>
+        <v>-1.871441353054108e-06</v>
       </c>
       <c r="H2">
-        <v>-1.4081335535266328e-06</v>
+        <v>-1.4156907478443695e-06</v>
       </c>
       <c r="I2">
-        <v>-7.8965533249664074e-06</v>
+        <v>-6.1135437101854472e-06</v>
       </c>
       <c r="J2">
-        <v>-3.3217205403445613e-05</v>
+        <v>-3.3698552340810027e-05</v>
       </c>
       <c r="K2">
-        <v>3.8201189270419618e-06</v>
+        <v>3.1307998966519318e-06</v>
       </c>
       <c r="L2">
-        <v>4.1563256104613694e-06</v>
+        <v>3.1761806143800039e-06</v>
       </c>
       <c r="M2">
-        <v>5.428423587112085e-06</v>
+        <v>4.8535961069677992e-06</v>
       </c>
       <c r="N2">
-        <v>1.4927718324272082e-05</v>
+        <v>1.4547170666140625e-05</v>
       </c>
       <c r="O2">
-        <v>1.4887441034216219e-06</v>
+        <v>-1.0601821740640126e-06</v>
       </c>
       <c r="P2">
-        <v>2.03229226350316e-06</v>
+        <v>2.5212991322689632e-06</v>
       </c>
       <c r="Q2">
-        <v>1.8156373648022923e-06</v>
+        <v>2.9277803947183983e-06</v>
       </c>
       <c r="R2">
-        <v>3.0239619789284084e-06</v>
+        <v>2.5708226695140533e-06</v>
       </c>
       <c r="S2">
-        <v>1.8997586306835277e-06</v>
+        <v>4.1040298432993168e-06</v>
       </c>
       <c r="T2">
-        <v>-4.8436909280624247e-07</v>
+        <v>1.7654201243843757e-06</v>
       </c>
       <c r="U2">
-        <v>1.3015700873776471e-06</v>
+        <v>-6.9598869265954627e-07</v>
       </c>
       <c r="V2">
-        <v>-2.9098187938785718e-06</v>
+        <v>1.4750777456203317e-06</v>
       </c>
       <c r="W2">
-        <v>-0.00051792998311778128</v>
+        <v>-4.2284302571463537e-06</v>
+      </c>
+      <c r="X2">
+        <v>-0.00054057944944402108</v>
       </c>
     </row>
     <row r="3">
@@ -5734,70 +6187,73 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>-0.0019832320296936652</v>
+        <v>-0.0020684361624454225</v>
       </c>
       <c r="C3">
-        <v>-2.4820806753585671e-07</v>
+        <v>-2.4781471538406612e-07</v>
       </c>
       <c r="D3">
-        <v>2.7414406097762328e-09</v>
+        <v>2.7900932109124119e-09</v>
       </c>
       <c r="E3">
-        <v>-4.3350434623869452e-07</v>
+        <v>-4.3172855894701129e-07</v>
       </c>
       <c r="F3">
-        <v>-2.2204538131267579e-07</v>
+        <v>-2.2278380195257146e-07</v>
       </c>
       <c r="G3">
-        <v>9.0230980078174794e-09</v>
+        <v>9.1920947646383474e-09</v>
       </c>
       <c r="H3">
-        <v>4.2372438593813441e-09</v>
+        <v>4.6465668552564386e-09</v>
       </c>
       <c r="I3">
-        <v>1.5068014277023063e-08</v>
+        <v>2.9268242745414059e-08</v>
       </c>
       <c r="J3">
-        <v>4.0099550812207758e-07</v>
+        <v>4.0354054516428494e-07</v>
       </c>
       <c r="K3">
-        <v>-4.2365052368979701e-08</v>
+        <v>-4.6719037907298532e-08</v>
       </c>
       <c r="L3">
-        <v>-4.195761738377673e-08</v>
+        <v>-4.8674358127368984e-08</v>
       </c>
       <c r="M3">
-        <v>-3.8362252831692966e-08</v>
+        <v>-4.4411982544474474e-08</v>
       </c>
       <c r="N3">
-        <v>-1.1081216818507283e-07</v>
+        <v>-1.1821271655358617e-07</v>
       </c>
       <c r="O3">
-        <v>-1.1111336493412349e-08</v>
+        <v>-5.6540585542554466e-09</v>
       </c>
       <c r="P3">
-        <v>-1.9224342983125847e-08</v>
+        <v>-6.3232184559323251e-09</v>
       </c>
       <c r="Q3">
-        <v>-1.5591255410859481e-08</v>
+        <v>-1.6289870595530218e-08</v>
       </c>
       <c r="R3">
-        <v>-2.8460373058014049e-08</v>
+        <v>-1.2447768351795096e-08</v>
       </c>
       <c r="S3">
-        <v>-1.7667353608075601e-08</v>
+        <v>-2.3521204232151073e-08</v>
       </c>
       <c r="T3">
-        <v>6.6560095154321312e-09</v>
+        <v>-1.7771499173437399e-08</v>
       </c>
       <c r="U3">
-        <v>-1.3691669125166148e-08</v>
+        <v>4.7458599336776544e-09</v>
       </c>
       <c r="V3">
-        <v>2.5378159441799093e-08</v>
+        <v>-1.2792534026133469e-08</v>
       </c>
       <c r="W3">
-        <v>5.1289228655816393e-06</v>
+        <v>2.0378803995301816e-08</v>
+      </c>
+      <c r="X3">
+        <v>5.1140111431976424e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5805,70 +6261,73 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>-0.22275121640299903</v>
+        <v>-0.29227788920247844</v>
       </c>
       <c r="C4">
-        <v>8.6408013488834266e-05</v>
+        <v>8.9992337032211291e-05</v>
       </c>
       <c r="D4">
-        <v>-4.3350434623869452e-07</v>
+        <v>-4.3172855894701129e-07</v>
       </c>
       <c r="E4">
-        <v>0.0052646824506722718</v>
+        <v>0.0053179465406590354</v>
       </c>
       <c r="F4">
-        <v>0.0023679355620368756</v>
+        <v>0.0023980839588208049</v>
       </c>
       <c r="G4">
-        <v>-0.00010790667223245455</v>
+        <v>-0.00010886462498312239</v>
       </c>
       <c r="H4">
-        <v>-4.8290508043234794e-05</v>
+        <v>-4.8632555366926551e-05</v>
       </c>
       <c r="I4">
-        <v>1.6549984870608197e-05</v>
+        <v>2.5371374610768961e-05</v>
       </c>
       <c r="J4">
-        <v>-7.6911246156981567e-05</v>
+        <v>-7.983041056551713e-05</v>
       </c>
       <c r="K4">
-        <v>1.8594887747565162e-05</v>
+        <v>1.5050183932374716e-05</v>
       </c>
       <c r="L4">
-        <v>2.5256702000577653e-05</v>
+        <v>2.1452726595416142e-05</v>
       </c>
       <c r="M4">
-        <v>1.7312353319764518e-05</v>
+        <v>1.4009842321260424e-05</v>
       </c>
       <c r="N4">
-        <v>3.4169145854522813e-05</v>
+        <v>3.1519949870845859e-05</v>
       </c>
       <c r="O4">
-        <v>4.5850450757501972e-05</v>
+        <v>-3.7474247265342233e-06</v>
       </c>
       <c r="P4">
-        <v>2.2205987656579847e-05</v>
+        <v>5.0393339931903613e-05</v>
       </c>
       <c r="Q4">
-        <v>2.9608143243960488e-05</v>
+        <v>2.585748535985696e-05</v>
       </c>
       <c r="R4">
-        <v>3.3770902387213425e-05</v>
+        <v>3.3209817615330942e-05</v>
       </c>
       <c r="S4">
-        <v>2.8341807186208341e-06</v>
+        <v>3.7488734382354297e-05</v>
       </c>
       <c r="T4">
-        <v>-2.0422293928908707e-05</v>
+        <v>3.9979604830924566e-06</v>
       </c>
       <c r="U4">
-        <v>1.1432320977549063e-05</v>
+        <v>-2.2278152181945843e-05</v>
       </c>
       <c r="V4">
-        <v>1.8320606347170743e-05</v>
+        <v>1.1537406637497247e-05</v>
       </c>
       <c r="W4">
-        <v>-0.0031633818660566052</v>
+        <v>1.5238091444653381e-05</v>
+      </c>
+      <c r="X4">
+        <v>-0.003256949224582978</v>
       </c>
     </row>
     <row r="5">
@@ -5876,70 +6335,73 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>-0.36570833073382869</v>
+        <v>-0.44667168852768968</v>
       </c>
       <c r="C5">
-        <v>6.7457607841798042e-05</v>
+        <v>7.1774710709165504e-05</v>
       </c>
       <c r="D5">
-        <v>-2.2204538131267579e-07</v>
+        <v>-2.2278380195257146e-07</v>
       </c>
       <c r="E5">
-        <v>0.0023679355620368756</v>
+        <v>0.0023980839588208049</v>
       </c>
       <c r="F5">
-        <v>0.0042295931833614946</v>
+        <v>0.0042856563467501005</v>
       </c>
       <c r="G5">
-        <v>-4.8367082182713379e-05</v>
+        <v>-4.8810558780926032e-05</v>
       </c>
       <c r="H5">
-        <v>-8.5075806256518696e-05</v>
+        <v>-8.5884981272916946e-05</v>
       </c>
       <c r="I5">
-        <v>2.3534372520484107e-05</v>
+        <v>3.3146869394592279e-05</v>
       </c>
       <c r="J5">
-        <v>-0.00010982638060223331</v>
+        <v>-0.00011427405461822478</v>
       </c>
       <c r="K5">
-        <v>1.6641639592278627e-05</v>
+        <v>1.3448546992121408e-05</v>
       </c>
       <c r="L5">
-        <v>-1.7576749405986535e-06</v>
+        <v>-6.4375243549750008e-06</v>
       </c>
       <c r="M5">
-        <v>-1.6906245438257951e-05</v>
+        <v>-2.0011563104284456e-05</v>
       </c>
       <c r="N5">
-        <v>3.1769177679788485e-05</v>
+        <v>2.9416041601911577e-05</v>
       </c>
       <c r="O5">
-        <v>5.2600385190004992e-05</v>
+        <v>-4.3051586548841169e-06</v>
       </c>
       <c r="P5">
-        <v>3.2622738381269241e-05</v>
+        <v>5.7884949724156648e-05</v>
       </c>
       <c r="Q5">
-        <v>-1.070565831753603e-05</v>
+        <v>3.6984453170407447e-05</v>
       </c>
       <c r="R5">
-        <v>9.2690361454529931e-06</v>
+        <v>-8.2963687293079272e-06</v>
       </c>
       <c r="S5">
-        <v>-4.8950482656448721e-05</v>
+        <v>1.2869893110453501e-05</v>
       </c>
       <c r="T5">
-        <v>-3.0773233842658323e-05</v>
+        <v>-4.97772626877715e-05</v>
       </c>
       <c r="U5">
-        <v>3.3713068571135743e-05</v>
+        <v>-3.2443761640259041e-05</v>
       </c>
       <c r="V5">
-        <v>1.8525096321798343e-05</v>
+        <v>3.4063932884740325e-05</v>
       </c>
       <c r="W5">
-        <v>-0.0027218393645978807</v>
+        <v>1.3104743402725966e-05</v>
+      </c>
+      <c r="X5">
+        <v>-0.0028312914769374506</v>
       </c>
     </row>
     <row r="6">
@@ -5947,70 +6409,73 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>0.0024959611437965915</v>
+        <v>0.0025952954044890127</v>
       </c>
       <c r="C6">
-        <v>-1.8434634246555212e-06</v>
+        <v>-1.871441353054108e-06</v>
       </c>
       <c r="D6">
-        <v>9.0230980078174794e-09</v>
+        <v>9.1920947646383474e-09</v>
       </c>
       <c r="E6">
-        <v>-0.00010790667223245455</v>
+        <v>-0.00010886462498312239</v>
       </c>
       <c r="F6">
-        <v>-4.8367082182713379e-05</v>
+        <v>-4.8810558780926032e-05</v>
       </c>
       <c r="G6">
-        <v>2.3784752538931853e-06</v>
+        <v>2.4009855988592328e-06</v>
       </c>
       <c r="H6">
-        <v>1.0573045182685934e-06</v>
+        <v>1.0669834287196533e-06</v>
       </c>
       <c r="I6">
-        <v>-5.2512357571415426e-07</v>
+        <v>-5.6391993540621097e-07</v>
       </c>
       <c r="J6">
-        <v>1.807452026875073e-06</v>
+        <v>1.8647984304583498e-06</v>
       </c>
       <c r="K6">
-        <v>-5.610257151061379e-07</v>
+        <v>-5.26780616384529e-07</v>
       </c>
       <c r="L6">
-        <v>-6.8888894900172109e-07</v>
+        <v>-6.7144642183569349e-07</v>
       </c>
       <c r="M6">
-        <v>-2.3530083083896913e-07</v>
+        <v>-1.892610328936453e-07</v>
       </c>
       <c r="N6">
-        <v>-4.3244651287649999e-07</v>
+        <v>-3.8311041961155057e-07</v>
       </c>
       <c r="O6">
-        <v>-9.0399812006259743e-07</v>
+        <v>4.4936900405905211e-09</v>
       </c>
       <c r="P6">
-        <v>-2.2536731230999098e-07</v>
+        <v>-9.238541681639709e-07</v>
       </c>
       <c r="Q6">
-        <v>-7.5139241710276621e-07</v>
+        <v>-2.4613997489067761e-07</v>
       </c>
       <c r="R6">
-        <v>-7.7944983956979658e-07</v>
+        <v>-7.7264199007269203e-07</v>
       </c>
       <c r="S6">
-        <v>-1.8987809407692353e-07</v>
+        <v>-7.9947434440482916e-07</v>
       </c>
       <c r="T6">
-        <v>3.4386245143992356e-07</v>
+        <v>-2.302490913074499e-07</v>
       </c>
       <c r="U6">
-        <v>-2.7005505003890763e-07</v>
+        <v>3.5712546343391346e-07</v>
       </c>
       <c r="V6">
-        <v>-3.0177493836406789e-07</v>
+        <v>-2.680109354773859e-07</v>
       </c>
       <c r="W6">
-        <v>6.4616123727413073e-05</v>
+        <v>-3.3728226015020431e-07</v>
+      </c>
+      <c r="X6">
+        <v>6.5385808151112082e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6018,70 +6483,73 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>0.0017946439855713201</v>
+        <v>0.0010832796149259582</v>
       </c>
       <c r="C7">
-        <v>-1.4081335535266328e-06</v>
+        <v>-1.4156907478443695e-06</v>
       </c>
       <c r="D7">
-        <v>4.2372438593813441e-09</v>
+        <v>4.6465668552564386e-09</v>
       </c>
       <c r="E7">
-        <v>-4.8290508043234794e-05</v>
+        <v>-4.8632555366926551e-05</v>
       </c>
       <c r="F7">
-        <v>-8.5075806256518696e-05</v>
+        <v>-8.5884981272916946e-05</v>
       </c>
       <c r="G7">
-        <v>1.0573045182685934e-06</v>
+        <v>1.0669834287196533e-06</v>
       </c>
       <c r="H7">
-        <v>1.8350158717330006e-06</v>
+        <v>1.8563063968662699e-06</v>
       </c>
       <c r="I7">
-        <v>-8.2461717323305428e-07</v>
+        <v>-7.5908072670335989e-07</v>
       </c>
       <c r="J7">
-        <v>2.4958049621340877e-06</v>
+        <v>2.5725252845665725e-06</v>
       </c>
       <c r="K7">
-        <v>-2.804823844159378e-07</v>
+        <v>-3.0907264097319596e-07</v>
       </c>
       <c r="L7">
-        <v>2.5176871281655064e-07</v>
+        <v>2.1181571420212945e-07</v>
       </c>
       <c r="M7">
-        <v>1.1183227139817159e-06</v>
+        <v>1.1008501551402014e-06</v>
       </c>
       <c r="N7">
-        <v>4.5813655212707986e-07</v>
+        <v>4.395918365954519e-07</v>
       </c>
       <c r="O7">
-        <v>-8.1067390634716506e-07</v>
+        <v>-4.2829192514480309e-08</v>
       </c>
       <c r="P7">
-        <v>-6.502496964190471e-08</v>
+        <v>-7.9928630442462957e-07</v>
       </c>
       <c r="Q7">
-        <v>-3.376908544652675e-07</v>
+        <v>-6.8978836658499704e-08</v>
       </c>
       <c r="R7">
-        <v>-1.4331432780875421e-07</v>
+        <v>-3.0358753615579227e-07</v>
       </c>
       <c r="S7">
-        <v>5.4114081621088774e-07</v>
+        <v>-1.2276981240485897e-07</v>
       </c>
       <c r="T7">
-        <v>5.357136052397941e-07</v>
+        <v>5.2505152846397309e-07</v>
       </c>
       <c r="U7">
-        <v>-6.6007886198071827e-07</v>
+        <v>5.1496108179817472e-07</v>
       </c>
       <c r="V7">
-        <v>-2.2294268233629018e-07</v>
+        <v>-6.5516504121722797e-07</v>
       </c>
       <c r="W7">
-        <v>5.3859539755439353e-05</v>
+        <v>-2.7496197442075613e-07</v>
+      </c>
+      <c r="X7">
+        <v>5.4121772535331095e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6089,70 +6557,73 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>0.17952524860044669</v>
+        <v>0.11612289748458911</v>
       </c>
       <c r="C8">
-        <v>-7.8965533249664074e-06</v>
+        <v>-6.1135437101854472e-06</v>
       </c>
       <c r="D8">
-        <v>1.5068014277023063e-08</v>
+        <v>2.9268242745414059e-08</v>
       </c>
       <c r="E8">
-        <v>1.6549984870608197e-05</v>
+        <v>2.5371374610768961e-05</v>
       </c>
       <c r="F8">
-        <v>2.3534372520484107e-05</v>
+        <v>3.3146869394592279e-05</v>
       </c>
       <c r="G8">
-        <v>-5.2512357571415426e-07</v>
+        <v>-5.6391993540621097e-07</v>
       </c>
       <c r="H8">
-        <v>-8.2461717323305428e-07</v>
+        <v>-7.5908072670335989e-07</v>
       </c>
       <c r="I8">
-        <v>0.00039689609939575073</v>
+        <v>0.00041184536254883263</v>
       </c>
       <c r="J8">
-        <v>-0.00019742129769217796</v>
+        <v>-0.00020099205727683986</v>
       </c>
       <c r="K8">
-        <v>-1.4019610193710646e-05</v>
+        <v>-1.8578434604930183e-05</v>
       </c>
       <c r="L8">
-        <v>-1.3140519018680742e-05</v>
+        <v>-1.783682468435526e-05</v>
       </c>
       <c r="M8">
-        <v>-1.9336077266941346e-05</v>
+        <v>-2.3243848933831379e-05</v>
       </c>
       <c r="N8">
-        <v>-2.0733365363726523e-05</v>
+        <v>-2.484129204660171e-05</v>
       </c>
       <c r="O8">
-        <v>3.5436580866210084e-06</v>
+        <v>-3.5403374688584939e-06</v>
       </c>
       <c r="P8">
-        <v>-6.3062673897952084e-06</v>
+        <v>6.7805721580186897e-06</v>
       </c>
       <c r="Q8">
-        <v>6.4266253342069854e-08</v>
+        <v>-4.6454960509561525e-06</v>
       </c>
       <c r="R8">
-        <v>-3.7232696090030961e-06</v>
+        <v>1.7891089509285772e-06</v>
       </c>
       <c r="S8">
-        <v>-8.250902906451324e-06</v>
+        <v>-8.1717194422822738e-07</v>
       </c>
       <c r="T8">
-        <v>5.7062722753078933e-06</v>
+        <v>-8.2485490359202191e-06</v>
       </c>
       <c r="U8">
-        <v>1.667930938045684e-07</v>
+        <v>5.1042035099523057e-06</v>
       </c>
       <c r="V8">
-        <v>1.2450794712038474e-05</v>
+        <v>3.8974210028826616e-07</v>
       </c>
       <c r="W8">
-        <v>0.00016783263513429428</v>
+        <v>9.5600290807126135e-06</v>
+      </c>
+      <c r="X8">
+        <v>0.00012279351370194915</v>
       </c>
     </row>
     <row r="9">
@@ -6160,70 +6631,73 @@
         <v>31</v>
       </c>
       <c r="B9">
-        <v>0.011141269386880072</v>
+        <v>0.0149047019443592</v>
       </c>
       <c r="C9">
-        <v>-3.3217205403445613e-05</v>
+        <v>-3.3698552340810027e-05</v>
       </c>
       <c r="D9">
-        <v>4.0099550812207758e-07</v>
+        <v>4.0354054516428494e-07</v>
       </c>
       <c r="E9">
-        <v>-7.6911246156981567e-05</v>
+        <v>-7.983041056551713e-05</v>
       </c>
       <c r="F9">
-        <v>-0.00010982638060223331</v>
+        <v>-0.00011427405461822478</v>
       </c>
       <c r="G9">
-        <v>1.807452026875073e-06</v>
+        <v>1.8647984304583498e-06</v>
       </c>
       <c r="H9">
-        <v>2.4958049621340877e-06</v>
+        <v>2.5725252845665725e-06</v>
       </c>
       <c r="I9">
-        <v>-0.00019742129769217796</v>
+        <v>-0.00020099205727683986</v>
       </c>
       <c r="J9">
-        <v>0.00039101346861878289</v>
+        <v>0.00039680114111456471</v>
       </c>
       <c r="K9">
-        <v>-1.7446192468079135e-06</v>
+        <v>-4.4401734242670039e-07</v>
       </c>
       <c r="L9">
-        <v>-7.086421962048642e-06</v>
+        <v>-7.0095863807844913e-06</v>
       </c>
       <c r="M9">
-        <v>-1.3000399484950346e-05</v>
+        <v>-1.3301219127380724e-05</v>
       </c>
       <c r="N9">
-        <v>-1.2195986185794703e-05</v>
+        <v>-1.2176807187709007e-05</v>
       </c>
       <c r="O9">
-        <v>-9.8711444358592342e-06</v>
+        <v>2.2908311599562932e-07</v>
       </c>
       <c r="P9">
-        <v>-4.2932516950534637e-06</v>
+        <v>-1.055899662092402e-05</v>
       </c>
       <c r="Q9">
-        <v>-7.4470725386476121e-06</v>
+        <v>-4.5220882479889691e-06</v>
       </c>
       <c r="R9">
-        <v>-9.2957689913393204e-06</v>
+        <v>-7.5569092760729971e-06</v>
       </c>
       <c r="S9">
-        <v>-1.4179326848369978e-05</v>
+        <v>-9.5051509810079266e-06</v>
       </c>
       <c r="T9">
-        <v>2.2331090593866136e-06</v>
+        <v>-1.4397323509221695e-05</v>
       </c>
       <c r="U9">
-        <v>-6.0341965785401773e-06</v>
+        <v>1.8388522107043201e-06</v>
       </c>
       <c r="V9">
-        <v>-4.3447695952284772e-06</v>
+        <v>-5.599474106808954e-06</v>
       </c>
       <c r="W9">
-        <v>0.00062828002645894045</v>
+        <v>-3.9188401864702773e-06</v>
+      </c>
+      <c r="X9">
+        <v>0.00064042453386075899</v>
       </c>
     </row>
     <row r="10">
@@ -6231,70 +6705,73 @@
         <v>32</v>
       </c>
       <c r="B10">
-        <v>0.18164741490466885</v>
+        <v>0.2042545905887864</v>
       </c>
       <c r="C10">
-        <v>3.8201189270419618e-06</v>
+        <v>3.1307998966519318e-06</v>
       </c>
       <c r="D10">
-        <v>-4.2365052368979701e-08</v>
+        <v>-4.6719037907298532e-08</v>
       </c>
       <c r="E10">
-        <v>1.8594887747565162e-05</v>
+        <v>1.5050183932374716e-05</v>
       </c>
       <c r="F10">
-        <v>1.6641639592278627e-05</v>
+        <v>1.3448546992121408e-05</v>
       </c>
       <c r="G10">
-        <v>-5.610257151061379e-07</v>
+        <v>-5.26780616384529e-07</v>
       </c>
       <c r="H10">
-        <v>-2.804823844159378e-07</v>
+        <v>-3.0907264097319596e-07</v>
       </c>
       <c r="I10">
-        <v>-1.4019610193710646e-05</v>
+        <v>-1.8578434604930183e-05</v>
       </c>
       <c r="J10">
-        <v>-1.7446192468079135e-06</v>
+        <v>-4.4401734242670039e-07</v>
       </c>
       <c r="K10">
-        <v>0.0091321539298681899</v>
+        <v>0.0092186951037441893</v>
       </c>
       <c r="L10">
-        <v>0.00758031571176623</v>
+        <v>0.0076403906362856088</v>
       </c>
       <c r="M10">
-        <v>0.0075784221761371201</v>
+        <v>0.0076381919769748898</v>
       </c>
       <c r="N10">
-        <v>0.007576305581060626</v>
+        <v>0.007636169813847034</v>
       </c>
       <c r="O10">
-        <v>1.2421228453616872e-05</v>
+        <v>1.2481928972486983e-06</v>
       </c>
       <c r="P10">
-        <v>9.2529956072158774e-06</v>
+        <v>1.239671973773032e-05</v>
       </c>
       <c r="Q10">
-        <v>-1.7708136540186208e-05</v>
+        <v>5.7302287926933829e-06</v>
       </c>
       <c r="R10">
-        <v>-8.3200992319852065e-06</v>
+        <v>-2.028932963346074e-05</v>
       </c>
       <c r="S10">
-        <v>3.4636756817547866e-06</v>
+        <v>-1.1799902542452585e-05</v>
       </c>
       <c r="T10">
-        <v>1.491369661422263e-05</v>
+        <v>3.0818011606993797e-06</v>
       </c>
       <c r="U10">
-        <v>7.3133474030168382e-07</v>
+        <v>1.3568085277106356e-05</v>
       </c>
       <c r="V10">
-        <v>-7.2531352844108895e-06</v>
+        <v>2.0764773014529035e-07</v>
       </c>
       <c r="W10">
-        <v>-0.0076467330770613991</v>
+        <v>-5.1756086716378538e-06</v>
+      </c>
+      <c r="X10">
+        <v>-0.0076875039904136548</v>
       </c>
     </row>
     <row r="11">
@@ -6302,70 +6779,73 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>0.66157334877777085</v>
+        <v>0.68842331315682737</v>
       </c>
       <c r="C11">
-        <v>4.1563256104613694e-06</v>
+        <v>3.1761806143800039e-06</v>
       </c>
       <c r="D11">
-        <v>-4.195761738377673e-08</v>
+        <v>-4.8674358127368984e-08</v>
       </c>
       <c r="E11">
-        <v>2.5256702000577653e-05</v>
+        <v>2.1452726595416142e-05</v>
       </c>
       <c r="F11">
-        <v>-1.7576749405986535e-06</v>
+        <v>-6.4375243549750008e-06</v>
       </c>
       <c r="G11">
-        <v>-6.8888894900172109e-07</v>
+        <v>-6.7144642183569349e-07</v>
       </c>
       <c r="H11">
-        <v>2.5176871281655064e-07</v>
+        <v>2.1181571420212945e-07</v>
       </c>
       <c r="I11">
-        <v>-1.3140519018680742e-05</v>
+        <v>-1.783682468435526e-05</v>
       </c>
       <c r="J11">
-        <v>-7.086421962048642e-06</v>
+        <v>-7.0095863807844913e-06</v>
       </c>
       <c r="K11">
-        <v>0.00758031571176623</v>
+        <v>0.0076403906362856088</v>
       </c>
       <c r="L11">
-        <v>0.00788210296748822</v>
+        <v>0.0079487166374433999</v>
       </c>
       <c r="M11">
-        <v>0.0075844446249812066</v>
+        <v>0.0076447658055607669</v>
       </c>
       <c r="N11">
-        <v>0.0075868582307381822</v>
+        <v>0.0076473067528071634</v>
       </c>
       <c r="O11">
-        <v>1.1085000429976861e-05</v>
+        <v>1.81018046302545e-06</v>
       </c>
       <c r="P11">
-        <v>3.5105525446026543e-07</v>
+        <v>1.060612379584681e-05</v>
       </c>
       <c r="Q11">
-        <v>-3.0195715737612005e-05</v>
+        <v>-2.533568059526946e-06</v>
       </c>
       <c r="R11">
-        <v>-1.4715440560455058e-05</v>
+        <v>-3.2513711919898242e-05</v>
       </c>
       <c r="S11">
-        <v>-6.0205819075949993e-06</v>
+        <v>-1.7933626921282227e-05</v>
       </c>
       <c r="T11">
-        <v>4.4946440056452134e-07</v>
+        <v>-6.211110326416648e-06</v>
       </c>
       <c r="U11">
-        <v>1.7034134946836298e-06</v>
+        <v>-7.3669711331242988e-08</v>
       </c>
       <c r="V11">
-        <v>-8.1473352704591869e-06</v>
+        <v>9.5134290550966967e-07</v>
       </c>
       <c r="W11">
-        <v>-0.007663895437148782</v>
+        <v>-5.69753190111703e-06</v>
+      </c>
+      <c r="X11">
+        <v>-0.0076981569175421311</v>
       </c>
     </row>
     <row r="12">
@@ -6373,70 +6853,73 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0.8726881507313855</v>
+        <v>0.88985132794174293</v>
       </c>
       <c r="C12">
-        <v>5.428423587112085e-06</v>
+        <v>4.8535961069677992e-06</v>
       </c>
       <c r="D12">
-        <v>-3.8362252831692966e-08</v>
+        <v>-4.4411982544474474e-08</v>
       </c>
       <c r="E12">
-        <v>1.7312353319764518e-05</v>
+        <v>1.4009842321260424e-05</v>
       </c>
       <c r="F12">
-        <v>-1.6906245438257951e-05</v>
+        <v>-2.0011563104284456e-05</v>
       </c>
       <c r="G12">
-        <v>-2.3530083083896913e-07</v>
+        <v>-1.892610328936453e-07</v>
       </c>
       <c r="H12">
-        <v>1.1183227139817159e-06</v>
+        <v>1.1008501551402014e-06</v>
       </c>
       <c r="I12">
-        <v>-1.9336077266941346e-05</v>
+        <v>-2.3243848933831379e-05</v>
       </c>
       <c r="J12">
-        <v>-1.3000399484950346e-05</v>
+        <v>-1.3301219127380724e-05</v>
       </c>
       <c r="K12">
-        <v>0.0075784221761371201</v>
+        <v>0.0076381919769748898</v>
       </c>
       <c r="L12">
-        <v>0.0075844446249812066</v>
+        <v>0.0076447658055607669</v>
       </c>
       <c r="M12">
-        <v>0.0076845395875990326</v>
+        <v>0.0077463860920138376</v>
       </c>
       <c r="N12">
-        <v>0.0076189897261084057</v>
+        <v>0.0076798977974858809</v>
       </c>
       <c r="O12">
-        <v>9.1360213707919382e-06</v>
+        <v>1.3150343552501004e-06</v>
       </c>
       <c r="P12">
-        <v>-5.4254068739799388e-06</v>
+        <v>9.1490736439156354e-06</v>
       </c>
       <c r="Q12">
-        <v>-3.6055582464771435e-05</v>
+        <v>-8.1876997777332043e-06</v>
       </c>
       <c r="R12">
-        <v>-1.4073670842270405e-05</v>
+        <v>-3.8571045034523169e-05</v>
       </c>
       <c r="S12">
-        <v>-9.5464824860947036e-06</v>
+        <v>-1.666079758833787e-05</v>
       </c>
       <c r="T12">
-        <v>1.8321113575335866e-05</v>
+        <v>-9.9267095047759482e-06</v>
       </c>
       <c r="U12">
-        <v>-2.4277793420343909e-06</v>
+        <v>1.7164411692962043e-05</v>
       </c>
       <c r="V12">
-        <v>-5.9753852560077972e-06</v>
+        <v>-3.458881433916144e-06</v>
       </c>
       <c r="W12">
-        <v>-0.0077535733879639298</v>
+        <v>-4.2684905043261993e-06</v>
+      </c>
+      <c r="X12">
+        <v>-0.0077984543585157516</v>
       </c>
     </row>
     <row r="13">
@@ -6444,70 +6927,73 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>0.92818931514050085</v>
+        <v>0.94424828223584989</v>
       </c>
       <c r="C13">
-        <v>1.4927718324272082e-05</v>
+        <v>1.4547170666140625e-05</v>
       </c>
       <c r="D13">
-        <v>-1.1081216818507283e-07</v>
+        <v>-1.1821271655358617e-07</v>
       </c>
       <c r="E13">
-        <v>3.4169145854522813e-05</v>
+        <v>3.1519949870845859e-05</v>
       </c>
       <c r="F13">
-        <v>3.1769177679788485e-05</v>
+        <v>2.9416041601911577e-05</v>
       </c>
       <c r="G13">
-        <v>-4.3244651287649999e-07</v>
+        <v>-3.8311041961155057e-07</v>
       </c>
       <c r="H13">
-        <v>4.5813655212707986e-07</v>
+        <v>4.395918365954519e-07</v>
       </c>
       <c r="I13">
-        <v>-2.0733365363726523e-05</v>
+        <v>-2.484129204660171e-05</v>
       </c>
       <c r="J13">
-        <v>-1.2195986185794703e-05</v>
+        <v>-1.2176807187709007e-05</v>
       </c>
       <c r="K13">
-        <v>0.007576305581060626</v>
+        <v>0.007636169813847034</v>
       </c>
       <c r="L13">
-        <v>0.0075868582307381822</v>
+        <v>0.0076473067528071634</v>
       </c>
       <c r="M13">
-        <v>0.0076189897261084057</v>
+        <v>0.0076798977974858809</v>
       </c>
       <c r="N13">
-        <v>0.0079500572457554576</v>
+        <v>0.0080159249490932283</v>
       </c>
       <c r="O13">
-        <v>-4.090095516640004e-07</v>
+        <v>1.2782072574094619e-06</v>
       </c>
       <c r="P13">
-        <v>-1.6549812709951427e-05</v>
+        <v>-8.3271280029191671e-07</v>
       </c>
       <c r="Q13">
-        <v>-4.2011316991313706e-05</v>
+        <v>-1.9409001473582747e-05</v>
       </c>
       <c r="R13">
-        <v>-3.5294802414292487e-05</v>
+        <v>-4.4754915133767361e-05</v>
       </c>
       <c r="S13">
-        <v>-2.9122395137945201e-05</v>
+        <v>-3.818498986969603e-05</v>
       </c>
       <c r="T13">
-        <v>-1.8017249153346609e-06</v>
+        <v>-2.9748099327511914e-05</v>
       </c>
       <c r="U13">
-        <v>-9.9841911143385114e-06</v>
+        <v>-2.9793098809607216e-06</v>
       </c>
       <c r="V13">
-        <v>-1.2043613251549614e-05</v>
+        <v>-1.1038358189740907e-05</v>
       </c>
       <c r="W13">
-        <v>-0.0080403468402342401</v>
+        <v>-1.0823135923286659e-05</v>
+      </c>
+      <c r="X13">
+        <v>-0.0080907800031771067</v>
       </c>
     </row>
     <row r="14">
@@ -6515,70 +7001,73 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>0.068998076444433107</v>
+        <v>0.032196419356795472</v>
       </c>
       <c r="C14">
-        <v>1.4887441034216219e-06</v>
+        <v>-1.0601821740640126e-06</v>
       </c>
       <c r="D14">
-        <v>-1.1111336493412349e-08</v>
+        <v>-5.6540585542554466e-09</v>
       </c>
       <c r="E14">
-        <v>4.5850450757501972e-05</v>
+        <v>-3.7474247265342233e-06</v>
       </c>
       <c r="F14">
-        <v>5.2600385190004992e-05</v>
+        <v>-4.3051586548841169e-06</v>
       </c>
       <c r="G14">
-        <v>-9.0399812006259743e-07</v>
+        <v>4.4936900405905211e-09</v>
       </c>
       <c r="H14">
-        <v>-8.1067390634716506e-07</v>
+        <v>-4.2829192514480309e-08</v>
       </c>
       <c r="I14">
-        <v>3.5436580866210084e-06</v>
+        <v>-3.5403374688584939e-06</v>
       </c>
       <c r="J14">
-        <v>-9.8711444358592342e-06</v>
+        <v>2.2908311599562932e-07</v>
       </c>
       <c r="K14">
-        <v>1.2421228453616872e-05</v>
+        <v>1.2481928972486983e-06</v>
       </c>
       <c r="L14">
-        <v>1.1085000429976861e-05</v>
+        <v>1.81018046302545e-06</v>
       </c>
       <c r="M14">
-        <v>9.1360213707919382e-06</v>
+        <v>1.3150343552501004e-06</v>
       </c>
       <c r="N14">
-        <v>-4.090095516640004e-07</v>
+        <v>1.2782072574094619e-06</v>
       </c>
       <c r="O14">
-        <v>0.00077009147491231692</v>
+        <v>1.7567152931154692e-06</v>
       </c>
       <c r="P14">
-        <v>0.00041716814642973839</v>
+        <v>-1.5907984353518056e-06</v>
       </c>
       <c r="Q14">
-        <v>0.00041383367747480039</v>
+        <v>-1.2325149350897839e-06</v>
       </c>
       <c r="R14">
-        <v>0.0004162682087066788</v>
+        <v>-1.1365322641028694e-06</v>
       </c>
       <c r="S14">
-        <v>0.00041440486610124134</v>
+        <v>-1.6383583637494718e-06</v>
       </c>
       <c r="T14">
-        <v>0.00041476956488913845</v>
+        <v>2.0821850361982903e-07</v>
       </c>
       <c r="U14">
-        <v>6.6022638563916448e-06</v>
+        <v>4.3469011888009401e-07</v>
       </c>
       <c r="V14">
-        <v>4.5790182839544131e-06</v>
+        <v>-2.7027280709442942e-07</v>
       </c>
       <c r="W14">
-        <v>-0.00047355690283225961</v>
+        <v>1.9400827500487567e-06</v>
+      </c>
+      <c r="X14">
+        <v>2.5749635814570678e-05</v>
       </c>
     </row>
     <row r="15">
@@ -6586,70 +7075,73 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>0.025969852097722155</v>
+        <v>0.038866409861163839</v>
       </c>
       <c r="C15">
-        <v>2.03229226350316e-06</v>
+        <v>2.5212991322689632e-06</v>
       </c>
       <c r="D15">
-        <v>-1.9224342983125847e-08</v>
+        <v>-6.3232184559323251e-09</v>
       </c>
       <c r="E15">
-        <v>2.2205987656579847e-05</v>
+        <v>5.0393339931903613e-05</v>
       </c>
       <c r="F15">
-        <v>3.2622738381269241e-05</v>
+        <v>5.7884949724156648e-05</v>
       </c>
       <c r="G15">
-        <v>-2.2536731230999098e-07</v>
+        <v>-9.238541681639709e-07</v>
       </c>
       <c r="H15">
-        <v>-6.502496964190471e-08</v>
+        <v>-7.9928630442462957e-07</v>
       </c>
       <c r="I15">
-        <v>-6.3062673897952084e-06</v>
+        <v>6.7805721580186897e-06</v>
       </c>
       <c r="J15">
-        <v>-4.2932516950534637e-06</v>
+        <v>-1.055899662092402e-05</v>
       </c>
       <c r="K15">
-        <v>9.2529956072158774e-06</v>
+        <v>1.239671973773032e-05</v>
       </c>
       <c r="L15">
-        <v>3.5105525446026543e-07</v>
+        <v>1.060612379584681e-05</v>
       </c>
       <c r="M15">
-        <v>-5.4254068739799388e-06</v>
+        <v>9.1490736439156354e-06</v>
       </c>
       <c r="N15">
-        <v>-1.6549812709951427e-05</v>
+        <v>-8.3271280029191671e-07</v>
       </c>
       <c r="O15">
-        <v>0.00041716814642973839</v>
+        <v>-1.5907984353518056e-06</v>
       </c>
       <c r="P15">
-        <v>0.00093609830986330809</v>
+        <v>0.00078276105430458934</v>
       </c>
       <c r="Q15">
-        <v>0.00041280913728009461</v>
+        <v>0.00042474823491208107</v>
       </c>
       <c r="R15">
-        <v>0.00041668703233415565</v>
+        <v>0.00042134407407342202</v>
       </c>
       <c r="S15">
-        <v>0.00041419995165539362</v>
+        <v>0.00042418267844771348</v>
       </c>
       <c r="T15">
-        <v>0.00041466491513443587</v>
+        <v>0.0004207294367466329</v>
       </c>
       <c r="U15">
-        <v>-1.7432117282338792e-06</v>
+        <v>0.00042081170373698876</v>
       </c>
       <c r="V15">
-        <v>-1.2584826548470499e-05</v>
+        <v>6.6453602558542034e-06</v>
       </c>
       <c r="W15">
-        <v>-0.00046895674276341081</v>
+        <v>2.7989340227289095e-06</v>
+      </c>
+      <c r="X15">
+        <v>-0.00050698698938114132</v>
       </c>
     </row>
     <row r="16">
@@ -6657,70 +7149,73 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>-0.070976755656184512</v>
+        <v>0.0021843904961852045</v>
       </c>
       <c r="C16">
-        <v>1.8156373648022923e-06</v>
+        <v>2.9277803947183983e-06</v>
       </c>
       <c r="D16">
-        <v>-1.5591255410859481e-08</v>
+        <v>-1.6289870595530218e-08</v>
       </c>
       <c r="E16">
-        <v>2.9608143243960488e-05</v>
+        <v>2.585748535985696e-05</v>
       </c>
       <c r="F16">
-        <v>-1.070565831753603e-05</v>
+        <v>3.6984453170407447e-05</v>
       </c>
       <c r="G16">
-        <v>-7.5139241710276621e-07</v>
+        <v>-2.4613997489067761e-07</v>
       </c>
       <c r="H16">
-        <v>-3.376908544652675e-07</v>
+        <v>-6.8978836658499704e-08</v>
       </c>
       <c r="I16">
-        <v>6.4266253342069854e-08</v>
+        <v>-4.6454960509561525e-06</v>
       </c>
       <c r="J16">
-        <v>-7.4470725386476121e-06</v>
+        <v>-4.5220882479889691e-06</v>
       </c>
       <c r="K16">
-        <v>-1.7708136540186208e-05</v>
+        <v>5.7302287926933829e-06</v>
       </c>
       <c r="L16">
-        <v>-3.0195715737612005e-05</v>
+        <v>-2.533568059526946e-06</v>
       </c>
       <c r="M16">
-        <v>-3.6055582464771435e-05</v>
+        <v>-8.1876997777332043e-06</v>
       </c>
       <c r="N16">
-        <v>-4.2011316991313706e-05</v>
+        <v>-1.9409001473582747e-05</v>
       </c>
       <c r="O16">
-        <v>0.00041383367747480039</v>
+        <v>-1.2325149350897839e-06</v>
       </c>
       <c r="P16">
-        <v>0.00041280913728009461</v>
+        <v>0.00042474823491208107</v>
       </c>
       <c r="Q16">
-        <v>0.000717316889988816</v>
+        <v>0.00095096879676460065</v>
       </c>
       <c r="R16">
-        <v>0.00041540001576074548</v>
+        <v>0.00042018500664739293</v>
       </c>
       <c r="S16">
-        <v>0.00041838212714494108</v>
+        <v>0.00042418069261664808</v>
       </c>
       <c r="T16">
-        <v>0.00041517518376969157</v>
+        <v>0.00042055477265931409</v>
       </c>
       <c r="U16">
-        <v>-4.6605262847580832e-06</v>
+        <v>0.00042068933980881458</v>
       </c>
       <c r="V16">
-        <v>-5.5274118045836598e-06</v>
+        <v>-1.8613833245922236e-06</v>
       </c>
       <c r="W16">
-        <v>-0.00041331565857763642</v>
+        <v>-1.4725930460058909e-05</v>
+      </c>
+      <c r="X16">
+        <v>-0.00049552115527861241</v>
       </c>
     </row>
     <row r="17">
@@ -6728,70 +7223,73 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>0.026368401286869105</v>
+        <v>-0.091462118694026026</v>
       </c>
       <c r="C17">
-        <v>3.0239619789284084e-06</v>
+        <v>2.5708226695140533e-06</v>
       </c>
       <c r="D17">
-        <v>-2.8460373058014049e-08</v>
+        <v>-1.2447768351795096e-08</v>
       </c>
       <c r="E17">
-        <v>3.3770902387213425e-05</v>
+        <v>3.3209817615330942e-05</v>
       </c>
       <c r="F17">
-        <v>9.2690361454529931e-06</v>
+        <v>-8.2963687293079272e-06</v>
       </c>
       <c r="G17">
-        <v>-7.7944983956979658e-07</v>
+        <v>-7.7264199007269203e-07</v>
       </c>
       <c r="H17">
-        <v>-1.4331432780875421e-07</v>
+        <v>-3.0358753615579227e-07</v>
       </c>
       <c r="I17">
-        <v>-3.7232696090030961e-06</v>
+        <v>1.7891089509285772e-06</v>
       </c>
       <c r="J17">
-        <v>-9.2957689913393204e-06</v>
+        <v>-7.5569092760729971e-06</v>
       </c>
       <c r="K17">
-        <v>-8.3200992319852065e-06</v>
+        <v>-2.028932963346074e-05</v>
       </c>
       <c r="L17">
-        <v>-1.4715440560455058e-05</v>
+        <v>-3.2513711919898242e-05</v>
       </c>
       <c r="M17">
-        <v>-1.4073670842270405e-05</v>
+        <v>-3.8571045034523169e-05</v>
       </c>
       <c r="N17">
-        <v>-3.5294802414292487e-05</v>
+        <v>-4.4754915133767361e-05</v>
       </c>
       <c r="O17">
-        <v>0.0004162682087066788</v>
+        <v>-1.1365322641028694e-06</v>
       </c>
       <c r="P17">
-        <v>0.00041668703233415565</v>
+        <v>0.00042134407407342202</v>
       </c>
       <c r="Q17">
-        <v>0.00041540001576074548</v>
+        <v>0.00042018500664739293</v>
       </c>
       <c r="R17">
-        <v>0.00063472436437972597</v>
+        <v>0.00072946270462546611</v>
       </c>
       <c r="S17">
-        <v>0.00041704670728968349</v>
+        <v>0.00042307058806762319</v>
       </c>
       <c r="T17">
-        <v>0.000416182851340523</v>
+        <v>0.00042482382037139935</v>
       </c>
       <c r="U17">
-        <v>1.5230567760312229e-05</v>
+        <v>0.00042142109910764381</v>
       </c>
       <c r="V17">
-        <v>1.0101795022944654e-05</v>
+        <v>-5.2136846385675308e-06</v>
       </c>
       <c r="W17">
-        <v>-0.00046995617542857596</v>
+        <v>-6.9251453071111808e-06</v>
+      </c>
+      <c r="X17">
+        <v>-0.00043660090022548122</v>
       </c>
     </row>
     <row r="18">
@@ -6799,70 +7297,73 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>-0.12950859782892746</v>
+        <v>-0.0046482790764338453</v>
       </c>
       <c r="C18">
-        <v>1.8997586306835277e-06</v>
+        <v>4.1040298432993168e-06</v>
       </c>
       <c r="D18">
-        <v>-1.7667353608075601e-08</v>
+        <v>-2.3521204232151073e-08</v>
       </c>
       <c r="E18">
-        <v>2.8341807186208341e-06</v>
+        <v>3.7488734382354297e-05</v>
       </c>
       <c r="F18">
-        <v>-4.8950482656448721e-05</v>
+        <v>1.2869893110453501e-05</v>
       </c>
       <c r="G18">
-        <v>-1.8987809407692353e-07</v>
+        <v>-7.9947434440482916e-07</v>
       </c>
       <c r="H18">
-        <v>5.4114081621088774e-07</v>
+        <v>-1.2276981240485897e-07</v>
       </c>
       <c r="I18">
-        <v>-8.250902906451324e-06</v>
+        <v>-8.1717194422822738e-07</v>
       </c>
       <c r="J18">
-        <v>-1.4179326848369978e-05</v>
+        <v>-9.5051509810079266e-06</v>
       </c>
       <c r="K18">
-        <v>3.4636756817547866e-06</v>
+        <v>-1.1799902542452585e-05</v>
       </c>
       <c r="L18">
-        <v>-6.0205819075949993e-06</v>
+        <v>-1.7933626921282227e-05</v>
       </c>
       <c r="M18">
-        <v>-9.5464824860947036e-06</v>
+        <v>-1.666079758833787e-05</v>
       </c>
       <c r="N18">
-        <v>-2.9122395137945201e-05</v>
+        <v>-3.818498986969603e-05</v>
       </c>
       <c r="O18">
-        <v>0.00041440486610124134</v>
+        <v>-1.6383583637494718e-06</v>
       </c>
       <c r="P18">
-        <v>0.00041419995165539362</v>
+        <v>0.00042418267844771348</v>
       </c>
       <c r="Q18">
-        <v>0.00041838212714494108</v>
+        <v>0.00042418069261664808</v>
       </c>
       <c r="R18">
-        <v>0.00041704670728968349</v>
+        <v>0.00042307058806762319</v>
       </c>
       <c r="S18">
-        <v>0.00068776826643983857</v>
+        <v>0.00064703370860677578</v>
       </c>
       <c r="T18">
-        <v>0.00041645822058770173</v>
+        <v>0.00042349619227651799</v>
       </c>
       <c r="U18">
-        <v>4.1308021335949055e-07</v>
+        <v>0.00042231295713313386</v>
       </c>
       <c r="V18">
-        <v>-1.6897011452332796e-06</v>
+        <v>1.590360335907399e-05</v>
       </c>
       <c r="W18">
-        <v>-0.00043075975717233185</v>
+        <v>9.4275548392100357e-06</v>
+      </c>
+      <c r="X18">
+        <v>-0.00050156320161313505</v>
       </c>
     </row>
     <row r="19">
@@ -6870,70 +7371,73 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>-0.14572879973353967</v>
+        <v>-0.12553541898019088</v>
       </c>
       <c r="C19">
-        <v>-4.8436909280624247e-07</v>
+        <v>1.7654201243843757e-06</v>
       </c>
       <c r="D19">
-        <v>6.6560095154321312e-09</v>
+        <v>-1.7771499173437399e-08</v>
       </c>
       <c r="E19">
-        <v>-2.0422293928908707e-05</v>
+        <v>3.9979604830924566e-06</v>
       </c>
       <c r="F19">
-        <v>-3.0773233842658323e-05</v>
+        <v>-4.97772626877715e-05</v>
       </c>
       <c r="G19">
-        <v>3.4386245143992356e-07</v>
+        <v>-2.302490913074499e-07</v>
       </c>
       <c r="H19">
-        <v>5.357136052397941e-07</v>
+        <v>5.2505152846397309e-07</v>
       </c>
       <c r="I19">
-        <v>5.7062722753078933e-06</v>
+        <v>-8.2485490359202191e-06</v>
       </c>
       <c r="J19">
-        <v>2.2331090593866136e-06</v>
+        <v>-1.4397323509221695e-05</v>
       </c>
       <c r="K19">
-        <v>1.491369661422263e-05</v>
+        <v>3.0818011606993797e-06</v>
       </c>
       <c r="L19">
-        <v>4.4946440056452134e-07</v>
+        <v>-6.211110326416648e-06</v>
       </c>
       <c r="M19">
-        <v>1.8321113575335866e-05</v>
+        <v>-9.9267095047759482e-06</v>
       </c>
       <c r="N19">
-        <v>-1.8017249153346609e-06</v>
+        <v>-2.9748099327511914e-05</v>
       </c>
       <c r="O19">
-        <v>0.00041476956488913845</v>
+        <v>2.0821850361982903e-07</v>
       </c>
       <c r="P19">
-        <v>0.00041466491513443587</v>
+        <v>0.0004207294367466329</v>
       </c>
       <c r="Q19">
-        <v>0.00041517518376969157</v>
+        <v>0.00042055477265931409</v>
       </c>
       <c r="R19">
-        <v>0.000416182851340523</v>
+        <v>0.00042482382037139935</v>
       </c>
       <c r="S19">
-        <v>0.00041645822058770173</v>
+        <v>0.00042349619227651799</v>
       </c>
       <c r="T19">
-        <v>0.0017970159288647417</v>
+        <v>0.00069934212285242272</v>
       </c>
       <c r="U19">
-        <v>1.103328140871752e-05</v>
+        <v>0.00042311513326021255</v>
       </c>
       <c r="V19">
-        <v>4.7210220195765013e-06</v>
+        <v>6.283951357532029e-07</v>
       </c>
       <c r="W19">
-        <v>-0.00042175353088571996</v>
+        <v>-1.4671849786805885e-06</v>
+      </c>
+      <c r="X19">
+        <v>-0.00043440805149392854</v>
       </c>
     </row>
     <row r="20">
@@ -6941,70 +7445,73 @@
         <v>42</v>
       </c>
       <c r="B20">
-        <v>-0.067141051890866291</v>
+        <v>-0.13860195463822969</v>
       </c>
       <c r="C20">
-        <v>1.3015700873776471e-06</v>
+        <v>-6.9598869265954627e-07</v>
       </c>
       <c r="D20">
-        <v>-1.3691669125166148e-08</v>
+        <v>4.7458599336776544e-09</v>
       </c>
       <c r="E20">
-        <v>1.1432320977549063e-05</v>
+        <v>-2.2278152181945843e-05</v>
       </c>
       <c r="F20">
-        <v>3.3713068571135743e-05</v>
+        <v>-3.2443761640259041e-05</v>
       </c>
       <c r="G20">
-        <v>-2.7005505003890763e-07</v>
+        <v>3.5712546343391346e-07</v>
       </c>
       <c r="H20">
-        <v>-6.6007886198071827e-07</v>
+        <v>5.1496108179817472e-07</v>
       </c>
       <c r="I20">
-        <v>1.667930938045684e-07</v>
+        <v>5.1042035099523057e-06</v>
       </c>
       <c r="J20">
-        <v>-6.0341965785401773e-06</v>
+        <v>1.8388522107043201e-06</v>
       </c>
       <c r="K20">
-        <v>7.3133474030168382e-07</v>
+        <v>1.3568085277106356e-05</v>
       </c>
       <c r="L20">
-        <v>1.7034134946836298e-06</v>
+        <v>-7.3669711331242988e-08</v>
       </c>
       <c r="M20">
-        <v>-2.4277793420343909e-06</v>
+        <v>1.7164411692962043e-05</v>
       </c>
       <c r="N20">
-        <v>-9.9841911143385114e-06</v>
+        <v>-2.9793098809607216e-06</v>
       </c>
       <c r="O20">
-        <v>6.6022638563916448e-06</v>
+        <v>4.3469011888009401e-07</v>
       </c>
       <c r="P20">
-        <v>-1.7432117282338792e-06</v>
+        <v>0.00042081170373698876</v>
       </c>
       <c r="Q20">
-        <v>-4.6605262847580832e-06</v>
+        <v>0.00042068933980881458</v>
       </c>
       <c r="R20">
-        <v>1.5230567760312229e-05</v>
+        <v>0.00042142109910764381</v>
       </c>
       <c r="S20">
-        <v>4.1308021335949055e-07</v>
+        <v>0.00042231295713313386</v>
       </c>
       <c r="T20">
-        <v>1.103328140871752e-05</v>
+        <v>0.00042311513326021255</v>
       </c>
       <c r="U20">
-        <v>0.00089284862034612344</v>
+        <v>0.0018236194260051141</v>
       </c>
       <c r="V20">
-        <v>5.8568750274647503e-05</v>
+        <v>1.1392216731668779e-05</v>
       </c>
       <c r="W20">
-        <v>-8.6326860105429533e-05</v>
+        <v>6.2376091831457136e-06</v>
+      </c>
+      <c r="X20">
+        <v>-0.00042120178974491438</v>
       </c>
     </row>
     <row r="21">
@@ -7012,70 +7519,73 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>0.10802277472818979</v>
+        <v>-0.070372769749389344</v>
       </c>
       <c r="C21">
-        <v>-2.9098187938785718e-06</v>
+        <v>1.4750777456203317e-06</v>
       </c>
       <c r="D21">
-        <v>2.5378159441799093e-08</v>
+        <v>-1.2792534026133469e-08</v>
       </c>
       <c r="E21">
-        <v>1.8320606347170743e-05</v>
+        <v>1.1537406637497247e-05</v>
       </c>
       <c r="F21">
-        <v>1.8525096321798343e-05</v>
+        <v>3.4063932884740325e-05</v>
       </c>
       <c r="G21">
-        <v>-3.0177493836406789e-07</v>
+        <v>-2.680109354773859e-07</v>
       </c>
       <c r="H21">
-        <v>-2.2294268233629018e-07</v>
+        <v>-6.5516504121722797e-07</v>
       </c>
       <c r="I21">
-        <v>1.2450794712038474e-05</v>
+        <v>3.8974210028826616e-07</v>
       </c>
       <c r="J21">
-        <v>-4.3447695952284772e-06</v>
+        <v>-5.599474106808954e-06</v>
       </c>
       <c r="K21">
-        <v>-7.2531352844108895e-06</v>
+        <v>2.0764773014529035e-07</v>
       </c>
       <c r="L21">
-        <v>-8.1473352704591869e-06</v>
+        <v>9.5134290550966967e-07</v>
       </c>
       <c r="M21">
-        <v>-5.9753852560077972e-06</v>
+        <v>-3.458881433916144e-06</v>
       </c>
       <c r="N21">
-        <v>-1.2043613251549614e-05</v>
+        <v>-1.1038358189740907e-05</v>
       </c>
       <c r="O21">
-        <v>4.5790182839544131e-06</v>
+        <v>-2.7027280709442942e-07</v>
       </c>
       <c r="P21">
-        <v>-1.2584826548470499e-05</v>
+        <v>6.6453602558542034e-06</v>
       </c>
       <c r="Q21">
-        <v>-5.5274118045836598e-06</v>
+        <v>-1.8613833245922236e-06</v>
       </c>
       <c r="R21">
-        <v>1.0101795022944654e-05</v>
+        <v>-5.2136846385675308e-06</v>
       </c>
       <c r="S21">
-        <v>-1.6897011452332796e-06</v>
+        <v>1.590360335907399e-05</v>
       </c>
       <c r="T21">
-        <v>4.7210220195765013e-06</v>
+        <v>6.283951357532029e-07</v>
       </c>
       <c r="U21">
-        <v>5.8568750274647503e-05</v>
+        <v>1.1392216731668779e-05</v>
       </c>
       <c r="V21">
-        <v>0.0011272281330778893</v>
+        <v>0.00091038294353172654</v>
       </c>
       <c r="W21">
-        <v>1.437497765263601e-05</v>
+        <v>5.9268259315905936e-05</v>
+      </c>
+      <c r="X21">
+        <v>-9.0676239495711305e-05</v>
       </c>
     </row>
     <row r="22">
@@ -7083,70 +7593,147 @@
         <v>44</v>
       </c>
       <c r="B22">
-        <v>-2.9911167933604648</v>
+        <v>0.14015406186661447</v>
       </c>
       <c r="C22">
-        <v>-0.00051792998311778128</v>
+        <v>-4.2284302571463537e-06</v>
       </c>
       <c r="D22">
-        <v>5.1289228655816393e-06</v>
+        <v>2.0378803995301816e-08</v>
       </c>
       <c r="E22">
-        <v>-0.0031633818660566052</v>
+        <v>1.5238091444653381e-05</v>
       </c>
       <c r="F22">
-        <v>-0.0027218393645978807</v>
+        <v>1.3104743402725966e-05</v>
       </c>
       <c r="G22">
-        <v>6.4616123727413073e-05</v>
+        <v>-3.3728226015020431e-07</v>
       </c>
       <c r="H22">
-        <v>5.3859539755439353e-05</v>
+        <v>-2.7496197442075613e-07</v>
       </c>
       <c r="I22">
-        <v>0.00016783263513429428</v>
+        <v>9.5600290807126135e-06</v>
       </c>
       <c r="J22">
-        <v>0.00062828002645894045</v>
+        <v>-3.9188401864702773e-06</v>
       </c>
       <c r="K22">
-        <v>-0.0076467330770613991</v>
+        <v>-5.1756086716378538e-06</v>
       </c>
       <c r="L22">
-        <v>-0.007663895437148782</v>
+        <v>-5.69753190111703e-06</v>
       </c>
       <c r="M22">
-        <v>-0.0077535733879639298</v>
+        <v>-4.2684905043261993e-06</v>
       </c>
       <c r="N22">
-        <v>-0.0080403468402342401</v>
+        <v>-1.0823135923286659e-05</v>
       </c>
       <c r="O22">
-        <v>-0.00047355690283225961</v>
+        <v>1.9400827500487567e-06</v>
       </c>
       <c r="P22">
-        <v>-0.00046895674276341081</v>
+        <v>2.7989340227289095e-06</v>
       </c>
       <c r="Q22">
-        <v>-0.00041331565857763642</v>
+        <v>-1.4725930460058909e-05</v>
       </c>
       <c r="R22">
-        <v>-0.00046995617542857596</v>
+        <v>-6.9251453071111808e-06</v>
       </c>
       <c r="S22">
-        <v>-0.00043075975717233185</v>
+        <v>9.4275548392100357e-06</v>
       </c>
       <c r="T22">
-        <v>-0.00042175353088571996</v>
+        <v>-1.4671849786805885e-06</v>
       </c>
       <c r="U22">
-        <v>-8.6326860105429533e-05</v>
+        <v>6.2376091831457136e-06</v>
       </c>
       <c r="V22">
-        <v>1.437497765263601e-05</v>
+        <v>5.9268259315905936e-05</v>
       </c>
       <c r="W22">
-        <v>0.020184952179908927</v>
+        <v>0.001154925962350056</v>
+      </c>
+      <c r="X22">
+        <v>4.5238984509744287e-05</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23">
+        <v>-2.4754007281135761</v>
+      </c>
+      <c r="C23">
+        <v>-0.00054057944944402108</v>
+      </c>
+      <c r="D23">
+        <v>5.1140111431976424e-06</v>
+      </c>
+      <c r="E23">
+        <v>-0.003256949224582978</v>
+      </c>
+      <c r="F23">
+        <v>-0.0028312914769374506</v>
+      </c>
+      <c r="G23">
+        <v>6.5385808151112082e-05</v>
+      </c>
+      <c r="H23">
+        <v>5.4121772535331095e-05</v>
+      </c>
+      <c r="I23">
+        <v>0.00012279351370194915</v>
+      </c>
+      <c r="J23">
+        <v>0.00064042453386075899</v>
+      </c>
+      <c r="K23">
+        <v>-0.0076875039904136548</v>
+      </c>
+      <c r="L23">
+        <v>-0.0076981569175421311</v>
+      </c>
+      <c r="M23">
+        <v>-0.0077984543585157516</v>
+      </c>
+      <c r="N23">
+        <v>-0.0080907800031771067</v>
+      </c>
+      <c r="O23">
+        <v>2.5749635814570678e-05</v>
+      </c>
+      <c r="P23">
+        <v>-0.00050698698938114132</v>
+      </c>
+      <c r="Q23">
+        <v>-0.00049552115527861241</v>
+      </c>
+      <c r="R23">
+        <v>-0.00043660090022548122</v>
+      </c>
+      <c r="S23">
+        <v>-0.00050156320161313505</v>
+      </c>
+      <c r="T23">
+        <v>-0.00043440805149392854</v>
+      </c>
+      <c r="U23">
+        <v>-0.00042120178974491438</v>
+      </c>
+      <c r="V23">
+        <v>-9.0676239495711305e-05</v>
+      </c>
+      <c r="W23">
+        <v>4.5238984509744287e-05</v>
+      </c>
+      <c r="X23">
+        <v>0.020797365453993279</v>
       </c>
     </row>
   </sheetData>
